--- a/IndicatorsForClusters.xlsx
+++ b/IndicatorsForClusters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1c3256d208fb6548/Personlig/Aske Banke Consultancy/YALE/Metodeartikel_WorldDevelopmentJournal/WorldDevelopmentArticleGit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="128" documentId="8_{9856C943-DD01-465B-AD17-0E409E296684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C2B9F03-2D73-470D-901F-32ED3B6D81C9}"/>
+  <xr:revisionPtr revIDLastSave="285" documentId="8_{9856C943-DD01-465B-AD17-0E409E296684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23EDE1B2-84D2-4188-A152-77CD044CA0DF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{726B2859-724A-4801-8E74-5A4E1AFAB973}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{726B2859-724A-4801-8E74-5A4E1AFAB973}"/>
   </bookViews>
   <sheets>
     <sheet name="Experiment Descriptions" sheetId="2" r:id="rId1"/>
@@ -55,7 +55,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="8">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -70,25 +70,85 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="8">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
+    <bk>
+      <rc t="2" v="5"/>
+    </bk>
+    <bk>
+      <rc t="2" v="6"/>
+    </bk>
+    <bk>
+      <rc t="2" v="7"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="71">
   <si>
     <t>SPI</t>
   </si>
@@ -260,28 +320,49 @@
     <t>Physical connectedness (mobility) is not well represented globally through time</t>
   </si>
   <si>
-    <t>Only 3 PCs used, we may be able to include a larger portion of the variation</t>
-  </si>
-  <si>
-    <t>Only 2 PCs used, we may be able to include a larger portion of the variation</t>
-  </si>
-  <si>
     <t>Batch</t>
   </si>
   <si>
-    <t>Few_indicators_closest_DLS_coverage_95</t>
-  </si>
-  <si>
-    <t>Few indicators_SPI_preferred_95</t>
-  </si>
-  <si>
-    <t>Similar to previous test with the same name, but this time the PCA should include 95% of the information</t>
-  </si>
-  <si>
     <t>Batch2</t>
   </si>
   <si>
     <t>Batch1</t>
+  </si>
+  <si>
+    <t>Results</t>
+  </si>
+  <si>
+    <t>Few indicators_SPI_preferred_90</t>
+  </si>
+  <si>
+    <t>Few_indicators_closest_DLS_coverage_90</t>
+  </si>
+  <si>
+    <t>Similar to previous test with the same name, but this time the PCA should include 90% of the information</t>
+  </si>
+  <si>
+    <t>Few_indicators_closeDLS_subPrimSchool</t>
+  </si>
+  <si>
+    <t>No_non_DLS_90</t>
+  </si>
+  <si>
+    <t>Primary school enrollment (Ext) is substituted by mean years of schooling (SPI) to reduce the missingness going into the clusters</t>
+  </si>
+  <si>
+    <t>Few_Indicators_subWatSani</t>
+  </si>
+  <si>
+    <t>Imputations for  safely manged drinking water and sanitation (Ext), have a lot of uncertainty, in our countries of interest. This clustering substituses them, with the less strict indicators from SPI</t>
+  </si>
+  <si>
+    <t>% missing values in selected extended indicators</t>
+  </si>
+  <si>
+    <t>Only_OPP</t>
+  </si>
+  <si>
+    <t>OPP reflects the quality of the institutions in a country, the resulting clusters should align with the colonial data.</t>
   </si>
 </sst>
 </file>
@@ -392,15 +473,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -426,11 +498,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -452,23 +533,40 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -479,28 +577,12 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -746,13 +828,37 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="8">
   <rv s="0">
     <v>0</v>
     <v>5</v>
   </rv>
   <rv s="0">
     <v>1</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>2</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>3</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>4</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>5</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>6</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>7</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -771,6 +877,12 @@
 <richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <rel r:id="rId1"/>
   <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
+  <rel r:id="rId6"/>
+  <rel r:id="rId7"/>
+  <rel r:id="rId8"/>
 </richValueRels>
 </file>
 
@@ -1094,50 +1206,50 @@
   <sheetPr>
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AQ35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AY53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.33203125" customWidth="1"/>
+    <col min="2" max="2" width="35.28515625" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
-    <col min="5" max="16" width="4.33203125" customWidth="1"/>
-    <col min="19" max="19" width="8.88671875" customWidth="1"/>
+    <col min="5" max="16" width="4.28515625" customWidth="1"/>
+    <col min="19" max="19" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="J3" s="26"/>
+      <c r="C3" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="29"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
-      <c r="R3" s="25" t="s">
+      <c r="R3" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-    </row>
-    <row r="4" spans="1:22" ht="221.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S3" s="34"/>
+      <c r="T3" s="34"/>
+      <c r="U3" s="34"/>
+      <c r="V3" s="34"/>
+    </row>
+    <row r="4" spans="1:22" ht="221.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="15" t="s">
         <v>16</v>
       </c>
@@ -1161,22 +1273,22 @@
         <v>Only_%_of_pop</v>
       </c>
       <c r="I4" s="9" t="str">
-        <v>Few_indicators_closest_DLS_coverage_95</v>
+        <v>Few_indicators_closest_DLS_coverage_90</v>
       </c>
       <c r="J4" s="9" t="str">
-        <v>Few indicators_SPI_preferred_95</v>
-      </c>
-      <c r="K4" s="9">
-        <v>0</v>
-      </c>
-      <c r="L4" s="9">
-        <v>0</v>
-      </c>
-      <c r="M4" s="9">
-        <v>0</v>
-      </c>
-      <c r="N4" s="9">
-        <v>0</v>
+        <v>Few indicators_SPI_preferred_90</v>
+      </c>
+      <c r="K4" s="9" t="str">
+        <v>Few_indicators_closeDLS_subPrimSchool</v>
+      </c>
+      <c r="L4" s="9" t="str">
+        <v>No_non_DLS_90</v>
+      </c>
+      <c r="M4" s="9" t="str">
+        <v>Few_Indicators_subWatSani</v>
+      </c>
+      <c r="N4" s="9" t="str">
+        <v>Only_OPP</v>
       </c>
       <c r="O4" s="9">
         <v>0</v>
@@ -1184,15 +1296,15 @@
       <c r="P4">
         <v>0</v>
       </c>
-      <c r="R4" s="23" t="s">
+      <c r="R4" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="S4" s="24"/>
-      <c r="T4" s="24"/>
-      <c r="U4" s="24"/>
-      <c r="V4" s="24"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="S4" s="33"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="33"/>
+      <c r="V4" s="33"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="str" cm="1">
         <f t="array" ref="B5:B15">_xlfn.UNIQUE('Overview of indicators and DLS'!C4:C67)</f>
         <v>Food &amp; Nutrition</v>
@@ -1217,35 +1329,35 @@
         <f t="array" ref="G5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!G$2:G$64=1))</f>
         <v>5</v>
       </c>
-      <c r="H5" s="32" cm="1">
+      <c r="H5" s="8" cm="1">
         <f t="array" ref="H5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!H$2:H$64=1))</f>
         <v>2</v>
       </c>
-      <c r="I5" s="33" cm="1">
+      <c r="I5" s="18" cm="1">
         <f t="array" ref="I5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!I$2:I$64=1))</f>
         <v>1</v>
       </c>
-      <c r="J5" s="32" cm="1">
+      <c r="J5" s="8" cm="1">
         <f t="array" ref="J5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!J$2:J$64=1))</f>
         <v>1</v>
       </c>
-      <c r="K5" s="32" cm="1">
+      <c r="K5" s="8" cm="1">
         <f t="array" ref="K5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!K$2:K$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="L5" s="32" cm="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="8" cm="1">
         <f t="array" ref="L5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!L$2:L$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="M5" s="32" cm="1">
+        <v>5</v>
+      </c>
+      <c r="M5" s="8" cm="1">
         <f t="array" ref="M5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!M$2:M$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="N5" s="32" cm="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="8" cm="1">
         <f t="array" ref="N5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!N$2:N$64=1))</f>
         <v>0</v>
       </c>
-      <c r="O5" s="32" cm="1">
+      <c r="O5" s="8" cm="1">
         <f t="array" ref="O5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!O$2:O$64=1))</f>
         <v>0</v>
       </c>
@@ -1253,7 +1365,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="str">
         <v>Health Care</v>
       </c>
@@ -1277,40 +1389,40 @@
         <f t="array" ref="G6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!G$2:G$64=1))</f>
         <v>10</v>
       </c>
-      <c r="H6" s="32" cm="1">
+      <c r="H6" s="8" cm="1">
         <f t="array" ref="H6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!H$2:H$64=1))</f>
         <v>1</v>
       </c>
-      <c r="I6" s="33" cm="1">
+      <c r="I6" s="18" cm="1">
         <f t="array" ref="I6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!I$2:I$64=1))</f>
         <v>1</v>
       </c>
-      <c r="J6" s="32" cm="1">
+      <c r="J6" s="8" cm="1">
         <f t="array" ref="J6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!J$2:J$64=1))</f>
         <v>1</v>
       </c>
-      <c r="K6" s="32" cm="1">
+      <c r="K6" s="8" cm="1">
         <f t="array" ref="K6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!K$2:K$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="32" cm="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="8" cm="1">
         <f t="array" ref="L6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!L$2:L$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="32" cm="1">
+        <v>10</v>
+      </c>
+      <c r="M6" s="8" cm="1">
         <f t="array" ref="M6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!M$2:M$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="32" cm="1">
+        <v>1</v>
+      </c>
+      <c r="N6" s="8" cm="1">
         <f t="array" ref="N6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!N$2:N$64=1))</f>
         <v>0</v>
       </c>
-      <c r="O6" s="32" cm="1">
+      <c r="O6" s="8" cm="1">
         <f t="array" ref="O6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!O$2:O$64=1))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="str">
         <v>Water</v>
       </c>
@@ -1334,40 +1446,40 @@
         <f t="array" ref="G7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!G$2:G$64=1))</f>
         <v>4</v>
       </c>
-      <c r="H7" s="32" cm="1">
+      <c r="H7" s="8" cm="1">
         <f t="array" ref="H7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!H$2:H$64=1))</f>
         <v>1</v>
       </c>
-      <c r="I7" s="33" cm="1">
+      <c r="I7" s="18" cm="1">
         <f t="array" ref="I7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!I$2:I$64=1))</f>
         <v>2</v>
       </c>
-      <c r="J7" s="32" cm="1">
+      <c r="J7" s="8" cm="1">
         <f t="array" ref="J7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!J$2:J$64=1))</f>
         <v>2</v>
       </c>
-      <c r="K7" s="32" cm="1">
+      <c r="K7" s="8" cm="1">
         <f t="array" ref="K7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!K$2:K$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="32" cm="1">
+        <v>2</v>
+      </c>
+      <c r="L7" s="8" cm="1">
         <f t="array" ref="L7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!L$2:L$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="32" cm="1">
+        <v>4</v>
+      </c>
+      <c r="M7" s="8" cm="1">
         <f t="array" ref="M7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!M$2:M$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="32" cm="1">
+        <v>2</v>
+      </c>
+      <c r="N7" s="8" cm="1">
         <f t="array" ref="N7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!N$2:N$64=1))</f>
         <v>0</v>
       </c>
-      <c r="O7" s="32" cm="1">
+      <c r="O7" s="8" cm="1">
         <f t="array" ref="O7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!O$2:O$64=1))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="str">
         <v>Sanitation</v>
       </c>
@@ -1391,40 +1503,40 @@
         <f t="array" ref="G8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!G$2:G$64=1))</f>
         <v>2</v>
       </c>
-      <c r="H8" s="32" cm="1">
+      <c r="H8" s="8" cm="1">
         <f t="array" ref="H8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!H$2:H$64=1))</f>
         <v>1</v>
       </c>
-      <c r="I8" s="33" cm="1">
+      <c r="I8" s="18" cm="1">
         <f t="array" ref="I8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!I$2:I$64=1))</f>
         <v>1</v>
       </c>
-      <c r="J8" s="32" cm="1">
+      <c r="J8" s="8" cm="1">
         <f t="array" ref="J8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!J$2:J$64=1))</f>
         <v>1</v>
       </c>
-      <c r="K8" s="32" cm="1">
+      <c r="K8" s="8" cm="1">
         <f t="array" ref="K8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!K$2:K$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="32" cm="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="8" cm="1">
         <f t="array" ref="L8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!L$2:L$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="32" cm="1">
+        <v>2</v>
+      </c>
+      <c r="M8" s="8" cm="1">
         <f t="array" ref="M8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!M$2:M$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="N8" s="32" cm="1">
+        <v>1</v>
+      </c>
+      <c r="N8" s="8" cm="1">
         <f t="array" ref="N8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!N$2:N$64=1))</f>
         <v>0</v>
       </c>
-      <c r="O8" s="32" cm="1">
+      <c r="O8" s="8" cm="1">
         <f t="array" ref="O8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!O$2:O$64=1))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="str">
         <v>Food preparation</v>
       </c>
@@ -1448,40 +1560,40 @@
         <f t="array" ref="G9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!G$2:G$64=1))</f>
         <v>3</v>
       </c>
-      <c r="H9" s="32" cm="1">
+      <c r="H9" s="8" cm="1">
         <f t="array" ref="H9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!H$2:H$64=1))</f>
         <v>1</v>
       </c>
-      <c r="I9" s="33" cm="1">
+      <c r="I9" s="18" cm="1">
         <f t="array" ref="I9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!I$2:I$64=1))</f>
         <v>1</v>
       </c>
-      <c r="J9" s="32" cm="1">
+      <c r="J9" s="8" cm="1">
         <f t="array" ref="J9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!J$2:J$64=1))</f>
         <v>1</v>
       </c>
-      <c r="K9" s="32" cm="1">
+      <c r="K9" s="8" cm="1">
         <f t="array" ref="K9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!K$2:K$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="32" cm="1">
+        <v>1</v>
+      </c>
+      <c r="L9" s="8" cm="1">
         <f t="array" ref="L9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!L$2:L$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="32" cm="1">
+        <v>3</v>
+      </c>
+      <c r="M9" s="8" cm="1">
         <f t="array" ref="M9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!M$2:M$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="32" cm="1">
+        <v>1</v>
+      </c>
+      <c r="N9" s="8" cm="1">
         <f t="array" ref="N9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!N$2:N$64=1))</f>
         <v>0</v>
       </c>
-      <c r="O9" s="32" cm="1">
+      <c r="O9" s="8" cm="1">
         <f t="array" ref="O9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!O$2:O$64=1))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="str">
         <v>Thermal comfort</v>
       </c>
@@ -1505,40 +1617,40 @@
         <f t="array" ref="G10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!G$2:G$64=1))</f>
         <v>1</v>
       </c>
-      <c r="H10" s="32" cm="1">
+      <c r="H10" s="8" cm="1">
         <f t="array" ref="H10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!H$2:H$64=1))</f>
         <v>1</v>
       </c>
-      <c r="I10" s="33" cm="1">
+      <c r="I10" s="18" cm="1">
         <f t="array" ref="I10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!I$2:I$64=1))</f>
         <v>1</v>
       </c>
-      <c r="J10" s="32" cm="1">
+      <c r="J10" s="8" cm="1">
         <f t="array" ref="J10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!J$2:J$64=1))</f>
         <v>1</v>
       </c>
-      <c r="K10" s="32" cm="1">
+      <c r="K10" s="8" cm="1">
         <f t="array" ref="K10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!K$2:K$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="32" cm="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="8" cm="1">
         <f t="array" ref="L10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!L$2:L$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="32" cm="1">
+        <v>1</v>
+      </c>
+      <c r="M10" s="8" cm="1">
         <f t="array" ref="M10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!M$2:M$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="N10" s="32" cm="1">
+        <v>1</v>
+      </c>
+      <c r="N10" s="8" cm="1">
         <f t="array" ref="N10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!N$2:N$64=1))</f>
         <v>0</v>
       </c>
-      <c r="O10" s="32" cm="1">
+      <c r="O10" s="8" cm="1">
         <f t="array" ref="O10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!O$2:O$64=1))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="str">
         <v>Non material / Non-DLS</v>
       </c>
@@ -1562,40 +1674,40 @@
         <f t="array" ref="G11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!G$2:G$64=1))</f>
         <v>0</v>
       </c>
-      <c r="H11" s="32" cm="1">
+      <c r="H11" s="8" cm="1">
         <f t="array" ref="H11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!H$2:H$64=1))</f>
         <v>2</v>
       </c>
-      <c r="I11" s="33" cm="1">
+      <c r="I11" s="18" cm="1">
         <f t="array" ref="I11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!I$2:I$64=1))</f>
         <v>0</v>
       </c>
-      <c r="J11" s="32" cm="1">
+      <c r="J11" s="8" cm="1">
         <f t="array" ref="J11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!J$2:J$64=1))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="32" cm="1">
+      <c r="K11" s="8" cm="1">
         <f t="array" ref="K11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!K$2:K$64=1))</f>
         <v>0</v>
       </c>
-      <c r="L11" s="32" cm="1">
+      <c r="L11" s="8" cm="1">
         <f t="array" ref="L11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!L$2:L$64=1))</f>
         <v>0</v>
       </c>
-      <c r="M11" s="32" cm="1">
+      <c r="M11" s="8" cm="1">
         <f t="array" ref="M11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!M$2:M$64=1))</f>
         <v>0</v>
       </c>
-      <c r="N11" s="32" cm="1">
+      <c r="N11" s="8" cm="1">
         <f t="array" ref="N11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!N$2:N$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="O11" s="32" cm="1">
+        <v>15</v>
+      </c>
+      <c r="O11" s="8" cm="1">
         <f t="array" ref="O11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!O$2:O$64=1))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="str">
         <v>Education</v>
       </c>
@@ -1619,40 +1731,40 @@
         <f t="array" ref="G12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!G$2:G$64=1))</f>
         <v>9</v>
       </c>
-      <c r="H12" s="32" cm="1">
+      <c r="H12" s="8" cm="1">
         <f t="array" ref="H12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!H$2:H$64=1))</f>
         <v>3</v>
       </c>
-      <c r="I12" s="33" cm="1">
+      <c r="I12" s="18" cm="1">
         <f t="array" ref="I12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!I$2:I$64=1))</f>
         <v>1</v>
       </c>
-      <c r="J12" s="32" cm="1">
+      <c r="J12" s="8" cm="1">
         <f t="array" ref="J12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!J$2:J$64=1))</f>
         <v>1</v>
       </c>
-      <c r="K12" s="32" cm="1">
+      <c r="K12" s="8" cm="1">
         <f t="array" ref="K12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!K$2:K$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="32" cm="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="8" cm="1">
         <f t="array" ref="L12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!L$2:L$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="32" cm="1">
+        <v>9</v>
+      </c>
+      <c r="M12" s="8" cm="1">
         <f t="array" ref="M12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!M$2:M$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="N12" s="32" cm="1">
+        <v>1</v>
+      </c>
+      <c r="N12" s="8" cm="1">
         <f t="array" ref="N12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!N$2:N$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="O12" s="32" cm="1">
+        <v>4</v>
+      </c>
+      <c r="O12" s="8" cm="1">
         <f t="array" ref="O12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!O$2:O$64=1))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="str">
         <v>Social connectedness</v>
       </c>
@@ -1676,40 +1788,40 @@
         <f t="array" ref="G13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!G$2:G$64=1))</f>
         <v>3</v>
       </c>
-      <c r="H13" s="32" cm="1">
+      <c r="H13" s="8" cm="1">
         <f t="array" ref="H13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!H$2:H$64=1))</f>
         <v>2</v>
       </c>
-      <c r="I13" s="33" cm="1">
+      <c r="I13" s="18" cm="1">
         <f t="array" ref="I13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!I$2:I$64=1))</f>
         <v>2</v>
       </c>
-      <c r="J13" s="32" cm="1">
+      <c r="J13" s="8" cm="1">
         <f t="array" ref="J13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!J$2:J$64=1))</f>
         <v>2</v>
       </c>
-      <c r="K13" s="32" cm="1">
+      <c r="K13" s="8" cm="1">
         <f t="array" ref="K13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!K$2:K$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="32" cm="1">
+        <v>2</v>
+      </c>
+      <c r="L13" s="8" cm="1">
         <f t="array" ref="L13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!L$2:L$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="32" cm="1">
+        <v>3</v>
+      </c>
+      <c r="M13" s="8" cm="1">
         <f t="array" ref="M13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!M$2:M$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="32" cm="1">
+        <v>2</v>
+      </c>
+      <c r="N13" s="8" cm="1">
         <f t="array" ref="N13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!N$2:N$64=1))</f>
         <v>0</v>
       </c>
-      <c r="O13" s="32" cm="1">
+      <c r="O13" s="8" cm="1">
         <f t="array" ref="O13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!O$2:O$64=1))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="str">
         <v>Housing</v>
       </c>
@@ -1733,40 +1845,40 @@
         <f t="array" ref="G14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!G$2:G$64=1))</f>
         <v>1</v>
       </c>
-      <c r="H14" s="32" cm="1">
+      <c r="H14" s="8" cm="1">
         <f t="array" ref="H14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!H$2:H$64=1))</f>
         <v>1</v>
       </c>
-      <c r="I14" s="33" cm="1">
+      <c r="I14" s="18" cm="1">
         <f t="array" ref="I14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!I$2:I$64=1))</f>
         <v>1</v>
       </c>
-      <c r="J14" s="32" cm="1">
+      <c r="J14" s="8" cm="1">
         <f t="array" ref="J14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!J$2:J$64=1))</f>
         <v>1</v>
       </c>
-      <c r="K14" s="32" cm="1">
+      <c r="K14" s="8" cm="1">
         <f t="array" ref="K14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!K$2:K$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="32" cm="1">
+        <v>1</v>
+      </c>
+      <c r="L14" s="8" cm="1">
         <f t="array" ref="L14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!L$2:L$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="32" cm="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="8" cm="1">
         <f t="array" ref="M14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!M$2:M$64=1))</f>
-        <v>0</v>
-      </c>
-      <c r="N14" s="32" cm="1">
+        <v>1</v>
+      </c>
+      <c r="N14" s="8" cm="1">
         <f t="array" ref="N14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!N$2:N$64=1))</f>
         <v>0</v>
       </c>
-      <c r="O14" s="32" cm="1">
+      <c r="O14" s="8" cm="1">
         <f t="array" ref="O14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!O$2:O$64=1))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B15" s="13" t="str">
         <v>Physical Connectedness</v>
       </c>
@@ -1794,7 +1906,7 @@
         <f t="array" ref="H15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!H$2:H$64=1))</f>
         <v>0</v>
       </c>
-      <c r="I15" s="34" cm="1">
+      <c r="I15" s="19" cm="1">
         <f t="array" ref="I15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!I$2:I$64=1))</f>
         <v>0</v>
       </c>
@@ -1826,7 +1938,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B16" s="11"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
@@ -1842,7 +1954,7 @@
       <c r="N16" s="8"/>
       <c r="O16" s="8"/>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>33</v>
       </c>
@@ -1855,7 +1967,7 @@
         <v>44</v>
       </c>
       <c r="E17" s="14">
-        <f t="shared" ref="E17:O17" si="0">SUM(E5:E15)</f>
+        <f t="shared" ref="E17:H17" si="0">SUM(E5:E15)</f>
         <v>11</v>
       </c>
       <c r="F17" s="14">
@@ -1866,40 +1978,40 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="H17" s="36">
+      <c r="H17" s="14">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="I17" s="37">
+      <c r="I17" s="20">
         <f t="shared" ref="I17:O17" si="1">SUM(I5:I15)</f>
         <v>11</v>
       </c>
-      <c r="J17" s="36">
+      <c r="J17" s="14">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="K17" s="36">
+      <c r="K17" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L17" s="36">
+        <v>11</v>
+      </c>
+      <c r="L17" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="36">
+        <v>38</v>
+      </c>
+      <c r="M17" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N17" s="36">
+        <v>11</v>
+      </c>
+      <c r="N17" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O17" s="36">
+        <v>19</v>
+      </c>
+      <c r="O17" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
         <v>34</v>
       </c>
@@ -1923,40 +2035,40 @@
         <f>SUM(Experiments!G2:G53)</f>
         <v>28</v>
       </c>
-      <c r="H18" s="32">
+      <c r="H18" s="8">
         <f>SUM(Experiments!H2:H53)</f>
         <v>11</v>
       </c>
-      <c r="I18" s="33">
+      <c r="I18" s="18">
         <f>SUM(Experiments!I2:I53)</f>
         <v>7</v>
       </c>
-      <c r="J18" s="32">
+      <c r="J18" s="8">
         <f>SUM(Experiments!J2:J53)</f>
         <v>10</v>
       </c>
-      <c r="K18" s="32">
+      <c r="K18" s="8">
         <f>SUM(Experiments!K2:K53)</f>
-        <v>0</v>
-      </c>
-      <c r="L18" s="32">
+        <v>8</v>
+      </c>
+      <c r="L18" s="8">
         <f>SUM(Experiments!L2:L53)</f>
-        <v>0</v>
-      </c>
-      <c r="M18" s="32">
+        <v>28</v>
+      </c>
+      <c r="M18" s="8">
         <f>SUM(Experiments!M2:M53)</f>
-        <v>0</v>
-      </c>
-      <c r="N18" s="32">
+        <v>9</v>
+      </c>
+      <c r="N18" s="8">
         <f>SUM(Experiments!N2:N53)</f>
-        <v>0</v>
-      </c>
-      <c r="O18" s="32">
+        <v>19</v>
+      </c>
+      <c r="O18" s="8">
         <f>SUM(Experiments!O2:O53)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B19" s="11" t="s">
         <v>35</v>
       </c>
@@ -1980,65 +2092,71 @@
         <f>SUM(Experiments!G54:G64)</f>
         <v>10</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="8">
         <f>SUM(Experiments!H54:H64)</f>
         <v>4</v>
       </c>
-      <c r="I19" s="33">
+      <c r="I19" s="18">
         <f>SUM(Experiments!I54:I64)</f>
         <v>4</v>
       </c>
-      <c r="J19" s="32">
+      <c r="J19" s="8">
         <f>SUM(Experiments!J54:J64)</f>
         <v>1</v>
       </c>
-      <c r="K19" s="32">
+      <c r="K19" s="8">
         <f>SUM(Experiments!K54:K64)</f>
-        <v>0</v>
-      </c>
-      <c r="L19" s="32">
+        <v>3</v>
+      </c>
+      <c r="L19" s="8">
         <f>SUM(Experiments!L54:L64)</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="32">
+        <v>10</v>
+      </c>
+      <c r="M19" s="8">
         <f>SUM(Experiments!M54:M64)</f>
-        <v>0</v>
-      </c>
-      <c r="N19" s="32">
+        <v>2</v>
+      </c>
+      <c r="N19" s="8">
         <f>SUM(Experiments!N54:N64)</f>
         <v>0</v>
       </c>
-      <c r="O19" s="32">
+      <c r="O19" s="8">
         <f>SUM(Experiments!O54:O64)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22" t="s">
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="22"/>
-      <c r="N21" s="22"/>
-      <c r="O21" s="22"/>
-    </row>
-    <row r="22" spans="1:43" ht="90.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
+      <c r="Q21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AR21" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:51" ht="90.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1</v>
       </c>
@@ -2046,463 +2164,1066 @@
         <f t="array" ref="B22:B35">TRANSPOSE(_xlfn.ANCHORARRAY(C4))</f>
         <v>BHN_FWB</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
-      <c r="O22" s="21"/>
-      <c r="Q22" s="28" t="e" vm="1">
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="27"/>
+      <c r="Q22" s="22" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="R22" s="28"/>
-      <c r="S22" s="28"/>
-      <c r="T22" s="28"/>
-      <c r="U22" s="28"/>
-      <c r="V22" s="28"/>
-      <c r="W22" s="28"/>
-      <c r="X22" s="28"/>
-      <c r="Y22" s="28"/>
-      <c r="Z22" s="28"/>
-      <c r="AA22" s="28"/>
-      <c r="AB22" s="28" t="e" vm="2">
+      <c r="R22" s="22"/>
+      <c r="S22" s="22"/>
+      <c r="T22" s="22"/>
+      <c r="U22" s="22"/>
+      <c r="V22" s="22"/>
+      <c r="W22" s="22"/>
+      <c r="X22" s="22"/>
+      <c r="Y22" s="22"/>
+      <c r="Z22" s="22"/>
+      <c r="AA22" s="22"/>
+      <c r="AB22" s="22" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="AC22" s="28"/>
-      <c r="AD22" s="28"/>
-      <c r="AE22" s="28"/>
-      <c r="AF22" s="28"/>
-      <c r="AG22" s="28"/>
-      <c r="AH22" s="28"/>
-      <c r="AI22" s="28"/>
-      <c r="AJ22" s="28"/>
-      <c r="AK22" s="28"/>
-      <c r="AL22" s="28"/>
-      <c r="AM22" s="28"/>
-      <c r="AN22" s="28"/>
-      <c r="AO22" s="28"/>
-      <c r="AP22" s="28"/>
-      <c r="AQ22" s="28"/>
-    </row>
-    <row r="23" spans="1:43" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AC22" s="22"/>
+      <c r="AD22" s="22"/>
+      <c r="AE22" s="22"/>
+      <c r="AF22" s="22"/>
+      <c r="AG22" s="22"/>
+      <c r="AH22" s="22"/>
+      <c r="AI22" s="22"/>
+      <c r="AJ22" s="22"/>
+      <c r="AK22" s="22"/>
+      <c r="AL22" s="22"/>
+      <c r="AM22" s="22"/>
+      <c r="AN22" s="22"/>
+      <c r="AO22" s="22"/>
+      <c r="AP22" s="22"/>
+      <c r="AQ22" s="22"/>
+      <c r="AR22" s="22" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AS22" s="22"/>
+      <c r="AT22" s="22"/>
+      <c r="AU22" s="22"/>
+      <c r="AV22" s="22"/>
+      <c r="AW22" s="22"/>
+      <c r="AX22" s="22"/>
+      <c r="AY22" s="22"/>
+    </row>
+    <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23" s="7" t="str">
         <v>BHN_FWB_AllExt</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="21"/>
-      <c r="N23" s="21"/>
-      <c r="O23" s="21"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="28"/>
-      <c r="U23" s="28"/>
-      <c r="V23" s="28"/>
-      <c r="W23" s="28"/>
-      <c r="X23" s="28"/>
-      <c r="Y23" s="28"/>
-      <c r="Z23" s="28"/>
-      <c r="AA23" s="28"/>
-      <c r="AB23" s="28"/>
-      <c r="AC23" s="28"/>
-      <c r="AD23" s="28"/>
-      <c r="AE23" s="28"/>
-      <c r="AF23" s="28"/>
-      <c r="AG23" s="28"/>
-      <c r="AH23" s="28"/>
-      <c r="AI23" s="28"/>
-      <c r="AJ23" s="28"/>
-      <c r="AK23" s="28"/>
-      <c r="AL23" s="28"/>
-      <c r="AM23" s="28"/>
-      <c r="AN23" s="28"/>
-      <c r="AO23" s="28"/>
-      <c r="AP23" s="28"/>
-      <c r="AQ23" s="28"/>
-    </row>
-    <row r="24" spans="1:43" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
+      <c r="Q23" s="22"/>
+      <c r="R23" s="22"/>
+      <c r="S23" s="22"/>
+      <c r="T23" s="22"/>
+      <c r="U23" s="22"/>
+      <c r="V23" s="22"/>
+      <c r="W23" s="22"/>
+      <c r="X23" s="22"/>
+      <c r="Y23" s="22"/>
+      <c r="Z23" s="22"/>
+      <c r="AA23" s="22"/>
+      <c r="AB23" s="22"/>
+      <c r="AC23" s="22"/>
+      <c r="AD23" s="22"/>
+      <c r="AE23" s="22"/>
+      <c r="AF23" s="22"/>
+      <c r="AG23" s="22"/>
+      <c r="AH23" s="22"/>
+      <c r="AI23" s="22"/>
+      <c r="AJ23" s="22"/>
+      <c r="AK23" s="22"/>
+      <c r="AL23" s="22"/>
+      <c r="AM23" s="22"/>
+      <c r="AN23" s="22"/>
+      <c r="AO23" s="22"/>
+      <c r="AP23" s="22"/>
+      <c r="AQ23" s="22"/>
+      <c r="AR23" s="22"/>
+      <c r="AS23" s="22"/>
+      <c r="AT23" s="22"/>
+      <c r="AU23" s="22"/>
+      <c r="AV23" s="22"/>
+      <c r="AW23" s="22"/>
+      <c r="AX23" s="22"/>
+      <c r="AY23" s="22"/>
+    </row>
+    <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24" s="7" t="str">
         <v>Few_indicators_closest_DLS_coverage</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
-      <c r="N24" s="21"/>
-      <c r="O24" s="21"/>
-      <c r="Q24" s="28"/>
-      <c r="R24" s="28"/>
-      <c r="S24" s="28"/>
-      <c r="T24" s="28"/>
-      <c r="U24" s="28"/>
-      <c r="V24" s="28"/>
-      <c r="W24" s="28"/>
-      <c r="X24" s="28"/>
-      <c r="Y24" s="28"/>
-      <c r="Z24" s="28"/>
-      <c r="AA24" s="28"/>
-      <c r="AB24" s="28"/>
-      <c r="AC24" s="28"/>
-      <c r="AD24" s="28"/>
-      <c r="AE24" s="28"/>
-      <c r="AF24" s="28"/>
-      <c r="AG24" s="28"/>
-      <c r="AH24" s="28"/>
-      <c r="AI24" s="28"/>
-      <c r="AJ24" s="28"/>
-      <c r="AK24" s="28"/>
-      <c r="AL24" s="28"/>
-      <c r="AM24" s="28"/>
-      <c r="AN24" s="28"/>
-      <c r="AO24" s="28"/>
-      <c r="AP24" s="28"/>
-      <c r="AQ24" s="28"/>
-    </row>
-    <row r="25" spans="1:43" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="27"/>
+      <c r="Q24" s="22"/>
+      <c r="R24" s="22"/>
+      <c r="S24" s="22"/>
+      <c r="T24" s="22"/>
+      <c r="U24" s="22"/>
+      <c r="V24" s="22"/>
+      <c r="W24" s="22"/>
+      <c r="X24" s="22"/>
+      <c r="Y24" s="22"/>
+      <c r="Z24" s="22"/>
+      <c r="AA24" s="22"/>
+      <c r="AB24" s="22"/>
+      <c r="AC24" s="22"/>
+      <c r="AD24" s="22"/>
+      <c r="AE24" s="22"/>
+      <c r="AF24" s="22"/>
+      <c r="AG24" s="22"/>
+      <c r="AH24" s="22"/>
+      <c r="AI24" s="22"/>
+      <c r="AJ24" s="22"/>
+      <c r="AK24" s="22"/>
+      <c r="AL24" s="22"/>
+      <c r="AM24" s="22"/>
+      <c r="AN24" s="22"/>
+      <c r="AO24" s="22"/>
+      <c r="AP24" s="22"/>
+      <c r="AQ24" s="22"/>
+      <c r="AR24" s="22"/>
+      <c r="AS24" s="22"/>
+      <c r="AT24" s="22"/>
+      <c r="AU24" s="22"/>
+      <c r="AV24" s="22"/>
+      <c r="AW24" s="22"/>
+      <c r="AX24" s="22"/>
+      <c r="AY24" s="22"/>
+    </row>
+    <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25" s="7" t="str">
         <v>Few indicators_SPI_preferred</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="J25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
-      <c r="O25" s="21"/>
-      <c r="Q25" s="28"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="28"/>
-      <c r="U25" s="28"/>
-      <c r="V25" s="28"/>
-      <c r="W25" s="28"/>
-      <c r="X25" s="28"/>
-      <c r="Y25" s="28"/>
-      <c r="Z25" s="28"/>
-      <c r="AA25" s="28"/>
-      <c r="AB25" s="28"/>
-      <c r="AC25" s="28"/>
-      <c r="AD25" s="28"/>
-      <c r="AE25" s="28"/>
-      <c r="AF25" s="28"/>
-      <c r="AG25" s="28"/>
-      <c r="AH25" s="28"/>
-      <c r="AI25" s="28"/>
-      <c r="AJ25" s="28"/>
-      <c r="AK25" s="28"/>
-      <c r="AL25" s="28"/>
-      <c r="AM25" s="28"/>
-      <c r="AN25" s="28"/>
-      <c r="AO25" s="28"/>
-      <c r="AP25" s="28"/>
-      <c r="AQ25" s="28"/>
-    </row>
-    <row r="26" spans="1:43" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="27"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="27"/>
+      <c r="O25" s="27"/>
+      <c r="Q25" s="22"/>
+      <c r="R25" s="22"/>
+      <c r="S25" s="22"/>
+      <c r="T25" s="22"/>
+      <c r="U25" s="22"/>
+      <c r="V25" s="22"/>
+      <c r="W25" s="22"/>
+      <c r="X25" s="22"/>
+      <c r="Y25" s="22"/>
+      <c r="Z25" s="22"/>
+      <c r="AA25" s="22"/>
+      <c r="AB25" s="22"/>
+      <c r="AC25" s="22"/>
+      <c r="AD25" s="22"/>
+      <c r="AE25" s="22"/>
+      <c r="AF25" s="22"/>
+      <c r="AG25" s="22"/>
+      <c r="AH25" s="22"/>
+      <c r="AI25" s="22"/>
+      <c r="AJ25" s="22"/>
+      <c r="AK25" s="22"/>
+      <c r="AL25" s="22"/>
+      <c r="AM25" s="22"/>
+      <c r="AN25" s="22"/>
+      <c r="AO25" s="22"/>
+      <c r="AP25" s="22"/>
+      <c r="AQ25" s="22"/>
+    </row>
+    <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26" s="7" t="str">
         <v>No_non_DLS</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
-      <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
-      <c r="O26" s="21"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29"/>
-      <c r="Y26" s="29"/>
-      <c r="Z26" s="29"/>
-      <c r="AA26" s="29"/>
-      <c r="AB26" s="28"/>
-      <c r="AC26" s="28"/>
-      <c r="AD26" s="28"/>
-      <c r="AE26" s="28"/>
-      <c r="AF26" s="28"/>
-      <c r="AG26" s="28"/>
-      <c r="AH26" s="28"/>
-      <c r="AI26" s="28"/>
-      <c r="AJ26" s="28"/>
-      <c r="AK26" s="28"/>
-      <c r="AL26" s="28"/>
-      <c r="AM26" s="28"/>
-      <c r="AN26" s="28"/>
-      <c r="AO26" s="28"/>
-      <c r="AP26" s="28"/>
-      <c r="AQ26" s="28"/>
-    </row>
-    <row r="27" spans="1:43" ht="93" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="27"/>
+      <c r="N26" s="27"/>
+      <c r="O26" s="27"/>
+      <c r="Q26" s="22" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R26" s="22"/>
+      <c r="S26" s="22"/>
+      <c r="T26" s="22"/>
+      <c r="U26" s="22"/>
+      <c r="V26" s="22"/>
+      <c r="W26" s="22"/>
+      <c r="X26" s="22"/>
+      <c r="Y26" s="22"/>
+      <c r="Z26" s="22"/>
+      <c r="AA26" s="22"/>
+      <c r="AB26" s="22"/>
+      <c r="AC26" s="22"/>
+      <c r="AD26" s="22"/>
+      <c r="AE26" s="22"/>
+      <c r="AF26" s="22"/>
+      <c r="AG26" s="22"/>
+      <c r="AH26" s="22"/>
+      <c r="AI26" s="22"/>
+      <c r="AJ26" s="22"/>
+      <c r="AK26" s="22"/>
+      <c r="AL26" s="22"/>
+      <c r="AM26" s="22"/>
+      <c r="AN26" s="22"/>
+      <c r="AO26" s="22"/>
+      <c r="AP26" s="22"/>
+      <c r="AQ26" s="22"/>
+    </row>
+    <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27" s="7" t="str">
         <v>Only_%_of_pop</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21"/>
-      <c r="K27" s="21"/>
-      <c r="L27" s="21"/>
-      <c r="M27" s="21"/>
-      <c r="N27" s="21"/>
-      <c r="O27" s="21"/>
-      <c r="Q27" s="29"/>
-      <c r="R27" s="29"/>
-      <c r="S27" s="29"/>
-      <c r="T27" s="29"/>
-      <c r="U27" s="29"/>
-      <c r="V27" s="29"/>
-      <c r="W27" s="29"/>
-      <c r="X27" s="29"/>
-      <c r="Y27" s="29"/>
-      <c r="Z27" s="29"/>
-      <c r="AA27" s="29"/>
-      <c r="AB27" s="28"/>
-      <c r="AC27" s="28"/>
-      <c r="AD27" s="28"/>
-      <c r="AE27" s="28"/>
-      <c r="AF27" s="28"/>
-      <c r="AG27" s="28"/>
-      <c r="AH27" s="28"/>
-      <c r="AI27" s="28"/>
-      <c r="AJ27" s="28"/>
-      <c r="AK27" s="28"/>
-      <c r="AL27" s="28"/>
-      <c r="AM27" s="28"/>
-      <c r="AN27" s="28"/>
-      <c r="AO27" s="28"/>
-      <c r="AP27" s="28"/>
-      <c r="AQ27" s="28"/>
-    </row>
-    <row r="28" spans="1:43" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="27"/>
+      <c r="O27" s="27"/>
+      <c r="Q27" s="22"/>
+      <c r="R27" s="22"/>
+      <c r="S27" s="22"/>
+      <c r="T27" s="22"/>
+      <c r="U27" s="22"/>
+      <c r="V27" s="22"/>
+      <c r="W27" s="22"/>
+      <c r="X27" s="22"/>
+      <c r="Y27" s="22"/>
+      <c r="Z27" s="22"/>
+      <c r="AA27" s="22"/>
+      <c r="AB27" s="22"/>
+      <c r="AC27" s="22"/>
+      <c r="AD27" s="22"/>
+      <c r="AE27" s="22"/>
+      <c r="AF27" s="22"/>
+      <c r="AG27" s="22"/>
+      <c r="AH27" s="22"/>
+      <c r="AI27" s="22"/>
+      <c r="AJ27" s="22"/>
+      <c r="AK27" s="22"/>
+      <c r="AL27" s="22"/>
+      <c r="AM27" s="22"/>
+      <c r="AN27" s="22"/>
+      <c r="AO27" s="22"/>
+      <c r="AP27" s="22"/>
+      <c r="AQ27" s="22"/>
+    </row>
+    <row r="28" spans="1:51" ht="65.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2</v>
       </c>
-      <c r="B28" s="31" t="str">
-        <v>Few_indicators_closest_DLS_coverage_95</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="18"/>
-      <c r="K28" s="18"/>
-      <c r="L28" s="18"/>
-      <c r="M28" s="18"/>
-      <c r="N28" s="18"/>
-      <c r="O28" s="18"/>
-    </row>
-    <row r="29" spans="1:43" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="17" t="str">
+        <v>Few_indicators_closest_DLS_coverage_90</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="Q28" s="22"/>
+      <c r="R28" s="22"/>
+      <c r="S28" s="22"/>
+      <c r="T28" s="22"/>
+      <c r="U28" s="22"/>
+      <c r="V28" s="22"/>
+      <c r="W28" s="22"/>
+      <c r="X28" s="22"/>
+      <c r="Y28" s="22"/>
+      <c r="Z28" s="22"/>
+      <c r="AA28" s="22"/>
+      <c r="AB28" s="22" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC28" s="22"/>
+      <c r="AD28" s="22"/>
+      <c r="AE28" s="22"/>
+      <c r="AF28" s="22"/>
+      <c r="AG28" s="22"/>
+      <c r="AH28" s="22"/>
+      <c r="AI28" s="22"/>
+      <c r="AJ28" s="22"/>
+      <c r="AK28" s="22"/>
+      <c r="AL28" s="22"/>
+      <c r="AM28" s="22"/>
+      <c r="AN28" s="22"/>
+      <c r="AO28" s="22"/>
+      <c r="AP28" s="22"/>
+      <c r="AQ28" s="22"/>
+    </row>
+    <row r="29" spans="1:51" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2</v>
       </c>
-      <c r="B29" s="31" t="str">
-        <v>Few indicators_SPI_preferred_95</v>
-      </c>
-      <c r="C29" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
-    </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="B30" s="6">
-        <v>0</v>
-      </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
-    </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="B31" s="6">
-        <v>0</v>
-      </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17"/>
-      <c r="O31" s="17"/>
-    </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="B32" s="6">
-        <v>0</v>
-      </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B33" s="6">
-        <v>0</v>
-      </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B29" s="17" t="str">
+        <v>Few indicators_SPI_preferred_90</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="26"/>
+      <c r="O29" s="26"/>
+      <c r="Q29" s="22"/>
+      <c r="R29" s="22"/>
+      <c r="S29" s="22"/>
+      <c r="T29" s="22"/>
+      <c r="U29" s="22"/>
+      <c r="V29" s="22"/>
+      <c r="W29" s="22"/>
+      <c r="X29" s="22"/>
+      <c r="Y29" s="22"/>
+      <c r="Z29" s="22"/>
+      <c r="AA29" s="22"/>
+      <c r="AB29" s="22"/>
+      <c r="AC29" s="22"/>
+      <c r="AD29" s="22"/>
+      <c r="AE29" s="22"/>
+      <c r="AF29" s="22"/>
+      <c r="AG29" s="22"/>
+      <c r="AH29" s="22"/>
+      <c r="AI29" s="22"/>
+      <c r="AJ29" s="22"/>
+      <c r="AK29" s="22"/>
+      <c r="AL29" s="22"/>
+      <c r="AM29" s="22"/>
+      <c r="AN29" s="22"/>
+      <c r="AO29" s="22"/>
+      <c r="AP29" s="22"/>
+      <c r="AQ29" s="22"/>
+    </row>
+    <row r="30" spans="1:51" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>3</v>
+      </c>
+      <c r="B30" s="17" t="str">
+        <v>Few_indicators_closeDLS_subPrimSchool</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="26"/>
+      <c r="O30" s="26"/>
+      <c r="Q30" s="22" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R30" s="22"/>
+      <c r="S30" s="22"/>
+      <c r="T30" s="22"/>
+      <c r="U30" s="22"/>
+      <c r="V30" s="22"/>
+      <c r="W30" s="22"/>
+      <c r="X30" s="22"/>
+      <c r="Y30" s="22"/>
+      <c r="Z30" s="22"/>
+      <c r="AA30" s="22"/>
+      <c r="AB30" s="22"/>
+      <c r="AC30" s="22"/>
+      <c r="AD30" s="22"/>
+      <c r="AE30" s="22"/>
+      <c r="AF30" s="22"/>
+      <c r="AG30" s="22"/>
+      <c r="AH30" s="22"/>
+      <c r="AI30" s="22"/>
+      <c r="AJ30" s="22"/>
+      <c r="AK30" s="22"/>
+      <c r="AL30" s="22"/>
+      <c r="AM30" s="22"/>
+      <c r="AN30" s="22"/>
+      <c r="AO30" s="22"/>
+      <c r="AP30" s="22"/>
+      <c r="AQ30" s="22"/>
+    </row>
+    <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>3</v>
+      </c>
+      <c r="B31" s="17" t="str">
+        <v>No_non_DLS_90</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="26"/>
+      <c r="Q31" s="22"/>
+      <c r="R31" s="22"/>
+      <c r="S31" s="22"/>
+      <c r="T31" s="22"/>
+      <c r="U31" s="22"/>
+      <c r="V31" s="22"/>
+      <c r="W31" s="22"/>
+      <c r="X31" s="22"/>
+      <c r="Y31" s="22"/>
+      <c r="Z31" s="22"/>
+      <c r="AA31" s="22"/>
+      <c r="AB31" s="22"/>
+      <c r="AC31" s="22"/>
+      <c r="AD31" s="22"/>
+      <c r="AE31" s="22"/>
+      <c r="AF31" s="22"/>
+      <c r="AG31" s="22"/>
+      <c r="AH31" s="22"/>
+      <c r="AI31" s="22"/>
+      <c r="AJ31" s="22"/>
+      <c r="AK31" s="22"/>
+      <c r="AL31" s="22"/>
+      <c r="AM31" s="22"/>
+      <c r="AN31" s="22"/>
+      <c r="AO31" s="22"/>
+      <c r="AP31" s="22"/>
+      <c r="AQ31" s="22"/>
+    </row>
+    <row r="32" spans="1:51" ht="103.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32" s="17" t="str">
+        <v>Few_Indicators_subWatSani</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="Q32" s="22"/>
+      <c r="R32" s="22"/>
+      <c r="S32" s="22"/>
+      <c r="T32" s="22"/>
+      <c r="U32" s="22"/>
+      <c r="V32" s="22"/>
+      <c r="W32" s="22"/>
+      <c r="X32" s="22"/>
+      <c r="Y32" s="22"/>
+      <c r="Z32" s="22"/>
+      <c r="AA32" s="22"/>
+      <c r="AB32" s="22" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC32" s="22"/>
+      <c r="AD32" s="22"/>
+      <c r="AE32" s="22"/>
+      <c r="AF32" s="22"/>
+      <c r="AG32" s="22"/>
+      <c r="AH32" s="22"/>
+      <c r="AI32" s="22"/>
+      <c r="AJ32" s="22"/>
+      <c r="AK32" s="22"/>
+      <c r="AL32" s="22"/>
+      <c r="AM32" s="22"/>
+      <c r="AN32" s="22"/>
+      <c r="AO32" s="22"/>
+      <c r="AP32" s="22"/>
+      <c r="AQ32" s="22"/>
+    </row>
+    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33" s="6" t="str">
+        <v>Only_OPP</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="24"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="24"/>
+      <c r="N33" s="24"/>
+      <c r="O33" s="24"/>
+      <c r="Q33" s="22"/>
+      <c r="R33" s="22"/>
+      <c r="S33" s="22"/>
+      <c r="T33" s="22"/>
+      <c r="U33" s="22"/>
+      <c r="V33" s="22"/>
+      <c r="W33" s="22"/>
+      <c r="X33" s="22"/>
+      <c r="Y33" s="22"/>
+      <c r="Z33" s="22"/>
+      <c r="AA33" s="22"/>
+      <c r="AB33" s="22"/>
+      <c r="AC33" s="22"/>
+      <c r="AD33" s="22"/>
+      <c r="AE33" s="22"/>
+      <c r="AF33" s="22"/>
+      <c r="AG33" s="22"/>
+      <c r="AH33" s="22"/>
+      <c r="AI33" s="22"/>
+      <c r="AJ33" s="22"/>
+      <c r="AK33" s="22"/>
+      <c r="AL33" s="22"/>
+      <c r="AM33" s="22"/>
+      <c r="AN33" s="22"/>
+      <c r="AO33" s="22"/>
+      <c r="AP33" s="22"/>
+      <c r="AQ33" s="22"/>
+    </row>
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B34" s="6">
         <v>0</v>
       </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24"/>
+      <c r="K34" s="24"/>
+      <c r="L34" s="24"/>
+      <c r="M34" s="24"/>
+      <c r="N34" s="24"/>
+      <c r="O34" s="24"/>
+      <c r="Q34" s="22"/>
+      <c r="R34" s="22"/>
+      <c r="S34" s="22"/>
+      <c r="T34" s="22"/>
+      <c r="U34" s="22"/>
+      <c r="V34" s="22"/>
+      <c r="W34" s="22"/>
+      <c r="X34" s="22"/>
+      <c r="Y34" s="22"/>
+      <c r="Z34" s="22"/>
+      <c r="AA34" s="22"/>
+      <c r="AB34" s="22"/>
+      <c r="AC34" s="22"/>
+      <c r="AD34" s="22"/>
+      <c r="AE34" s="22"/>
+      <c r="AF34" s="22"/>
+      <c r="AG34" s="22"/>
+      <c r="AH34" s="22"/>
+      <c r="AI34" s="22"/>
+      <c r="AJ34" s="22"/>
+      <c r="AK34" s="22"/>
+      <c r="AL34" s="22"/>
+      <c r="AM34" s="22"/>
+      <c r="AN34" s="22"/>
+      <c r="AO34" s="22"/>
+      <c r="AP34" s="22"/>
+      <c r="AQ34" s="22"/>
+    </row>
+    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B35" s="6">
         <v>0</v>
       </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
+      <c r="N35" s="24"/>
+      <c r="O35" s="24"/>
+      <c r="Q35" s="22"/>
+      <c r="R35" s="22"/>
+      <c r="S35" s="22"/>
+      <c r="T35" s="22"/>
+      <c r="U35" s="22"/>
+      <c r="V35" s="22"/>
+      <c r="W35" s="22"/>
+      <c r="X35" s="22"/>
+      <c r="Y35" s="22"/>
+      <c r="Z35" s="22"/>
+      <c r="AA35" s="22"/>
+      <c r="AB35" s="22"/>
+      <c r="AC35" s="22"/>
+      <c r="AD35" s="22"/>
+      <c r="AE35" s="22"/>
+      <c r="AF35" s="22"/>
+      <c r="AG35" s="22"/>
+      <c r="AH35" s="22"/>
+      <c r="AI35" s="22"/>
+      <c r="AJ35" s="22"/>
+      <c r="AK35" s="22"/>
+      <c r="AL35" s="22"/>
+      <c r="AM35" s="22"/>
+      <c r="AN35" s="22"/>
+      <c r="AO35" s="22"/>
+      <c r="AP35" s="22"/>
+      <c r="AQ35" s="22"/>
+    </row>
+    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="Q36" s="22"/>
+      <c r="R36" s="22"/>
+      <c r="S36" s="22"/>
+      <c r="T36" s="22"/>
+      <c r="U36" s="22"/>
+      <c r="V36" s="22"/>
+      <c r="W36" s="22"/>
+      <c r="X36" s="22"/>
+      <c r="Y36" s="22"/>
+      <c r="Z36" s="22"/>
+      <c r="AA36" s="22"/>
+      <c r="AB36" s="22"/>
+      <c r="AC36" s="22"/>
+      <c r="AD36" s="22"/>
+      <c r="AE36" s="22"/>
+      <c r="AF36" s="22"/>
+      <c r="AG36" s="22"/>
+      <c r="AH36" s="22"/>
+      <c r="AI36" s="22"/>
+      <c r="AJ36" s="22"/>
+      <c r="AK36" s="22"/>
+      <c r="AL36" s="22"/>
+      <c r="AM36" s="22"/>
+      <c r="AN36" s="22"/>
+      <c r="AO36" s="22"/>
+      <c r="AP36" s="22"/>
+      <c r="AQ36" s="22"/>
+    </row>
+    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB37" s="22"/>
+      <c r="AC37" s="22"/>
+      <c r="AD37" s="22"/>
+      <c r="AE37" s="22"/>
+      <c r="AF37" s="22"/>
+      <c r="AG37" s="22"/>
+      <c r="AH37" s="22"/>
+      <c r="AI37" s="22"/>
+      <c r="AJ37" s="22"/>
+      <c r="AK37" s="22"/>
+      <c r="AL37" s="22"/>
+      <c r="AM37" s="22"/>
+      <c r="AN37" s="22"/>
+      <c r="AO37" s="22"/>
+      <c r="AP37" s="22"/>
+      <c r="AQ37" s="22"/>
+    </row>
+    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB38" s="22"/>
+      <c r="AC38" s="22"/>
+      <c r="AD38" s="22"/>
+      <c r="AE38" s="22"/>
+      <c r="AF38" s="22"/>
+      <c r="AG38" s="22"/>
+      <c r="AH38" s="22"/>
+      <c r="AI38" s="22"/>
+      <c r="AJ38" s="22"/>
+      <c r="AK38" s="22"/>
+      <c r="AL38" s="22"/>
+      <c r="AM38" s="22"/>
+      <c r="AN38" s="22"/>
+      <c r="AO38" s="22"/>
+      <c r="AP38" s="22"/>
+      <c r="AQ38" s="22"/>
+    </row>
+    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB39" s="22"/>
+      <c r="AC39" s="22"/>
+      <c r="AD39" s="22"/>
+      <c r="AE39" s="22"/>
+      <c r="AF39" s="22"/>
+      <c r="AG39" s="22"/>
+      <c r="AH39" s="22"/>
+      <c r="AI39" s="22"/>
+      <c r="AJ39" s="22"/>
+      <c r="AK39" s="22"/>
+      <c r="AL39" s="22"/>
+      <c r="AM39" s="22"/>
+      <c r="AN39" s="22"/>
+      <c r="AO39" s="22"/>
+      <c r="AP39" s="22"/>
+      <c r="AQ39" s="22"/>
+    </row>
+    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB40" s="22"/>
+      <c r="AC40" s="22"/>
+      <c r="AD40" s="22"/>
+      <c r="AE40" s="22"/>
+      <c r="AF40" s="22"/>
+      <c r="AG40" s="22"/>
+      <c r="AH40" s="22"/>
+      <c r="AI40" s="22"/>
+      <c r="AJ40" s="22"/>
+      <c r="AK40" s="22"/>
+      <c r="AL40" s="22"/>
+      <c r="AM40" s="22"/>
+      <c r="AN40" s="22"/>
+      <c r="AO40" s="22"/>
+      <c r="AP40" s="22"/>
+      <c r="AQ40" s="22"/>
+    </row>
+    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB41" s="22"/>
+      <c r="AC41" s="22"/>
+      <c r="AD41" s="22"/>
+      <c r="AE41" s="22"/>
+      <c r="AF41" s="22"/>
+      <c r="AG41" s="22"/>
+      <c r="AH41" s="22"/>
+      <c r="AI41" s="22"/>
+      <c r="AJ41" s="22"/>
+      <c r="AK41" s="22"/>
+      <c r="AL41" s="22"/>
+      <c r="AM41" s="22"/>
+      <c r="AN41" s="22"/>
+      <c r="AO41" s="22"/>
+      <c r="AP41" s="22"/>
+      <c r="AQ41" s="22"/>
+    </row>
+    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB42" s="22" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC42" s="22"/>
+      <c r="AD42" s="22"/>
+      <c r="AE42" s="22"/>
+      <c r="AF42" s="22"/>
+      <c r="AG42" s="22"/>
+      <c r="AH42" s="22"/>
+      <c r="AI42" s="22"/>
+      <c r="AJ42" s="22"/>
+      <c r="AK42" s="22"/>
+      <c r="AL42" s="22"/>
+      <c r="AM42" s="22"/>
+      <c r="AN42" s="22"/>
+      <c r="AO42" s="22"/>
+      <c r="AP42" s="22"/>
+      <c r="AQ42" s="22"/>
+    </row>
+    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB43" s="22"/>
+      <c r="AC43" s="22"/>
+      <c r="AD43" s="22"/>
+      <c r="AE43" s="22"/>
+      <c r="AF43" s="22"/>
+      <c r="AG43" s="22"/>
+      <c r="AH43" s="22"/>
+      <c r="AI43" s="22"/>
+      <c r="AJ43" s="22"/>
+      <c r="AK43" s="22"/>
+      <c r="AL43" s="22"/>
+      <c r="AM43" s="22"/>
+      <c r="AN43" s="22"/>
+      <c r="AO43" s="22"/>
+      <c r="AP43" s="22"/>
+      <c r="AQ43" s="22"/>
+    </row>
+    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB44" s="22"/>
+      <c r="AC44" s="22"/>
+      <c r="AD44" s="22"/>
+      <c r="AE44" s="22"/>
+      <c r="AF44" s="22"/>
+      <c r="AG44" s="22"/>
+      <c r="AH44" s="22"/>
+      <c r="AI44" s="22"/>
+      <c r="AJ44" s="22"/>
+      <c r="AK44" s="22"/>
+      <c r="AL44" s="22"/>
+      <c r="AM44" s="22"/>
+      <c r="AN44" s="22"/>
+      <c r="AO44" s="22"/>
+      <c r="AP44" s="22"/>
+      <c r="AQ44" s="22"/>
+    </row>
+    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB45" s="22"/>
+      <c r="AC45" s="22"/>
+      <c r="AD45" s="22"/>
+      <c r="AE45" s="22"/>
+      <c r="AF45" s="22"/>
+      <c r="AG45" s="22"/>
+      <c r="AH45" s="22"/>
+      <c r="AI45" s="22"/>
+      <c r="AJ45" s="22"/>
+      <c r="AK45" s="22"/>
+      <c r="AL45" s="22"/>
+      <c r="AM45" s="22"/>
+      <c r="AN45" s="22"/>
+      <c r="AO45" s="22"/>
+      <c r="AP45" s="22"/>
+      <c r="AQ45" s="22"/>
+    </row>
+    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB46" s="22"/>
+      <c r="AC46" s="22"/>
+      <c r="AD46" s="22"/>
+      <c r="AE46" s="22"/>
+      <c r="AF46" s="22"/>
+      <c r="AG46" s="22"/>
+      <c r="AH46" s="22"/>
+      <c r="AI46" s="22"/>
+      <c r="AJ46" s="22"/>
+      <c r="AK46" s="22"/>
+      <c r="AL46" s="22"/>
+      <c r="AM46" s="22"/>
+      <c r="AN46" s="22"/>
+      <c r="AO46" s="22"/>
+      <c r="AP46" s="22"/>
+      <c r="AQ46" s="22"/>
+    </row>
+    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB47" s="22"/>
+      <c r="AC47" s="22"/>
+      <c r="AD47" s="22"/>
+      <c r="AE47" s="22"/>
+      <c r="AF47" s="22"/>
+      <c r="AG47" s="22"/>
+      <c r="AH47" s="22"/>
+      <c r="AI47" s="22"/>
+      <c r="AJ47" s="22"/>
+      <c r="AK47" s="22"/>
+      <c r="AL47" s="22"/>
+      <c r="AM47" s="22"/>
+      <c r="AN47" s="22"/>
+      <c r="AO47" s="22"/>
+      <c r="AP47" s="22"/>
+      <c r="AQ47" s="22"/>
+    </row>
+    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB48" s="22"/>
+      <c r="AC48" s="22"/>
+      <c r="AD48" s="22"/>
+      <c r="AE48" s="22"/>
+      <c r="AF48" s="22"/>
+      <c r="AG48" s="22"/>
+      <c r="AH48" s="22"/>
+      <c r="AI48" s="22"/>
+      <c r="AJ48" s="22"/>
+      <c r="AK48" s="22"/>
+      <c r="AL48" s="22"/>
+      <c r="AM48" s="22"/>
+      <c r="AN48" s="22"/>
+      <c r="AO48" s="22"/>
+      <c r="AP48" s="22"/>
+      <c r="AQ48" s="22"/>
+    </row>
+    <row r="49" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB49" s="22"/>
+      <c r="AC49" s="22"/>
+      <c r="AD49" s="22"/>
+      <c r="AE49" s="22"/>
+      <c r="AF49" s="22"/>
+      <c r="AG49" s="22"/>
+      <c r="AH49" s="22"/>
+      <c r="AI49" s="22"/>
+      <c r="AJ49" s="22"/>
+      <c r="AK49" s="22"/>
+      <c r="AL49" s="22"/>
+      <c r="AM49" s="22"/>
+      <c r="AN49" s="22"/>
+      <c r="AO49" s="22"/>
+      <c r="AP49" s="22"/>
+      <c r="AQ49" s="22"/>
+    </row>
+    <row r="50" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB50" s="22"/>
+      <c r="AC50" s="22"/>
+      <c r="AD50" s="22"/>
+      <c r="AE50" s="22"/>
+      <c r="AF50" s="22"/>
+      <c r="AG50" s="22"/>
+      <c r="AH50" s="22"/>
+      <c r="AI50" s="22"/>
+      <c r="AJ50" s="22"/>
+      <c r="AK50" s="22"/>
+      <c r="AL50" s="22"/>
+      <c r="AM50" s="22"/>
+      <c r="AN50" s="22"/>
+      <c r="AO50" s="22"/>
+      <c r="AP50" s="22"/>
+      <c r="AQ50" s="22"/>
+    </row>
+    <row r="51" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB51" s="22"/>
+      <c r="AC51" s="22"/>
+      <c r="AD51" s="22"/>
+      <c r="AE51" s="22"/>
+      <c r="AF51" s="22"/>
+      <c r="AG51" s="22"/>
+      <c r="AH51" s="22"/>
+      <c r="AI51" s="22"/>
+      <c r="AJ51" s="22"/>
+      <c r="AK51" s="22"/>
+      <c r="AL51" s="22"/>
+      <c r="AM51" s="22"/>
+      <c r="AN51" s="22"/>
+      <c r="AO51" s="22"/>
+      <c r="AP51" s="22"/>
+      <c r="AQ51" s="22"/>
+    </row>
+    <row r="52" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB52" s="22"/>
+      <c r="AC52" s="22"/>
+      <c r="AD52" s="22"/>
+      <c r="AE52" s="22"/>
+      <c r="AF52" s="22"/>
+      <c r="AG52" s="22"/>
+      <c r="AH52" s="22"/>
+      <c r="AI52" s="22"/>
+      <c r="AJ52" s="22"/>
+      <c r="AK52" s="22"/>
+      <c r="AL52" s="22"/>
+      <c r="AM52" s="22"/>
+      <c r="AN52" s="22"/>
+      <c r="AO52" s="22"/>
+      <c r="AP52" s="22"/>
+      <c r="AQ52" s="22"/>
+    </row>
+    <row r="53" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB53" s="22"/>
+      <c r="AC53" s="22"/>
+      <c r="AD53" s="22"/>
+      <c r="AE53" s="22"/>
+      <c r="AF53" s="22"/>
+      <c r="AG53" s="22"/>
+      <c r="AH53" s="22"/>
+      <c r="AI53" s="22"/>
+      <c r="AJ53" s="22"/>
+      <c r="AK53" s="22"/>
+      <c r="AL53" s="22"/>
+      <c r="AM53" s="22"/>
+      <c r="AN53" s="22"/>
+      <c r="AO53" s="22"/>
+      <c r="AP53" s="22"/>
+      <c r="AQ53" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="42">
     <mergeCell ref="AB22:AQ27"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="I21:O21"/>
@@ -2515,8 +3236,6 @@
     <mergeCell ref="C3:H3"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="Q22:AA25"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="I28:O28"/>
     <mergeCell ref="C24:H24"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
@@ -2525,6 +3244,19 @@
     <mergeCell ref="I25:O25"/>
     <mergeCell ref="I26:O26"/>
     <mergeCell ref="I27:O27"/>
+    <mergeCell ref="I32:O32"/>
+    <mergeCell ref="I33:O33"/>
+    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="I28:O28"/>
+    <mergeCell ref="I29:O29"/>
+    <mergeCell ref="AR22:AY24"/>
+    <mergeCell ref="Q30:AA36"/>
+    <mergeCell ref="AB32:AQ41"/>
+    <mergeCell ref="AB42:AQ53"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="AB28:AQ31"/>
+    <mergeCell ref="Q26:AA29"/>
     <mergeCell ref="I35:O35"/>
     <mergeCell ref="C29:H29"/>
     <mergeCell ref="C31:H31"/>
@@ -2534,9 +3266,6 @@
     <mergeCell ref="C35:H35"/>
     <mergeCell ref="I30:O30"/>
     <mergeCell ref="I31:O31"/>
-    <mergeCell ref="I32:O32"/>
-    <mergeCell ref="I33:O33"/>
-    <mergeCell ref="I34:O34"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:O15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
@@ -2552,21 +3281,22 @@
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N65"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="62.5546875" customWidth="1"/>
-    <col min="2" max="2" width="25.21875" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" customWidth="1"/>
+    <col min="1" max="1" width="62.5703125" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" customWidth="1"/>
-    <col min="9" max="9" width="13.21875" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -2591,14 +3321,26 @@
       <c r="H1" t="s">
         <v>38</v>
       </c>
-      <c r="I1" t="s">
-        <v>59</v>
+      <c r="I1" s="21" t="s">
+        <v>61</v>
       </c>
       <c r="J1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="L1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" t="s">
+        <v>66</v>
+      </c>
+      <c r="N1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="str" cm="1">
         <f t="array" ref="A2:A53">TRANSPOSE('[1]1990-2020 Time-series data'!$Y$2:$BX$2)</f>
         <v xml:space="preserve">Child stunting (% of pop.) </v>
@@ -2624,14 +3366,26 @@
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="21">
         <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" s="21">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="str">
         <v>Deaths from infectious diseases (deaths/100,000)</v>
       </c>
@@ -2656,14 +3410,26 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="21">
         <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" s="21">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="str">
         <v xml:space="preserve">Maternal mortality  (deaths/100,000 live births) </v>
       </c>
@@ -2688,14 +3454,26 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="21">
         <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" s="21">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="str">
         <v xml:space="preserve">Nutritional deficiencies (% of pop.) </v>
       </c>
@@ -2720,14 +3498,26 @@
       <c r="H5">
         <v>1</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="21">
         <v>1</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" s="21">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="str">
         <v xml:space="preserve">Diet low in fruits and vegetables (0=low risk; 100=high risk) </v>
       </c>
@@ -2752,14 +3542,26 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="21">
         <v>0</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6" s="21">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="str">
         <v xml:space="preserve">Child mortality (deaths/1,000 live births) </v>
       </c>
@@ -2784,14 +3586,26 @@
       <c r="H7">
         <v>0</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="21">
         <v>0</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7" s="21">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="str">
         <v xml:space="preserve">No access to a handwashing facility (0=low risk; 100=high risk) </v>
       </c>
@@ -2816,14 +3630,26 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="21">
         <v>1</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8" s="21">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="str">
         <v>Deaths from unsafe water, sanitation and hygiene (deaths/100,000)</v>
       </c>
@@ -2848,14 +3674,26 @@
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="21">
         <v>0</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K9" s="21">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="str">
         <v xml:space="preserve">Improved sanitation (proportion of pop.) </v>
       </c>
@@ -2880,14 +3718,26 @@
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="21">
         <v>0</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10" s="21">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="str">
         <v xml:space="preserve">Improved water source (proportion of pop.) </v>
       </c>
@@ -2912,14 +3762,26 @@
       <c r="H11">
         <v>0</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="21">
         <v>0</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K11" s="21">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="str">
         <v>Deaths from household air pollution (deaths/100,000)</v>
       </c>
@@ -2944,14 +3806,26 @@
       <c r="H12">
         <v>0</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="21">
         <v>0</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K12" s="21">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="str">
         <v xml:space="preserve">Prevalence of cooking with coal/biomass (proportion of pop.) </v>
       </c>
@@ -2976,14 +3850,26 @@
       <c r="H13">
         <v>1</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="21">
         <v>1</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K13" s="21">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="str">
         <v xml:space="preserve">Access to electricity (% of pop.) </v>
       </c>
@@ -3008,14 +3894,26 @@
       <c r="H14">
         <v>1</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="21">
         <v>1</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K14" s="21">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="str">
         <v>Deaths from road injuries (deaths/100,000)</v>
       </c>
@@ -3040,14 +3938,26 @@
       <c r="H15">
         <v>0</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="21">
         <v>0</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K15" s="21">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="str">
         <v xml:space="preserve">Political violence (0=no violence; 4=violence often) </v>
       </c>
@@ -3072,14 +3982,26 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="21">
         <v>0</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K16" s="21">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="str">
         <v>Political killings and torture (0=low freedom; 1=high freedom)</v>
       </c>
@@ -3104,14 +4026,26 @@
       <c r="H17">
         <v>0</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="21">
         <v>0</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17" s="21">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="str">
         <v xml:space="preserve">Intimate partner violence against women (% of women aged 15+) </v>
       </c>
@@ -3136,14 +4070,26 @@
       <c r="H18">
         <v>0</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="21">
         <v>0</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K18" s="21">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="str">
         <v>Interpersonal violence  (deaths/100,000)</v>
       </c>
@@ -3168,14 +4114,26 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="21">
         <v>0</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K19" s="21">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="str">
         <v xml:space="preserve">Population with no education (proportion of pop.) </v>
       </c>
@@ -3200,14 +4158,26 @@
       <c r="H20">
         <v>1</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="21">
         <v>0</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K20" s="21">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="str">
         <v xml:space="preserve">Gender parity in basic education (distance from parity) </v>
       </c>
@@ -3232,14 +4202,26 @@
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="21">
         <v>0</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K21" s="21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="str">
         <v xml:space="preserve">Equal access to quality education (0=unequal; 4=equal) </v>
       </c>
@@ -3264,14 +4246,26 @@
       <c r="H22">
         <v>0</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="21">
         <v>0</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K22" s="21">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="str">
         <v>Mean years of schooling (years)</v>
       </c>
@@ -3296,14 +4290,26 @@
       <c r="H23">
         <v>0</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="21">
         <v>0</v>
       </c>
       <c r="J23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K23" s="21">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="str">
         <v>Alternative sources of information (0=low; 1=high)</v>
       </c>
@@ -3328,14 +4334,26 @@
       <c r="H24">
         <v>0</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="21">
         <v>0</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K24" s="21">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="str">
         <v xml:space="preserve">Internet users (% of pop.) </v>
       </c>
@@ -3360,14 +4378,26 @@
       <c r="H25">
         <v>1</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="21">
         <v>1</v>
       </c>
       <c r="J25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K25" s="21">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="str">
         <v xml:space="preserve">Mobile and landline telephone subscriptions (subscriptions/100 people) </v>
       </c>
@@ -3392,14 +4422,26 @@
       <c r="H26">
         <v>1</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="21">
         <v>1</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K26" s="21">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="str">
         <v>Life expectancy at 60 (years)</v>
       </c>
@@ -3424,14 +4466,26 @@
       <c r="H27">
         <v>0</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="21">
         <v>0</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K27" s="21">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="str">
         <v>Premature deaths from non-communicable diseases (deaths/100,000)</v>
       </c>
@@ -3456,14 +4510,26 @@
       <c r="H28">
         <v>0</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="21">
         <v>0</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K28" s="21">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="str">
         <v xml:space="preserve">Equal access to quality healthcare (0=unequal; 4=equal) </v>
       </c>
@@ -3488,14 +4554,26 @@
       <c r="H29">
         <v>0</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="21">
         <v>0</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K29" s="21">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="str">
         <v xml:space="preserve">Universal health coverage (% of pop.) </v>
       </c>
@@ -3520,14 +4598,26 @@
       <c r="H30">
         <v>1</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="21">
         <v>1</v>
       </c>
       <c r="J30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K30" s="21">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="str">
         <v>Deaths from outdoor air pollution (deaths/100,000)</v>
       </c>
@@ -3552,14 +4642,26 @@
       <c r="H31">
         <v>0</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="21">
         <v>0</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K31" s="21">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="str">
         <v>Particulate matter (2.5) pollution (mean annual exposure, µg/m3)</v>
       </c>
@@ -3584,14 +4686,26 @@
       <c r="H32">
         <v>0</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="21">
         <v>0</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K32" s="21">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="str">
         <v>Deaths from lead exposure (deaths/100,000)</v>
       </c>
@@ -3616,14 +4730,26 @@
       <c r="H33">
         <v>0</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="21">
         <v>0</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K33" s="21">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="str">
         <v>Species protection (0=low; 100=high)</v>
       </c>
@@ -3648,14 +4774,26 @@
       <c r="H34">
         <v>0</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="21">
         <v>0</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K34" s="21">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="str">
         <v xml:space="preserve">Freedom of religion (0=no freedom; 4=full freedom) </v>
       </c>
@@ -3680,14 +4818,26 @@
       <c r="H35">
         <v>0</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="21">
         <v>0</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K35" s="21">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="str">
         <v xml:space="preserve">Property rights for women (0=no rights; 5=full rights) </v>
       </c>
@@ -3712,14 +4862,26 @@
       <c r="H36">
         <v>0</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="21">
         <v>0</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K36" s="21">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="str">
         <v xml:space="preserve">Freedom of assembly (0=no freedom; 4=full freedom) </v>
       </c>
@@ -3744,14 +4906,26 @@
       <c r="H37">
         <v>0</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="21">
         <v>0</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K37" s="21">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="str">
         <v>Access to justice (0=nonexistent; 1=observed)</v>
       </c>
@@ -3776,14 +4950,26 @@
       <c r="H38">
         <v>0</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="21">
         <v>0</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K38" s="21">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="str">
         <v>Freedom of discussion (0=low; 1=high)</v>
       </c>
@@ -3808,14 +4994,26 @@
       <c r="H39">
         <v>0</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="21">
         <v>0</v>
       </c>
       <c r="J39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K39" s="21">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="str">
         <v>Political rights (1=full rights; 7=no rights)</v>
       </c>
@@ -3840,14 +5038,26 @@
       <c r="H40">
         <v>0</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="21">
         <v>0</v>
       </c>
       <c r="J40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K40" s="21">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="str">
         <v>Public sector corruption (0=low corruption; 1=high corruption)</v>
       </c>
@@ -3872,14 +5082,26 @@
       <c r="H41">
         <v>0</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="21">
         <v>0</v>
       </c>
       <c r="J41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K41" s="21">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="str">
         <v>Freedom of domestic movement (0=low; 1=high)</v>
       </c>
@@ -3904,14 +5126,26 @@
       <c r="H42">
         <v>0</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="21">
         <v>0</v>
       </c>
       <c r="J42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K42" s="21">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="str">
         <v>Satisfied demand for contraception (% satisfied demand)</v>
       </c>
@@ -3936,14 +5170,26 @@
       <c r="H43">
         <v>1</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="21">
         <v>0</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K43" s="21">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="str">
         <v>Early marriage (% of married women aged 15-19)</v>
       </c>
@@ -3968,14 +5214,26 @@
       <c r="H44">
         <v>0</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="21">
         <v>0</v>
       </c>
       <c r="J44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K44" s="21">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="str">
         <v xml:space="preserve">Vulnerable employment (% of total employment) </v>
       </c>
@@ -4000,14 +5258,26 @@
       <c r="H45">
         <v>1</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="21">
         <v>0</v>
       </c>
       <c r="J45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K45" s="21">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="str">
         <v>Equal protection of social groups (0=low; 1=high)</v>
       </c>
@@ -4032,14 +5302,26 @@
       <c r="H46">
         <v>0</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="21">
         <v>0</v>
       </c>
       <c r="J46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K46" s="21">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="str">
         <v>Equal access to power (0=low; 1=high)</v>
       </c>
@@ -4064,14 +5346,26 @@
       <c r="H47">
         <v>0</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="21">
         <v>0</v>
       </c>
       <c r="J47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K47" s="21">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="str">
         <v xml:space="preserve">Power distributed by sexual orientation (0=extremely unequal; 3=equal) </v>
       </c>
@@ -4096,14 +5390,26 @@
       <c r="H48">
         <v>0</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="21">
         <v>0</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K48" s="21">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="str">
         <v xml:space="preserve">Access to public services distributed by social group (0=extremely unequal; 4=equal) </v>
       </c>
@@ -4128,14 +5434,26 @@
       <c r="H49">
         <v>0</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="21">
         <v>0</v>
       </c>
       <c r="J49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K49" s="21">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="str">
         <v xml:space="preserve">Population with advanced education (proportion of pop.) </v>
       </c>
@@ -4160,14 +5478,26 @@
       <c r="H50">
         <v>1</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="21">
         <v>0</v>
       </c>
       <c r="J50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K50" s="21">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>1</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="str">
         <v xml:space="preserve">Gender parity in advanced education (distance from parity) </v>
       </c>
@@ -4192,14 +5522,26 @@
       <c r="H51">
         <v>0</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="21">
         <v>0</v>
       </c>
       <c r="J51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K51" s="21">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>1</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="str">
         <v>Respect for academic freedom (0=low; 1=high)</v>
       </c>
@@ -4224,14 +5566,26 @@
       <c r="H52">
         <v>0</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="21">
         <v>0</v>
       </c>
       <c r="J52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K52" s="21">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>1</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="str">
         <v>Years of tertiary schooling (years)</v>
       </c>
@@ -4256,14 +5610,26 @@
       <c r="H53">
         <v>0</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="21">
         <v>0</v>
       </c>
       <c r="J53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K53" s="21">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>1</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>2</v>
       </c>
@@ -4288,14 +5654,26 @@
       <c r="H54">
         <v>1</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="21">
         <v>1</v>
       </c>
       <c r="J54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K54" s="21">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>1</v>
+      </c>
+      <c r="M54">
+        <v>1</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>3</v>
       </c>
@@ -4320,14 +5698,26 @@
       <c r="H55">
         <v>0</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="21">
         <v>0</v>
       </c>
       <c r="J55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K55" s="21">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>1</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -4352,14 +5742,26 @@
       <c r="H56">
         <v>0</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="21">
         <v>0</v>
       </c>
       <c r="J56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K56" s="21">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -4384,14 +5786,26 @@
       <c r="H57">
         <v>0</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="21">
         <v>0</v>
       </c>
       <c r="J57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K57" s="21">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>1</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -4416,14 +5830,26 @@
       <c r="H58">
         <v>1</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="21">
         <v>1</v>
       </c>
       <c r="J58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K58" s="21">
+        <v>1</v>
+      </c>
+      <c r="L58">
+        <v>1</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -4448,14 +5874,26 @@
       <c r="H59">
         <v>1</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="21">
         <v>1</v>
       </c>
       <c r="J59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K59" s="21">
+        <v>1</v>
+      </c>
+      <c r="L59">
+        <v>1</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -4480,14 +5918,26 @@
       <c r="H60">
         <v>0</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="21">
         <v>0</v>
       </c>
       <c r="J60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K60" s="21">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>1</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -4512,14 +5962,26 @@
       <c r="H61">
         <v>0</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="21">
         <v>0</v>
       </c>
       <c r="J61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K61" s="21">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>1</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -4544,14 +6006,26 @@
       <c r="H62">
         <v>0</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="21">
         <v>0</v>
       </c>
       <c r="J62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K62" s="21">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>1</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -4576,14 +6050,26 @@
       <c r="H63">
         <v>1</v>
       </c>
-      <c r="I63">
+      <c r="I63" s="21">
         <v>1</v>
       </c>
       <c r="J63">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K63" s="21">
+        <v>1</v>
+      </c>
+      <c r="L63">
+        <v>1</v>
+      </c>
+      <c r="M63">
+        <v>1</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>12</v>
       </c>
@@ -4608,14 +6094,26 @@
       <c r="H64">
         <v>0</v>
       </c>
-      <c r="I64">
+      <c r="I64" s="21">
         <v>0</v>
       </c>
       <c r="J64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="K64" s="21">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>27</v>
       </c>
@@ -4631,13 +6129,13 @@
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A3:D67"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="61.77734375" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" customWidth="1"/>
+    <col min="2" max="2" width="61.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -4648,7 +6146,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -4660,7 +6158,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="str">
         <v>Deaths from infectious diseases (deaths/100,000)</v>
       </c>
@@ -4668,7 +6166,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="str">
         <v xml:space="preserve">Maternal mortality  (deaths/100,000 live births) </v>
       </c>
@@ -4676,7 +6174,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="str">
         <v xml:space="preserve">Nutritional deficiencies (% of pop.) </v>
       </c>
@@ -4684,7 +6182,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="str">
         <v xml:space="preserve">Diet low in fruits and vegetables (0=low risk; 100=high risk) </v>
       </c>
@@ -4692,7 +6190,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="str">
         <v xml:space="preserve">Child mortality (deaths/1,000 live births) </v>
       </c>
@@ -4700,7 +6198,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="str">
         <v xml:space="preserve">No access to a handwashing facility (0=low risk; 100=high risk) </v>
       </c>
@@ -4708,7 +6206,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="str">
         <v>Deaths from unsafe water, sanitation and hygiene (deaths/100,000)</v>
       </c>
@@ -4716,7 +6214,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="str">
         <v xml:space="preserve">Improved sanitation (proportion of pop.) </v>
       </c>
@@ -4724,7 +6222,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="str">
         <v xml:space="preserve">Improved water source (proportion of pop.) </v>
       </c>
@@ -4732,7 +6230,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -4743,7 +6241,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="str">
         <v xml:space="preserve">Prevalence of cooking with coal/biomass (proportion of pop.) </v>
       </c>
@@ -4751,7 +6249,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="str">
         <v xml:space="preserve">Access to electricity (% of pop.) </v>
       </c>
@@ -4759,7 +6257,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="str">
         <v>Deaths from road injuries (deaths/100,000)</v>
       </c>
@@ -4767,7 +6265,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="str">
         <v xml:space="preserve">Political violence (0=no violence; 4=violence often) </v>
       </c>
@@ -4775,7 +6273,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="str">
         <v>Political killings and torture (0=low freedom; 1=high freedom)</v>
       </c>
@@ -4783,7 +6281,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="str">
         <v xml:space="preserve">Intimate partner violence against women (% of women aged 15+) </v>
       </c>
@@ -4791,7 +6289,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="str">
         <v>Interpersonal violence  (deaths/100,000)</v>
       </c>
@@ -4799,7 +6297,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="str">
         <v xml:space="preserve">Population with no education (proportion of pop.) </v>
       </c>
@@ -4807,7 +6305,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="str">
         <v xml:space="preserve">Gender parity in basic education (distance from parity) </v>
       </c>
@@ -4815,7 +6313,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="str">
         <v xml:space="preserve">Equal access to quality education (0=unequal; 4=equal) </v>
       </c>
@@ -4823,7 +6321,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="str">
         <v>Mean years of schooling (years)</v>
       </c>
@@ -4831,7 +6329,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="str">
         <v>Alternative sources of information (0=low; 1=high)</v>
       </c>
@@ -4839,7 +6337,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="str">
         <v xml:space="preserve">Internet users (% of pop.) </v>
       </c>
@@ -4847,7 +6345,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="str">
         <v xml:space="preserve">Mobile and landline telephone subscriptions (subscriptions/100 people) </v>
       </c>
@@ -4855,7 +6353,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="str">
         <v>Life expectancy at 60 (years)</v>
       </c>
@@ -4863,7 +6361,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="str">
         <v>Premature deaths from non-communicable diseases (deaths/100,000)</v>
       </c>
@@ -4871,7 +6369,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="str">
         <v xml:space="preserve">Equal access to quality healthcare (0=unequal; 4=equal) </v>
       </c>
@@ -4879,7 +6377,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="str">
         <v xml:space="preserve">Universal health coverage (% of pop.) </v>
       </c>
@@ -4887,7 +6385,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="str">
         <v>Deaths from outdoor air pollution (deaths/100,000)</v>
       </c>
@@ -4895,7 +6393,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="str">
         <v>Particulate matter (2.5) pollution (mean annual exposure, µg/m3)</v>
       </c>
@@ -4903,7 +6401,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="str">
         <v>Deaths from lead exposure (deaths/100,000)</v>
       </c>
@@ -4911,7 +6409,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="str">
         <v>Species protection (0=low; 100=high)</v>
       </c>
@@ -4919,7 +6417,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -4930,7 +6428,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B38" s="4" t="str">
         <v xml:space="preserve">Property rights for women (0=no rights; 5=full rights) </v>
       </c>
@@ -4938,7 +6436,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B39" s="4" t="str">
         <v xml:space="preserve">Freedom of assembly (0=no freedom; 4=full freedom) </v>
       </c>
@@ -4946,7 +6444,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="str">
         <v>Access to justice (0=nonexistent; 1=observed)</v>
       </c>
@@ -4954,7 +6452,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B41" s="4" t="str">
         <v>Freedom of discussion (0=low; 1=high)</v>
       </c>
@@ -4962,7 +6460,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B42" s="4" t="str">
         <v>Political rights (1=full rights; 7=no rights)</v>
       </c>
@@ -4970,7 +6468,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B43" s="4" t="str">
         <v>Public sector corruption (0=low corruption; 1=high corruption)</v>
       </c>
@@ -4978,7 +6476,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B44" s="4" t="str">
         <v>Freedom of domestic movement (0=low; 1=high)</v>
       </c>
@@ -4986,7 +6484,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="str">
         <v>Satisfied demand for contraception (% satisfied demand)</v>
       </c>
@@ -4994,7 +6492,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B46" s="4" t="str">
         <v>Early marriage (% of married women aged 15-19)</v>
       </c>
@@ -5002,7 +6500,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B47" s="4" t="str">
         <v xml:space="preserve">Vulnerable employment (% of total employment) </v>
       </c>
@@ -5010,7 +6508,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B48" s="4" t="str">
         <v>Equal protection of social groups (0=low; 1=high)</v>
       </c>
@@ -5018,7 +6516,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B49" s="4" t="str">
         <v>Equal access to power (0=low; 1=high)</v>
       </c>
@@ -5026,7 +6524,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B50" s="4" t="str">
         <v xml:space="preserve">Power distributed by sexual orientation (0=extremely unequal; 3=equal) </v>
       </c>
@@ -5034,7 +6532,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="str">
         <v xml:space="preserve">Access to public services distributed by social group (0=extremely unequal; 4=equal) </v>
       </c>
@@ -5042,7 +6540,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B52" s="4" t="str">
         <v xml:space="preserve">Population with advanced education (proportion of pop.) </v>
       </c>
@@ -5050,7 +6548,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="str">
         <v xml:space="preserve">Gender parity in advanced education (distance from parity) </v>
       </c>
@@ -5058,7 +6556,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B54" s="4" t="str">
         <v>Respect for academic freedom (0=low; 1=high)</v>
       </c>
@@ -5066,7 +6564,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B55" s="4" t="str">
         <v>Years of tertiary schooling (years)</v>
       </c>
@@ -5074,7 +6572,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>1</v>
       </c>
@@ -5085,7 +6583,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>3</v>
       </c>
@@ -5093,7 +6591,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>4</v>
       </c>
@@ -5101,7 +6599,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>5</v>
       </c>
@@ -5109,7 +6607,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>7</v>
       </c>
@@ -5117,7 +6615,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>6</v>
       </c>
@@ -5125,7 +6623,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>8</v>
       </c>
@@ -5133,7 +6631,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>9</v>
       </c>
@@ -5141,7 +6639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>10</v>
       </c>
@@ -5149,7 +6647,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>11</v>
       </c>
@@ -5157,7 +6655,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>12</v>
       </c>
@@ -5165,7 +6663,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
         <v>27</v>
       </c>

--- a/IndicatorsForClusters.xlsx
+++ b/IndicatorsForClusters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1c3256d208fb6548/Personlig/Aske Banke Consultancy/YALE/Metodeartikel_WorldDevelopmentJournal/WorldDevelopmentArticleGit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="285" documentId="8_{9856C943-DD01-465B-AD17-0E409E296684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23EDE1B2-84D2-4188-A152-77CD044CA0DF}"/>
+  <xr:revisionPtr revIDLastSave="344" documentId="8_{9856C943-DD01-465B-AD17-0E409E296684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25CE3741-CEC2-4E93-A54F-DAF1EC870D74}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{726B2859-724A-4801-8E74-5A4E1AFAB973}"/>
   </bookViews>
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="75">
   <si>
     <t>SPI</t>
   </si>
@@ -364,6 +364,18 @@
   <si>
     <t>OPP reflects the quality of the institutions in a country, the resulting clusters should align with the colonial data.</t>
   </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>No_nonDLS_limExt</t>
+  </si>
+  <si>
+    <t>Too many clusters</t>
+  </si>
+  <si>
+    <t>Clustering the whole world using BHN indicators led to too few clusters. Clustering only the countries present in the colonial data and the results are look promising</t>
+  </si>
 </sst>
 </file>
 
@@ -511,7 +523,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -538,23 +550,17 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -568,19 +574,31 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1215,46 +1233,46 @@
     <col min="19" max="19" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="28" t="s">
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="29"/>
+      <c r="J3" s="27"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
-      <c r="R3" s="34" t="s">
+      <c r="T3" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="S3" s="34"/>
-      <c r="T3" s="34"/>
-      <c r="U3" s="34"/>
-      <c r="V3" s="34"/>
-    </row>
-    <row r="4" spans="1:22" ht="221.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U3" s="24"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="24"/>
+      <c r="X3" s="24"/>
+    </row>
+    <row r="4" spans="1:24" ht="221.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="15" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="9" t="str" cm="1">
-        <f t="array" ref="C4:P4">Experiments!C1:P1</f>
+        <f t="array" ref="C4:Q4">Experiments!C1:Q1</f>
         <v>BHN_FWB</v>
       </c>
       <c r="D4" s="9" t="str">
@@ -1290,21 +1308,24 @@
       <c r="N4" s="9" t="str">
         <v>Only_OPP</v>
       </c>
-      <c r="O4" s="9">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="R4" s="32" t="s">
+      <c r="O4" s="9" t="str">
+        <v>Baseline</v>
+      </c>
+      <c r="P4" s="9" t="str">
+        <v>No_nonDLS_limExt</v>
+      </c>
+      <c r="Q4" s="9" t="str">
+        <v>BHN</v>
+      </c>
+      <c r="T4" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="33"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U4" s="23"/>
+      <c r="V4" s="23"/>
+      <c r="W4" s="23"/>
+      <c r="X4" s="23"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="str" cm="1">
         <f t="array" ref="B5:B15">_xlfn.UNIQUE('Overview of indicators and DLS'!C4:C67)</f>
         <v>Food &amp; Nutrition</v>
@@ -1359,13 +1380,21 @@
       </c>
       <c r="O5" s="8" cm="1">
         <f t="array" ref="O5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!O$2:O$64=1))</f>
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="P5" s="8" cm="1">
+        <f t="array" ref="P5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!P$2:P$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="Q5" s="8" cm="1">
+        <f t="array" ref="Q5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!Q$2:Q$64=1))</f>
+        <v>3</v>
       </c>
       <c r="R5" s="16" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="str">
         <v>Health Care</v>
       </c>
@@ -1419,10 +1448,18 @@
       </c>
       <c r="O6" s="8" cm="1">
         <f t="array" ref="O6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!O$2:O$64=1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="P6" s="8" cm="1">
+        <f t="array" ref="P6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!P$2:P$64=1))</f>
+        <v>7</v>
+      </c>
+      <c r="Q6" s="8" cm="1">
+        <f t="array" ref="Q6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!Q$2:Q$64=1))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="str">
         <v>Water</v>
       </c>
@@ -1476,10 +1513,18 @@
       </c>
       <c r="O7" s="8" cm="1">
         <f t="array" ref="O7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!O$2:O$64=1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="P7" s="8" cm="1">
+        <f t="array" ref="P7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!P$2:P$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="Q7" s="8" cm="1">
+        <f t="array" ref="Q7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!Q$2:Q$64=1))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="str">
         <v>Sanitation</v>
       </c>
@@ -1533,10 +1578,18 @@
       </c>
       <c r="O8" s="8" cm="1">
         <f t="array" ref="O8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!O$2:O$64=1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="P8" s="8" cm="1">
+        <f t="array" ref="P8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!P$2:P$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="Q8" s="8" cm="1">
+        <f t="array" ref="Q8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!Q$2:Q$64=1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="str">
         <v>Food preparation</v>
       </c>
@@ -1590,10 +1643,18 @@
       </c>
       <c r="O9" s="8" cm="1">
         <f t="array" ref="O9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!O$2:O$64=1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="P9" s="8" cm="1">
+        <f t="array" ref="P9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!P$2:P$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="Q9" s="8" cm="1">
+        <f t="array" ref="Q9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!Q$2:Q$64=1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="str">
         <v>Thermal comfort</v>
       </c>
@@ -1647,10 +1708,18 @@
       </c>
       <c r="O10" s="8" cm="1">
         <f t="array" ref="O10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!O$2:O$64=1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="P10" s="8" cm="1">
+        <f t="array" ref="P10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!P$2:P$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="Q10" s="8" cm="1">
+        <f t="array" ref="Q10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!Q$2:Q$64=1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="str">
         <v>Non material / Non-DLS</v>
       </c>
@@ -1704,10 +1773,18 @@
       </c>
       <c r="O11" s="8" cm="1">
         <f t="array" ref="O11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!O$2:O$64=1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="P11" s="8" cm="1">
+        <f t="array" ref="P11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!P$2:P$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8" cm="1">
+        <f t="array" ref="Q11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!Q$2:Q$64=1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="str">
         <v>Education</v>
       </c>
@@ -1761,10 +1838,18 @@
       </c>
       <c r="O12" s="8" cm="1">
         <f t="array" ref="O12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!O$2:O$64=1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="P12" s="8" cm="1">
+        <f t="array" ref="P12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!P$2:P$64=1))</f>
+        <v>8</v>
+      </c>
+      <c r="Q12" s="8" cm="1">
+        <f t="array" ref="Q12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!Q$2:Q$64=1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="str">
         <v>Social connectedness</v>
       </c>
@@ -1818,10 +1903,18 @@
       </c>
       <c r="O13" s="8" cm="1">
         <f t="array" ref="O13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!O$2:O$64=1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="P13" s="8" cm="1">
+        <f t="array" ref="P13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!P$2:P$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="Q13" s="8" cm="1">
+        <f t="array" ref="Q13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!Q$2:Q$64=1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="str">
         <v>Housing</v>
       </c>
@@ -1877,8 +1970,16 @@
         <f t="array" ref="O14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!O$2:O$64=1))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="P14" s="8" cm="1">
+        <f t="array" ref="P14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!P$2:P$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="8" cm="1">
+        <f t="array" ref="Q14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!Q$2:Q$64=1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B15" s="13" t="str">
         <v>Physical Connectedness</v>
       </c>
@@ -1934,11 +2035,19 @@
         <f t="array" ref="O15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!O$2:O$64=1))</f>
         <v>0</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="P15" s="12" cm="1">
+        <f t="array" ref="P15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!P$2:P$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="12" cm="1">
+        <f t="array" ref="Q15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!Q$2:Q$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="R15" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B16" s="11"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
@@ -1953,6 +2062,8 @@
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
       <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
     </row>
     <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
@@ -2008,7 +2119,15 @@
       </c>
       <c r="O17" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="P17" s="14">
+        <f t="shared" ref="P17" si="2">SUM(P5:P15)</f>
+        <v>29</v>
+      </c>
+      <c r="Q17" s="14">
+        <f t="shared" ref="Q17" si="3">SUM(Q5:Q15)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:51" x14ac:dyDescent="0.25">
@@ -2065,7 +2184,15 @@
       </c>
       <c r="O18" s="8">
         <f>SUM(Experiments!O2:O53)</f>
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="P18" s="8">
+        <f>SUM(Experiments!P2:P53)</f>
+        <v>28</v>
+      </c>
+      <c r="Q18" s="8">
+        <f>SUM(Experiments!Q2:Q53)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:51" x14ac:dyDescent="0.25">
@@ -2124,6 +2251,14 @@
         <f>SUM(Experiments!O54:O64)</f>
         <v>0</v>
       </c>
+      <c r="P19" s="8">
+        <f>SUM(Experiments!P54:P64)</f>
+        <v>1</v>
+      </c>
+      <c r="Q19" s="8">
+        <f>SUM(Experiments!Q54:Q64)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -2132,23 +2267,23 @@
       <c r="B21" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C21" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30" t="s">
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="30"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="28"/>
       <c r="Q21" s="1" t="s">
         <v>59</v>
       </c>
@@ -2161,65 +2296,65 @@
         <v>1</v>
       </c>
       <c r="B22" s="7" t="str" cm="1">
-        <f t="array" ref="B22:B35">TRANSPOSE(_xlfn.ANCHORARRAY(C4))</f>
+        <f t="array" ref="B22:B36">TRANSPOSE(_xlfn.ANCHORARRAY(C4))</f>
         <v>BHN_FWB</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C22" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="27"/>
-      <c r="M22" s="27"/>
-      <c r="N22" s="27"/>
-      <c r="O22" s="27"/>
-      <c r="Q22" s="22" t="e" vm="1">
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="Q22" s="25" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="R22" s="22"/>
-      <c r="S22" s="22"/>
-      <c r="T22" s="22"/>
-      <c r="U22" s="22"/>
-      <c r="V22" s="22"/>
-      <c r="W22" s="22"/>
-      <c r="X22" s="22"/>
-      <c r="Y22" s="22"/>
-      <c r="Z22" s="22"/>
-      <c r="AA22" s="22"/>
-      <c r="AB22" s="22" t="e" vm="2">
+      <c r="R22" s="25"/>
+      <c r="S22" s="25"/>
+      <c r="T22" s="25"/>
+      <c r="U22" s="25"/>
+      <c r="V22" s="25"/>
+      <c r="W22" s="25"/>
+      <c r="X22" s="25"/>
+      <c r="Y22" s="25"/>
+      <c r="Z22" s="25"/>
+      <c r="AA22" s="25"/>
+      <c r="AB22" s="25" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="AC22" s="22"/>
-      <c r="AD22" s="22"/>
-      <c r="AE22" s="22"/>
-      <c r="AF22" s="22"/>
-      <c r="AG22" s="22"/>
-      <c r="AH22" s="22"/>
-      <c r="AI22" s="22"/>
-      <c r="AJ22" s="22"/>
-      <c r="AK22" s="22"/>
-      <c r="AL22" s="22"/>
-      <c r="AM22" s="22"/>
-      <c r="AN22" s="22"/>
-      <c r="AO22" s="22"/>
-      <c r="AP22" s="22"/>
-      <c r="AQ22" s="22"/>
-      <c r="AR22" s="22" t="e" vm="3">
+      <c r="AC22" s="25"/>
+      <c r="AD22" s="25"/>
+      <c r="AE22" s="25"/>
+      <c r="AF22" s="25"/>
+      <c r="AG22" s="25"/>
+      <c r="AH22" s="25"/>
+      <c r="AI22" s="25"/>
+      <c r="AJ22" s="25"/>
+      <c r="AK22" s="25"/>
+      <c r="AL22" s="25"/>
+      <c r="AM22" s="25"/>
+      <c r="AN22" s="25"/>
+      <c r="AO22" s="25"/>
+      <c r="AP22" s="25"/>
+      <c r="AQ22" s="25"/>
+      <c r="AR22" s="25" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="AS22" s="22"/>
-      <c r="AT22" s="22"/>
-      <c r="AU22" s="22"/>
-      <c r="AV22" s="22"/>
-      <c r="AW22" s="22"/>
-      <c r="AX22" s="22"/>
-      <c r="AY22" s="22"/>
+      <c r="AS22" s="25"/>
+      <c r="AT22" s="25"/>
+      <c r="AU22" s="25"/>
+      <c r="AV22" s="25"/>
+      <c r="AW22" s="25"/>
+      <c r="AX22" s="25"/>
+      <c r="AY22" s="25"/>
     </row>
     <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
@@ -2228,56 +2363,56 @@
       <c r="B23" s="7" t="str">
         <v>BHN_FWB_AllExt</v>
       </c>
-      <c r="C23" s="31" t="s">
+      <c r="C23" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="Q23" s="22"/>
-      <c r="R23" s="22"/>
-      <c r="S23" s="22"/>
-      <c r="T23" s="22"/>
-      <c r="U23" s="22"/>
-      <c r="V23" s="22"/>
-      <c r="W23" s="22"/>
-      <c r="X23" s="22"/>
-      <c r="Y23" s="22"/>
-      <c r="Z23" s="22"/>
-      <c r="AA23" s="22"/>
-      <c r="AB23" s="22"/>
-      <c r="AC23" s="22"/>
-      <c r="AD23" s="22"/>
-      <c r="AE23" s="22"/>
-      <c r="AF23" s="22"/>
-      <c r="AG23" s="22"/>
-      <c r="AH23" s="22"/>
-      <c r="AI23" s="22"/>
-      <c r="AJ23" s="22"/>
-      <c r="AK23" s="22"/>
-      <c r="AL23" s="22"/>
-      <c r="AM23" s="22"/>
-      <c r="AN23" s="22"/>
-      <c r="AO23" s="22"/>
-      <c r="AP23" s="22"/>
-      <c r="AQ23" s="22"/>
-      <c r="AR23" s="22"/>
-      <c r="AS23" s="22"/>
-      <c r="AT23" s="22"/>
-      <c r="AU23" s="22"/>
-      <c r="AV23" s="22"/>
-      <c r="AW23" s="22"/>
-      <c r="AX23" s="22"/>
-      <c r="AY23" s="22"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="25"/>
+      <c r="V23" s="25"/>
+      <c r="W23" s="25"/>
+      <c r="X23" s="25"/>
+      <c r="Y23" s="25"/>
+      <c r="Z23" s="25"/>
+      <c r="AA23" s="25"/>
+      <c r="AB23" s="25"/>
+      <c r="AC23" s="25"/>
+      <c r="AD23" s="25"/>
+      <c r="AE23" s="25"/>
+      <c r="AF23" s="25"/>
+      <c r="AG23" s="25"/>
+      <c r="AH23" s="25"/>
+      <c r="AI23" s="25"/>
+      <c r="AJ23" s="25"/>
+      <c r="AK23" s="25"/>
+      <c r="AL23" s="25"/>
+      <c r="AM23" s="25"/>
+      <c r="AN23" s="25"/>
+      <c r="AO23" s="25"/>
+      <c r="AP23" s="25"/>
+      <c r="AQ23" s="25"/>
+      <c r="AR23" s="25"/>
+      <c r="AS23" s="25"/>
+      <c r="AT23" s="25"/>
+      <c r="AU23" s="25"/>
+      <c r="AV23" s="25"/>
+      <c r="AW23" s="25"/>
+      <c r="AX23" s="25"/>
+      <c r="AY23" s="25"/>
     </row>
     <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
@@ -2286,56 +2421,56 @@
       <c r="B24" s="7" t="str">
         <v>Few_indicators_closest_DLS_coverage</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="27"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="27"/>
-      <c r="O24" s="27"/>
-      <c r="Q24" s="22"/>
-      <c r="R24" s="22"/>
-      <c r="S24" s="22"/>
-      <c r="T24" s="22"/>
-      <c r="U24" s="22"/>
-      <c r="V24" s="22"/>
-      <c r="W24" s="22"/>
-      <c r="X24" s="22"/>
-      <c r="Y24" s="22"/>
-      <c r="Z24" s="22"/>
-      <c r="AA24" s="22"/>
-      <c r="AB24" s="22"/>
-      <c r="AC24" s="22"/>
-      <c r="AD24" s="22"/>
-      <c r="AE24" s="22"/>
-      <c r="AF24" s="22"/>
-      <c r="AG24" s="22"/>
-      <c r="AH24" s="22"/>
-      <c r="AI24" s="22"/>
-      <c r="AJ24" s="22"/>
-      <c r="AK24" s="22"/>
-      <c r="AL24" s="22"/>
-      <c r="AM24" s="22"/>
-      <c r="AN24" s="22"/>
-      <c r="AO24" s="22"/>
-      <c r="AP24" s="22"/>
-      <c r="AQ24" s="22"/>
-      <c r="AR24" s="22"/>
-      <c r="AS24" s="22"/>
-      <c r="AT24" s="22"/>
-      <c r="AU24" s="22"/>
-      <c r="AV24" s="22"/>
-      <c r="AW24" s="22"/>
-      <c r="AX24" s="22"/>
-      <c r="AY24" s="22"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="30"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="25"/>
+      <c r="U24" s="25"/>
+      <c r="V24" s="25"/>
+      <c r="W24" s="25"/>
+      <c r="X24" s="25"/>
+      <c r="Y24" s="25"/>
+      <c r="Z24" s="25"/>
+      <c r="AA24" s="25"/>
+      <c r="AB24" s="25"/>
+      <c r="AC24" s="25"/>
+      <c r="AD24" s="25"/>
+      <c r="AE24" s="25"/>
+      <c r="AF24" s="25"/>
+      <c r="AG24" s="25"/>
+      <c r="AH24" s="25"/>
+      <c r="AI24" s="25"/>
+      <c r="AJ24" s="25"/>
+      <c r="AK24" s="25"/>
+      <c r="AL24" s="25"/>
+      <c r="AM24" s="25"/>
+      <c r="AN24" s="25"/>
+      <c r="AO24" s="25"/>
+      <c r="AP24" s="25"/>
+      <c r="AQ24" s="25"/>
+      <c r="AR24" s="25"/>
+      <c r="AS24" s="25"/>
+      <c r="AT24" s="25"/>
+      <c r="AU24" s="25"/>
+      <c r="AV24" s="25"/>
+      <c r="AW24" s="25"/>
+      <c r="AX24" s="25"/>
+      <c r="AY24" s="25"/>
     </row>
     <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
@@ -2344,48 +2479,48 @@
       <c r="B25" s="7" t="str">
         <v>Few indicators_SPI_preferred</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="C25" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="Q25" s="22"/>
-      <c r="R25" s="22"/>
-      <c r="S25" s="22"/>
-      <c r="T25" s="22"/>
-      <c r="U25" s="22"/>
-      <c r="V25" s="22"/>
-      <c r="W25" s="22"/>
-      <c r="X25" s="22"/>
-      <c r="Y25" s="22"/>
-      <c r="Z25" s="22"/>
-      <c r="AA25" s="22"/>
-      <c r="AB25" s="22"/>
-      <c r="AC25" s="22"/>
-      <c r="AD25" s="22"/>
-      <c r="AE25" s="22"/>
-      <c r="AF25" s="22"/>
-      <c r="AG25" s="22"/>
-      <c r="AH25" s="22"/>
-      <c r="AI25" s="22"/>
-      <c r="AJ25" s="22"/>
-      <c r="AK25" s="22"/>
-      <c r="AL25" s="22"/>
-      <c r="AM25" s="22"/>
-      <c r="AN25" s="22"/>
-      <c r="AO25" s="22"/>
-      <c r="AP25" s="22"/>
-      <c r="AQ25" s="22"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="25"/>
+      <c r="U25" s="25"/>
+      <c r="V25" s="25"/>
+      <c r="W25" s="25"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="25"/>
+      <c r="Z25" s="25"/>
+      <c r="AA25" s="25"/>
+      <c r="AB25" s="25"/>
+      <c r="AC25" s="25"/>
+      <c r="AD25" s="25"/>
+      <c r="AE25" s="25"/>
+      <c r="AF25" s="25"/>
+      <c r="AG25" s="25"/>
+      <c r="AH25" s="25"/>
+      <c r="AI25" s="25"/>
+      <c r="AJ25" s="25"/>
+      <c r="AK25" s="25"/>
+      <c r="AL25" s="25"/>
+      <c r="AM25" s="25"/>
+      <c r="AN25" s="25"/>
+      <c r="AO25" s="25"/>
+      <c r="AP25" s="25"/>
+      <c r="AQ25" s="25"/>
     </row>
     <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
@@ -2394,50 +2529,50 @@
       <c r="B26" s="7" t="str">
         <v>No_non_DLS</v>
       </c>
-      <c r="C26" s="36" t="s">
+      <c r="C26" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="27"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="27"/>
-      <c r="Q26" s="22" t="e" vm="4">
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="Q26" s="25" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="R26" s="22"/>
-      <c r="S26" s="22"/>
-      <c r="T26" s="22"/>
-      <c r="U26" s="22"/>
-      <c r="V26" s="22"/>
-      <c r="W26" s="22"/>
-      <c r="X26" s="22"/>
-      <c r="Y26" s="22"/>
-      <c r="Z26" s="22"/>
-      <c r="AA26" s="22"/>
-      <c r="AB26" s="22"/>
-      <c r="AC26" s="22"/>
-      <c r="AD26" s="22"/>
-      <c r="AE26" s="22"/>
-      <c r="AF26" s="22"/>
-      <c r="AG26" s="22"/>
-      <c r="AH26" s="22"/>
-      <c r="AI26" s="22"/>
-      <c r="AJ26" s="22"/>
-      <c r="AK26" s="22"/>
-      <c r="AL26" s="22"/>
-      <c r="AM26" s="22"/>
-      <c r="AN26" s="22"/>
-      <c r="AO26" s="22"/>
-      <c r="AP26" s="22"/>
-      <c r="AQ26" s="22"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25"/>
+      <c r="U26" s="25"/>
+      <c r="V26" s="25"/>
+      <c r="W26" s="25"/>
+      <c r="X26" s="25"/>
+      <c r="Y26" s="25"/>
+      <c r="Z26" s="25"/>
+      <c r="AA26" s="25"/>
+      <c r="AB26" s="25"/>
+      <c r="AC26" s="25"/>
+      <c r="AD26" s="25"/>
+      <c r="AE26" s="25"/>
+      <c r="AF26" s="25"/>
+      <c r="AG26" s="25"/>
+      <c r="AH26" s="25"/>
+      <c r="AI26" s="25"/>
+      <c r="AJ26" s="25"/>
+      <c r="AK26" s="25"/>
+      <c r="AL26" s="25"/>
+      <c r="AM26" s="25"/>
+      <c r="AN26" s="25"/>
+      <c r="AO26" s="25"/>
+      <c r="AP26" s="25"/>
+      <c r="AQ26" s="25"/>
     </row>
     <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
@@ -2446,48 +2581,48 @@
       <c r="B27" s="7" t="str">
         <v>Only_%_of_pop</v>
       </c>
-      <c r="C27" s="36" t="s">
+      <c r="C27" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="27"/>
-      <c r="L27" s="27"/>
-      <c r="M27" s="27"/>
-      <c r="N27" s="27"/>
-      <c r="O27" s="27"/>
-      <c r="Q27" s="22"/>
-      <c r="R27" s="22"/>
-      <c r="S27" s="22"/>
-      <c r="T27" s="22"/>
-      <c r="U27" s="22"/>
-      <c r="V27" s="22"/>
-      <c r="W27" s="22"/>
-      <c r="X27" s="22"/>
-      <c r="Y27" s="22"/>
-      <c r="Z27" s="22"/>
-      <c r="AA27" s="22"/>
-      <c r="AB27" s="22"/>
-      <c r="AC27" s="22"/>
-      <c r="AD27" s="22"/>
-      <c r="AE27" s="22"/>
-      <c r="AF27" s="22"/>
-      <c r="AG27" s="22"/>
-      <c r="AH27" s="22"/>
-      <c r="AI27" s="22"/>
-      <c r="AJ27" s="22"/>
-      <c r="AK27" s="22"/>
-      <c r="AL27" s="22"/>
-      <c r="AM27" s="22"/>
-      <c r="AN27" s="22"/>
-      <c r="AO27" s="22"/>
-      <c r="AP27" s="22"/>
-      <c r="AQ27" s="22"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="25"/>
+      <c r="T27" s="25"/>
+      <c r="U27" s="25"/>
+      <c r="V27" s="25"/>
+      <c r="W27" s="25"/>
+      <c r="X27" s="25"/>
+      <c r="Y27" s="25"/>
+      <c r="Z27" s="25"/>
+      <c r="AA27" s="25"/>
+      <c r="AB27" s="25"/>
+      <c r="AC27" s="25"/>
+      <c r="AD27" s="25"/>
+      <c r="AE27" s="25"/>
+      <c r="AF27" s="25"/>
+      <c r="AG27" s="25"/>
+      <c r="AH27" s="25"/>
+      <c r="AI27" s="25"/>
+      <c r="AJ27" s="25"/>
+      <c r="AK27" s="25"/>
+      <c r="AL27" s="25"/>
+      <c r="AM27" s="25"/>
+      <c r="AN27" s="25"/>
+      <c r="AO27" s="25"/>
+      <c r="AP27" s="25"/>
+      <c r="AQ27" s="25"/>
     </row>
     <row r="28" spans="1:51" ht="65.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
@@ -2496,50 +2631,50 @@
       <c r="B28" s="17" t="str">
         <v>Few_indicators_closest_DLS_coverage_90</v>
       </c>
-      <c r="C28" s="25" t="s">
+      <c r="C28" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="26"/>
-      <c r="O28" s="26"/>
-      <c r="Q28" s="22"/>
-      <c r="R28" s="22"/>
-      <c r="S28" s="22"/>
-      <c r="T28" s="22"/>
-      <c r="U28" s="22"/>
-      <c r="V28" s="22"/>
-      <c r="W28" s="22"/>
-      <c r="X28" s="22"/>
-      <c r="Y28" s="22"/>
-      <c r="Z28" s="22"/>
-      <c r="AA28" s="22"/>
-      <c r="AB28" s="22" t="e" vm="5">
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="33"/>
+      <c r="Q28" s="25"/>
+      <c r="R28" s="25"/>
+      <c r="S28" s="25"/>
+      <c r="T28" s="25"/>
+      <c r="U28" s="25"/>
+      <c r="V28" s="25"/>
+      <c r="W28" s="25"/>
+      <c r="X28" s="25"/>
+      <c r="Y28" s="25"/>
+      <c r="Z28" s="25"/>
+      <c r="AA28" s="25"/>
+      <c r="AB28" s="25" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="AC28" s="22"/>
-      <c r="AD28" s="22"/>
-      <c r="AE28" s="22"/>
-      <c r="AF28" s="22"/>
-      <c r="AG28" s="22"/>
-      <c r="AH28" s="22"/>
-      <c r="AI28" s="22"/>
-      <c r="AJ28" s="22"/>
-      <c r="AK28" s="22"/>
-      <c r="AL28" s="22"/>
-      <c r="AM28" s="22"/>
-      <c r="AN28" s="22"/>
-      <c r="AO28" s="22"/>
-      <c r="AP28" s="22"/>
-      <c r="AQ28" s="22"/>
+      <c r="AC28" s="25"/>
+      <c r="AD28" s="25"/>
+      <c r="AE28" s="25"/>
+      <c r="AF28" s="25"/>
+      <c r="AG28" s="25"/>
+      <c r="AH28" s="25"/>
+      <c r="AI28" s="25"/>
+      <c r="AJ28" s="25"/>
+      <c r="AK28" s="25"/>
+      <c r="AL28" s="25"/>
+      <c r="AM28" s="25"/>
+      <c r="AN28" s="25"/>
+      <c r="AO28" s="25"/>
+      <c r="AP28" s="25"/>
+      <c r="AQ28" s="25"/>
     </row>
     <row r="29" spans="1:51" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
@@ -2548,48 +2683,48 @@
       <c r="B29" s="17" t="str">
         <v>Few indicators_SPI_preferred_90</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="C29" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="26"/>
-      <c r="O29" s="26"/>
-      <c r="Q29" s="22"/>
-      <c r="R29" s="22"/>
-      <c r="S29" s="22"/>
-      <c r="T29" s="22"/>
-      <c r="U29" s="22"/>
-      <c r="V29" s="22"/>
-      <c r="W29" s="22"/>
-      <c r="X29" s="22"/>
-      <c r="Y29" s="22"/>
-      <c r="Z29" s="22"/>
-      <c r="AA29" s="22"/>
-      <c r="AB29" s="22"/>
-      <c r="AC29" s="22"/>
-      <c r="AD29" s="22"/>
-      <c r="AE29" s="22"/>
-      <c r="AF29" s="22"/>
-      <c r="AG29" s="22"/>
-      <c r="AH29" s="22"/>
-      <c r="AI29" s="22"/>
-      <c r="AJ29" s="22"/>
-      <c r="AK29" s="22"/>
-      <c r="AL29" s="22"/>
-      <c r="AM29" s="22"/>
-      <c r="AN29" s="22"/>
-      <c r="AO29" s="22"/>
-      <c r="AP29" s="22"/>
-      <c r="AQ29" s="22"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="33"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="25"/>
+      <c r="S29" s="25"/>
+      <c r="T29" s="25"/>
+      <c r="U29" s="25"/>
+      <c r="V29" s="25"/>
+      <c r="W29" s="25"/>
+      <c r="X29" s="25"/>
+      <c r="Y29" s="25"/>
+      <c r="Z29" s="25"/>
+      <c r="AA29" s="25"/>
+      <c r="AB29" s="25"/>
+      <c r="AC29" s="25"/>
+      <c r="AD29" s="25"/>
+      <c r="AE29" s="25"/>
+      <c r="AF29" s="25"/>
+      <c r="AG29" s="25"/>
+      <c r="AH29" s="25"/>
+      <c r="AI29" s="25"/>
+      <c r="AJ29" s="25"/>
+      <c r="AK29" s="25"/>
+      <c r="AL29" s="25"/>
+      <c r="AM29" s="25"/>
+      <c r="AN29" s="25"/>
+      <c r="AO29" s="25"/>
+      <c r="AP29" s="25"/>
+      <c r="AQ29" s="25"/>
     </row>
     <row r="30" spans="1:51" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
@@ -2598,50 +2733,50 @@
       <c r="B30" s="17" t="str">
         <v>Few_indicators_closeDLS_subPrimSchool</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="26"/>
-      <c r="L30" s="26"/>
-      <c r="M30" s="26"/>
-      <c r="N30" s="26"/>
-      <c r="O30" s="26"/>
-      <c r="Q30" s="22" t="e" vm="6">
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
+      <c r="O30" s="33"/>
+      <c r="Q30" s="25" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
-      <c r="R30" s="22"/>
-      <c r="S30" s="22"/>
-      <c r="T30" s="22"/>
-      <c r="U30" s="22"/>
-      <c r="V30" s="22"/>
-      <c r="W30" s="22"/>
-      <c r="X30" s="22"/>
-      <c r="Y30" s="22"/>
-      <c r="Z30" s="22"/>
-      <c r="AA30" s="22"/>
-      <c r="AB30" s="22"/>
-      <c r="AC30" s="22"/>
-      <c r="AD30" s="22"/>
-      <c r="AE30" s="22"/>
-      <c r="AF30" s="22"/>
-      <c r="AG30" s="22"/>
-      <c r="AH30" s="22"/>
-      <c r="AI30" s="22"/>
-      <c r="AJ30" s="22"/>
-      <c r="AK30" s="22"/>
-      <c r="AL30" s="22"/>
-      <c r="AM30" s="22"/>
-      <c r="AN30" s="22"/>
-      <c r="AO30" s="22"/>
-      <c r="AP30" s="22"/>
-      <c r="AQ30" s="22"/>
+      <c r="R30" s="25"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="25"/>
+      <c r="U30" s="25"/>
+      <c r="V30" s="25"/>
+      <c r="W30" s="25"/>
+      <c r="X30" s="25"/>
+      <c r="Y30" s="25"/>
+      <c r="Z30" s="25"/>
+      <c r="AA30" s="25"/>
+      <c r="AB30" s="25"/>
+      <c r="AC30" s="25"/>
+      <c r="AD30" s="25"/>
+      <c r="AE30" s="25"/>
+      <c r="AF30" s="25"/>
+      <c r="AG30" s="25"/>
+      <c r="AH30" s="25"/>
+      <c r="AI30" s="25"/>
+      <c r="AJ30" s="25"/>
+      <c r="AK30" s="25"/>
+      <c r="AL30" s="25"/>
+      <c r="AM30" s="25"/>
+      <c r="AN30" s="25"/>
+      <c r="AO30" s="25"/>
+      <c r="AP30" s="25"/>
+      <c r="AQ30" s="25"/>
     </row>
     <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
@@ -2650,48 +2785,48 @@
       <c r="B31" s="17" t="str">
         <v>No_non_DLS_90</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C31" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="26"/>
-      <c r="O31" s="26"/>
-      <c r="Q31" s="22"/>
-      <c r="R31" s="22"/>
-      <c r="S31" s="22"/>
-      <c r="T31" s="22"/>
-      <c r="U31" s="22"/>
-      <c r="V31" s="22"/>
-      <c r="W31" s="22"/>
-      <c r="X31" s="22"/>
-      <c r="Y31" s="22"/>
-      <c r="Z31" s="22"/>
-      <c r="AA31" s="22"/>
-      <c r="AB31" s="22"/>
-      <c r="AC31" s="22"/>
-      <c r="AD31" s="22"/>
-      <c r="AE31" s="22"/>
-      <c r="AF31" s="22"/>
-      <c r="AG31" s="22"/>
-      <c r="AH31" s="22"/>
-      <c r="AI31" s="22"/>
-      <c r="AJ31" s="22"/>
-      <c r="AK31" s="22"/>
-      <c r="AL31" s="22"/>
-      <c r="AM31" s="22"/>
-      <c r="AN31" s="22"/>
-      <c r="AO31" s="22"/>
-      <c r="AP31" s="22"/>
-      <c r="AQ31" s="22"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="33"/>
+      <c r="M31" s="33"/>
+      <c r="N31" s="33"/>
+      <c r="O31" s="33"/>
+      <c r="Q31" s="25"/>
+      <c r="R31" s="25"/>
+      <c r="S31" s="25"/>
+      <c r="T31" s="25"/>
+      <c r="U31" s="25"/>
+      <c r="V31" s="25"/>
+      <c r="W31" s="25"/>
+      <c r="X31" s="25"/>
+      <c r="Y31" s="25"/>
+      <c r="Z31" s="25"/>
+      <c r="AA31" s="25"/>
+      <c r="AB31" s="25"/>
+      <c r="AC31" s="25"/>
+      <c r="AD31" s="25"/>
+      <c r="AE31" s="25"/>
+      <c r="AF31" s="25"/>
+      <c r="AG31" s="25"/>
+      <c r="AH31" s="25"/>
+      <c r="AI31" s="25"/>
+      <c r="AJ31" s="25"/>
+      <c r="AK31" s="25"/>
+      <c r="AL31" s="25"/>
+      <c r="AM31" s="25"/>
+      <c r="AN31" s="25"/>
+      <c r="AO31" s="25"/>
+      <c r="AP31" s="25"/>
+      <c r="AQ31" s="25"/>
     </row>
     <row r="32" spans="1:51" ht="103.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -2700,50 +2835,50 @@
       <c r="B32" s="17" t="str">
         <v>Few_Indicators_subWatSani</v>
       </c>
-      <c r="C32" s="25" t="s">
+      <c r="C32" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="26"/>
-      <c r="O32" s="26"/>
-      <c r="Q32" s="22"/>
-      <c r="R32" s="22"/>
-      <c r="S32" s="22"/>
-      <c r="T32" s="22"/>
-      <c r="U32" s="22"/>
-      <c r="V32" s="22"/>
-      <c r="W32" s="22"/>
-      <c r="X32" s="22"/>
-      <c r="Y32" s="22"/>
-      <c r="Z32" s="22"/>
-      <c r="AA32" s="22"/>
-      <c r="AB32" s="22" t="e" vm="7">
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="33"/>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
+      <c r="O32" s="33"/>
+      <c r="Q32" s="25"/>
+      <c r="R32" s="25"/>
+      <c r="S32" s="25"/>
+      <c r="T32" s="25"/>
+      <c r="U32" s="25"/>
+      <c r="V32" s="25"/>
+      <c r="W32" s="25"/>
+      <c r="X32" s="25"/>
+      <c r="Y32" s="25"/>
+      <c r="Z32" s="25"/>
+      <c r="AA32" s="25"/>
+      <c r="AB32" s="25" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
-      <c r="AC32" s="22"/>
-      <c r="AD32" s="22"/>
-      <c r="AE32" s="22"/>
-      <c r="AF32" s="22"/>
-      <c r="AG32" s="22"/>
-      <c r="AH32" s="22"/>
-      <c r="AI32" s="22"/>
-      <c r="AJ32" s="22"/>
-      <c r="AK32" s="22"/>
-      <c r="AL32" s="22"/>
-      <c r="AM32" s="22"/>
-      <c r="AN32" s="22"/>
-      <c r="AO32" s="22"/>
-      <c r="AP32" s="22"/>
-      <c r="AQ32" s="22"/>
+      <c r="AC32" s="25"/>
+      <c r="AD32" s="25"/>
+      <c r="AE32" s="25"/>
+      <c r="AF32" s="25"/>
+      <c r="AG32" s="25"/>
+      <c r="AH32" s="25"/>
+      <c r="AI32" s="25"/>
+      <c r="AJ32" s="25"/>
+      <c r="AK32" s="25"/>
+      <c r="AL32" s="25"/>
+      <c r="AM32" s="25"/>
+      <c r="AN32" s="25"/>
+      <c r="AO32" s="25"/>
+      <c r="AP32" s="25"/>
+      <c r="AQ32" s="25"/>
     </row>
     <row r="33" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A33">
@@ -2752,507 +2887,498 @@
       <c r="B33" s="6" t="str">
         <v>Only_OPP</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="24"/>
-      <c r="K33" s="24"/>
-      <c r="L33" s="24"/>
-      <c r="M33" s="24"/>
-      <c r="N33" s="24"/>
-      <c r="O33" s="24"/>
-      <c r="Q33" s="22"/>
-      <c r="R33" s="22"/>
-      <c r="S33" s="22"/>
-      <c r="T33" s="22"/>
-      <c r="U33" s="22"/>
-      <c r="V33" s="22"/>
-      <c r="W33" s="22"/>
-      <c r="X33" s="22"/>
-      <c r="Y33" s="22"/>
-      <c r="Z33" s="22"/>
-      <c r="AA33" s="22"/>
-      <c r="AB33" s="22"/>
-      <c r="AC33" s="22"/>
-      <c r="AD33" s="22"/>
-      <c r="AE33" s="22"/>
-      <c r="AF33" s="22"/>
-      <c r="AG33" s="22"/>
-      <c r="AH33" s="22"/>
-      <c r="AI33" s="22"/>
-      <c r="AJ33" s="22"/>
-      <c r="AK33" s="22"/>
-      <c r="AL33" s="22"/>
-      <c r="AM33" s="22"/>
-      <c r="AN33" s="22"/>
-      <c r="AO33" s="22"/>
-      <c r="AP33" s="22"/>
-      <c r="AQ33" s="22"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="34"/>
+      <c r="K33" s="34"/>
+      <c r="L33" s="34"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
+      <c r="O33" s="34"/>
+      <c r="Q33" s="25"/>
+      <c r="R33" s="25"/>
+      <c r="S33" s="25"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="25"/>
+      <c r="V33" s="25"/>
+      <c r="W33" s="25"/>
+      <c r="X33" s="25"/>
+      <c r="Y33" s="25"/>
+      <c r="Z33" s="25"/>
+      <c r="AA33" s="25"/>
+      <c r="AB33" s="25"/>
+      <c r="AC33" s="25"/>
+      <c r="AD33" s="25"/>
+      <c r="AE33" s="25"/>
+      <c r="AF33" s="25"/>
+      <c r="AG33" s="25"/>
+      <c r="AH33" s="25"/>
+      <c r="AI33" s="25"/>
+      <c r="AJ33" s="25"/>
+      <c r="AK33" s="25"/>
+      <c r="AL33" s="25"/>
+      <c r="AM33" s="25"/>
+      <c r="AN33" s="25"/>
+      <c r="AO33" s="25"/>
+      <c r="AP33" s="25"/>
+      <c r="AQ33" s="25"/>
     </row>
     <row r="34" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="B34" s="6">
-        <v>0</v>
-      </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="24"/>
-      <c r="N34" s="24"/>
-      <c r="O34" s="24"/>
-      <c r="Q34" s="22"/>
-      <c r="R34" s="22"/>
-      <c r="S34" s="22"/>
-      <c r="T34" s="22"/>
-      <c r="U34" s="22"/>
-      <c r="V34" s="22"/>
-      <c r="W34" s="22"/>
-      <c r="X34" s="22"/>
-      <c r="Y34" s="22"/>
-      <c r="Z34" s="22"/>
-      <c r="AA34" s="22"/>
-      <c r="AB34" s="22"/>
-      <c r="AC34" s="22"/>
-      <c r="AD34" s="22"/>
-      <c r="AE34" s="22"/>
-      <c r="AF34" s="22"/>
-      <c r="AG34" s="22"/>
-      <c r="AH34" s="22"/>
-      <c r="AI34" s="22"/>
-      <c r="AJ34" s="22"/>
-      <c r="AK34" s="22"/>
-      <c r="AL34" s="22"/>
-      <c r="AM34" s="22"/>
-      <c r="AN34" s="22"/>
-      <c r="AO34" s="22"/>
-      <c r="AP34" s="22"/>
-      <c r="AQ34" s="22"/>
+      <c r="B34" s="6" t="str">
+        <v>Baseline</v>
+      </c>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="34"/>
+      <c r="N34" s="34"/>
+      <c r="O34" s="34"/>
+      <c r="Q34" s="25"/>
+      <c r="R34" s="25"/>
+      <c r="S34" s="25"/>
+      <c r="T34" s="25"/>
+      <c r="U34" s="25"/>
+      <c r="V34" s="25"/>
+      <c r="W34" s="25"/>
+      <c r="X34" s="25"/>
+      <c r="Y34" s="25"/>
+      <c r="Z34" s="25"/>
+      <c r="AA34" s="25"/>
+      <c r="AB34" s="25"/>
+      <c r="AC34" s="25"/>
+      <c r="AD34" s="25"/>
+      <c r="AE34" s="25"/>
+      <c r="AF34" s="25"/>
+      <c r="AG34" s="25"/>
+      <c r="AH34" s="25"/>
+      <c r="AI34" s="25"/>
+      <c r="AJ34" s="25"/>
+      <c r="AK34" s="25"/>
+      <c r="AL34" s="25"/>
+      <c r="AM34" s="25"/>
+      <c r="AN34" s="25"/>
+      <c r="AO34" s="25"/>
+      <c r="AP34" s="25"/>
+      <c r="AQ34" s="25"/>
     </row>
     <row r="35" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="B35" s="6">
-        <v>0</v>
-      </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="24"/>
-      <c r="N35" s="24"/>
-      <c r="O35" s="24"/>
-      <c r="Q35" s="22"/>
-      <c r="R35" s="22"/>
-      <c r="S35" s="22"/>
-      <c r="T35" s="22"/>
-      <c r="U35" s="22"/>
-      <c r="V35" s="22"/>
-      <c r="W35" s="22"/>
-      <c r="X35" s="22"/>
-      <c r="Y35" s="22"/>
-      <c r="Z35" s="22"/>
-      <c r="AA35" s="22"/>
-      <c r="AB35" s="22"/>
-      <c r="AC35" s="22"/>
-      <c r="AD35" s="22"/>
-      <c r="AE35" s="22"/>
-      <c r="AF35" s="22"/>
-      <c r="AG35" s="22"/>
-      <c r="AH35" s="22"/>
-      <c r="AI35" s="22"/>
-      <c r="AJ35" s="22"/>
-      <c r="AK35" s="22"/>
-      <c r="AL35" s="22"/>
-      <c r="AM35" s="22"/>
-      <c r="AN35" s="22"/>
-      <c r="AO35" s="22"/>
-      <c r="AP35" s="22"/>
-      <c r="AQ35" s="22"/>
-    </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="Q36" s="22"/>
-      <c r="R36" s="22"/>
-      <c r="S36" s="22"/>
-      <c r="T36" s="22"/>
-      <c r="U36" s="22"/>
-      <c r="V36" s="22"/>
-      <c r="W36" s="22"/>
-      <c r="X36" s="22"/>
-      <c r="Y36" s="22"/>
-      <c r="Z36" s="22"/>
-      <c r="AA36" s="22"/>
-      <c r="AB36" s="22"/>
-      <c r="AC36" s="22"/>
-      <c r="AD36" s="22"/>
-      <c r="AE36" s="22"/>
-      <c r="AF36" s="22"/>
-      <c r="AG36" s="22"/>
-      <c r="AH36" s="22"/>
-      <c r="AI36" s="22"/>
-      <c r="AJ36" s="22"/>
-      <c r="AK36" s="22"/>
-      <c r="AL36" s="22"/>
-      <c r="AM36" s="22"/>
-      <c r="AN36" s="22"/>
-      <c r="AO36" s="22"/>
-      <c r="AP36" s="22"/>
-      <c r="AQ36" s="22"/>
+      <c r="B35" s="6" t="str">
+        <v>No_nonDLS_limExt</v>
+      </c>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="J35" s="34"/>
+      <c r="K35" s="34"/>
+      <c r="L35" s="34"/>
+      <c r="M35" s="34"/>
+      <c r="N35" s="34"/>
+      <c r="O35" s="34"/>
+      <c r="Q35" s="25"/>
+      <c r="R35" s="25"/>
+      <c r="S35" s="25"/>
+      <c r="T35" s="25"/>
+      <c r="U35" s="25"/>
+      <c r="V35" s="25"/>
+      <c r="W35" s="25"/>
+      <c r="X35" s="25"/>
+      <c r="Y35" s="25"/>
+      <c r="Z35" s="25"/>
+      <c r="AA35" s="25"/>
+      <c r="AB35" s="25"/>
+      <c r="AC35" s="25"/>
+      <c r="AD35" s="25"/>
+      <c r="AE35" s="25"/>
+      <c r="AF35" s="25"/>
+      <c r="AG35" s="25"/>
+      <c r="AH35" s="25"/>
+      <c r="AI35" s="25"/>
+      <c r="AJ35" s="25"/>
+      <c r="AK35" s="25"/>
+      <c r="AL35" s="25"/>
+      <c r="AM35" s="25"/>
+      <c r="AN35" s="25"/>
+      <c r="AO35" s="25"/>
+      <c r="AP35" s="25"/>
+      <c r="AQ35" s="25"/>
+    </row>
+    <row r="36" spans="1:43" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="6" t="str">
+        <v>BHN</v>
+      </c>
+      <c r="C36" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="34"/>
+      <c r="J36" s="34"/>
+      <c r="K36" s="34"/>
+      <c r="L36" s="34"/>
+      <c r="M36" s="34"/>
+      <c r="N36" s="34"/>
+      <c r="O36" s="34"/>
+      <c r="Q36" s="25"/>
+      <c r="R36" s="25"/>
+      <c r="S36" s="25"/>
+      <c r="T36" s="25"/>
+      <c r="U36" s="25"/>
+      <c r="V36" s="25"/>
+      <c r="W36" s="25"/>
+      <c r="X36" s="25"/>
+      <c r="Y36" s="25"/>
+      <c r="Z36" s="25"/>
+      <c r="AA36" s="25"/>
+      <c r="AB36" s="25"/>
+      <c r="AC36" s="25"/>
+      <c r="AD36" s="25"/>
+      <c r="AE36" s="25"/>
+      <c r="AF36" s="25"/>
+      <c r="AG36" s="25"/>
+      <c r="AH36" s="25"/>
+      <c r="AI36" s="25"/>
+      <c r="AJ36" s="25"/>
+      <c r="AK36" s="25"/>
+      <c r="AL36" s="25"/>
+      <c r="AM36" s="25"/>
+      <c r="AN36" s="25"/>
+      <c r="AO36" s="25"/>
+      <c r="AP36" s="25"/>
+      <c r="AQ36" s="25"/>
     </row>
     <row r="37" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB37" s="22"/>
-      <c r="AC37" s="22"/>
-      <c r="AD37" s="22"/>
-      <c r="AE37" s="22"/>
-      <c r="AF37" s="22"/>
-      <c r="AG37" s="22"/>
-      <c r="AH37" s="22"/>
-      <c r="AI37" s="22"/>
-      <c r="AJ37" s="22"/>
-      <c r="AK37" s="22"/>
-      <c r="AL37" s="22"/>
-      <c r="AM37" s="22"/>
-      <c r="AN37" s="22"/>
-      <c r="AO37" s="22"/>
-      <c r="AP37" s="22"/>
-      <c r="AQ37" s="22"/>
+      <c r="AB37" s="25"/>
+      <c r="AC37" s="25"/>
+      <c r="AD37" s="25"/>
+      <c r="AE37" s="25"/>
+      <c r="AF37" s="25"/>
+      <c r="AG37" s="25"/>
+      <c r="AH37" s="25"/>
+      <c r="AI37" s="25"/>
+      <c r="AJ37" s="25"/>
+      <c r="AK37" s="25"/>
+      <c r="AL37" s="25"/>
+      <c r="AM37" s="25"/>
+      <c r="AN37" s="25"/>
+      <c r="AO37" s="25"/>
+      <c r="AP37" s="25"/>
+      <c r="AQ37" s="25"/>
     </row>
     <row r="38" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB38" s="22"/>
-      <c r="AC38" s="22"/>
-      <c r="AD38" s="22"/>
-      <c r="AE38" s="22"/>
-      <c r="AF38" s="22"/>
-      <c r="AG38" s="22"/>
-      <c r="AH38" s="22"/>
-      <c r="AI38" s="22"/>
-      <c r="AJ38" s="22"/>
-      <c r="AK38" s="22"/>
-      <c r="AL38" s="22"/>
-      <c r="AM38" s="22"/>
-      <c r="AN38" s="22"/>
-      <c r="AO38" s="22"/>
-      <c r="AP38" s="22"/>
-      <c r="AQ38" s="22"/>
+      <c r="AB38" s="25"/>
+      <c r="AC38" s="25"/>
+      <c r="AD38" s="25"/>
+      <c r="AE38" s="25"/>
+      <c r="AF38" s="25"/>
+      <c r="AG38" s="25"/>
+      <c r="AH38" s="25"/>
+      <c r="AI38" s="25"/>
+      <c r="AJ38" s="25"/>
+      <c r="AK38" s="25"/>
+      <c r="AL38" s="25"/>
+      <c r="AM38" s="25"/>
+      <c r="AN38" s="25"/>
+      <c r="AO38" s="25"/>
+      <c r="AP38" s="25"/>
+      <c r="AQ38" s="25"/>
     </row>
     <row r="39" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB39" s="22"/>
-      <c r="AC39" s="22"/>
-      <c r="AD39" s="22"/>
-      <c r="AE39" s="22"/>
-      <c r="AF39" s="22"/>
-      <c r="AG39" s="22"/>
-      <c r="AH39" s="22"/>
-      <c r="AI39" s="22"/>
-      <c r="AJ39" s="22"/>
-      <c r="AK39" s="22"/>
-      <c r="AL39" s="22"/>
-      <c r="AM39" s="22"/>
-      <c r="AN39" s="22"/>
-      <c r="AO39" s="22"/>
-      <c r="AP39" s="22"/>
-      <c r="AQ39" s="22"/>
+      <c r="AB39" s="25"/>
+      <c r="AC39" s="25"/>
+      <c r="AD39" s="25"/>
+      <c r="AE39" s="25"/>
+      <c r="AF39" s="25"/>
+      <c r="AG39" s="25"/>
+      <c r="AH39" s="25"/>
+      <c r="AI39" s="25"/>
+      <c r="AJ39" s="25"/>
+      <c r="AK39" s="25"/>
+      <c r="AL39" s="25"/>
+      <c r="AM39" s="25"/>
+      <c r="AN39" s="25"/>
+      <c r="AO39" s="25"/>
+      <c r="AP39" s="25"/>
+      <c r="AQ39" s="25"/>
     </row>
     <row r="40" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB40" s="22"/>
-      <c r="AC40" s="22"/>
-      <c r="AD40" s="22"/>
-      <c r="AE40" s="22"/>
-      <c r="AF40" s="22"/>
-      <c r="AG40" s="22"/>
-      <c r="AH40" s="22"/>
-      <c r="AI40" s="22"/>
-      <c r="AJ40" s="22"/>
-      <c r="AK40" s="22"/>
-      <c r="AL40" s="22"/>
-      <c r="AM40" s="22"/>
-      <c r="AN40" s="22"/>
-      <c r="AO40" s="22"/>
-      <c r="AP40" s="22"/>
-      <c r="AQ40" s="22"/>
+      <c r="AB40" s="25"/>
+      <c r="AC40" s="25"/>
+      <c r="AD40" s="25"/>
+      <c r="AE40" s="25"/>
+      <c r="AF40" s="25"/>
+      <c r="AG40" s="25"/>
+      <c r="AH40" s="25"/>
+      <c r="AI40" s="25"/>
+      <c r="AJ40" s="25"/>
+      <c r="AK40" s="25"/>
+      <c r="AL40" s="25"/>
+      <c r="AM40" s="25"/>
+      <c r="AN40" s="25"/>
+      <c r="AO40" s="25"/>
+      <c r="AP40" s="25"/>
+      <c r="AQ40" s="25"/>
     </row>
     <row r="41" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB41" s="22"/>
-      <c r="AC41" s="22"/>
-      <c r="AD41" s="22"/>
-      <c r="AE41" s="22"/>
-      <c r="AF41" s="22"/>
-      <c r="AG41" s="22"/>
-      <c r="AH41" s="22"/>
-      <c r="AI41" s="22"/>
-      <c r="AJ41" s="22"/>
-      <c r="AK41" s="22"/>
-      <c r="AL41" s="22"/>
-      <c r="AM41" s="22"/>
-      <c r="AN41" s="22"/>
-      <c r="AO41" s="22"/>
-      <c r="AP41" s="22"/>
-      <c r="AQ41" s="22"/>
+      <c r="AB41" s="25"/>
+      <c r="AC41" s="25"/>
+      <c r="AD41" s="25"/>
+      <c r="AE41" s="25"/>
+      <c r="AF41" s="25"/>
+      <c r="AG41" s="25"/>
+      <c r="AH41" s="25"/>
+      <c r="AI41" s="25"/>
+      <c r="AJ41" s="25"/>
+      <c r="AK41" s="25"/>
+      <c r="AL41" s="25"/>
+      <c r="AM41" s="25"/>
+      <c r="AN41" s="25"/>
+      <c r="AO41" s="25"/>
+      <c r="AP41" s="25"/>
+      <c r="AQ41" s="25"/>
     </row>
     <row r="42" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB42" s="22" t="e" vm="8">
+      <c r="AB42" s="25" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-      <c r="AC42" s="22"/>
-      <c r="AD42" s="22"/>
-      <c r="AE42" s="22"/>
-      <c r="AF42" s="22"/>
-      <c r="AG42" s="22"/>
-      <c r="AH42" s="22"/>
-      <c r="AI42" s="22"/>
-      <c r="AJ42" s="22"/>
-      <c r="AK42" s="22"/>
-      <c r="AL42" s="22"/>
-      <c r="AM42" s="22"/>
-      <c r="AN42" s="22"/>
-      <c r="AO42" s="22"/>
-      <c r="AP42" s="22"/>
-      <c r="AQ42" s="22"/>
+      <c r="AC42" s="25"/>
+      <c r="AD42" s="25"/>
+      <c r="AE42" s="25"/>
+      <c r="AF42" s="25"/>
+      <c r="AG42" s="25"/>
+      <c r="AH42" s="25"/>
+      <c r="AI42" s="25"/>
+      <c r="AJ42" s="25"/>
+      <c r="AK42" s="25"/>
+      <c r="AL42" s="25"/>
+      <c r="AM42" s="25"/>
+      <c r="AN42" s="25"/>
+      <c r="AO42" s="25"/>
+      <c r="AP42" s="25"/>
+      <c r="AQ42" s="25"/>
     </row>
     <row r="43" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB43" s="22"/>
-      <c r="AC43" s="22"/>
-      <c r="AD43" s="22"/>
-      <c r="AE43" s="22"/>
-      <c r="AF43" s="22"/>
-      <c r="AG43" s="22"/>
-      <c r="AH43" s="22"/>
-      <c r="AI43" s="22"/>
-      <c r="AJ43" s="22"/>
-      <c r="AK43" s="22"/>
-      <c r="AL43" s="22"/>
-      <c r="AM43" s="22"/>
-      <c r="AN43" s="22"/>
-      <c r="AO43" s="22"/>
-      <c r="AP43" s="22"/>
-      <c r="AQ43" s="22"/>
+      <c r="AB43" s="25"/>
+      <c r="AC43" s="25"/>
+      <c r="AD43" s="25"/>
+      <c r="AE43" s="25"/>
+      <c r="AF43" s="25"/>
+      <c r="AG43" s="25"/>
+      <c r="AH43" s="25"/>
+      <c r="AI43" s="25"/>
+      <c r="AJ43" s="25"/>
+      <c r="AK43" s="25"/>
+      <c r="AL43" s="25"/>
+      <c r="AM43" s="25"/>
+      <c r="AN43" s="25"/>
+      <c r="AO43" s="25"/>
+      <c r="AP43" s="25"/>
+      <c r="AQ43" s="25"/>
     </row>
     <row r="44" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB44" s="22"/>
-      <c r="AC44" s="22"/>
-      <c r="AD44" s="22"/>
-      <c r="AE44" s="22"/>
-      <c r="AF44" s="22"/>
-      <c r="AG44" s="22"/>
-      <c r="AH44" s="22"/>
-      <c r="AI44" s="22"/>
-      <c r="AJ44" s="22"/>
-      <c r="AK44" s="22"/>
-      <c r="AL44" s="22"/>
-      <c r="AM44" s="22"/>
-      <c r="AN44" s="22"/>
-      <c r="AO44" s="22"/>
-      <c r="AP44" s="22"/>
-      <c r="AQ44" s="22"/>
+      <c r="AB44" s="25"/>
+      <c r="AC44" s="25"/>
+      <c r="AD44" s="25"/>
+      <c r="AE44" s="25"/>
+      <c r="AF44" s="25"/>
+      <c r="AG44" s="25"/>
+      <c r="AH44" s="25"/>
+      <c r="AI44" s="25"/>
+      <c r="AJ44" s="25"/>
+      <c r="AK44" s="25"/>
+      <c r="AL44" s="25"/>
+      <c r="AM44" s="25"/>
+      <c r="AN44" s="25"/>
+      <c r="AO44" s="25"/>
+      <c r="AP44" s="25"/>
+      <c r="AQ44" s="25"/>
     </row>
     <row r="45" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB45" s="22"/>
-      <c r="AC45" s="22"/>
-      <c r="AD45" s="22"/>
-      <c r="AE45" s="22"/>
-      <c r="AF45" s="22"/>
-      <c r="AG45" s="22"/>
-      <c r="AH45" s="22"/>
-      <c r="AI45" s="22"/>
-      <c r="AJ45" s="22"/>
-      <c r="AK45" s="22"/>
-      <c r="AL45" s="22"/>
-      <c r="AM45" s="22"/>
-      <c r="AN45" s="22"/>
-      <c r="AO45" s="22"/>
-      <c r="AP45" s="22"/>
-      <c r="AQ45" s="22"/>
+      <c r="AB45" s="25"/>
+      <c r="AC45" s="25"/>
+      <c r="AD45" s="25"/>
+      <c r="AE45" s="25"/>
+      <c r="AF45" s="25"/>
+      <c r="AG45" s="25"/>
+      <c r="AH45" s="25"/>
+      <c r="AI45" s="25"/>
+      <c r="AJ45" s="25"/>
+      <c r="AK45" s="25"/>
+      <c r="AL45" s="25"/>
+      <c r="AM45" s="25"/>
+      <c r="AN45" s="25"/>
+      <c r="AO45" s="25"/>
+      <c r="AP45" s="25"/>
+      <c r="AQ45" s="25"/>
     </row>
     <row r="46" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB46" s="22"/>
-      <c r="AC46" s="22"/>
-      <c r="AD46" s="22"/>
-      <c r="AE46" s="22"/>
-      <c r="AF46" s="22"/>
-      <c r="AG46" s="22"/>
-      <c r="AH46" s="22"/>
-      <c r="AI46" s="22"/>
-      <c r="AJ46" s="22"/>
-      <c r="AK46" s="22"/>
-      <c r="AL46" s="22"/>
-      <c r="AM46" s="22"/>
-      <c r="AN46" s="22"/>
-      <c r="AO46" s="22"/>
-      <c r="AP46" s="22"/>
-      <c r="AQ46" s="22"/>
+      <c r="AB46" s="25"/>
+      <c r="AC46" s="25"/>
+      <c r="AD46" s="25"/>
+      <c r="AE46" s="25"/>
+      <c r="AF46" s="25"/>
+      <c r="AG46" s="25"/>
+      <c r="AH46" s="25"/>
+      <c r="AI46" s="25"/>
+      <c r="AJ46" s="25"/>
+      <c r="AK46" s="25"/>
+      <c r="AL46" s="25"/>
+      <c r="AM46" s="25"/>
+      <c r="AN46" s="25"/>
+      <c r="AO46" s="25"/>
+      <c r="AP46" s="25"/>
+      <c r="AQ46" s="25"/>
     </row>
     <row r="47" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB47" s="22"/>
-      <c r="AC47" s="22"/>
-      <c r="AD47" s="22"/>
-      <c r="AE47" s="22"/>
-      <c r="AF47" s="22"/>
-      <c r="AG47" s="22"/>
-      <c r="AH47" s="22"/>
-      <c r="AI47" s="22"/>
-      <c r="AJ47" s="22"/>
-      <c r="AK47" s="22"/>
-      <c r="AL47" s="22"/>
-      <c r="AM47" s="22"/>
-      <c r="AN47" s="22"/>
-      <c r="AO47" s="22"/>
-      <c r="AP47" s="22"/>
-      <c r="AQ47" s="22"/>
+      <c r="AB47" s="25"/>
+      <c r="AC47" s="25"/>
+      <c r="AD47" s="25"/>
+      <c r="AE47" s="25"/>
+      <c r="AF47" s="25"/>
+      <c r="AG47" s="25"/>
+      <c r="AH47" s="25"/>
+      <c r="AI47" s="25"/>
+      <c r="AJ47" s="25"/>
+      <c r="AK47" s="25"/>
+      <c r="AL47" s="25"/>
+      <c r="AM47" s="25"/>
+      <c r="AN47" s="25"/>
+      <c r="AO47" s="25"/>
+      <c r="AP47" s="25"/>
+      <c r="AQ47" s="25"/>
     </row>
     <row r="48" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB48" s="22"/>
-      <c r="AC48" s="22"/>
-      <c r="AD48" s="22"/>
-      <c r="AE48" s="22"/>
-      <c r="AF48" s="22"/>
-      <c r="AG48" s="22"/>
-      <c r="AH48" s="22"/>
-      <c r="AI48" s="22"/>
-      <c r="AJ48" s="22"/>
-      <c r="AK48" s="22"/>
-      <c r="AL48" s="22"/>
-      <c r="AM48" s="22"/>
-      <c r="AN48" s="22"/>
-      <c r="AO48" s="22"/>
-      <c r="AP48" s="22"/>
-      <c r="AQ48" s="22"/>
+      <c r="AB48" s="25"/>
+      <c r="AC48" s="25"/>
+      <c r="AD48" s="25"/>
+      <c r="AE48" s="25"/>
+      <c r="AF48" s="25"/>
+      <c r="AG48" s="25"/>
+      <c r="AH48" s="25"/>
+      <c r="AI48" s="25"/>
+      <c r="AJ48" s="25"/>
+      <c r="AK48" s="25"/>
+      <c r="AL48" s="25"/>
+      <c r="AM48" s="25"/>
+      <c r="AN48" s="25"/>
+      <c r="AO48" s="25"/>
+      <c r="AP48" s="25"/>
+      <c r="AQ48" s="25"/>
     </row>
     <row r="49" spans="28:43" x14ac:dyDescent="0.25">
-      <c r="AB49" s="22"/>
-      <c r="AC49" s="22"/>
-      <c r="AD49" s="22"/>
-      <c r="AE49" s="22"/>
-      <c r="AF49" s="22"/>
-      <c r="AG49" s="22"/>
-      <c r="AH49" s="22"/>
-      <c r="AI49" s="22"/>
-      <c r="AJ49" s="22"/>
-      <c r="AK49" s="22"/>
-      <c r="AL49" s="22"/>
-      <c r="AM49" s="22"/>
-      <c r="AN49" s="22"/>
-      <c r="AO49" s="22"/>
-      <c r="AP49" s="22"/>
-      <c r="AQ49" s="22"/>
+      <c r="AB49" s="25"/>
+      <c r="AC49" s="25"/>
+      <c r="AD49" s="25"/>
+      <c r="AE49" s="25"/>
+      <c r="AF49" s="25"/>
+      <c r="AG49" s="25"/>
+      <c r="AH49" s="25"/>
+      <c r="AI49" s="25"/>
+      <c r="AJ49" s="25"/>
+      <c r="AK49" s="25"/>
+      <c r="AL49" s="25"/>
+      <c r="AM49" s="25"/>
+      <c r="AN49" s="25"/>
+      <c r="AO49" s="25"/>
+      <c r="AP49" s="25"/>
+      <c r="AQ49" s="25"/>
     </row>
     <row r="50" spans="28:43" x14ac:dyDescent="0.25">
-      <c r="AB50" s="22"/>
-      <c r="AC50" s="22"/>
-      <c r="AD50" s="22"/>
-      <c r="AE50" s="22"/>
-      <c r="AF50" s="22"/>
-      <c r="AG50" s="22"/>
-      <c r="AH50" s="22"/>
-      <c r="AI50" s="22"/>
-      <c r="AJ50" s="22"/>
-      <c r="AK50" s="22"/>
-      <c r="AL50" s="22"/>
-      <c r="AM50" s="22"/>
-      <c r="AN50" s="22"/>
-      <c r="AO50" s="22"/>
-      <c r="AP50" s="22"/>
-      <c r="AQ50" s="22"/>
+      <c r="AB50" s="25"/>
+      <c r="AC50" s="25"/>
+      <c r="AD50" s="25"/>
+      <c r="AE50" s="25"/>
+      <c r="AF50" s="25"/>
+      <c r="AG50" s="25"/>
+      <c r="AH50" s="25"/>
+      <c r="AI50" s="25"/>
+      <c r="AJ50" s="25"/>
+      <c r="AK50" s="25"/>
+      <c r="AL50" s="25"/>
+      <c r="AM50" s="25"/>
+      <c r="AN50" s="25"/>
+      <c r="AO50" s="25"/>
+      <c r="AP50" s="25"/>
+      <c r="AQ50" s="25"/>
     </row>
     <row r="51" spans="28:43" x14ac:dyDescent="0.25">
-      <c r="AB51" s="22"/>
-      <c r="AC51" s="22"/>
-      <c r="AD51" s="22"/>
-      <c r="AE51" s="22"/>
-      <c r="AF51" s="22"/>
-      <c r="AG51" s="22"/>
-      <c r="AH51" s="22"/>
-      <c r="AI51" s="22"/>
-      <c r="AJ51" s="22"/>
-      <c r="AK51" s="22"/>
-      <c r="AL51" s="22"/>
-      <c r="AM51" s="22"/>
-      <c r="AN51" s="22"/>
-      <c r="AO51" s="22"/>
-      <c r="AP51" s="22"/>
-      <c r="AQ51" s="22"/>
+      <c r="AB51" s="25"/>
+      <c r="AC51" s="25"/>
+      <c r="AD51" s="25"/>
+      <c r="AE51" s="25"/>
+      <c r="AF51" s="25"/>
+      <c r="AG51" s="25"/>
+      <c r="AH51" s="25"/>
+      <c r="AI51" s="25"/>
+      <c r="AJ51" s="25"/>
+      <c r="AK51" s="25"/>
+      <c r="AL51" s="25"/>
+      <c r="AM51" s="25"/>
+      <c r="AN51" s="25"/>
+      <c r="AO51" s="25"/>
+      <c r="AP51" s="25"/>
+      <c r="AQ51" s="25"/>
     </row>
     <row r="52" spans="28:43" x14ac:dyDescent="0.25">
-      <c r="AB52" s="22"/>
-      <c r="AC52" s="22"/>
-      <c r="AD52" s="22"/>
-      <c r="AE52" s="22"/>
-      <c r="AF52" s="22"/>
-      <c r="AG52" s="22"/>
-      <c r="AH52" s="22"/>
-      <c r="AI52" s="22"/>
-      <c r="AJ52" s="22"/>
-      <c r="AK52" s="22"/>
-      <c r="AL52" s="22"/>
-      <c r="AM52" s="22"/>
-      <c r="AN52" s="22"/>
-      <c r="AO52" s="22"/>
-      <c r="AP52" s="22"/>
-      <c r="AQ52" s="22"/>
+      <c r="AB52" s="25"/>
+      <c r="AC52" s="25"/>
+      <c r="AD52" s="25"/>
+      <c r="AE52" s="25"/>
+      <c r="AF52" s="25"/>
+      <c r="AG52" s="25"/>
+      <c r="AH52" s="25"/>
+      <c r="AI52" s="25"/>
+      <c r="AJ52" s="25"/>
+      <c r="AK52" s="25"/>
+      <c r="AL52" s="25"/>
+      <c r="AM52" s="25"/>
+      <c r="AN52" s="25"/>
+      <c r="AO52" s="25"/>
+      <c r="AP52" s="25"/>
+      <c r="AQ52" s="25"/>
     </row>
     <row r="53" spans="28:43" x14ac:dyDescent="0.25">
-      <c r="AB53" s="22"/>
-      <c r="AC53" s="22"/>
-      <c r="AD53" s="22"/>
-      <c r="AE53" s="22"/>
-      <c r="AF53" s="22"/>
-      <c r="AG53" s="22"/>
-      <c r="AH53" s="22"/>
-      <c r="AI53" s="22"/>
-      <c r="AJ53" s="22"/>
-      <c r="AK53" s="22"/>
-      <c r="AL53" s="22"/>
-      <c r="AM53" s="22"/>
-      <c r="AN53" s="22"/>
-      <c r="AO53" s="22"/>
-      <c r="AP53" s="22"/>
-      <c r="AQ53" s="22"/>
+      <c r="AB53" s="25"/>
+      <c r="AC53" s="25"/>
+      <c r="AD53" s="25"/>
+      <c r="AE53" s="25"/>
+      <c r="AF53" s="25"/>
+      <c r="AG53" s="25"/>
+      <c r="AH53" s="25"/>
+      <c r="AI53" s="25"/>
+      <c r="AJ53" s="25"/>
+      <c r="AK53" s="25"/>
+      <c r="AL53" s="25"/>
+      <c r="AM53" s="25"/>
+      <c r="AN53" s="25"/>
+      <c r="AO53" s="25"/>
+      <c r="AP53" s="25"/>
+      <c r="AQ53" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="AB22:AQ27"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I21:O21"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C23:H23"/>
-    <mergeCell ref="R4:V4"/>
-    <mergeCell ref="R3:V3"/>
-    <mergeCell ref="I22:O22"/>
-    <mergeCell ref="I23:O23"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="Q22:AA25"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="I24:O24"/>
-    <mergeCell ref="I25:O25"/>
-    <mergeCell ref="I26:O26"/>
-    <mergeCell ref="I27:O27"/>
-    <mergeCell ref="I32:O32"/>
-    <mergeCell ref="I33:O33"/>
-    <mergeCell ref="I34:O34"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="I28:O28"/>
-    <mergeCell ref="I29:O29"/>
-    <mergeCell ref="AR22:AY24"/>
-    <mergeCell ref="Q30:AA36"/>
-    <mergeCell ref="AB32:AQ41"/>
     <mergeCell ref="AB42:AQ53"/>
     <mergeCell ref="C30:H30"/>
     <mergeCell ref="AB28:AQ31"/>
@@ -3266,8 +3392,37 @@
     <mergeCell ref="C35:H35"/>
     <mergeCell ref="I30:O30"/>
     <mergeCell ref="I31:O31"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="I28:O28"/>
+    <mergeCell ref="I29:O29"/>
+    <mergeCell ref="AR22:AY24"/>
+    <mergeCell ref="Q30:AA36"/>
+    <mergeCell ref="AB32:AQ41"/>
+    <mergeCell ref="I26:O26"/>
+    <mergeCell ref="I27:O27"/>
+    <mergeCell ref="I32:O32"/>
+    <mergeCell ref="I33:O33"/>
+    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="AB22:AQ27"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I21:O21"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="I22:O22"/>
+    <mergeCell ref="I23:O23"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="Q22:AA25"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="I24:O24"/>
+    <mergeCell ref="I25:O25"/>
   </mergeCells>
-  <conditionalFormatting sqref="C5:O15">
+  <conditionalFormatting sqref="C5:Q15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -3281,7 +3436,7 @@
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:Q65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="62.5703125" customWidth="1"/>
@@ -3296,7 +3451,7 @@
     <col min="11" max="11" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -3339,8 +3494,17 @@
       <c r="N1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="str" cm="1">
         <f t="array" ref="A2:A53">TRANSPOSE('[1]1990-2020 Time-series data'!$Y$2:$BX$2)</f>
         <v xml:space="preserve">Child stunting (% of pop.) </v>
@@ -3384,8 +3548,17 @@
       <c r="N2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="str">
         <v>Deaths from infectious diseases (deaths/100,000)</v>
       </c>
@@ -3428,8 +3601,17 @@
       <c r="N3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="str">
         <v xml:space="preserve">Maternal mortality  (deaths/100,000 live births) </v>
       </c>
@@ -3472,8 +3654,17 @@
       <c r="N4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="str">
         <v xml:space="preserve">Nutritional deficiencies (% of pop.) </v>
       </c>
@@ -3516,8 +3707,17 @@
       <c r="N5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="str">
         <v xml:space="preserve">Diet low in fruits and vegetables (0=low risk; 100=high risk) </v>
       </c>
@@ -3560,8 +3760,17 @@
       <c r="N6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="str">
         <v xml:space="preserve">Child mortality (deaths/1,000 live births) </v>
       </c>
@@ -3604,8 +3813,17 @@
       <c r="N7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="str">
         <v xml:space="preserve">No access to a handwashing facility (0=low risk; 100=high risk) </v>
       </c>
@@ -3648,8 +3866,17 @@
       <c r="N8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="str">
         <v>Deaths from unsafe water, sanitation and hygiene (deaths/100,000)</v>
       </c>
@@ -3692,8 +3919,17 @@
       <c r="N9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="str">
         <v xml:space="preserve">Improved sanitation (proportion of pop.) </v>
       </c>
@@ -3736,8 +3972,17 @@
       <c r="N10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="str">
         <v xml:space="preserve">Improved water source (proportion of pop.) </v>
       </c>
@@ -3780,8 +4025,17 @@
       <c r="N11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="str">
         <v>Deaths from household air pollution (deaths/100,000)</v>
       </c>
@@ -3824,8 +4078,17 @@
       <c r="N12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="str">
         <v xml:space="preserve">Prevalence of cooking with coal/biomass (proportion of pop.) </v>
       </c>
@@ -3868,8 +4131,17 @@
       <c r="N13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="str">
         <v xml:space="preserve">Access to electricity (% of pop.) </v>
       </c>
@@ -3912,8 +4184,17 @@
       <c r="N14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="str">
         <v>Deaths from road injuries (deaths/100,000)</v>
       </c>
@@ -3956,8 +4237,17 @@
       <c r="N15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="str">
         <v xml:space="preserve">Political violence (0=no violence; 4=violence often) </v>
       </c>
@@ -4000,8 +4290,17 @@
       <c r="N16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="str">
         <v>Political killings and torture (0=low freedom; 1=high freedom)</v>
       </c>
@@ -4044,8 +4343,17 @@
       <c r="N17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="str">
         <v xml:space="preserve">Intimate partner violence against women (% of women aged 15+) </v>
       </c>
@@ -4088,8 +4396,17 @@
       <c r="N18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="str">
         <v>Interpersonal violence  (deaths/100,000)</v>
       </c>
@@ -4132,8 +4449,17 @@
       <c r="N19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="str">
         <v xml:space="preserve">Population with no education (proportion of pop.) </v>
       </c>
@@ -4176,8 +4502,17 @@
       <c r="N20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="str">
         <v xml:space="preserve">Gender parity in basic education (distance from parity) </v>
       </c>
@@ -4220,8 +4555,17 @@
       <c r="N21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="str">
         <v xml:space="preserve">Equal access to quality education (0=unequal; 4=equal) </v>
       </c>
@@ -4264,8 +4608,17 @@
       <c r="N22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="str">
         <v>Mean years of schooling (years)</v>
       </c>
@@ -4308,8 +4661,17 @@
       <c r="N23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="str">
         <v>Alternative sources of information (0=low; 1=high)</v>
       </c>
@@ -4352,8 +4714,17 @@
       <c r="N24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="str">
         <v xml:space="preserve">Internet users (% of pop.) </v>
       </c>
@@ -4396,8 +4767,17 @@
       <c r="N25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O25">
+        <v>1</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="str">
         <v xml:space="preserve">Mobile and landline telephone subscriptions (subscriptions/100 people) </v>
       </c>
@@ -4440,8 +4820,17 @@
       <c r="N26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="str">
         <v>Life expectancy at 60 (years)</v>
       </c>
@@ -4484,8 +4873,17 @@
       <c r="N27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O27">
+        <v>1</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="str">
         <v>Premature deaths from non-communicable diseases (deaths/100,000)</v>
       </c>
@@ -4528,8 +4926,17 @@
       <c r="N28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O28">
+        <v>1</v>
+      </c>
+      <c r="P28">
+        <v>1</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="str">
         <v xml:space="preserve">Equal access to quality healthcare (0=unequal; 4=equal) </v>
       </c>
@@ -4572,8 +4979,17 @@
       <c r="N29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="P29">
+        <v>1</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="str">
         <v xml:space="preserve">Universal health coverage (% of pop.) </v>
       </c>
@@ -4616,8 +5032,17 @@
       <c r="N30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O30">
+        <v>1</v>
+      </c>
+      <c r="P30">
+        <v>1</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="str">
         <v>Deaths from outdoor air pollution (deaths/100,000)</v>
       </c>
@@ -4660,8 +5085,17 @@
       <c r="N31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O31">
+        <v>1</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="str">
         <v>Particulate matter (2.5) pollution (mean annual exposure, µg/m3)</v>
       </c>
@@ -4704,8 +5138,17 @@
       <c r="N32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O32">
+        <v>1</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="str">
         <v>Deaths from lead exposure (deaths/100,000)</v>
       </c>
@@ -4748,8 +5191,17 @@
       <c r="N33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O33">
+        <v>1</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="str">
         <v>Species protection (0=low; 100=high)</v>
       </c>
@@ -4792,8 +5244,17 @@
       <c r="N34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O34">
+        <v>1</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="str">
         <v xml:space="preserve">Freedom of religion (0=no freedom; 4=full freedom) </v>
       </c>
@@ -4836,8 +5297,17 @@
       <c r="N35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O35">
+        <v>1</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="str">
         <v xml:space="preserve">Property rights for women (0=no rights; 5=full rights) </v>
       </c>
@@ -4880,8 +5350,17 @@
       <c r="N36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O36">
+        <v>1</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="str">
         <v xml:space="preserve">Freedom of assembly (0=no freedom; 4=full freedom) </v>
       </c>
@@ -4924,8 +5403,17 @@
       <c r="N37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O37">
+        <v>1</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="str">
         <v>Access to justice (0=nonexistent; 1=observed)</v>
       </c>
@@ -4968,8 +5456,17 @@
       <c r="N38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O38">
+        <v>1</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="str">
         <v>Freedom of discussion (0=low; 1=high)</v>
       </c>
@@ -5012,8 +5509,17 @@
       <c r="N39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O39">
+        <v>1</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="str">
         <v>Political rights (1=full rights; 7=no rights)</v>
       </c>
@@ -5056,8 +5562,17 @@
       <c r="N40">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O40">
+        <v>1</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="str">
         <v>Public sector corruption (0=low corruption; 1=high corruption)</v>
       </c>
@@ -5100,8 +5615,17 @@
       <c r="N41">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O41">
+        <v>1</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="str">
         <v>Freedom of domestic movement (0=low; 1=high)</v>
       </c>
@@ -5144,8 +5668,17 @@
       <c r="N42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O42">
+        <v>1</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="str">
         <v>Satisfied demand for contraception (% satisfied demand)</v>
       </c>
@@ -5188,8 +5721,17 @@
       <c r="N43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O43">
+        <v>1</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="str">
         <v>Early marriage (% of married women aged 15-19)</v>
       </c>
@@ -5232,8 +5774,17 @@
       <c r="N44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O44">
+        <v>1</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="str">
         <v xml:space="preserve">Vulnerable employment (% of total employment) </v>
       </c>
@@ -5276,8 +5827,17 @@
       <c r="N45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O45">
+        <v>1</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="str">
         <v>Equal protection of social groups (0=low; 1=high)</v>
       </c>
@@ -5320,8 +5880,17 @@
       <c r="N46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O46">
+        <v>1</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="str">
         <v>Equal access to power (0=low; 1=high)</v>
       </c>
@@ -5364,8 +5933,17 @@
       <c r="N47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O47">
+        <v>1</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="str">
         <v xml:space="preserve">Power distributed by sexual orientation (0=extremely unequal; 3=equal) </v>
       </c>
@@ -5408,8 +5986,17 @@
       <c r="N48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O48">
+        <v>1</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="str">
         <v xml:space="preserve">Access to public services distributed by social group (0=extremely unequal; 4=equal) </v>
       </c>
@@ -5452,8 +6039,17 @@
       <c r="N49">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O49">
+        <v>1</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="str">
         <v xml:space="preserve">Population with advanced education (proportion of pop.) </v>
       </c>
@@ -5496,8 +6092,17 @@
       <c r="N50">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O50">
+        <v>1</v>
+      </c>
+      <c r="P50">
+        <v>1</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="str">
         <v xml:space="preserve">Gender parity in advanced education (distance from parity) </v>
       </c>
@@ -5540,8 +6145,17 @@
       <c r="N51">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O51">
+        <v>1</v>
+      </c>
+      <c r="P51">
+        <v>1</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="str">
         <v>Respect for academic freedom (0=low; 1=high)</v>
       </c>
@@ -5584,8 +6198,17 @@
       <c r="N52">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O52">
+        <v>1</v>
+      </c>
+      <c r="P52">
+        <v>1</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="str">
         <v>Years of tertiary schooling (years)</v>
       </c>
@@ -5628,8 +6251,17 @@
       <c r="N53">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O53">
+        <v>1</v>
+      </c>
+      <c r="P53">
+        <v>1</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>2</v>
       </c>
@@ -5672,8 +6304,17 @@
       <c r="N54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>3</v>
       </c>
@@ -5716,8 +6357,17 @@
       <c r="N55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -5760,8 +6410,17 @@
       <c r="N56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -5804,8 +6463,17 @@
       <c r="N57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -5848,8 +6516,17 @@
       <c r="N58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -5892,8 +6569,17 @@
       <c r="N59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -5936,8 +6622,17 @@
       <c r="N60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -5980,8 +6675,17 @@
       <c r="N61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -6024,8 +6728,17 @@
       <c r="N62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -6068,8 +6781,17 @@
       <c r="N63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>1</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>12</v>
       </c>
@@ -6110,6 +6832,15 @@
         <v>0</v>
       </c>
       <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
         <v>0</v>
       </c>
     </row>

--- a/IndicatorsForClusters.xlsx
+++ b/IndicatorsForClusters.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1c3256d208fb6548/Personlig/Aske Banke Consultancy/YALE/Metodeartikel_WorldDevelopmentJournal/WorldDevelopmentArticleGit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="344" documentId="8_{9856C943-DD01-465B-AD17-0E409E296684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25CE3741-CEC2-4E93-A54F-DAF1EC870D74}"/>
+  <xr:revisionPtr revIDLastSave="378" documentId="8_{9856C943-DD01-465B-AD17-0E409E296684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D1A4087-8AD9-4244-BD0C-2C8BE0F7DC61}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{726B2859-724A-4801-8E74-5A4E1AFAB973}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{726B2859-724A-4801-8E74-5A4E1AFAB973}"/>
   </bookViews>
   <sheets>
-    <sheet name="Experiment Descriptions" sheetId="2" r:id="rId1"/>
-    <sheet name="Experiments" sheetId="3" r:id="rId2"/>
-    <sheet name="Overview of indicators and DLS" sheetId="1" r:id="rId3"/>
+    <sheet name="Unscaled Experiments" sheetId="2" r:id="rId1"/>
+    <sheet name="Scaled Experiments" sheetId="5" r:id="rId2"/>
+    <sheet name="Experiments" sheetId="3" r:id="rId3"/>
+    <sheet name="Overview of indicators and DLS" sheetId="1" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -148,7 +149,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="77">
   <si>
     <t>SPI</t>
   </si>
@@ -376,12 +377,18 @@
   <si>
     <t>Clustering the whole world using BHN indicators led to too few clusters. Clustering only the countries present in the colonial data and the results are look promising</t>
   </si>
+  <si>
+    <t>These experiments were performed in a second round, where after imputation, the SPI indicators were scaled according to their scaling system. The new lag/lead imputation was used.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excluded due to exteme variation in the clustering </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -393,6 +400,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-0.499984740745262"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-0.249977111117893"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -523,7 +544,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -562,6 +583,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -574,38 +616,65 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1225,35 +1294,35 @@
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AY53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.28515625" customWidth="1"/>
+    <col min="2" max="2" width="35.33203125" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
-    <col min="5" max="16" width="4.28515625" customWidth="1"/>
-    <col min="19" max="19" width="8.85546875" customWidth="1"/>
+    <col min="5" max="16" width="4.33203125" customWidth="1"/>
+    <col min="19" max="19" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="26" t="s">
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="27"/>
+      <c r="J3" s="34"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
@@ -1267,7 +1336,7 @@
       <c r="W3" s="24"/>
       <c r="X3" s="24"/>
     </row>
-    <row r="4" spans="1:24" ht="221.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="221.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="15" t="s">
         <v>16</v>
       </c>
@@ -1325,7 +1394,7 @@
       <c r="W4" s="23"/>
       <c r="X4" s="23"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="str" cm="1">
         <f t="array" ref="B5:B15">_xlfn.UNIQUE('Overview of indicators and DLS'!C4:C67)</f>
         <v>Food &amp; Nutrition</v>
@@ -1394,7 +1463,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="str">
         <v>Health Care</v>
       </c>
@@ -1459,7 +1528,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="str">
         <v>Water</v>
       </c>
@@ -1524,7 +1593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="11" t="str">
         <v>Sanitation</v>
       </c>
@@ -1589,7 +1658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="11" t="str">
         <v>Food preparation</v>
       </c>
@@ -1654,7 +1723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B10" s="11" t="str">
         <v>Thermal comfort</v>
       </c>
@@ -1719,7 +1788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B11" s="11" t="str">
         <v>Non material / Non-DLS</v>
       </c>
@@ -1784,7 +1853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="str">
         <v>Education</v>
       </c>
@@ -1849,7 +1918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="str">
         <v>Social connectedness</v>
       </c>
@@ -1914,7 +1983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="str">
         <v>Housing</v>
       </c>
@@ -1979,7 +2048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="str">
         <v>Physical Connectedness</v>
       </c>
@@ -2047,7 +2116,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="11"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
@@ -2065,7 +2134,7 @@
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.3">
       <c r="B17" s="15" t="s">
         <v>33</v>
       </c>
@@ -2130,7 +2199,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.3">
       <c r="B18" s="11" t="s">
         <v>34</v>
       </c>
@@ -2195,7 +2264,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.3">
       <c r="B19" s="11" t="s">
         <v>35</v>
       </c>
@@ -2260,30 +2329,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>56</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28" t="s">
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="J21" s="28"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="28"/>
-      <c r="M21" s="28"/>
-      <c r="N21" s="28"/>
-      <c r="O21" s="28"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
       <c r="Q21" s="1" t="s">
         <v>59</v>
       </c>
@@ -2291,7 +2360,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:51" ht="90.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" ht="90.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1</v>
       </c>
@@ -2299,21 +2368,21 @@
         <f t="array" ref="B22:B36">TRANSPOSE(_xlfn.ANCHORARRAY(C4))</f>
         <v>BHN_FWB</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="30"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="32"/>
+      <c r="O22" s="32"/>
       <c r="Q22" s="25" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -2356,28 +2425,28 @@
       <c r="AX22" s="25"/>
       <c r="AY22" s="25"/>
     </row>
-    <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23" s="7" t="str">
         <v>BHN_FWB_AllExt</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
       <c r="Q23" s="25"/>
       <c r="R23" s="25"/>
       <c r="S23" s="25"/>
@@ -2414,28 +2483,28 @@
       <c r="AX23" s="25"/>
       <c r="AY23" s="25"/>
     </row>
-    <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24" s="7" t="str">
         <v>Few_indicators_closest_DLS_coverage</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
       <c r="Q24" s="25"/>
       <c r="R24" s="25"/>
       <c r="S24" s="25"/>
@@ -2472,28 +2541,28 @@
       <c r="AX24" s="25"/>
       <c r="AY24" s="25"/>
     </row>
-    <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25" s="7" t="str">
         <v>Few indicators_SPI_preferred</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="30"/>
-      <c r="O25" s="30"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
+      <c r="O25" s="32"/>
       <c r="Q25" s="25"/>
       <c r="R25" s="25"/>
       <c r="S25" s="25"/>
@@ -2522,28 +2591,28 @@
       <c r="AP25" s="25"/>
       <c r="AQ25" s="25"/>
     </row>
-    <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26" s="7" t="str">
         <v>No_non_DLS</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
-      <c r="O26" s="30"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
       <c r="Q26" s="25" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
@@ -2574,28 +2643,28 @@
       <c r="AP26" s="25"/>
       <c r="AQ26" s="25"/>
     </row>
-    <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27" s="7" t="str">
         <v>Only_%_of_pop</v>
       </c>
-      <c r="C27" s="32" t="s">
+      <c r="C27" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="30"/>
-      <c r="L27" s="30"/>
-      <c r="M27" s="30"/>
-      <c r="N27" s="30"/>
-      <c r="O27" s="30"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
+      <c r="N27" s="32"/>
+      <c r="O27" s="32"/>
       <c r="Q27" s="25"/>
       <c r="R27" s="25"/>
       <c r="S27" s="25"/>
@@ -2624,28 +2693,28 @@
       <c r="AP27" s="25"/>
       <c r="AQ27" s="25"/>
     </row>
-    <row r="28" spans="1:51" ht="65.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" s="17" t="str">
         <v>Few_indicators_closest_DLS_coverage_90</v>
       </c>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33"/>
-      <c r="N28" s="33"/>
-      <c r="O28" s="33"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
       <c r="Q28" s="25"/>
       <c r="R28" s="25"/>
       <c r="S28" s="25"/>
@@ -2676,28 +2745,28 @@
       <c r="AP28" s="25"/>
       <c r="AQ28" s="25"/>
     </row>
-    <row r="29" spans="1:51" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2</v>
       </c>
       <c r="B29" s="17" t="str">
         <v>Few indicators_SPI_preferred_90</v>
       </c>
-      <c r="C29" s="35" t="s">
+      <c r="C29" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="33"/>
-      <c r="N29" s="33"/>
-      <c r="O29" s="33"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
       <c r="Q29" s="25"/>
       <c r="R29" s="25"/>
       <c r="S29" s="25"/>
@@ -2726,28 +2795,28 @@
       <c r="AP29" s="25"/>
       <c r="AQ29" s="25"/>
     </row>
-    <row r="30" spans="1:51" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
       <c r="B30" s="17" t="str">
         <v>Few_indicators_closeDLS_subPrimSchool</v>
       </c>
-      <c r="C30" s="36" t="s">
+      <c r="C30" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
-      <c r="L30" s="33"/>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
-      <c r="O30" s="33"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
       <c r="Q30" s="25" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
@@ -2778,28 +2847,28 @@
       <c r="AP30" s="25"/>
       <c r="AQ30" s="25"/>
     </row>
-    <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
       <c r="B31" s="17" t="str">
         <v>No_non_DLS_90</v>
       </c>
-      <c r="C31" s="35" t="s">
+      <c r="C31" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="33"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="33"/>
-      <c r="N31" s="33"/>
-      <c r="O31" s="33"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
       <c r="Q31" s="25"/>
       <c r="R31" s="25"/>
       <c r="S31" s="25"/>
@@ -2828,28 +2897,28 @@
       <c r="AP31" s="25"/>
       <c r="AQ31" s="25"/>
     </row>
-    <row r="32" spans="1:51" ht="103.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" ht="103.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
       <c r="B32" s="17" t="str">
         <v>Few_Indicators_subWatSani</v>
       </c>
-      <c r="C32" s="35" t="s">
+      <c r="C32" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="33"/>
-      <c r="K32" s="33"/>
-      <c r="L32" s="33"/>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
-      <c r="O32" s="33"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
       <c r="Q32" s="25"/>
       <c r="R32" s="25"/>
       <c r="S32" s="25"/>
@@ -2880,28 +2949,28 @@
       <c r="AP32" s="25"/>
       <c r="AQ32" s="25"/>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>4</v>
       </c>
       <c r="B33" s="6" t="str">
         <v>Only_OPP</v>
       </c>
-      <c r="C33" s="37" t="s">
+      <c r="C33" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="37"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="37"/>
-      <c r="H33" s="37"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="34"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="34"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="27"/>
+      <c r="K33" s="27"/>
+      <c r="L33" s="27"/>
+      <c r="M33" s="27"/>
+      <c r="N33" s="27"/>
+      <c r="O33" s="27"/>
       <c r="Q33" s="25"/>
       <c r="R33" s="25"/>
       <c r="S33" s="25"/>
@@ -2930,23 +2999,23 @@
       <c r="AP33" s="25"/>
       <c r="AQ33" s="25"/>
     </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
       <c r="B34" s="6" t="str">
         <v>Baseline</v>
       </c>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-      <c r="O34" s="34"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="27"/>
+      <c r="J34" s="27"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="27"/>
+      <c r="N34" s="27"/>
+      <c r="O34" s="27"/>
       <c r="Q34" s="25"/>
       <c r="R34" s="25"/>
       <c r="S34" s="25"/>
@@ -2975,25 +3044,25 @@
       <c r="AP34" s="25"/>
       <c r="AQ34" s="25"/>
     </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:43" x14ac:dyDescent="0.3">
       <c r="B35" s="6" t="str">
         <v>No_nonDLS_limExt</v>
       </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34" t="s">
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
-      <c r="O35" s="34"/>
+      <c r="J35" s="27"/>
+      <c r="K35" s="27"/>
+      <c r="L35" s="27"/>
+      <c r="M35" s="27"/>
+      <c r="N35" s="27"/>
+      <c r="O35" s="27"/>
       <c r="Q35" s="25"/>
       <c r="R35" s="25"/>
       <c r="S35" s="25"/>
@@ -3022,25 +3091,25 @@
       <c r="AP35" s="25"/>
       <c r="AQ35" s="25"/>
     </row>
-    <row r="36" spans="1:43" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:43" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="str">
         <v>BHN</v>
       </c>
-      <c r="C36" s="38" t="s">
+      <c r="C36" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="34"/>
-      <c r="O36" s="34"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="27"/>
+      <c r="L36" s="27"/>
+      <c r="M36" s="27"/>
+      <c r="N36" s="27"/>
+      <c r="O36" s="27"/>
       <c r="Q36" s="25"/>
       <c r="R36" s="25"/>
       <c r="S36" s="25"/>
@@ -3069,7 +3138,7 @@
       <c r="AP36" s="25"/>
       <c r="AQ36" s="25"/>
     </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:43" x14ac:dyDescent="0.3">
       <c r="AB37" s="25"/>
       <c r="AC37" s="25"/>
       <c r="AD37" s="25"/>
@@ -3087,7 +3156,7 @@
       <c r="AP37" s="25"/>
       <c r="AQ37" s="25"/>
     </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:43" x14ac:dyDescent="0.3">
       <c r="AB38" s="25"/>
       <c r="AC38" s="25"/>
       <c r="AD38" s="25"/>
@@ -3105,7 +3174,7 @@
       <c r="AP38" s="25"/>
       <c r="AQ38" s="25"/>
     </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:43" x14ac:dyDescent="0.3">
       <c r="AB39" s="25"/>
       <c r="AC39" s="25"/>
       <c r="AD39" s="25"/>
@@ -3123,7 +3192,7 @@
       <c r="AP39" s="25"/>
       <c r="AQ39" s="25"/>
     </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:43" x14ac:dyDescent="0.3">
       <c r="AB40" s="25"/>
       <c r="AC40" s="25"/>
       <c r="AD40" s="25"/>
@@ -3141,7 +3210,7 @@
       <c r="AP40" s="25"/>
       <c r="AQ40" s="25"/>
     </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:43" x14ac:dyDescent="0.3">
       <c r="AB41" s="25"/>
       <c r="AC41" s="25"/>
       <c r="AD41" s="25"/>
@@ -3159,7 +3228,7 @@
       <c r="AP41" s="25"/>
       <c r="AQ41" s="25"/>
     </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:43" x14ac:dyDescent="0.3">
       <c r="AB42" s="25" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
@@ -3179,7 +3248,7 @@
       <c r="AP42" s="25"/>
       <c r="AQ42" s="25"/>
     </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:43" x14ac:dyDescent="0.3">
       <c r="AB43" s="25"/>
       <c r="AC43" s="25"/>
       <c r="AD43" s="25"/>
@@ -3197,7 +3266,7 @@
       <c r="AP43" s="25"/>
       <c r="AQ43" s="25"/>
     </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:43" x14ac:dyDescent="0.3">
       <c r="AB44" s="25"/>
       <c r="AC44" s="25"/>
       <c r="AD44" s="25"/>
@@ -3215,7 +3284,7 @@
       <c r="AP44" s="25"/>
       <c r="AQ44" s="25"/>
     </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:43" x14ac:dyDescent="0.3">
       <c r="AB45" s="25"/>
       <c r="AC45" s="25"/>
       <c r="AD45" s="25"/>
@@ -3233,7 +3302,7 @@
       <c r="AP45" s="25"/>
       <c r="AQ45" s="25"/>
     </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:43" x14ac:dyDescent="0.3">
       <c r="AB46" s="25"/>
       <c r="AC46" s="25"/>
       <c r="AD46" s="25"/>
@@ -3251,7 +3320,7 @@
       <c r="AP46" s="25"/>
       <c r="AQ46" s="25"/>
     </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:43" x14ac:dyDescent="0.3">
       <c r="AB47" s="25"/>
       <c r="AC47" s="25"/>
       <c r="AD47" s="25"/>
@@ -3269,7 +3338,7 @@
       <c r="AP47" s="25"/>
       <c r="AQ47" s="25"/>
     </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:43" x14ac:dyDescent="0.3">
       <c r="AB48" s="25"/>
       <c r="AC48" s="25"/>
       <c r="AD48" s="25"/>
@@ -3287,7 +3356,7 @@
       <c r="AP48" s="25"/>
       <c r="AQ48" s="25"/>
     </row>
-    <row r="49" spans="28:43" x14ac:dyDescent="0.25">
+    <row r="49" spans="28:43" x14ac:dyDescent="0.3">
       <c r="AB49" s="25"/>
       <c r="AC49" s="25"/>
       <c r="AD49" s="25"/>
@@ -3305,7 +3374,7 @@
       <c r="AP49" s="25"/>
       <c r="AQ49" s="25"/>
     </row>
-    <row r="50" spans="28:43" x14ac:dyDescent="0.25">
+    <row r="50" spans="28:43" x14ac:dyDescent="0.3">
       <c r="AB50" s="25"/>
       <c r="AC50" s="25"/>
       <c r="AD50" s="25"/>
@@ -3323,7 +3392,7 @@
       <c r="AP50" s="25"/>
       <c r="AQ50" s="25"/>
     </row>
-    <row r="51" spans="28:43" x14ac:dyDescent="0.25">
+    <row r="51" spans="28:43" x14ac:dyDescent="0.3">
       <c r="AB51" s="25"/>
       <c r="AC51" s="25"/>
       <c r="AD51" s="25"/>
@@ -3341,7 +3410,7 @@
       <c r="AP51" s="25"/>
       <c r="AQ51" s="25"/>
     </row>
-    <row r="52" spans="28:43" x14ac:dyDescent="0.25">
+    <row r="52" spans="28:43" x14ac:dyDescent="0.3">
       <c r="AB52" s="25"/>
       <c r="AC52" s="25"/>
       <c r="AD52" s="25"/>
@@ -3359,7 +3428,7 @@
       <c r="AP52" s="25"/>
       <c r="AQ52" s="25"/>
     </row>
-    <row r="53" spans="28:43" x14ac:dyDescent="0.25">
+    <row r="53" spans="28:43" x14ac:dyDescent="0.3">
       <c r="AB53" s="25"/>
       <c r="AC53" s="25"/>
       <c r="AD53" s="25"/>
@@ -3379,6 +3448,32 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="I24:O24"/>
+    <mergeCell ref="I25:O25"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I21:O21"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="I22:O22"/>
+    <mergeCell ref="I23:O23"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="I28:O28"/>
+    <mergeCell ref="I29:O29"/>
+    <mergeCell ref="AR22:AY24"/>
+    <mergeCell ref="Q30:AA36"/>
+    <mergeCell ref="AB32:AQ41"/>
+    <mergeCell ref="I26:O26"/>
+    <mergeCell ref="I27:O27"/>
+    <mergeCell ref="I32:O32"/>
+    <mergeCell ref="I33:O33"/>
+    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="AB22:AQ27"/>
+    <mergeCell ref="Q22:AA25"/>
     <mergeCell ref="AB42:AQ53"/>
     <mergeCell ref="C30:H30"/>
     <mergeCell ref="AB28:AQ31"/>
@@ -3395,32 +3490,2205 @@
     <mergeCell ref="C36:H36"/>
     <mergeCell ref="I36:O36"/>
     <mergeCell ref="C28:H28"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5:Q15">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6396A80-D06A-496C-A485-2D593CA0EE86}">
+  <sheetPr>
+    <tabColor theme="2" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:AY53"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="35.33203125" customWidth="1"/>
+    <col min="4" max="4" width="6" customWidth="1"/>
+    <col min="5" max="16" width="4.33203125" customWidth="1"/>
+    <col min="19" max="19" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B3" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="33"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="T3" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="U3" s="24"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="24"/>
+      <c r="X3" s="24"/>
+    </row>
+    <row r="4" spans="1:24" ht="221.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="42" t="str" cm="1">
+        <f t="array" ref="C4:Q4">Experiments!C1:Q1</f>
+        <v>BHN_FWB</v>
+      </c>
+      <c r="D4" s="46" t="str">
+        <v>BHN_FWB_AllExt</v>
+      </c>
+      <c r="E4" s="43" t="str">
+        <v>Few_indicators_closest_DLS_coverage</v>
+      </c>
+      <c r="F4" s="43" t="str">
+        <v>Few indicators_SPI_preferred</v>
+      </c>
+      <c r="G4" s="43" t="str">
+        <v>No_non_DLS</v>
+      </c>
+      <c r="H4" s="40" t="str">
+        <v>Only_%_of_pop</v>
+      </c>
+      <c r="I4" s="42" t="str">
+        <v>Few_indicators_closest_DLS_coverage_90</v>
+      </c>
+      <c r="J4" s="43" t="str">
+        <v>Few indicators_SPI_preferred_90</v>
+      </c>
+      <c r="K4" s="39" t="str">
+        <v>Few_indicators_closeDLS_subPrimSchool</v>
+      </c>
+      <c r="L4" s="39" t="str">
+        <v>No_non_DLS_90</v>
+      </c>
+      <c r="M4" s="39" t="str">
+        <v>Few_Indicators_subWatSani</v>
+      </c>
+      <c r="N4" s="39" t="str">
+        <v>Only_OPP</v>
+      </c>
+      <c r="O4" s="9" t="str">
+        <v>Baseline</v>
+      </c>
+      <c r="P4" s="39" t="str">
+        <v>No_nonDLS_limExt</v>
+      </c>
+      <c r="Q4" s="39" t="str">
+        <v>BHN</v>
+      </c>
+      <c r="T4" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="U4" s="47"/>
+      <c r="V4" s="47"/>
+      <c r="W4" s="47"/>
+      <c r="X4" s="47"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B5" s="11" t="str" cm="1">
+        <f t="array" ref="B5:B15">_xlfn.UNIQUE('Overview of indicators and DLS'!C4:C67)</f>
+        <v>Food &amp; Nutrition</v>
+      </c>
+      <c r="C5" s="18" cm="1">
+        <f t="array" ref="C5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!C$2:C$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="D5" s="44" cm="1">
+        <f t="array" ref="D5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!D$2:D$64=1))</f>
+        <v>5</v>
+      </c>
+      <c r="E5" s="44" cm="1">
+        <f t="array" ref="E5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!E$2:E$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="F5" s="44" cm="1">
+        <f t="array" ref="F5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!F$2:F$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="G5" s="44" cm="1">
+        <f t="array" ref="G5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!G$2:G$64=1))</f>
+        <v>5</v>
+      </c>
+      <c r="H5" s="11" cm="1">
+        <f t="array" ref="H5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!H$2:H$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="I5" s="18" cm="1">
+        <f t="array" ref="I5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!I$2:I$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="J5" s="44" cm="1">
+        <f t="array" ref="J5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!J$2:J$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="K5" s="8" cm="1">
+        <f t="array" ref="K5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!K$2:K$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="L5" s="8" cm="1">
+        <f t="array" ref="L5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!L$2:L$64=1))</f>
+        <v>5</v>
+      </c>
+      <c r="M5" s="8" cm="1">
+        <f t="array" ref="M5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!M$2:M$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="N5" s="8" cm="1">
+        <f t="array" ref="N5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!N$2:N$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="8" cm="1">
+        <f t="array" ref="O5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!O$2:O$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="P5" s="8" cm="1">
+        <f t="array" ref="P5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!P$2:P$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="Q5" s="8" cm="1">
+        <f t="array" ref="Q5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!Q$2:Q$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="R5" s="16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="11" t="str">
+        <v>Health Care</v>
+      </c>
+      <c r="C6" s="18" cm="1">
+        <f t="array" ref="C6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!C$2:C$64=1))</f>
+        <v>7</v>
+      </c>
+      <c r="D6" s="44" cm="1">
+        <f t="array" ref="D6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!D$2:D$64=1))</f>
+        <v>10</v>
+      </c>
+      <c r="E6" s="44" cm="1">
+        <f t="array" ref="E6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!E$2:E$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="F6" s="44" cm="1">
+        <f t="array" ref="F6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!F$2:F$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="G6" s="44" cm="1">
+        <f t="array" ref="G6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!G$2:G$64=1))</f>
+        <v>10</v>
+      </c>
+      <c r="H6" s="11" cm="1">
+        <f t="array" ref="H6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!H$2:H$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="I6" s="18" cm="1">
+        <f t="array" ref="I6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!I$2:I$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="J6" s="44" cm="1">
+        <f t="array" ref="J6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!J$2:J$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="K6" s="8" cm="1">
+        <f t="array" ref="K6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!K$2:K$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="L6" s="8" cm="1">
+        <f t="array" ref="L6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!L$2:L$64=1))</f>
+        <v>10</v>
+      </c>
+      <c r="M6" s="8" cm="1">
+        <f t="array" ref="M6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!M$2:M$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="N6" s="8" cm="1">
+        <f t="array" ref="N6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!N$2:N$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="8" cm="1">
+        <f t="array" ref="O6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!O$2:O$64=1))</f>
+        <v>7</v>
+      </c>
+      <c r="P6" s="8" cm="1">
+        <f t="array" ref="P6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!P$2:P$64=1))</f>
+        <v>7</v>
+      </c>
+      <c r="Q6" s="8" cm="1">
+        <f t="array" ref="Q6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!Q$2:Q$64=1))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="11" t="str">
+        <v>Water</v>
+      </c>
+      <c r="C7" s="18" cm="1">
+        <f t="array" ref="C7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!C$2:C$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="D7" s="44" cm="1">
+        <f t="array" ref="D7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!D$2:D$64=1))</f>
+        <v>4</v>
+      </c>
+      <c r="E7" s="44" cm="1">
+        <f t="array" ref="E7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!E$2:E$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="F7" s="44" cm="1">
+        <f t="array" ref="F7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!F$2:F$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="G7" s="44" cm="1">
+        <f t="array" ref="G7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!G$2:G$64=1))</f>
+        <v>4</v>
+      </c>
+      <c r="H7" s="11" cm="1">
+        <f t="array" ref="H7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!H$2:H$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="I7" s="18" cm="1">
+        <f t="array" ref="I7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!I$2:I$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="J7" s="44" cm="1">
+        <f t="array" ref="J7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!J$2:J$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="K7" s="8" cm="1">
+        <f t="array" ref="K7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!K$2:K$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="L7" s="8" cm="1">
+        <f t="array" ref="L7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!L$2:L$64=1))</f>
+        <v>4</v>
+      </c>
+      <c r="M7" s="8" cm="1">
+        <f t="array" ref="M7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!M$2:M$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="N7" s="8" cm="1">
+        <f t="array" ref="N7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!N$2:N$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="8" cm="1">
+        <f t="array" ref="O7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!O$2:O$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="P7" s="8" cm="1">
+        <f t="array" ref="P7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!P$2:P$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="Q7" s="8" cm="1">
+        <f t="array" ref="Q7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!Q$2:Q$64=1))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="11" t="str">
+        <v>Sanitation</v>
+      </c>
+      <c r="C8" s="18" cm="1">
+        <f t="array" ref="C8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!C$2:C$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="D8" s="44" cm="1">
+        <f t="array" ref="D8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!D$2:D$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="E8" s="44" cm="1">
+        <f t="array" ref="E8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!E$2:E$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="F8" s="44" cm="1">
+        <f t="array" ref="F8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!F$2:F$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="G8" s="44" cm="1">
+        <f t="array" ref="G8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!G$2:G$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="H8" s="11" cm="1">
+        <f t="array" ref="H8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!H$2:H$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="I8" s="18" cm="1">
+        <f t="array" ref="I8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!I$2:I$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="J8" s="44" cm="1">
+        <f t="array" ref="J8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!J$2:J$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="K8" s="8" cm="1">
+        <f t="array" ref="K8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!K$2:K$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="L8" s="8" cm="1">
+        <f t="array" ref="L8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!L$2:L$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="M8" s="8" cm="1">
+        <f t="array" ref="M8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!M$2:M$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="N8" s="8" cm="1">
+        <f t="array" ref="N8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!N$2:N$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="8" cm="1">
+        <f t="array" ref="O8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!O$2:O$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="P8" s="8" cm="1">
+        <f t="array" ref="P8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!P$2:P$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="Q8" s="8" cm="1">
+        <f t="array" ref="Q8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!Q$2:Q$64=1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="11" t="str">
+        <v>Food preparation</v>
+      </c>
+      <c r="C9" s="18" cm="1">
+        <f t="array" ref="C9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!C$2:C$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="D9" s="44" cm="1">
+        <f t="array" ref="D9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!D$2:D$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="E9" s="44" cm="1">
+        <f t="array" ref="E9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!E$2:E$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="F9" s="44" cm="1">
+        <f t="array" ref="F9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!F$2:F$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="G9" s="44" cm="1">
+        <f t="array" ref="G9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!G$2:G$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="H9" s="11" cm="1">
+        <f t="array" ref="H9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!H$2:H$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="I9" s="18" cm="1">
+        <f t="array" ref="I9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!I$2:I$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="J9" s="44" cm="1">
+        <f t="array" ref="J9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!J$2:J$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="K9" s="8" cm="1">
+        <f t="array" ref="K9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!K$2:K$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="L9" s="8" cm="1">
+        <f t="array" ref="L9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!L$2:L$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="M9" s="8" cm="1">
+        <f t="array" ref="M9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!M$2:M$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="N9" s="8" cm="1">
+        <f t="array" ref="N9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!N$2:N$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="8" cm="1">
+        <f t="array" ref="O9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!O$2:O$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="P9" s="8" cm="1">
+        <f t="array" ref="P9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!P$2:P$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="Q9" s="8" cm="1">
+        <f t="array" ref="Q9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!Q$2:Q$64=1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B10" s="11" t="str">
+        <v>Thermal comfort</v>
+      </c>
+      <c r="C10" s="18" cm="1">
+        <f t="array" ref="C10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!C$2:C$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="D10" s="44" cm="1">
+        <f t="array" ref="D10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!D$2:D$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="E10" s="44" cm="1">
+        <f t="array" ref="E10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!E$2:E$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="F10" s="44" cm="1">
+        <f t="array" ref="F10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!F$2:F$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="G10" s="44" cm="1">
+        <f t="array" ref="G10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!G$2:G$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="H10" s="11" cm="1">
+        <f t="array" ref="H10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!H$2:H$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="I10" s="18" cm="1">
+        <f t="array" ref="I10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!I$2:I$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="J10" s="44" cm="1">
+        <f t="array" ref="J10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!J$2:J$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="K10" s="8" cm="1">
+        <f t="array" ref="K10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!K$2:K$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="L10" s="8" cm="1">
+        <f t="array" ref="L10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!L$2:L$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="M10" s="8" cm="1">
+        <f t="array" ref="M10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!M$2:M$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="N10" s="8" cm="1">
+        <f t="array" ref="N10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!N$2:N$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="8" cm="1">
+        <f t="array" ref="O10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!O$2:O$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="P10" s="8" cm="1">
+        <f t="array" ref="P10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!P$2:P$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="Q10" s="8" cm="1">
+        <f t="array" ref="Q10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!Q$2:Q$64=1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B11" s="11" t="str">
+        <v>Non material / Non-DLS</v>
+      </c>
+      <c r="C11" s="18" cm="1">
+        <f t="array" ref="C11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!C$2:C$64=1))</f>
+        <v>9</v>
+      </c>
+      <c r="D11" s="44" cm="1">
+        <f t="array" ref="D11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!D$2:D$64=1))</f>
+        <v>10</v>
+      </c>
+      <c r="E11" s="44" cm="1">
+        <f t="array" ref="E11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!E$2:E$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="44" cm="1">
+        <f t="array" ref="F11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!F$2:F$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="44" cm="1">
+        <f t="array" ref="G11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!G$2:G$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="11" cm="1">
+        <f t="array" ref="H11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!H$2:H$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="I11" s="18" cm="1">
+        <f t="array" ref="I11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!I$2:I$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="44" cm="1">
+        <f t="array" ref="J11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!J$2:J$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="8" cm="1">
+        <f t="array" ref="K11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!K$2:K$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="8" cm="1">
+        <f t="array" ref="L11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!L$2:L$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="8" cm="1">
+        <f t="array" ref="M11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!M$2:M$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="8" cm="1">
+        <f t="array" ref="N11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!N$2:N$64=1))</f>
+        <v>15</v>
+      </c>
+      <c r="O11" s="8" cm="1">
+        <f t="array" ref="O11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!O$2:O$64=1))</f>
+        <v>24</v>
+      </c>
+      <c r="P11" s="8" cm="1">
+        <f t="array" ref="P11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!P$2:P$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8" cm="1">
+        <f t="array" ref="Q11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!Q$2:Q$64=1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B12" s="11" t="str">
+        <v>Education</v>
+      </c>
+      <c r="C12" s="18" cm="1">
+        <f t="array" ref="C12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!C$2:C$64=1))</f>
+        <v>4</v>
+      </c>
+      <c r="D12" s="44" cm="1">
+        <f t="array" ref="D12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!D$2:D$64=1))</f>
+        <v>5</v>
+      </c>
+      <c r="E12" s="44" cm="1">
+        <f t="array" ref="E12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!E$2:E$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="F12" s="44" cm="1">
+        <f t="array" ref="F12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!F$2:F$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="G12" s="44" cm="1">
+        <f t="array" ref="G12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!G$2:G$64=1))</f>
+        <v>9</v>
+      </c>
+      <c r="H12" s="11" cm="1">
+        <f t="array" ref="H12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!H$2:H$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="I12" s="18" cm="1">
+        <f t="array" ref="I12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!I$2:I$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="J12" s="44" cm="1">
+        <f t="array" ref="J12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!J$2:J$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="K12" s="8" cm="1">
+        <f t="array" ref="K12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!K$2:K$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="L12" s="8" cm="1">
+        <f t="array" ref="L12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!L$2:L$64=1))</f>
+        <v>9</v>
+      </c>
+      <c r="M12" s="8" cm="1">
+        <f t="array" ref="M12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!M$2:M$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="N12" s="8" cm="1">
+        <f t="array" ref="N12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!N$2:N$64=1))</f>
+        <v>4</v>
+      </c>
+      <c r="O12" s="8" cm="1">
+        <f t="array" ref="O12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!O$2:O$64=1))</f>
+        <v>8</v>
+      </c>
+      <c r="P12" s="8" cm="1">
+        <f t="array" ref="P12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!P$2:P$64=1))</f>
+        <v>8</v>
+      </c>
+      <c r="Q12" s="8" cm="1">
+        <f t="array" ref="Q12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!Q$2:Q$64=1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B13" s="11" t="str">
+        <v>Social connectedness</v>
+      </c>
+      <c r="C13" s="18" cm="1">
+        <f t="array" ref="C13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!C$2:C$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="D13" s="44" cm="1">
+        <f t="array" ref="D13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!D$2:D$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="E13" s="44" cm="1">
+        <f t="array" ref="E13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!E$2:E$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="F13" s="44" cm="1">
+        <f t="array" ref="F13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!F$2:F$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="G13" s="44" cm="1">
+        <f t="array" ref="G13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!G$2:G$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="H13" s="11" cm="1">
+        <f t="array" ref="H13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!H$2:H$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="I13" s="18" cm="1">
+        <f t="array" ref="I13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!I$2:I$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="J13" s="44" cm="1">
+        <f t="array" ref="J13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!J$2:J$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="K13" s="8" cm="1">
+        <f t="array" ref="K13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!K$2:K$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="L13" s="8" cm="1">
+        <f t="array" ref="L13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!L$2:L$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="M13" s="8" cm="1">
+        <f t="array" ref="M13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!M$2:M$64=1))</f>
+        <v>2</v>
+      </c>
+      <c r="N13" s="8" cm="1">
+        <f t="array" ref="N13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!N$2:N$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="8" cm="1">
+        <f t="array" ref="O13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!O$2:O$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="P13" s="8" cm="1">
+        <f t="array" ref="P13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!P$2:P$64=1))</f>
+        <v>3</v>
+      </c>
+      <c r="Q13" s="8" cm="1">
+        <f t="array" ref="Q13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!Q$2:Q$64=1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B14" s="11" t="str">
+        <v>Housing</v>
+      </c>
+      <c r="C14" s="18" cm="1">
+        <f t="array" ref="C14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!C$2:C$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="44" cm="1">
+        <f t="array" ref="D14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!D$2:D$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="E14" s="44" cm="1">
+        <f t="array" ref="E14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!E$2:E$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="F14" s="44" cm="1">
+        <f t="array" ref="F14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!F$2:F$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="44" cm="1">
+        <f t="array" ref="G14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!G$2:G$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="11" cm="1">
+        <f t="array" ref="H14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!H$2:H$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="I14" s="18" cm="1">
+        <f t="array" ref="I14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!I$2:I$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="J14" s="44" cm="1">
+        <f t="array" ref="J14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!J$2:J$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="K14" s="8" cm="1">
+        <f t="array" ref="K14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!K$2:K$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="L14" s="8" cm="1">
+        <f t="array" ref="L14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!L$2:L$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="M14" s="8" cm="1">
+        <f t="array" ref="M14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!M$2:M$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="N14" s="8" cm="1">
+        <f t="array" ref="N14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!N$2:N$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="8" cm="1">
+        <f t="array" ref="O14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!O$2:O$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="8" cm="1">
+        <f t="array" ref="P14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!P$2:P$64=1))</f>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="8" cm="1">
+        <f t="array" ref="Q14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!Q$2:Q$64=1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B15" s="13" t="str">
+        <v>Physical Connectedness</v>
+      </c>
+      <c r="C15" s="19" cm="1">
+        <f t="array" ref="C15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!C$2:C$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="12" cm="1">
+        <f t="array" ref="D15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!D$2:D$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="12" cm="1">
+        <f t="array" ref="E15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!E$2:E$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="12" cm="1">
+        <f t="array" ref="F15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!F$2:F$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="12" cm="1">
+        <f t="array" ref="G15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!G$2:G$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="13" cm="1">
+        <f t="array" ref="H15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!H$2:H$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="19" cm="1">
+        <f t="array" ref="I15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!I$2:I$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="12" cm="1">
+        <f t="array" ref="J15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!J$2:J$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="12" cm="1">
+        <f t="array" ref="K15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!K$2:K$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="12" cm="1">
+        <f t="array" ref="L15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!L$2:L$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="12" cm="1">
+        <f t="array" ref="M15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!M$2:M$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="12" cm="1">
+        <f t="array" ref="N15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!N$2:N$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="12" cm="1">
+        <f t="array" ref="O15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!O$2:O$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="12" cm="1">
+        <f t="array" ref="P15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!P$2:P$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="12" cm="1">
+        <f t="array" ref="Q15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!Q$2:Q$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="R15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B16" s="11"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+    </row>
+    <row r="17" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="B17" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="20">
+        <f>SUM(C5:C15)</f>
+        <v>33</v>
+      </c>
+      <c r="D17" s="45">
+        <f>SUM(D5:D15)</f>
+        <v>44</v>
+      </c>
+      <c r="E17" s="45">
+        <f t="shared" ref="E17:Q17" si="0">SUM(E5:E15)</f>
+        <v>11</v>
+      </c>
+      <c r="F17" s="45">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="G17" s="45">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="H17" s="15">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="I17" s="20">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="J17" s="45">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="K17" s="14">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="L17" s="14">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="M17" s="14">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="N17" s="14">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="O17" s="14">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="P17" s="14">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="Q17" s="14">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="B18" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="18">
+        <f>SUM(Experiments!C2:C53)</f>
+        <v>33</v>
+      </c>
+      <c r="D18" s="44">
+        <f>SUM(Experiments!D2:D53)</f>
+        <v>33</v>
+      </c>
+      <c r="E18" s="44">
+        <f>SUM(Experiments!E2:E53)</f>
+        <v>7</v>
+      </c>
+      <c r="F18" s="44">
+        <f>SUM(Experiments!F2:F53)</f>
+        <v>10</v>
+      </c>
+      <c r="G18" s="44">
+        <f>SUM(Experiments!G2:G53)</f>
+        <v>28</v>
+      </c>
+      <c r="H18" s="11">
+        <f>SUM(Experiments!H2:H53)</f>
+        <v>11</v>
+      </c>
+      <c r="I18" s="18">
+        <f>SUM(Experiments!I2:I53)</f>
+        <v>7</v>
+      </c>
+      <c r="J18" s="44">
+        <f>SUM(Experiments!J2:J53)</f>
+        <v>10</v>
+      </c>
+      <c r="K18" s="8">
+        <f>SUM(Experiments!K2:K53)</f>
+        <v>8</v>
+      </c>
+      <c r="L18" s="8">
+        <f>SUM(Experiments!L2:L53)</f>
+        <v>28</v>
+      </c>
+      <c r="M18" s="8">
+        <f>SUM(Experiments!M2:M53)</f>
+        <v>9</v>
+      </c>
+      <c r="N18" s="8">
+        <f>SUM(Experiments!N2:N53)</f>
+        <v>19</v>
+      </c>
+      <c r="O18" s="8">
+        <f>SUM(Experiments!O2:O53)</f>
+        <v>52</v>
+      </c>
+      <c r="P18" s="8">
+        <f>SUM(Experiments!P2:P53)</f>
+        <v>28</v>
+      </c>
+      <c r="Q18" s="8">
+        <f>SUM(Experiments!Q2:Q53)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="B19" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="18">
+        <f>SUM(Experiments!C54:C64)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="44">
+        <f>SUM(Experiments!D54:D64)</f>
+        <v>11</v>
+      </c>
+      <c r="E19" s="44">
+        <f>SUM(Experiments!E54:E64)</f>
+        <v>4</v>
+      </c>
+      <c r="F19" s="44">
+        <f>SUM(Experiments!F54:F64)</f>
+        <v>1</v>
+      </c>
+      <c r="G19" s="44">
+        <f>SUM(Experiments!G54:G64)</f>
+        <v>10</v>
+      </c>
+      <c r="H19" s="11">
+        <f>SUM(Experiments!H54:H64)</f>
+        <v>4</v>
+      </c>
+      <c r="I19" s="18">
+        <f>SUM(Experiments!I54:I64)</f>
+        <v>4</v>
+      </c>
+      <c r="J19" s="44">
+        <f>SUM(Experiments!J54:J64)</f>
+        <v>1</v>
+      </c>
+      <c r="K19" s="8">
+        <f>SUM(Experiments!K54:K64)</f>
+        <v>3</v>
+      </c>
+      <c r="L19" s="8">
+        <f>SUM(Experiments!L54:L64)</f>
+        <v>10</v>
+      </c>
+      <c r="M19" s="8">
+        <f>SUM(Experiments!M54:M64)</f>
+        <v>2</v>
+      </c>
+      <c r="N19" s="8">
+        <f>SUM(Experiments!N54:N64)</f>
+        <v>0</v>
+      </c>
+      <c r="O19" s="8">
+        <f>SUM(Experiments!O54:O64)</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="8">
+        <f>SUM(Experiments!P54:P64)</f>
+        <v>1</v>
+      </c>
+      <c r="Q19" s="8">
+        <f>SUM(Experiments!Q54:Q64)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
+      <c r="Q21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AR21" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:51" ht="90.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22" s="7" t="str" cm="1">
+        <f t="array" ref="B22:B36">TRANSPOSE(_xlfn.ANCHORARRAY(C4))</f>
+        <v>BHN_FWB</v>
+      </c>
+      <c r="C22" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="32"/>
+      <c r="O22" s="32"/>
+      <c r="Q22" s="25"/>
+      <c r="R22" s="25"/>
+      <c r="S22" s="25"/>
+      <c r="T22" s="25"/>
+      <c r="U22" s="25"/>
+      <c r="V22" s="25"/>
+      <c r="W22" s="25"/>
+      <c r="X22" s="25"/>
+      <c r="Y22" s="25"/>
+      <c r="Z22" s="25"/>
+      <c r="AA22" s="25"/>
+      <c r="AB22" s="25"/>
+      <c r="AC22" s="25"/>
+      <c r="AD22" s="25"/>
+      <c r="AE22" s="25"/>
+      <c r="AF22" s="25"/>
+      <c r="AG22" s="25"/>
+      <c r="AH22" s="25"/>
+      <c r="AI22" s="25"/>
+      <c r="AJ22" s="25"/>
+      <c r="AK22" s="25"/>
+      <c r="AL22" s="25"/>
+      <c r="AM22" s="25"/>
+      <c r="AN22" s="25"/>
+      <c r="AO22" s="25"/>
+      <c r="AP22" s="25"/>
+      <c r="AQ22" s="25"/>
+      <c r="AR22" s="25" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AS22" s="25"/>
+      <c r="AT22" s="25"/>
+      <c r="AU22" s="25"/>
+      <c r="AV22" s="25"/>
+      <c r="AW22" s="25"/>
+      <c r="AX22" s="25"/>
+      <c r="AY22" s="25"/>
+    </row>
+    <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23" s="48" t="str">
+        <v>BHN_FWB_AllExt</v>
+      </c>
+      <c r="C23" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="25"/>
+      <c r="V23" s="25"/>
+      <c r="W23" s="25"/>
+      <c r="X23" s="25"/>
+      <c r="Y23" s="25"/>
+      <c r="Z23" s="25"/>
+      <c r="AA23" s="25"/>
+      <c r="AB23" s="25"/>
+      <c r="AC23" s="25"/>
+      <c r="AD23" s="25"/>
+      <c r="AE23" s="25"/>
+      <c r="AF23" s="25"/>
+      <c r="AG23" s="25"/>
+      <c r="AH23" s="25"/>
+      <c r="AI23" s="25"/>
+      <c r="AJ23" s="25"/>
+      <c r="AK23" s="25"/>
+      <c r="AL23" s="25"/>
+      <c r="AM23" s="25"/>
+      <c r="AN23" s="25"/>
+      <c r="AO23" s="25"/>
+      <c r="AP23" s="25"/>
+      <c r="AQ23" s="25"/>
+      <c r="AR23" s="25"/>
+      <c r="AS23" s="25"/>
+      <c r="AT23" s="25"/>
+      <c r="AU23" s="25"/>
+      <c r="AV23" s="25"/>
+      <c r="AW23" s="25"/>
+      <c r="AX23" s="25"/>
+      <c r="AY23" s="25"/>
+    </row>
+    <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24" s="7" t="str">
+        <v>Few_indicators_closest_DLS_coverage</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="25"/>
+      <c r="U24" s="25"/>
+      <c r="V24" s="25"/>
+      <c r="W24" s="25"/>
+      <c r="X24" s="25"/>
+      <c r="Y24" s="25"/>
+      <c r="Z24" s="25"/>
+      <c r="AA24" s="25"/>
+      <c r="AB24" s="25"/>
+      <c r="AC24" s="25"/>
+      <c r="AD24" s="25"/>
+      <c r="AE24" s="25"/>
+      <c r="AF24" s="25"/>
+      <c r="AG24" s="25"/>
+      <c r="AH24" s="25"/>
+      <c r="AI24" s="25"/>
+      <c r="AJ24" s="25"/>
+      <c r="AK24" s="25"/>
+      <c r="AL24" s="25"/>
+      <c r="AM24" s="25"/>
+      <c r="AN24" s="25"/>
+      <c r="AO24" s="25"/>
+      <c r="AP24" s="25"/>
+      <c r="AQ24" s="25"/>
+      <c r="AR24" s="25"/>
+      <c r="AS24" s="25"/>
+      <c r="AT24" s="25"/>
+      <c r="AU24" s="25"/>
+      <c r="AV24" s="25"/>
+      <c r="AW24" s="25"/>
+      <c r="AX24" s="25"/>
+      <c r="AY24" s="25"/>
+    </row>
+    <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25" s="7" t="str">
+        <v>Few indicators_SPI_preferred</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
+      <c r="O25" s="32"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="25"/>
+      <c r="U25" s="25"/>
+      <c r="V25" s="25"/>
+      <c r="W25" s="25"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="25"/>
+      <c r="Z25" s="25"/>
+      <c r="AA25" s="25"/>
+      <c r="AB25" s="25"/>
+      <c r="AC25" s="25"/>
+      <c r="AD25" s="25"/>
+      <c r="AE25" s="25"/>
+      <c r="AF25" s="25"/>
+      <c r="AG25" s="25"/>
+      <c r="AH25" s="25"/>
+      <c r="AI25" s="25"/>
+      <c r="AJ25" s="25"/>
+      <c r="AK25" s="25"/>
+      <c r="AL25" s="25"/>
+      <c r="AM25" s="25"/>
+      <c r="AN25" s="25"/>
+      <c r="AO25" s="25"/>
+      <c r="AP25" s="25"/>
+      <c r="AQ25" s="25"/>
+    </row>
+    <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>1</v>
+      </c>
+      <c r="B26" s="7" t="str">
+        <v>No_non_DLS</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25"/>
+      <c r="U26" s="25"/>
+      <c r="V26" s="25"/>
+      <c r="W26" s="25"/>
+      <c r="X26" s="25"/>
+      <c r="Y26" s="25"/>
+      <c r="Z26" s="25"/>
+      <c r="AA26" s="25"/>
+      <c r="AB26" s="25"/>
+      <c r="AC26" s="25"/>
+      <c r="AD26" s="25"/>
+      <c r="AE26" s="25"/>
+      <c r="AF26" s="25"/>
+      <c r="AG26" s="25"/>
+      <c r="AH26" s="25"/>
+      <c r="AI26" s="25"/>
+      <c r="AJ26" s="25"/>
+      <c r="AK26" s="25"/>
+      <c r="AL26" s="25"/>
+      <c r="AM26" s="25"/>
+      <c r="AN26" s="25"/>
+      <c r="AO26" s="25"/>
+      <c r="AP26" s="25"/>
+      <c r="AQ26" s="25"/>
+    </row>
+    <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27" s="48" t="str">
+        <v>Only_%_of_pop</v>
+      </c>
+      <c r="C27" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
+      <c r="N27" s="32"/>
+      <c r="O27" s="32"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="25"/>
+      <c r="T27" s="25"/>
+      <c r="U27" s="25"/>
+      <c r="V27" s="25"/>
+      <c r="W27" s="25"/>
+      <c r="X27" s="25"/>
+      <c r="Y27" s="25"/>
+      <c r="Z27" s="25"/>
+      <c r="AA27" s="25"/>
+      <c r="AB27" s="25"/>
+      <c r="AC27" s="25"/>
+      <c r="AD27" s="25"/>
+      <c r="AE27" s="25"/>
+      <c r="AF27" s="25"/>
+      <c r="AG27" s="25"/>
+      <c r="AH27" s="25"/>
+      <c r="AI27" s="25"/>
+      <c r="AJ27" s="25"/>
+      <c r="AK27" s="25"/>
+      <c r="AL27" s="25"/>
+      <c r="AM27" s="25"/>
+      <c r="AN27" s="25"/>
+      <c r="AO27" s="25"/>
+      <c r="AP27" s="25"/>
+      <c r="AQ27" s="25"/>
+    </row>
+    <row r="28" spans="1:51" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>2</v>
+      </c>
+      <c r="B28" s="17" t="str">
+        <v>Few_indicators_closest_DLS_coverage_90</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+      <c r="Q28" s="25"/>
+      <c r="R28" s="25"/>
+      <c r="S28" s="25"/>
+      <c r="T28" s="25"/>
+      <c r="U28" s="25"/>
+      <c r="V28" s="25"/>
+      <c r="W28" s="25"/>
+      <c r="X28" s="25"/>
+      <c r="Y28" s="25"/>
+      <c r="Z28" s="25"/>
+      <c r="AA28" s="25"/>
+      <c r="AB28" s="25"/>
+      <c r="AC28" s="25"/>
+      <c r="AD28" s="25"/>
+      <c r="AE28" s="25"/>
+      <c r="AF28" s="25"/>
+      <c r="AG28" s="25"/>
+      <c r="AH28" s="25"/>
+      <c r="AI28" s="25"/>
+      <c r="AJ28" s="25"/>
+      <c r="AK28" s="25"/>
+      <c r="AL28" s="25"/>
+      <c r="AM28" s="25"/>
+      <c r="AN28" s="25"/>
+      <c r="AO28" s="25"/>
+      <c r="AP28" s="25"/>
+      <c r="AQ28" s="25"/>
+    </row>
+    <row r="29" spans="1:51" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29" s="17" t="str">
+        <v>Few indicators_SPI_preferred_90</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="25"/>
+      <c r="S29" s="25"/>
+      <c r="T29" s="25"/>
+      <c r="U29" s="25"/>
+      <c r="V29" s="25"/>
+      <c r="W29" s="25"/>
+      <c r="X29" s="25"/>
+      <c r="Y29" s="25"/>
+      <c r="Z29" s="25"/>
+      <c r="AA29" s="25"/>
+      <c r="AB29" s="25"/>
+      <c r="AC29" s="25"/>
+      <c r="AD29" s="25"/>
+      <c r="AE29" s="25"/>
+      <c r="AF29" s="25"/>
+      <c r="AG29" s="25"/>
+      <c r="AH29" s="25"/>
+      <c r="AI29" s="25"/>
+      <c r="AJ29" s="25"/>
+      <c r="AK29" s="25"/>
+      <c r="AL29" s="25"/>
+      <c r="AM29" s="25"/>
+      <c r="AN29" s="25"/>
+      <c r="AO29" s="25"/>
+      <c r="AP29" s="25"/>
+      <c r="AQ29" s="25"/>
+    </row>
+    <row r="30" spans="1:51" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>3</v>
+      </c>
+      <c r="B30" s="17" t="str">
+        <v>Few_indicators_closeDLS_subPrimSchool</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
+      <c r="Q30" s="25"/>
+      <c r="R30" s="25"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="25"/>
+      <c r="U30" s="25"/>
+      <c r="V30" s="25"/>
+      <c r="W30" s="25"/>
+      <c r="X30" s="25"/>
+      <c r="Y30" s="25"/>
+      <c r="Z30" s="25"/>
+      <c r="AA30" s="25"/>
+      <c r="AB30" s="25"/>
+      <c r="AC30" s="25"/>
+      <c r="AD30" s="25"/>
+      <c r="AE30" s="25"/>
+      <c r="AF30" s="25"/>
+      <c r="AG30" s="25"/>
+      <c r="AH30" s="25"/>
+      <c r="AI30" s="25"/>
+      <c r="AJ30" s="25"/>
+      <c r="AK30" s="25"/>
+      <c r="AL30" s="25"/>
+      <c r="AM30" s="25"/>
+      <c r="AN30" s="25"/>
+      <c r="AO30" s="25"/>
+      <c r="AP30" s="25"/>
+      <c r="AQ30" s="25"/>
+    </row>
+    <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>3</v>
+      </c>
+      <c r="B31" s="51" t="str">
+        <v>No_non_DLS_90</v>
+      </c>
+      <c r="C31" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52" t="s">
+        <v>76</v>
+      </c>
+      <c r="J31" s="52"/>
+      <c r="K31" s="52"/>
+      <c r="L31" s="52"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="52"/>
+      <c r="O31" s="52"/>
+      <c r="Q31" s="25"/>
+      <c r="R31" s="25"/>
+      <c r="S31" s="25"/>
+      <c r="T31" s="25"/>
+      <c r="U31" s="25"/>
+      <c r="V31" s="25"/>
+      <c r="W31" s="25"/>
+      <c r="X31" s="25"/>
+      <c r="Y31" s="25"/>
+      <c r="Z31" s="25"/>
+      <c r="AA31" s="25"/>
+      <c r="AB31" s="25"/>
+      <c r="AC31" s="25"/>
+      <c r="AD31" s="25"/>
+      <c r="AE31" s="25"/>
+      <c r="AF31" s="25"/>
+      <c r="AG31" s="25"/>
+      <c r="AH31" s="25"/>
+      <c r="AI31" s="25"/>
+      <c r="AJ31" s="25"/>
+      <c r="AK31" s="25"/>
+      <c r="AL31" s="25"/>
+      <c r="AM31" s="25"/>
+      <c r="AN31" s="25"/>
+      <c r="AO31" s="25"/>
+      <c r="AP31" s="25"/>
+      <c r="AQ31" s="25"/>
+    </row>
+    <row r="32" spans="1:51" ht="103.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32" s="51" t="str">
+        <v>Few_Indicators_subWatSani</v>
+      </c>
+      <c r="C32" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="Q32" s="25"/>
+      <c r="R32" s="25"/>
+      <c r="S32" s="25"/>
+      <c r="T32" s="25"/>
+      <c r="U32" s="25"/>
+      <c r="V32" s="25"/>
+      <c r="W32" s="25"/>
+      <c r="X32" s="25"/>
+      <c r="Y32" s="25"/>
+      <c r="Z32" s="25"/>
+      <c r="AA32" s="25"/>
+      <c r="AB32" s="25"/>
+      <c r="AC32" s="25"/>
+      <c r="AD32" s="25"/>
+      <c r="AE32" s="25"/>
+      <c r="AF32" s="25"/>
+      <c r="AG32" s="25"/>
+      <c r="AH32" s="25"/>
+      <c r="AI32" s="25"/>
+      <c r="AJ32" s="25"/>
+      <c r="AK32" s="25"/>
+      <c r="AL32" s="25"/>
+      <c r="AM32" s="25"/>
+      <c r="AN32" s="25"/>
+      <c r="AO32" s="25"/>
+      <c r="AP32" s="25"/>
+      <c r="AQ32" s="25"/>
+    </row>
+    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33" s="53" t="str">
+        <v>Only_OPP</v>
+      </c>
+      <c r="C33" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="27"/>
+      <c r="K33" s="27"/>
+      <c r="L33" s="27"/>
+      <c r="M33" s="27"/>
+      <c r="N33" s="27"/>
+      <c r="O33" s="27"/>
+      <c r="Q33" s="25"/>
+      <c r="R33" s="25"/>
+      <c r="S33" s="25"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="25"/>
+      <c r="V33" s="25"/>
+      <c r="W33" s="25"/>
+      <c r="X33" s="25"/>
+      <c r="Y33" s="25"/>
+      <c r="Z33" s="25"/>
+      <c r="AA33" s="25"/>
+      <c r="AB33" s="25"/>
+      <c r="AC33" s="25"/>
+      <c r="AD33" s="25"/>
+      <c r="AE33" s="25"/>
+      <c r="AF33" s="25"/>
+      <c r="AG33" s="25"/>
+      <c r="AH33" s="25"/>
+      <c r="AI33" s="25"/>
+      <c r="AJ33" s="25"/>
+      <c r="AK33" s="25"/>
+      <c r="AL33" s="25"/>
+      <c r="AM33" s="25"/>
+      <c r="AN33" s="25"/>
+      <c r="AO33" s="25"/>
+      <c r="AP33" s="25"/>
+      <c r="AQ33" s="25"/>
+    </row>
+    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="B34" s="6" t="str">
+        <v>Baseline</v>
+      </c>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="27"/>
+      <c r="J34" s="27"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="27"/>
+      <c r="N34" s="27"/>
+      <c r="O34" s="27"/>
+      <c r="Q34" s="25"/>
+      <c r="R34" s="25"/>
+      <c r="S34" s="25"/>
+      <c r="T34" s="25"/>
+      <c r="U34" s="25"/>
+      <c r="V34" s="25"/>
+      <c r="W34" s="25"/>
+      <c r="X34" s="25"/>
+      <c r="Y34" s="25"/>
+      <c r="Z34" s="25"/>
+      <c r="AA34" s="25"/>
+      <c r="AB34" s="25"/>
+      <c r="AC34" s="25"/>
+      <c r="AD34" s="25"/>
+      <c r="AE34" s="25"/>
+      <c r="AF34" s="25"/>
+      <c r="AG34" s="25"/>
+      <c r="AH34" s="25"/>
+      <c r="AI34" s="25"/>
+      <c r="AJ34" s="25"/>
+      <c r="AK34" s="25"/>
+      <c r="AL34" s="25"/>
+      <c r="AM34" s="25"/>
+      <c r="AN34" s="25"/>
+      <c r="AO34" s="25"/>
+      <c r="AP34" s="25"/>
+      <c r="AQ34" s="25"/>
+    </row>
+    <row r="35" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="B35" s="53" t="str">
+        <v>No_nonDLS_limExt</v>
+      </c>
+      <c r="C35" s="55"/>
+      <c r="D35" s="55"/>
+      <c r="E35" s="55"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="55"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="J35" s="55"/>
+      <c r="K35" s="55"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="55"/>
+      <c r="N35" s="55"/>
+      <c r="O35" s="55"/>
+      <c r="Q35" s="25"/>
+      <c r="R35" s="25"/>
+      <c r="S35" s="25"/>
+      <c r="T35" s="25"/>
+      <c r="U35" s="25"/>
+      <c r="V35" s="25"/>
+      <c r="W35" s="25"/>
+      <c r="X35" s="25"/>
+      <c r="Y35" s="25"/>
+      <c r="Z35" s="25"/>
+      <c r="AA35" s="25"/>
+      <c r="AB35" s="25"/>
+      <c r="AC35" s="25"/>
+      <c r="AD35" s="25"/>
+      <c r="AE35" s="25"/>
+      <c r="AF35" s="25"/>
+      <c r="AG35" s="25"/>
+      <c r="AH35" s="25"/>
+      <c r="AI35" s="25"/>
+      <c r="AJ35" s="25"/>
+      <c r="AK35" s="25"/>
+      <c r="AL35" s="25"/>
+      <c r="AM35" s="25"/>
+      <c r="AN35" s="25"/>
+      <c r="AO35" s="25"/>
+      <c r="AP35" s="25"/>
+      <c r="AQ35" s="25"/>
+    </row>
+    <row r="36" spans="1:43" ht="76.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="6" t="str">
+        <v>BHN</v>
+      </c>
+      <c r="C36" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="27"/>
+      <c r="L36" s="27"/>
+      <c r="M36" s="27"/>
+      <c r="N36" s="27"/>
+      <c r="O36" s="27"/>
+      <c r="Q36" s="25"/>
+      <c r="R36" s="25"/>
+      <c r="S36" s="25"/>
+      <c r="T36" s="25"/>
+      <c r="U36" s="25"/>
+      <c r="V36" s="25"/>
+      <c r="W36" s="25"/>
+      <c r="X36" s="25"/>
+      <c r="Y36" s="25"/>
+      <c r="Z36" s="25"/>
+      <c r="AA36" s="25"/>
+      <c r="AB36" s="25"/>
+      <c r="AC36" s="25"/>
+      <c r="AD36" s="25"/>
+      <c r="AE36" s="25"/>
+      <c r="AF36" s="25"/>
+      <c r="AG36" s="25"/>
+      <c r="AH36" s="25"/>
+      <c r="AI36" s="25"/>
+      <c r="AJ36" s="25"/>
+      <c r="AK36" s="25"/>
+      <c r="AL36" s="25"/>
+      <c r="AM36" s="25"/>
+      <c r="AN36" s="25"/>
+      <c r="AO36" s="25"/>
+      <c r="AP36" s="25"/>
+      <c r="AQ36" s="25"/>
+    </row>
+    <row r="37" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB37" s="25"/>
+      <c r="AC37" s="25"/>
+      <c r="AD37" s="25"/>
+      <c r="AE37" s="25"/>
+      <c r="AF37" s="25"/>
+      <c r="AG37" s="25"/>
+      <c r="AH37" s="25"/>
+      <c r="AI37" s="25"/>
+      <c r="AJ37" s="25"/>
+      <c r="AK37" s="25"/>
+      <c r="AL37" s="25"/>
+      <c r="AM37" s="25"/>
+      <c r="AN37" s="25"/>
+      <c r="AO37" s="25"/>
+      <c r="AP37" s="25"/>
+      <c r="AQ37" s="25"/>
+    </row>
+    <row r="38" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB38" s="25"/>
+      <c r="AC38" s="25"/>
+      <c r="AD38" s="25"/>
+      <c r="AE38" s="25"/>
+      <c r="AF38" s="25"/>
+      <c r="AG38" s="25"/>
+      <c r="AH38" s="25"/>
+      <c r="AI38" s="25"/>
+      <c r="AJ38" s="25"/>
+      <c r="AK38" s="25"/>
+      <c r="AL38" s="25"/>
+      <c r="AM38" s="25"/>
+      <c r="AN38" s="25"/>
+      <c r="AO38" s="25"/>
+      <c r="AP38" s="25"/>
+      <c r="AQ38" s="25"/>
+    </row>
+    <row r="39" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB39" s="25"/>
+      <c r="AC39" s="25"/>
+      <c r="AD39" s="25"/>
+      <c r="AE39" s="25"/>
+      <c r="AF39" s="25"/>
+      <c r="AG39" s="25"/>
+      <c r="AH39" s="25"/>
+      <c r="AI39" s="25"/>
+      <c r="AJ39" s="25"/>
+      <c r="AK39" s="25"/>
+      <c r="AL39" s="25"/>
+      <c r="AM39" s="25"/>
+      <c r="AN39" s="25"/>
+      <c r="AO39" s="25"/>
+      <c r="AP39" s="25"/>
+      <c r="AQ39" s="25"/>
+    </row>
+    <row r="40" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB40" s="25"/>
+      <c r="AC40" s="25"/>
+      <c r="AD40" s="25"/>
+      <c r="AE40" s="25"/>
+      <c r="AF40" s="25"/>
+      <c r="AG40" s="25"/>
+      <c r="AH40" s="25"/>
+      <c r="AI40" s="25"/>
+      <c r="AJ40" s="25"/>
+      <c r="AK40" s="25"/>
+      <c r="AL40" s="25"/>
+      <c r="AM40" s="25"/>
+      <c r="AN40" s="25"/>
+      <c r="AO40" s="25"/>
+      <c r="AP40" s="25"/>
+      <c r="AQ40" s="25"/>
+    </row>
+    <row r="41" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB41" s="25"/>
+      <c r="AC41" s="25"/>
+      <c r="AD41" s="25"/>
+      <c r="AE41" s="25"/>
+      <c r="AF41" s="25"/>
+      <c r="AG41" s="25"/>
+      <c r="AH41" s="25"/>
+      <c r="AI41" s="25"/>
+      <c r="AJ41" s="25"/>
+      <c r="AK41" s="25"/>
+      <c r="AL41" s="25"/>
+      <c r="AM41" s="25"/>
+      <c r="AN41" s="25"/>
+      <c r="AO41" s="25"/>
+      <c r="AP41" s="25"/>
+      <c r="AQ41" s="25"/>
+    </row>
+    <row r="42" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB42" s="25" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC42" s="25"/>
+      <c r="AD42" s="25"/>
+      <c r="AE42" s="25"/>
+      <c r="AF42" s="25"/>
+      <c r="AG42" s="25"/>
+      <c r="AH42" s="25"/>
+      <c r="AI42" s="25"/>
+      <c r="AJ42" s="25"/>
+      <c r="AK42" s="25"/>
+      <c r="AL42" s="25"/>
+      <c r="AM42" s="25"/>
+      <c r="AN42" s="25"/>
+      <c r="AO42" s="25"/>
+      <c r="AP42" s="25"/>
+      <c r="AQ42" s="25"/>
+    </row>
+    <row r="43" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB43" s="25"/>
+      <c r="AC43" s="25"/>
+      <c r="AD43" s="25"/>
+      <c r="AE43" s="25"/>
+      <c r="AF43" s="25"/>
+      <c r="AG43" s="25"/>
+      <c r="AH43" s="25"/>
+      <c r="AI43" s="25"/>
+      <c r="AJ43" s="25"/>
+      <c r="AK43" s="25"/>
+      <c r="AL43" s="25"/>
+      <c r="AM43" s="25"/>
+      <c r="AN43" s="25"/>
+      <c r="AO43" s="25"/>
+      <c r="AP43" s="25"/>
+      <c r="AQ43" s="25"/>
+    </row>
+    <row r="44" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB44" s="25"/>
+      <c r="AC44" s="25"/>
+      <c r="AD44" s="25"/>
+      <c r="AE44" s="25"/>
+      <c r="AF44" s="25"/>
+      <c r="AG44" s="25"/>
+      <c r="AH44" s="25"/>
+      <c r="AI44" s="25"/>
+      <c r="AJ44" s="25"/>
+      <c r="AK44" s="25"/>
+      <c r="AL44" s="25"/>
+      <c r="AM44" s="25"/>
+      <c r="AN44" s="25"/>
+      <c r="AO44" s="25"/>
+      <c r="AP44" s="25"/>
+      <c r="AQ44" s="25"/>
+    </row>
+    <row r="45" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB45" s="25"/>
+      <c r="AC45" s="25"/>
+      <c r="AD45" s="25"/>
+      <c r="AE45" s="25"/>
+      <c r="AF45" s="25"/>
+      <c r="AG45" s="25"/>
+      <c r="AH45" s="25"/>
+      <c r="AI45" s="25"/>
+      <c r="AJ45" s="25"/>
+      <c r="AK45" s="25"/>
+      <c r="AL45" s="25"/>
+      <c r="AM45" s="25"/>
+      <c r="AN45" s="25"/>
+      <c r="AO45" s="25"/>
+      <c r="AP45" s="25"/>
+      <c r="AQ45" s="25"/>
+    </row>
+    <row r="46" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB46" s="25"/>
+      <c r="AC46" s="25"/>
+      <c r="AD46" s="25"/>
+      <c r="AE46" s="25"/>
+      <c r="AF46" s="25"/>
+      <c r="AG46" s="25"/>
+      <c r="AH46" s="25"/>
+      <c r="AI46" s="25"/>
+      <c r="AJ46" s="25"/>
+      <c r="AK46" s="25"/>
+      <c r="AL46" s="25"/>
+      <c r="AM46" s="25"/>
+      <c r="AN46" s="25"/>
+      <c r="AO46" s="25"/>
+      <c r="AP46" s="25"/>
+      <c r="AQ46" s="25"/>
+    </row>
+    <row r="47" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB47" s="25"/>
+      <c r="AC47" s="25"/>
+      <c r="AD47" s="25"/>
+      <c r="AE47" s="25"/>
+      <c r="AF47" s="25"/>
+      <c r="AG47" s="25"/>
+      <c r="AH47" s="25"/>
+      <c r="AI47" s="25"/>
+      <c r="AJ47" s="25"/>
+      <c r="AK47" s="25"/>
+      <c r="AL47" s="25"/>
+      <c r="AM47" s="25"/>
+      <c r="AN47" s="25"/>
+      <c r="AO47" s="25"/>
+      <c r="AP47" s="25"/>
+      <c r="AQ47" s="25"/>
+    </row>
+    <row r="48" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB48" s="25"/>
+      <c r="AC48" s="25"/>
+      <c r="AD48" s="25"/>
+      <c r="AE48" s="25"/>
+      <c r="AF48" s="25"/>
+      <c r="AG48" s="25"/>
+      <c r="AH48" s="25"/>
+      <c r="AI48" s="25"/>
+      <c r="AJ48" s="25"/>
+      <c r="AK48" s="25"/>
+      <c r="AL48" s="25"/>
+      <c r="AM48" s="25"/>
+      <c r="AN48" s="25"/>
+      <c r="AO48" s="25"/>
+      <c r="AP48" s="25"/>
+      <c r="AQ48" s="25"/>
+    </row>
+    <row r="49" spans="28:43" x14ac:dyDescent="0.3">
+      <c r="AB49" s="25"/>
+      <c r="AC49" s="25"/>
+      <c r="AD49" s="25"/>
+      <c r="AE49" s="25"/>
+      <c r="AF49" s="25"/>
+      <c r="AG49" s="25"/>
+      <c r="AH49" s="25"/>
+      <c r="AI49" s="25"/>
+      <c r="AJ49" s="25"/>
+      <c r="AK49" s="25"/>
+      <c r="AL49" s="25"/>
+      <c r="AM49" s="25"/>
+      <c r="AN49" s="25"/>
+      <c r="AO49" s="25"/>
+      <c r="AP49" s="25"/>
+      <c r="AQ49" s="25"/>
+    </row>
+    <row r="50" spans="28:43" x14ac:dyDescent="0.3">
+      <c r="AB50" s="25"/>
+      <c r="AC50" s="25"/>
+      <c r="AD50" s="25"/>
+      <c r="AE50" s="25"/>
+      <c r="AF50" s="25"/>
+      <c r="AG50" s="25"/>
+      <c r="AH50" s="25"/>
+      <c r="AI50" s="25"/>
+      <c r="AJ50" s="25"/>
+      <c r="AK50" s="25"/>
+      <c r="AL50" s="25"/>
+      <c r="AM50" s="25"/>
+      <c r="AN50" s="25"/>
+      <c r="AO50" s="25"/>
+      <c r="AP50" s="25"/>
+      <c r="AQ50" s="25"/>
+    </row>
+    <row r="51" spans="28:43" x14ac:dyDescent="0.3">
+      <c r="AB51" s="25"/>
+      <c r="AC51" s="25"/>
+      <c r="AD51" s="25"/>
+      <c r="AE51" s="25"/>
+      <c r="AF51" s="25"/>
+      <c r="AG51" s="25"/>
+      <c r="AH51" s="25"/>
+      <c r="AI51" s="25"/>
+      <c r="AJ51" s="25"/>
+      <c r="AK51" s="25"/>
+      <c r="AL51" s="25"/>
+      <c r="AM51" s="25"/>
+      <c r="AN51" s="25"/>
+      <c r="AO51" s="25"/>
+      <c r="AP51" s="25"/>
+      <c r="AQ51" s="25"/>
+    </row>
+    <row r="52" spans="28:43" x14ac:dyDescent="0.3">
+      <c r="AB52" s="25"/>
+      <c r="AC52" s="25"/>
+      <c r="AD52" s="25"/>
+      <c r="AE52" s="25"/>
+      <c r="AF52" s="25"/>
+      <c r="AG52" s="25"/>
+      <c r="AH52" s="25"/>
+      <c r="AI52" s="25"/>
+      <c r="AJ52" s="25"/>
+      <c r="AK52" s="25"/>
+      <c r="AL52" s="25"/>
+      <c r="AM52" s="25"/>
+      <c r="AN52" s="25"/>
+      <c r="AO52" s="25"/>
+      <c r="AP52" s="25"/>
+      <c r="AQ52" s="25"/>
+    </row>
+    <row r="53" spans="28:43" x14ac:dyDescent="0.3">
+      <c r="AB53" s="25"/>
+      <c r="AC53" s="25"/>
+      <c r="AD53" s="25"/>
+      <c r="AE53" s="25"/>
+      <c r="AF53" s="25"/>
+      <c r="AG53" s="25"/>
+      <c r="AH53" s="25"/>
+      <c r="AI53" s="25"/>
+      <c r="AJ53" s="25"/>
+      <c r="AK53" s="25"/>
+      <c r="AL53" s="25"/>
+      <c r="AM53" s="25"/>
+      <c r="AN53" s="25"/>
+      <c r="AO53" s="25"/>
+      <c r="AP53" s="25"/>
+      <c r="AQ53" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="43">
+    <mergeCell ref="AB42:AQ53"/>
+    <mergeCell ref="T4:X4"/>
+    <mergeCell ref="AB32:AQ41"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="I33:O33"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="I35:O35"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="AB28:AQ31"/>
+    <mergeCell ref="C29:H29"/>
+    <mergeCell ref="I29:O29"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="I30:O30"/>
+    <mergeCell ref="Q30:AA36"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="I31:O31"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="I32:O32"/>
+    <mergeCell ref="I26:O26"/>
+    <mergeCell ref="Q26:AA29"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="I27:O27"/>
+    <mergeCell ref="C28:H28"/>
     <mergeCell ref="I28:O28"/>
-    <mergeCell ref="I29:O29"/>
+    <mergeCell ref="Q22:AA25"/>
+    <mergeCell ref="AB22:AQ27"/>
     <mergeCell ref="AR22:AY24"/>
-    <mergeCell ref="Q30:AA36"/>
-    <mergeCell ref="AB32:AQ41"/>
-    <mergeCell ref="I26:O26"/>
-    <mergeCell ref="I27:O27"/>
-    <mergeCell ref="I32:O32"/>
-    <mergeCell ref="I33:O33"/>
-    <mergeCell ref="I34:O34"/>
-    <mergeCell ref="AB22:AQ27"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="I23:O23"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="I24:O24"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="I25:O25"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C3:H3"/>
     <mergeCell ref="I3:J3"/>
+    <mergeCell ref="C21:H21"/>
     <mergeCell ref="I21:O21"/>
     <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C23:H23"/>
     <mergeCell ref="I22:O22"/>
-    <mergeCell ref="I23:O23"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="Q22:AA25"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="I24:O24"/>
-    <mergeCell ref="I25:O25"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:Q15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
@@ -3431,27 +5699,27 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82213708-7016-4142-ADAA-C3FCCAD91158}">
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:Q65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="62.5703125" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="1" max="1" width="62.5546875" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" customWidth="1"/>
+    <col min="11" max="11" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -3504,7 +5772,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="str" cm="1">
         <f t="array" ref="A2:A53">TRANSPOSE('[1]1990-2020 Time-series data'!$Y$2:$BX$2)</f>
         <v xml:space="preserve">Child stunting (% of pop.) </v>
@@ -3558,7 +5826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="str">
         <v>Deaths from infectious diseases (deaths/100,000)</v>
       </c>
@@ -3611,7 +5879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="str">
         <v xml:space="preserve">Maternal mortality  (deaths/100,000 live births) </v>
       </c>
@@ -3664,7 +5932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="str">
         <v xml:space="preserve">Nutritional deficiencies (% of pop.) </v>
       </c>
@@ -3717,7 +5985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="str">
         <v xml:space="preserve">Diet low in fruits and vegetables (0=low risk; 100=high risk) </v>
       </c>
@@ -3770,7 +6038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="str">
         <v xml:space="preserve">Child mortality (deaths/1,000 live births) </v>
       </c>
@@ -3823,7 +6091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="str">
         <v xml:space="preserve">No access to a handwashing facility (0=low risk; 100=high risk) </v>
       </c>
@@ -3876,7 +6144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="str">
         <v>Deaths from unsafe water, sanitation and hygiene (deaths/100,000)</v>
       </c>
@@ -3929,7 +6197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="str">
         <v xml:space="preserve">Improved sanitation (proportion of pop.) </v>
       </c>
@@ -3982,7 +6250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="str">
         <v xml:space="preserve">Improved water source (proportion of pop.) </v>
       </c>
@@ -4035,7 +6303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="str">
         <v>Deaths from household air pollution (deaths/100,000)</v>
       </c>
@@ -4088,7 +6356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="str">
         <v xml:space="preserve">Prevalence of cooking with coal/biomass (proportion of pop.) </v>
       </c>
@@ -4141,7 +6409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="str">
         <v xml:space="preserve">Access to electricity (% of pop.) </v>
       </c>
@@ -4194,7 +6462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="str">
         <v>Deaths from road injuries (deaths/100,000)</v>
       </c>
@@ -4247,7 +6515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="str">
         <v xml:space="preserve">Political violence (0=no violence; 4=violence often) </v>
       </c>
@@ -4300,7 +6568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="str">
         <v>Political killings and torture (0=low freedom; 1=high freedom)</v>
       </c>
@@ -4353,7 +6621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="str">
         <v xml:space="preserve">Intimate partner violence against women (% of women aged 15+) </v>
       </c>
@@ -4406,7 +6674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="str">
         <v>Interpersonal violence  (deaths/100,000)</v>
       </c>
@@ -4459,7 +6727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="str">
         <v xml:space="preserve">Population with no education (proportion of pop.) </v>
       </c>
@@ -4512,7 +6780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="str">
         <v xml:space="preserve">Gender parity in basic education (distance from parity) </v>
       </c>
@@ -4565,7 +6833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="str">
         <v xml:space="preserve">Equal access to quality education (0=unequal; 4=equal) </v>
       </c>
@@ -4618,7 +6886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="str">
         <v>Mean years of schooling (years)</v>
       </c>
@@ -4671,7 +6939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="str">
         <v>Alternative sources of information (0=low; 1=high)</v>
       </c>
@@ -4724,7 +6992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="str">
         <v xml:space="preserve">Internet users (% of pop.) </v>
       </c>
@@ -4777,7 +7045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="str">
         <v xml:space="preserve">Mobile and landline telephone subscriptions (subscriptions/100 people) </v>
       </c>
@@ -4830,7 +7098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="str">
         <v>Life expectancy at 60 (years)</v>
       </c>
@@ -4883,7 +7151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="str">
         <v>Premature deaths from non-communicable diseases (deaths/100,000)</v>
       </c>
@@ -4936,7 +7204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="str">
         <v xml:space="preserve">Equal access to quality healthcare (0=unequal; 4=equal) </v>
       </c>
@@ -4989,7 +7257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="str">
         <v xml:space="preserve">Universal health coverage (% of pop.) </v>
       </c>
@@ -5042,7 +7310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="str">
         <v>Deaths from outdoor air pollution (deaths/100,000)</v>
       </c>
@@ -5095,7 +7363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="str">
         <v>Particulate matter (2.5) pollution (mean annual exposure, µg/m3)</v>
       </c>
@@ -5148,7 +7416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="str">
         <v>Deaths from lead exposure (deaths/100,000)</v>
       </c>
@@ -5201,7 +7469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="str">
         <v>Species protection (0=low; 100=high)</v>
       </c>
@@ -5254,7 +7522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="str">
         <v xml:space="preserve">Freedom of religion (0=no freedom; 4=full freedom) </v>
       </c>
@@ -5307,7 +7575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="str">
         <v xml:space="preserve">Property rights for women (0=no rights; 5=full rights) </v>
       </c>
@@ -5360,7 +7628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="str">
         <v xml:space="preserve">Freedom of assembly (0=no freedom; 4=full freedom) </v>
       </c>
@@ -5413,7 +7681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="str">
         <v>Access to justice (0=nonexistent; 1=observed)</v>
       </c>
@@ -5466,7 +7734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="str">
         <v>Freedom of discussion (0=low; 1=high)</v>
       </c>
@@ -5519,7 +7787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="str">
         <v>Political rights (1=full rights; 7=no rights)</v>
       </c>
@@ -5572,7 +7840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="str">
         <v>Public sector corruption (0=low corruption; 1=high corruption)</v>
       </c>
@@ -5625,7 +7893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="str">
         <v>Freedom of domestic movement (0=low; 1=high)</v>
       </c>
@@ -5678,7 +7946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="str">
         <v>Satisfied demand for contraception (% satisfied demand)</v>
       </c>
@@ -5731,7 +7999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="str">
         <v>Early marriage (% of married women aged 15-19)</v>
       </c>
@@ -5784,7 +8052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="str">
         <v xml:space="preserve">Vulnerable employment (% of total employment) </v>
       </c>
@@ -5837,7 +8105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="str">
         <v>Equal protection of social groups (0=low; 1=high)</v>
       </c>
@@ -5890,7 +8158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="str">
         <v>Equal access to power (0=low; 1=high)</v>
       </c>
@@ -5943,7 +8211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="str">
         <v xml:space="preserve">Power distributed by sexual orientation (0=extremely unequal; 3=equal) </v>
       </c>
@@ -5996,7 +8264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="str">
         <v xml:space="preserve">Access to public services distributed by social group (0=extremely unequal; 4=equal) </v>
       </c>
@@ -6049,7 +8317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="str">
         <v xml:space="preserve">Population with advanced education (proportion of pop.) </v>
       </c>
@@ -6102,7 +8370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="str">
         <v xml:space="preserve">Gender parity in advanced education (distance from parity) </v>
       </c>
@@ -6155,7 +8423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="str">
         <v>Respect for academic freedom (0=low; 1=high)</v>
       </c>
@@ -6208,7 +8476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="str">
         <v>Years of tertiary schooling (years)</v>
       </c>
@@ -6261,7 +8529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>2</v>
       </c>
@@ -6314,7 +8582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>3</v>
       </c>
@@ -6367,7 +8635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -6420,7 +8688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -6473,7 +8741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -6526,7 +8794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -6579,7 +8847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -6632,7 +8900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -6685,7 +8953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -6738,7 +9006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -6791,7 +9059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>12</v>
       </c>
@@ -6844,7 +9112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>27</v>
       </c>
@@ -6854,19 +9122,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF7AB827-50C5-4E2E-BFA5-DFF2F72F5247}">
   <sheetPr>
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A3:D67"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="61.7109375" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="61.6640625" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -6877,7 +9145,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -6889,7 +9157,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="str">
         <v>Deaths from infectious diseases (deaths/100,000)</v>
       </c>
@@ -6897,7 +9165,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="str">
         <v xml:space="preserve">Maternal mortality  (deaths/100,000 live births) </v>
       </c>
@@ -6905,7 +9173,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="str">
         <v xml:space="preserve">Nutritional deficiencies (% of pop.) </v>
       </c>
@@ -6913,7 +9181,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="str">
         <v xml:space="preserve">Diet low in fruits and vegetables (0=low risk; 100=high risk) </v>
       </c>
@@ -6921,7 +9189,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="str">
         <v xml:space="preserve">Child mortality (deaths/1,000 live births) </v>
       </c>
@@ -6929,7 +9197,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="str">
         <v xml:space="preserve">No access to a handwashing facility (0=low risk; 100=high risk) </v>
       </c>
@@ -6937,7 +9205,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="str">
         <v>Deaths from unsafe water, sanitation and hygiene (deaths/100,000)</v>
       </c>
@@ -6945,7 +9213,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="str">
         <v xml:space="preserve">Improved sanitation (proportion of pop.) </v>
       </c>
@@ -6953,7 +9221,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="str">
         <v xml:space="preserve">Improved water source (proportion of pop.) </v>
       </c>
@@ -6961,7 +9229,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -6972,7 +9240,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="str">
         <v xml:space="preserve">Prevalence of cooking with coal/biomass (proportion of pop.) </v>
       </c>
@@ -6980,7 +9248,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="str">
         <v xml:space="preserve">Access to electricity (% of pop.) </v>
       </c>
@@ -6988,7 +9256,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="str">
         <v>Deaths from road injuries (deaths/100,000)</v>
       </c>
@@ -6996,7 +9264,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="str">
         <v xml:space="preserve">Political violence (0=no violence; 4=violence often) </v>
       </c>
@@ -7004,7 +9272,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="str">
         <v>Political killings and torture (0=low freedom; 1=high freedom)</v>
       </c>
@@ -7012,7 +9280,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="str">
         <v xml:space="preserve">Intimate partner violence against women (% of women aged 15+) </v>
       </c>
@@ -7020,7 +9288,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="str">
         <v>Interpersonal violence  (deaths/100,000)</v>
       </c>
@@ -7028,7 +9296,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="str">
         <v xml:space="preserve">Population with no education (proportion of pop.) </v>
       </c>
@@ -7036,7 +9304,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="str">
         <v xml:space="preserve">Gender parity in basic education (distance from parity) </v>
       </c>
@@ -7044,7 +9312,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="str">
         <v xml:space="preserve">Equal access to quality education (0=unequal; 4=equal) </v>
       </c>
@@ -7052,7 +9320,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="str">
         <v>Mean years of schooling (years)</v>
       </c>
@@ -7060,7 +9328,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="str">
         <v>Alternative sources of information (0=low; 1=high)</v>
       </c>
@@ -7068,7 +9336,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="str">
         <v xml:space="preserve">Internet users (% of pop.) </v>
       </c>
@@ -7076,7 +9344,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="str">
         <v xml:space="preserve">Mobile and landline telephone subscriptions (subscriptions/100 people) </v>
       </c>
@@ -7084,7 +9352,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="str">
         <v>Life expectancy at 60 (years)</v>
       </c>
@@ -7092,7 +9360,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="str">
         <v>Premature deaths from non-communicable diseases (deaths/100,000)</v>
       </c>
@@ -7100,7 +9368,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="str">
         <v xml:space="preserve">Equal access to quality healthcare (0=unequal; 4=equal) </v>
       </c>
@@ -7108,7 +9376,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="str">
         <v xml:space="preserve">Universal health coverage (% of pop.) </v>
       </c>
@@ -7116,7 +9384,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B33" s="2" t="str">
         <v>Deaths from outdoor air pollution (deaths/100,000)</v>
       </c>
@@ -7124,7 +9392,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B34" s="2" t="str">
         <v>Particulate matter (2.5) pollution (mean annual exposure, µg/m3)</v>
       </c>
@@ -7132,7 +9400,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B35" s="2" t="str">
         <v>Deaths from lead exposure (deaths/100,000)</v>
       </c>
@@ -7140,7 +9408,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="str">
         <v>Species protection (0=low; 100=high)</v>
       </c>
@@ -7148,7 +9416,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -7159,7 +9427,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="str">
         <v xml:space="preserve">Property rights for women (0=no rights; 5=full rights) </v>
       </c>
@@ -7167,7 +9435,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="str">
         <v xml:space="preserve">Freedom of assembly (0=no freedom; 4=full freedom) </v>
       </c>
@@ -7175,7 +9443,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="str">
         <v>Access to justice (0=nonexistent; 1=observed)</v>
       </c>
@@ -7183,7 +9451,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="str">
         <v>Freedom of discussion (0=low; 1=high)</v>
       </c>
@@ -7191,7 +9459,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="str">
         <v>Political rights (1=full rights; 7=no rights)</v>
       </c>
@@ -7199,7 +9467,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="str">
         <v>Public sector corruption (0=low corruption; 1=high corruption)</v>
       </c>
@@ -7207,7 +9475,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="str">
         <v>Freedom of domestic movement (0=low; 1=high)</v>
       </c>
@@ -7215,7 +9483,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="str">
         <v>Satisfied demand for contraception (% satisfied demand)</v>
       </c>
@@ -7223,7 +9491,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="str">
         <v>Early marriage (% of married women aged 15-19)</v>
       </c>
@@ -7231,7 +9499,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="str">
         <v xml:space="preserve">Vulnerable employment (% of total employment) </v>
       </c>
@@ -7239,7 +9507,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="str">
         <v>Equal protection of social groups (0=low; 1=high)</v>
       </c>
@@ -7247,7 +9515,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="str">
         <v>Equal access to power (0=low; 1=high)</v>
       </c>
@@ -7255,7 +9523,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="str">
         <v xml:space="preserve">Power distributed by sexual orientation (0=extremely unequal; 3=equal) </v>
       </c>
@@ -7263,7 +9531,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="str">
         <v xml:space="preserve">Access to public services distributed by social group (0=extremely unequal; 4=equal) </v>
       </c>
@@ -7271,7 +9539,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="str">
         <v xml:space="preserve">Population with advanced education (proportion of pop.) </v>
       </c>
@@ -7279,7 +9547,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="str">
         <v xml:space="preserve">Gender parity in advanced education (distance from parity) </v>
       </c>
@@ -7287,7 +9555,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="str">
         <v>Respect for academic freedom (0=low; 1=high)</v>
       </c>
@@ -7295,7 +9563,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="str">
         <v>Years of tertiary schooling (years)</v>
       </c>
@@ -7303,7 +9571,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>1</v>
       </c>
@@ -7314,7 +9582,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>3</v>
       </c>
@@ -7322,7 +9590,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>4</v>
       </c>
@@ -7330,7 +9598,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>5</v>
       </c>
@@ -7338,7 +9606,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>7</v>
       </c>
@@ -7346,7 +9614,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>6</v>
       </c>
@@ -7354,7 +9622,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>8</v>
       </c>
@@ -7362,7 +9630,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>9</v>
       </c>
@@ -7370,7 +9638,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>10</v>
       </c>
@@ -7378,7 +9646,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>11</v>
       </c>
@@ -7386,7 +9654,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>12</v>
       </c>
@@ -7394,7 +9662,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C67" t="s">
         <v>27</v>
       </c>

--- a/IndicatorsForClusters.xlsx
+++ b/IndicatorsForClusters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1c3256d208fb6548/Personlig/Aske Banke Consultancy/YALE/Metodeartikel_WorldDevelopmentJournal/WorldDevelopmentArticleGit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="378" documentId="8_{9856C943-DD01-465B-AD17-0E409E296684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D1A4087-8AD9-4244-BD0C-2C8BE0F7DC61}"/>
+  <xr:revisionPtr revIDLastSave="387" documentId="8_{9856C943-DD01-465B-AD17-0E409E296684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8AAB6F5-8537-4C3C-BE36-255FD9E56484}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{726B2859-724A-4801-8E74-5A4E1AFAB973}"/>
   </bookViews>
@@ -56,7 +56,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="8">
+  <futureMetadata name="XLRICHVALUE" count="10">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -113,13 +113,27 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="8">
+  <valueMetadata count="10">
     <bk>
       <rc t="2" v="0"/>
     </bk>
@@ -143,6 +157,12 @@
     </bk>
     <bk>
       <rc t="2" v="7"/>
+    </bk>
+    <bk>
+      <rc t="2" v="8"/>
+    </bk>
+    <bk>
+      <rc t="2" v="9"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -544,7 +564,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -571,14 +591,23 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -622,47 +651,22 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -915,7 +919,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="8">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -948,6 +952,14 @@
     <v>7</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>8</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>9</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -970,6 +982,8 @@
   <rel r:id="rId6"/>
   <rel r:id="rId7"/>
   <rel r:id="rId8"/>
+  <rel r:id="rId9"/>
+  <rel r:id="rId10"/>
 </richValueRels>
 </file>
 
@@ -1311,30 +1325,30 @@
       <c r="B3" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="33" t="s">
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="34"/>
+      <c r="J3" s="39"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
-      <c r="T3" s="24" t="s">
+      <c r="T3" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24"/>
-      <c r="W3" s="24"/>
-      <c r="X3" s="24"/>
+      <c r="U3" s="22"/>
+      <c r="V3" s="22"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="22"/>
     </row>
     <row r="4" spans="1:24" ht="221.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="15" t="s">
@@ -1386,13 +1400,13 @@
       <c r="Q4" s="9" t="str">
         <v>BHN</v>
       </c>
-      <c r="T4" s="22" t="s">
+      <c r="T4" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="U4" s="23"/>
-      <c r="V4" s="23"/>
-      <c r="W4" s="23"/>
-      <c r="X4" s="23"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="29"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="str" cm="1">
@@ -2336,23 +2350,23 @@
       <c r="B21" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35" t="s">
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="35"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="40"/>
       <c r="Q21" s="1" t="s">
         <v>59</v>
       </c>
@@ -2368,62 +2382,62 @@
         <f t="array" ref="B22:B36">TRANSPOSE(_xlfn.ANCHORARRAY(C4))</f>
         <v>BHN_FWB</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C22" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="32"/>
-      <c r="O22" s="32"/>
-      <c r="Q22" s="25" t="e" vm="1">
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="37"/>
+      <c r="M22" s="37"/>
+      <c r="N22" s="37"/>
+      <c r="O22" s="37"/>
+      <c r="Q22" s="30" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="R22" s="25"/>
-      <c r="S22" s="25"/>
-      <c r="T22" s="25"/>
-      <c r="U22" s="25"/>
-      <c r="V22" s="25"/>
-      <c r="W22" s="25"/>
-      <c r="X22" s="25"/>
-      <c r="Y22" s="25"/>
-      <c r="Z22" s="25"/>
-      <c r="AA22" s="25"/>
-      <c r="AB22" s="25" t="e" vm="2">
+      <c r="R22" s="30"/>
+      <c r="S22" s="30"/>
+      <c r="T22" s="30"/>
+      <c r="U22" s="30"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="30"/>
+      <c r="X22" s="30"/>
+      <c r="Y22" s="30"/>
+      <c r="Z22" s="30"/>
+      <c r="AA22" s="30"/>
+      <c r="AB22" s="30" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="AC22" s="25"/>
-      <c r="AD22" s="25"/>
-      <c r="AE22" s="25"/>
-      <c r="AF22" s="25"/>
-      <c r="AG22" s="25"/>
-      <c r="AH22" s="25"/>
-      <c r="AI22" s="25"/>
-      <c r="AJ22" s="25"/>
-      <c r="AK22" s="25"/>
-      <c r="AL22" s="25"/>
-      <c r="AM22" s="25"/>
-      <c r="AN22" s="25"/>
-      <c r="AO22" s="25"/>
-      <c r="AP22" s="25"/>
-      <c r="AQ22" s="25"/>
-      <c r="AR22" s="25" t="e" vm="3">
+      <c r="AC22" s="30"/>
+      <c r="AD22" s="30"/>
+      <c r="AE22" s="30"/>
+      <c r="AF22" s="30"/>
+      <c r="AG22" s="30"/>
+      <c r="AH22" s="30"/>
+      <c r="AI22" s="30"/>
+      <c r="AJ22" s="30"/>
+      <c r="AK22" s="30"/>
+      <c r="AL22" s="30"/>
+      <c r="AM22" s="30"/>
+      <c r="AN22" s="30"/>
+      <c r="AO22" s="30"/>
+      <c r="AP22" s="30"/>
+      <c r="AQ22" s="30"/>
+      <c r="AR22" s="30" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="AS22" s="25"/>
-      <c r="AT22" s="25"/>
-      <c r="AU22" s="25"/>
-      <c r="AV22" s="25"/>
-      <c r="AW22" s="25"/>
-      <c r="AX22" s="25"/>
-      <c r="AY22" s="25"/>
+      <c r="AS22" s="30"/>
+      <c r="AT22" s="30"/>
+      <c r="AU22" s="30"/>
+      <c r="AV22" s="30"/>
+      <c r="AW22" s="30"/>
+      <c r="AX22" s="30"/>
+      <c r="AY22" s="30"/>
     </row>
     <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23">
@@ -2432,56 +2446,56 @@
       <c r="B23" s="7" t="str">
         <v>BHN_FWB_AllExt</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="32"/>
-      <c r="O23" s="32"/>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="25"/>
-      <c r="S23" s="25"/>
-      <c r="T23" s="25"/>
-      <c r="U23" s="25"/>
-      <c r="V23" s="25"/>
-      <c r="W23" s="25"/>
-      <c r="X23" s="25"/>
-      <c r="Y23" s="25"/>
-      <c r="Z23" s="25"/>
-      <c r="AA23" s="25"/>
-      <c r="AB23" s="25"/>
-      <c r="AC23" s="25"/>
-      <c r="AD23" s="25"/>
-      <c r="AE23" s="25"/>
-      <c r="AF23" s="25"/>
-      <c r="AG23" s="25"/>
-      <c r="AH23" s="25"/>
-      <c r="AI23" s="25"/>
-      <c r="AJ23" s="25"/>
-      <c r="AK23" s="25"/>
-      <c r="AL23" s="25"/>
-      <c r="AM23" s="25"/>
-      <c r="AN23" s="25"/>
-      <c r="AO23" s="25"/>
-      <c r="AP23" s="25"/>
-      <c r="AQ23" s="25"/>
-      <c r="AR23" s="25"/>
-      <c r="AS23" s="25"/>
-      <c r="AT23" s="25"/>
-      <c r="AU23" s="25"/>
-      <c r="AV23" s="25"/>
-      <c r="AW23" s="25"/>
-      <c r="AX23" s="25"/>
-      <c r="AY23" s="25"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
+      <c r="M23" s="37"/>
+      <c r="N23" s="37"/>
+      <c r="O23" s="37"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
+      <c r="AA23" s="30"/>
+      <c r="AB23" s="30"/>
+      <c r="AC23" s="30"/>
+      <c r="AD23" s="30"/>
+      <c r="AE23" s="30"/>
+      <c r="AF23" s="30"/>
+      <c r="AG23" s="30"/>
+      <c r="AH23" s="30"/>
+      <c r="AI23" s="30"/>
+      <c r="AJ23" s="30"/>
+      <c r="AK23" s="30"/>
+      <c r="AL23" s="30"/>
+      <c r="AM23" s="30"/>
+      <c r="AN23" s="30"/>
+      <c r="AO23" s="30"/>
+      <c r="AP23" s="30"/>
+      <c r="AQ23" s="30"/>
+      <c r="AR23" s="30"/>
+      <c r="AS23" s="30"/>
+      <c r="AT23" s="30"/>
+      <c r="AU23" s="30"/>
+      <c r="AV23" s="30"/>
+      <c r="AW23" s="30"/>
+      <c r="AX23" s="30"/>
+      <c r="AY23" s="30"/>
     </row>
     <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24">
@@ -2490,56 +2504,56 @@
       <c r="B24" s="7" t="str">
         <v>Few_indicators_closest_DLS_coverage</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C24" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32"/>
-      <c r="M24" s="32"/>
-      <c r="N24" s="32"/>
-      <c r="O24" s="32"/>
-      <c r="Q24" s="25"/>
-      <c r="R24" s="25"/>
-      <c r="S24" s="25"/>
-      <c r="T24" s="25"/>
-      <c r="U24" s="25"/>
-      <c r="V24" s="25"/>
-      <c r="W24" s="25"/>
-      <c r="X24" s="25"/>
-      <c r="Y24" s="25"/>
-      <c r="Z24" s="25"/>
-      <c r="AA24" s="25"/>
-      <c r="AB24" s="25"/>
-      <c r="AC24" s="25"/>
-      <c r="AD24" s="25"/>
-      <c r="AE24" s="25"/>
-      <c r="AF24" s="25"/>
-      <c r="AG24" s="25"/>
-      <c r="AH24" s="25"/>
-      <c r="AI24" s="25"/>
-      <c r="AJ24" s="25"/>
-      <c r="AK24" s="25"/>
-      <c r="AL24" s="25"/>
-      <c r="AM24" s="25"/>
-      <c r="AN24" s="25"/>
-      <c r="AO24" s="25"/>
-      <c r="AP24" s="25"/>
-      <c r="AQ24" s="25"/>
-      <c r="AR24" s="25"/>
-      <c r="AS24" s="25"/>
-      <c r="AT24" s="25"/>
-      <c r="AU24" s="25"/>
-      <c r="AV24" s="25"/>
-      <c r="AW24" s="25"/>
-      <c r="AX24" s="25"/>
-      <c r="AY24" s="25"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="37"/>
+      <c r="M24" s="37"/>
+      <c r="N24" s="37"/>
+      <c r="O24" s="37"/>
+      <c r="Q24" s="30"/>
+      <c r="R24" s="30"/>
+      <c r="S24" s="30"/>
+      <c r="T24" s="30"/>
+      <c r="U24" s="30"/>
+      <c r="V24" s="30"/>
+      <c r="W24" s="30"/>
+      <c r="X24" s="30"/>
+      <c r="Y24" s="30"/>
+      <c r="Z24" s="30"/>
+      <c r="AA24" s="30"/>
+      <c r="AB24" s="30"/>
+      <c r="AC24" s="30"/>
+      <c r="AD24" s="30"/>
+      <c r="AE24" s="30"/>
+      <c r="AF24" s="30"/>
+      <c r="AG24" s="30"/>
+      <c r="AH24" s="30"/>
+      <c r="AI24" s="30"/>
+      <c r="AJ24" s="30"/>
+      <c r="AK24" s="30"/>
+      <c r="AL24" s="30"/>
+      <c r="AM24" s="30"/>
+      <c r="AN24" s="30"/>
+      <c r="AO24" s="30"/>
+      <c r="AP24" s="30"/>
+      <c r="AQ24" s="30"/>
+      <c r="AR24" s="30"/>
+      <c r="AS24" s="30"/>
+      <c r="AT24" s="30"/>
+      <c r="AU24" s="30"/>
+      <c r="AV24" s="30"/>
+      <c r="AW24" s="30"/>
+      <c r="AX24" s="30"/>
+      <c r="AY24" s="30"/>
     </row>
     <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25">
@@ -2548,48 +2562,48 @@
       <c r="B25" s="7" t="str">
         <v>Few indicators_SPI_preferred</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
-      <c r="N25" s="32"/>
-      <c r="O25" s="32"/>
-      <c r="Q25" s="25"/>
-      <c r="R25" s="25"/>
-      <c r="S25" s="25"/>
-      <c r="T25" s="25"/>
-      <c r="U25" s="25"/>
-      <c r="V25" s="25"/>
-      <c r="W25" s="25"/>
-      <c r="X25" s="25"/>
-      <c r="Y25" s="25"/>
-      <c r="Z25" s="25"/>
-      <c r="AA25" s="25"/>
-      <c r="AB25" s="25"/>
-      <c r="AC25" s="25"/>
-      <c r="AD25" s="25"/>
-      <c r="AE25" s="25"/>
-      <c r="AF25" s="25"/>
-      <c r="AG25" s="25"/>
-      <c r="AH25" s="25"/>
-      <c r="AI25" s="25"/>
-      <c r="AJ25" s="25"/>
-      <c r="AK25" s="25"/>
-      <c r="AL25" s="25"/>
-      <c r="AM25" s="25"/>
-      <c r="AN25" s="25"/>
-      <c r="AO25" s="25"/>
-      <c r="AP25" s="25"/>
-      <c r="AQ25" s="25"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="37"/>
+      <c r="K25" s="37"/>
+      <c r="L25" s="37"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="Q25" s="30"/>
+      <c r="R25" s="30"/>
+      <c r="S25" s="30"/>
+      <c r="T25" s="30"/>
+      <c r="U25" s="30"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="30"/>
+      <c r="X25" s="30"/>
+      <c r="Y25" s="30"/>
+      <c r="Z25" s="30"/>
+      <c r="AA25" s="30"/>
+      <c r="AB25" s="30"/>
+      <c r="AC25" s="30"/>
+      <c r="AD25" s="30"/>
+      <c r="AE25" s="30"/>
+      <c r="AF25" s="30"/>
+      <c r="AG25" s="30"/>
+      <c r="AH25" s="30"/>
+      <c r="AI25" s="30"/>
+      <c r="AJ25" s="30"/>
+      <c r="AK25" s="30"/>
+      <c r="AL25" s="30"/>
+      <c r="AM25" s="30"/>
+      <c r="AN25" s="30"/>
+      <c r="AO25" s="30"/>
+      <c r="AP25" s="30"/>
+      <c r="AQ25" s="30"/>
     </row>
     <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26">
@@ -2598,50 +2612,50 @@
       <c r="B26" s="7" t="str">
         <v>No_non_DLS</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="C26" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
-      <c r="N26" s="32"/>
-      <c r="O26" s="32"/>
-      <c r="Q26" s="25" t="e" vm="4">
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="37"/>
+      <c r="M26" s="37"/>
+      <c r="N26" s="37"/>
+      <c r="O26" s="37"/>
+      <c r="Q26" s="30" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="R26" s="25"/>
-      <c r="S26" s="25"/>
-      <c r="T26" s="25"/>
-      <c r="U26" s="25"/>
-      <c r="V26" s="25"/>
-      <c r="W26" s="25"/>
-      <c r="X26" s="25"/>
-      <c r="Y26" s="25"/>
-      <c r="Z26" s="25"/>
-      <c r="AA26" s="25"/>
-      <c r="AB26" s="25"/>
-      <c r="AC26" s="25"/>
-      <c r="AD26" s="25"/>
-      <c r="AE26" s="25"/>
-      <c r="AF26" s="25"/>
-      <c r="AG26" s="25"/>
-      <c r="AH26" s="25"/>
-      <c r="AI26" s="25"/>
-      <c r="AJ26" s="25"/>
-      <c r="AK26" s="25"/>
-      <c r="AL26" s="25"/>
-      <c r="AM26" s="25"/>
-      <c r="AN26" s="25"/>
-      <c r="AO26" s="25"/>
-      <c r="AP26" s="25"/>
-      <c r="AQ26" s="25"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
+      <c r="AA26" s="30"/>
+      <c r="AB26" s="30"/>
+      <c r="AC26" s="30"/>
+      <c r="AD26" s="30"/>
+      <c r="AE26" s="30"/>
+      <c r="AF26" s="30"/>
+      <c r="AG26" s="30"/>
+      <c r="AH26" s="30"/>
+      <c r="AI26" s="30"/>
+      <c r="AJ26" s="30"/>
+      <c r="AK26" s="30"/>
+      <c r="AL26" s="30"/>
+      <c r="AM26" s="30"/>
+      <c r="AN26" s="30"/>
+      <c r="AO26" s="30"/>
+      <c r="AP26" s="30"/>
+      <c r="AQ26" s="30"/>
     </row>
     <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27">
@@ -2650,48 +2664,48 @@
       <c r="B27" s="7" t="str">
         <v>Only_%_of_pop</v>
       </c>
-      <c r="C27" s="38" t="s">
+      <c r="C27" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
-      <c r="M27" s="32"/>
-      <c r="N27" s="32"/>
-      <c r="O27" s="32"/>
-      <c r="Q27" s="25"/>
-      <c r="R27" s="25"/>
-      <c r="S27" s="25"/>
-      <c r="T27" s="25"/>
-      <c r="U27" s="25"/>
-      <c r="V27" s="25"/>
-      <c r="W27" s="25"/>
-      <c r="X27" s="25"/>
-      <c r="Y27" s="25"/>
-      <c r="Z27" s="25"/>
-      <c r="AA27" s="25"/>
-      <c r="AB27" s="25"/>
-      <c r="AC27" s="25"/>
-      <c r="AD27" s="25"/>
-      <c r="AE27" s="25"/>
-      <c r="AF27" s="25"/>
-      <c r="AG27" s="25"/>
-      <c r="AH27" s="25"/>
-      <c r="AI27" s="25"/>
-      <c r="AJ27" s="25"/>
-      <c r="AK27" s="25"/>
-      <c r="AL27" s="25"/>
-      <c r="AM27" s="25"/>
-      <c r="AN27" s="25"/>
-      <c r="AO27" s="25"/>
-      <c r="AP27" s="25"/>
-      <c r="AQ27" s="25"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="37"/>
+      <c r="M27" s="37"/>
+      <c r="N27" s="37"/>
+      <c r="O27" s="37"/>
+      <c r="Q27" s="30"/>
+      <c r="R27" s="30"/>
+      <c r="S27" s="30"/>
+      <c r="T27" s="30"/>
+      <c r="U27" s="30"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="30"/>
+      <c r="X27" s="30"/>
+      <c r="Y27" s="30"/>
+      <c r="Z27" s="30"/>
+      <c r="AA27" s="30"/>
+      <c r="AB27" s="30"/>
+      <c r="AC27" s="30"/>
+      <c r="AD27" s="30"/>
+      <c r="AE27" s="30"/>
+      <c r="AF27" s="30"/>
+      <c r="AG27" s="30"/>
+      <c r="AH27" s="30"/>
+      <c r="AI27" s="30"/>
+      <c r="AJ27" s="30"/>
+      <c r="AK27" s="30"/>
+      <c r="AL27" s="30"/>
+      <c r="AM27" s="30"/>
+      <c r="AN27" s="30"/>
+      <c r="AO27" s="30"/>
+      <c r="AP27" s="30"/>
+      <c r="AQ27" s="30"/>
     </row>
     <row r="28" spans="1:51" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28">
@@ -2700,50 +2714,50 @@
       <c r="B28" s="17" t="str">
         <v>Few_indicators_closest_DLS_coverage_90</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="30"/>
-      <c r="O28" s="30"/>
-      <c r="Q28" s="25"/>
-      <c r="R28" s="25"/>
-      <c r="S28" s="25"/>
-      <c r="T28" s="25"/>
-      <c r="U28" s="25"/>
-      <c r="V28" s="25"/>
-      <c r="W28" s="25"/>
-      <c r="X28" s="25"/>
-      <c r="Y28" s="25"/>
-      <c r="Z28" s="25"/>
-      <c r="AA28" s="25"/>
-      <c r="AB28" s="25" t="e" vm="5">
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="35"/>
+      <c r="Q28" s="30"/>
+      <c r="R28" s="30"/>
+      <c r="S28" s="30"/>
+      <c r="T28" s="30"/>
+      <c r="U28" s="30"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="30"/>
+      <c r="X28" s="30"/>
+      <c r="Y28" s="30"/>
+      <c r="Z28" s="30"/>
+      <c r="AA28" s="30"/>
+      <c r="AB28" s="30" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="AC28" s="25"/>
-      <c r="AD28" s="25"/>
-      <c r="AE28" s="25"/>
-      <c r="AF28" s="25"/>
-      <c r="AG28" s="25"/>
-      <c r="AH28" s="25"/>
-      <c r="AI28" s="25"/>
-      <c r="AJ28" s="25"/>
-      <c r="AK28" s="25"/>
-      <c r="AL28" s="25"/>
-      <c r="AM28" s="25"/>
-      <c r="AN28" s="25"/>
-      <c r="AO28" s="25"/>
-      <c r="AP28" s="25"/>
-      <c r="AQ28" s="25"/>
+      <c r="AC28" s="30"/>
+      <c r="AD28" s="30"/>
+      <c r="AE28" s="30"/>
+      <c r="AF28" s="30"/>
+      <c r="AG28" s="30"/>
+      <c r="AH28" s="30"/>
+      <c r="AI28" s="30"/>
+      <c r="AJ28" s="30"/>
+      <c r="AK28" s="30"/>
+      <c r="AL28" s="30"/>
+      <c r="AM28" s="30"/>
+      <c r="AN28" s="30"/>
+      <c r="AO28" s="30"/>
+      <c r="AP28" s="30"/>
+      <c r="AQ28" s="30"/>
     </row>
     <row r="29" spans="1:51" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29">
@@ -2752,48 +2766,48 @@
       <c r="B29" s="17" t="str">
         <v>Few indicators_SPI_preferred_90</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="Q29" s="25"/>
-      <c r="R29" s="25"/>
-      <c r="S29" s="25"/>
-      <c r="T29" s="25"/>
-      <c r="U29" s="25"/>
-      <c r="V29" s="25"/>
-      <c r="W29" s="25"/>
-      <c r="X29" s="25"/>
-      <c r="Y29" s="25"/>
-      <c r="Z29" s="25"/>
-      <c r="AA29" s="25"/>
-      <c r="AB29" s="25"/>
-      <c r="AC29" s="25"/>
-      <c r="AD29" s="25"/>
-      <c r="AE29" s="25"/>
-      <c r="AF29" s="25"/>
-      <c r="AG29" s="25"/>
-      <c r="AH29" s="25"/>
-      <c r="AI29" s="25"/>
-      <c r="AJ29" s="25"/>
-      <c r="AK29" s="25"/>
-      <c r="AL29" s="25"/>
-      <c r="AM29" s="25"/>
-      <c r="AN29" s="25"/>
-      <c r="AO29" s="25"/>
-      <c r="AP29" s="25"/>
-      <c r="AQ29" s="25"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="35"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
+      <c r="AA29" s="30"/>
+      <c r="AB29" s="30"/>
+      <c r="AC29" s="30"/>
+      <c r="AD29" s="30"/>
+      <c r="AE29" s="30"/>
+      <c r="AF29" s="30"/>
+      <c r="AG29" s="30"/>
+      <c r="AH29" s="30"/>
+      <c r="AI29" s="30"/>
+      <c r="AJ29" s="30"/>
+      <c r="AK29" s="30"/>
+      <c r="AL29" s="30"/>
+      <c r="AM29" s="30"/>
+      <c r="AN29" s="30"/>
+      <c r="AO29" s="30"/>
+      <c r="AP29" s="30"/>
+      <c r="AQ29" s="30"/>
     </row>
     <row r="30" spans="1:51" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30">
@@ -2802,50 +2816,50 @@
       <c r="B30" s="17" t="str">
         <v>Few_indicators_closeDLS_subPrimSchool</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="30"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="30"/>
-      <c r="O30" s="30"/>
-      <c r="Q30" s="25" t="e" vm="6">
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
+      <c r="N30" s="35"/>
+      <c r="O30" s="35"/>
+      <c r="Q30" s="30" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
-      <c r="R30" s="25"/>
-      <c r="S30" s="25"/>
-      <c r="T30" s="25"/>
-      <c r="U30" s="25"/>
-      <c r="V30" s="25"/>
-      <c r="W30" s="25"/>
-      <c r="X30" s="25"/>
-      <c r="Y30" s="25"/>
-      <c r="Z30" s="25"/>
-      <c r="AA30" s="25"/>
-      <c r="AB30" s="25"/>
-      <c r="AC30" s="25"/>
-      <c r="AD30" s="25"/>
-      <c r="AE30" s="25"/>
-      <c r="AF30" s="25"/>
-      <c r="AG30" s="25"/>
-      <c r="AH30" s="25"/>
-      <c r="AI30" s="25"/>
-      <c r="AJ30" s="25"/>
-      <c r="AK30" s="25"/>
-      <c r="AL30" s="25"/>
-      <c r="AM30" s="25"/>
-      <c r="AN30" s="25"/>
-      <c r="AO30" s="25"/>
-      <c r="AP30" s="25"/>
-      <c r="AQ30" s="25"/>
+      <c r="R30" s="30"/>
+      <c r="S30" s="30"/>
+      <c r="T30" s="30"/>
+      <c r="U30" s="30"/>
+      <c r="V30" s="30"/>
+      <c r="W30" s="30"/>
+      <c r="X30" s="30"/>
+      <c r="Y30" s="30"/>
+      <c r="Z30" s="30"/>
+      <c r="AA30" s="30"/>
+      <c r="AB30" s="30"/>
+      <c r="AC30" s="30"/>
+      <c r="AD30" s="30"/>
+      <c r="AE30" s="30"/>
+      <c r="AF30" s="30"/>
+      <c r="AG30" s="30"/>
+      <c r="AH30" s="30"/>
+      <c r="AI30" s="30"/>
+      <c r="AJ30" s="30"/>
+      <c r="AK30" s="30"/>
+      <c r="AL30" s="30"/>
+      <c r="AM30" s="30"/>
+      <c r="AN30" s="30"/>
+      <c r="AO30" s="30"/>
+      <c r="AP30" s="30"/>
+      <c r="AQ30" s="30"/>
     </row>
     <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31">
@@ -2854,48 +2868,48 @@
       <c r="B31" s="17" t="str">
         <v>No_non_DLS_90</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30"/>
-      <c r="L31" s="30"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="30"/>
-      <c r="O31" s="30"/>
-      <c r="Q31" s="25"/>
-      <c r="R31" s="25"/>
-      <c r="S31" s="25"/>
-      <c r="T31" s="25"/>
-      <c r="U31" s="25"/>
-      <c r="V31" s="25"/>
-      <c r="W31" s="25"/>
-      <c r="X31" s="25"/>
-      <c r="Y31" s="25"/>
-      <c r="Z31" s="25"/>
-      <c r="AA31" s="25"/>
-      <c r="AB31" s="25"/>
-      <c r="AC31" s="25"/>
-      <c r="AD31" s="25"/>
-      <c r="AE31" s="25"/>
-      <c r="AF31" s="25"/>
-      <c r="AG31" s="25"/>
-      <c r="AH31" s="25"/>
-      <c r="AI31" s="25"/>
-      <c r="AJ31" s="25"/>
-      <c r="AK31" s="25"/>
-      <c r="AL31" s="25"/>
-      <c r="AM31" s="25"/>
-      <c r="AN31" s="25"/>
-      <c r="AO31" s="25"/>
-      <c r="AP31" s="25"/>
-      <c r="AQ31" s="25"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="Q31" s="30"/>
+      <c r="R31" s="30"/>
+      <c r="S31" s="30"/>
+      <c r="T31" s="30"/>
+      <c r="U31" s="30"/>
+      <c r="V31" s="30"/>
+      <c r="W31" s="30"/>
+      <c r="X31" s="30"/>
+      <c r="Y31" s="30"/>
+      <c r="Z31" s="30"/>
+      <c r="AA31" s="30"/>
+      <c r="AB31" s="30"/>
+      <c r="AC31" s="30"/>
+      <c r="AD31" s="30"/>
+      <c r="AE31" s="30"/>
+      <c r="AF31" s="30"/>
+      <c r="AG31" s="30"/>
+      <c r="AH31" s="30"/>
+      <c r="AI31" s="30"/>
+      <c r="AJ31" s="30"/>
+      <c r="AK31" s="30"/>
+      <c r="AL31" s="30"/>
+      <c r="AM31" s="30"/>
+      <c r="AN31" s="30"/>
+      <c r="AO31" s="30"/>
+      <c r="AP31" s="30"/>
+      <c r="AQ31" s="30"/>
     </row>
     <row r="32" spans="1:51" ht="103.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32">
@@ -2904,50 +2918,50 @@
       <c r="B32" s="17" t="str">
         <v>Few_Indicators_subWatSani</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="Q32" s="25"/>
-      <c r="R32" s="25"/>
-      <c r="S32" s="25"/>
-      <c r="T32" s="25"/>
-      <c r="U32" s="25"/>
-      <c r="V32" s="25"/>
-      <c r="W32" s="25"/>
-      <c r="X32" s="25"/>
-      <c r="Y32" s="25"/>
-      <c r="Z32" s="25"/>
-      <c r="AA32" s="25"/>
-      <c r="AB32" s="25" t="e" vm="7">
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="35"/>
+      <c r="N32" s="35"/>
+      <c r="O32" s="35"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="30"/>
+      <c r="AA32" s="30"/>
+      <c r="AB32" s="30" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
-      <c r="AC32" s="25"/>
-      <c r="AD32" s="25"/>
-      <c r="AE32" s="25"/>
-      <c r="AF32" s="25"/>
-      <c r="AG32" s="25"/>
-      <c r="AH32" s="25"/>
-      <c r="AI32" s="25"/>
-      <c r="AJ32" s="25"/>
-      <c r="AK32" s="25"/>
-      <c r="AL32" s="25"/>
-      <c r="AM32" s="25"/>
-      <c r="AN32" s="25"/>
-      <c r="AO32" s="25"/>
-      <c r="AP32" s="25"/>
-      <c r="AQ32" s="25"/>
+      <c r="AC32" s="30"/>
+      <c r="AD32" s="30"/>
+      <c r="AE32" s="30"/>
+      <c r="AF32" s="30"/>
+      <c r="AG32" s="30"/>
+      <c r="AH32" s="30"/>
+      <c r="AI32" s="30"/>
+      <c r="AJ32" s="30"/>
+      <c r="AK32" s="30"/>
+      <c r="AL32" s="30"/>
+      <c r="AM32" s="30"/>
+      <c r="AN32" s="30"/>
+      <c r="AO32" s="30"/>
+      <c r="AP32" s="30"/>
+      <c r="AQ32" s="30"/>
     </row>
     <row r="33" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A33">
@@ -2956,501 +2970,498 @@
       <c r="B33" s="6" t="str">
         <v>Only_OPP</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="27"/>
-      <c r="J33" s="27"/>
-      <c r="K33" s="27"/>
-      <c r="L33" s="27"/>
-      <c r="M33" s="27"/>
-      <c r="N33" s="27"/>
-      <c r="O33" s="27"/>
-      <c r="Q33" s="25"/>
-      <c r="R33" s="25"/>
-      <c r="S33" s="25"/>
-      <c r="T33" s="25"/>
-      <c r="U33" s="25"/>
-      <c r="V33" s="25"/>
-      <c r="W33" s="25"/>
-      <c r="X33" s="25"/>
-      <c r="Y33" s="25"/>
-      <c r="Z33" s="25"/>
-      <c r="AA33" s="25"/>
-      <c r="AB33" s="25"/>
-      <c r="AC33" s="25"/>
-      <c r="AD33" s="25"/>
-      <c r="AE33" s="25"/>
-      <c r="AF33" s="25"/>
-      <c r="AG33" s="25"/>
-      <c r="AH33" s="25"/>
-      <c r="AI33" s="25"/>
-      <c r="AJ33" s="25"/>
-      <c r="AK33" s="25"/>
-      <c r="AL33" s="25"/>
-      <c r="AM33" s="25"/>
-      <c r="AN33" s="25"/>
-      <c r="AO33" s="25"/>
-      <c r="AP33" s="25"/>
-      <c r="AQ33" s="25"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
+      <c r="Q33" s="30"/>
+      <c r="R33" s="30"/>
+      <c r="S33" s="30"/>
+      <c r="T33" s="30"/>
+      <c r="U33" s="30"/>
+      <c r="V33" s="30"/>
+      <c r="W33" s="30"/>
+      <c r="X33" s="30"/>
+      <c r="Y33" s="30"/>
+      <c r="Z33" s="30"/>
+      <c r="AA33" s="30"/>
+      <c r="AB33" s="30"/>
+      <c r="AC33" s="30"/>
+      <c r="AD33" s="30"/>
+      <c r="AE33" s="30"/>
+      <c r="AF33" s="30"/>
+      <c r="AG33" s="30"/>
+      <c r="AH33" s="30"/>
+      <c r="AI33" s="30"/>
+      <c r="AJ33" s="30"/>
+      <c r="AK33" s="30"/>
+      <c r="AL33" s="30"/>
+      <c r="AM33" s="30"/>
+      <c r="AN33" s="30"/>
+      <c r="AO33" s="30"/>
+      <c r="AP33" s="30"/>
+      <c r="AQ33" s="30"/>
     </row>
     <row r="34" spans="1:43" x14ac:dyDescent="0.3">
       <c r="B34" s="6" t="str">
         <v>Baseline</v>
       </c>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="27"/>
-      <c r="K34" s="27"/>
-      <c r="L34" s="27"/>
-      <c r="M34" s="27"/>
-      <c r="N34" s="27"/>
-      <c r="O34" s="27"/>
-      <c r="Q34" s="25"/>
-      <c r="R34" s="25"/>
-      <c r="S34" s="25"/>
-      <c r="T34" s="25"/>
-      <c r="U34" s="25"/>
-      <c r="V34" s="25"/>
-      <c r="W34" s="25"/>
-      <c r="X34" s="25"/>
-      <c r="Y34" s="25"/>
-      <c r="Z34" s="25"/>
-      <c r="AA34" s="25"/>
-      <c r="AB34" s="25"/>
-      <c r="AC34" s="25"/>
-      <c r="AD34" s="25"/>
-      <c r="AE34" s="25"/>
-      <c r="AF34" s="25"/>
-      <c r="AG34" s="25"/>
-      <c r="AH34" s="25"/>
-      <c r="AI34" s="25"/>
-      <c r="AJ34" s="25"/>
-      <c r="AK34" s="25"/>
-      <c r="AL34" s="25"/>
-      <c r="AM34" s="25"/>
-      <c r="AN34" s="25"/>
-      <c r="AO34" s="25"/>
-      <c r="AP34" s="25"/>
-      <c r="AQ34" s="25"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="32"/>
+      <c r="K34" s="32"/>
+      <c r="L34" s="32"/>
+      <c r="M34" s="32"/>
+      <c r="N34" s="32"/>
+      <c r="O34" s="32"/>
+      <c r="Q34" s="30"/>
+      <c r="R34" s="30"/>
+      <c r="S34" s="30"/>
+      <c r="T34" s="30"/>
+      <c r="U34" s="30"/>
+      <c r="V34" s="30"/>
+      <c r="W34" s="30"/>
+      <c r="X34" s="30"/>
+      <c r="Y34" s="30"/>
+      <c r="Z34" s="30"/>
+      <c r="AA34" s="30"/>
+      <c r="AB34" s="30"/>
+      <c r="AC34" s="30"/>
+      <c r="AD34" s="30"/>
+      <c r="AE34" s="30"/>
+      <c r="AF34" s="30"/>
+      <c r="AG34" s="30"/>
+      <c r="AH34" s="30"/>
+      <c r="AI34" s="30"/>
+      <c r="AJ34" s="30"/>
+      <c r="AK34" s="30"/>
+      <c r="AL34" s="30"/>
+      <c r="AM34" s="30"/>
+      <c r="AN34" s="30"/>
+      <c r="AO34" s="30"/>
+      <c r="AP34" s="30"/>
+      <c r="AQ34" s="30"/>
     </row>
     <row r="35" spans="1:43" x14ac:dyDescent="0.3">
       <c r="B35" s="6" t="str">
         <v>No_nonDLS_limExt</v>
       </c>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27" t="s">
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="J35" s="27"/>
-      <c r="K35" s="27"/>
-      <c r="L35" s="27"/>
-      <c r="M35" s="27"/>
-      <c r="N35" s="27"/>
-      <c r="O35" s="27"/>
-      <c r="Q35" s="25"/>
-      <c r="R35" s="25"/>
-      <c r="S35" s="25"/>
-      <c r="T35" s="25"/>
-      <c r="U35" s="25"/>
-      <c r="V35" s="25"/>
-      <c r="W35" s="25"/>
-      <c r="X35" s="25"/>
-      <c r="Y35" s="25"/>
-      <c r="Z35" s="25"/>
-      <c r="AA35" s="25"/>
-      <c r="AB35" s="25"/>
-      <c r="AC35" s="25"/>
-      <c r="AD35" s="25"/>
-      <c r="AE35" s="25"/>
-      <c r="AF35" s="25"/>
-      <c r="AG35" s="25"/>
-      <c r="AH35" s="25"/>
-      <c r="AI35" s="25"/>
-      <c r="AJ35" s="25"/>
-      <c r="AK35" s="25"/>
-      <c r="AL35" s="25"/>
-      <c r="AM35" s="25"/>
-      <c r="AN35" s="25"/>
-      <c r="AO35" s="25"/>
-      <c r="AP35" s="25"/>
-      <c r="AQ35" s="25"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
+      <c r="L35" s="32"/>
+      <c r="M35" s="32"/>
+      <c r="N35" s="32"/>
+      <c r="O35" s="32"/>
+      <c r="Q35" s="30"/>
+      <c r="R35" s="30"/>
+      <c r="S35" s="30"/>
+      <c r="T35" s="30"/>
+      <c r="U35" s="30"/>
+      <c r="V35" s="30"/>
+      <c r="W35" s="30"/>
+      <c r="X35" s="30"/>
+      <c r="Y35" s="30"/>
+      <c r="Z35" s="30"/>
+      <c r="AA35" s="30"/>
+      <c r="AB35" s="30"/>
+      <c r="AC35" s="30"/>
+      <c r="AD35" s="30"/>
+      <c r="AE35" s="30"/>
+      <c r="AF35" s="30"/>
+      <c r="AG35" s="30"/>
+      <c r="AH35" s="30"/>
+      <c r="AI35" s="30"/>
+      <c r="AJ35" s="30"/>
+      <c r="AK35" s="30"/>
+      <c r="AL35" s="30"/>
+      <c r="AM35" s="30"/>
+      <c r="AN35" s="30"/>
+      <c r="AO35" s="30"/>
+      <c r="AP35" s="30"/>
+      <c r="AQ35" s="30"/>
     </row>
     <row r="36" spans="1:43" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="str">
         <v>BHN</v>
       </c>
-      <c r="C36" s="31" t="s">
+      <c r="C36" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="27"/>
-      <c r="L36" s="27"/>
-      <c r="M36" s="27"/>
-      <c r="N36" s="27"/>
-      <c r="O36" s="27"/>
-      <c r="Q36" s="25"/>
-      <c r="R36" s="25"/>
-      <c r="S36" s="25"/>
-      <c r="T36" s="25"/>
-      <c r="U36" s="25"/>
-      <c r="V36" s="25"/>
-      <c r="W36" s="25"/>
-      <c r="X36" s="25"/>
-      <c r="Y36" s="25"/>
-      <c r="Z36" s="25"/>
-      <c r="AA36" s="25"/>
-      <c r="AB36" s="25"/>
-      <c r="AC36" s="25"/>
-      <c r="AD36" s="25"/>
-      <c r="AE36" s="25"/>
-      <c r="AF36" s="25"/>
-      <c r="AG36" s="25"/>
-      <c r="AH36" s="25"/>
-      <c r="AI36" s="25"/>
-      <c r="AJ36" s="25"/>
-      <c r="AK36" s="25"/>
-      <c r="AL36" s="25"/>
-      <c r="AM36" s="25"/>
-      <c r="AN36" s="25"/>
-      <c r="AO36" s="25"/>
-      <c r="AP36" s="25"/>
-      <c r="AQ36" s="25"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="32"/>
+      <c r="Q36" s="30"/>
+      <c r="R36" s="30"/>
+      <c r="S36" s="30"/>
+      <c r="T36" s="30"/>
+      <c r="U36" s="30"/>
+      <c r="V36" s="30"/>
+      <c r="W36" s="30"/>
+      <c r="X36" s="30"/>
+      <c r="Y36" s="30"/>
+      <c r="Z36" s="30"/>
+      <c r="AA36" s="30"/>
+      <c r="AB36" s="30"/>
+      <c r="AC36" s="30"/>
+      <c r="AD36" s="30"/>
+      <c r="AE36" s="30"/>
+      <c r="AF36" s="30"/>
+      <c r="AG36" s="30"/>
+      <c r="AH36" s="30"/>
+      <c r="AI36" s="30"/>
+      <c r="AJ36" s="30"/>
+      <c r="AK36" s="30"/>
+      <c r="AL36" s="30"/>
+      <c r="AM36" s="30"/>
+      <c r="AN36" s="30"/>
+      <c r="AO36" s="30"/>
+      <c r="AP36" s="30"/>
+      <c r="AQ36" s="30"/>
     </row>
     <row r="37" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB37" s="25"/>
-      <c r="AC37" s="25"/>
-      <c r="AD37" s="25"/>
-      <c r="AE37" s="25"/>
-      <c r="AF37" s="25"/>
-      <c r="AG37" s="25"/>
-      <c r="AH37" s="25"/>
-      <c r="AI37" s="25"/>
-      <c r="AJ37" s="25"/>
-      <c r="AK37" s="25"/>
-      <c r="AL37" s="25"/>
-      <c r="AM37" s="25"/>
-      <c r="AN37" s="25"/>
-      <c r="AO37" s="25"/>
-      <c r="AP37" s="25"/>
-      <c r="AQ37" s="25"/>
+      <c r="AB37" s="30"/>
+      <c r="AC37" s="30"/>
+      <c r="AD37" s="30"/>
+      <c r="AE37" s="30"/>
+      <c r="AF37" s="30"/>
+      <c r="AG37" s="30"/>
+      <c r="AH37" s="30"/>
+      <c r="AI37" s="30"/>
+      <c r="AJ37" s="30"/>
+      <c r="AK37" s="30"/>
+      <c r="AL37" s="30"/>
+      <c r="AM37" s="30"/>
+      <c r="AN37" s="30"/>
+      <c r="AO37" s="30"/>
+      <c r="AP37" s="30"/>
+      <c r="AQ37" s="30"/>
     </row>
     <row r="38" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB38" s="25"/>
-      <c r="AC38" s="25"/>
-      <c r="AD38" s="25"/>
-      <c r="AE38" s="25"/>
-      <c r="AF38" s="25"/>
-      <c r="AG38" s="25"/>
-      <c r="AH38" s="25"/>
-      <c r="AI38" s="25"/>
-      <c r="AJ38" s="25"/>
-      <c r="AK38" s="25"/>
-      <c r="AL38" s="25"/>
-      <c r="AM38" s="25"/>
-      <c r="AN38" s="25"/>
-      <c r="AO38" s="25"/>
-      <c r="AP38" s="25"/>
-      <c r="AQ38" s="25"/>
+      <c r="AB38" s="30"/>
+      <c r="AC38" s="30"/>
+      <c r="AD38" s="30"/>
+      <c r="AE38" s="30"/>
+      <c r="AF38" s="30"/>
+      <c r="AG38" s="30"/>
+      <c r="AH38" s="30"/>
+      <c r="AI38" s="30"/>
+      <c r="AJ38" s="30"/>
+      <c r="AK38" s="30"/>
+      <c r="AL38" s="30"/>
+      <c r="AM38" s="30"/>
+      <c r="AN38" s="30"/>
+      <c r="AO38" s="30"/>
+      <c r="AP38" s="30"/>
+      <c r="AQ38" s="30"/>
     </row>
     <row r="39" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB39" s="25"/>
-      <c r="AC39" s="25"/>
-      <c r="AD39" s="25"/>
-      <c r="AE39" s="25"/>
-      <c r="AF39" s="25"/>
-      <c r="AG39" s="25"/>
-      <c r="AH39" s="25"/>
-      <c r="AI39" s="25"/>
-      <c r="AJ39" s="25"/>
-      <c r="AK39" s="25"/>
-      <c r="AL39" s="25"/>
-      <c r="AM39" s="25"/>
-      <c r="AN39" s="25"/>
-      <c r="AO39" s="25"/>
-      <c r="AP39" s="25"/>
-      <c r="AQ39" s="25"/>
+      <c r="AB39" s="30"/>
+      <c r="AC39" s="30"/>
+      <c r="AD39" s="30"/>
+      <c r="AE39" s="30"/>
+      <c r="AF39" s="30"/>
+      <c r="AG39" s="30"/>
+      <c r="AH39" s="30"/>
+      <c r="AI39" s="30"/>
+      <c r="AJ39" s="30"/>
+      <c r="AK39" s="30"/>
+      <c r="AL39" s="30"/>
+      <c r="AM39" s="30"/>
+      <c r="AN39" s="30"/>
+      <c r="AO39" s="30"/>
+      <c r="AP39" s="30"/>
+      <c r="AQ39" s="30"/>
     </row>
     <row r="40" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB40" s="25"/>
-      <c r="AC40" s="25"/>
-      <c r="AD40" s="25"/>
-      <c r="AE40" s="25"/>
-      <c r="AF40" s="25"/>
-      <c r="AG40" s="25"/>
-      <c r="AH40" s="25"/>
-      <c r="AI40" s="25"/>
-      <c r="AJ40" s="25"/>
-      <c r="AK40" s="25"/>
-      <c r="AL40" s="25"/>
-      <c r="AM40" s="25"/>
-      <c r="AN40" s="25"/>
-      <c r="AO40" s="25"/>
-      <c r="AP40" s="25"/>
-      <c r="AQ40" s="25"/>
+      <c r="AB40" s="30"/>
+      <c r="AC40" s="30"/>
+      <c r="AD40" s="30"/>
+      <c r="AE40" s="30"/>
+      <c r="AF40" s="30"/>
+      <c r="AG40" s="30"/>
+      <c r="AH40" s="30"/>
+      <c r="AI40" s="30"/>
+      <c r="AJ40" s="30"/>
+      <c r="AK40" s="30"/>
+      <c r="AL40" s="30"/>
+      <c r="AM40" s="30"/>
+      <c r="AN40" s="30"/>
+      <c r="AO40" s="30"/>
+      <c r="AP40" s="30"/>
+      <c r="AQ40" s="30"/>
     </row>
     <row r="41" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB41" s="25"/>
-      <c r="AC41" s="25"/>
-      <c r="AD41" s="25"/>
-      <c r="AE41" s="25"/>
-      <c r="AF41" s="25"/>
-      <c r="AG41" s="25"/>
-      <c r="AH41" s="25"/>
-      <c r="AI41" s="25"/>
-      <c r="AJ41" s="25"/>
-      <c r="AK41" s="25"/>
-      <c r="AL41" s="25"/>
-      <c r="AM41" s="25"/>
-      <c r="AN41" s="25"/>
-      <c r="AO41" s="25"/>
-      <c r="AP41" s="25"/>
-      <c r="AQ41" s="25"/>
+      <c r="AB41" s="30"/>
+      <c r="AC41" s="30"/>
+      <c r="AD41" s="30"/>
+      <c r="AE41" s="30"/>
+      <c r="AF41" s="30"/>
+      <c r="AG41" s="30"/>
+      <c r="AH41" s="30"/>
+      <c r="AI41" s="30"/>
+      <c r="AJ41" s="30"/>
+      <c r="AK41" s="30"/>
+      <c r="AL41" s="30"/>
+      <c r="AM41" s="30"/>
+      <c r="AN41" s="30"/>
+      <c r="AO41" s="30"/>
+      <c r="AP41" s="30"/>
+      <c r="AQ41" s="30"/>
     </row>
     <row r="42" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB42" s="25" t="e" vm="8">
+      <c r="AB42" s="30" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-      <c r="AC42" s="25"/>
-      <c r="AD42" s="25"/>
-      <c r="AE42" s="25"/>
-      <c r="AF42" s="25"/>
-      <c r="AG42" s="25"/>
-      <c r="AH42" s="25"/>
-      <c r="AI42" s="25"/>
-      <c r="AJ42" s="25"/>
-      <c r="AK42" s="25"/>
-      <c r="AL42" s="25"/>
-      <c r="AM42" s="25"/>
-      <c r="AN42" s="25"/>
-      <c r="AO42" s="25"/>
-      <c r="AP42" s="25"/>
-      <c r="AQ42" s="25"/>
+      <c r="AC42" s="30"/>
+      <c r="AD42" s="30"/>
+      <c r="AE42" s="30"/>
+      <c r="AF42" s="30"/>
+      <c r="AG42" s="30"/>
+      <c r="AH42" s="30"/>
+      <c r="AI42" s="30"/>
+      <c r="AJ42" s="30"/>
+      <c r="AK42" s="30"/>
+      <c r="AL42" s="30"/>
+      <c r="AM42" s="30"/>
+      <c r="AN42" s="30"/>
+      <c r="AO42" s="30"/>
+      <c r="AP42" s="30"/>
+      <c r="AQ42" s="30"/>
     </row>
     <row r="43" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB43" s="25"/>
-      <c r="AC43" s="25"/>
-      <c r="AD43" s="25"/>
-      <c r="AE43" s="25"/>
-      <c r="AF43" s="25"/>
-      <c r="AG43" s="25"/>
-      <c r="AH43" s="25"/>
-      <c r="AI43" s="25"/>
-      <c r="AJ43" s="25"/>
-      <c r="AK43" s="25"/>
-      <c r="AL43" s="25"/>
-      <c r="AM43" s="25"/>
-      <c r="AN43" s="25"/>
-      <c r="AO43" s="25"/>
-      <c r="AP43" s="25"/>
-      <c r="AQ43" s="25"/>
+      <c r="AB43" s="30"/>
+      <c r="AC43" s="30"/>
+      <c r="AD43" s="30"/>
+      <c r="AE43" s="30"/>
+      <c r="AF43" s="30"/>
+      <c r="AG43" s="30"/>
+      <c r="AH43" s="30"/>
+      <c r="AI43" s="30"/>
+      <c r="AJ43" s="30"/>
+      <c r="AK43" s="30"/>
+      <c r="AL43" s="30"/>
+      <c r="AM43" s="30"/>
+      <c r="AN43" s="30"/>
+      <c r="AO43" s="30"/>
+      <c r="AP43" s="30"/>
+      <c r="AQ43" s="30"/>
     </row>
     <row r="44" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB44" s="25"/>
-      <c r="AC44" s="25"/>
-      <c r="AD44" s="25"/>
-      <c r="AE44" s="25"/>
-      <c r="AF44" s="25"/>
-      <c r="AG44" s="25"/>
-      <c r="AH44" s="25"/>
-      <c r="AI44" s="25"/>
-      <c r="AJ44" s="25"/>
-      <c r="AK44" s="25"/>
-      <c r="AL44" s="25"/>
-      <c r="AM44" s="25"/>
-      <c r="AN44" s="25"/>
-      <c r="AO44" s="25"/>
-      <c r="AP44" s="25"/>
-      <c r="AQ44" s="25"/>
+      <c r="AB44" s="30"/>
+      <c r="AC44" s="30"/>
+      <c r="AD44" s="30"/>
+      <c r="AE44" s="30"/>
+      <c r="AF44" s="30"/>
+      <c r="AG44" s="30"/>
+      <c r="AH44" s="30"/>
+      <c r="AI44" s="30"/>
+      <c r="AJ44" s="30"/>
+      <c r="AK44" s="30"/>
+      <c r="AL44" s="30"/>
+      <c r="AM44" s="30"/>
+      <c r="AN44" s="30"/>
+      <c r="AO44" s="30"/>
+      <c r="AP44" s="30"/>
+      <c r="AQ44" s="30"/>
     </row>
     <row r="45" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB45" s="25"/>
-      <c r="AC45" s="25"/>
-      <c r="AD45" s="25"/>
-      <c r="AE45" s="25"/>
-      <c r="AF45" s="25"/>
-      <c r="AG45" s="25"/>
-      <c r="AH45" s="25"/>
-      <c r="AI45" s="25"/>
-      <c r="AJ45" s="25"/>
-      <c r="AK45" s="25"/>
-      <c r="AL45" s="25"/>
-      <c r="AM45" s="25"/>
-      <c r="AN45" s="25"/>
-      <c r="AO45" s="25"/>
-      <c r="AP45" s="25"/>
-      <c r="AQ45" s="25"/>
+      <c r="AB45" s="30"/>
+      <c r="AC45" s="30"/>
+      <c r="AD45" s="30"/>
+      <c r="AE45" s="30"/>
+      <c r="AF45" s="30"/>
+      <c r="AG45" s="30"/>
+      <c r="AH45" s="30"/>
+      <c r="AI45" s="30"/>
+      <c r="AJ45" s="30"/>
+      <c r="AK45" s="30"/>
+      <c r="AL45" s="30"/>
+      <c r="AM45" s="30"/>
+      <c r="AN45" s="30"/>
+      <c r="AO45" s="30"/>
+      <c r="AP45" s="30"/>
+      <c r="AQ45" s="30"/>
     </row>
     <row r="46" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB46" s="25"/>
-      <c r="AC46" s="25"/>
-      <c r="AD46" s="25"/>
-      <c r="AE46" s="25"/>
-      <c r="AF46" s="25"/>
-      <c r="AG46" s="25"/>
-      <c r="AH46" s="25"/>
-      <c r="AI46" s="25"/>
-      <c r="AJ46" s="25"/>
-      <c r="AK46" s="25"/>
-      <c r="AL46" s="25"/>
-      <c r="AM46" s="25"/>
-      <c r="AN46" s="25"/>
-      <c r="AO46" s="25"/>
-      <c r="AP46" s="25"/>
-      <c r="AQ46" s="25"/>
+      <c r="AB46" s="30"/>
+      <c r="AC46" s="30"/>
+      <c r="AD46" s="30"/>
+      <c r="AE46" s="30"/>
+      <c r="AF46" s="30"/>
+      <c r="AG46" s="30"/>
+      <c r="AH46" s="30"/>
+      <c r="AI46" s="30"/>
+      <c r="AJ46" s="30"/>
+      <c r="AK46" s="30"/>
+      <c r="AL46" s="30"/>
+      <c r="AM46" s="30"/>
+      <c r="AN46" s="30"/>
+      <c r="AO46" s="30"/>
+      <c r="AP46" s="30"/>
+      <c r="AQ46" s="30"/>
     </row>
     <row r="47" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB47" s="25"/>
-      <c r="AC47" s="25"/>
-      <c r="AD47" s="25"/>
-      <c r="AE47" s="25"/>
-      <c r="AF47" s="25"/>
-      <c r="AG47" s="25"/>
-      <c r="AH47" s="25"/>
-      <c r="AI47" s="25"/>
-      <c r="AJ47" s="25"/>
-      <c r="AK47" s="25"/>
-      <c r="AL47" s="25"/>
-      <c r="AM47" s="25"/>
-      <c r="AN47" s="25"/>
-      <c r="AO47" s="25"/>
-      <c r="AP47" s="25"/>
-      <c r="AQ47" s="25"/>
+      <c r="AB47" s="30"/>
+      <c r="AC47" s="30"/>
+      <c r="AD47" s="30"/>
+      <c r="AE47" s="30"/>
+      <c r="AF47" s="30"/>
+      <c r="AG47" s="30"/>
+      <c r="AH47" s="30"/>
+      <c r="AI47" s="30"/>
+      <c r="AJ47" s="30"/>
+      <c r="AK47" s="30"/>
+      <c r="AL47" s="30"/>
+      <c r="AM47" s="30"/>
+      <c r="AN47" s="30"/>
+      <c r="AO47" s="30"/>
+      <c r="AP47" s="30"/>
+      <c r="AQ47" s="30"/>
     </row>
     <row r="48" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB48" s="25"/>
-      <c r="AC48" s="25"/>
-      <c r="AD48" s="25"/>
-      <c r="AE48" s="25"/>
-      <c r="AF48" s="25"/>
-      <c r="AG48" s="25"/>
-      <c r="AH48" s="25"/>
-      <c r="AI48" s="25"/>
-      <c r="AJ48" s="25"/>
-      <c r="AK48" s="25"/>
-      <c r="AL48" s="25"/>
-      <c r="AM48" s="25"/>
-      <c r="AN48" s="25"/>
-      <c r="AO48" s="25"/>
-      <c r="AP48" s="25"/>
-      <c r="AQ48" s="25"/>
+      <c r="AB48" s="30"/>
+      <c r="AC48" s="30"/>
+      <c r="AD48" s="30"/>
+      <c r="AE48" s="30"/>
+      <c r="AF48" s="30"/>
+      <c r="AG48" s="30"/>
+      <c r="AH48" s="30"/>
+      <c r="AI48" s="30"/>
+      <c r="AJ48" s="30"/>
+      <c r="AK48" s="30"/>
+      <c r="AL48" s="30"/>
+      <c r="AM48" s="30"/>
+      <c r="AN48" s="30"/>
+      <c r="AO48" s="30"/>
+      <c r="AP48" s="30"/>
+      <c r="AQ48" s="30"/>
     </row>
     <row r="49" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB49" s="25"/>
-      <c r="AC49" s="25"/>
-      <c r="AD49" s="25"/>
-      <c r="AE49" s="25"/>
-      <c r="AF49" s="25"/>
-      <c r="AG49" s="25"/>
-      <c r="AH49" s="25"/>
-      <c r="AI49" s="25"/>
-      <c r="AJ49" s="25"/>
-      <c r="AK49" s="25"/>
-      <c r="AL49" s="25"/>
-      <c r="AM49" s="25"/>
-      <c r="AN49" s="25"/>
-      <c r="AO49" s="25"/>
-      <c r="AP49" s="25"/>
-      <c r="AQ49" s="25"/>
+      <c r="AB49" s="30"/>
+      <c r="AC49" s="30"/>
+      <c r="AD49" s="30"/>
+      <c r="AE49" s="30"/>
+      <c r="AF49" s="30"/>
+      <c r="AG49" s="30"/>
+      <c r="AH49" s="30"/>
+      <c r="AI49" s="30"/>
+      <c r="AJ49" s="30"/>
+      <c r="AK49" s="30"/>
+      <c r="AL49" s="30"/>
+      <c r="AM49" s="30"/>
+      <c r="AN49" s="30"/>
+      <c r="AO49" s="30"/>
+      <c r="AP49" s="30"/>
+      <c r="AQ49" s="30"/>
     </row>
     <row r="50" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB50" s="25"/>
-      <c r="AC50" s="25"/>
-      <c r="AD50" s="25"/>
-      <c r="AE50" s="25"/>
-      <c r="AF50" s="25"/>
-      <c r="AG50" s="25"/>
-      <c r="AH50" s="25"/>
-      <c r="AI50" s="25"/>
-      <c r="AJ50" s="25"/>
-      <c r="AK50" s="25"/>
-      <c r="AL50" s="25"/>
-      <c r="AM50" s="25"/>
-      <c r="AN50" s="25"/>
-      <c r="AO50" s="25"/>
-      <c r="AP50" s="25"/>
-      <c r="AQ50" s="25"/>
+      <c r="AB50" s="30"/>
+      <c r="AC50" s="30"/>
+      <c r="AD50" s="30"/>
+      <c r="AE50" s="30"/>
+      <c r="AF50" s="30"/>
+      <c r="AG50" s="30"/>
+      <c r="AH50" s="30"/>
+      <c r="AI50" s="30"/>
+      <c r="AJ50" s="30"/>
+      <c r="AK50" s="30"/>
+      <c r="AL50" s="30"/>
+      <c r="AM50" s="30"/>
+      <c r="AN50" s="30"/>
+      <c r="AO50" s="30"/>
+      <c r="AP50" s="30"/>
+      <c r="AQ50" s="30"/>
     </row>
     <row r="51" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB51" s="25"/>
-      <c r="AC51" s="25"/>
-      <c r="AD51" s="25"/>
-      <c r="AE51" s="25"/>
-      <c r="AF51" s="25"/>
-      <c r="AG51" s="25"/>
-      <c r="AH51" s="25"/>
-      <c r="AI51" s="25"/>
-      <c r="AJ51" s="25"/>
-      <c r="AK51" s="25"/>
-      <c r="AL51" s="25"/>
-      <c r="AM51" s="25"/>
-      <c r="AN51" s="25"/>
-      <c r="AO51" s="25"/>
-      <c r="AP51" s="25"/>
-      <c r="AQ51" s="25"/>
+      <c r="AB51" s="30"/>
+      <c r="AC51" s="30"/>
+      <c r="AD51" s="30"/>
+      <c r="AE51" s="30"/>
+      <c r="AF51" s="30"/>
+      <c r="AG51" s="30"/>
+      <c r="AH51" s="30"/>
+      <c r="AI51" s="30"/>
+      <c r="AJ51" s="30"/>
+      <c r="AK51" s="30"/>
+      <c r="AL51" s="30"/>
+      <c r="AM51" s="30"/>
+      <c r="AN51" s="30"/>
+      <c r="AO51" s="30"/>
+      <c r="AP51" s="30"/>
+      <c r="AQ51" s="30"/>
     </row>
     <row r="52" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB52" s="25"/>
-      <c r="AC52" s="25"/>
-      <c r="AD52" s="25"/>
-      <c r="AE52" s="25"/>
-      <c r="AF52" s="25"/>
-      <c r="AG52" s="25"/>
-      <c r="AH52" s="25"/>
-      <c r="AI52" s="25"/>
-      <c r="AJ52" s="25"/>
-      <c r="AK52" s="25"/>
-      <c r="AL52" s="25"/>
-      <c r="AM52" s="25"/>
-      <c r="AN52" s="25"/>
-      <c r="AO52" s="25"/>
-      <c r="AP52" s="25"/>
-      <c r="AQ52" s="25"/>
+      <c r="AB52" s="30"/>
+      <c r="AC52" s="30"/>
+      <c r="AD52" s="30"/>
+      <c r="AE52" s="30"/>
+      <c r="AF52" s="30"/>
+      <c r="AG52" s="30"/>
+      <c r="AH52" s="30"/>
+      <c r="AI52" s="30"/>
+      <c r="AJ52" s="30"/>
+      <c r="AK52" s="30"/>
+      <c r="AL52" s="30"/>
+      <c r="AM52" s="30"/>
+      <c r="AN52" s="30"/>
+      <c r="AO52" s="30"/>
+      <c r="AP52" s="30"/>
+      <c r="AQ52" s="30"/>
     </row>
     <row r="53" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB53" s="25"/>
-      <c r="AC53" s="25"/>
-      <c r="AD53" s="25"/>
-      <c r="AE53" s="25"/>
-      <c r="AF53" s="25"/>
-      <c r="AG53" s="25"/>
-      <c r="AH53" s="25"/>
-      <c r="AI53" s="25"/>
-      <c r="AJ53" s="25"/>
-      <c r="AK53" s="25"/>
-      <c r="AL53" s="25"/>
-      <c r="AM53" s="25"/>
-      <c r="AN53" s="25"/>
-      <c r="AO53" s="25"/>
-      <c r="AP53" s="25"/>
-      <c r="AQ53" s="25"/>
+      <c r="AB53" s="30"/>
+      <c r="AC53" s="30"/>
+      <c r="AD53" s="30"/>
+      <c r="AE53" s="30"/>
+      <c r="AF53" s="30"/>
+      <c r="AG53" s="30"/>
+      <c r="AH53" s="30"/>
+      <c r="AI53" s="30"/>
+      <c r="AJ53" s="30"/>
+      <c r="AK53" s="30"/>
+      <c r="AL53" s="30"/>
+      <c r="AM53" s="30"/>
+      <c r="AN53" s="30"/>
+      <c r="AO53" s="30"/>
+      <c r="AP53" s="30"/>
+      <c r="AQ53" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="42">
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="C26:H26"/>
+  <mergeCells count="43">
     <mergeCell ref="C27:H27"/>
     <mergeCell ref="I24:O24"/>
     <mergeCell ref="I25:O25"/>
@@ -3462,6 +3473,7 @@
     <mergeCell ref="I23:O23"/>
     <mergeCell ref="C3:H3"/>
     <mergeCell ref="C21:H21"/>
+    <mergeCell ref="C28:H28"/>
     <mergeCell ref="I28:O28"/>
     <mergeCell ref="I29:O29"/>
     <mergeCell ref="AR22:AY24"/>
@@ -3474,6 +3486,10 @@
     <mergeCell ref="I34:O34"/>
     <mergeCell ref="AB22:AQ27"/>
     <mergeCell ref="Q22:AA25"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="T4:X4"/>
     <mergeCell ref="AB42:AQ53"/>
     <mergeCell ref="C30:H30"/>
     <mergeCell ref="AB28:AQ31"/>
@@ -3489,7 +3505,6 @@
     <mergeCell ref="I31:O31"/>
     <mergeCell ref="C36:H36"/>
     <mergeCell ref="I36:O36"/>
-    <mergeCell ref="C28:H28"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:Q15">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
@@ -3523,84 +3538,84 @@
       <c r="B3" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="41"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="39"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
-      <c r="T3" s="24" t="s">
+      <c r="T3" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24"/>
-      <c r="W3" s="24"/>
-      <c r="X3" s="24"/>
+      <c r="U3" s="22"/>
+      <c r="V3" s="22"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="22"/>
     </row>
     <row r="4" spans="1:24" ht="221.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="42" t="str" cm="1">
+      <c r="C4" s="25" t="str" cm="1">
         <f t="array" ref="C4:Q4">Experiments!C1:Q1</f>
         <v>BHN_FWB</v>
       </c>
-      <c r="D4" s="46" t="str">
+      <c r="D4" s="23" t="str">
         <v>BHN_FWB_AllExt</v>
       </c>
-      <c r="E4" s="43" t="str">
+      <c r="E4" s="9" t="str">
         <v>Few_indicators_closest_DLS_coverage</v>
       </c>
-      <c r="F4" s="43" t="str">
+      <c r="F4" s="9" t="str">
         <v>Few indicators_SPI_preferred</v>
       </c>
-      <c r="G4" s="43" t="str">
+      <c r="G4" s="9" t="str">
         <v>No_non_DLS</v>
       </c>
-      <c r="H4" s="40" t="str">
+      <c r="H4" s="24" t="str">
         <v>Only_%_of_pop</v>
       </c>
-      <c r="I4" s="42" t="str">
+      <c r="I4" s="25" t="str">
         <v>Few_indicators_closest_DLS_coverage_90</v>
       </c>
-      <c r="J4" s="43" t="str">
+      <c r="J4" s="9" t="str">
         <v>Few indicators_SPI_preferred_90</v>
       </c>
-      <c r="K4" s="39" t="str">
+      <c r="K4" s="23" t="str">
         <v>Few_indicators_closeDLS_subPrimSchool</v>
       </c>
-      <c r="L4" s="39" t="str">
+      <c r="L4" s="23" t="str">
         <v>No_non_DLS_90</v>
       </c>
-      <c r="M4" s="39" t="str">
+      <c r="M4" s="23" t="str">
         <v>Few_Indicators_subWatSani</v>
       </c>
-      <c r="N4" s="39" t="str">
+      <c r="N4" s="23" t="str">
         <v>Only_OPP</v>
       </c>
       <c r="O4" s="9" t="str">
         <v>Baseline</v>
       </c>
-      <c r="P4" s="39" t="str">
+      <c r="P4" s="23" t="str">
         <v>No_nonDLS_limExt</v>
       </c>
-      <c r="Q4" s="39" t="str">
+      <c r="Q4" s="23" t="str">
         <v>BHN</v>
       </c>
-      <c r="T4" s="47" t="s">
+      <c r="T4" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="W4" s="47"/>
-      <c r="X4" s="47"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="29"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="str" cm="1">
@@ -3611,19 +3626,19 @@
         <f t="array" ref="C5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!C$2:C$64=1))</f>
         <v>3</v>
       </c>
-      <c r="D5" s="44" cm="1">
+      <c r="D5" s="8" cm="1">
         <f t="array" ref="D5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!D$2:D$64=1))</f>
         <v>5</v>
       </c>
-      <c r="E5" s="44" cm="1">
+      <c r="E5" s="8" cm="1">
         <f t="array" ref="E5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!E$2:E$64=1))</f>
         <v>1</v>
       </c>
-      <c r="F5" s="44" cm="1">
+      <c r="F5" s="8" cm="1">
         <f t="array" ref="F5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!F$2:F$64=1))</f>
         <v>1</v>
       </c>
-      <c r="G5" s="44" cm="1">
+      <c r="G5" s="8" cm="1">
         <f t="array" ref="G5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!G$2:G$64=1))</f>
         <v>5</v>
       </c>
@@ -3635,7 +3650,7 @@
         <f t="array" ref="I5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!I$2:I$64=1))</f>
         <v>1</v>
       </c>
-      <c r="J5" s="44" cm="1">
+      <c r="J5" s="8" cm="1">
         <f t="array" ref="J5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!J$2:J$64=1))</f>
         <v>1</v>
       </c>
@@ -3679,19 +3694,19 @@
         <f t="array" ref="C6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!C$2:C$64=1))</f>
         <v>7</v>
       </c>
-      <c r="D6" s="44" cm="1">
+      <c r="D6" s="8" cm="1">
         <f t="array" ref="D6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!D$2:D$64=1))</f>
         <v>10</v>
       </c>
-      <c r="E6" s="44" cm="1">
+      <c r="E6" s="8" cm="1">
         <f t="array" ref="E6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!E$2:E$64=1))</f>
         <v>1</v>
       </c>
-      <c r="F6" s="44" cm="1">
+      <c r="F6" s="8" cm="1">
         <f t="array" ref="F6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!F$2:F$64=1))</f>
         <v>1</v>
       </c>
-      <c r="G6" s="44" cm="1">
+      <c r="G6" s="8" cm="1">
         <f t="array" ref="G6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!G$2:G$64=1))</f>
         <v>10</v>
       </c>
@@ -3703,7 +3718,7 @@
         <f t="array" ref="I6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!I$2:I$64=1))</f>
         <v>1</v>
       </c>
-      <c r="J6" s="44" cm="1">
+      <c r="J6" s="8" cm="1">
         <f t="array" ref="J6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!J$2:J$64=1))</f>
         <v>1</v>
       </c>
@@ -3744,19 +3759,19 @@
         <f t="array" ref="C7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!C$2:C$64=1))</f>
         <v>3</v>
       </c>
-      <c r="D7" s="44" cm="1">
+      <c r="D7" s="8" cm="1">
         <f t="array" ref="D7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!D$2:D$64=1))</f>
         <v>4</v>
       </c>
-      <c r="E7" s="44" cm="1">
+      <c r="E7" s="8" cm="1">
         <f t="array" ref="E7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!E$2:E$64=1))</f>
         <v>2</v>
       </c>
-      <c r="F7" s="44" cm="1">
+      <c r="F7" s="8" cm="1">
         <f t="array" ref="F7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!F$2:F$64=1))</f>
         <v>2</v>
       </c>
-      <c r="G7" s="44" cm="1">
+      <c r="G7" s="8" cm="1">
         <f t="array" ref="G7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!G$2:G$64=1))</f>
         <v>4</v>
       </c>
@@ -3768,7 +3783,7 @@
         <f t="array" ref="I7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!I$2:I$64=1))</f>
         <v>2</v>
       </c>
-      <c r="J7" s="44" cm="1">
+      <c r="J7" s="8" cm="1">
         <f t="array" ref="J7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!J$2:J$64=1))</f>
         <v>2</v>
       </c>
@@ -3809,19 +3824,19 @@
         <f t="array" ref="C8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!C$2:C$64=1))</f>
         <v>1</v>
       </c>
-      <c r="D8" s="44" cm="1">
+      <c r="D8" s="8" cm="1">
         <f t="array" ref="D8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!D$2:D$64=1))</f>
         <v>2</v>
       </c>
-      <c r="E8" s="44" cm="1">
+      <c r="E8" s="8" cm="1">
         <f t="array" ref="E8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!E$2:E$64=1))</f>
         <v>1</v>
       </c>
-      <c r="F8" s="44" cm="1">
+      <c r="F8" s="8" cm="1">
         <f t="array" ref="F8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!F$2:F$64=1))</f>
         <v>1</v>
       </c>
-      <c r="G8" s="44" cm="1">
+      <c r="G8" s="8" cm="1">
         <f t="array" ref="G8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!G$2:G$64=1))</f>
         <v>2</v>
       </c>
@@ -3833,7 +3848,7 @@
         <f t="array" ref="I8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!I$2:I$64=1))</f>
         <v>1</v>
       </c>
-      <c r="J8" s="44" cm="1">
+      <c r="J8" s="8" cm="1">
         <f t="array" ref="J8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!J$2:J$64=1))</f>
         <v>1</v>
       </c>
@@ -3874,19 +3889,19 @@
         <f t="array" ref="C9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!C$2:C$64=1))</f>
         <v>2</v>
       </c>
-      <c r="D9" s="44" cm="1">
+      <c r="D9" s="8" cm="1">
         <f t="array" ref="D9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!D$2:D$64=1))</f>
         <v>3</v>
       </c>
-      <c r="E9" s="44" cm="1">
+      <c r="E9" s="8" cm="1">
         <f t="array" ref="E9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!E$2:E$64=1))</f>
         <v>1</v>
       </c>
-      <c r="F9" s="44" cm="1">
+      <c r="F9" s="8" cm="1">
         <f t="array" ref="F9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!F$2:F$64=1))</f>
         <v>1</v>
       </c>
-      <c r="G9" s="44" cm="1">
+      <c r="G9" s="8" cm="1">
         <f t="array" ref="G9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!G$2:G$64=1))</f>
         <v>3</v>
       </c>
@@ -3898,7 +3913,7 @@
         <f t="array" ref="I9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!I$2:I$64=1))</f>
         <v>1</v>
       </c>
-      <c r="J9" s="44" cm="1">
+      <c r="J9" s="8" cm="1">
         <f t="array" ref="J9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!J$2:J$64=1))</f>
         <v>1</v>
       </c>
@@ -3939,19 +3954,19 @@
         <f t="array" ref="C10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!C$2:C$64=1))</f>
         <v>1</v>
       </c>
-      <c r="D10" s="44" cm="1">
+      <c r="D10" s="8" cm="1">
         <f t="array" ref="D10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!D$2:D$64=1))</f>
         <v>1</v>
       </c>
-      <c r="E10" s="44" cm="1">
+      <c r="E10" s="8" cm="1">
         <f t="array" ref="E10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!E$2:E$64=1))</f>
         <v>1</v>
       </c>
-      <c r="F10" s="44" cm="1">
+      <c r="F10" s="8" cm="1">
         <f t="array" ref="F10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!F$2:F$64=1))</f>
         <v>1</v>
       </c>
-      <c r="G10" s="44" cm="1">
+      <c r="G10" s="8" cm="1">
         <f t="array" ref="G10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!G$2:G$64=1))</f>
         <v>1</v>
       </c>
@@ -3963,7 +3978,7 @@
         <f t="array" ref="I10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!I$2:I$64=1))</f>
         <v>1</v>
       </c>
-      <c r="J10" s="44" cm="1">
+      <c r="J10" s="8" cm="1">
         <f t="array" ref="J10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!J$2:J$64=1))</f>
         <v>1</v>
       </c>
@@ -4004,19 +4019,19 @@
         <f t="array" ref="C11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!C$2:C$64=1))</f>
         <v>9</v>
       </c>
-      <c r="D11" s="44" cm="1">
+      <c r="D11" s="8" cm="1">
         <f t="array" ref="D11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!D$2:D$64=1))</f>
         <v>10</v>
       </c>
-      <c r="E11" s="44" cm="1">
+      <c r="E11" s="8" cm="1">
         <f t="array" ref="E11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!E$2:E$64=1))</f>
         <v>0</v>
       </c>
-      <c r="F11" s="44" cm="1">
+      <c r="F11" s="8" cm="1">
         <f t="array" ref="F11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!F$2:F$64=1))</f>
         <v>0</v>
       </c>
-      <c r="G11" s="44" cm="1">
+      <c r="G11" s="8" cm="1">
         <f t="array" ref="G11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!G$2:G$64=1))</f>
         <v>0</v>
       </c>
@@ -4028,7 +4043,7 @@
         <f t="array" ref="I11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!I$2:I$64=1))</f>
         <v>0</v>
       </c>
-      <c r="J11" s="44" cm="1">
+      <c r="J11" s="8" cm="1">
         <f t="array" ref="J11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!J$2:J$64=1))</f>
         <v>0</v>
       </c>
@@ -4069,19 +4084,19 @@
         <f t="array" ref="C12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!C$2:C$64=1))</f>
         <v>4</v>
       </c>
-      <c r="D12" s="44" cm="1">
+      <c r="D12" s="8" cm="1">
         <f t="array" ref="D12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!D$2:D$64=1))</f>
         <v>5</v>
       </c>
-      <c r="E12" s="44" cm="1">
+      <c r="E12" s="8" cm="1">
         <f t="array" ref="E12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!E$2:E$64=1))</f>
         <v>1</v>
       </c>
-      <c r="F12" s="44" cm="1">
+      <c r="F12" s="8" cm="1">
         <f t="array" ref="F12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!F$2:F$64=1))</f>
         <v>1</v>
       </c>
-      <c r="G12" s="44" cm="1">
+      <c r="G12" s="8" cm="1">
         <f t="array" ref="G12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!G$2:G$64=1))</f>
         <v>9</v>
       </c>
@@ -4093,7 +4108,7 @@
         <f t="array" ref="I12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!I$2:I$64=1))</f>
         <v>1</v>
       </c>
-      <c r="J12" s="44" cm="1">
+      <c r="J12" s="8" cm="1">
         <f t="array" ref="J12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!J$2:J$64=1))</f>
         <v>1</v>
       </c>
@@ -4134,19 +4149,19 @@
         <f t="array" ref="C13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!C$2:C$64=1))</f>
         <v>3</v>
       </c>
-      <c r="D13" s="44" cm="1">
+      <c r="D13" s="8" cm="1">
         <f t="array" ref="D13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!D$2:D$64=1))</f>
         <v>3</v>
       </c>
-      <c r="E13" s="44" cm="1">
+      <c r="E13" s="8" cm="1">
         <f t="array" ref="E13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!E$2:E$64=1))</f>
         <v>2</v>
       </c>
-      <c r="F13" s="44" cm="1">
+      <c r="F13" s="8" cm="1">
         <f t="array" ref="F13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!F$2:F$64=1))</f>
         <v>2</v>
       </c>
-      <c r="G13" s="44" cm="1">
+      <c r="G13" s="8" cm="1">
         <f t="array" ref="G13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!G$2:G$64=1))</f>
         <v>3</v>
       </c>
@@ -4158,7 +4173,7 @@
         <f t="array" ref="I13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!I$2:I$64=1))</f>
         <v>2</v>
       </c>
-      <c r="J13" s="44" cm="1">
+      <c r="J13" s="8" cm="1">
         <f t="array" ref="J13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!J$2:J$64=1))</f>
         <v>2</v>
       </c>
@@ -4199,19 +4214,19 @@
         <f t="array" ref="C14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!C$2:C$64=1))</f>
         <v>0</v>
       </c>
-      <c r="D14" s="44" cm="1">
+      <c r="D14" s="8" cm="1">
         <f t="array" ref="D14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!D$2:D$64=1))</f>
         <v>1</v>
       </c>
-      <c r="E14" s="44" cm="1">
+      <c r="E14" s="8" cm="1">
         <f t="array" ref="E14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!E$2:E$64=1))</f>
         <v>1</v>
       </c>
-      <c r="F14" s="44" cm="1">
+      <c r="F14" s="8" cm="1">
         <f t="array" ref="F14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!F$2:F$64=1))</f>
         <v>1</v>
       </c>
-      <c r="G14" s="44" cm="1">
+      <c r="G14" s="8" cm="1">
         <f t="array" ref="G14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!G$2:G$64=1))</f>
         <v>1</v>
       </c>
@@ -4223,7 +4238,7 @@
         <f t="array" ref="I14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!I$2:I$64=1))</f>
         <v>1</v>
       </c>
-      <c r="J14" s="44" cm="1">
+      <c r="J14" s="8" cm="1">
         <f t="array" ref="J14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!J$2:J$64=1))</f>
         <v>1</v>
       </c>
@@ -4327,13 +4342,13 @@
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="11"/>
       <c r="C16" s="20"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
       <c r="H16" s="11"/>
       <c r="I16" s="18"/>
-      <c r="J16" s="44"/>
+      <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
@@ -4350,19 +4365,19 @@
         <f>SUM(C5:C15)</f>
         <v>33</v>
       </c>
-      <c r="D17" s="45">
+      <c r="D17" s="14">
         <f>SUM(D5:D15)</f>
         <v>44</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="14">
         <f t="shared" ref="E17:Q17" si="0">SUM(E5:E15)</f>
         <v>11</v>
       </c>
-      <c r="F17" s="45">
+      <c r="F17" s="14">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="G17" s="45">
+      <c r="G17" s="14">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
@@ -4374,7 +4389,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="J17" s="45">
+      <c r="J17" s="14">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -4415,19 +4430,19 @@
         <f>SUM(Experiments!C2:C53)</f>
         <v>33</v>
       </c>
-      <c r="D18" s="44">
+      <c r="D18" s="8">
         <f>SUM(Experiments!D2:D53)</f>
         <v>33</v>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="8">
         <f>SUM(Experiments!E2:E53)</f>
         <v>7</v>
       </c>
-      <c r="F18" s="44">
+      <c r="F18" s="8">
         <f>SUM(Experiments!F2:F53)</f>
         <v>10</v>
       </c>
-      <c r="G18" s="44">
+      <c r="G18" s="8">
         <f>SUM(Experiments!G2:G53)</f>
         <v>28</v>
       </c>
@@ -4439,7 +4454,7 @@
         <f>SUM(Experiments!I2:I53)</f>
         <v>7</v>
       </c>
-      <c r="J18" s="44">
+      <c r="J18" s="8">
         <f>SUM(Experiments!J2:J53)</f>
         <v>10</v>
       </c>
@@ -4480,19 +4495,19 @@
         <f>SUM(Experiments!C54:C64)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="44">
+      <c r="D19" s="8">
         <f>SUM(Experiments!D54:D64)</f>
         <v>11</v>
       </c>
-      <c r="E19" s="44">
+      <c r="E19" s="8">
         <f>SUM(Experiments!E54:E64)</f>
         <v>4</v>
       </c>
-      <c r="F19" s="44">
+      <c r="F19" s="8">
         <f>SUM(Experiments!F54:F64)</f>
         <v>1</v>
       </c>
-      <c r="G19" s="44">
+      <c r="G19" s="8">
         <f>SUM(Experiments!G54:G64)</f>
         <v>10</v>
       </c>
@@ -4504,7 +4519,7 @@
         <f>SUM(Experiments!I54:I64)</f>
         <v>4</v>
       </c>
-      <c r="J19" s="44">
+      <c r="J19" s="8">
         <f>SUM(Experiments!J54:J64)</f>
         <v>1</v>
       </c>
@@ -4544,23 +4559,23 @@
       <c r="B21" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35" t="s">
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="35"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="40"/>
       <c r="Q21" s="1" t="s">
         <v>59</v>
       </c>
@@ -4576,116 +4591,120 @@
         <f t="array" ref="B22:B36">TRANSPOSE(_xlfn.ANCHORARRAY(C4))</f>
         <v>BHN_FWB</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C22" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="32"/>
-      <c r="O22" s="32"/>
-      <c r="Q22" s="25"/>
-      <c r="R22" s="25"/>
-      <c r="S22" s="25"/>
-      <c r="T22" s="25"/>
-      <c r="U22" s="25"/>
-      <c r="V22" s="25"/>
-      <c r="W22" s="25"/>
-      <c r="X22" s="25"/>
-      <c r="Y22" s="25"/>
-      <c r="Z22" s="25"/>
-      <c r="AA22" s="25"/>
-      <c r="AB22" s="25"/>
-      <c r="AC22" s="25"/>
-      <c r="AD22" s="25"/>
-      <c r="AE22" s="25"/>
-      <c r="AF22" s="25"/>
-      <c r="AG22" s="25"/>
-      <c r="AH22" s="25"/>
-      <c r="AI22" s="25"/>
-      <c r="AJ22" s="25"/>
-      <c r="AK22" s="25"/>
-      <c r="AL22" s="25"/>
-      <c r="AM22" s="25"/>
-      <c r="AN22" s="25"/>
-      <c r="AO22" s="25"/>
-      <c r="AP22" s="25"/>
-      <c r="AQ22" s="25"/>
-      <c r="AR22" s="25" t="e" vm="3">
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="37"/>
+      <c r="M22" s="37"/>
+      <c r="N22" s="37"/>
+      <c r="O22" s="37"/>
+      <c r="Q22" s="30" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
-      <c r="AS22" s="25"/>
-      <c r="AT22" s="25"/>
-      <c r="AU22" s="25"/>
-      <c r="AV22" s="25"/>
-      <c r="AW22" s="25"/>
-      <c r="AX22" s="25"/>
-      <c r="AY22" s="25"/>
+      <c r="R22" s="30"/>
+      <c r="S22" s="30"/>
+      <c r="T22" s="30"/>
+      <c r="U22" s="30"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="30"/>
+      <c r="X22" s="30"/>
+      <c r="Y22" s="30"/>
+      <c r="Z22" s="30"/>
+      <c r="AA22" s="30"/>
+      <c r="AB22" s="30" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC22" s="30"/>
+      <c r="AD22" s="30"/>
+      <c r="AE22" s="30"/>
+      <c r="AF22" s="30"/>
+      <c r="AG22" s="30"/>
+      <c r="AH22" s="30"/>
+      <c r="AI22" s="30"/>
+      <c r="AJ22" s="30"/>
+      <c r="AK22" s="30"/>
+      <c r="AL22" s="30"/>
+      <c r="AM22" s="30"/>
+      <c r="AN22" s="30"/>
+      <c r="AO22" s="30"/>
+      <c r="AP22" s="30"/>
+      <c r="AQ22" s="30"/>
+      <c r="AR22" s="30" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AS22" s="30"/>
+      <c r="AT22" s="30"/>
+      <c r="AU22" s="30"/>
+      <c r="AV22" s="30"/>
+      <c r="AW22" s="30"/>
+      <c r="AX22" s="30"/>
+      <c r="AY22" s="30"/>
     </row>
     <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1</v>
       </c>
-      <c r="B23" s="48" t="str">
+      <c r="B23" s="26" t="str">
         <v>BHN_FWB_AllExt</v>
       </c>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="32"/>
-      <c r="O23" s="32"/>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="25"/>
-      <c r="S23" s="25"/>
-      <c r="T23" s="25"/>
-      <c r="U23" s="25"/>
-      <c r="V23" s="25"/>
-      <c r="W23" s="25"/>
-      <c r="X23" s="25"/>
-      <c r="Y23" s="25"/>
-      <c r="Z23" s="25"/>
-      <c r="AA23" s="25"/>
-      <c r="AB23" s="25"/>
-      <c r="AC23" s="25"/>
-      <c r="AD23" s="25"/>
-      <c r="AE23" s="25"/>
-      <c r="AF23" s="25"/>
-      <c r="AG23" s="25"/>
-      <c r="AH23" s="25"/>
-      <c r="AI23" s="25"/>
-      <c r="AJ23" s="25"/>
-      <c r="AK23" s="25"/>
-      <c r="AL23" s="25"/>
-      <c r="AM23" s="25"/>
-      <c r="AN23" s="25"/>
-      <c r="AO23" s="25"/>
-      <c r="AP23" s="25"/>
-      <c r="AQ23" s="25"/>
-      <c r="AR23" s="25"/>
-      <c r="AS23" s="25"/>
-      <c r="AT23" s="25"/>
-      <c r="AU23" s="25"/>
-      <c r="AV23" s="25"/>
-      <c r="AW23" s="25"/>
-      <c r="AX23" s="25"/>
-      <c r="AY23" s="25"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
+      <c r="M23" s="37"/>
+      <c r="N23" s="37"/>
+      <c r="O23" s="37"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
+      <c r="AA23" s="30"/>
+      <c r="AB23" s="30"/>
+      <c r="AC23" s="30"/>
+      <c r="AD23" s="30"/>
+      <c r="AE23" s="30"/>
+      <c r="AF23" s="30"/>
+      <c r="AG23" s="30"/>
+      <c r="AH23" s="30"/>
+      <c r="AI23" s="30"/>
+      <c r="AJ23" s="30"/>
+      <c r="AK23" s="30"/>
+      <c r="AL23" s="30"/>
+      <c r="AM23" s="30"/>
+      <c r="AN23" s="30"/>
+      <c r="AO23" s="30"/>
+      <c r="AP23" s="30"/>
+      <c r="AQ23" s="30"/>
+      <c r="AR23" s="30"/>
+      <c r="AS23" s="30"/>
+      <c r="AT23" s="30"/>
+      <c r="AU23" s="30"/>
+      <c r="AV23" s="30"/>
+      <c r="AW23" s="30"/>
+      <c r="AX23" s="30"/>
+      <c r="AY23" s="30"/>
     </row>
     <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24">
@@ -4694,56 +4713,56 @@
       <c r="B24" s="7" t="str">
         <v>Few_indicators_closest_DLS_coverage</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C24" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32"/>
-      <c r="M24" s="32"/>
-      <c r="N24" s="32"/>
-      <c r="O24" s="32"/>
-      <c r="Q24" s="25"/>
-      <c r="R24" s="25"/>
-      <c r="S24" s="25"/>
-      <c r="T24" s="25"/>
-      <c r="U24" s="25"/>
-      <c r="V24" s="25"/>
-      <c r="W24" s="25"/>
-      <c r="X24" s="25"/>
-      <c r="Y24" s="25"/>
-      <c r="Z24" s="25"/>
-      <c r="AA24" s="25"/>
-      <c r="AB24" s="25"/>
-      <c r="AC24" s="25"/>
-      <c r="AD24" s="25"/>
-      <c r="AE24" s="25"/>
-      <c r="AF24" s="25"/>
-      <c r="AG24" s="25"/>
-      <c r="AH24" s="25"/>
-      <c r="AI24" s="25"/>
-      <c r="AJ24" s="25"/>
-      <c r="AK24" s="25"/>
-      <c r="AL24" s="25"/>
-      <c r="AM24" s="25"/>
-      <c r="AN24" s="25"/>
-      <c r="AO24" s="25"/>
-      <c r="AP24" s="25"/>
-      <c r="AQ24" s="25"/>
-      <c r="AR24" s="25"/>
-      <c r="AS24" s="25"/>
-      <c r="AT24" s="25"/>
-      <c r="AU24" s="25"/>
-      <c r="AV24" s="25"/>
-      <c r="AW24" s="25"/>
-      <c r="AX24" s="25"/>
-      <c r="AY24" s="25"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="37"/>
+      <c r="M24" s="37"/>
+      <c r="N24" s="37"/>
+      <c r="O24" s="37"/>
+      <c r="Q24" s="30"/>
+      <c r="R24" s="30"/>
+      <c r="S24" s="30"/>
+      <c r="T24" s="30"/>
+      <c r="U24" s="30"/>
+      <c r="V24" s="30"/>
+      <c r="W24" s="30"/>
+      <c r="X24" s="30"/>
+      <c r="Y24" s="30"/>
+      <c r="Z24" s="30"/>
+      <c r="AA24" s="30"/>
+      <c r="AB24" s="30"/>
+      <c r="AC24" s="30"/>
+      <c r="AD24" s="30"/>
+      <c r="AE24" s="30"/>
+      <c r="AF24" s="30"/>
+      <c r="AG24" s="30"/>
+      <c r="AH24" s="30"/>
+      <c r="AI24" s="30"/>
+      <c r="AJ24" s="30"/>
+      <c r="AK24" s="30"/>
+      <c r="AL24" s="30"/>
+      <c r="AM24" s="30"/>
+      <c r="AN24" s="30"/>
+      <c r="AO24" s="30"/>
+      <c r="AP24" s="30"/>
+      <c r="AQ24" s="30"/>
+      <c r="AR24" s="30"/>
+      <c r="AS24" s="30"/>
+      <c r="AT24" s="30"/>
+      <c r="AU24" s="30"/>
+      <c r="AV24" s="30"/>
+      <c r="AW24" s="30"/>
+      <c r="AX24" s="30"/>
+      <c r="AY24" s="30"/>
     </row>
     <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25">
@@ -4752,48 +4771,48 @@
       <c r="B25" s="7" t="str">
         <v>Few indicators_SPI_preferred</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
-      <c r="N25" s="32"/>
-      <c r="O25" s="32"/>
-      <c r="Q25" s="25"/>
-      <c r="R25" s="25"/>
-      <c r="S25" s="25"/>
-      <c r="T25" s="25"/>
-      <c r="U25" s="25"/>
-      <c r="V25" s="25"/>
-      <c r="W25" s="25"/>
-      <c r="X25" s="25"/>
-      <c r="Y25" s="25"/>
-      <c r="Z25" s="25"/>
-      <c r="AA25" s="25"/>
-      <c r="AB25" s="25"/>
-      <c r="AC25" s="25"/>
-      <c r="AD25" s="25"/>
-      <c r="AE25" s="25"/>
-      <c r="AF25" s="25"/>
-      <c r="AG25" s="25"/>
-      <c r="AH25" s="25"/>
-      <c r="AI25" s="25"/>
-      <c r="AJ25" s="25"/>
-      <c r="AK25" s="25"/>
-      <c r="AL25" s="25"/>
-      <c r="AM25" s="25"/>
-      <c r="AN25" s="25"/>
-      <c r="AO25" s="25"/>
-      <c r="AP25" s="25"/>
-      <c r="AQ25" s="25"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="37"/>
+      <c r="K25" s="37"/>
+      <c r="L25" s="37"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="Q25" s="49"/>
+      <c r="R25" s="49"/>
+      <c r="S25" s="49"/>
+      <c r="T25" s="49"/>
+      <c r="U25" s="49"/>
+      <c r="V25" s="49"/>
+      <c r="W25" s="49"/>
+      <c r="X25" s="49"/>
+      <c r="Y25" s="49"/>
+      <c r="Z25" s="49"/>
+      <c r="AA25" s="49"/>
+      <c r="AB25" s="30"/>
+      <c r="AC25" s="30"/>
+      <c r="AD25" s="30"/>
+      <c r="AE25" s="30"/>
+      <c r="AF25" s="30"/>
+      <c r="AG25" s="30"/>
+      <c r="AH25" s="30"/>
+      <c r="AI25" s="30"/>
+      <c r="AJ25" s="30"/>
+      <c r="AK25" s="30"/>
+      <c r="AL25" s="30"/>
+      <c r="AM25" s="30"/>
+      <c r="AN25" s="30"/>
+      <c r="AO25" s="30"/>
+      <c r="AP25" s="30"/>
+      <c r="AQ25" s="30"/>
     </row>
     <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26">
@@ -4802,98 +4821,98 @@
       <c r="B26" s="7" t="str">
         <v>No_non_DLS</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="C26" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
-      <c r="N26" s="32"/>
-      <c r="O26" s="32"/>
-      <c r="Q26" s="25"/>
-      <c r="R26" s="25"/>
-      <c r="S26" s="25"/>
-      <c r="T26" s="25"/>
-      <c r="U26" s="25"/>
-      <c r="V26" s="25"/>
-      <c r="W26" s="25"/>
-      <c r="X26" s="25"/>
-      <c r="Y26" s="25"/>
-      <c r="Z26" s="25"/>
-      <c r="AA26" s="25"/>
-      <c r="AB26" s="25"/>
-      <c r="AC26" s="25"/>
-      <c r="AD26" s="25"/>
-      <c r="AE26" s="25"/>
-      <c r="AF26" s="25"/>
-      <c r="AG26" s="25"/>
-      <c r="AH26" s="25"/>
-      <c r="AI26" s="25"/>
-      <c r="AJ26" s="25"/>
-      <c r="AK26" s="25"/>
-      <c r="AL26" s="25"/>
-      <c r="AM26" s="25"/>
-      <c r="AN26" s="25"/>
-      <c r="AO26" s="25"/>
-      <c r="AP26" s="25"/>
-      <c r="AQ26" s="25"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="37"/>
+      <c r="M26" s="37"/>
+      <c r="N26" s="37"/>
+      <c r="O26" s="37"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
+      <c r="AA26" s="30"/>
+      <c r="AB26" s="30"/>
+      <c r="AC26" s="30"/>
+      <c r="AD26" s="30"/>
+      <c r="AE26" s="30"/>
+      <c r="AF26" s="30"/>
+      <c r="AG26" s="30"/>
+      <c r="AH26" s="30"/>
+      <c r="AI26" s="30"/>
+      <c r="AJ26" s="30"/>
+      <c r="AK26" s="30"/>
+      <c r="AL26" s="30"/>
+      <c r="AM26" s="30"/>
+      <c r="AN26" s="30"/>
+      <c r="AO26" s="30"/>
+      <c r="AP26" s="30"/>
+      <c r="AQ26" s="30"/>
     </row>
     <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1</v>
       </c>
-      <c r="B27" s="48" t="str">
+      <c r="B27" s="26" t="str">
         <v>Only_%_of_pop</v>
       </c>
-      <c r="C27" s="50" t="s">
+      <c r="C27" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
-      <c r="M27" s="32"/>
-      <c r="N27" s="32"/>
-      <c r="O27" s="32"/>
-      <c r="Q27" s="25"/>
-      <c r="R27" s="25"/>
-      <c r="S27" s="25"/>
-      <c r="T27" s="25"/>
-      <c r="U27" s="25"/>
-      <c r="V27" s="25"/>
-      <c r="W27" s="25"/>
-      <c r="X27" s="25"/>
-      <c r="Y27" s="25"/>
-      <c r="Z27" s="25"/>
-      <c r="AA27" s="25"/>
-      <c r="AB27" s="25"/>
-      <c r="AC27" s="25"/>
-      <c r="AD27" s="25"/>
-      <c r="AE27" s="25"/>
-      <c r="AF27" s="25"/>
-      <c r="AG27" s="25"/>
-      <c r="AH27" s="25"/>
-      <c r="AI27" s="25"/>
-      <c r="AJ27" s="25"/>
-      <c r="AK27" s="25"/>
-      <c r="AL27" s="25"/>
-      <c r="AM27" s="25"/>
-      <c r="AN27" s="25"/>
-      <c r="AO27" s="25"/>
-      <c r="AP27" s="25"/>
-      <c r="AQ27" s="25"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="37"/>
+      <c r="M27" s="37"/>
+      <c r="N27" s="37"/>
+      <c r="O27" s="37"/>
+      <c r="Q27" s="30"/>
+      <c r="R27" s="30"/>
+      <c r="S27" s="30"/>
+      <c r="T27" s="30"/>
+      <c r="U27" s="30"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="30"/>
+      <c r="X27" s="30"/>
+      <c r="Y27" s="30"/>
+      <c r="Z27" s="30"/>
+      <c r="AA27" s="30"/>
+      <c r="AB27" s="30"/>
+      <c r="AC27" s="30"/>
+      <c r="AD27" s="30"/>
+      <c r="AE27" s="30"/>
+      <c r="AF27" s="30"/>
+      <c r="AG27" s="30"/>
+      <c r="AH27" s="30"/>
+      <c r="AI27" s="30"/>
+      <c r="AJ27" s="30"/>
+      <c r="AK27" s="30"/>
+      <c r="AL27" s="30"/>
+      <c r="AM27" s="30"/>
+      <c r="AN27" s="30"/>
+      <c r="AO27" s="30"/>
+      <c r="AP27" s="30"/>
+      <c r="AQ27" s="30"/>
     </row>
     <row r="28" spans="1:51" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28">
@@ -4902,48 +4921,48 @@
       <c r="B28" s="17" t="str">
         <v>Few_indicators_closest_DLS_coverage_90</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="30"/>
-      <c r="O28" s="30"/>
-      <c r="Q28" s="25"/>
-      <c r="R28" s="25"/>
-      <c r="S28" s="25"/>
-      <c r="T28" s="25"/>
-      <c r="U28" s="25"/>
-      <c r="V28" s="25"/>
-      <c r="W28" s="25"/>
-      <c r="X28" s="25"/>
-      <c r="Y28" s="25"/>
-      <c r="Z28" s="25"/>
-      <c r="AA28" s="25"/>
-      <c r="AB28" s="25"/>
-      <c r="AC28" s="25"/>
-      <c r="AD28" s="25"/>
-      <c r="AE28" s="25"/>
-      <c r="AF28" s="25"/>
-      <c r="AG28" s="25"/>
-      <c r="AH28" s="25"/>
-      <c r="AI28" s="25"/>
-      <c r="AJ28" s="25"/>
-      <c r="AK28" s="25"/>
-      <c r="AL28" s="25"/>
-      <c r="AM28" s="25"/>
-      <c r="AN28" s="25"/>
-      <c r="AO28" s="25"/>
-      <c r="AP28" s="25"/>
-      <c r="AQ28" s="25"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="35"/>
+      <c r="Q28" s="30"/>
+      <c r="R28" s="30"/>
+      <c r="S28" s="30"/>
+      <c r="T28" s="30"/>
+      <c r="U28" s="30"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="30"/>
+      <c r="X28" s="30"/>
+      <c r="Y28" s="30"/>
+      <c r="Z28" s="30"/>
+      <c r="AA28" s="30"/>
+      <c r="AB28" s="30"/>
+      <c r="AC28" s="30"/>
+      <c r="AD28" s="30"/>
+      <c r="AE28" s="30"/>
+      <c r="AF28" s="30"/>
+      <c r="AG28" s="30"/>
+      <c r="AH28" s="30"/>
+      <c r="AI28" s="30"/>
+      <c r="AJ28" s="30"/>
+      <c r="AK28" s="30"/>
+      <c r="AL28" s="30"/>
+      <c r="AM28" s="30"/>
+      <c r="AN28" s="30"/>
+      <c r="AO28" s="30"/>
+      <c r="AP28" s="30"/>
+      <c r="AQ28" s="30"/>
     </row>
     <row r="29" spans="1:51" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29">
@@ -4952,48 +4971,48 @@
       <c r="B29" s="17" t="str">
         <v>Few indicators_SPI_preferred_90</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="Q29" s="25"/>
-      <c r="R29" s="25"/>
-      <c r="S29" s="25"/>
-      <c r="T29" s="25"/>
-      <c r="U29" s="25"/>
-      <c r="V29" s="25"/>
-      <c r="W29" s="25"/>
-      <c r="X29" s="25"/>
-      <c r="Y29" s="25"/>
-      <c r="Z29" s="25"/>
-      <c r="AA29" s="25"/>
-      <c r="AB29" s="25"/>
-      <c r="AC29" s="25"/>
-      <c r="AD29" s="25"/>
-      <c r="AE29" s="25"/>
-      <c r="AF29" s="25"/>
-      <c r="AG29" s="25"/>
-      <c r="AH29" s="25"/>
-      <c r="AI29" s="25"/>
-      <c r="AJ29" s="25"/>
-      <c r="AK29" s="25"/>
-      <c r="AL29" s="25"/>
-      <c r="AM29" s="25"/>
-      <c r="AN29" s="25"/>
-      <c r="AO29" s="25"/>
-      <c r="AP29" s="25"/>
-      <c r="AQ29" s="25"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="35"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
+      <c r="AA29" s="30"/>
+      <c r="AB29" s="30"/>
+      <c r="AC29" s="30"/>
+      <c r="AD29" s="30"/>
+      <c r="AE29" s="30"/>
+      <c r="AF29" s="30"/>
+      <c r="AG29" s="30"/>
+      <c r="AH29" s="30"/>
+      <c r="AI29" s="30"/>
+      <c r="AJ29" s="30"/>
+      <c r="AK29" s="30"/>
+      <c r="AL29" s="30"/>
+      <c r="AM29" s="30"/>
+      <c r="AN29" s="30"/>
+      <c r="AO29" s="30"/>
+      <c r="AP29" s="30"/>
+      <c r="AQ29" s="30"/>
     </row>
     <row r="30" spans="1:51" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30">
@@ -5002,650 +5021,652 @@
       <c r="B30" s="17" t="str">
         <v>Few_indicators_closeDLS_subPrimSchool</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="30"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="30"/>
-      <c r="O30" s="30"/>
-      <c r="Q30" s="25"/>
-      <c r="R30" s="25"/>
-      <c r="S30" s="25"/>
-      <c r="T30" s="25"/>
-      <c r="U30" s="25"/>
-      <c r="V30" s="25"/>
-      <c r="W30" s="25"/>
-      <c r="X30" s="25"/>
-      <c r="Y30" s="25"/>
-      <c r="Z30" s="25"/>
-      <c r="AA30" s="25"/>
-      <c r="AB30" s="25"/>
-      <c r="AC30" s="25"/>
-      <c r="AD30" s="25"/>
-      <c r="AE30" s="25"/>
-      <c r="AF30" s="25"/>
-      <c r="AG30" s="25"/>
-      <c r="AH30" s="25"/>
-      <c r="AI30" s="25"/>
-      <c r="AJ30" s="25"/>
-      <c r="AK30" s="25"/>
-      <c r="AL30" s="25"/>
-      <c r="AM30" s="25"/>
-      <c r="AN30" s="25"/>
-      <c r="AO30" s="25"/>
-      <c r="AP30" s="25"/>
-      <c r="AQ30" s="25"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
+      <c r="N30" s="35"/>
+      <c r="O30" s="35"/>
+      <c r="Q30" s="30"/>
+      <c r="R30" s="30"/>
+      <c r="S30" s="30"/>
+      <c r="T30" s="30"/>
+      <c r="U30" s="30"/>
+      <c r="V30" s="30"/>
+      <c r="W30" s="30"/>
+      <c r="X30" s="30"/>
+      <c r="Y30" s="30"/>
+      <c r="Z30" s="30"/>
+      <c r="AA30" s="30"/>
+      <c r="AB30" s="30"/>
+      <c r="AC30" s="30"/>
+      <c r="AD30" s="30"/>
+      <c r="AE30" s="30"/>
+      <c r="AF30" s="30"/>
+      <c r="AG30" s="30"/>
+      <c r="AH30" s="30"/>
+      <c r="AI30" s="30"/>
+      <c r="AJ30" s="30"/>
+      <c r="AK30" s="30"/>
+      <c r="AL30" s="30"/>
+      <c r="AM30" s="30"/>
+      <c r="AN30" s="30"/>
+      <c r="AO30" s="30"/>
+      <c r="AP30" s="30"/>
+      <c r="AQ30" s="30"/>
     </row>
     <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
-      <c r="B31" s="51" t="str">
+      <c r="B31" s="27" t="str">
         <v>No_non_DLS_90</v>
       </c>
-      <c r="C31" s="52" t="s">
+      <c r="C31" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="52" t="s">
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="J31" s="52"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="52"/>
-      <c r="M31" s="52"/>
-      <c r="N31" s="52"/>
-      <c r="O31" s="52"/>
-      <c r="Q31" s="25"/>
-      <c r="R31" s="25"/>
-      <c r="S31" s="25"/>
-      <c r="T31" s="25"/>
-      <c r="U31" s="25"/>
-      <c r="V31" s="25"/>
-      <c r="W31" s="25"/>
-      <c r="X31" s="25"/>
-      <c r="Y31" s="25"/>
-      <c r="Z31" s="25"/>
-      <c r="AA31" s="25"/>
-      <c r="AB31" s="25"/>
-      <c r="AC31" s="25"/>
-      <c r="AD31" s="25"/>
-      <c r="AE31" s="25"/>
-      <c r="AF31" s="25"/>
-      <c r="AG31" s="25"/>
-      <c r="AH31" s="25"/>
-      <c r="AI31" s="25"/>
-      <c r="AJ31" s="25"/>
-      <c r="AK31" s="25"/>
-      <c r="AL31" s="25"/>
-      <c r="AM31" s="25"/>
-      <c r="AN31" s="25"/>
-      <c r="AO31" s="25"/>
-      <c r="AP31" s="25"/>
-      <c r="AQ31" s="25"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
+      <c r="Q31" s="30"/>
+      <c r="R31" s="30"/>
+      <c r="S31" s="30"/>
+      <c r="T31" s="30"/>
+      <c r="U31" s="30"/>
+      <c r="V31" s="30"/>
+      <c r="W31" s="30"/>
+      <c r="X31" s="30"/>
+      <c r="Y31" s="30"/>
+      <c r="Z31" s="30"/>
+      <c r="AA31" s="30"/>
+      <c r="AB31" s="30"/>
+      <c r="AC31" s="30"/>
+      <c r="AD31" s="30"/>
+      <c r="AE31" s="30"/>
+      <c r="AF31" s="30"/>
+      <c r="AG31" s="30"/>
+      <c r="AH31" s="30"/>
+      <c r="AI31" s="30"/>
+      <c r="AJ31" s="30"/>
+      <c r="AK31" s="30"/>
+      <c r="AL31" s="30"/>
+      <c r="AM31" s="30"/>
+      <c r="AN31" s="30"/>
+      <c r="AO31" s="30"/>
+      <c r="AP31" s="30"/>
+      <c r="AQ31" s="30"/>
     </row>
     <row r="32" spans="1:51" ht="103.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
-      <c r="B32" s="51" t="str">
+      <c r="B32" s="27" t="str">
         <v>Few_Indicators_subWatSani</v>
       </c>
-      <c r="C32" s="52" t="s">
+      <c r="C32" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="Q32" s="25"/>
-      <c r="R32" s="25"/>
-      <c r="S32" s="25"/>
-      <c r="T32" s="25"/>
-      <c r="U32" s="25"/>
-      <c r="V32" s="25"/>
-      <c r="W32" s="25"/>
-      <c r="X32" s="25"/>
-      <c r="Y32" s="25"/>
-      <c r="Z32" s="25"/>
-      <c r="AA32" s="25"/>
-      <c r="AB32" s="25"/>
-      <c r="AC32" s="25"/>
-      <c r="AD32" s="25"/>
-      <c r="AE32" s="25"/>
-      <c r="AF32" s="25"/>
-      <c r="AG32" s="25"/>
-      <c r="AH32" s="25"/>
-      <c r="AI32" s="25"/>
-      <c r="AJ32" s="25"/>
-      <c r="AK32" s="25"/>
-      <c r="AL32" s="25"/>
-      <c r="AM32" s="25"/>
-      <c r="AN32" s="25"/>
-      <c r="AO32" s="25"/>
-      <c r="AP32" s="25"/>
-      <c r="AQ32" s="25"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="46"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="35"/>
+      <c r="N32" s="35"/>
+      <c r="O32" s="35"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="30"/>
+      <c r="AA32" s="30"/>
+      <c r="AB32" s="30"/>
+      <c r="AC32" s="30"/>
+      <c r="AD32" s="30"/>
+      <c r="AE32" s="30"/>
+      <c r="AF32" s="30"/>
+      <c r="AG32" s="30"/>
+      <c r="AH32" s="30"/>
+      <c r="AI32" s="30"/>
+      <c r="AJ32" s="30"/>
+      <c r="AK32" s="30"/>
+      <c r="AL32" s="30"/>
+      <c r="AM32" s="30"/>
+      <c r="AN32" s="30"/>
+      <c r="AO32" s="30"/>
+      <c r="AP32" s="30"/>
+      <c r="AQ32" s="30"/>
     </row>
     <row r="33" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>4</v>
       </c>
-      <c r="B33" s="53" t="str">
+      <c r="B33" s="28" t="str">
         <v>Only_OPP</v>
       </c>
-      <c r="C33" s="54" t="s">
+      <c r="C33" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="27"/>
-      <c r="J33" s="27"/>
-      <c r="K33" s="27"/>
-      <c r="L33" s="27"/>
-      <c r="M33" s="27"/>
-      <c r="N33" s="27"/>
-      <c r="O33" s="27"/>
-      <c r="Q33" s="25"/>
-      <c r="R33" s="25"/>
-      <c r="S33" s="25"/>
-      <c r="T33" s="25"/>
-      <c r="U33" s="25"/>
-      <c r="V33" s="25"/>
-      <c r="W33" s="25"/>
-      <c r="X33" s="25"/>
-      <c r="Y33" s="25"/>
-      <c r="Z33" s="25"/>
-      <c r="AA33" s="25"/>
-      <c r="AB33" s="25"/>
-      <c r="AC33" s="25"/>
-      <c r="AD33" s="25"/>
-      <c r="AE33" s="25"/>
-      <c r="AF33" s="25"/>
-      <c r="AG33" s="25"/>
-      <c r="AH33" s="25"/>
-      <c r="AI33" s="25"/>
-      <c r="AJ33" s="25"/>
-      <c r="AK33" s="25"/>
-      <c r="AL33" s="25"/>
-      <c r="AM33" s="25"/>
-      <c r="AN33" s="25"/>
-      <c r="AO33" s="25"/>
-      <c r="AP33" s="25"/>
-      <c r="AQ33" s="25"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
+      <c r="Q33" s="30"/>
+      <c r="R33" s="30"/>
+      <c r="S33" s="30"/>
+      <c r="T33" s="30"/>
+      <c r="U33" s="30"/>
+      <c r="V33" s="30"/>
+      <c r="W33" s="30"/>
+      <c r="X33" s="30"/>
+      <c r="Y33" s="30"/>
+      <c r="Z33" s="30"/>
+      <c r="AA33" s="30"/>
+      <c r="AB33" s="30"/>
+      <c r="AC33" s="30"/>
+      <c r="AD33" s="30"/>
+      <c r="AE33" s="30"/>
+      <c r="AF33" s="30"/>
+      <c r="AG33" s="30"/>
+      <c r="AH33" s="30"/>
+      <c r="AI33" s="30"/>
+      <c r="AJ33" s="30"/>
+      <c r="AK33" s="30"/>
+      <c r="AL33" s="30"/>
+      <c r="AM33" s="30"/>
+      <c r="AN33" s="30"/>
+      <c r="AO33" s="30"/>
+      <c r="AP33" s="30"/>
+      <c r="AQ33" s="30"/>
     </row>
     <row r="34" spans="1:43" x14ac:dyDescent="0.3">
       <c r="B34" s="6" t="str">
         <v>Baseline</v>
       </c>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="27"/>
-      <c r="K34" s="27"/>
-      <c r="L34" s="27"/>
-      <c r="M34" s="27"/>
-      <c r="N34" s="27"/>
-      <c r="O34" s="27"/>
-      <c r="Q34" s="25"/>
-      <c r="R34" s="25"/>
-      <c r="S34" s="25"/>
-      <c r="T34" s="25"/>
-      <c r="U34" s="25"/>
-      <c r="V34" s="25"/>
-      <c r="W34" s="25"/>
-      <c r="X34" s="25"/>
-      <c r="Y34" s="25"/>
-      <c r="Z34" s="25"/>
-      <c r="AA34" s="25"/>
-      <c r="AB34" s="25"/>
-      <c r="AC34" s="25"/>
-      <c r="AD34" s="25"/>
-      <c r="AE34" s="25"/>
-      <c r="AF34" s="25"/>
-      <c r="AG34" s="25"/>
-      <c r="AH34" s="25"/>
-      <c r="AI34" s="25"/>
-      <c r="AJ34" s="25"/>
-      <c r="AK34" s="25"/>
-      <c r="AL34" s="25"/>
-      <c r="AM34" s="25"/>
-      <c r="AN34" s="25"/>
-      <c r="AO34" s="25"/>
-      <c r="AP34" s="25"/>
-      <c r="AQ34" s="25"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="32"/>
+      <c r="K34" s="32"/>
+      <c r="L34" s="32"/>
+      <c r="M34" s="32"/>
+      <c r="N34" s="32"/>
+      <c r="O34" s="32"/>
+      <c r="Q34" s="30"/>
+      <c r="R34" s="30"/>
+      <c r="S34" s="30"/>
+      <c r="T34" s="30"/>
+      <c r="U34" s="30"/>
+      <c r="V34" s="30"/>
+      <c r="W34" s="30"/>
+      <c r="X34" s="30"/>
+      <c r="Y34" s="30"/>
+      <c r="Z34" s="30"/>
+      <c r="AA34" s="30"/>
+      <c r="AB34" s="30"/>
+      <c r="AC34" s="30"/>
+      <c r="AD34" s="30"/>
+      <c r="AE34" s="30"/>
+      <c r="AF34" s="30"/>
+      <c r="AG34" s="30"/>
+      <c r="AH34" s="30"/>
+      <c r="AI34" s="30"/>
+      <c r="AJ34" s="30"/>
+      <c r="AK34" s="30"/>
+      <c r="AL34" s="30"/>
+      <c r="AM34" s="30"/>
+      <c r="AN34" s="30"/>
+      <c r="AO34" s="30"/>
+      <c r="AP34" s="30"/>
+      <c r="AQ34" s="30"/>
     </row>
     <row r="35" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="B35" s="53" t="str">
+      <c r="B35" s="28" t="str">
         <v>No_nonDLS_limExt</v>
       </c>
-      <c r="C35" s="55"/>
-      <c r="D35" s="55"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="55"/>
-      <c r="H35" s="55"/>
-      <c r="I35" s="55" t="s">
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="J35" s="55"/>
-      <c r="K35" s="55"/>
-      <c r="L35" s="55"/>
-      <c r="M35" s="55"/>
-      <c r="N35" s="55"/>
-      <c r="O35" s="55"/>
-      <c r="Q35" s="25"/>
-      <c r="R35" s="25"/>
-      <c r="S35" s="25"/>
-      <c r="T35" s="25"/>
-      <c r="U35" s="25"/>
-      <c r="V35" s="25"/>
-      <c r="W35" s="25"/>
-      <c r="X35" s="25"/>
-      <c r="Y35" s="25"/>
-      <c r="Z35" s="25"/>
-      <c r="AA35" s="25"/>
-      <c r="AB35" s="25"/>
-      <c r="AC35" s="25"/>
-      <c r="AD35" s="25"/>
-      <c r="AE35" s="25"/>
-      <c r="AF35" s="25"/>
-      <c r="AG35" s="25"/>
-      <c r="AH35" s="25"/>
-      <c r="AI35" s="25"/>
-      <c r="AJ35" s="25"/>
-      <c r="AK35" s="25"/>
-      <c r="AL35" s="25"/>
-      <c r="AM35" s="25"/>
-      <c r="AN35" s="25"/>
-      <c r="AO35" s="25"/>
-      <c r="AP35" s="25"/>
-      <c r="AQ35" s="25"/>
+      <c r="J35" s="48"/>
+      <c r="K35" s="48"/>
+      <c r="L35" s="48"/>
+      <c r="M35" s="48"/>
+      <c r="N35" s="48"/>
+      <c r="O35" s="48"/>
+      <c r="Q35" s="30"/>
+      <c r="R35" s="30"/>
+      <c r="S35" s="30"/>
+      <c r="T35" s="30"/>
+      <c r="U35" s="30"/>
+      <c r="V35" s="30"/>
+      <c r="W35" s="30"/>
+      <c r="X35" s="30"/>
+      <c r="Y35" s="30"/>
+      <c r="Z35" s="30"/>
+      <c r="AA35" s="30"/>
+      <c r="AB35" s="30"/>
+      <c r="AC35" s="30"/>
+      <c r="AD35" s="30"/>
+      <c r="AE35" s="30"/>
+      <c r="AF35" s="30"/>
+      <c r="AG35" s="30"/>
+      <c r="AH35" s="30"/>
+      <c r="AI35" s="30"/>
+      <c r="AJ35" s="30"/>
+      <c r="AK35" s="30"/>
+      <c r="AL35" s="30"/>
+      <c r="AM35" s="30"/>
+      <c r="AN35" s="30"/>
+      <c r="AO35" s="30"/>
+      <c r="AP35" s="30"/>
+      <c r="AQ35" s="30"/>
     </row>
     <row r="36" spans="1:43" ht="76.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="str">
         <v>BHN</v>
       </c>
-      <c r="C36" s="31" t="s">
+      <c r="C36" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="27"/>
-      <c r="L36" s="27"/>
-      <c r="M36" s="27"/>
-      <c r="N36" s="27"/>
-      <c r="O36" s="27"/>
-      <c r="Q36" s="25"/>
-      <c r="R36" s="25"/>
-      <c r="S36" s="25"/>
-      <c r="T36" s="25"/>
-      <c r="U36" s="25"/>
-      <c r="V36" s="25"/>
-      <c r="W36" s="25"/>
-      <c r="X36" s="25"/>
-      <c r="Y36" s="25"/>
-      <c r="Z36" s="25"/>
-      <c r="AA36" s="25"/>
-      <c r="AB36" s="25"/>
-      <c r="AC36" s="25"/>
-      <c r="AD36" s="25"/>
-      <c r="AE36" s="25"/>
-      <c r="AF36" s="25"/>
-      <c r="AG36" s="25"/>
-      <c r="AH36" s="25"/>
-      <c r="AI36" s="25"/>
-      <c r="AJ36" s="25"/>
-      <c r="AK36" s="25"/>
-      <c r="AL36" s="25"/>
-      <c r="AM36" s="25"/>
-      <c r="AN36" s="25"/>
-      <c r="AO36" s="25"/>
-      <c r="AP36" s="25"/>
-      <c r="AQ36" s="25"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="32"/>
+      <c r="Q36" s="30"/>
+      <c r="R36" s="30"/>
+      <c r="S36" s="30"/>
+      <c r="T36" s="30"/>
+      <c r="U36" s="30"/>
+      <c r="V36" s="30"/>
+      <c r="W36" s="30"/>
+      <c r="X36" s="30"/>
+      <c r="Y36" s="30"/>
+      <c r="Z36" s="30"/>
+      <c r="AA36" s="30"/>
+      <c r="AB36" s="30"/>
+      <c r="AC36" s="30"/>
+      <c r="AD36" s="30"/>
+      <c r="AE36" s="30"/>
+      <c r="AF36" s="30"/>
+      <c r="AG36" s="30"/>
+      <c r="AH36" s="30"/>
+      <c r="AI36" s="30"/>
+      <c r="AJ36" s="30"/>
+      <c r="AK36" s="30"/>
+      <c r="AL36" s="30"/>
+      <c r="AM36" s="30"/>
+      <c r="AN36" s="30"/>
+      <c r="AO36" s="30"/>
+      <c r="AP36" s="30"/>
+      <c r="AQ36" s="30"/>
     </row>
     <row r="37" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB37" s="25"/>
-      <c r="AC37" s="25"/>
-      <c r="AD37" s="25"/>
-      <c r="AE37" s="25"/>
-      <c r="AF37" s="25"/>
-      <c r="AG37" s="25"/>
-      <c r="AH37" s="25"/>
-      <c r="AI37" s="25"/>
-      <c r="AJ37" s="25"/>
-      <c r="AK37" s="25"/>
-      <c r="AL37" s="25"/>
-      <c r="AM37" s="25"/>
-      <c r="AN37" s="25"/>
-      <c r="AO37" s="25"/>
-      <c r="AP37" s="25"/>
-      <c r="AQ37" s="25"/>
+      <c r="AB37" s="30"/>
+      <c r="AC37" s="30"/>
+      <c r="AD37" s="30"/>
+      <c r="AE37" s="30"/>
+      <c r="AF37" s="30"/>
+      <c r="AG37" s="30"/>
+      <c r="AH37" s="30"/>
+      <c r="AI37" s="30"/>
+      <c r="AJ37" s="30"/>
+      <c r="AK37" s="30"/>
+      <c r="AL37" s="30"/>
+      <c r="AM37" s="30"/>
+      <c r="AN37" s="30"/>
+      <c r="AO37" s="30"/>
+      <c r="AP37" s="30"/>
+      <c r="AQ37" s="30"/>
     </row>
     <row r="38" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB38" s="25"/>
-      <c r="AC38" s="25"/>
-      <c r="AD38" s="25"/>
-      <c r="AE38" s="25"/>
-      <c r="AF38" s="25"/>
-      <c r="AG38" s="25"/>
-      <c r="AH38" s="25"/>
-      <c r="AI38" s="25"/>
-      <c r="AJ38" s="25"/>
-      <c r="AK38" s="25"/>
-      <c r="AL38" s="25"/>
-      <c r="AM38" s="25"/>
-      <c r="AN38" s="25"/>
-      <c r="AO38" s="25"/>
-      <c r="AP38" s="25"/>
-      <c r="AQ38" s="25"/>
+      <c r="AB38" s="30"/>
+      <c r="AC38" s="30"/>
+      <c r="AD38" s="30"/>
+      <c r="AE38" s="30"/>
+      <c r="AF38" s="30"/>
+      <c r="AG38" s="30"/>
+      <c r="AH38" s="30"/>
+      <c r="AI38" s="30"/>
+      <c r="AJ38" s="30"/>
+      <c r="AK38" s="30"/>
+      <c r="AL38" s="30"/>
+      <c r="AM38" s="30"/>
+      <c r="AN38" s="30"/>
+      <c r="AO38" s="30"/>
+      <c r="AP38" s="30"/>
+      <c r="AQ38" s="30"/>
     </row>
     <row r="39" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB39" s="25"/>
-      <c r="AC39" s="25"/>
-      <c r="AD39" s="25"/>
-      <c r="AE39" s="25"/>
-      <c r="AF39" s="25"/>
-      <c r="AG39" s="25"/>
-      <c r="AH39" s="25"/>
-      <c r="AI39" s="25"/>
-      <c r="AJ39" s="25"/>
-      <c r="AK39" s="25"/>
-      <c r="AL39" s="25"/>
-      <c r="AM39" s="25"/>
-      <c r="AN39" s="25"/>
-      <c r="AO39" s="25"/>
-      <c r="AP39" s="25"/>
-      <c r="AQ39" s="25"/>
+      <c r="AB39" s="30"/>
+      <c r="AC39" s="30"/>
+      <c r="AD39" s="30"/>
+      <c r="AE39" s="30"/>
+      <c r="AF39" s="30"/>
+      <c r="AG39" s="30"/>
+      <c r="AH39" s="30"/>
+      <c r="AI39" s="30"/>
+      <c r="AJ39" s="30"/>
+      <c r="AK39" s="30"/>
+      <c r="AL39" s="30"/>
+      <c r="AM39" s="30"/>
+      <c r="AN39" s="30"/>
+      <c r="AO39" s="30"/>
+      <c r="AP39" s="30"/>
+      <c r="AQ39" s="30"/>
     </row>
     <row r="40" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB40" s="25"/>
-      <c r="AC40" s="25"/>
-      <c r="AD40" s="25"/>
-      <c r="AE40" s="25"/>
-      <c r="AF40" s="25"/>
-      <c r="AG40" s="25"/>
-      <c r="AH40" s="25"/>
-      <c r="AI40" s="25"/>
-      <c r="AJ40" s="25"/>
-      <c r="AK40" s="25"/>
-      <c r="AL40" s="25"/>
-      <c r="AM40" s="25"/>
-      <c r="AN40" s="25"/>
-      <c r="AO40" s="25"/>
-      <c r="AP40" s="25"/>
-      <c r="AQ40" s="25"/>
+      <c r="AB40" s="30"/>
+      <c r="AC40" s="30"/>
+      <c r="AD40" s="30"/>
+      <c r="AE40" s="30"/>
+      <c r="AF40" s="30"/>
+      <c r="AG40" s="30"/>
+      <c r="AH40" s="30"/>
+      <c r="AI40" s="30"/>
+      <c r="AJ40" s="30"/>
+      <c r="AK40" s="30"/>
+      <c r="AL40" s="30"/>
+      <c r="AM40" s="30"/>
+      <c r="AN40" s="30"/>
+      <c r="AO40" s="30"/>
+      <c r="AP40" s="30"/>
+      <c r="AQ40" s="30"/>
     </row>
     <row r="41" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB41" s="25"/>
-      <c r="AC41" s="25"/>
-      <c r="AD41" s="25"/>
-      <c r="AE41" s="25"/>
-      <c r="AF41" s="25"/>
-      <c r="AG41" s="25"/>
-      <c r="AH41" s="25"/>
-      <c r="AI41" s="25"/>
-      <c r="AJ41" s="25"/>
-      <c r="AK41" s="25"/>
-      <c r="AL41" s="25"/>
-      <c r="AM41" s="25"/>
-      <c r="AN41" s="25"/>
-      <c r="AO41" s="25"/>
-      <c r="AP41" s="25"/>
-      <c r="AQ41" s="25"/>
+      <c r="AB41" s="30"/>
+      <c r="AC41" s="30"/>
+      <c r="AD41" s="30"/>
+      <c r="AE41" s="30"/>
+      <c r="AF41" s="30"/>
+      <c r="AG41" s="30"/>
+      <c r="AH41" s="30"/>
+      <c r="AI41" s="30"/>
+      <c r="AJ41" s="30"/>
+      <c r="AK41" s="30"/>
+      <c r="AL41" s="30"/>
+      <c r="AM41" s="30"/>
+      <c r="AN41" s="30"/>
+      <c r="AO41" s="30"/>
+      <c r="AP41" s="30"/>
+      <c r="AQ41" s="30"/>
     </row>
     <row r="42" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB42" s="25" t="e" vm="8">
+      <c r="AB42" s="30" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-      <c r="AC42" s="25"/>
-      <c r="AD42" s="25"/>
-      <c r="AE42" s="25"/>
-      <c r="AF42" s="25"/>
-      <c r="AG42" s="25"/>
-      <c r="AH42" s="25"/>
-      <c r="AI42" s="25"/>
-      <c r="AJ42" s="25"/>
-      <c r="AK42" s="25"/>
-      <c r="AL42" s="25"/>
-      <c r="AM42" s="25"/>
-      <c r="AN42" s="25"/>
-      <c r="AO42" s="25"/>
-      <c r="AP42" s="25"/>
-      <c r="AQ42" s="25"/>
+      <c r="AC42" s="30"/>
+      <c r="AD42" s="30"/>
+      <c r="AE42" s="30"/>
+      <c r="AF42" s="30"/>
+      <c r="AG42" s="30"/>
+      <c r="AH42" s="30"/>
+      <c r="AI42" s="30"/>
+      <c r="AJ42" s="30"/>
+      <c r="AK42" s="30"/>
+      <c r="AL42" s="30"/>
+      <c r="AM42" s="30"/>
+      <c r="AN42" s="30"/>
+      <c r="AO42" s="30"/>
+      <c r="AP42" s="30"/>
+      <c r="AQ42" s="30"/>
     </row>
     <row r="43" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB43" s="25"/>
-      <c r="AC43" s="25"/>
-      <c r="AD43" s="25"/>
-      <c r="AE43" s="25"/>
-      <c r="AF43" s="25"/>
-      <c r="AG43" s="25"/>
-      <c r="AH43" s="25"/>
-      <c r="AI43" s="25"/>
-      <c r="AJ43" s="25"/>
-      <c r="AK43" s="25"/>
-      <c r="AL43" s="25"/>
-      <c r="AM43" s="25"/>
-      <c r="AN43" s="25"/>
-      <c r="AO43" s="25"/>
-      <c r="AP43" s="25"/>
-      <c r="AQ43" s="25"/>
+      <c r="AB43" s="30"/>
+      <c r="AC43" s="30"/>
+      <c r="AD43" s="30"/>
+      <c r="AE43" s="30"/>
+      <c r="AF43" s="30"/>
+      <c r="AG43" s="30"/>
+      <c r="AH43" s="30"/>
+      <c r="AI43" s="30"/>
+      <c r="AJ43" s="30"/>
+      <c r="AK43" s="30"/>
+      <c r="AL43" s="30"/>
+      <c r="AM43" s="30"/>
+      <c r="AN43" s="30"/>
+      <c r="AO43" s="30"/>
+      <c r="AP43" s="30"/>
+      <c r="AQ43" s="30"/>
     </row>
     <row r="44" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB44" s="25"/>
-      <c r="AC44" s="25"/>
-      <c r="AD44" s="25"/>
-      <c r="AE44" s="25"/>
-      <c r="AF44" s="25"/>
-      <c r="AG44" s="25"/>
-      <c r="AH44" s="25"/>
-      <c r="AI44" s="25"/>
-      <c r="AJ44" s="25"/>
-      <c r="AK44" s="25"/>
-      <c r="AL44" s="25"/>
-      <c r="AM44" s="25"/>
-      <c r="AN44" s="25"/>
-      <c r="AO44" s="25"/>
-      <c r="AP44" s="25"/>
-      <c r="AQ44" s="25"/>
+      <c r="AB44" s="30"/>
+      <c r="AC44" s="30"/>
+      <c r="AD44" s="30"/>
+      <c r="AE44" s="30"/>
+      <c r="AF44" s="30"/>
+      <c r="AG44" s="30"/>
+      <c r="AH44" s="30"/>
+      <c r="AI44" s="30"/>
+      <c r="AJ44" s="30"/>
+      <c r="AK44" s="30"/>
+      <c r="AL44" s="30"/>
+      <c r="AM44" s="30"/>
+      <c r="AN44" s="30"/>
+      <c r="AO44" s="30"/>
+      <c r="AP44" s="30"/>
+      <c r="AQ44" s="30"/>
     </row>
     <row r="45" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB45" s="25"/>
-      <c r="AC45" s="25"/>
-      <c r="AD45" s="25"/>
-      <c r="AE45" s="25"/>
-      <c r="AF45" s="25"/>
-      <c r="AG45" s="25"/>
-      <c r="AH45" s="25"/>
-      <c r="AI45" s="25"/>
-      <c r="AJ45" s="25"/>
-      <c r="AK45" s="25"/>
-      <c r="AL45" s="25"/>
-      <c r="AM45" s="25"/>
-      <c r="AN45" s="25"/>
-      <c r="AO45" s="25"/>
-      <c r="AP45" s="25"/>
-      <c r="AQ45" s="25"/>
+      <c r="AB45" s="30"/>
+      <c r="AC45" s="30"/>
+      <c r="AD45" s="30"/>
+      <c r="AE45" s="30"/>
+      <c r="AF45" s="30"/>
+      <c r="AG45" s="30"/>
+      <c r="AH45" s="30"/>
+      <c r="AI45" s="30"/>
+      <c r="AJ45" s="30"/>
+      <c r="AK45" s="30"/>
+      <c r="AL45" s="30"/>
+      <c r="AM45" s="30"/>
+      <c r="AN45" s="30"/>
+      <c r="AO45" s="30"/>
+      <c r="AP45" s="30"/>
+      <c r="AQ45" s="30"/>
     </row>
     <row r="46" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB46" s="25"/>
-      <c r="AC46" s="25"/>
-      <c r="AD46" s="25"/>
-      <c r="AE46" s="25"/>
-      <c r="AF46" s="25"/>
-      <c r="AG46" s="25"/>
-      <c r="AH46" s="25"/>
-      <c r="AI46" s="25"/>
-      <c r="AJ46" s="25"/>
-      <c r="AK46" s="25"/>
-      <c r="AL46" s="25"/>
-      <c r="AM46" s="25"/>
-      <c r="AN46" s="25"/>
-      <c r="AO46" s="25"/>
-      <c r="AP46" s="25"/>
-      <c r="AQ46" s="25"/>
+      <c r="AB46" s="30"/>
+      <c r="AC46" s="30"/>
+      <c r="AD46" s="30"/>
+      <c r="AE46" s="30"/>
+      <c r="AF46" s="30"/>
+      <c r="AG46" s="30"/>
+      <c r="AH46" s="30"/>
+      <c r="AI46" s="30"/>
+      <c r="AJ46" s="30"/>
+      <c r="AK46" s="30"/>
+      <c r="AL46" s="30"/>
+      <c r="AM46" s="30"/>
+      <c r="AN46" s="30"/>
+      <c r="AO46" s="30"/>
+      <c r="AP46" s="30"/>
+      <c r="AQ46" s="30"/>
     </row>
     <row r="47" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB47" s="25"/>
-      <c r="AC47" s="25"/>
-      <c r="AD47" s="25"/>
-      <c r="AE47" s="25"/>
-      <c r="AF47" s="25"/>
-      <c r="AG47" s="25"/>
-      <c r="AH47" s="25"/>
-      <c r="AI47" s="25"/>
-      <c r="AJ47" s="25"/>
-      <c r="AK47" s="25"/>
-      <c r="AL47" s="25"/>
-      <c r="AM47" s="25"/>
-      <c r="AN47" s="25"/>
-      <c r="AO47" s="25"/>
-      <c r="AP47" s="25"/>
-      <c r="AQ47" s="25"/>
+      <c r="AB47" s="30"/>
+      <c r="AC47" s="30"/>
+      <c r="AD47" s="30"/>
+      <c r="AE47" s="30"/>
+      <c r="AF47" s="30"/>
+      <c r="AG47" s="30"/>
+      <c r="AH47" s="30"/>
+      <c r="AI47" s="30"/>
+      <c r="AJ47" s="30"/>
+      <c r="AK47" s="30"/>
+      <c r="AL47" s="30"/>
+      <c r="AM47" s="30"/>
+      <c r="AN47" s="30"/>
+      <c r="AO47" s="30"/>
+      <c r="AP47" s="30"/>
+      <c r="AQ47" s="30"/>
     </row>
     <row r="48" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB48" s="25"/>
-      <c r="AC48" s="25"/>
-      <c r="AD48" s="25"/>
-      <c r="AE48" s="25"/>
-      <c r="AF48" s="25"/>
-      <c r="AG48" s="25"/>
-      <c r="AH48" s="25"/>
-      <c r="AI48" s="25"/>
-      <c r="AJ48" s="25"/>
-      <c r="AK48" s="25"/>
-      <c r="AL48" s="25"/>
-      <c r="AM48" s="25"/>
-      <c r="AN48" s="25"/>
-      <c r="AO48" s="25"/>
-      <c r="AP48" s="25"/>
-      <c r="AQ48" s="25"/>
+      <c r="AB48" s="30"/>
+      <c r="AC48" s="30"/>
+      <c r="AD48" s="30"/>
+      <c r="AE48" s="30"/>
+      <c r="AF48" s="30"/>
+      <c r="AG48" s="30"/>
+      <c r="AH48" s="30"/>
+      <c r="AI48" s="30"/>
+      <c r="AJ48" s="30"/>
+      <c r="AK48" s="30"/>
+      <c r="AL48" s="30"/>
+      <c r="AM48" s="30"/>
+      <c r="AN48" s="30"/>
+      <c r="AO48" s="30"/>
+      <c r="AP48" s="30"/>
+      <c r="AQ48" s="30"/>
     </row>
     <row r="49" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB49" s="25"/>
-      <c r="AC49" s="25"/>
-      <c r="AD49" s="25"/>
-      <c r="AE49" s="25"/>
-      <c r="AF49" s="25"/>
-      <c r="AG49" s="25"/>
-      <c r="AH49" s="25"/>
-      <c r="AI49" s="25"/>
-      <c r="AJ49" s="25"/>
-      <c r="AK49" s="25"/>
-      <c r="AL49" s="25"/>
-      <c r="AM49" s="25"/>
-      <c r="AN49" s="25"/>
-      <c r="AO49" s="25"/>
-      <c r="AP49" s="25"/>
-      <c r="AQ49" s="25"/>
+      <c r="AB49" s="30"/>
+      <c r="AC49" s="30"/>
+      <c r="AD49" s="30"/>
+      <c r="AE49" s="30"/>
+      <c r="AF49" s="30"/>
+      <c r="AG49" s="30"/>
+      <c r="AH49" s="30"/>
+      <c r="AI49" s="30"/>
+      <c r="AJ49" s="30"/>
+      <c r="AK49" s="30"/>
+      <c r="AL49" s="30"/>
+      <c r="AM49" s="30"/>
+      <c r="AN49" s="30"/>
+      <c r="AO49" s="30"/>
+      <c r="AP49" s="30"/>
+      <c r="AQ49" s="30"/>
     </row>
     <row r="50" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB50" s="25"/>
-      <c r="AC50" s="25"/>
-      <c r="AD50" s="25"/>
-      <c r="AE50" s="25"/>
-      <c r="AF50" s="25"/>
-      <c r="AG50" s="25"/>
-      <c r="AH50" s="25"/>
-      <c r="AI50" s="25"/>
-      <c r="AJ50" s="25"/>
-      <c r="AK50" s="25"/>
-      <c r="AL50" s="25"/>
-      <c r="AM50" s="25"/>
-      <c r="AN50" s="25"/>
-      <c r="AO50" s="25"/>
-      <c r="AP50" s="25"/>
-      <c r="AQ50" s="25"/>
+      <c r="AB50" s="30"/>
+      <c r="AC50" s="30"/>
+      <c r="AD50" s="30"/>
+      <c r="AE50" s="30"/>
+      <c r="AF50" s="30"/>
+      <c r="AG50" s="30"/>
+      <c r="AH50" s="30"/>
+      <c r="AI50" s="30"/>
+      <c r="AJ50" s="30"/>
+      <c r="AK50" s="30"/>
+      <c r="AL50" s="30"/>
+      <c r="AM50" s="30"/>
+      <c r="AN50" s="30"/>
+      <c r="AO50" s="30"/>
+      <c r="AP50" s="30"/>
+      <c r="AQ50" s="30"/>
     </row>
     <row r="51" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB51" s="25"/>
-      <c r="AC51" s="25"/>
-      <c r="AD51" s="25"/>
-      <c r="AE51" s="25"/>
-      <c r="AF51" s="25"/>
-      <c r="AG51" s="25"/>
-      <c r="AH51" s="25"/>
-      <c r="AI51" s="25"/>
-      <c r="AJ51" s="25"/>
-      <c r="AK51" s="25"/>
-      <c r="AL51" s="25"/>
-      <c r="AM51" s="25"/>
-      <c r="AN51" s="25"/>
-      <c r="AO51" s="25"/>
-      <c r="AP51" s="25"/>
-      <c r="AQ51" s="25"/>
+      <c r="AB51" s="30"/>
+      <c r="AC51" s="30"/>
+      <c r="AD51" s="30"/>
+      <c r="AE51" s="30"/>
+      <c r="AF51" s="30"/>
+      <c r="AG51" s="30"/>
+      <c r="AH51" s="30"/>
+      <c r="AI51" s="30"/>
+      <c r="AJ51" s="30"/>
+      <c r="AK51" s="30"/>
+      <c r="AL51" s="30"/>
+      <c r="AM51" s="30"/>
+      <c r="AN51" s="30"/>
+      <c r="AO51" s="30"/>
+      <c r="AP51" s="30"/>
+      <c r="AQ51" s="30"/>
     </row>
     <row r="52" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB52" s="25"/>
-      <c r="AC52" s="25"/>
-      <c r="AD52" s="25"/>
-      <c r="AE52" s="25"/>
-      <c r="AF52" s="25"/>
-      <c r="AG52" s="25"/>
-      <c r="AH52" s="25"/>
-      <c r="AI52" s="25"/>
-      <c r="AJ52" s="25"/>
-      <c r="AK52" s="25"/>
-      <c r="AL52" s="25"/>
-      <c r="AM52" s="25"/>
-      <c r="AN52" s="25"/>
-      <c r="AO52" s="25"/>
-      <c r="AP52" s="25"/>
-      <c r="AQ52" s="25"/>
+      <c r="AB52" s="30"/>
+      <c r="AC52" s="30"/>
+      <c r="AD52" s="30"/>
+      <c r="AE52" s="30"/>
+      <c r="AF52" s="30"/>
+      <c r="AG52" s="30"/>
+      <c r="AH52" s="30"/>
+      <c r="AI52" s="30"/>
+      <c r="AJ52" s="30"/>
+      <c r="AK52" s="30"/>
+      <c r="AL52" s="30"/>
+      <c r="AM52" s="30"/>
+      <c r="AN52" s="30"/>
+      <c r="AO52" s="30"/>
+      <c r="AP52" s="30"/>
+      <c r="AQ52" s="30"/>
     </row>
     <row r="53" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB53" s="25"/>
-      <c r="AC53" s="25"/>
-      <c r="AD53" s="25"/>
-      <c r="AE53" s="25"/>
-      <c r="AF53" s="25"/>
-      <c r="AG53" s="25"/>
-      <c r="AH53" s="25"/>
-      <c r="AI53" s="25"/>
-      <c r="AJ53" s="25"/>
-      <c r="AK53" s="25"/>
-      <c r="AL53" s="25"/>
-      <c r="AM53" s="25"/>
-      <c r="AN53" s="25"/>
-      <c r="AO53" s="25"/>
-      <c r="AP53" s="25"/>
-      <c r="AQ53" s="25"/>
+      <c r="AB53" s="30"/>
+      <c r="AC53" s="30"/>
+      <c r="AD53" s="30"/>
+      <c r="AE53" s="30"/>
+      <c r="AF53" s="30"/>
+      <c r="AG53" s="30"/>
+      <c r="AH53" s="30"/>
+      <c r="AI53" s="30"/>
+      <c r="AJ53" s="30"/>
+      <c r="AK53" s="30"/>
+      <c r="AL53" s="30"/>
+      <c r="AM53" s="30"/>
+      <c r="AN53" s="30"/>
+      <c r="AO53" s="30"/>
+      <c r="AP53" s="30"/>
+      <c r="AQ53" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="42">
+    <mergeCell ref="Q22:AA24"/>
+    <mergeCell ref="AB22:AQ31"/>
     <mergeCell ref="AB42:AQ53"/>
     <mergeCell ref="T4:X4"/>
     <mergeCell ref="AB32:AQ41"/>
@@ -5657,7 +5678,6 @@
     <mergeCell ref="I35:O35"/>
     <mergeCell ref="C36:H36"/>
     <mergeCell ref="I36:O36"/>
-    <mergeCell ref="AB28:AQ31"/>
     <mergeCell ref="C29:H29"/>
     <mergeCell ref="I29:O29"/>
     <mergeCell ref="C30:H30"/>
@@ -5667,14 +5687,6 @@
     <mergeCell ref="I31:O31"/>
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="I32:O32"/>
-    <mergeCell ref="I26:O26"/>
-    <mergeCell ref="Q26:AA29"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="I27:O27"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="I28:O28"/>
-    <mergeCell ref="Q22:AA25"/>
-    <mergeCell ref="AB22:AQ27"/>
     <mergeCell ref="AR22:AY24"/>
     <mergeCell ref="C23:H23"/>
     <mergeCell ref="I23:O23"/>
@@ -5683,6 +5695,12 @@
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="I25:O25"/>
     <mergeCell ref="C26:H26"/>
+    <mergeCell ref="I26:O26"/>
+    <mergeCell ref="Q26:AA29"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="I27:O27"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="I28:O28"/>
     <mergeCell ref="C3:H3"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="C21:H21"/>

--- a/IndicatorsForClusters.xlsx
+++ b/IndicatorsForClusters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1c3256d208fb6548/Personlig/Aske Banke Consultancy/YALE/Metodeartikel_WorldDevelopmentJournal/WorldDevelopmentArticleGit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="387" documentId="8_{9856C943-DD01-465B-AD17-0E409E296684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8AAB6F5-8537-4C3C-BE36-255FD9E56484}"/>
+  <xr:revisionPtr revIDLastSave="461" documentId="8_{9856C943-DD01-465B-AD17-0E409E296684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC628B2D-6AED-4B73-AE36-E8ED2E2600B0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{726B2859-724A-4801-8E74-5A4E1AFAB973}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{726B2859-724A-4801-8E74-5A4E1AFAB973}"/>
   </bookViews>
   <sheets>
     <sheet name="Unscaled Experiments" sheetId="2" r:id="rId1"/>
@@ -169,7 +169,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="79">
   <si>
     <t>SPI</t>
   </si>
@@ -403,12 +403,20 @@
   <si>
     <t xml:space="preserve">Excluded due to exteme variation in the clustering </t>
   </si>
+  <si>
+    <t>Sheet "Unscaled experiments/Scaled experiments" holds an overview of the different experiemnts. The table to the left should not be touched, but comments to experiments can be written in the blue table below.
+Sheet "Experiments" is where the exact indicators going into the experiments can be found. New experiments can be created by adding a new column with 0s and 1s denoting which indicators should be included. 
+Sheet "Overview of indicators and DLS" shows my evaluation of our indicators' relation to DLS.</t>
+  </si>
+  <si>
+    <t>No_non_DLS_BHNFWB</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,6 +442,12 @@
     <font>
       <sz val="11"/>
       <color theme="2" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -606,6 +620,9 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -633,6 +650,12 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -642,20 +665,17 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -663,10 +683,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1308,35 +1324,35 @@
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AY53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.33203125" customWidth="1"/>
+    <col min="2" max="2" width="35.28515625" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
-    <col min="5" max="16" width="4.33203125" customWidth="1"/>
-    <col min="19" max="19" width="8.88671875" customWidth="1"/>
+    <col min="5" max="16" width="4.28515625" customWidth="1"/>
+    <col min="19" max="19" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="38" t="s">
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="39"/>
+      <c r="J3" s="42"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
@@ -1350,7 +1366,7 @@
       <c r="W3" s="22"/>
       <c r="X3" s="22"/>
     </row>
-    <row r="4" spans="1:24" ht="221.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" ht="221.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="15" t="s">
         <v>16</v>
       </c>
@@ -1400,15 +1416,15 @@
       <c r="Q4" s="9" t="str">
         <v>BHN</v>
       </c>
-      <c r="T4" s="29" t="s">
+      <c r="T4" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="U4" s="29"/>
-      <c r="V4" s="29"/>
-      <c r="W4" s="29"/>
-      <c r="X4" s="29"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="U4" s="30"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30"/>
+      <c r="X4" s="30"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="str" cm="1">
         <f t="array" ref="B5:B15">_xlfn.UNIQUE('Overview of indicators and DLS'!C4:C67)</f>
         <v>Food &amp; Nutrition</v>
@@ -1477,7 +1493,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="str">
         <v>Health Care</v>
       </c>
@@ -1542,7 +1558,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="str">
         <v>Water</v>
       </c>
@@ -1607,7 +1623,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="str">
         <v>Sanitation</v>
       </c>
@@ -1672,7 +1688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="str">
         <v>Food preparation</v>
       </c>
@@ -1737,7 +1753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="str">
         <v>Thermal comfort</v>
       </c>
@@ -1802,7 +1818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="str">
         <v>Non material / Non-DLS</v>
       </c>
@@ -1867,7 +1883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="str">
         <v>Education</v>
       </c>
@@ -1932,7 +1948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="str">
         <v>Social connectedness</v>
       </c>
@@ -1997,7 +2013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="str">
         <v>Housing</v>
       </c>
@@ -2062,7 +2078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B15" s="13" t="str">
         <v>Physical Connectedness</v>
       </c>
@@ -2130,7 +2146,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B16" s="11"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
@@ -2148,7 +2164,7 @@
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>33</v>
       </c>
@@ -2213,7 +2229,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
         <v>34</v>
       </c>
@@ -2278,7 +2294,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B19" s="11" t="s">
         <v>35</v>
       </c>
@@ -2343,30 +2359,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>56</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40" t="s">
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="J21" s="40"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="40"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="43"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="43"/>
       <c r="Q21" s="1" t="s">
         <v>59</v>
       </c>
@@ -2374,7 +2390,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:51" ht="90.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:51" ht="90.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1</v>
       </c>
@@ -2382,1083 +2398,1083 @@
         <f t="array" ref="B22:B36">TRANSPOSE(_xlfn.ANCHORARRAY(C4))</f>
         <v>BHN_FWB</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="37"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="Q22" s="30" t="e" vm="1">
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="38"/>
+      <c r="L22" s="38"/>
+      <c r="M22" s="38"/>
+      <c r="N22" s="38"/>
+      <c r="O22" s="38"/>
+      <c r="Q22" s="31" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="R22" s="30"/>
-      <c r="S22" s="30"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="30"/>
-      <c r="V22" s="30"/>
-      <c r="W22" s="30"/>
-      <c r="X22" s="30"/>
-      <c r="Y22" s="30"/>
-      <c r="Z22" s="30"/>
-      <c r="AA22" s="30"/>
-      <c r="AB22" s="30" t="e" vm="2">
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="31"/>
+      <c r="V22" s="31"/>
+      <c r="W22" s="31"/>
+      <c r="X22" s="31"/>
+      <c r="Y22" s="31"/>
+      <c r="Z22" s="31"/>
+      <c r="AA22" s="31"/>
+      <c r="AB22" s="31" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="AC22" s="30"/>
-      <c r="AD22" s="30"/>
-      <c r="AE22" s="30"/>
-      <c r="AF22" s="30"/>
-      <c r="AG22" s="30"/>
-      <c r="AH22" s="30"/>
-      <c r="AI22" s="30"/>
-      <c r="AJ22" s="30"/>
-      <c r="AK22" s="30"/>
-      <c r="AL22" s="30"/>
-      <c r="AM22" s="30"/>
-      <c r="AN22" s="30"/>
-      <c r="AO22" s="30"/>
-      <c r="AP22" s="30"/>
-      <c r="AQ22" s="30"/>
-      <c r="AR22" s="30" t="e" vm="3">
+      <c r="AC22" s="31"/>
+      <c r="AD22" s="31"/>
+      <c r="AE22" s="31"/>
+      <c r="AF22" s="31"/>
+      <c r="AG22" s="31"/>
+      <c r="AH22" s="31"/>
+      <c r="AI22" s="31"/>
+      <c r="AJ22" s="31"/>
+      <c r="AK22" s="31"/>
+      <c r="AL22" s="31"/>
+      <c r="AM22" s="31"/>
+      <c r="AN22" s="31"/>
+      <c r="AO22" s="31"/>
+      <c r="AP22" s="31"/>
+      <c r="AQ22" s="31"/>
+      <c r="AR22" s="31" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="AS22" s="30"/>
-      <c r="AT22" s="30"/>
-      <c r="AU22" s="30"/>
-      <c r="AV22" s="30"/>
-      <c r="AW22" s="30"/>
-      <c r="AX22" s="30"/>
-      <c r="AY22" s="30"/>
-    </row>
-    <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AS22" s="31"/>
+      <c r="AT22" s="31"/>
+      <c r="AU22" s="31"/>
+      <c r="AV22" s="31"/>
+      <c r="AW22" s="31"/>
+      <c r="AX22" s="31"/>
+      <c r="AY22" s="31"/>
+    </row>
+    <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23" s="7" t="str">
         <v>BHN_FWB_AllExt</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="C23" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="37"/>
-      <c r="N23" s="37"/>
-      <c r="O23" s="37"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
-      <c r="X23" s="30"/>
-      <c r="Y23" s="30"/>
-      <c r="Z23" s="30"/>
-      <c r="AA23" s="30"/>
-      <c r="AB23" s="30"/>
-      <c r="AC23" s="30"/>
-      <c r="AD23" s="30"/>
-      <c r="AE23" s="30"/>
-      <c r="AF23" s="30"/>
-      <c r="AG23" s="30"/>
-      <c r="AH23" s="30"/>
-      <c r="AI23" s="30"/>
-      <c r="AJ23" s="30"/>
-      <c r="AK23" s="30"/>
-      <c r="AL23" s="30"/>
-      <c r="AM23" s="30"/>
-      <c r="AN23" s="30"/>
-      <c r="AO23" s="30"/>
-      <c r="AP23" s="30"/>
-      <c r="AQ23" s="30"/>
-      <c r="AR23" s="30"/>
-      <c r="AS23" s="30"/>
-      <c r="AT23" s="30"/>
-      <c r="AU23" s="30"/>
-      <c r="AV23" s="30"/>
-      <c r="AW23" s="30"/>
-      <c r="AX23" s="30"/>
-      <c r="AY23" s="30"/>
-    </row>
-    <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="38"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="31"/>
+      <c r="V23" s="31"/>
+      <c r="W23" s="31"/>
+      <c r="X23" s="31"/>
+      <c r="Y23" s="31"/>
+      <c r="Z23" s="31"/>
+      <c r="AA23" s="31"/>
+      <c r="AB23" s="31"/>
+      <c r="AC23" s="31"/>
+      <c r="AD23" s="31"/>
+      <c r="AE23" s="31"/>
+      <c r="AF23" s="31"/>
+      <c r="AG23" s="31"/>
+      <c r="AH23" s="31"/>
+      <c r="AI23" s="31"/>
+      <c r="AJ23" s="31"/>
+      <c r="AK23" s="31"/>
+      <c r="AL23" s="31"/>
+      <c r="AM23" s="31"/>
+      <c r="AN23" s="31"/>
+      <c r="AO23" s="31"/>
+      <c r="AP23" s="31"/>
+      <c r="AQ23" s="31"/>
+      <c r="AR23" s="31"/>
+      <c r="AS23" s="31"/>
+      <c r="AT23" s="31"/>
+      <c r="AU23" s="31"/>
+      <c r="AV23" s="31"/>
+      <c r="AW23" s="31"/>
+      <c r="AX23" s="31"/>
+      <c r="AY23" s="31"/>
+    </row>
+    <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24" s="7" t="str">
         <v>Few_indicators_closest_DLS_coverage</v>
       </c>
-      <c r="C24" s="41" t="s">
+      <c r="C24" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="37"/>
-      <c r="K24" s="37"/>
-      <c r="L24" s="37"/>
-      <c r="M24" s="37"/>
-      <c r="N24" s="37"/>
-      <c r="O24" s="37"/>
-      <c r="Q24" s="30"/>
-      <c r="R24" s="30"/>
-      <c r="S24" s="30"/>
-      <c r="T24" s="30"/>
-      <c r="U24" s="30"/>
-      <c r="V24" s="30"/>
-      <c r="W24" s="30"/>
-      <c r="X24" s="30"/>
-      <c r="Y24" s="30"/>
-      <c r="Z24" s="30"/>
-      <c r="AA24" s="30"/>
-      <c r="AB24" s="30"/>
-      <c r="AC24" s="30"/>
-      <c r="AD24" s="30"/>
-      <c r="AE24" s="30"/>
-      <c r="AF24" s="30"/>
-      <c r="AG24" s="30"/>
-      <c r="AH24" s="30"/>
-      <c r="AI24" s="30"/>
-      <c r="AJ24" s="30"/>
-      <c r="AK24" s="30"/>
-      <c r="AL24" s="30"/>
-      <c r="AM24" s="30"/>
-      <c r="AN24" s="30"/>
-      <c r="AO24" s="30"/>
-      <c r="AP24" s="30"/>
-      <c r="AQ24" s="30"/>
-      <c r="AR24" s="30"/>
-      <c r="AS24" s="30"/>
-      <c r="AT24" s="30"/>
-      <c r="AU24" s="30"/>
-      <c r="AV24" s="30"/>
-      <c r="AW24" s="30"/>
-      <c r="AX24" s="30"/>
-      <c r="AY24" s="30"/>
-    </row>
-    <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="38"/>
+      <c r="Q24" s="31"/>
+      <c r="R24" s="31"/>
+      <c r="S24" s="31"/>
+      <c r="T24" s="31"/>
+      <c r="U24" s="31"/>
+      <c r="V24" s="31"/>
+      <c r="W24" s="31"/>
+      <c r="X24" s="31"/>
+      <c r="Y24" s="31"/>
+      <c r="Z24" s="31"/>
+      <c r="AA24" s="31"/>
+      <c r="AB24" s="31"/>
+      <c r="AC24" s="31"/>
+      <c r="AD24" s="31"/>
+      <c r="AE24" s="31"/>
+      <c r="AF24" s="31"/>
+      <c r="AG24" s="31"/>
+      <c r="AH24" s="31"/>
+      <c r="AI24" s="31"/>
+      <c r="AJ24" s="31"/>
+      <c r="AK24" s="31"/>
+      <c r="AL24" s="31"/>
+      <c r="AM24" s="31"/>
+      <c r="AN24" s="31"/>
+      <c r="AO24" s="31"/>
+      <c r="AP24" s="31"/>
+      <c r="AQ24" s="31"/>
+      <c r="AR24" s="31"/>
+      <c r="AS24" s="31"/>
+      <c r="AT24" s="31"/>
+      <c r="AU24" s="31"/>
+      <c r="AV24" s="31"/>
+      <c r="AW24" s="31"/>
+      <c r="AX24" s="31"/>
+      <c r="AY24" s="31"/>
+    </row>
+    <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25" s="7" t="str">
         <v>Few indicators_SPI_preferred</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="C25" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="37"/>
-      <c r="L25" s="37"/>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="Q25" s="30"/>
-      <c r="R25" s="30"/>
-      <c r="S25" s="30"/>
-      <c r="T25" s="30"/>
-      <c r="U25" s="30"/>
-      <c r="V25" s="30"/>
-      <c r="W25" s="30"/>
-      <c r="X25" s="30"/>
-      <c r="Y25" s="30"/>
-      <c r="Z25" s="30"/>
-      <c r="AA25" s="30"/>
-      <c r="AB25" s="30"/>
-      <c r="AC25" s="30"/>
-      <c r="AD25" s="30"/>
-      <c r="AE25" s="30"/>
-      <c r="AF25" s="30"/>
-      <c r="AG25" s="30"/>
-      <c r="AH25" s="30"/>
-      <c r="AI25" s="30"/>
-      <c r="AJ25" s="30"/>
-      <c r="AK25" s="30"/>
-      <c r="AL25" s="30"/>
-      <c r="AM25" s="30"/>
-      <c r="AN25" s="30"/>
-      <c r="AO25" s="30"/>
-      <c r="AP25" s="30"/>
-      <c r="AQ25" s="30"/>
-    </row>
-    <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="38"/>
+      <c r="M25" s="38"/>
+      <c r="N25" s="38"/>
+      <c r="O25" s="38"/>
+      <c r="Q25" s="31"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="31"/>
+      <c r="T25" s="31"/>
+      <c r="U25" s="31"/>
+      <c r="V25" s="31"/>
+      <c r="W25" s="31"/>
+      <c r="X25" s="31"/>
+      <c r="Y25" s="31"/>
+      <c r="Z25" s="31"/>
+      <c r="AA25" s="31"/>
+      <c r="AB25" s="31"/>
+      <c r="AC25" s="31"/>
+      <c r="AD25" s="31"/>
+      <c r="AE25" s="31"/>
+      <c r="AF25" s="31"/>
+      <c r="AG25" s="31"/>
+      <c r="AH25" s="31"/>
+      <c r="AI25" s="31"/>
+      <c r="AJ25" s="31"/>
+      <c r="AK25" s="31"/>
+      <c r="AL25" s="31"/>
+      <c r="AM25" s="31"/>
+      <c r="AN25" s="31"/>
+      <c r="AO25" s="31"/>
+      <c r="AP25" s="31"/>
+      <c r="AQ25" s="31"/>
+    </row>
+    <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26" s="7" t="str">
         <v>No_non_DLS</v>
       </c>
-      <c r="C26" s="43" t="s">
+      <c r="C26" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="37"/>
-      <c r="L26" s="37"/>
-      <c r="M26" s="37"/>
-      <c r="N26" s="37"/>
-      <c r="O26" s="37"/>
-      <c r="Q26" s="30" t="e" vm="4">
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="38"/>
+      <c r="Q26" s="31" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="R26" s="30"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="30"/>
-      <c r="X26" s="30"/>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="30"/>
-      <c r="AA26" s="30"/>
-      <c r="AB26" s="30"/>
-      <c r="AC26" s="30"/>
-      <c r="AD26" s="30"/>
-      <c r="AE26" s="30"/>
-      <c r="AF26" s="30"/>
-      <c r="AG26" s="30"/>
-      <c r="AH26" s="30"/>
-      <c r="AI26" s="30"/>
-      <c r="AJ26" s="30"/>
-      <c r="AK26" s="30"/>
-      <c r="AL26" s="30"/>
-      <c r="AM26" s="30"/>
-      <c r="AN26" s="30"/>
-      <c r="AO26" s="30"/>
-      <c r="AP26" s="30"/>
-      <c r="AQ26" s="30"/>
-    </row>
-    <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="31"/>
+      <c r="Y26" s="31"/>
+      <c r="Z26" s="31"/>
+      <c r="AA26" s="31"/>
+      <c r="AB26" s="31"/>
+      <c r="AC26" s="31"/>
+      <c r="AD26" s="31"/>
+      <c r="AE26" s="31"/>
+      <c r="AF26" s="31"/>
+      <c r="AG26" s="31"/>
+      <c r="AH26" s="31"/>
+      <c r="AI26" s="31"/>
+      <c r="AJ26" s="31"/>
+      <c r="AK26" s="31"/>
+      <c r="AL26" s="31"/>
+      <c r="AM26" s="31"/>
+      <c r="AN26" s="31"/>
+      <c r="AO26" s="31"/>
+      <c r="AP26" s="31"/>
+      <c r="AQ26" s="31"/>
+    </row>
+    <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27" s="7" t="str">
         <v>Only_%_of_pop</v>
       </c>
-      <c r="C27" s="43" t="s">
+      <c r="C27" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="37"/>
-      <c r="L27" s="37"/>
-      <c r="M27" s="37"/>
-      <c r="N27" s="37"/>
-      <c r="O27" s="37"/>
-      <c r="Q27" s="30"/>
-      <c r="R27" s="30"/>
-      <c r="S27" s="30"/>
-      <c r="T27" s="30"/>
-      <c r="U27" s="30"/>
-      <c r="V27" s="30"/>
-      <c r="W27" s="30"/>
-      <c r="X27" s="30"/>
-      <c r="Y27" s="30"/>
-      <c r="Z27" s="30"/>
-      <c r="AA27" s="30"/>
-      <c r="AB27" s="30"/>
-      <c r="AC27" s="30"/>
-      <c r="AD27" s="30"/>
-      <c r="AE27" s="30"/>
-      <c r="AF27" s="30"/>
-      <c r="AG27" s="30"/>
-      <c r="AH27" s="30"/>
-      <c r="AI27" s="30"/>
-      <c r="AJ27" s="30"/>
-      <c r="AK27" s="30"/>
-      <c r="AL27" s="30"/>
-      <c r="AM27" s="30"/>
-      <c r="AN27" s="30"/>
-      <c r="AO27" s="30"/>
-      <c r="AP27" s="30"/>
-      <c r="AQ27" s="30"/>
-    </row>
-    <row r="28" spans="1:51" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="38"/>
+      <c r="M27" s="38"/>
+      <c r="N27" s="38"/>
+      <c r="O27" s="38"/>
+      <c r="Q27" s="31"/>
+      <c r="R27" s="31"/>
+      <c r="S27" s="31"/>
+      <c r="T27" s="31"/>
+      <c r="U27" s="31"/>
+      <c r="V27" s="31"/>
+      <c r="W27" s="31"/>
+      <c r="X27" s="31"/>
+      <c r="Y27" s="31"/>
+      <c r="Z27" s="31"/>
+      <c r="AA27" s="31"/>
+      <c r="AB27" s="31"/>
+      <c r="AC27" s="31"/>
+      <c r="AD27" s="31"/>
+      <c r="AE27" s="31"/>
+      <c r="AF27" s="31"/>
+      <c r="AG27" s="31"/>
+      <c r="AH27" s="31"/>
+      <c r="AI27" s="31"/>
+      <c r="AJ27" s="31"/>
+      <c r="AK27" s="31"/>
+      <c r="AL27" s="31"/>
+      <c r="AM27" s="31"/>
+      <c r="AN27" s="31"/>
+      <c r="AO27" s="31"/>
+      <c r="AP27" s="31"/>
+      <c r="AQ27" s="31"/>
+    </row>
+    <row r="28" spans="1:51" ht="65.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" s="17" t="str">
         <v>Few_indicators_closest_DLS_coverage_90</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="35"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="Q28" s="30"/>
-      <c r="R28" s="30"/>
-      <c r="S28" s="30"/>
-      <c r="T28" s="30"/>
-      <c r="U28" s="30"/>
-      <c r="V28" s="30"/>
-      <c r="W28" s="30"/>
-      <c r="X28" s="30"/>
-      <c r="Y28" s="30"/>
-      <c r="Z28" s="30"/>
-      <c r="AA28" s="30"/>
-      <c r="AB28" s="30" t="e" vm="5">
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="36"/>
+      <c r="L28" s="36"/>
+      <c r="M28" s="36"/>
+      <c r="N28" s="36"/>
+      <c r="O28" s="36"/>
+      <c r="Q28" s="31"/>
+      <c r="R28" s="31"/>
+      <c r="S28" s="31"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="31"/>
+      <c r="V28" s="31"/>
+      <c r="W28" s="31"/>
+      <c r="X28" s="31"/>
+      <c r="Y28" s="31"/>
+      <c r="Z28" s="31"/>
+      <c r="AA28" s="31"/>
+      <c r="AB28" s="31" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="AC28" s="30"/>
-      <c r="AD28" s="30"/>
-      <c r="AE28" s="30"/>
-      <c r="AF28" s="30"/>
-      <c r="AG28" s="30"/>
-      <c r="AH28" s="30"/>
-      <c r="AI28" s="30"/>
-      <c r="AJ28" s="30"/>
-      <c r="AK28" s="30"/>
-      <c r="AL28" s="30"/>
-      <c r="AM28" s="30"/>
-      <c r="AN28" s="30"/>
-      <c r="AO28" s="30"/>
-      <c r="AP28" s="30"/>
-      <c r="AQ28" s="30"/>
-    </row>
-    <row r="29" spans="1:51" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AC28" s="31"/>
+      <c r="AD28" s="31"/>
+      <c r="AE28" s="31"/>
+      <c r="AF28" s="31"/>
+      <c r="AG28" s="31"/>
+      <c r="AH28" s="31"/>
+      <c r="AI28" s="31"/>
+      <c r="AJ28" s="31"/>
+      <c r="AK28" s="31"/>
+      <c r="AL28" s="31"/>
+      <c r="AM28" s="31"/>
+      <c r="AN28" s="31"/>
+      <c r="AO28" s="31"/>
+      <c r="AP28" s="31"/>
+      <c r="AQ28" s="31"/>
+    </row>
+    <row r="29" spans="1:51" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2</v>
       </c>
       <c r="B29" s="17" t="str">
         <v>Few indicators_SPI_preferred_90</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="35"/>
-      <c r="K29" s="35"/>
-      <c r="L29" s="35"/>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="35"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
-      <c r="AC29" s="30"/>
-      <c r="AD29" s="30"/>
-      <c r="AE29" s="30"/>
-      <c r="AF29" s="30"/>
-      <c r="AG29" s="30"/>
-      <c r="AH29" s="30"/>
-      <c r="AI29" s="30"/>
-      <c r="AJ29" s="30"/>
-      <c r="AK29" s="30"/>
-      <c r="AL29" s="30"/>
-      <c r="AM29" s="30"/>
-      <c r="AN29" s="30"/>
-      <c r="AO29" s="30"/>
-      <c r="AP29" s="30"/>
-      <c r="AQ29" s="30"/>
-    </row>
-    <row r="30" spans="1:51" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="36"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="36"/>
+      <c r="L29" s="36"/>
+      <c r="M29" s="36"/>
+      <c r="N29" s="36"/>
+      <c r="O29" s="36"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="31"/>
+      <c r="V29" s="31"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="31"/>
+      <c r="Y29" s="31"/>
+      <c r="Z29" s="31"/>
+      <c r="AA29" s="31"/>
+      <c r="AB29" s="31"/>
+      <c r="AC29" s="31"/>
+      <c r="AD29" s="31"/>
+      <c r="AE29" s="31"/>
+      <c r="AF29" s="31"/>
+      <c r="AG29" s="31"/>
+      <c r="AH29" s="31"/>
+      <c r="AI29" s="31"/>
+      <c r="AJ29" s="31"/>
+      <c r="AK29" s="31"/>
+      <c r="AL29" s="31"/>
+      <c r="AM29" s="31"/>
+      <c r="AN29" s="31"/>
+      <c r="AO29" s="31"/>
+      <c r="AP29" s="31"/>
+      <c r="AQ29" s="31"/>
+    </row>
+    <row r="30" spans="1:51" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>3</v>
       </c>
       <c r="B30" s="17" t="str">
         <v>Few_indicators_closeDLS_subPrimSchool</v>
       </c>
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="35"/>
-      <c r="K30" s="35"/>
-      <c r="L30" s="35"/>
-      <c r="M30" s="35"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="35"/>
-      <c r="Q30" s="30" t="e" vm="6">
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="36"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="36"/>
+      <c r="O30" s="36"/>
+      <c r="Q30" s="31" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
-      <c r="R30" s="30"/>
-      <c r="S30" s="30"/>
-      <c r="T30" s="30"/>
-      <c r="U30" s="30"/>
-      <c r="V30" s="30"/>
-      <c r="W30" s="30"/>
-      <c r="X30" s="30"/>
-      <c r="Y30" s="30"/>
-      <c r="Z30" s="30"/>
-      <c r="AA30" s="30"/>
-      <c r="AB30" s="30"/>
-      <c r="AC30" s="30"/>
-      <c r="AD30" s="30"/>
-      <c r="AE30" s="30"/>
-      <c r="AF30" s="30"/>
-      <c r="AG30" s="30"/>
-      <c r="AH30" s="30"/>
-      <c r="AI30" s="30"/>
-      <c r="AJ30" s="30"/>
-      <c r="AK30" s="30"/>
-      <c r="AL30" s="30"/>
-      <c r="AM30" s="30"/>
-      <c r="AN30" s="30"/>
-      <c r="AO30" s="30"/>
-      <c r="AP30" s="30"/>
-      <c r="AQ30" s="30"/>
-    </row>
-    <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R30" s="31"/>
+      <c r="S30" s="31"/>
+      <c r="T30" s="31"/>
+      <c r="U30" s="31"/>
+      <c r="V30" s="31"/>
+      <c r="W30" s="31"/>
+      <c r="X30" s="31"/>
+      <c r="Y30" s="31"/>
+      <c r="Z30" s="31"/>
+      <c r="AA30" s="31"/>
+      <c r="AB30" s="31"/>
+      <c r="AC30" s="31"/>
+      <c r="AD30" s="31"/>
+      <c r="AE30" s="31"/>
+      <c r="AF30" s="31"/>
+      <c r="AG30" s="31"/>
+      <c r="AH30" s="31"/>
+      <c r="AI30" s="31"/>
+      <c r="AJ30" s="31"/>
+      <c r="AK30" s="31"/>
+      <c r="AL30" s="31"/>
+      <c r="AM30" s="31"/>
+      <c r="AN30" s="31"/>
+      <c r="AO30" s="31"/>
+      <c r="AP30" s="31"/>
+      <c r="AQ30" s="31"/>
+    </row>
+    <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>3</v>
       </c>
       <c r="B31" s="17" t="str">
         <v>No_non_DLS_90</v>
       </c>
-      <c r="C31" s="33" t="s">
+      <c r="C31" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="35"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="Q31" s="30"/>
-      <c r="R31" s="30"/>
-      <c r="S31" s="30"/>
-      <c r="T31" s="30"/>
-      <c r="U31" s="30"/>
-      <c r="V31" s="30"/>
-      <c r="W31" s="30"/>
-      <c r="X31" s="30"/>
-      <c r="Y31" s="30"/>
-      <c r="Z31" s="30"/>
-      <c r="AA31" s="30"/>
-      <c r="AB31" s="30"/>
-      <c r="AC31" s="30"/>
-      <c r="AD31" s="30"/>
-      <c r="AE31" s="30"/>
-      <c r="AF31" s="30"/>
-      <c r="AG31" s="30"/>
-      <c r="AH31" s="30"/>
-      <c r="AI31" s="30"/>
-      <c r="AJ31" s="30"/>
-      <c r="AK31" s="30"/>
-      <c r="AL31" s="30"/>
-      <c r="AM31" s="30"/>
-      <c r="AN31" s="30"/>
-      <c r="AO31" s="30"/>
-      <c r="AP31" s="30"/>
-      <c r="AQ31" s="30"/>
-    </row>
-    <row r="32" spans="1:51" ht="103.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="36"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="36"/>
+      <c r="M31" s="36"/>
+      <c r="N31" s="36"/>
+      <c r="O31" s="36"/>
+      <c r="Q31" s="31"/>
+      <c r="R31" s="31"/>
+      <c r="S31" s="31"/>
+      <c r="T31" s="31"/>
+      <c r="U31" s="31"/>
+      <c r="V31" s="31"/>
+      <c r="W31" s="31"/>
+      <c r="X31" s="31"/>
+      <c r="Y31" s="31"/>
+      <c r="Z31" s="31"/>
+      <c r="AA31" s="31"/>
+      <c r="AB31" s="31"/>
+      <c r="AC31" s="31"/>
+      <c r="AD31" s="31"/>
+      <c r="AE31" s="31"/>
+      <c r="AF31" s="31"/>
+      <c r="AG31" s="31"/>
+      <c r="AH31" s="31"/>
+      <c r="AI31" s="31"/>
+      <c r="AJ31" s="31"/>
+      <c r="AK31" s="31"/>
+      <c r="AL31" s="31"/>
+      <c r="AM31" s="31"/>
+      <c r="AN31" s="31"/>
+      <c r="AO31" s="31"/>
+      <c r="AP31" s="31"/>
+      <c r="AQ31" s="31"/>
+    </row>
+    <row r="32" spans="1:51" ht="103.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>3</v>
       </c>
       <c r="B32" s="17" t="str">
         <v>Few_Indicators_subWatSani</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="35"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="35"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="30"/>
-      <c r="T32" s="30"/>
-      <c r="U32" s="30"/>
-      <c r="V32" s="30"/>
-      <c r="W32" s="30"/>
-      <c r="X32" s="30"/>
-      <c r="Y32" s="30"/>
-      <c r="Z32" s="30"/>
-      <c r="AA32" s="30"/>
-      <c r="AB32" s="30" t="e" vm="7">
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="36"/>
+      <c r="M32" s="36"/>
+      <c r="N32" s="36"/>
+      <c r="O32" s="36"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="31"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="31"/>
+      <c r="V32" s="31"/>
+      <c r="W32" s="31"/>
+      <c r="X32" s="31"/>
+      <c r="Y32" s="31"/>
+      <c r="Z32" s="31"/>
+      <c r="AA32" s="31"/>
+      <c r="AB32" s="31" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
-      <c r="AC32" s="30"/>
-      <c r="AD32" s="30"/>
-      <c r="AE32" s="30"/>
-      <c r="AF32" s="30"/>
-      <c r="AG32" s="30"/>
-      <c r="AH32" s="30"/>
-      <c r="AI32" s="30"/>
-      <c r="AJ32" s="30"/>
-      <c r="AK32" s="30"/>
-      <c r="AL32" s="30"/>
-      <c r="AM32" s="30"/>
-      <c r="AN32" s="30"/>
-      <c r="AO32" s="30"/>
-      <c r="AP32" s="30"/>
-      <c r="AQ32" s="30"/>
-    </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AC32" s="31"/>
+      <c r="AD32" s="31"/>
+      <c r="AE32" s="31"/>
+      <c r="AF32" s="31"/>
+      <c r="AG32" s="31"/>
+      <c r="AH32" s="31"/>
+      <c r="AI32" s="31"/>
+      <c r="AJ32" s="31"/>
+      <c r="AK32" s="31"/>
+      <c r="AL32" s="31"/>
+      <c r="AM32" s="31"/>
+      <c r="AN32" s="31"/>
+      <c r="AO32" s="31"/>
+      <c r="AP32" s="31"/>
+      <c r="AQ32" s="31"/>
+    </row>
+    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>4</v>
       </c>
       <c r="B33" s="6" t="str">
         <v>Only_OPP</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
-      <c r="L33" s="32"/>
-      <c r="M33" s="32"/>
-      <c r="N33" s="32"/>
-      <c r="O33" s="32"/>
-      <c r="Q33" s="30"/>
-      <c r="R33" s="30"/>
-      <c r="S33" s="30"/>
-      <c r="T33" s="30"/>
-      <c r="U33" s="30"/>
-      <c r="V33" s="30"/>
-      <c r="W33" s="30"/>
-      <c r="X33" s="30"/>
-      <c r="Y33" s="30"/>
-      <c r="Z33" s="30"/>
-      <c r="AA33" s="30"/>
-      <c r="AB33" s="30"/>
-      <c r="AC33" s="30"/>
-      <c r="AD33" s="30"/>
-      <c r="AE33" s="30"/>
-      <c r="AF33" s="30"/>
-      <c r="AG33" s="30"/>
-      <c r="AH33" s="30"/>
-      <c r="AI33" s="30"/>
-      <c r="AJ33" s="30"/>
-      <c r="AK33" s="30"/>
-      <c r="AL33" s="30"/>
-      <c r="AM33" s="30"/>
-      <c r="AN33" s="30"/>
-      <c r="AO33" s="30"/>
-      <c r="AP33" s="30"/>
-      <c r="AQ33" s="30"/>
-    </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="D33" s="35"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="33"/>
+      <c r="N33" s="33"/>
+      <c r="O33" s="33"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="31"/>
+      <c r="S33" s="31"/>
+      <c r="T33" s="31"/>
+      <c r="U33" s="31"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+      <c r="Z33" s="31"/>
+      <c r="AA33" s="31"/>
+      <c r="AB33" s="31"/>
+      <c r="AC33" s="31"/>
+      <c r="AD33" s="31"/>
+      <c r="AE33" s="31"/>
+      <c r="AF33" s="31"/>
+      <c r="AG33" s="31"/>
+      <c r="AH33" s="31"/>
+      <c r="AI33" s="31"/>
+      <c r="AJ33" s="31"/>
+      <c r="AK33" s="31"/>
+      <c r="AL33" s="31"/>
+      <c r="AM33" s="31"/>
+      <c r="AN33" s="31"/>
+      <c r="AO33" s="31"/>
+      <c r="AP33" s="31"/>
+      <c r="AQ33" s="31"/>
+    </row>
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="str">
         <v>Baseline</v>
       </c>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
-      <c r="L34" s="32"/>
-      <c r="M34" s="32"/>
-      <c r="N34" s="32"/>
-      <c r="O34" s="32"/>
-      <c r="Q34" s="30"/>
-      <c r="R34" s="30"/>
-      <c r="S34" s="30"/>
-      <c r="T34" s="30"/>
-      <c r="U34" s="30"/>
-      <c r="V34" s="30"/>
-      <c r="W34" s="30"/>
-      <c r="X34" s="30"/>
-      <c r="Y34" s="30"/>
-      <c r="Z34" s="30"/>
-      <c r="AA34" s="30"/>
-      <c r="AB34" s="30"/>
-      <c r="AC34" s="30"/>
-      <c r="AD34" s="30"/>
-      <c r="AE34" s="30"/>
-      <c r="AF34" s="30"/>
-      <c r="AG34" s="30"/>
-      <c r="AH34" s="30"/>
-      <c r="AI34" s="30"/>
-      <c r="AJ34" s="30"/>
-      <c r="AK34" s="30"/>
-      <c r="AL34" s="30"/>
-      <c r="AM34" s="30"/>
-      <c r="AN34" s="30"/>
-      <c r="AO34" s="30"/>
-      <c r="AP34" s="30"/>
-      <c r="AQ34" s="30"/>
-    </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="33"/>
+      <c r="M34" s="33"/>
+      <c r="N34" s="33"/>
+      <c r="O34" s="33"/>
+      <c r="Q34" s="31"/>
+      <c r="R34" s="31"/>
+      <c r="S34" s="31"/>
+      <c r="T34" s="31"/>
+      <c r="U34" s="31"/>
+      <c r="V34" s="31"/>
+      <c r="W34" s="31"/>
+      <c r="X34" s="31"/>
+      <c r="Y34" s="31"/>
+      <c r="Z34" s="31"/>
+      <c r="AA34" s="31"/>
+      <c r="AB34" s="31"/>
+      <c r="AC34" s="31"/>
+      <c r="AD34" s="31"/>
+      <c r="AE34" s="31"/>
+      <c r="AF34" s="31"/>
+      <c r="AG34" s="31"/>
+      <c r="AH34" s="31"/>
+      <c r="AI34" s="31"/>
+      <c r="AJ34" s="31"/>
+      <c r="AK34" s="31"/>
+      <c r="AL34" s="31"/>
+      <c r="AM34" s="31"/>
+      <c r="AN34" s="31"/>
+      <c r="AO34" s="31"/>
+      <c r="AP34" s="31"/>
+      <c r="AQ34" s="31"/>
+    </row>
+    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B35" s="6" t="str">
         <v>No_nonDLS_limExt</v>
       </c>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32" t="s">
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="33"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="J35" s="32"/>
-      <c r="K35" s="32"/>
-      <c r="L35" s="32"/>
-      <c r="M35" s="32"/>
-      <c r="N35" s="32"/>
-      <c r="O35" s="32"/>
-      <c r="Q35" s="30"/>
-      <c r="R35" s="30"/>
-      <c r="S35" s="30"/>
-      <c r="T35" s="30"/>
-      <c r="U35" s="30"/>
-      <c r="V35" s="30"/>
-      <c r="W35" s="30"/>
-      <c r="X35" s="30"/>
-      <c r="Y35" s="30"/>
-      <c r="Z35" s="30"/>
-      <c r="AA35" s="30"/>
-      <c r="AB35" s="30"/>
-      <c r="AC35" s="30"/>
-      <c r="AD35" s="30"/>
-      <c r="AE35" s="30"/>
-      <c r="AF35" s="30"/>
-      <c r="AG35" s="30"/>
-      <c r="AH35" s="30"/>
-      <c r="AI35" s="30"/>
-      <c r="AJ35" s="30"/>
-      <c r="AK35" s="30"/>
-      <c r="AL35" s="30"/>
-      <c r="AM35" s="30"/>
-      <c r="AN35" s="30"/>
-      <c r="AO35" s="30"/>
-      <c r="AP35" s="30"/>
-      <c r="AQ35" s="30"/>
-    </row>
-    <row r="36" spans="1:43" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J35" s="33"/>
+      <c r="K35" s="33"/>
+      <c r="L35" s="33"/>
+      <c r="M35" s="33"/>
+      <c r="N35" s="33"/>
+      <c r="O35" s="33"/>
+      <c r="Q35" s="31"/>
+      <c r="R35" s="31"/>
+      <c r="S35" s="31"/>
+      <c r="T35" s="31"/>
+      <c r="U35" s="31"/>
+      <c r="V35" s="31"/>
+      <c r="W35" s="31"/>
+      <c r="X35" s="31"/>
+      <c r="Y35" s="31"/>
+      <c r="Z35" s="31"/>
+      <c r="AA35" s="31"/>
+      <c r="AB35" s="31"/>
+      <c r="AC35" s="31"/>
+      <c r="AD35" s="31"/>
+      <c r="AE35" s="31"/>
+      <c r="AF35" s="31"/>
+      <c r="AG35" s="31"/>
+      <c r="AH35" s="31"/>
+      <c r="AI35" s="31"/>
+      <c r="AJ35" s="31"/>
+      <c r="AK35" s="31"/>
+      <c r="AL35" s="31"/>
+      <c r="AM35" s="31"/>
+      <c r="AN35" s="31"/>
+      <c r="AO35" s="31"/>
+      <c r="AP35" s="31"/>
+      <c r="AQ35" s="31"/>
+    </row>
+    <row r="36" spans="1:43" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="6" t="str">
         <v>BHN</v>
       </c>
-      <c r="C36" s="36" t="s">
+      <c r="C36" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="32"/>
-      <c r="N36" s="32"/>
-      <c r="O36" s="32"/>
-      <c r="Q36" s="30"/>
-      <c r="R36" s="30"/>
-      <c r="S36" s="30"/>
-      <c r="T36" s="30"/>
-      <c r="U36" s="30"/>
-      <c r="V36" s="30"/>
-      <c r="W36" s="30"/>
-      <c r="X36" s="30"/>
-      <c r="Y36" s="30"/>
-      <c r="Z36" s="30"/>
-      <c r="AA36" s="30"/>
-      <c r="AB36" s="30"/>
-      <c r="AC36" s="30"/>
-      <c r="AD36" s="30"/>
-      <c r="AE36" s="30"/>
-      <c r="AF36" s="30"/>
-      <c r="AG36" s="30"/>
-      <c r="AH36" s="30"/>
-      <c r="AI36" s="30"/>
-      <c r="AJ36" s="30"/>
-      <c r="AK36" s="30"/>
-      <c r="AL36" s="30"/>
-      <c r="AM36" s="30"/>
-      <c r="AN36" s="30"/>
-      <c r="AO36" s="30"/>
-      <c r="AP36" s="30"/>
-      <c r="AQ36" s="30"/>
-    </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB37" s="30"/>
-      <c r="AC37" s="30"/>
-      <c r="AD37" s="30"/>
-      <c r="AE37" s="30"/>
-      <c r="AF37" s="30"/>
-      <c r="AG37" s="30"/>
-      <c r="AH37" s="30"/>
-      <c r="AI37" s="30"/>
-      <c r="AJ37" s="30"/>
-      <c r="AK37" s="30"/>
-      <c r="AL37" s="30"/>
-      <c r="AM37" s="30"/>
-      <c r="AN37" s="30"/>
-      <c r="AO37" s="30"/>
-      <c r="AP37" s="30"/>
-      <c r="AQ37" s="30"/>
-    </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB38" s="30"/>
-      <c r="AC38" s="30"/>
-      <c r="AD38" s="30"/>
-      <c r="AE38" s="30"/>
-      <c r="AF38" s="30"/>
-      <c r="AG38" s="30"/>
-      <c r="AH38" s="30"/>
-      <c r="AI38" s="30"/>
-      <c r="AJ38" s="30"/>
-      <c r="AK38" s="30"/>
-      <c r="AL38" s="30"/>
-      <c r="AM38" s="30"/>
-      <c r="AN38" s="30"/>
-      <c r="AO38" s="30"/>
-      <c r="AP38" s="30"/>
-      <c r="AQ38" s="30"/>
-    </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB39" s="30"/>
-      <c r="AC39" s="30"/>
-      <c r="AD39" s="30"/>
-      <c r="AE39" s="30"/>
-      <c r="AF39" s="30"/>
-      <c r="AG39" s="30"/>
-      <c r="AH39" s="30"/>
-      <c r="AI39" s="30"/>
-      <c r="AJ39" s="30"/>
-      <c r="AK39" s="30"/>
-      <c r="AL39" s="30"/>
-      <c r="AM39" s="30"/>
-      <c r="AN39" s="30"/>
-      <c r="AO39" s="30"/>
-      <c r="AP39" s="30"/>
-      <c r="AQ39" s="30"/>
-    </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB40" s="30"/>
-      <c r="AC40" s="30"/>
-      <c r="AD40" s="30"/>
-      <c r="AE40" s="30"/>
-      <c r="AF40" s="30"/>
-      <c r="AG40" s="30"/>
-      <c r="AH40" s="30"/>
-      <c r="AI40" s="30"/>
-      <c r="AJ40" s="30"/>
-      <c r="AK40" s="30"/>
-      <c r="AL40" s="30"/>
-      <c r="AM40" s="30"/>
-      <c r="AN40" s="30"/>
-      <c r="AO40" s="30"/>
-      <c r="AP40" s="30"/>
-      <c r="AQ40" s="30"/>
-    </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB41" s="30"/>
-      <c r="AC41" s="30"/>
-      <c r="AD41" s="30"/>
-      <c r="AE41" s="30"/>
-      <c r="AF41" s="30"/>
-      <c r="AG41" s="30"/>
-      <c r="AH41" s="30"/>
-      <c r="AI41" s="30"/>
-      <c r="AJ41" s="30"/>
-      <c r="AK41" s="30"/>
-      <c r="AL41" s="30"/>
-      <c r="AM41" s="30"/>
-      <c r="AN41" s="30"/>
-      <c r="AO41" s="30"/>
-      <c r="AP41" s="30"/>
-      <c r="AQ41" s="30"/>
-    </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB42" s="30" t="e" vm="8">
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="37"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="33"/>
+      <c r="N36" s="33"/>
+      <c r="O36" s="33"/>
+      <c r="Q36" s="31"/>
+      <c r="R36" s="31"/>
+      <c r="S36" s="31"/>
+      <c r="T36" s="31"/>
+      <c r="U36" s="31"/>
+      <c r="V36" s="31"/>
+      <c r="W36" s="31"/>
+      <c r="X36" s="31"/>
+      <c r="Y36" s="31"/>
+      <c r="Z36" s="31"/>
+      <c r="AA36" s="31"/>
+      <c r="AB36" s="31"/>
+      <c r="AC36" s="31"/>
+      <c r="AD36" s="31"/>
+      <c r="AE36" s="31"/>
+      <c r="AF36" s="31"/>
+      <c r="AG36" s="31"/>
+      <c r="AH36" s="31"/>
+      <c r="AI36" s="31"/>
+      <c r="AJ36" s="31"/>
+      <c r="AK36" s="31"/>
+      <c r="AL36" s="31"/>
+      <c r="AM36" s="31"/>
+      <c r="AN36" s="31"/>
+      <c r="AO36" s="31"/>
+      <c r="AP36" s="31"/>
+      <c r="AQ36" s="31"/>
+    </row>
+    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB37" s="31"/>
+      <c r="AC37" s="31"/>
+      <c r="AD37" s="31"/>
+      <c r="AE37" s="31"/>
+      <c r="AF37" s="31"/>
+      <c r="AG37" s="31"/>
+      <c r="AH37" s="31"/>
+      <c r="AI37" s="31"/>
+      <c r="AJ37" s="31"/>
+      <c r="AK37" s="31"/>
+      <c r="AL37" s="31"/>
+      <c r="AM37" s="31"/>
+      <c r="AN37" s="31"/>
+      <c r="AO37" s="31"/>
+      <c r="AP37" s="31"/>
+      <c r="AQ37" s="31"/>
+    </row>
+    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB38" s="31"/>
+      <c r="AC38" s="31"/>
+      <c r="AD38" s="31"/>
+      <c r="AE38" s="31"/>
+      <c r="AF38" s="31"/>
+      <c r="AG38" s="31"/>
+      <c r="AH38" s="31"/>
+      <c r="AI38" s="31"/>
+      <c r="AJ38" s="31"/>
+      <c r="AK38" s="31"/>
+      <c r="AL38" s="31"/>
+      <c r="AM38" s="31"/>
+      <c r="AN38" s="31"/>
+      <c r="AO38" s="31"/>
+      <c r="AP38" s="31"/>
+      <c r="AQ38" s="31"/>
+    </row>
+    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB39" s="31"/>
+      <c r="AC39" s="31"/>
+      <c r="AD39" s="31"/>
+      <c r="AE39" s="31"/>
+      <c r="AF39" s="31"/>
+      <c r="AG39" s="31"/>
+      <c r="AH39" s="31"/>
+      <c r="AI39" s="31"/>
+      <c r="AJ39" s="31"/>
+      <c r="AK39" s="31"/>
+      <c r="AL39" s="31"/>
+      <c r="AM39" s="31"/>
+      <c r="AN39" s="31"/>
+      <c r="AO39" s="31"/>
+      <c r="AP39" s="31"/>
+      <c r="AQ39" s="31"/>
+    </row>
+    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB40" s="31"/>
+      <c r="AC40" s="31"/>
+      <c r="AD40" s="31"/>
+      <c r="AE40" s="31"/>
+      <c r="AF40" s="31"/>
+      <c r="AG40" s="31"/>
+      <c r="AH40" s="31"/>
+      <c r="AI40" s="31"/>
+      <c r="AJ40" s="31"/>
+      <c r="AK40" s="31"/>
+      <c r="AL40" s="31"/>
+      <c r="AM40" s="31"/>
+      <c r="AN40" s="31"/>
+      <c r="AO40" s="31"/>
+      <c r="AP40" s="31"/>
+      <c r="AQ40" s="31"/>
+    </row>
+    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB41" s="31"/>
+      <c r="AC41" s="31"/>
+      <c r="AD41" s="31"/>
+      <c r="AE41" s="31"/>
+      <c r="AF41" s="31"/>
+      <c r="AG41" s="31"/>
+      <c r="AH41" s="31"/>
+      <c r="AI41" s="31"/>
+      <c r="AJ41" s="31"/>
+      <c r="AK41" s="31"/>
+      <c r="AL41" s="31"/>
+      <c r="AM41" s="31"/>
+      <c r="AN41" s="31"/>
+      <c r="AO41" s="31"/>
+      <c r="AP41" s="31"/>
+      <c r="AQ41" s="31"/>
+    </row>
+    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB42" s="31" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-      <c r="AC42" s="30"/>
-      <c r="AD42" s="30"/>
-      <c r="AE42" s="30"/>
-      <c r="AF42" s="30"/>
-      <c r="AG42" s="30"/>
-      <c r="AH42" s="30"/>
-      <c r="AI42" s="30"/>
-      <c r="AJ42" s="30"/>
-      <c r="AK42" s="30"/>
-      <c r="AL42" s="30"/>
-      <c r="AM42" s="30"/>
-      <c r="AN42" s="30"/>
-      <c r="AO42" s="30"/>
-      <c r="AP42" s="30"/>
-      <c r="AQ42" s="30"/>
-    </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB43" s="30"/>
-      <c r="AC43" s="30"/>
-      <c r="AD43" s="30"/>
-      <c r="AE43" s="30"/>
-      <c r="AF43" s="30"/>
-      <c r="AG43" s="30"/>
-      <c r="AH43" s="30"/>
-      <c r="AI43" s="30"/>
-      <c r="AJ43" s="30"/>
-      <c r="AK43" s="30"/>
-      <c r="AL43" s="30"/>
-      <c r="AM43" s="30"/>
-      <c r="AN43" s="30"/>
-      <c r="AO43" s="30"/>
-      <c r="AP43" s="30"/>
-      <c r="AQ43" s="30"/>
-    </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB44" s="30"/>
-      <c r="AC44" s="30"/>
-      <c r="AD44" s="30"/>
-      <c r="AE44" s="30"/>
-      <c r="AF44" s="30"/>
-      <c r="AG44" s="30"/>
-      <c r="AH44" s="30"/>
-      <c r="AI44" s="30"/>
-      <c r="AJ44" s="30"/>
-      <c r="AK44" s="30"/>
-      <c r="AL44" s="30"/>
-      <c r="AM44" s="30"/>
-      <c r="AN44" s="30"/>
-      <c r="AO44" s="30"/>
-      <c r="AP44" s="30"/>
-      <c r="AQ44" s="30"/>
-    </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB45" s="30"/>
-      <c r="AC45" s="30"/>
-      <c r="AD45" s="30"/>
-      <c r="AE45" s="30"/>
-      <c r="AF45" s="30"/>
-      <c r="AG45" s="30"/>
-      <c r="AH45" s="30"/>
-      <c r="AI45" s="30"/>
-      <c r="AJ45" s="30"/>
-      <c r="AK45" s="30"/>
-      <c r="AL45" s="30"/>
-      <c r="AM45" s="30"/>
-      <c r="AN45" s="30"/>
-      <c r="AO45" s="30"/>
-      <c r="AP45" s="30"/>
-      <c r="AQ45" s="30"/>
-    </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB46" s="30"/>
-      <c r="AC46" s="30"/>
-      <c r="AD46" s="30"/>
-      <c r="AE46" s="30"/>
-      <c r="AF46" s="30"/>
-      <c r="AG46" s="30"/>
-      <c r="AH46" s="30"/>
-      <c r="AI46" s="30"/>
-      <c r="AJ46" s="30"/>
-      <c r="AK46" s="30"/>
-      <c r="AL46" s="30"/>
-      <c r="AM46" s="30"/>
-      <c r="AN46" s="30"/>
-      <c r="AO46" s="30"/>
-      <c r="AP46" s="30"/>
-      <c r="AQ46" s="30"/>
-    </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB47" s="30"/>
-      <c r="AC47" s="30"/>
-      <c r="AD47" s="30"/>
-      <c r="AE47" s="30"/>
-      <c r="AF47" s="30"/>
-      <c r="AG47" s="30"/>
-      <c r="AH47" s="30"/>
-      <c r="AI47" s="30"/>
-      <c r="AJ47" s="30"/>
-      <c r="AK47" s="30"/>
-      <c r="AL47" s="30"/>
-      <c r="AM47" s="30"/>
-      <c r="AN47" s="30"/>
-      <c r="AO47" s="30"/>
-      <c r="AP47" s="30"/>
-      <c r="AQ47" s="30"/>
-    </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB48" s="30"/>
-      <c r="AC48" s="30"/>
-      <c r="AD48" s="30"/>
-      <c r="AE48" s="30"/>
-      <c r="AF48" s="30"/>
-      <c r="AG48" s="30"/>
-      <c r="AH48" s="30"/>
-      <c r="AI48" s="30"/>
-      <c r="AJ48" s="30"/>
-      <c r="AK48" s="30"/>
-      <c r="AL48" s="30"/>
-      <c r="AM48" s="30"/>
-      <c r="AN48" s="30"/>
-      <c r="AO48" s="30"/>
-      <c r="AP48" s="30"/>
-      <c r="AQ48" s="30"/>
-    </row>
-    <row r="49" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB49" s="30"/>
-      <c r="AC49" s="30"/>
-      <c r="AD49" s="30"/>
-      <c r="AE49" s="30"/>
-      <c r="AF49" s="30"/>
-      <c r="AG49" s="30"/>
-      <c r="AH49" s="30"/>
-      <c r="AI49" s="30"/>
-      <c r="AJ49" s="30"/>
-      <c r="AK49" s="30"/>
-      <c r="AL49" s="30"/>
-      <c r="AM49" s="30"/>
-      <c r="AN49" s="30"/>
-      <c r="AO49" s="30"/>
-      <c r="AP49" s="30"/>
-      <c r="AQ49" s="30"/>
-    </row>
-    <row r="50" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB50" s="30"/>
-      <c r="AC50" s="30"/>
-      <c r="AD50" s="30"/>
-      <c r="AE50" s="30"/>
-      <c r="AF50" s="30"/>
-      <c r="AG50" s="30"/>
-      <c r="AH50" s="30"/>
-      <c r="AI50" s="30"/>
-      <c r="AJ50" s="30"/>
-      <c r="AK50" s="30"/>
-      <c r="AL50" s="30"/>
-      <c r="AM50" s="30"/>
-      <c r="AN50" s="30"/>
-      <c r="AO50" s="30"/>
-      <c r="AP50" s="30"/>
-      <c r="AQ50" s="30"/>
-    </row>
-    <row r="51" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB51" s="30"/>
-      <c r="AC51" s="30"/>
-      <c r="AD51" s="30"/>
-      <c r="AE51" s="30"/>
-      <c r="AF51" s="30"/>
-      <c r="AG51" s="30"/>
-      <c r="AH51" s="30"/>
-      <c r="AI51" s="30"/>
-      <c r="AJ51" s="30"/>
-      <c r="AK51" s="30"/>
-      <c r="AL51" s="30"/>
-      <c r="AM51" s="30"/>
-      <c r="AN51" s="30"/>
-      <c r="AO51" s="30"/>
-      <c r="AP51" s="30"/>
-      <c r="AQ51" s="30"/>
-    </row>
-    <row r="52" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB52" s="30"/>
-      <c r="AC52" s="30"/>
-      <c r="AD52" s="30"/>
-      <c r="AE52" s="30"/>
-      <c r="AF52" s="30"/>
-      <c r="AG52" s="30"/>
-      <c r="AH52" s="30"/>
-      <c r="AI52" s="30"/>
-      <c r="AJ52" s="30"/>
-      <c r="AK52" s="30"/>
-      <c r="AL52" s="30"/>
-      <c r="AM52" s="30"/>
-      <c r="AN52" s="30"/>
-      <c r="AO52" s="30"/>
-      <c r="AP52" s="30"/>
-      <c r="AQ52" s="30"/>
-    </row>
-    <row r="53" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB53" s="30"/>
-      <c r="AC53" s="30"/>
-      <c r="AD53" s="30"/>
-      <c r="AE53" s="30"/>
-      <c r="AF53" s="30"/>
-      <c r="AG53" s="30"/>
-      <c r="AH53" s="30"/>
-      <c r="AI53" s="30"/>
-      <c r="AJ53" s="30"/>
-      <c r="AK53" s="30"/>
-      <c r="AL53" s="30"/>
-      <c r="AM53" s="30"/>
-      <c r="AN53" s="30"/>
-      <c r="AO53" s="30"/>
-      <c r="AP53" s="30"/>
-      <c r="AQ53" s="30"/>
+      <c r="AC42" s="31"/>
+      <c r="AD42" s="31"/>
+      <c r="AE42" s="31"/>
+      <c r="AF42" s="31"/>
+      <c r="AG42" s="31"/>
+      <c r="AH42" s="31"/>
+      <c r="AI42" s="31"/>
+      <c r="AJ42" s="31"/>
+      <c r="AK42" s="31"/>
+      <c r="AL42" s="31"/>
+      <c r="AM42" s="31"/>
+      <c r="AN42" s="31"/>
+      <c r="AO42" s="31"/>
+      <c r="AP42" s="31"/>
+      <c r="AQ42" s="31"/>
+    </row>
+    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB43" s="31"/>
+      <c r="AC43" s="31"/>
+      <c r="AD43" s="31"/>
+      <c r="AE43" s="31"/>
+      <c r="AF43" s="31"/>
+      <c r="AG43" s="31"/>
+      <c r="AH43" s="31"/>
+      <c r="AI43" s="31"/>
+      <c r="AJ43" s="31"/>
+      <c r="AK43" s="31"/>
+      <c r="AL43" s="31"/>
+      <c r="AM43" s="31"/>
+      <c r="AN43" s="31"/>
+      <c r="AO43" s="31"/>
+      <c r="AP43" s="31"/>
+      <c r="AQ43" s="31"/>
+    </row>
+    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB44" s="31"/>
+      <c r="AC44" s="31"/>
+      <c r="AD44" s="31"/>
+      <c r="AE44" s="31"/>
+      <c r="AF44" s="31"/>
+      <c r="AG44" s="31"/>
+      <c r="AH44" s="31"/>
+      <c r="AI44" s="31"/>
+      <c r="AJ44" s="31"/>
+      <c r="AK44" s="31"/>
+      <c r="AL44" s="31"/>
+      <c r="AM44" s="31"/>
+      <c r="AN44" s="31"/>
+      <c r="AO44" s="31"/>
+      <c r="AP44" s="31"/>
+      <c r="AQ44" s="31"/>
+    </row>
+    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB45" s="31"/>
+      <c r="AC45" s="31"/>
+      <c r="AD45" s="31"/>
+      <c r="AE45" s="31"/>
+      <c r="AF45" s="31"/>
+      <c r="AG45" s="31"/>
+      <c r="AH45" s="31"/>
+      <c r="AI45" s="31"/>
+      <c r="AJ45" s="31"/>
+      <c r="AK45" s="31"/>
+      <c r="AL45" s="31"/>
+      <c r="AM45" s="31"/>
+      <c r="AN45" s="31"/>
+      <c r="AO45" s="31"/>
+      <c r="AP45" s="31"/>
+      <c r="AQ45" s="31"/>
+    </row>
+    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB46" s="31"/>
+      <c r="AC46" s="31"/>
+      <c r="AD46" s="31"/>
+      <c r="AE46" s="31"/>
+      <c r="AF46" s="31"/>
+      <c r="AG46" s="31"/>
+      <c r="AH46" s="31"/>
+      <c r="AI46" s="31"/>
+      <c r="AJ46" s="31"/>
+      <c r="AK46" s="31"/>
+      <c r="AL46" s="31"/>
+      <c r="AM46" s="31"/>
+      <c r="AN46" s="31"/>
+      <c r="AO46" s="31"/>
+      <c r="AP46" s="31"/>
+      <c r="AQ46" s="31"/>
+    </row>
+    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB47" s="31"/>
+      <c r="AC47" s="31"/>
+      <c r="AD47" s="31"/>
+      <c r="AE47" s="31"/>
+      <c r="AF47" s="31"/>
+      <c r="AG47" s="31"/>
+      <c r="AH47" s="31"/>
+      <c r="AI47" s="31"/>
+      <c r="AJ47" s="31"/>
+      <c r="AK47" s="31"/>
+      <c r="AL47" s="31"/>
+      <c r="AM47" s="31"/>
+      <c r="AN47" s="31"/>
+      <c r="AO47" s="31"/>
+      <c r="AP47" s="31"/>
+      <c r="AQ47" s="31"/>
+    </row>
+    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB48" s="31"/>
+      <c r="AC48" s="31"/>
+      <c r="AD48" s="31"/>
+      <c r="AE48" s="31"/>
+      <c r="AF48" s="31"/>
+      <c r="AG48" s="31"/>
+      <c r="AH48" s="31"/>
+      <c r="AI48" s="31"/>
+      <c r="AJ48" s="31"/>
+      <c r="AK48" s="31"/>
+      <c r="AL48" s="31"/>
+      <c r="AM48" s="31"/>
+      <c r="AN48" s="31"/>
+      <c r="AO48" s="31"/>
+      <c r="AP48" s="31"/>
+      <c r="AQ48" s="31"/>
+    </row>
+    <row r="49" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB49" s="31"/>
+      <c r="AC49" s="31"/>
+      <c r="AD49" s="31"/>
+      <c r="AE49" s="31"/>
+      <c r="AF49" s="31"/>
+      <c r="AG49" s="31"/>
+      <c r="AH49" s="31"/>
+      <c r="AI49" s="31"/>
+      <c r="AJ49" s="31"/>
+      <c r="AK49" s="31"/>
+      <c r="AL49" s="31"/>
+      <c r="AM49" s="31"/>
+      <c r="AN49" s="31"/>
+      <c r="AO49" s="31"/>
+      <c r="AP49" s="31"/>
+      <c r="AQ49" s="31"/>
+    </row>
+    <row r="50" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB50" s="31"/>
+      <c r="AC50" s="31"/>
+      <c r="AD50" s="31"/>
+      <c r="AE50" s="31"/>
+      <c r="AF50" s="31"/>
+      <c r="AG50" s="31"/>
+      <c r="AH50" s="31"/>
+      <c r="AI50" s="31"/>
+      <c r="AJ50" s="31"/>
+      <c r="AK50" s="31"/>
+      <c r="AL50" s="31"/>
+      <c r="AM50" s="31"/>
+      <c r="AN50" s="31"/>
+      <c r="AO50" s="31"/>
+      <c r="AP50" s="31"/>
+      <c r="AQ50" s="31"/>
+    </row>
+    <row r="51" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB51" s="31"/>
+      <c r="AC51" s="31"/>
+      <c r="AD51" s="31"/>
+      <c r="AE51" s="31"/>
+      <c r="AF51" s="31"/>
+      <c r="AG51" s="31"/>
+      <c r="AH51" s="31"/>
+      <c r="AI51" s="31"/>
+      <c r="AJ51" s="31"/>
+      <c r="AK51" s="31"/>
+      <c r="AL51" s="31"/>
+      <c r="AM51" s="31"/>
+      <c r="AN51" s="31"/>
+      <c r="AO51" s="31"/>
+      <c r="AP51" s="31"/>
+      <c r="AQ51" s="31"/>
+    </row>
+    <row r="52" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB52" s="31"/>
+      <c r="AC52" s="31"/>
+      <c r="AD52" s="31"/>
+      <c r="AE52" s="31"/>
+      <c r="AF52" s="31"/>
+      <c r="AG52" s="31"/>
+      <c r="AH52" s="31"/>
+      <c r="AI52" s="31"/>
+      <c r="AJ52" s="31"/>
+      <c r="AK52" s="31"/>
+      <c r="AL52" s="31"/>
+      <c r="AM52" s="31"/>
+      <c r="AN52" s="31"/>
+      <c r="AO52" s="31"/>
+      <c r="AP52" s="31"/>
+      <c r="AQ52" s="31"/>
+    </row>
+    <row r="53" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB53" s="31"/>
+      <c r="AC53" s="31"/>
+      <c r="AD53" s="31"/>
+      <c r="AE53" s="31"/>
+      <c r="AF53" s="31"/>
+      <c r="AG53" s="31"/>
+      <c r="AH53" s="31"/>
+      <c r="AI53" s="31"/>
+      <c r="AJ53" s="31"/>
+      <c r="AK53" s="31"/>
+      <c r="AL53" s="31"/>
+      <c r="AM53" s="31"/>
+      <c r="AN53" s="31"/>
+      <c r="AO53" s="31"/>
+      <c r="AP53" s="31"/>
+      <c r="AQ53" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="43">
@@ -3521,31 +3537,31 @@
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AY53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.33203125" customWidth="1"/>
+    <col min="2" max="2" width="35.28515625" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
-    <col min="5" max="16" width="4.33203125" customWidth="1"/>
-    <col min="19" max="19" width="8.88671875" customWidth="1"/>
+    <col min="5" max="16" width="4.28515625" customWidth="1"/>
+    <col min="19" max="19" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="39"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="42"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
@@ -3559,12 +3575,12 @@
       <c r="W3" s="22"/>
       <c r="X3" s="22"/>
     </row>
-    <row r="4" spans="1:24" ht="221.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" ht="221.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="15" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="25" t="str" cm="1">
-        <f t="array" ref="C4:Q4">Experiments!C1:Q1</f>
+        <f t="array" ref="C4:R4">Experiments!C1:R1</f>
         <v>BHN_FWB</v>
       </c>
       <c r="D4" s="23" t="str">
@@ -3603,21 +3619,24 @@
       <c r="O4" s="9" t="str">
         <v>Baseline</v>
       </c>
-      <c r="P4" s="23" t="str">
+      <c r="P4" s="29" t="str">
         <v>No_nonDLS_limExt</v>
       </c>
       <c r="Q4" s="23" t="str">
         <v>BHN</v>
       </c>
-      <c r="T4" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="U4" s="29"/>
-      <c r="V4" s="29"/>
-      <c r="W4" s="29"/>
-      <c r="X4" s="29"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="R4" s="23" t="str">
+        <v>No_non_DLS_BHNFWB</v>
+      </c>
+      <c r="T4" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="U4" s="30"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30"/>
+      <c r="X4" s="30"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="str" cm="1">
         <f t="array" ref="B5:B15">_xlfn.UNIQUE('Overview of indicators and DLS'!C4:C67)</f>
         <v>Food &amp; Nutrition</v>
@@ -3682,11 +3701,12 @@
         <f t="array" ref="Q5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!Q$2:Q$64=1))</f>
         <v>3</v>
       </c>
-      <c r="R5" s="16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R5" s="8" cm="1">
+        <f t="array" ref="R5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!R$2:R$64=1))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="str">
         <v>Health Care</v>
       </c>
@@ -3750,8 +3770,12 @@
         <f t="array" ref="Q6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!Q$2:Q$64=1))</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R6" s="8" cm="1">
+        <f t="array" ref="R6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!R$2:R$64=1))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="str">
         <v>Water</v>
       </c>
@@ -3815,8 +3839,12 @@
         <f t="array" ref="Q7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!Q$2:Q$64=1))</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R7" s="8" cm="1">
+        <f t="array" ref="R7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!R$2:R$64=1))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="str">
         <v>Sanitation</v>
       </c>
@@ -3880,8 +3908,12 @@
         <f t="array" ref="Q8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!Q$2:Q$64=1))</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R8" s="8" cm="1">
+        <f t="array" ref="R8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!R$2:R$64=1))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="str">
         <v>Food preparation</v>
       </c>
@@ -3945,8 +3977,12 @@
         <f t="array" ref="Q9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!Q$2:Q$64=1))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="R9" s="8" cm="1">
+        <f t="array" ref="R9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!R$2:R$64=1))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="str">
         <v>Thermal comfort</v>
       </c>
@@ -4010,8 +4046,12 @@
         <f t="array" ref="Q10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!Q$2:Q$64=1))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="R10" s="8" cm="1">
+        <f t="array" ref="R10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!R$2:R$64=1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="str">
         <v>Non material / Non-DLS</v>
       </c>
@@ -4075,8 +4115,12 @@
         <f t="array" ref="Q11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!Q$2:Q$64=1))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="R11" s="8" cm="1">
+        <f t="array" ref="R11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!R$2:R$64=1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="str">
         <v>Education</v>
       </c>
@@ -4140,8 +4184,12 @@
         <f t="array" ref="Q12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!Q$2:Q$64=1))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="R12" s="8" cm="1">
+        <f t="array" ref="R12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!R$2:R$64=1))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="str">
         <v>Social connectedness</v>
       </c>
@@ -4205,8 +4253,12 @@
         <f t="array" ref="Q13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!Q$2:Q$64=1))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="R13" s="8" cm="1">
+        <f t="array" ref="R13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!R$2:R$64=1))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="str">
         <v>Housing</v>
       </c>
@@ -4270,8 +4322,12 @@
         <f t="array" ref="Q14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!Q$2:Q$64=1))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="R14" s="8" cm="1">
+        <f t="array" ref="R14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!R$2:R$64=1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B15" s="13" t="str">
         <v>Physical Connectedness</v>
       </c>
@@ -4335,11 +4391,15 @@
         <f t="array" ref="Q15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!Q$2:Q$64=1))</f>
         <v>0</v>
       </c>
-      <c r="R15" t="s">
+      <c r="R15" s="12" cm="1">
+        <f t="array" ref="R15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!R$2:R$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="S15" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B16" s="11"/>
       <c r="C16" s="20"/>
       <c r="D16" s="14"/>
@@ -4356,8 +4416,9 @@
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
-    </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="R16" s="8"/>
+    </row>
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>33</v>
       </c>
@@ -4421,8 +4482,12 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="R17" s="14">
+        <f t="shared" ref="R17" si="1">SUM(R5:R15)</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
         <v>34</v>
       </c>
@@ -4486,8 +4551,12 @@
         <f>SUM(Experiments!Q2:Q53)</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="R18" s="8">
+        <f>SUM(Experiments!R2:R53)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B19" s="11" t="s">
         <v>35</v>
       </c>
@@ -4551,31 +4620,35 @@
         <f>SUM(Experiments!Q54:Q64)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="R19" s="8">
+        <f>SUM(Experiments!R54:R64)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>56</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40" t="s">
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="J21" s="40"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="40"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="43"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="43"/>
       <c r="Q21" s="1" t="s">
         <v>59</v>
       </c>
@@ -4583,288 +4656,277 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:51" ht="90.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:51" ht="90.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22" s="7" t="str" cm="1">
-        <f t="array" ref="B22:B36">TRANSPOSE(_xlfn.ANCHORARRAY(C4))</f>
+        <f t="array" ref="B22:B37">TRANSPOSE(_xlfn.ANCHORARRAY(C4))</f>
         <v>BHN_FWB</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="37"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="Q22" s="30" t="e" vm="9">
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="38"/>
+      <c r="L22" s="38"/>
+      <c r="M22" s="38"/>
+      <c r="N22" s="38"/>
+      <c r="O22" s="38"/>
+      <c r="Q22" s="31" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
-      <c r="R22" s="30"/>
-      <c r="S22" s="30"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="30"/>
-      <c r="V22" s="30"/>
-      <c r="W22" s="30"/>
-      <c r="X22" s="30"/>
-      <c r="Y22" s="30"/>
-      <c r="Z22" s="30"/>
-      <c r="AA22" s="30"/>
-      <c r="AB22" s="30" t="e" vm="10">
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="31"/>
+      <c r="V22" s="31"/>
+      <c r="W22" s="31"/>
+      <c r="X22" s="31"/>
+      <c r="Y22" s="31"/>
+      <c r="Z22" s="31"/>
+      <c r="AA22" s="31"/>
+      <c r="AB22" s="31" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
-      <c r="AC22" s="30"/>
-      <c r="AD22" s="30"/>
-      <c r="AE22" s="30"/>
-      <c r="AF22" s="30"/>
-      <c r="AG22" s="30"/>
-      <c r="AH22" s="30"/>
-      <c r="AI22" s="30"/>
-      <c r="AJ22" s="30"/>
-      <c r="AK22" s="30"/>
-      <c r="AL22" s="30"/>
-      <c r="AM22" s="30"/>
-      <c r="AN22" s="30"/>
-      <c r="AO22" s="30"/>
-      <c r="AP22" s="30"/>
-      <c r="AQ22" s="30"/>
-      <c r="AR22" s="30" t="e" vm="3">
+      <c r="AC22" s="31"/>
+      <c r="AD22" s="31"/>
+      <c r="AE22" s="31"/>
+      <c r="AF22" s="31"/>
+      <c r="AG22" s="31"/>
+      <c r="AH22" s="31"/>
+      <c r="AI22" s="31"/>
+      <c r="AJ22" s="31"/>
+      <c r="AK22" s="31"/>
+      <c r="AL22" s="31"/>
+      <c r="AM22" s="31"/>
+      <c r="AN22" s="31"/>
+      <c r="AO22" s="31"/>
+      <c r="AP22" s="31"/>
+      <c r="AQ22" s="31"/>
+      <c r="AR22" s="31" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="AS22" s="30"/>
-      <c r="AT22" s="30"/>
-      <c r="AU22" s="30"/>
-      <c r="AV22" s="30"/>
-      <c r="AW22" s="30"/>
-      <c r="AX22" s="30"/>
-      <c r="AY22" s="30"/>
-    </row>
-    <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AS22" s="31"/>
+      <c r="AT22" s="31"/>
+      <c r="AU22" s="31"/>
+      <c r="AV22" s="31"/>
+      <c r="AW22" s="31"/>
+      <c r="AX22" s="31"/>
+      <c r="AY22" s="31"/>
+    </row>
+    <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23" s="26" t="str">
         <v>BHN_FWB_AllExt</v>
       </c>
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="37"/>
-      <c r="N23" s="37"/>
-      <c r="O23" s="37"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
-      <c r="X23" s="30"/>
-      <c r="Y23" s="30"/>
-      <c r="Z23" s="30"/>
-      <c r="AA23" s="30"/>
-      <c r="AB23" s="30"/>
-      <c r="AC23" s="30"/>
-      <c r="AD23" s="30"/>
-      <c r="AE23" s="30"/>
-      <c r="AF23" s="30"/>
-      <c r="AG23" s="30"/>
-      <c r="AH23" s="30"/>
-      <c r="AI23" s="30"/>
-      <c r="AJ23" s="30"/>
-      <c r="AK23" s="30"/>
-      <c r="AL23" s="30"/>
-      <c r="AM23" s="30"/>
-      <c r="AN23" s="30"/>
-      <c r="AO23" s="30"/>
-      <c r="AP23" s="30"/>
-      <c r="AQ23" s="30"/>
-      <c r="AR23" s="30"/>
-      <c r="AS23" s="30"/>
-      <c r="AT23" s="30"/>
-      <c r="AU23" s="30"/>
-      <c r="AV23" s="30"/>
-      <c r="AW23" s="30"/>
-      <c r="AX23" s="30"/>
-      <c r="AY23" s="30"/>
-    </row>
-    <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="38"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="31"/>
+      <c r="V23" s="31"/>
+      <c r="W23" s="31"/>
+      <c r="X23" s="31"/>
+      <c r="Y23" s="31"/>
+      <c r="Z23" s="31"/>
+      <c r="AA23" s="31"/>
+      <c r="AB23" s="31"/>
+      <c r="AC23" s="31"/>
+      <c r="AD23" s="31"/>
+      <c r="AE23" s="31"/>
+      <c r="AF23" s="31"/>
+      <c r="AG23" s="31"/>
+      <c r="AH23" s="31"/>
+      <c r="AI23" s="31"/>
+      <c r="AJ23" s="31"/>
+      <c r="AK23" s="31"/>
+      <c r="AL23" s="31"/>
+      <c r="AM23" s="31"/>
+      <c r="AN23" s="31"/>
+      <c r="AO23" s="31"/>
+      <c r="AP23" s="31"/>
+      <c r="AQ23" s="31"/>
+      <c r="AR23" s="31"/>
+      <c r="AS23" s="31"/>
+      <c r="AT23" s="31"/>
+      <c r="AU23" s="31"/>
+      <c r="AV23" s="31"/>
+      <c r="AW23" s="31"/>
+      <c r="AX23" s="31"/>
+      <c r="AY23" s="31"/>
+    </row>
+    <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24" s="7" t="str">
         <v>Few_indicators_closest_DLS_coverage</v>
       </c>
-      <c r="C24" s="41" t="s">
+      <c r="C24" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="37"/>
-      <c r="K24" s="37"/>
-      <c r="L24" s="37"/>
-      <c r="M24" s="37"/>
-      <c r="N24" s="37"/>
-      <c r="O24" s="37"/>
-      <c r="Q24" s="30"/>
-      <c r="R24" s="30"/>
-      <c r="S24" s="30"/>
-      <c r="T24" s="30"/>
-      <c r="U24" s="30"/>
-      <c r="V24" s="30"/>
-      <c r="W24" s="30"/>
-      <c r="X24" s="30"/>
-      <c r="Y24" s="30"/>
-      <c r="Z24" s="30"/>
-      <c r="AA24" s="30"/>
-      <c r="AB24" s="30"/>
-      <c r="AC24" s="30"/>
-      <c r="AD24" s="30"/>
-      <c r="AE24" s="30"/>
-      <c r="AF24" s="30"/>
-      <c r="AG24" s="30"/>
-      <c r="AH24" s="30"/>
-      <c r="AI24" s="30"/>
-      <c r="AJ24" s="30"/>
-      <c r="AK24" s="30"/>
-      <c r="AL24" s="30"/>
-      <c r="AM24" s="30"/>
-      <c r="AN24" s="30"/>
-      <c r="AO24" s="30"/>
-      <c r="AP24" s="30"/>
-      <c r="AQ24" s="30"/>
-      <c r="AR24" s="30"/>
-      <c r="AS24" s="30"/>
-      <c r="AT24" s="30"/>
-      <c r="AU24" s="30"/>
-      <c r="AV24" s="30"/>
-      <c r="AW24" s="30"/>
-      <c r="AX24" s="30"/>
-      <c r="AY24" s="30"/>
-    </row>
-    <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="38"/>
+      <c r="Q24" s="31"/>
+      <c r="R24" s="31"/>
+      <c r="S24" s="31"/>
+      <c r="T24" s="31"/>
+      <c r="U24" s="31"/>
+      <c r="V24" s="31"/>
+      <c r="W24" s="31"/>
+      <c r="X24" s="31"/>
+      <c r="Y24" s="31"/>
+      <c r="Z24" s="31"/>
+      <c r="AA24" s="31"/>
+      <c r="AB24" s="31"/>
+      <c r="AC24" s="31"/>
+      <c r="AD24" s="31"/>
+      <c r="AE24" s="31"/>
+      <c r="AF24" s="31"/>
+      <c r="AG24" s="31"/>
+      <c r="AH24" s="31"/>
+      <c r="AI24" s="31"/>
+      <c r="AJ24" s="31"/>
+      <c r="AK24" s="31"/>
+      <c r="AL24" s="31"/>
+      <c r="AM24" s="31"/>
+      <c r="AN24" s="31"/>
+      <c r="AO24" s="31"/>
+      <c r="AP24" s="31"/>
+      <c r="AQ24" s="31"/>
+      <c r="AR24" s="31"/>
+      <c r="AS24" s="31"/>
+      <c r="AT24" s="31"/>
+      <c r="AU24" s="31"/>
+      <c r="AV24" s="31"/>
+      <c r="AW24" s="31"/>
+      <c r="AX24" s="31"/>
+      <c r="AY24" s="31"/>
+    </row>
+    <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25" s="7" t="str">
         <v>Few indicators_SPI_preferred</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="C25" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="37"/>
-      <c r="L25" s="37"/>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="Q25" s="49"/>
-      <c r="R25" s="49"/>
-      <c r="S25" s="49"/>
-      <c r="T25" s="49"/>
-      <c r="U25" s="49"/>
-      <c r="V25" s="49"/>
-      <c r="W25" s="49"/>
-      <c r="X25" s="49"/>
-      <c r="Y25" s="49"/>
-      <c r="Z25" s="49"/>
-      <c r="AA25" s="49"/>
-      <c r="AB25" s="30"/>
-      <c r="AC25" s="30"/>
-      <c r="AD25" s="30"/>
-      <c r="AE25" s="30"/>
-      <c r="AF25" s="30"/>
-      <c r="AG25" s="30"/>
-      <c r="AH25" s="30"/>
-      <c r="AI25" s="30"/>
-      <c r="AJ25" s="30"/>
-      <c r="AK25" s="30"/>
-      <c r="AL25" s="30"/>
-      <c r="AM25" s="30"/>
-      <c r="AN25" s="30"/>
-      <c r="AO25" s="30"/>
-      <c r="AP25" s="30"/>
-      <c r="AQ25" s="30"/>
-    </row>
-    <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="38"/>
+      <c r="M25" s="38"/>
+      <c r="N25" s="38"/>
+      <c r="O25" s="38"/>
+      <c r="AB25" s="31"/>
+      <c r="AC25" s="31"/>
+      <c r="AD25" s="31"/>
+      <c r="AE25" s="31"/>
+      <c r="AF25" s="31"/>
+      <c r="AG25" s="31"/>
+      <c r="AH25" s="31"/>
+      <c r="AI25" s="31"/>
+      <c r="AJ25" s="31"/>
+      <c r="AK25" s="31"/>
+      <c r="AL25" s="31"/>
+      <c r="AM25" s="31"/>
+      <c r="AN25" s="31"/>
+      <c r="AO25" s="31"/>
+      <c r="AP25" s="31"/>
+      <c r="AQ25" s="31"/>
+    </row>
+    <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26" s="7" t="str">
         <v>No_non_DLS</v>
       </c>
-      <c r="C26" s="43" t="s">
+      <c r="C26" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="37"/>
-      <c r="L26" s="37"/>
-      <c r="M26" s="37"/>
-      <c r="N26" s="37"/>
-      <c r="O26" s="37"/>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="30"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="30"/>
-      <c r="X26" s="30"/>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="30"/>
-      <c r="AA26" s="30"/>
-      <c r="AB26" s="30"/>
-      <c r="AC26" s="30"/>
-      <c r="AD26" s="30"/>
-      <c r="AE26" s="30"/>
-      <c r="AF26" s="30"/>
-      <c r="AG26" s="30"/>
-      <c r="AH26" s="30"/>
-      <c r="AI26" s="30"/>
-      <c r="AJ26" s="30"/>
-      <c r="AK26" s="30"/>
-      <c r="AL26" s="30"/>
-      <c r="AM26" s="30"/>
-      <c r="AN26" s="30"/>
-      <c r="AO26" s="30"/>
-      <c r="AP26" s="30"/>
-      <c r="AQ26" s="30"/>
-    </row>
-    <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="38"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="31"/>
+      <c r="Y26" s="31"/>
+      <c r="Z26" s="31"/>
+      <c r="AA26" s="31"/>
+      <c r="AB26" s="31"/>
+      <c r="AC26" s="31"/>
+      <c r="AD26" s="31"/>
+      <c r="AE26" s="31"/>
+      <c r="AF26" s="31"/>
+      <c r="AG26" s="31"/>
+      <c r="AH26" s="31"/>
+      <c r="AI26" s="31"/>
+      <c r="AJ26" s="31"/>
+      <c r="AK26" s="31"/>
+      <c r="AL26" s="31"/>
+      <c r="AM26" s="31"/>
+      <c r="AN26" s="31"/>
+      <c r="AO26" s="31"/>
+      <c r="AP26" s="31"/>
+      <c r="AQ26" s="31"/>
+    </row>
+    <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1</v>
       </c>
@@ -4879,819 +4941,822 @@
       <c r="F27" s="45"/>
       <c r="G27" s="45"/>
       <c r="H27" s="45"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="37"/>
-      <c r="L27" s="37"/>
-      <c r="M27" s="37"/>
-      <c r="N27" s="37"/>
-      <c r="O27" s="37"/>
-      <c r="Q27" s="30"/>
-      <c r="R27" s="30"/>
-      <c r="S27" s="30"/>
-      <c r="T27" s="30"/>
-      <c r="U27" s="30"/>
-      <c r="V27" s="30"/>
-      <c r="W27" s="30"/>
-      <c r="X27" s="30"/>
-      <c r="Y27" s="30"/>
-      <c r="Z27" s="30"/>
-      <c r="AA27" s="30"/>
-      <c r="AB27" s="30"/>
-      <c r="AC27" s="30"/>
-      <c r="AD27" s="30"/>
-      <c r="AE27" s="30"/>
-      <c r="AF27" s="30"/>
-      <c r="AG27" s="30"/>
-      <c r="AH27" s="30"/>
-      <c r="AI27" s="30"/>
-      <c r="AJ27" s="30"/>
-      <c r="AK27" s="30"/>
-      <c r="AL27" s="30"/>
-      <c r="AM27" s="30"/>
-      <c r="AN27" s="30"/>
-      <c r="AO27" s="30"/>
-      <c r="AP27" s="30"/>
-      <c r="AQ27" s="30"/>
-    </row>
-    <row r="28" spans="1:51" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="38"/>
+      <c r="M27" s="38"/>
+      <c r="N27" s="38"/>
+      <c r="O27" s="38"/>
+      <c r="Q27" s="31"/>
+      <c r="R27" s="31"/>
+      <c r="S27" s="31"/>
+      <c r="T27" s="31"/>
+      <c r="U27" s="31"/>
+      <c r="V27" s="31"/>
+      <c r="W27" s="31"/>
+      <c r="X27" s="31"/>
+      <c r="Y27" s="31"/>
+      <c r="Z27" s="31"/>
+      <c r="AA27" s="31"/>
+      <c r="AB27" s="31"/>
+      <c r="AC27" s="31"/>
+      <c r="AD27" s="31"/>
+      <c r="AE27" s="31"/>
+      <c r="AF27" s="31"/>
+      <c r="AG27" s="31"/>
+      <c r="AH27" s="31"/>
+      <c r="AI27" s="31"/>
+      <c r="AJ27" s="31"/>
+      <c r="AK27" s="31"/>
+      <c r="AL27" s="31"/>
+      <c r="AM27" s="31"/>
+      <c r="AN27" s="31"/>
+      <c r="AO27" s="31"/>
+      <c r="AP27" s="31"/>
+      <c r="AQ27" s="31"/>
+    </row>
+    <row r="28" spans="1:51" ht="65.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" s="17" t="str">
         <v>Few_indicators_closest_DLS_coverage_90</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="35"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="Q28" s="30"/>
-      <c r="R28" s="30"/>
-      <c r="S28" s="30"/>
-      <c r="T28" s="30"/>
-      <c r="U28" s="30"/>
-      <c r="V28" s="30"/>
-      <c r="W28" s="30"/>
-      <c r="X28" s="30"/>
-      <c r="Y28" s="30"/>
-      <c r="Z28" s="30"/>
-      <c r="AA28" s="30"/>
-      <c r="AB28" s="30"/>
-      <c r="AC28" s="30"/>
-      <c r="AD28" s="30"/>
-      <c r="AE28" s="30"/>
-      <c r="AF28" s="30"/>
-      <c r="AG28" s="30"/>
-      <c r="AH28" s="30"/>
-      <c r="AI28" s="30"/>
-      <c r="AJ28" s="30"/>
-      <c r="AK28" s="30"/>
-      <c r="AL28" s="30"/>
-      <c r="AM28" s="30"/>
-      <c r="AN28" s="30"/>
-      <c r="AO28" s="30"/>
-      <c r="AP28" s="30"/>
-      <c r="AQ28" s="30"/>
-    </row>
-    <row r="29" spans="1:51" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="36"/>
+      <c r="L28" s="36"/>
+      <c r="M28" s="36"/>
+      <c r="N28" s="36"/>
+      <c r="O28" s="36"/>
+      <c r="Q28" s="31"/>
+      <c r="R28" s="31"/>
+      <c r="S28" s="31"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="31"/>
+      <c r="V28" s="31"/>
+      <c r="W28" s="31"/>
+      <c r="X28" s="31"/>
+      <c r="Y28" s="31"/>
+      <c r="Z28" s="31"/>
+      <c r="AA28" s="31"/>
+      <c r="AB28" s="31"/>
+      <c r="AC28" s="31"/>
+      <c r="AD28" s="31"/>
+      <c r="AE28" s="31"/>
+      <c r="AF28" s="31"/>
+      <c r="AG28" s="31"/>
+      <c r="AH28" s="31"/>
+      <c r="AI28" s="31"/>
+      <c r="AJ28" s="31"/>
+      <c r="AK28" s="31"/>
+      <c r="AL28" s="31"/>
+      <c r="AM28" s="31"/>
+      <c r="AN28" s="31"/>
+      <c r="AO28" s="31"/>
+      <c r="AP28" s="31"/>
+      <c r="AQ28" s="31"/>
+    </row>
+    <row r="29" spans="1:51" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2</v>
       </c>
       <c r="B29" s="17" t="str">
         <v>Few indicators_SPI_preferred_90</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="35"/>
-      <c r="K29" s="35"/>
-      <c r="L29" s="35"/>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="35"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
-      <c r="AC29" s="30"/>
-      <c r="AD29" s="30"/>
-      <c r="AE29" s="30"/>
-      <c r="AF29" s="30"/>
-      <c r="AG29" s="30"/>
-      <c r="AH29" s="30"/>
-      <c r="AI29" s="30"/>
-      <c r="AJ29" s="30"/>
-      <c r="AK29" s="30"/>
-      <c r="AL29" s="30"/>
-      <c r="AM29" s="30"/>
-      <c r="AN29" s="30"/>
-      <c r="AO29" s="30"/>
-      <c r="AP29" s="30"/>
-      <c r="AQ29" s="30"/>
-    </row>
-    <row r="30" spans="1:51" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="36"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="36"/>
+      <c r="L29" s="36"/>
+      <c r="M29" s="36"/>
+      <c r="N29" s="36"/>
+      <c r="O29" s="36"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="31"/>
+      <c r="V29" s="31"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="31"/>
+      <c r="Y29" s="31"/>
+      <c r="Z29" s="31"/>
+      <c r="AA29" s="31"/>
+      <c r="AB29" s="31"/>
+      <c r="AC29" s="31"/>
+      <c r="AD29" s="31"/>
+      <c r="AE29" s="31"/>
+      <c r="AF29" s="31"/>
+      <c r="AG29" s="31"/>
+      <c r="AH29" s="31"/>
+      <c r="AI29" s="31"/>
+      <c r="AJ29" s="31"/>
+      <c r="AK29" s="31"/>
+      <c r="AL29" s="31"/>
+      <c r="AM29" s="31"/>
+      <c r="AN29" s="31"/>
+      <c r="AO29" s="31"/>
+      <c r="AP29" s="31"/>
+      <c r="AQ29" s="31"/>
+    </row>
+    <row r="30" spans="1:51" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>3</v>
       </c>
       <c r="B30" s="17" t="str">
         <v>Few_indicators_closeDLS_subPrimSchool</v>
       </c>
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="35"/>
-      <c r="K30" s="35"/>
-      <c r="L30" s="35"/>
-      <c r="M30" s="35"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="35"/>
-      <c r="Q30" s="30"/>
-      <c r="R30" s="30"/>
-      <c r="S30" s="30"/>
-      <c r="T30" s="30"/>
-      <c r="U30" s="30"/>
-      <c r="V30" s="30"/>
-      <c r="W30" s="30"/>
-      <c r="X30" s="30"/>
-      <c r="Y30" s="30"/>
-      <c r="Z30" s="30"/>
-      <c r="AA30" s="30"/>
-      <c r="AB30" s="30"/>
-      <c r="AC30" s="30"/>
-      <c r="AD30" s="30"/>
-      <c r="AE30" s="30"/>
-      <c r="AF30" s="30"/>
-      <c r="AG30" s="30"/>
-      <c r="AH30" s="30"/>
-      <c r="AI30" s="30"/>
-      <c r="AJ30" s="30"/>
-      <c r="AK30" s="30"/>
-      <c r="AL30" s="30"/>
-      <c r="AM30" s="30"/>
-      <c r="AN30" s="30"/>
-      <c r="AO30" s="30"/>
-      <c r="AP30" s="30"/>
-      <c r="AQ30" s="30"/>
-    </row>
-    <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="36"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="36"/>
+      <c r="O30" s="36"/>
+      <c r="Q30" s="31"/>
+      <c r="R30" s="31"/>
+      <c r="S30" s="31"/>
+      <c r="T30" s="31"/>
+      <c r="U30" s="31"/>
+      <c r="V30" s="31"/>
+      <c r="W30" s="31"/>
+      <c r="X30" s="31"/>
+      <c r="Y30" s="31"/>
+      <c r="Z30" s="31"/>
+      <c r="AA30" s="31"/>
+      <c r="AB30" s="31"/>
+      <c r="AC30" s="31"/>
+      <c r="AD30" s="31"/>
+      <c r="AE30" s="31"/>
+      <c r="AF30" s="31"/>
+      <c r="AG30" s="31"/>
+      <c r="AH30" s="31"/>
+      <c r="AI30" s="31"/>
+      <c r="AJ30" s="31"/>
+      <c r="AK30" s="31"/>
+      <c r="AL30" s="31"/>
+      <c r="AM30" s="31"/>
+      <c r="AN30" s="31"/>
+      <c r="AO30" s="31"/>
+      <c r="AP30" s="31"/>
+      <c r="AQ30" s="31"/>
+    </row>
+    <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>3</v>
       </c>
       <c r="B31" s="27" t="str">
         <v>No_non_DLS_90</v>
       </c>
-      <c r="C31" s="46" t="s">
+      <c r="C31" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="D31" s="46"/>
-      <c r="E31" s="46"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="46"/>
-      <c r="H31" s="46"/>
-      <c r="I31" s="46" t="s">
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="J31" s="46"/>
-      <c r="K31" s="46"/>
-      <c r="L31" s="46"/>
-      <c r="M31" s="46"/>
-      <c r="N31" s="46"/>
-      <c r="O31" s="46"/>
-      <c r="Q31" s="30"/>
-      <c r="R31" s="30"/>
-      <c r="S31" s="30"/>
-      <c r="T31" s="30"/>
-      <c r="U31" s="30"/>
-      <c r="V31" s="30"/>
-      <c r="W31" s="30"/>
-      <c r="X31" s="30"/>
-      <c r="Y31" s="30"/>
-      <c r="Z31" s="30"/>
-      <c r="AA31" s="30"/>
-      <c r="AB31" s="30"/>
-      <c r="AC31" s="30"/>
-      <c r="AD31" s="30"/>
-      <c r="AE31" s="30"/>
-      <c r="AF31" s="30"/>
-      <c r="AG31" s="30"/>
-      <c r="AH31" s="30"/>
-      <c r="AI31" s="30"/>
-      <c r="AJ31" s="30"/>
-      <c r="AK31" s="30"/>
-      <c r="AL31" s="30"/>
-      <c r="AM31" s="30"/>
-      <c r="AN31" s="30"/>
-      <c r="AO31" s="30"/>
-      <c r="AP31" s="30"/>
-      <c r="AQ31" s="30"/>
-    </row>
-    <row r="32" spans="1:51" ht="103.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J31" s="48"/>
+      <c r="K31" s="48"/>
+      <c r="L31" s="48"/>
+      <c r="M31" s="48"/>
+      <c r="N31" s="48"/>
+      <c r="O31" s="48"/>
+      <c r="Q31" s="31"/>
+      <c r="R31" s="31"/>
+      <c r="S31" s="31"/>
+      <c r="T31" s="31"/>
+      <c r="U31" s="31"/>
+      <c r="V31" s="31"/>
+      <c r="W31" s="31"/>
+      <c r="X31" s="31"/>
+      <c r="Y31" s="31"/>
+      <c r="Z31" s="31"/>
+      <c r="AA31" s="31"/>
+      <c r="AB31" s="31"/>
+      <c r="AC31" s="31"/>
+      <c r="AD31" s="31"/>
+      <c r="AE31" s="31"/>
+      <c r="AF31" s="31"/>
+      <c r="AG31" s="31"/>
+      <c r="AH31" s="31"/>
+      <c r="AI31" s="31"/>
+      <c r="AJ31" s="31"/>
+      <c r="AK31" s="31"/>
+      <c r="AL31" s="31"/>
+      <c r="AM31" s="31"/>
+      <c r="AN31" s="31"/>
+      <c r="AO31" s="31"/>
+      <c r="AP31" s="31"/>
+      <c r="AQ31" s="31"/>
+    </row>
+    <row r="32" spans="1:51" ht="103.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>3</v>
       </c>
       <c r="B32" s="27" t="str">
         <v>Few_Indicators_subWatSani</v>
       </c>
-      <c r="C32" s="46" t="s">
+      <c r="C32" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="D32" s="46"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="46"/>
-      <c r="H32" s="46"/>
-      <c r="I32" s="35"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="35"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="30"/>
-      <c r="T32" s="30"/>
-      <c r="U32" s="30"/>
-      <c r="V32" s="30"/>
-      <c r="W32" s="30"/>
-      <c r="X32" s="30"/>
-      <c r="Y32" s="30"/>
-      <c r="Z32" s="30"/>
-      <c r="AA32" s="30"/>
-      <c r="AB32" s="30"/>
-      <c r="AC32" s="30"/>
-      <c r="AD32" s="30"/>
-      <c r="AE32" s="30"/>
-      <c r="AF32" s="30"/>
-      <c r="AG32" s="30"/>
-      <c r="AH32" s="30"/>
-      <c r="AI32" s="30"/>
-      <c r="AJ32" s="30"/>
-      <c r="AK32" s="30"/>
-      <c r="AL32" s="30"/>
-      <c r="AM32" s="30"/>
-      <c r="AN32" s="30"/>
-      <c r="AO32" s="30"/>
-      <c r="AP32" s="30"/>
-      <c r="AQ32" s="30"/>
-    </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="36"/>
+      <c r="M32" s="36"/>
+      <c r="N32" s="36"/>
+      <c r="O32" s="36"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="31"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="31"/>
+      <c r="V32" s="31"/>
+      <c r="W32" s="31"/>
+      <c r="X32" s="31"/>
+      <c r="Y32" s="31"/>
+      <c r="Z32" s="31"/>
+      <c r="AA32" s="31"/>
+      <c r="AB32" s="31"/>
+      <c r="AC32" s="31"/>
+      <c r="AD32" s="31"/>
+      <c r="AE32" s="31"/>
+      <c r="AF32" s="31"/>
+      <c r="AG32" s="31"/>
+      <c r="AH32" s="31"/>
+      <c r="AI32" s="31"/>
+      <c r="AJ32" s="31"/>
+      <c r="AK32" s="31"/>
+      <c r="AL32" s="31"/>
+      <c r="AM32" s="31"/>
+      <c r="AN32" s="31"/>
+      <c r="AO32" s="31"/>
+      <c r="AP32" s="31"/>
+      <c r="AQ32" s="31"/>
+    </row>
+    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>4</v>
       </c>
       <c r="B33" s="28" t="str">
         <v>Only_OPP</v>
       </c>
-      <c r="C33" s="47" t="s">
+      <c r="C33" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="47"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
-      <c r="L33" s="32"/>
-      <c r="M33" s="32"/>
-      <c r="N33" s="32"/>
-      <c r="O33" s="32"/>
-      <c r="Q33" s="30"/>
-      <c r="R33" s="30"/>
-      <c r="S33" s="30"/>
-      <c r="T33" s="30"/>
-      <c r="U33" s="30"/>
-      <c r="V33" s="30"/>
-      <c r="W33" s="30"/>
-      <c r="X33" s="30"/>
-      <c r="Y33" s="30"/>
-      <c r="Z33" s="30"/>
-      <c r="AA33" s="30"/>
-      <c r="AB33" s="30"/>
-      <c r="AC33" s="30"/>
-      <c r="AD33" s="30"/>
-      <c r="AE33" s="30"/>
-      <c r="AF33" s="30"/>
-      <c r="AG33" s="30"/>
-      <c r="AH33" s="30"/>
-      <c r="AI33" s="30"/>
-      <c r="AJ33" s="30"/>
-      <c r="AK33" s="30"/>
-      <c r="AL33" s="30"/>
-      <c r="AM33" s="30"/>
-      <c r="AN33" s="30"/>
-      <c r="AO33" s="30"/>
-      <c r="AP33" s="30"/>
-      <c r="AQ33" s="30"/>
-    </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="33"/>
+      <c r="N33" s="33"/>
+      <c r="O33" s="33"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="31"/>
+      <c r="S33" s="31"/>
+      <c r="T33" s="31"/>
+      <c r="U33" s="31"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+      <c r="Z33" s="31"/>
+      <c r="AA33" s="31"/>
+      <c r="AB33" s="31"/>
+      <c r="AC33" s="31"/>
+      <c r="AD33" s="31"/>
+      <c r="AE33" s="31"/>
+      <c r="AF33" s="31"/>
+      <c r="AG33" s="31"/>
+      <c r="AH33" s="31"/>
+      <c r="AI33" s="31"/>
+      <c r="AJ33" s="31"/>
+      <c r="AK33" s="31"/>
+      <c r="AL33" s="31"/>
+      <c r="AM33" s="31"/>
+      <c r="AN33" s="31"/>
+      <c r="AO33" s="31"/>
+      <c r="AP33" s="31"/>
+      <c r="AQ33" s="31"/>
+    </row>
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="str">
         <v>Baseline</v>
       </c>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
-      <c r="L34" s="32"/>
-      <c r="M34" s="32"/>
-      <c r="N34" s="32"/>
-      <c r="O34" s="32"/>
-      <c r="Q34" s="30"/>
-      <c r="R34" s="30"/>
-      <c r="S34" s="30"/>
-      <c r="T34" s="30"/>
-      <c r="U34" s="30"/>
-      <c r="V34" s="30"/>
-      <c r="W34" s="30"/>
-      <c r="X34" s="30"/>
-      <c r="Y34" s="30"/>
-      <c r="Z34" s="30"/>
-      <c r="AA34" s="30"/>
-      <c r="AB34" s="30"/>
-      <c r="AC34" s="30"/>
-      <c r="AD34" s="30"/>
-      <c r="AE34" s="30"/>
-      <c r="AF34" s="30"/>
-      <c r="AG34" s="30"/>
-      <c r="AH34" s="30"/>
-      <c r="AI34" s="30"/>
-      <c r="AJ34" s="30"/>
-      <c r="AK34" s="30"/>
-      <c r="AL34" s="30"/>
-      <c r="AM34" s="30"/>
-      <c r="AN34" s="30"/>
-      <c r="AO34" s="30"/>
-      <c r="AP34" s="30"/>
-      <c r="AQ34" s="30"/>
-    </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="33"/>
+      <c r="M34" s="33"/>
+      <c r="N34" s="33"/>
+      <c r="O34" s="33"/>
+      <c r="Q34" s="31"/>
+      <c r="R34" s="31"/>
+      <c r="S34" s="31"/>
+      <c r="T34" s="31"/>
+      <c r="U34" s="31"/>
+      <c r="V34" s="31"/>
+      <c r="W34" s="31"/>
+      <c r="X34" s="31"/>
+      <c r="Y34" s="31"/>
+      <c r="Z34" s="31"/>
+      <c r="AA34" s="31"/>
+      <c r="AB34" s="31"/>
+      <c r="AC34" s="31"/>
+      <c r="AD34" s="31"/>
+      <c r="AE34" s="31"/>
+      <c r="AF34" s="31"/>
+      <c r="AG34" s="31"/>
+      <c r="AH34" s="31"/>
+      <c r="AI34" s="31"/>
+      <c r="AJ34" s="31"/>
+      <c r="AK34" s="31"/>
+      <c r="AL34" s="31"/>
+      <c r="AM34" s="31"/>
+      <c r="AN34" s="31"/>
+      <c r="AO34" s="31"/>
+      <c r="AP34" s="31"/>
+      <c r="AQ34" s="31"/>
+    </row>
+    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B35" s="28" t="str">
         <v>No_nonDLS_limExt</v>
       </c>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48" t="s">
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="46"/>
+      <c r="I35" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="J35" s="48"/>
-      <c r="K35" s="48"/>
-      <c r="L35" s="48"/>
-      <c r="M35" s="48"/>
-      <c r="N35" s="48"/>
-      <c r="O35" s="48"/>
-      <c r="Q35" s="30"/>
-      <c r="R35" s="30"/>
-      <c r="S35" s="30"/>
-      <c r="T35" s="30"/>
-      <c r="U35" s="30"/>
-      <c r="V35" s="30"/>
-      <c r="W35" s="30"/>
-      <c r="X35" s="30"/>
-      <c r="Y35" s="30"/>
-      <c r="Z35" s="30"/>
-      <c r="AA35" s="30"/>
-      <c r="AB35" s="30"/>
-      <c r="AC35" s="30"/>
-      <c r="AD35" s="30"/>
-      <c r="AE35" s="30"/>
-      <c r="AF35" s="30"/>
-      <c r="AG35" s="30"/>
-      <c r="AH35" s="30"/>
-      <c r="AI35" s="30"/>
-      <c r="AJ35" s="30"/>
-      <c r="AK35" s="30"/>
-      <c r="AL35" s="30"/>
-      <c r="AM35" s="30"/>
-      <c r="AN35" s="30"/>
-      <c r="AO35" s="30"/>
-      <c r="AP35" s="30"/>
-      <c r="AQ35" s="30"/>
-    </row>
-    <row r="36" spans="1:43" ht="76.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J35" s="46"/>
+      <c r="K35" s="46"/>
+      <c r="L35" s="46"/>
+      <c r="M35" s="46"/>
+      <c r="N35" s="46"/>
+      <c r="O35" s="46"/>
+      <c r="Q35" s="31"/>
+      <c r="R35" s="31"/>
+      <c r="S35" s="31"/>
+      <c r="T35" s="31"/>
+      <c r="U35" s="31"/>
+      <c r="V35" s="31"/>
+      <c r="W35" s="31"/>
+      <c r="X35" s="31"/>
+      <c r="Y35" s="31"/>
+      <c r="Z35" s="31"/>
+      <c r="AA35" s="31"/>
+      <c r="AB35" s="31"/>
+      <c r="AC35" s="31"/>
+      <c r="AD35" s="31"/>
+      <c r="AE35" s="31"/>
+      <c r="AF35" s="31"/>
+      <c r="AG35" s="31"/>
+      <c r="AH35" s="31"/>
+      <c r="AI35" s="31"/>
+      <c r="AJ35" s="31"/>
+      <c r="AK35" s="31"/>
+      <c r="AL35" s="31"/>
+      <c r="AM35" s="31"/>
+      <c r="AN35" s="31"/>
+      <c r="AO35" s="31"/>
+      <c r="AP35" s="31"/>
+      <c r="AQ35" s="31"/>
+    </row>
+    <row r="36" spans="1:43" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="6" t="str">
         <v>BHN</v>
       </c>
-      <c r="C36" s="36" t="s">
+      <c r="C36" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="32"/>
-      <c r="N36" s="32"/>
-      <c r="O36" s="32"/>
-      <c r="Q36" s="30"/>
-      <c r="R36" s="30"/>
-      <c r="S36" s="30"/>
-      <c r="T36" s="30"/>
-      <c r="U36" s="30"/>
-      <c r="V36" s="30"/>
-      <c r="W36" s="30"/>
-      <c r="X36" s="30"/>
-      <c r="Y36" s="30"/>
-      <c r="Z36" s="30"/>
-      <c r="AA36" s="30"/>
-      <c r="AB36" s="30"/>
-      <c r="AC36" s="30"/>
-      <c r="AD36" s="30"/>
-      <c r="AE36" s="30"/>
-      <c r="AF36" s="30"/>
-      <c r="AG36" s="30"/>
-      <c r="AH36" s="30"/>
-      <c r="AI36" s="30"/>
-      <c r="AJ36" s="30"/>
-      <c r="AK36" s="30"/>
-      <c r="AL36" s="30"/>
-      <c r="AM36" s="30"/>
-      <c r="AN36" s="30"/>
-      <c r="AO36" s="30"/>
-      <c r="AP36" s="30"/>
-      <c r="AQ36" s="30"/>
-    </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB37" s="30"/>
-      <c r="AC37" s="30"/>
-      <c r="AD37" s="30"/>
-      <c r="AE37" s="30"/>
-      <c r="AF37" s="30"/>
-      <c r="AG37" s="30"/>
-      <c r="AH37" s="30"/>
-      <c r="AI37" s="30"/>
-      <c r="AJ37" s="30"/>
-      <c r="AK37" s="30"/>
-      <c r="AL37" s="30"/>
-      <c r="AM37" s="30"/>
-      <c r="AN37" s="30"/>
-      <c r="AO37" s="30"/>
-      <c r="AP37" s="30"/>
-      <c r="AQ37" s="30"/>
-    </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB38" s="30"/>
-      <c r="AC38" s="30"/>
-      <c r="AD38" s="30"/>
-      <c r="AE38" s="30"/>
-      <c r="AF38" s="30"/>
-      <c r="AG38" s="30"/>
-      <c r="AH38" s="30"/>
-      <c r="AI38" s="30"/>
-      <c r="AJ38" s="30"/>
-      <c r="AK38" s="30"/>
-      <c r="AL38" s="30"/>
-      <c r="AM38" s="30"/>
-      <c r="AN38" s="30"/>
-      <c r="AO38" s="30"/>
-      <c r="AP38" s="30"/>
-      <c r="AQ38" s="30"/>
-    </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB39" s="30"/>
-      <c r="AC39" s="30"/>
-      <c r="AD39" s="30"/>
-      <c r="AE39" s="30"/>
-      <c r="AF39" s="30"/>
-      <c r="AG39" s="30"/>
-      <c r="AH39" s="30"/>
-      <c r="AI39" s="30"/>
-      <c r="AJ39" s="30"/>
-      <c r="AK39" s="30"/>
-      <c r="AL39" s="30"/>
-      <c r="AM39" s="30"/>
-      <c r="AN39" s="30"/>
-      <c r="AO39" s="30"/>
-      <c r="AP39" s="30"/>
-      <c r="AQ39" s="30"/>
-    </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB40" s="30"/>
-      <c r="AC40" s="30"/>
-      <c r="AD40" s="30"/>
-      <c r="AE40" s="30"/>
-      <c r="AF40" s="30"/>
-      <c r="AG40" s="30"/>
-      <c r="AH40" s="30"/>
-      <c r="AI40" s="30"/>
-      <c r="AJ40" s="30"/>
-      <c r="AK40" s="30"/>
-      <c r="AL40" s="30"/>
-      <c r="AM40" s="30"/>
-      <c r="AN40" s="30"/>
-      <c r="AO40" s="30"/>
-      <c r="AP40" s="30"/>
-      <c r="AQ40" s="30"/>
-    </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB41" s="30"/>
-      <c r="AC41" s="30"/>
-      <c r="AD41" s="30"/>
-      <c r="AE41" s="30"/>
-      <c r="AF41" s="30"/>
-      <c r="AG41" s="30"/>
-      <c r="AH41" s="30"/>
-      <c r="AI41" s="30"/>
-      <c r="AJ41" s="30"/>
-      <c r="AK41" s="30"/>
-      <c r="AL41" s="30"/>
-      <c r="AM41" s="30"/>
-      <c r="AN41" s="30"/>
-      <c r="AO41" s="30"/>
-      <c r="AP41" s="30"/>
-      <c r="AQ41" s="30"/>
-    </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB42" s="30" t="e" vm="8">
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="37"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="33"/>
+      <c r="N36" s="33"/>
+      <c r="O36" s="33"/>
+      <c r="Q36" s="31"/>
+      <c r="R36" s="31"/>
+      <c r="S36" s="31"/>
+      <c r="T36" s="31"/>
+      <c r="U36" s="31"/>
+      <c r="V36" s="31"/>
+      <c r="W36" s="31"/>
+      <c r="X36" s="31"/>
+      <c r="Y36" s="31"/>
+      <c r="Z36" s="31"/>
+      <c r="AA36" s="31"/>
+      <c r="AB36" s="31"/>
+      <c r="AC36" s="31"/>
+      <c r="AD36" s="31"/>
+      <c r="AE36" s="31"/>
+      <c r="AF36" s="31"/>
+      <c r="AG36" s="31"/>
+      <c r="AH36" s="31"/>
+      <c r="AI36" s="31"/>
+      <c r="AJ36" s="31"/>
+      <c r="AK36" s="31"/>
+      <c r="AL36" s="31"/>
+      <c r="AM36" s="31"/>
+      <c r="AN36" s="31"/>
+      <c r="AO36" s="31"/>
+      <c r="AP36" s="31"/>
+      <c r="AQ36" s="31"/>
+    </row>
+    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="B37" t="str">
+        <v>No_non_DLS_BHNFWB</v>
+      </c>
+      <c r="AB37" s="31"/>
+      <c r="AC37" s="31"/>
+      <c r="AD37" s="31"/>
+      <c r="AE37" s="31"/>
+      <c r="AF37" s="31"/>
+      <c r="AG37" s="31"/>
+      <c r="AH37" s="31"/>
+      <c r="AI37" s="31"/>
+      <c r="AJ37" s="31"/>
+      <c r="AK37" s="31"/>
+      <c r="AL37" s="31"/>
+      <c r="AM37" s="31"/>
+      <c r="AN37" s="31"/>
+      <c r="AO37" s="31"/>
+      <c r="AP37" s="31"/>
+      <c r="AQ37" s="31"/>
+    </row>
+    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB38" s="31"/>
+      <c r="AC38" s="31"/>
+      <c r="AD38" s="31"/>
+      <c r="AE38" s="31"/>
+      <c r="AF38" s="31"/>
+      <c r="AG38" s="31"/>
+      <c r="AH38" s="31"/>
+      <c r="AI38" s="31"/>
+      <c r="AJ38" s="31"/>
+      <c r="AK38" s="31"/>
+      <c r="AL38" s="31"/>
+      <c r="AM38" s="31"/>
+      <c r="AN38" s="31"/>
+      <c r="AO38" s="31"/>
+      <c r="AP38" s="31"/>
+      <c r="AQ38" s="31"/>
+    </row>
+    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB39" s="31"/>
+      <c r="AC39" s="31"/>
+      <c r="AD39" s="31"/>
+      <c r="AE39" s="31"/>
+      <c r="AF39" s="31"/>
+      <c r="AG39" s="31"/>
+      <c r="AH39" s="31"/>
+      <c r="AI39" s="31"/>
+      <c r="AJ39" s="31"/>
+      <c r="AK39" s="31"/>
+      <c r="AL39" s="31"/>
+      <c r="AM39" s="31"/>
+      <c r="AN39" s="31"/>
+      <c r="AO39" s="31"/>
+      <c r="AP39" s="31"/>
+      <c r="AQ39" s="31"/>
+    </row>
+    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB40" s="31"/>
+      <c r="AC40" s="31"/>
+      <c r="AD40" s="31"/>
+      <c r="AE40" s="31"/>
+      <c r="AF40" s="31"/>
+      <c r="AG40" s="31"/>
+      <c r="AH40" s="31"/>
+      <c r="AI40" s="31"/>
+      <c r="AJ40" s="31"/>
+      <c r="AK40" s="31"/>
+      <c r="AL40" s="31"/>
+      <c r="AM40" s="31"/>
+      <c r="AN40" s="31"/>
+      <c r="AO40" s="31"/>
+      <c r="AP40" s="31"/>
+      <c r="AQ40" s="31"/>
+    </row>
+    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB41" s="31"/>
+      <c r="AC41" s="31"/>
+      <c r="AD41" s="31"/>
+      <c r="AE41" s="31"/>
+      <c r="AF41" s="31"/>
+      <c r="AG41" s="31"/>
+      <c r="AH41" s="31"/>
+      <c r="AI41" s="31"/>
+      <c r="AJ41" s="31"/>
+      <c r="AK41" s="31"/>
+      <c r="AL41" s="31"/>
+      <c r="AM41" s="31"/>
+      <c r="AN41" s="31"/>
+      <c r="AO41" s="31"/>
+      <c r="AP41" s="31"/>
+      <c r="AQ41" s="31"/>
+    </row>
+    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB42" s="31" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-      <c r="AC42" s="30"/>
-      <c r="AD42" s="30"/>
-      <c r="AE42" s="30"/>
-      <c r="AF42" s="30"/>
-      <c r="AG42" s="30"/>
-      <c r="AH42" s="30"/>
-      <c r="AI42" s="30"/>
-      <c r="AJ42" s="30"/>
-      <c r="AK42" s="30"/>
-      <c r="AL42" s="30"/>
-      <c r="AM42" s="30"/>
-      <c r="AN42" s="30"/>
-      <c r="AO42" s="30"/>
-      <c r="AP42" s="30"/>
-      <c r="AQ42" s="30"/>
-    </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB43" s="30"/>
-      <c r="AC43" s="30"/>
-      <c r="AD43" s="30"/>
-      <c r="AE43" s="30"/>
-      <c r="AF43" s="30"/>
-      <c r="AG43" s="30"/>
-      <c r="AH43" s="30"/>
-      <c r="AI43" s="30"/>
-      <c r="AJ43" s="30"/>
-      <c r="AK43" s="30"/>
-      <c r="AL43" s="30"/>
-      <c r="AM43" s="30"/>
-      <c r="AN43" s="30"/>
-      <c r="AO43" s="30"/>
-      <c r="AP43" s="30"/>
-      <c r="AQ43" s="30"/>
-    </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB44" s="30"/>
-      <c r="AC44" s="30"/>
-      <c r="AD44" s="30"/>
-      <c r="AE44" s="30"/>
-      <c r="AF44" s="30"/>
-      <c r="AG44" s="30"/>
-      <c r="AH44" s="30"/>
-      <c r="AI44" s="30"/>
-      <c r="AJ44" s="30"/>
-      <c r="AK44" s="30"/>
-      <c r="AL44" s="30"/>
-      <c r="AM44" s="30"/>
-      <c r="AN44" s="30"/>
-      <c r="AO44" s="30"/>
-      <c r="AP44" s="30"/>
-      <c r="AQ44" s="30"/>
-    </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB45" s="30"/>
-      <c r="AC45" s="30"/>
-      <c r="AD45" s="30"/>
-      <c r="AE45" s="30"/>
-      <c r="AF45" s="30"/>
-      <c r="AG45" s="30"/>
-      <c r="AH45" s="30"/>
-      <c r="AI45" s="30"/>
-      <c r="AJ45" s="30"/>
-      <c r="AK45" s="30"/>
-      <c r="AL45" s="30"/>
-      <c r="AM45" s="30"/>
-      <c r="AN45" s="30"/>
-      <c r="AO45" s="30"/>
-      <c r="AP45" s="30"/>
-      <c r="AQ45" s="30"/>
-    </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB46" s="30"/>
-      <c r="AC46" s="30"/>
-      <c r="AD46" s="30"/>
-      <c r="AE46" s="30"/>
-      <c r="AF46" s="30"/>
-      <c r="AG46" s="30"/>
-      <c r="AH46" s="30"/>
-      <c r="AI46" s="30"/>
-      <c r="AJ46" s="30"/>
-      <c r="AK46" s="30"/>
-      <c r="AL46" s="30"/>
-      <c r="AM46" s="30"/>
-      <c r="AN46" s="30"/>
-      <c r="AO46" s="30"/>
-      <c r="AP46" s="30"/>
-      <c r="AQ46" s="30"/>
-    </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB47" s="30"/>
-      <c r="AC47" s="30"/>
-      <c r="AD47" s="30"/>
-      <c r="AE47" s="30"/>
-      <c r="AF47" s="30"/>
-      <c r="AG47" s="30"/>
-      <c r="AH47" s="30"/>
-      <c r="AI47" s="30"/>
-      <c r="AJ47" s="30"/>
-      <c r="AK47" s="30"/>
-      <c r="AL47" s="30"/>
-      <c r="AM47" s="30"/>
-      <c r="AN47" s="30"/>
-      <c r="AO47" s="30"/>
-      <c r="AP47" s="30"/>
-      <c r="AQ47" s="30"/>
-    </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB48" s="30"/>
-      <c r="AC48" s="30"/>
-      <c r="AD48" s="30"/>
-      <c r="AE48" s="30"/>
-      <c r="AF48" s="30"/>
-      <c r="AG48" s="30"/>
-      <c r="AH48" s="30"/>
-      <c r="AI48" s="30"/>
-      <c r="AJ48" s="30"/>
-      <c r="AK48" s="30"/>
-      <c r="AL48" s="30"/>
-      <c r="AM48" s="30"/>
-      <c r="AN48" s="30"/>
-      <c r="AO48" s="30"/>
-      <c r="AP48" s="30"/>
-      <c r="AQ48" s="30"/>
-    </row>
-    <row r="49" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB49" s="30"/>
-      <c r="AC49" s="30"/>
-      <c r="AD49" s="30"/>
-      <c r="AE49" s="30"/>
-      <c r="AF49" s="30"/>
-      <c r="AG49" s="30"/>
-      <c r="AH49" s="30"/>
-      <c r="AI49" s="30"/>
-      <c r="AJ49" s="30"/>
-      <c r="AK49" s="30"/>
-      <c r="AL49" s="30"/>
-      <c r="AM49" s="30"/>
-      <c r="AN49" s="30"/>
-      <c r="AO49" s="30"/>
-      <c r="AP49" s="30"/>
-      <c r="AQ49" s="30"/>
-    </row>
-    <row r="50" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB50" s="30"/>
-      <c r="AC50" s="30"/>
-      <c r="AD50" s="30"/>
-      <c r="AE50" s="30"/>
-      <c r="AF50" s="30"/>
-      <c r="AG50" s="30"/>
-      <c r="AH50" s="30"/>
-      <c r="AI50" s="30"/>
-      <c r="AJ50" s="30"/>
-      <c r="AK50" s="30"/>
-      <c r="AL50" s="30"/>
-      <c r="AM50" s="30"/>
-      <c r="AN50" s="30"/>
-      <c r="AO50" s="30"/>
-      <c r="AP50" s="30"/>
-      <c r="AQ50" s="30"/>
-    </row>
-    <row r="51" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB51" s="30"/>
-      <c r="AC51" s="30"/>
-      <c r="AD51" s="30"/>
-      <c r="AE51" s="30"/>
-      <c r="AF51" s="30"/>
-      <c r="AG51" s="30"/>
-      <c r="AH51" s="30"/>
-      <c r="AI51" s="30"/>
-      <c r="AJ51" s="30"/>
-      <c r="AK51" s="30"/>
-      <c r="AL51" s="30"/>
-      <c r="AM51" s="30"/>
-      <c r="AN51" s="30"/>
-      <c r="AO51" s="30"/>
-      <c r="AP51" s="30"/>
-      <c r="AQ51" s="30"/>
-    </row>
-    <row r="52" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB52" s="30"/>
-      <c r="AC52" s="30"/>
-      <c r="AD52" s="30"/>
-      <c r="AE52" s="30"/>
-      <c r="AF52" s="30"/>
-      <c r="AG52" s="30"/>
-      <c r="AH52" s="30"/>
-      <c r="AI52" s="30"/>
-      <c r="AJ52" s="30"/>
-      <c r="AK52" s="30"/>
-      <c r="AL52" s="30"/>
-      <c r="AM52" s="30"/>
-      <c r="AN52" s="30"/>
-      <c r="AO52" s="30"/>
-      <c r="AP52" s="30"/>
-      <c r="AQ52" s="30"/>
-    </row>
-    <row r="53" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB53" s="30"/>
-      <c r="AC53" s="30"/>
-      <c r="AD53" s="30"/>
-      <c r="AE53" s="30"/>
-      <c r="AF53" s="30"/>
-      <c r="AG53" s="30"/>
-      <c r="AH53" s="30"/>
-      <c r="AI53" s="30"/>
-      <c r="AJ53" s="30"/>
-      <c r="AK53" s="30"/>
-      <c r="AL53" s="30"/>
-      <c r="AM53" s="30"/>
-      <c r="AN53" s="30"/>
-      <c r="AO53" s="30"/>
-      <c r="AP53" s="30"/>
-      <c r="AQ53" s="30"/>
+      <c r="AC42" s="31"/>
+      <c r="AD42" s="31"/>
+      <c r="AE42" s="31"/>
+      <c r="AF42" s="31"/>
+      <c r="AG42" s="31"/>
+      <c r="AH42" s="31"/>
+      <c r="AI42" s="31"/>
+      <c r="AJ42" s="31"/>
+      <c r="AK42" s="31"/>
+      <c r="AL42" s="31"/>
+      <c r="AM42" s="31"/>
+      <c r="AN42" s="31"/>
+      <c r="AO42" s="31"/>
+      <c r="AP42" s="31"/>
+      <c r="AQ42" s="31"/>
+    </row>
+    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB43" s="31"/>
+      <c r="AC43" s="31"/>
+      <c r="AD43" s="31"/>
+      <c r="AE43" s="31"/>
+      <c r="AF43" s="31"/>
+      <c r="AG43" s="31"/>
+      <c r="AH43" s="31"/>
+      <c r="AI43" s="31"/>
+      <c r="AJ43" s="31"/>
+      <c r="AK43" s="31"/>
+      <c r="AL43" s="31"/>
+      <c r="AM43" s="31"/>
+      <c r="AN43" s="31"/>
+      <c r="AO43" s="31"/>
+      <c r="AP43" s="31"/>
+      <c r="AQ43" s="31"/>
+    </row>
+    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB44" s="31"/>
+      <c r="AC44" s="31"/>
+      <c r="AD44" s="31"/>
+      <c r="AE44" s="31"/>
+      <c r="AF44" s="31"/>
+      <c r="AG44" s="31"/>
+      <c r="AH44" s="31"/>
+      <c r="AI44" s="31"/>
+      <c r="AJ44" s="31"/>
+      <c r="AK44" s="31"/>
+      <c r="AL44" s="31"/>
+      <c r="AM44" s="31"/>
+      <c r="AN44" s="31"/>
+      <c r="AO44" s="31"/>
+      <c r="AP44" s="31"/>
+      <c r="AQ44" s="31"/>
+    </row>
+    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB45" s="31"/>
+      <c r="AC45" s="31"/>
+      <c r="AD45" s="31"/>
+      <c r="AE45" s="31"/>
+      <c r="AF45" s="31"/>
+      <c r="AG45" s="31"/>
+      <c r="AH45" s="31"/>
+      <c r="AI45" s="31"/>
+      <c r="AJ45" s="31"/>
+      <c r="AK45" s="31"/>
+      <c r="AL45" s="31"/>
+      <c r="AM45" s="31"/>
+      <c r="AN45" s="31"/>
+      <c r="AO45" s="31"/>
+      <c r="AP45" s="31"/>
+      <c r="AQ45" s="31"/>
+    </row>
+    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB46" s="31"/>
+      <c r="AC46" s="31"/>
+      <c r="AD46" s="31"/>
+      <c r="AE46" s="31"/>
+      <c r="AF46" s="31"/>
+      <c r="AG46" s="31"/>
+      <c r="AH46" s="31"/>
+      <c r="AI46" s="31"/>
+      <c r="AJ46" s="31"/>
+      <c r="AK46" s="31"/>
+      <c r="AL46" s="31"/>
+      <c r="AM46" s="31"/>
+      <c r="AN46" s="31"/>
+      <c r="AO46" s="31"/>
+      <c r="AP46" s="31"/>
+      <c r="AQ46" s="31"/>
+    </row>
+    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB47" s="31"/>
+      <c r="AC47" s="31"/>
+      <c r="AD47" s="31"/>
+      <c r="AE47" s="31"/>
+      <c r="AF47" s="31"/>
+      <c r="AG47" s="31"/>
+      <c r="AH47" s="31"/>
+      <c r="AI47" s="31"/>
+      <c r="AJ47" s="31"/>
+      <c r="AK47" s="31"/>
+      <c r="AL47" s="31"/>
+      <c r="AM47" s="31"/>
+      <c r="AN47" s="31"/>
+      <c r="AO47" s="31"/>
+      <c r="AP47" s="31"/>
+      <c r="AQ47" s="31"/>
+    </row>
+    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB48" s="31"/>
+      <c r="AC48" s="31"/>
+      <c r="AD48" s="31"/>
+      <c r="AE48" s="31"/>
+      <c r="AF48" s="31"/>
+      <c r="AG48" s="31"/>
+      <c r="AH48" s="31"/>
+      <c r="AI48" s="31"/>
+      <c r="AJ48" s="31"/>
+      <c r="AK48" s="31"/>
+      <c r="AL48" s="31"/>
+      <c r="AM48" s="31"/>
+      <c r="AN48" s="31"/>
+      <c r="AO48" s="31"/>
+      <c r="AP48" s="31"/>
+      <c r="AQ48" s="31"/>
+    </row>
+    <row r="49" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB49" s="31"/>
+      <c r="AC49" s="31"/>
+      <c r="AD49" s="31"/>
+      <c r="AE49" s="31"/>
+      <c r="AF49" s="31"/>
+      <c r="AG49" s="31"/>
+      <c r="AH49" s="31"/>
+      <c r="AI49" s="31"/>
+      <c r="AJ49" s="31"/>
+      <c r="AK49" s="31"/>
+      <c r="AL49" s="31"/>
+      <c r="AM49" s="31"/>
+      <c r="AN49" s="31"/>
+      <c r="AO49" s="31"/>
+      <c r="AP49" s="31"/>
+      <c r="AQ49" s="31"/>
+    </row>
+    <row r="50" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB50" s="31"/>
+      <c r="AC50" s="31"/>
+      <c r="AD50" s="31"/>
+      <c r="AE50" s="31"/>
+      <c r="AF50" s="31"/>
+      <c r="AG50" s="31"/>
+      <c r="AH50" s="31"/>
+      <c r="AI50" s="31"/>
+      <c r="AJ50" s="31"/>
+      <c r="AK50" s="31"/>
+      <c r="AL50" s="31"/>
+      <c r="AM50" s="31"/>
+      <c r="AN50" s="31"/>
+      <c r="AO50" s="31"/>
+      <c r="AP50" s="31"/>
+      <c r="AQ50" s="31"/>
+    </row>
+    <row r="51" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB51" s="31"/>
+      <c r="AC51" s="31"/>
+      <c r="AD51" s="31"/>
+      <c r="AE51" s="31"/>
+      <c r="AF51" s="31"/>
+      <c r="AG51" s="31"/>
+      <c r="AH51" s="31"/>
+      <c r="AI51" s="31"/>
+      <c r="AJ51" s="31"/>
+      <c r="AK51" s="31"/>
+      <c r="AL51" s="31"/>
+      <c r="AM51" s="31"/>
+      <c r="AN51" s="31"/>
+      <c r="AO51" s="31"/>
+      <c r="AP51" s="31"/>
+      <c r="AQ51" s="31"/>
+    </row>
+    <row r="52" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB52" s="31"/>
+      <c r="AC52" s="31"/>
+      <c r="AD52" s="31"/>
+      <c r="AE52" s="31"/>
+      <c r="AF52" s="31"/>
+      <c r="AG52" s="31"/>
+      <c r="AH52" s="31"/>
+      <c r="AI52" s="31"/>
+      <c r="AJ52" s="31"/>
+      <c r="AK52" s="31"/>
+      <c r="AL52" s="31"/>
+      <c r="AM52" s="31"/>
+      <c r="AN52" s="31"/>
+      <c r="AO52" s="31"/>
+      <c r="AP52" s="31"/>
+      <c r="AQ52" s="31"/>
+    </row>
+    <row r="53" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB53" s="31"/>
+      <c r="AC53" s="31"/>
+      <c r="AD53" s="31"/>
+      <c r="AE53" s="31"/>
+      <c r="AF53" s="31"/>
+      <c r="AG53" s="31"/>
+      <c r="AH53" s="31"/>
+      <c r="AI53" s="31"/>
+      <c r="AJ53" s="31"/>
+      <c r="AK53" s="31"/>
+      <c r="AL53" s="31"/>
+      <c r="AM53" s="31"/>
+      <c r="AN53" s="31"/>
+      <c r="AO53" s="31"/>
+      <c r="AP53" s="31"/>
+      <c r="AQ53" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="Q22:AA24"/>
-    <mergeCell ref="AB22:AQ31"/>
     <mergeCell ref="AB42:AQ53"/>
     <mergeCell ref="T4:X4"/>
     <mergeCell ref="AB32:AQ41"/>
+    <mergeCell ref="Q30:AA36"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="C29:H29"/>
+    <mergeCell ref="I29:O29"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="I30:O30"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="I31:O31"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="I32:O32"/>
     <mergeCell ref="C33:H33"/>
     <mergeCell ref="I33:O33"/>
     <mergeCell ref="C34:H34"/>
     <mergeCell ref="I34:O34"/>
     <mergeCell ref="C35:H35"/>
     <mergeCell ref="I35:O35"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="I36:O36"/>
-    <mergeCell ref="C29:H29"/>
-    <mergeCell ref="I29:O29"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="I30:O30"/>
-    <mergeCell ref="Q30:AA36"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="I31:O31"/>
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="I32:O32"/>
     <mergeCell ref="AR22:AY24"/>
     <mergeCell ref="C23:H23"/>
     <mergeCell ref="I23:O23"/>
     <mergeCell ref="C24:H24"/>
     <mergeCell ref="I24:O24"/>
+    <mergeCell ref="Q22:AA24"/>
+    <mergeCell ref="AB22:AQ31"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="I25:O25"/>
     <mergeCell ref="C26:H26"/>
@@ -5708,7 +5773,7 @@
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="I22:O22"/>
   </mergeCells>
-  <conditionalFormatting sqref="C5:Q15">
+  <conditionalFormatting sqref="C5:R15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -5722,22 +5787,22 @@
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R65"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="62.5546875" customWidth="1"/>
-    <col min="2" max="2" width="25.33203125" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" customWidth="1"/>
+    <col min="1" max="1" width="62.5703125" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" customWidth="1"/>
-    <col min="11" max="11" width="13.5546875" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -5789,8 +5854,11 @@
       <c r="Q1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="str" cm="1">
         <f t="array" ref="A2:A53">TRANSPOSE('[1]1990-2020 Time-series data'!$Y$2:$BX$2)</f>
         <v xml:space="preserve">Child stunting (% of pop.) </v>
@@ -5843,8 +5911,11 @@
       <c r="Q2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="str">
         <v>Deaths from infectious diseases (deaths/100,000)</v>
       </c>
@@ -5896,8 +5967,11 @@
       <c r="Q3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="str">
         <v xml:space="preserve">Maternal mortality  (deaths/100,000 live births) </v>
       </c>
@@ -5949,8 +6023,11 @@
       <c r="Q4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="str">
         <v xml:space="preserve">Nutritional deficiencies (% of pop.) </v>
       </c>
@@ -6002,8 +6079,11 @@
       <c r="Q5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="str">
         <v xml:space="preserve">Diet low in fruits and vegetables (0=low risk; 100=high risk) </v>
       </c>
@@ -6055,8 +6135,11 @@
       <c r="Q6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="str">
         <v xml:space="preserve">Child mortality (deaths/1,000 live births) </v>
       </c>
@@ -6108,8 +6191,11 @@
       <c r="Q7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="str">
         <v xml:space="preserve">No access to a handwashing facility (0=low risk; 100=high risk) </v>
       </c>
@@ -6161,8 +6247,11 @@
       <c r="Q8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="str">
         <v>Deaths from unsafe water, sanitation and hygiene (deaths/100,000)</v>
       </c>
@@ -6214,8 +6303,11 @@
       <c r="Q9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="str">
         <v xml:space="preserve">Improved sanitation (proportion of pop.) </v>
       </c>
@@ -6267,8 +6359,11 @@
       <c r="Q10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="str">
         <v xml:space="preserve">Improved water source (proportion of pop.) </v>
       </c>
@@ -6320,8 +6415,11 @@
       <c r="Q11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="str">
         <v>Deaths from household air pollution (deaths/100,000)</v>
       </c>
@@ -6373,8 +6471,11 @@
       <c r="Q12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="str">
         <v xml:space="preserve">Prevalence of cooking with coal/biomass (proportion of pop.) </v>
       </c>
@@ -6426,8 +6527,11 @@
       <c r="Q13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="str">
         <v xml:space="preserve">Access to electricity (% of pop.) </v>
       </c>
@@ -6479,8 +6583,11 @@
       <c r="Q14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="str">
         <v>Deaths from road injuries (deaths/100,000)</v>
       </c>
@@ -6532,8 +6639,11 @@
       <c r="Q15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="str">
         <v xml:space="preserve">Political violence (0=no violence; 4=violence often) </v>
       </c>
@@ -6585,8 +6695,11 @@
       <c r="Q16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="str">
         <v>Political killings and torture (0=low freedom; 1=high freedom)</v>
       </c>
@@ -6638,8 +6751,11 @@
       <c r="Q17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="str">
         <v xml:space="preserve">Intimate partner violence against women (% of women aged 15+) </v>
       </c>
@@ -6691,8 +6807,11 @@
       <c r="Q18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="str">
         <v>Interpersonal violence  (deaths/100,000)</v>
       </c>
@@ -6744,8 +6863,11 @@
       <c r="Q19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="str">
         <v xml:space="preserve">Population with no education (proportion of pop.) </v>
       </c>
@@ -6797,8 +6919,11 @@
       <c r="Q20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="str">
         <v xml:space="preserve">Gender parity in basic education (distance from parity) </v>
       </c>
@@ -6850,8 +6975,11 @@
       <c r="Q21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="str">
         <v xml:space="preserve">Equal access to quality education (0=unequal; 4=equal) </v>
       </c>
@@ -6903,8 +7031,11 @@
       <c r="Q22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="str">
         <v>Mean years of schooling (years)</v>
       </c>
@@ -6956,8 +7087,11 @@
       <c r="Q23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="str">
         <v>Alternative sources of information (0=low; 1=high)</v>
       </c>
@@ -7009,8 +7143,11 @@
       <c r="Q24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="str">
         <v xml:space="preserve">Internet users (% of pop.) </v>
       </c>
@@ -7062,8 +7199,11 @@
       <c r="Q25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="str">
         <v xml:space="preserve">Mobile and landline telephone subscriptions (subscriptions/100 people) </v>
       </c>
@@ -7115,8 +7255,11 @@
       <c r="Q26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="str">
         <v>Life expectancy at 60 (years)</v>
       </c>
@@ -7168,8 +7311,11 @@
       <c r="Q27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="str">
         <v>Premature deaths from non-communicable diseases (deaths/100,000)</v>
       </c>
@@ -7221,8 +7367,11 @@
       <c r="Q28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="str">
         <v xml:space="preserve">Equal access to quality healthcare (0=unequal; 4=equal) </v>
       </c>
@@ -7274,8 +7423,11 @@
       <c r="Q29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="str">
         <v xml:space="preserve">Universal health coverage (% of pop.) </v>
       </c>
@@ -7327,8 +7479,11 @@
       <c r="Q30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="str">
         <v>Deaths from outdoor air pollution (deaths/100,000)</v>
       </c>
@@ -7380,8 +7535,11 @@
       <c r="Q31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="str">
         <v>Particulate matter (2.5) pollution (mean annual exposure, µg/m3)</v>
       </c>
@@ -7433,8 +7591,11 @@
       <c r="Q32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="str">
         <v>Deaths from lead exposure (deaths/100,000)</v>
       </c>
@@ -7486,8 +7647,11 @@
       <c r="Q33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="str">
         <v>Species protection (0=low; 100=high)</v>
       </c>
@@ -7539,8 +7703,11 @@
       <c r="Q34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="str">
         <v xml:space="preserve">Freedom of religion (0=no freedom; 4=full freedom) </v>
       </c>
@@ -7592,8 +7759,11 @@
       <c r="Q35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="str">
         <v xml:space="preserve">Property rights for women (0=no rights; 5=full rights) </v>
       </c>
@@ -7645,8 +7815,11 @@
       <c r="Q36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="str">
         <v xml:space="preserve">Freedom of assembly (0=no freedom; 4=full freedom) </v>
       </c>
@@ -7698,8 +7871,11 @@
       <c r="Q37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="str">
         <v>Access to justice (0=nonexistent; 1=observed)</v>
       </c>
@@ -7751,8 +7927,11 @@
       <c r="Q38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="str">
         <v>Freedom of discussion (0=low; 1=high)</v>
       </c>
@@ -7804,8 +7983,11 @@
       <c r="Q39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="str">
         <v>Political rights (1=full rights; 7=no rights)</v>
       </c>
@@ -7857,8 +8039,11 @@
       <c r="Q40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="str">
         <v>Public sector corruption (0=low corruption; 1=high corruption)</v>
       </c>
@@ -7910,8 +8095,11 @@
       <c r="Q41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="str">
         <v>Freedom of domestic movement (0=low; 1=high)</v>
       </c>
@@ -7963,8 +8151,11 @@
       <c r="Q42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="str">
         <v>Satisfied demand for contraception (% satisfied demand)</v>
       </c>
@@ -8016,8 +8207,11 @@
       <c r="Q43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="str">
         <v>Early marriage (% of married women aged 15-19)</v>
       </c>
@@ -8069,8 +8263,11 @@
       <c r="Q44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="str">
         <v xml:space="preserve">Vulnerable employment (% of total employment) </v>
       </c>
@@ -8122,8 +8319,11 @@
       <c r="Q45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="str">
         <v>Equal protection of social groups (0=low; 1=high)</v>
       </c>
@@ -8175,8 +8375,11 @@
       <c r="Q46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="str">
         <v>Equal access to power (0=low; 1=high)</v>
       </c>
@@ -8228,8 +8431,11 @@
       <c r="Q47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="str">
         <v xml:space="preserve">Power distributed by sexual orientation (0=extremely unequal; 3=equal) </v>
       </c>
@@ -8281,8 +8487,11 @@
       <c r="Q48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="str">
         <v xml:space="preserve">Access to public services distributed by social group (0=extremely unequal; 4=equal) </v>
       </c>
@@ -8334,8 +8543,11 @@
       <c r="Q49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="str">
         <v xml:space="preserve">Population with advanced education (proportion of pop.) </v>
       </c>
@@ -8387,8 +8599,11 @@
       <c r="Q50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="str">
         <v xml:space="preserve">Gender parity in advanced education (distance from parity) </v>
       </c>
@@ -8440,8 +8655,11 @@
       <c r="Q51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="str">
         <v>Respect for academic freedom (0=low; 1=high)</v>
       </c>
@@ -8493,8 +8711,11 @@
       <c r="Q52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="str">
         <v>Years of tertiary schooling (years)</v>
       </c>
@@ -8546,8 +8767,11 @@
       <c r="Q53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>2</v>
       </c>
@@ -8599,8 +8823,11 @@
       <c r="Q54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>3</v>
       </c>
@@ -8652,8 +8879,11 @@
       <c r="Q55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -8705,8 +8935,11 @@
       <c r="Q56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -8758,8 +8991,11 @@
       <c r="Q57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -8811,8 +9047,11 @@
       <c r="Q58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -8864,8 +9103,11 @@
       <c r="Q59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -8917,8 +9159,11 @@
       <c r="Q60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -8970,8 +9215,11 @@
       <c r="Q61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -9023,8 +9271,11 @@
       <c r="Q62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -9076,8 +9327,11 @@
       <c r="Q63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>12</v>
       </c>
@@ -9129,8 +9383,11 @@
       <c r="Q64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="R64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>27</v>
       </c>
@@ -9146,13 +9403,13 @@
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A3:D67"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="61.6640625" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" customWidth="1"/>
+    <col min="2" max="2" width="61.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -9163,7 +9420,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -9175,7 +9432,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="str">
         <v>Deaths from infectious diseases (deaths/100,000)</v>
       </c>
@@ -9183,7 +9440,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="str">
         <v xml:space="preserve">Maternal mortality  (deaths/100,000 live births) </v>
       </c>
@@ -9191,7 +9448,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="str">
         <v xml:space="preserve">Nutritional deficiencies (% of pop.) </v>
       </c>
@@ -9199,7 +9456,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="str">
         <v xml:space="preserve">Diet low in fruits and vegetables (0=low risk; 100=high risk) </v>
       </c>
@@ -9207,7 +9464,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="str">
         <v xml:space="preserve">Child mortality (deaths/1,000 live births) </v>
       </c>
@@ -9215,7 +9472,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="str">
         <v xml:space="preserve">No access to a handwashing facility (0=low risk; 100=high risk) </v>
       </c>
@@ -9223,7 +9480,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="str">
         <v>Deaths from unsafe water, sanitation and hygiene (deaths/100,000)</v>
       </c>
@@ -9231,7 +9488,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="str">
         <v xml:space="preserve">Improved sanitation (proportion of pop.) </v>
       </c>
@@ -9239,7 +9496,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="str">
         <v xml:space="preserve">Improved water source (proportion of pop.) </v>
       </c>
@@ -9247,7 +9504,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -9258,7 +9515,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="str">
         <v xml:space="preserve">Prevalence of cooking with coal/biomass (proportion of pop.) </v>
       </c>
@@ -9266,7 +9523,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="str">
         <v xml:space="preserve">Access to electricity (% of pop.) </v>
       </c>
@@ -9274,7 +9531,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="str">
         <v>Deaths from road injuries (deaths/100,000)</v>
       </c>
@@ -9282,7 +9539,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="str">
         <v xml:space="preserve">Political violence (0=no violence; 4=violence often) </v>
       </c>
@@ -9290,7 +9547,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="str">
         <v>Political killings and torture (0=low freedom; 1=high freedom)</v>
       </c>
@@ -9298,7 +9555,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="str">
         <v xml:space="preserve">Intimate partner violence against women (% of women aged 15+) </v>
       </c>
@@ -9306,7 +9563,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="str">
         <v>Interpersonal violence  (deaths/100,000)</v>
       </c>
@@ -9314,7 +9571,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="str">
         <v xml:space="preserve">Population with no education (proportion of pop.) </v>
       </c>
@@ -9322,7 +9579,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="str">
         <v xml:space="preserve">Gender parity in basic education (distance from parity) </v>
       </c>
@@ -9330,7 +9587,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="str">
         <v xml:space="preserve">Equal access to quality education (0=unequal; 4=equal) </v>
       </c>
@@ -9338,7 +9595,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="str">
         <v>Mean years of schooling (years)</v>
       </c>
@@ -9346,7 +9603,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="str">
         <v>Alternative sources of information (0=low; 1=high)</v>
       </c>
@@ -9354,7 +9611,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="str">
         <v xml:space="preserve">Internet users (% of pop.) </v>
       </c>
@@ -9362,7 +9619,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="str">
         <v xml:space="preserve">Mobile and landline telephone subscriptions (subscriptions/100 people) </v>
       </c>
@@ -9370,7 +9627,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="str">
         <v>Life expectancy at 60 (years)</v>
       </c>
@@ -9378,7 +9635,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="str">
         <v>Premature deaths from non-communicable diseases (deaths/100,000)</v>
       </c>
@@ -9386,7 +9643,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="str">
         <v xml:space="preserve">Equal access to quality healthcare (0=unequal; 4=equal) </v>
       </c>
@@ -9394,7 +9651,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="str">
         <v xml:space="preserve">Universal health coverage (% of pop.) </v>
       </c>
@@ -9402,7 +9659,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="str">
         <v>Deaths from outdoor air pollution (deaths/100,000)</v>
       </c>
@@ -9410,7 +9667,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="str">
         <v>Particulate matter (2.5) pollution (mean annual exposure, µg/m3)</v>
       </c>
@@ -9418,7 +9675,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="str">
         <v>Deaths from lead exposure (deaths/100,000)</v>
       </c>
@@ -9426,7 +9683,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="str">
         <v>Species protection (0=low; 100=high)</v>
       </c>
@@ -9434,7 +9691,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -9445,7 +9702,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B38" s="4" t="str">
         <v xml:space="preserve">Property rights for women (0=no rights; 5=full rights) </v>
       </c>
@@ -9453,7 +9710,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B39" s="4" t="str">
         <v xml:space="preserve">Freedom of assembly (0=no freedom; 4=full freedom) </v>
       </c>
@@ -9461,7 +9718,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="str">
         <v>Access to justice (0=nonexistent; 1=observed)</v>
       </c>
@@ -9469,7 +9726,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B41" s="4" t="str">
         <v>Freedom of discussion (0=low; 1=high)</v>
       </c>
@@ -9477,7 +9734,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B42" s="4" t="str">
         <v>Political rights (1=full rights; 7=no rights)</v>
       </c>
@@ -9485,7 +9742,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B43" s="4" t="str">
         <v>Public sector corruption (0=low corruption; 1=high corruption)</v>
       </c>
@@ -9493,7 +9750,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B44" s="4" t="str">
         <v>Freedom of domestic movement (0=low; 1=high)</v>
       </c>
@@ -9501,7 +9758,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="str">
         <v>Satisfied demand for contraception (% satisfied demand)</v>
       </c>
@@ -9509,7 +9766,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B46" s="4" t="str">
         <v>Early marriage (% of married women aged 15-19)</v>
       </c>
@@ -9517,7 +9774,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B47" s="4" t="str">
         <v xml:space="preserve">Vulnerable employment (% of total employment) </v>
       </c>
@@ -9525,7 +9782,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B48" s="4" t="str">
         <v>Equal protection of social groups (0=low; 1=high)</v>
       </c>
@@ -9533,7 +9790,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B49" s="4" t="str">
         <v>Equal access to power (0=low; 1=high)</v>
       </c>
@@ -9541,7 +9798,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B50" s="4" t="str">
         <v xml:space="preserve">Power distributed by sexual orientation (0=extremely unequal; 3=equal) </v>
       </c>
@@ -9549,7 +9806,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="str">
         <v xml:space="preserve">Access to public services distributed by social group (0=extremely unequal; 4=equal) </v>
       </c>
@@ -9557,7 +9814,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B52" s="4" t="str">
         <v xml:space="preserve">Population with advanced education (proportion of pop.) </v>
       </c>
@@ -9565,7 +9822,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="str">
         <v xml:space="preserve">Gender parity in advanced education (distance from parity) </v>
       </c>
@@ -9573,7 +9830,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B54" s="4" t="str">
         <v>Respect for academic freedom (0=low; 1=high)</v>
       </c>
@@ -9581,7 +9838,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B55" s="4" t="str">
         <v>Years of tertiary schooling (years)</v>
       </c>
@@ -9589,7 +9846,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>1</v>
       </c>
@@ -9600,7 +9857,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>3</v>
       </c>
@@ -9608,7 +9865,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>4</v>
       </c>
@@ -9616,7 +9873,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>5</v>
       </c>
@@ -9624,7 +9881,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>7</v>
       </c>
@@ -9632,7 +9889,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>6</v>
       </c>
@@ -9640,7 +9897,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>8</v>
       </c>
@@ -9648,7 +9905,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>9</v>
       </c>
@@ -9656,7 +9913,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>10</v>
       </c>
@@ -9664,7 +9921,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>11</v>
       </c>
@@ -9672,7 +9929,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>12</v>
       </c>
@@ -9680,7 +9937,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
         <v>27</v>
       </c>

--- a/IndicatorsForClusters.xlsx
+++ b/IndicatorsForClusters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1c3256d208fb6548/Personlig/Aske Banke Consultancy/YALE/Metodeartikel_WorldDevelopmentJournal/WorldDevelopmentArticleGit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="461" documentId="8_{9856C943-DD01-465B-AD17-0E409E296684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC628B2D-6AED-4B73-AE36-E8ED2E2600B0}"/>
+  <xr:revisionPtr revIDLastSave="476" documentId="8_{9856C943-DD01-465B-AD17-0E409E296684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D884123-63F0-48D2-9055-F60C3EFE3D6D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{726B2859-724A-4801-8E74-5A4E1AFAB973}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{726B2859-724A-4801-8E74-5A4E1AFAB973}"/>
   </bookViews>
   <sheets>
     <sheet name="Unscaled Experiments" sheetId="2" r:id="rId1"/>
@@ -169,7 +169,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="80">
   <si>
     <t>SPI</t>
   </si>
@@ -291,9 +291,6 @@
     <t>Few_indicators_closest_DLS_coverage</t>
   </si>
   <si>
-    <t>Few indicators_SPI_preferred</t>
-  </si>
-  <si>
     <t>Before run</t>
   </si>
   <si>
@@ -353,9 +350,6 @@
     <t>Results</t>
   </si>
   <si>
-    <t>Few indicators_SPI_preferred_90</t>
-  </si>
-  <si>
     <t>Few_indicators_closest_DLS_coverage_90</t>
   </si>
   <si>
@@ -411,6 +405,15 @@
   <si>
     <t>No_non_DLS_BHNFWB</t>
   </si>
+  <si>
+    <t>All_indicators</t>
+  </si>
+  <si>
+    <t>Few_indicators_SPI_preferred_90</t>
+  </si>
+  <si>
+    <t>Few_indicators_SPI_preferred</t>
+  </si>
 </sst>
 </file>
 
@@ -453,7 +456,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -493,6 +496,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,7 +587,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -623,6 +632,7 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1324,49 +1334,49 @@
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AY53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.28515625" customWidth="1"/>
+    <col min="2" max="2" width="35.33203125" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
-    <col min="5" max="16" width="4.28515625" customWidth="1"/>
-    <col min="19" max="19" width="8.85546875" customWidth="1"/>
+    <col min="5" max="16" width="4.33203125" customWidth="1"/>
+    <col min="19" max="19" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="42"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="J3" s="43"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
       <c r="T3" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U3" s="22"/>
       <c r="V3" s="22"/>
       <c r="W3" s="22"/>
       <c r="X3" s="22"/>
     </row>
-    <row r="4" spans="1:24" ht="221.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="221.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="15" t="s">
         <v>16</v>
       </c>
@@ -1381,7 +1391,7 @@
         <v>Few_indicators_closest_DLS_coverage</v>
       </c>
       <c r="F4" s="9" t="str">
-        <v>Few indicators_SPI_preferred</v>
+        <v>Few_indicators_SPI_preferred</v>
       </c>
       <c r="G4" s="9" t="str">
         <v>No_non_DLS</v>
@@ -1393,7 +1403,7 @@
         <v>Few_indicators_closest_DLS_coverage_90</v>
       </c>
       <c r="J4" s="9" t="str">
-        <v>Few indicators_SPI_preferred_90</v>
+        <v>Few_indicators_SPI_preferred_90</v>
       </c>
       <c r="K4" s="9" t="str">
         <v>Few_indicators_closeDLS_subPrimSchool</v>
@@ -1416,15 +1426,15 @@
       <c r="Q4" s="9" t="str">
         <v>BHN</v>
       </c>
-      <c r="T4" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="U4" s="30"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="30"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="T4" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="str" cm="1">
         <f t="array" ref="B5:B15">_xlfn.UNIQUE('Overview of indicators and DLS'!C4:C67)</f>
         <v>Food &amp; Nutrition</v>
@@ -1490,10 +1500,10 @@
         <v>3</v>
       </c>
       <c r="R5" s="16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="str">
         <v>Health Care</v>
       </c>
@@ -1558,7 +1568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="str">
         <v>Water</v>
       </c>
@@ -1623,7 +1633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="11" t="str">
         <v>Sanitation</v>
       </c>
@@ -1688,7 +1698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="11" t="str">
         <v>Food preparation</v>
       </c>
@@ -1698,7 +1708,7 @@
       </c>
       <c r="D9" s="8" cm="1">
         <f t="array" ref="D9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!D$2:D$64=1))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="8" cm="1">
         <f t="array" ref="E9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!E$2:E$64=1))</f>
@@ -1710,7 +1720,7 @@
       </c>
       <c r="G9" s="8" cm="1">
         <f t="array" ref="G9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!G$2:G$64=1))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" s="8" cm="1">
         <f t="array" ref="H9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!H$2:H$64=1))</f>
@@ -1730,7 +1740,7 @@
       </c>
       <c r="L9" s="8" cm="1">
         <f t="array" ref="L9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!L$2:L$64=1))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M9" s="8" cm="1">
         <f t="array" ref="M9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!M$2:M$64=1))</f>
@@ -1753,7 +1763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B10" s="11" t="str">
         <v>Thermal comfort</v>
       </c>
@@ -1818,7 +1828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B11" s="11" t="str">
         <v>Non material / Non-DLS</v>
       </c>
@@ -1883,7 +1893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="str">
         <v>Education</v>
       </c>
@@ -1948,7 +1958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="str">
         <v>Social connectedness</v>
       </c>
@@ -2013,7 +2023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="str">
         <v>Housing</v>
       </c>
@@ -2078,7 +2088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="str">
         <v>Physical Connectedness</v>
       </c>
@@ -2143,10 +2153,10 @@
         <v>0</v>
       </c>
       <c r="R15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="11"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
@@ -2164,7 +2174,7 @@
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.3">
       <c r="B17" s="15" t="s">
         <v>33</v>
       </c>
@@ -2174,7 +2184,7 @@
       </c>
       <c r="D17" s="14">
         <f>SUM(D5:D15)</f>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E17" s="14">
         <f t="shared" ref="E17:H17" si="0">SUM(E5:E15)</f>
@@ -2186,7 +2196,7 @@
       </c>
       <c r="G17" s="14">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H17" s="14">
         <f t="shared" si="0"/>
@@ -2206,7 +2216,7 @@
       </c>
       <c r="L17" s="14">
         <f t="shared" si="1"/>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M17" s="14">
         <f t="shared" si="1"/>
@@ -2229,7 +2239,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.3">
       <c r="B18" s="11" t="s">
         <v>34</v>
       </c>
@@ -2294,7 +2304,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.3">
       <c r="B19" s="11" t="s">
         <v>35</v>
       </c>
@@ -2304,7 +2314,7 @@
       </c>
       <c r="D19" s="8">
         <f>SUM(Experiments!D54:D64)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" s="8">
         <f>SUM(Experiments!E54:E64)</f>
@@ -2316,7 +2326,7 @@
       </c>
       <c r="G19" s="8">
         <f>SUM(Experiments!G54:G64)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H19" s="8">
         <f>SUM(Experiments!H54:H64)</f>
@@ -2336,7 +2346,7 @@
       </c>
       <c r="L19" s="8">
         <f>SUM(Experiments!L54:L64)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M19" s="8">
         <f>SUM(Experiments!M54:M64)</f>
@@ -2359,38 +2369,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="43"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="43"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="44"/>
       <c r="Q21" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AR21" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:51" ht="90.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:51" ht="90.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1</v>
       </c>
@@ -2398,1083 +2408,1083 @@
         <f t="array" ref="B22:B36">TRANSPOSE(_xlfn.ANCHORARRAY(C4))</f>
         <v>BHN_FWB</v>
       </c>
-      <c r="C22" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="38"/>
-      <c r="Q22" s="31" t="e" vm="1">
+      <c r="C22" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="39"/>
+      <c r="Q22" s="32" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31"/>
-      <c r="T22" s="31"/>
-      <c r="U22" s="31"/>
-      <c r="V22" s="31"/>
-      <c r="W22" s="31"/>
-      <c r="X22" s="31"/>
-      <c r="Y22" s="31"/>
-      <c r="Z22" s="31"/>
-      <c r="AA22" s="31"/>
-      <c r="AB22" s="31" t="e" vm="2">
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="32"/>
+      <c r="U22" s="32"/>
+      <c r="V22" s="32"/>
+      <c r="W22" s="32"/>
+      <c r="X22" s="32"/>
+      <c r="Y22" s="32"/>
+      <c r="Z22" s="32"/>
+      <c r="AA22" s="32"/>
+      <c r="AB22" s="32" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="AC22" s="31"/>
-      <c r="AD22" s="31"/>
-      <c r="AE22" s="31"/>
-      <c r="AF22" s="31"/>
-      <c r="AG22" s="31"/>
-      <c r="AH22" s="31"/>
-      <c r="AI22" s="31"/>
-      <c r="AJ22" s="31"/>
-      <c r="AK22" s="31"/>
-      <c r="AL22" s="31"/>
-      <c r="AM22" s="31"/>
-      <c r="AN22" s="31"/>
-      <c r="AO22" s="31"/>
-      <c r="AP22" s="31"/>
-      <c r="AQ22" s="31"/>
-      <c r="AR22" s="31" t="e" vm="3">
+      <c r="AC22" s="32"/>
+      <c r="AD22" s="32"/>
+      <c r="AE22" s="32"/>
+      <c r="AF22" s="32"/>
+      <c r="AG22" s="32"/>
+      <c r="AH22" s="32"/>
+      <c r="AI22" s="32"/>
+      <c r="AJ22" s="32"/>
+      <c r="AK22" s="32"/>
+      <c r="AL22" s="32"/>
+      <c r="AM22" s="32"/>
+      <c r="AN22" s="32"/>
+      <c r="AO22" s="32"/>
+      <c r="AP22" s="32"/>
+      <c r="AQ22" s="32"/>
+      <c r="AR22" s="32" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="AS22" s="31"/>
-      <c r="AT22" s="31"/>
-      <c r="AU22" s="31"/>
-      <c r="AV22" s="31"/>
-      <c r="AW22" s="31"/>
-      <c r="AX22" s="31"/>
-      <c r="AY22" s="31"/>
-    </row>
-    <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AS22" s="32"/>
+      <c r="AT22" s="32"/>
+      <c r="AU22" s="32"/>
+      <c r="AV22" s="32"/>
+      <c r="AW22" s="32"/>
+      <c r="AX22" s="32"/>
+      <c r="AY22" s="32"/>
+    </row>
+    <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23" s="7" t="str">
         <v>BHN_FWB_AllExt</v>
       </c>
-      <c r="C23" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="38"/>
-      <c r="Q23" s="31"/>
-      <c r="R23" s="31"/>
-      <c r="S23" s="31"/>
-      <c r="T23" s="31"/>
-      <c r="U23" s="31"/>
-      <c r="V23" s="31"/>
-      <c r="W23" s="31"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="31"/>
-      <c r="Z23" s="31"/>
-      <c r="AA23" s="31"/>
-      <c r="AB23" s="31"/>
-      <c r="AC23" s="31"/>
-      <c r="AD23" s="31"/>
-      <c r="AE23" s="31"/>
-      <c r="AF23" s="31"/>
-      <c r="AG23" s="31"/>
-      <c r="AH23" s="31"/>
-      <c r="AI23" s="31"/>
-      <c r="AJ23" s="31"/>
-      <c r="AK23" s="31"/>
-      <c r="AL23" s="31"/>
-      <c r="AM23" s="31"/>
-      <c r="AN23" s="31"/>
-      <c r="AO23" s="31"/>
-      <c r="AP23" s="31"/>
-      <c r="AQ23" s="31"/>
-      <c r="AR23" s="31"/>
-      <c r="AS23" s="31"/>
-      <c r="AT23" s="31"/>
-      <c r="AU23" s="31"/>
-      <c r="AV23" s="31"/>
-      <c r="AW23" s="31"/>
-      <c r="AX23" s="31"/>
-      <c r="AY23" s="31"/>
-    </row>
-    <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="39"/>
+      <c r="Q23" s="32"/>
+      <c r="R23" s="32"/>
+      <c r="S23" s="32"/>
+      <c r="T23" s="32"/>
+      <c r="U23" s="32"/>
+      <c r="V23" s="32"/>
+      <c r="W23" s="32"/>
+      <c r="X23" s="32"/>
+      <c r="Y23" s="32"/>
+      <c r="Z23" s="32"/>
+      <c r="AA23" s="32"/>
+      <c r="AB23" s="32"/>
+      <c r="AC23" s="32"/>
+      <c r="AD23" s="32"/>
+      <c r="AE23" s="32"/>
+      <c r="AF23" s="32"/>
+      <c r="AG23" s="32"/>
+      <c r="AH23" s="32"/>
+      <c r="AI23" s="32"/>
+      <c r="AJ23" s="32"/>
+      <c r="AK23" s="32"/>
+      <c r="AL23" s="32"/>
+      <c r="AM23" s="32"/>
+      <c r="AN23" s="32"/>
+      <c r="AO23" s="32"/>
+      <c r="AP23" s="32"/>
+      <c r="AQ23" s="32"/>
+      <c r="AR23" s="32"/>
+      <c r="AS23" s="32"/>
+      <c r="AT23" s="32"/>
+      <c r="AU23" s="32"/>
+      <c r="AV23" s="32"/>
+      <c r="AW23" s="32"/>
+      <c r="AX23" s="32"/>
+      <c r="AY23" s="32"/>
+    </row>
+    <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24" s="7" t="str">
         <v>Few_indicators_closest_DLS_coverage</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="Q24" s="32"/>
+      <c r="R24" s="32"/>
+      <c r="S24" s="32"/>
+      <c r="T24" s="32"/>
+      <c r="U24" s="32"/>
+      <c r="V24" s="32"/>
+      <c r="W24" s="32"/>
+      <c r="X24" s="32"/>
+      <c r="Y24" s="32"/>
+      <c r="Z24" s="32"/>
+      <c r="AA24" s="32"/>
+      <c r="AB24" s="32"/>
+      <c r="AC24" s="32"/>
+      <c r="AD24" s="32"/>
+      <c r="AE24" s="32"/>
+      <c r="AF24" s="32"/>
+      <c r="AG24" s="32"/>
+      <c r="AH24" s="32"/>
+      <c r="AI24" s="32"/>
+      <c r="AJ24" s="32"/>
+      <c r="AK24" s="32"/>
+      <c r="AL24" s="32"/>
+      <c r="AM24" s="32"/>
+      <c r="AN24" s="32"/>
+      <c r="AO24" s="32"/>
+      <c r="AP24" s="32"/>
+      <c r="AQ24" s="32"/>
+      <c r="AR24" s="32"/>
+      <c r="AS24" s="32"/>
+      <c r="AT24" s="32"/>
+      <c r="AU24" s="32"/>
+      <c r="AV24" s="32"/>
+      <c r="AW24" s="32"/>
+      <c r="AX24" s="32"/>
+      <c r="AY24" s="32"/>
+    </row>
+    <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25" s="7" t="str">
+        <v>Few_indicators_SPI_preferred</v>
+      </c>
+      <c r="C25" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="38"/>
-      <c r="Q24" s="31"/>
-      <c r="R24" s="31"/>
-      <c r="S24" s="31"/>
-      <c r="T24" s="31"/>
-      <c r="U24" s="31"/>
-      <c r="V24" s="31"/>
-      <c r="W24" s="31"/>
-      <c r="X24" s="31"/>
-      <c r="Y24" s="31"/>
-      <c r="Z24" s="31"/>
-      <c r="AA24" s="31"/>
-      <c r="AB24" s="31"/>
-      <c r="AC24" s="31"/>
-      <c r="AD24" s="31"/>
-      <c r="AE24" s="31"/>
-      <c r="AF24" s="31"/>
-      <c r="AG24" s="31"/>
-      <c r="AH24" s="31"/>
-      <c r="AI24" s="31"/>
-      <c r="AJ24" s="31"/>
-      <c r="AK24" s="31"/>
-      <c r="AL24" s="31"/>
-      <c r="AM24" s="31"/>
-      <c r="AN24" s="31"/>
-      <c r="AO24" s="31"/>
-      <c r="AP24" s="31"/>
-      <c r="AQ24" s="31"/>
-      <c r="AR24" s="31"/>
-      <c r="AS24" s="31"/>
-      <c r="AT24" s="31"/>
-      <c r="AU24" s="31"/>
-      <c r="AV24" s="31"/>
-      <c r="AW24" s="31"/>
-      <c r="AX24" s="31"/>
-      <c r="AY24" s="31"/>
-    </row>
-    <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>1</v>
-      </c>
-      <c r="B25" s="7" t="str">
-        <v>Few indicators_SPI_preferred</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="38"/>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="38"/>
-      <c r="Q25" s="31"/>
-      <c r="R25" s="31"/>
-      <c r="S25" s="31"/>
-      <c r="T25" s="31"/>
-      <c r="U25" s="31"/>
-      <c r="V25" s="31"/>
-      <c r="W25" s="31"/>
-      <c r="X25" s="31"/>
-      <c r="Y25" s="31"/>
-      <c r="Z25" s="31"/>
-      <c r="AA25" s="31"/>
-      <c r="AB25" s="31"/>
-      <c r="AC25" s="31"/>
-      <c r="AD25" s="31"/>
-      <c r="AE25" s="31"/>
-      <c r="AF25" s="31"/>
-      <c r="AG25" s="31"/>
-      <c r="AH25" s="31"/>
-      <c r="AI25" s="31"/>
-      <c r="AJ25" s="31"/>
-      <c r="AK25" s="31"/>
-      <c r="AL25" s="31"/>
-      <c r="AM25" s="31"/>
-      <c r="AN25" s="31"/>
-      <c r="AO25" s="31"/>
-      <c r="AP25" s="31"/>
-      <c r="AQ25" s="31"/>
-    </row>
-    <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="39"/>
+      <c r="Q25" s="32"/>
+      <c r="R25" s="32"/>
+      <c r="S25" s="32"/>
+      <c r="T25" s="32"/>
+      <c r="U25" s="32"/>
+      <c r="V25" s="32"/>
+      <c r="W25" s="32"/>
+      <c r="X25" s="32"/>
+      <c r="Y25" s="32"/>
+      <c r="Z25" s="32"/>
+      <c r="AA25" s="32"/>
+      <c r="AB25" s="32"/>
+      <c r="AC25" s="32"/>
+      <c r="AD25" s="32"/>
+      <c r="AE25" s="32"/>
+      <c r="AF25" s="32"/>
+      <c r="AG25" s="32"/>
+      <c r="AH25" s="32"/>
+      <c r="AI25" s="32"/>
+      <c r="AJ25" s="32"/>
+      <c r="AK25" s="32"/>
+      <c r="AL25" s="32"/>
+      <c r="AM25" s="32"/>
+      <c r="AN25" s="32"/>
+      <c r="AO25" s="32"/>
+      <c r="AP25" s="32"/>
+      <c r="AQ25" s="32"/>
+    </row>
+    <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26" s="7" t="str">
         <v>No_non_DLS</v>
       </c>
-      <c r="C26" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="38"/>
-      <c r="L26" s="38"/>
-      <c r="M26" s="38"/>
-      <c r="N26" s="38"/>
-      <c r="O26" s="38"/>
-      <c r="Q26" s="31" t="e" vm="4">
+      <c r="C26" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="39"/>
+      <c r="Q26" s="32" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="R26" s="31"/>
-      <c r="S26" s="31"/>
-      <c r="T26" s="31"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="31"/>
-      <c r="W26" s="31"/>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="31"/>
-      <c r="Z26" s="31"/>
-      <c r="AA26" s="31"/>
-      <c r="AB26" s="31"/>
-      <c r="AC26" s="31"/>
-      <c r="AD26" s="31"/>
-      <c r="AE26" s="31"/>
-      <c r="AF26" s="31"/>
-      <c r="AG26" s="31"/>
-      <c r="AH26" s="31"/>
-      <c r="AI26" s="31"/>
-      <c r="AJ26" s="31"/>
-      <c r="AK26" s="31"/>
-      <c r="AL26" s="31"/>
-      <c r="AM26" s="31"/>
-      <c r="AN26" s="31"/>
-      <c r="AO26" s="31"/>
-      <c r="AP26" s="31"/>
-      <c r="AQ26" s="31"/>
-    </row>
-    <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="32"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="32"/>
+      <c r="X26" s="32"/>
+      <c r="Y26" s="32"/>
+      <c r="Z26" s="32"/>
+      <c r="AA26" s="32"/>
+      <c r="AB26" s="32"/>
+      <c r="AC26" s="32"/>
+      <c r="AD26" s="32"/>
+      <c r="AE26" s="32"/>
+      <c r="AF26" s="32"/>
+      <c r="AG26" s="32"/>
+      <c r="AH26" s="32"/>
+      <c r="AI26" s="32"/>
+      <c r="AJ26" s="32"/>
+      <c r="AK26" s="32"/>
+      <c r="AL26" s="32"/>
+      <c r="AM26" s="32"/>
+      <c r="AN26" s="32"/>
+      <c r="AO26" s="32"/>
+      <c r="AP26" s="32"/>
+      <c r="AQ26" s="32"/>
+    </row>
+    <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27" s="7" t="str">
         <v>Only_%_of_pop</v>
       </c>
-      <c r="C27" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="38"/>
-      <c r="J27" s="38"/>
-      <c r="K27" s="38"/>
-      <c r="L27" s="38"/>
-      <c r="M27" s="38"/>
-      <c r="N27" s="38"/>
-      <c r="O27" s="38"/>
-      <c r="Q27" s="31"/>
-      <c r="R27" s="31"/>
-      <c r="S27" s="31"/>
-      <c r="T27" s="31"/>
-      <c r="U27" s="31"/>
-      <c r="V27" s="31"/>
-      <c r="W27" s="31"/>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="31"/>
-      <c r="Z27" s="31"/>
-      <c r="AA27" s="31"/>
-      <c r="AB27" s="31"/>
-      <c r="AC27" s="31"/>
-      <c r="AD27" s="31"/>
-      <c r="AE27" s="31"/>
-      <c r="AF27" s="31"/>
-      <c r="AG27" s="31"/>
-      <c r="AH27" s="31"/>
-      <c r="AI27" s="31"/>
-      <c r="AJ27" s="31"/>
-      <c r="AK27" s="31"/>
-      <c r="AL27" s="31"/>
-      <c r="AM27" s="31"/>
-      <c r="AN27" s="31"/>
-      <c r="AO27" s="31"/>
-      <c r="AP27" s="31"/>
-      <c r="AQ27" s="31"/>
-    </row>
-    <row r="28" spans="1:51" ht="65.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="39"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="39"/>
+      <c r="Q27" s="32"/>
+      <c r="R27" s="32"/>
+      <c r="S27" s="32"/>
+      <c r="T27" s="32"/>
+      <c r="U27" s="32"/>
+      <c r="V27" s="32"/>
+      <c r="W27" s="32"/>
+      <c r="X27" s="32"/>
+      <c r="Y27" s="32"/>
+      <c r="Z27" s="32"/>
+      <c r="AA27" s="32"/>
+      <c r="AB27" s="32"/>
+      <c r="AC27" s="32"/>
+      <c r="AD27" s="32"/>
+      <c r="AE27" s="32"/>
+      <c r="AF27" s="32"/>
+      <c r="AG27" s="32"/>
+      <c r="AH27" s="32"/>
+      <c r="AI27" s="32"/>
+      <c r="AJ27" s="32"/>
+      <c r="AK27" s="32"/>
+      <c r="AL27" s="32"/>
+      <c r="AM27" s="32"/>
+      <c r="AN27" s="32"/>
+      <c r="AO27" s="32"/>
+      <c r="AP27" s="32"/>
+      <c r="AQ27" s="32"/>
+    </row>
+    <row r="28" spans="1:51" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" s="17" t="str">
         <v>Few_indicators_closest_DLS_coverage_90</v>
       </c>
-      <c r="C28" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="36"/>
-      <c r="K28" s="36"/>
-      <c r="L28" s="36"/>
-      <c r="M28" s="36"/>
-      <c r="N28" s="36"/>
-      <c r="O28" s="36"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="31"/>
-      <c r="V28" s="31"/>
-      <c r="W28" s="31"/>
-      <c r="X28" s="31"/>
-      <c r="Y28" s="31"/>
-      <c r="Z28" s="31"/>
-      <c r="AA28" s="31"/>
-      <c r="AB28" s="31" t="e" vm="5">
+      <c r="C28" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
+      <c r="O28" s="37"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="32"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="32"/>
+      <c r="X28" s="32"/>
+      <c r="Y28" s="32"/>
+      <c r="Z28" s="32"/>
+      <c r="AA28" s="32"/>
+      <c r="AB28" s="32" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="AC28" s="31"/>
-      <c r="AD28" s="31"/>
-      <c r="AE28" s="31"/>
-      <c r="AF28" s="31"/>
-      <c r="AG28" s="31"/>
-      <c r="AH28" s="31"/>
-      <c r="AI28" s="31"/>
-      <c r="AJ28" s="31"/>
-      <c r="AK28" s="31"/>
-      <c r="AL28" s="31"/>
-      <c r="AM28" s="31"/>
-      <c r="AN28" s="31"/>
-      <c r="AO28" s="31"/>
-      <c r="AP28" s="31"/>
-      <c r="AQ28" s="31"/>
-    </row>
-    <row r="29" spans="1:51" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AC28" s="32"/>
+      <c r="AD28" s="32"/>
+      <c r="AE28" s="32"/>
+      <c r="AF28" s="32"/>
+      <c r="AG28" s="32"/>
+      <c r="AH28" s="32"/>
+      <c r="AI28" s="32"/>
+      <c r="AJ28" s="32"/>
+      <c r="AK28" s="32"/>
+      <c r="AL28" s="32"/>
+      <c r="AM28" s="32"/>
+      <c r="AN28" s="32"/>
+      <c r="AO28" s="32"/>
+      <c r="AP28" s="32"/>
+      <c r="AQ28" s="32"/>
+    </row>
+    <row r="29" spans="1:51" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2</v>
       </c>
       <c r="B29" s="17" t="str">
-        <v>Few indicators_SPI_preferred_90</v>
-      </c>
-      <c r="C29" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="36"/>
-      <c r="K29" s="36"/>
-      <c r="L29" s="36"/>
-      <c r="M29" s="36"/>
-      <c r="N29" s="36"/>
-      <c r="O29" s="36"/>
-      <c r="Q29" s="31"/>
-      <c r="R29" s="31"/>
-      <c r="S29" s="31"/>
-      <c r="T29" s="31"/>
-      <c r="U29" s="31"/>
-      <c r="V29" s="31"/>
-      <c r="W29" s="31"/>
-      <c r="X29" s="31"/>
-      <c r="Y29" s="31"/>
-      <c r="Z29" s="31"/>
-      <c r="AA29" s="31"/>
-      <c r="AB29" s="31"/>
-      <c r="AC29" s="31"/>
-      <c r="AD29" s="31"/>
-      <c r="AE29" s="31"/>
-      <c r="AF29" s="31"/>
-      <c r="AG29" s="31"/>
-      <c r="AH29" s="31"/>
-      <c r="AI29" s="31"/>
-      <c r="AJ29" s="31"/>
-      <c r="AK29" s="31"/>
-      <c r="AL29" s="31"/>
-      <c r="AM29" s="31"/>
-      <c r="AN29" s="31"/>
-      <c r="AO29" s="31"/>
-      <c r="AP29" s="31"/>
-      <c r="AQ29" s="31"/>
-    </row>
-    <row r="30" spans="1:51" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>Few_indicators_SPI_preferred_90</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="37"/>
+      <c r="K29" s="37"/>
+      <c r="L29" s="37"/>
+      <c r="M29" s="37"/>
+      <c r="N29" s="37"/>
+      <c r="O29" s="37"/>
+      <c r="Q29" s="32"/>
+      <c r="R29" s="32"/>
+      <c r="S29" s="32"/>
+      <c r="T29" s="32"/>
+      <c r="U29" s="32"/>
+      <c r="V29" s="32"/>
+      <c r="W29" s="32"/>
+      <c r="X29" s="32"/>
+      <c r="Y29" s="32"/>
+      <c r="Z29" s="32"/>
+      <c r="AA29" s="32"/>
+      <c r="AB29" s="32"/>
+      <c r="AC29" s="32"/>
+      <c r="AD29" s="32"/>
+      <c r="AE29" s="32"/>
+      <c r="AF29" s="32"/>
+      <c r="AG29" s="32"/>
+      <c r="AH29" s="32"/>
+      <c r="AI29" s="32"/>
+      <c r="AJ29" s="32"/>
+      <c r="AK29" s="32"/>
+      <c r="AL29" s="32"/>
+      <c r="AM29" s="32"/>
+      <c r="AN29" s="32"/>
+      <c r="AO29" s="32"/>
+      <c r="AP29" s="32"/>
+      <c r="AQ29" s="32"/>
+    </row>
+    <row r="30" spans="1:51" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
       <c r="B30" s="17" t="str">
         <v>Few_indicators_closeDLS_subPrimSchool</v>
       </c>
-      <c r="C30" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
-      <c r="K30" s="36"/>
-      <c r="L30" s="36"/>
-      <c r="M30" s="36"/>
-      <c r="N30" s="36"/>
-      <c r="O30" s="36"/>
-      <c r="Q30" s="31" t="e" vm="6">
+      <c r="C30" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="33"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="37"/>
+      <c r="M30" s="37"/>
+      <c r="N30" s="37"/>
+      <c r="O30" s="37"/>
+      <c r="Q30" s="32" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
-      <c r="R30" s="31"/>
-      <c r="S30" s="31"/>
-      <c r="T30" s="31"/>
-      <c r="U30" s="31"/>
-      <c r="V30" s="31"/>
-      <c r="W30" s="31"/>
-      <c r="X30" s="31"/>
-      <c r="Y30" s="31"/>
-      <c r="Z30" s="31"/>
-      <c r="AA30" s="31"/>
-      <c r="AB30" s="31"/>
-      <c r="AC30" s="31"/>
-      <c r="AD30" s="31"/>
-      <c r="AE30" s="31"/>
-      <c r="AF30" s="31"/>
-      <c r="AG30" s="31"/>
-      <c r="AH30" s="31"/>
-      <c r="AI30" s="31"/>
-      <c r="AJ30" s="31"/>
-      <c r="AK30" s="31"/>
-      <c r="AL30" s="31"/>
-      <c r="AM30" s="31"/>
-      <c r="AN30" s="31"/>
-      <c r="AO30" s="31"/>
-      <c r="AP30" s="31"/>
-      <c r="AQ30" s="31"/>
-    </row>
-    <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R30" s="32"/>
+      <c r="S30" s="32"/>
+      <c r="T30" s="32"/>
+      <c r="U30" s="32"/>
+      <c r="V30" s="32"/>
+      <c r="W30" s="32"/>
+      <c r="X30" s="32"/>
+      <c r="Y30" s="32"/>
+      <c r="Z30" s="32"/>
+      <c r="AA30" s="32"/>
+      <c r="AB30" s="32"/>
+      <c r="AC30" s="32"/>
+      <c r="AD30" s="32"/>
+      <c r="AE30" s="32"/>
+      <c r="AF30" s="32"/>
+      <c r="AG30" s="32"/>
+      <c r="AH30" s="32"/>
+      <c r="AI30" s="32"/>
+      <c r="AJ30" s="32"/>
+      <c r="AK30" s="32"/>
+      <c r="AL30" s="32"/>
+      <c r="AM30" s="32"/>
+      <c r="AN30" s="32"/>
+      <c r="AO30" s="32"/>
+      <c r="AP30" s="32"/>
+      <c r="AQ30" s="32"/>
+    </row>
+    <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
       <c r="B31" s="17" t="str">
         <v>No_non_DLS_90</v>
       </c>
-      <c r="C31" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="36"/>
-      <c r="K31" s="36"/>
-      <c r="L31" s="36"/>
-      <c r="M31" s="36"/>
-      <c r="N31" s="36"/>
-      <c r="O31" s="36"/>
-      <c r="Q31" s="31"/>
-      <c r="R31" s="31"/>
-      <c r="S31" s="31"/>
-      <c r="T31" s="31"/>
-      <c r="U31" s="31"/>
-      <c r="V31" s="31"/>
-      <c r="W31" s="31"/>
-      <c r="X31" s="31"/>
-      <c r="Y31" s="31"/>
-      <c r="Z31" s="31"/>
-      <c r="AA31" s="31"/>
-      <c r="AB31" s="31"/>
-      <c r="AC31" s="31"/>
-      <c r="AD31" s="31"/>
-      <c r="AE31" s="31"/>
-      <c r="AF31" s="31"/>
-      <c r="AG31" s="31"/>
-      <c r="AH31" s="31"/>
-      <c r="AI31" s="31"/>
-      <c r="AJ31" s="31"/>
-      <c r="AK31" s="31"/>
-      <c r="AL31" s="31"/>
-      <c r="AM31" s="31"/>
-      <c r="AN31" s="31"/>
-      <c r="AO31" s="31"/>
-      <c r="AP31" s="31"/>
-      <c r="AQ31" s="31"/>
-    </row>
-    <row r="32" spans="1:51" ht="103.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="37"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="37"/>
+      <c r="L31" s="37"/>
+      <c r="M31" s="37"/>
+      <c r="N31" s="37"/>
+      <c r="O31" s="37"/>
+      <c r="Q31" s="32"/>
+      <c r="R31" s="32"/>
+      <c r="S31" s="32"/>
+      <c r="T31" s="32"/>
+      <c r="U31" s="32"/>
+      <c r="V31" s="32"/>
+      <c r="W31" s="32"/>
+      <c r="X31" s="32"/>
+      <c r="Y31" s="32"/>
+      <c r="Z31" s="32"/>
+      <c r="AA31" s="32"/>
+      <c r="AB31" s="32"/>
+      <c r="AC31" s="32"/>
+      <c r="AD31" s="32"/>
+      <c r="AE31" s="32"/>
+      <c r="AF31" s="32"/>
+      <c r="AG31" s="32"/>
+      <c r="AH31" s="32"/>
+      <c r="AI31" s="32"/>
+      <c r="AJ31" s="32"/>
+      <c r="AK31" s="32"/>
+      <c r="AL31" s="32"/>
+      <c r="AM31" s="32"/>
+      <c r="AN31" s="32"/>
+      <c r="AO31" s="32"/>
+      <c r="AP31" s="32"/>
+      <c r="AQ31" s="32"/>
+    </row>
+    <row r="32" spans="1:51" ht="103.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
       <c r="B32" s="17" t="str">
         <v>Few_Indicators_subWatSani</v>
       </c>
-      <c r="C32" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="36"/>
-      <c r="L32" s="36"/>
-      <c r="M32" s="36"/>
-      <c r="N32" s="36"/>
-      <c r="O32" s="36"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="31"/>
-      <c r="T32" s="31"/>
-      <c r="U32" s="31"/>
-      <c r="V32" s="31"/>
-      <c r="W32" s="31"/>
-      <c r="X32" s="31"/>
-      <c r="Y32" s="31"/>
-      <c r="Z32" s="31"/>
-      <c r="AA32" s="31"/>
-      <c r="AB32" s="31" t="e" vm="7">
+      <c r="C32" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="37"/>
+      <c r="J32" s="37"/>
+      <c r="K32" s="37"/>
+      <c r="L32" s="37"/>
+      <c r="M32" s="37"/>
+      <c r="N32" s="37"/>
+      <c r="O32" s="37"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
+      <c r="V32" s="32"/>
+      <c r="W32" s="32"/>
+      <c r="X32" s="32"/>
+      <c r="Y32" s="32"/>
+      <c r="Z32" s="32"/>
+      <c r="AA32" s="32"/>
+      <c r="AB32" s="32" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
-      <c r="AC32" s="31"/>
-      <c r="AD32" s="31"/>
-      <c r="AE32" s="31"/>
-      <c r="AF32" s="31"/>
-      <c r="AG32" s="31"/>
-      <c r="AH32" s="31"/>
-      <c r="AI32" s="31"/>
-      <c r="AJ32" s="31"/>
-      <c r="AK32" s="31"/>
-      <c r="AL32" s="31"/>
-      <c r="AM32" s="31"/>
-      <c r="AN32" s="31"/>
-      <c r="AO32" s="31"/>
-      <c r="AP32" s="31"/>
-      <c r="AQ32" s="31"/>
-    </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AC32" s="32"/>
+      <c r="AD32" s="32"/>
+      <c r="AE32" s="32"/>
+      <c r="AF32" s="32"/>
+      <c r="AG32" s="32"/>
+      <c r="AH32" s="32"/>
+      <c r="AI32" s="32"/>
+      <c r="AJ32" s="32"/>
+      <c r="AK32" s="32"/>
+      <c r="AL32" s="32"/>
+      <c r="AM32" s="32"/>
+      <c r="AN32" s="32"/>
+      <c r="AO32" s="32"/>
+      <c r="AP32" s="32"/>
+      <c r="AQ32" s="32"/>
+    </row>
+    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>4</v>
       </c>
       <c r="B33" s="6" t="str">
         <v>Only_OPP</v>
       </c>
-      <c r="C33" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
-      <c r="O33" s="33"/>
-      <c r="Q33" s="31"/>
-      <c r="R33" s="31"/>
-      <c r="S33" s="31"/>
-      <c r="T33" s="31"/>
-      <c r="U33" s="31"/>
-      <c r="V33" s="31"/>
-      <c r="W33" s="31"/>
-      <c r="X33" s="31"/>
-      <c r="Y33" s="31"/>
-      <c r="Z33" s="31"/>
-      <c r="AA33" s="31"/>
-      <c r="AB33" s="31"/>
-      <c r="AC33" s="31"/>
-      <c r="AD33" s="31"/>
-      <c r="AE33" s="31"/>
-      <c r="AF33" s="31"/>
-      <c r="AG33" s="31"/>
-      <c r="AH33" s="31"/>
-      <c r="AI33" s="31"/>
-      <c r="AJ33" s="31"/>
-      <c r="AK33" s="31"/>
-      <c r="AL33" s="31"/>
-      <c r="AM33" s="31"/>
-      <c r="AN33" s="31"/>
-      <c r="AO33" s="31"/>
-      <c r="AP33" s="31"/>
-      <c r="AQ33" s="31"/>
-    </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="C33" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="34"/>
+      <c r="K33" s="34"/>
+      <c r="L33" s="34"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
+      <c r="O33" s="34"/>
+      <c r="Q33" s="32"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="32"/>
+      <c r="T33" s="32"/>
+      <c r="U33" s="32"/>
+      <c r="V33" s="32"/>
+      <c r="W33" s="32"/>
+      <c r="X33" s="32"/>
+      <c r="Y33" s="32"/>
+      <c r="Z33" s="32"/>
+      <c r="AA33" s="32"/>
+      <c r="AB33" s="32"/>
+      <c r="AC33" s="32"/>
+      <c r="AD33" s="32"/>
+      <c r="AE33" s="32"/>
+      <c r="AF33" s="32"/>
+      <c r="AG33" s="32"/>
+      <c r="AH33" s="32"/>
+      <c r="AI33" s="32"/>
+      <c r="AJ33" s="32"/>
+      <c r="AK33" s="32"/>
+      <c r="AL33" s="32"/>
+      <c r="AM33" s="32"/>
+      <c r="AN33" s="32"/>
+      <c r="AO33" s="32"/>
+      <c r="AP33" s="32"/>
+      <c r="AQ33" s="32"/>
+    </row>
+    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
       <c r="B34" s="6" t="str">
         <v>Baseline</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="33"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="33"/>
-      <c r="N34" s="33"/>
-      <c r="O34" s="33"/>
-      <c r="Q34" s="31"/>
-      <c r="R34" s="31"/>
-      <c r="S34" s="31"/>
-      <c r="T34" s="31"/>
-      <c r="U34" s="31"/>
-      <c r="V34" s="31"/>
-      <c r="W34" s="31"/>
-      <c r="X34" s="31"/>
-      <c r="Y34" s="31"/>
-      <c r="Z34" s="31"/>
-      <c r="AA34" s="31"/>
-      <c r="AB34" s="31"/>
-      <c r="AC34" s="31"/>
-      <c r="AD34" s="31"/>
-      <c r="AE34" s="31"/>
-      <c r="AF34" s="31"/>
-      <c r="AG34" s="31"/>
-      <c r="AH34" s="31"/>
-      <c r="AI34" s="31"/>
-      <c r="AJ34" s="31"/>
-      <c r="AK34" s="31"/>
-      <c r="AL34" s="31"/>
-      <c r="AM34" s="31"/>
-      <c r="AN34" s="31"/>
-      <c r="AO34" s="31"/>
-      <c r="AP34" s="31"/>
-      <c r="AQ34" s="31"/>
-    </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="34"/>
+      <c r="N34" s="34"/>
+      <c r="O34" s="34"/>
+      <c r="Q34" s="32"/>
+      <c r="R34" s="32"/>
+      <c r="S34" s="32"/>
+      <c r="T34" s="32"/>
+      <c r="U34" s="32"/>
+      <c r="V34" s="32"/>
+      <c r="W34" s="32"/>
+      <c r="X34" s="32"/>
+      <c r="Y34" s="32"/>
+      <c r="Z34" s="32"/>
+      <c r="AA34" s="32"/>
+      <c r="AB34" s="32"/>
+      <c r="AC34" s="32"/>
+      <c r="AD34" s="32"/>
+      <c r="AE34" s="32"/>
+      <c r="AF34" s="32"/>
+      <c r="AG34" s="32"/>
+      <c r="AH34" s="32"/>
+      <c r="AI34" s="32"/>
+      <c r="AJ34" s="32"/>
+      <c r="AK34" s="32"/>
+      <c r="AL34" s="32"/>
+      <c r="AM34" s="32"/>
+      <c r="AN34" s="32"/>
+      <c r="AO34" s="32"/>
+      <c r="AP34" s="32"/>
+      <c r="AQ34" s="32"/>
+    </row>
+    <row r="35" spans="1:43" x14ac:dyDescent="0.3">
       <c r="B35" s="6" t="str">
         <v>No_nonDLS_limExt</v>
       </c>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="33"/>
-      <c r="I35" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="J35" s="33"/>
-      <c r="K35" s="33"/>
-      <c r="L35" s="33"/>
-      <c r="M35" s="33"/>
-      <c r="N35" s="33"/>
-      <c r="O35" s="33"/>
-      <c r="Q35" s="31"/>
-      <c r="R35" s="31"/>
-      <c r="S35" s="31"/>
-      <c r="T35" s="31"/>
-      <c r="U35" s="31"/>
-      <c r="V35" s="31"/>
-      <c r="W35" s="31"/>
-      <c r="X35" s="31"/>
-      <c r="Y35" s="31"/>
-      <c r="Z35" s="31"/>
-      <c r="AA35" s="31"/>
-      <c r="AB35" s="31"/>
-      <c r="AC35" s="31"/>
-      <c r="AD35" s="31"/>
-      <c r="AE35" s="31"/>
-      <c r="AF35" s="31"/>
-      <c r="AG35" s="31"/>
-      <c r="AH35" s="31"/>
-      <c r="AI35" s="31"/>
-      <c r="AJ35" s="31"/>
-      <c r="AK35" s="31"/>
-      <c r="AL35" s="31"/>
-      <c r="AM35" s="31"/>
-      <c r="AN35" s="31"/>
-      <c r="AO35" s="31"/>
-      <c r="AP35" s="31"/>
-      <c r="AQ35" s="31"/>
-    </row>
-    <row r="36" spans="1:43" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="J35" s="34"/>
+      <c r="K35" s="34"/>
+      <c r="L35" s="34"/>
+      <c r="M35" s="34"/>
+      <c r="N35" s="34"/>
+      <c r="O35" s="34"/>
+      <c r="Q35" s="32"/>
+      <c r="R35" s="32"/>
+      <c r="S35" s="32"/>
+      <c r="T35" s="32"/>
+      <c r="U35" s="32"/>
+      <c r="V35" s="32"/>
+      <c r="W35" s="32"/>
+      <c r="X35" s="32"/>
+      <c r="Y35" s="32"/>
+      <c r="Z35" s="32"/>
+      <c r="AA35" s="32"/>
+      <c r="AB35" s="32"/>
+      <c r="AC35" s="32"/>
+      <c r="AD35" s="32"/>
+      <c r="AE35" s="32"/>
+      <c r="AF35" s="32"/>
+      <c r="AG35" s="32"/>
+      <c r="AH35" s="32"/>
+      <c r="AI35" s="32"/>
+      <c r="AJ35" s="32"/>
+      <c r="AK35" s="32"/>
+      <c r="AL35" s="32"/>
+      <c r="AM35" s="32"/>
+      <c r="AN35" s="32"/>
+      <c r="AO35" s="32"/>
+      <c r="AP35" s="32"/>
+      <c r="AQ35" s="32"/>
+    </row>
+    <row r="36" spans="1:43" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="str">
         <v>BHN</v>
       </c>
-      <c r="C36" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="D36" s="37"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="37"/>
-      <c r="H36" s="37"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="33"/>
-      <c r="M36" s="33"/>
-      <c r="N36" s="33"/>
-      <c r="O36" s="33"/>
-      <c r="Q36" s="31"/>
-      <c r="R36" s="31"/>
-      <c r="S36" s="31"/>
-      <c r="T36" s="31"/>
-      <c r="U36" s="31"/>
-      <c r="V36" s="31"/>
-      <c r="W36" s="31"/>
-      <c r="X36" s="31"/>
-      <c r="Y36" s="31"/>
-      <c r="Z36" s="31"/>
-      <c r="AA36" s="31"/>
-      <c r="AB36" s="31"/>
-      <c r="AC36" s="31"/>
-      <c r="AD36" s="31"/>
-      <c r="AE36" s="31"/>
-      <c r="AF36" s="31"/>
-      <c r="AG36" s="31"/>
-      <c r="AH36" s="31"/>
-      <c r="AI36" s="31"/>
-      <c r="AJ36" s="31"/>
-      <c r="AK36" s="31"/>
-      <c r="AL36" s="31"/>
-      <c r="AM36" s="31"/>
-      <c r="AN36" s="31"/>
-      <c r="AO36" s="31"/>
-      <c r="AP36" s="31"/>
-      <c r="AQ36" s="31"/>
-    </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB37" s="31"/>
-      <c r="AC37" s="31"/>
-      <c r="AD37" s="31"/>
-      <c r="AE37" s="31"/>
-      <c r="AF37" s="31"/>
-      <c r="AG37" s="31"/>
-      <c r="AH37" s="31"/>
-      <c r="AI37" s="31"/>
-      <c r="AJ37" s="31"/>
-      <c r="AK37" s="31"/>
-      <c r="AL37" s="31"/>
-      <c r="AM37" s="31"/>
-      <c r="AN37" s="31"/>
-      <c r="AO37" s="31"/>
-      <c r="AP37" s="31"/>
-      <c r="AQ37" s="31"/>
-    </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB38" s="31"/>
-      <c r="AC38" s="31"/>
-      <c r="AD38" s="31"/>
-      <c r="AE38" s="31"/>
-      <c r="AF38" s="31"/>
-      <c r="AG38" s="31"/>
-      <c r="AH38" s="31"/>
-      <c r="AI38" s="31"/>
-      <c r="AJ38" s="31"/>
-      <c r="AK38" s="31"/>
-      <c r="AL38" s="31"/>
-      <c r="AM38" s="31"/>
-      <c r="AN38" s="31"/>
-      <c r="AO38" s="31"/>
-      <c r="AP38" s="31"/>
-      <c r="AQ38" s="31"/>
-    </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB39" s="31"/>
-      <c r="AC39" s="31"/>
-      <c r="AD39" s="31"/>
-      <c r="AE39" s="31"/>
-      <c r="AF39" s="31"/>
-      <c r="AG39" s="31"/>
-      <c r="AH39" s="31"/>
-      <c r="AI39" s="31"/>
-      <c r="AJ39" s="31"/>
-      <c r="AK39" s="31"/>
-      <c r="AL39" s="31"/>
-      <c r="AM39" s="31"/>
-      <c r="AN39" s="31"/>
-      <c r="AO39" s="31"/>
-      <c r="AP39" s="31"/>
-      <c r="AQ39" s="31"/>
-    </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB40" s="31"/>
-      <c r="AC40" s="31"/>
-      <c r="AD40" s="31"/>
-      <c r="AE40" s="31"/>
-      <c r="AF40" s="31"/>
-      <c r="AG40" s="31"/>
-      <c r="AH40" s="31"/>
-      <c r="AI40" s="31"/>
-      <c r="AJ40" s="31"/>
-      <c r="AK40" s="31"/>
-      <c r="AL40" s="31"/>
-      <c r="AM40" s="31"/>
-      <c r="AN40" s="31"/>
-      <c r="AO40" s="31"/>
-      <c r="AP40" s="31"/>
-      <c r="AQ40" s="31"/>
-    </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB41" s="31"/>
-      <c r="AC41" s="31"/>
-      <c r="AD41" s="31"/>
-      <c r="AE41" s="31"/>
-      <c r="AF41" s="31"/>
-      <c r="AG41" s="31"/>
-      <c r="AH41" s="31"/>
-      <c r="AI41" s="31"/>
-      <c r="AJ41" s="31"/>
-      <c r="AK41" s="31"/>
-      <c r="AL41" s="31"/>
-      <c r="AM41" s="31"/>
-      <c r="AN41" s="31"/>
-      <c r="AO41" s="31"/>
-      <c r="AP41" s="31"/>
-      <c r="AQ41" s="31"/>
-    </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB42" s="31" t="e" vm="8">
+      <c r="C36" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="34"/>
+      <c r="J36" s="34"/>
+      <c r="K36" s="34"/>
+      <c r="L36" s="34"/>
+      <c r="M36" s="34"/>
+      <c r="N36" s="34"/>
+      <c r="O36" s="34"/>
+      <c r="Q36" s="32"/>
+      <c r="R36" s="32"/>
+      <c r="S36" s="32"/>
+      <c r="T36" s="32"/>
+      <c r="U36" s="32"/>
+      <c r="V36" s="32"/>
+      <c r="W36" s="32"/>
+      <c r="X36" s="32"/>
+      <c r="Y36" s="32"/>
+      <c r="Z36" s="32"/>
+      <c r="AA36" s="32"/>
+      <c r="AB36" s="32"/>
+      <c r="AC36" s="32"/>
+      <c r="AD36" s="32"/>
+      <c r="AE36" s="32"/>
+      <c r="AF36" s="32"/>
+      <c r="AG36" s="32"/>
+      <c r="AH36" s="32"/>
+      <c r="AI36" s="32"/>
+      <c r="AJ36" s="32"/>
+      <c r="AK36" s="32"/>
+      <c r="AL36" s="32"/>
+      <c r="AM36" s="32"/>
+      <c r="AN36" s="32"/>
+      <c r="AO36" s="32"/>
+      <c r="AP36" s="32"/>
+      <c r="AQ36" s="32"/>
+    </row>
+    <row r="37" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB37" s="32"/>
+      <c r="AC37" s="32"/>
+      <c r="AD37" s="32"/>
+      <c r="AE37" s="32"/>
+      <c r="AF37" s="32"/>
+      <c r="AG37" s="32"/>
+      <c r="AH37" s="32"/>
+      <c r="AI37" s="32"/>
+      <c r="AJ37" s="32"/>
+      <c r="AK37" s="32"/>
+      <c r="AL37" s="32"/>
+      <c r="AM37" s="32"/>
+      <c r="AN37" s="32"/>
+      <c r="AO37" s="32"/>
+      <c r="AP37" s="32"/>
+      <c r="AQ37" s="32"/>
+    </row>
+    <row r="38" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB38" s="32"/>
+      <c r="AC38" s="32"/>
+      <c r="AD38" s="32"/>
+      <c r="AE38" s="32"/>
+      <c r="AF38" s="32"/>
+      <c r="AG38" s="32"/>
+      <c r="AH38" s="32"/>
+      <c r="AI38" s="32"/>
+      <c r="AJ38" s="32"/>
+      <c r="AK38" s="32"/>
+      <c r="AL38" s="32"/>
+      <c r="AM38" s="32"/>
+      <c r="AN38" s="32"/>
+      <c r="AO38" s="32"/>
+      <c r="AP38" s="32"/>
+      <c r="AQ38" s="32"/>
+    </row>
+    <row r="39" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB39" s="32"/>
+      <c r="AC39" s="32"/>
+      <c r="AD39" s="32"/>
+      <c r="AE39" s="32"/>
+      <c r="AF39" s="32"/>
+      <c r="AG39" s="32"/>
+      <c r="AH39" s="32"/>
+      <c r="AI39" s="32"/>
+      <c r="AJ39" s="32"/>
+      <c r="AK39" s="32"/>
+      <c r="AL39" s="32"/>
+      <c r="AM39" s="32"/>
+      <c r="AN39" s="32"/>
+      <c r="AO39" s="32"/>
+      <c r="AP39" s="32"/>
+      <c r="AQ39" s="32"/>
+    </row>
+    <row r="40" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB40" s="32"/>
+      <c r="AC40" s="32"/>
+      <c r="AD40" s="32"/>
+      <c r="AE40" s="32"/>
+      <c r="AF40" s="32"/>
+      <c r="AG40" s="32"/>
+      <c r="AH40" s="32"/>
+      <c r="AI40" s="32"/>
+      <c r="AJ40" s="32"/>
+      <c r="AK40" s="32"/>
+      <c r="AL40" s="32"/>
+      <c r="AM40" s="32"/>
+      <c r="AN40" s="32"/>
+      <c r="AO40" s="32"/>
+      <c r="AP40" s="32"/>
+      <c r="AQ40" s="32"/>
+    </row>
+    <row r="41" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB41" s="32"/>
+      <c r="AC41" s="32"/>
+      <c r="AD41" s="32"/>
+      <c r="AE41" s="32"/>
+      <c r="AF41" s="32"/>
+      <c r="AG41" s="32"/>
+      <c r="AH41" s="32"/>
+      <c r="AI41" s="32"/>
+      <c r="AJ41" s="32"/>
+      <c r="AK41" s="32"/>
+      <c r="AL41" s="32"/>
+      <c r="AM41" s="32"/>
+      <c r="AN41" s="32"/>
+      <c r="AO41" s="32"/>
+      <c r="AP41" s="32"/>
+      <c r="AQ41" s="32"/>
+    </row>
+    <row r="42" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB42" s="32" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-      <c r="AC42" s="31"/>
-      <c r="AD42" s="31"/>
-      <c r="AE42" s="31"/>
-      <c r="AF42" s="31"/>
-      <c r="AG42" s="31"/>
-      <c r="AH42" s="31"/>
-      <c r="AI42" s="31"/>
-      <c r="AJ42" s="31"/>
-      <c r="AK42" s="31"/>
-      <c r="AL42" s="31"/>
-      <c r="AM42" s="31"/>
-      <c r="AN42" s="31"/>
-      <c r="AO42" s="31"/>
-      <c r="AP42" s="31"/>
-      <c r="AQ42" s="31"/>
-    </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB43" s="31"/>
-      <c r="AC43" s="31"/>
-      <c r="AD43" s="31"/>
-      <c r="AE43" s="31"/>
-      <c r="AF43" s="31"/>
-      <c r="AG43" s="31"/>
-      <c r="AH43" s="31"/>
-      <c r="AI43" s="31"/>
-      <c r="AJ43" s="31"/>
-      <c r="AK43" s="31"/>
-      <c r="AL43" s="31"/>
-      <c r="AM43" s="31"/>
-      <c r="AN43" s="31"/>
-      <c r="AO43" s="31"/>
-      <c r="AP43" s="31"/>
-      <c r="AQ43" s="31"/>
-    </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB44" s="31"/>
-      <c r="AC44" s="31"/>
-      <c r="AD44" s="31"/>
-      <c r="AE44" s="31"/>
-      <c r="AF44" s="31"/>
-      <c r="AG44" s="31"/>
-      <c r="AH44" s="31"/>
-      <c r="AI44" s="31"/>
-      <c r="AJ44" s="31"/>
-      <c r="AK44" s="31"/>
-      <c r="AL44" s="31"/>
-      <c r="AM44" s="31"/>
-      <c r="AN44" s="31"/>
-      <c r="AO44" s="31"/>
-      <c r="AP44" s="31"/>
-      <c r="AQ44" s="31"/>
-    </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB45" s="31"/>
-      <c r="AC45" s="31"/>
-      <c r="AD45" s="31"/>
-      <c r="AE45" s="31"/>
-      <c r="AF45" s="31"/>
-      <c r="AG45" s="31"/>
-      <c r="AH45" s="31"/>
-      <c r="AI45" s="31"/>
-      <c r="AJ45" s="31"/>
-      <c r="AK45" s="31"/>
-      <c r="AL45" s="31"/>
-      <c r="AM45" s="31"/>
-      <c r="AN45" s="31"/>
-      <c r="AO45" s="31"/>
-      <c r="AP45" s="31"/>
-      <c r="AQ45" s="31"/>
-    </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB46" s="31"/>
-      <c r="AC46" s="31"/>
-      <c r="AD46" s="31"/>
-      <c r="AE46" s="31"/>
-      <c r="AF46" s="31"/>
-      <c r="AG46" s="31"/>
-      <c r="AH46" s="31"/>
-      <c r="AI46" s="31"/>
-      <c r="AJ46" s="31"/>
-      <c r="AK46" s="31"/>
-      <c r="AL46" s="31"/>
-      <c r="AM46" s="31"/>
-      <c r="AN46" s="31"/>
-      <c r="AO46" s="31"/>
-      <c r="AP46" s="31"/>
-      <c r="AQ46" s="31"/>
-    </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB47" s="31"/>
-      <c r="AC47" s="31"/>
-      <c r="AD47" s="31"/>
-      <c r="AE47" s="31"/>
-      <c r="AF47" s="31"/>
-      <c r="AG47" s="31"/>
-      <c r="AH47" s="31"/>
-      <c r="AI47" s="31"/>
-      <c r="AJ47" s="31"/>
-      <c r="AK47" s="31"/>
-      <c r="AL47" s="31"/>
-      <c r="AM47" s="31"/>
-      <c r="AN47" s="31"/>
-      <c r="AO47" s="31"/>
-      <c r="AP47" s="31"/>
-      <c r="AQ47" s="31"/>
-    </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB48" s="31"/>
-      <c r="AC48" s="31"/>
-      <c r="AD48" s="31"/>
-      <c r="AE48" s="31"/>
-      <c r="AF48" s="31"/>
-      <c r="AG48" s="31"/>
-      <c r="AH48" s="31"/>
-      <c r="AI48" s="31"/>
-      <c r="AJ48" s="31"/>
-      <c r="AK48" s="31"/>
-      <c r="AL48" s="31"/>
-      <c r="AM48" s="31"/>
-      <c r="AN48" s="31"/>
-      <c r="AO48" s="31"/>
-      <c r="AP48" s="31"/>
-      <c r="AQ48" s="31"/>
-    </row>
-    <row r="49" spans="28:43" x14ac:dyDescent="0.25">
-      <c r="AB49" s="31"/>
-      <c r="AC49" s="31"/>
-      <c r="AD49" s="31"/>
-      <c r="AE49" s="31"/>
-      <c r="AF49" s="31"/>
-      <c r="AG49" s="31"/>
-      <c r="AH49" s="31"/>
-      <c r="AI49" s="31"/>
-      <c r="AJ49" s="31"/>
-      <c r="AK49" s="31"/>
-      <c r="AL49" s="31"/>
-      <c r="AM49" s="31"/>
-      <c r="AN49" s="31"/>
-      <c r="AO49" s="31"/>
-      <c r="AP49" s="31"/>
-      <c r="AQ49" s="31"/>
-    </row>
-    <row r="50" spans="28:43" x14ac:dyDescent="0.25">
-      <c r="AB50" s="31"/>
-      <c r="AC50" s="31"/>
-      <c r="AD50" s="31"/>
-      <c r="AE50" s="31"/>
-      <c r="AF50" s="31"/>
-      <c r="AG50" s="31"/>
-      <c r="AH50" s="31"/>
-      <c r="AI50" s="31"/>
-      <c r="AJ50" s="31"/>
-      <c r="AK50" s="31"/>
-      <c r="AL50" s="31"/>
-      <c r="AM50" s="31"/>
-      <c r="AN50" s="31"/>
-      <c r="AO50" s="31"/>
-      <c r="AP50" s="31"/>
-      <c r="AQ50" s="31"/>
-    </row>
-    <row r="51" spans="28:43" x14ac:dyDescent="0.25">
-      <c r="AB51" s="31"/>
-      <c r="AC51" s="31"/>
-      <c r="AD51" s="31"/>
-      <c r="AE51" s="31"/>
-      <c r="AF51" s="31"/>
-      <c r="AG51" s="31"/>
-      <c r="AH51" s="31"/>
-      <c r="AI51" s="31"/>
-      <c r="AJ51" s="31"/>
-      <c r="AK51" s="31"/>
-      <c r="AL51" s="31"/>
-      <c r="AM51" s="31"/>
-      <c r="AN51" s="31"/>
-      <c r="AO51" s="31"/>
-      <c r="AP51" s="31"/>
-      <c r="AQ51" s="31"/>
-    </row>
-    <row r="52" spans="28:43" x14ac:dyDescent="0.25">
-      <c r="AB52" s="31"/>
-      <c r="AC52" s="31"/>
-      <c r="AD52" s="31"/>
-      <c r="AE52" s="31"/>
-      <c r="AF52" s="31"/>
-      <c r="AG52" s="31"/>
-      <c r="AH52" s="31"/>
-      <c r="AI52" s="31"/>
-      <c r="AJ52" s="31"/>
-      <c r="AK52" s="31"/>
-      <c r="AL52" s="31"/>
-      <c r="AM52" s="31"/>
-      <c r="AN52" s="31"/>
-      <c r="AO52" s="31"/>
-      <c r="AP52" s="31"/>
-      <c r="AQ52" s="31"/>
-    </row>
-    <row r="53" spans="28:43" x14ac:dyDescent="0.25">
-      <c r="AB53" s="31"/>
-      <c r="AC53" s="31"/>
-      <c r="AD53" s="31"/>
-      <c r="AE53" s="31"/>
-      <c r="AF53" s="31"/>
-      <c r="AG53" s="31"/>
-      <c r="AH53" s="31"/>
-      <c r="AI53" s="31"/>
-      <c r="AJ53" s="31"/>
-      <c r="AK53" s="31"/>
-      <c r="AL53" s="31"/>
-      <c r="AM53" s="31"/>
-      <c r="AN53" s="31"/>
-      <c r="AO53" s="31"/>
-      <c r="AP53" s="31"/>
-      <c r="AQ53" s="31"/>
+      <c r="AC42" s="32"/>
+      <c r="AD42" s="32"/>
+      <c r="AE42" s="32"/>
+      <c r="AF42" s="32"/>
+      <c r="AG42" s="32"/>
+      <c r="AH42" s="32"/>
+      <c r="AI42" s="32"/>
+      <c r="AJ42" s="32"/>
+      <c r="AK42" s="32"/>
+      <c r="AL42" s="32"/>
+      <c r="AM42" s="32"/>
+      <c r="AN42" s="32"/>
+      <c r="AO42" s="32"/>
+      <c r="AP42" s="32"/>
+      <c r="AQ42" s="32"/>
+    </row>
+    <row r="43" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB43" s="32"/>
+      <c r="AC43" s="32"/>
+      <c r="AD43" s="32"/>
+      <c r="AE43" s="32"/>
+      <c r="AF43" s="32"/>
+      <c r="AG43" s="32"/>
+      <c r="AH43" s="32"/>
+      <c r="AI43" s="32"/>
+      <c r="AJ43" s="32"/>
+      <c r="AK43" s="32"/>
+      <c r="AL43" s="32"/>
+      <c r="AM43" s="32"/>
+      <c r="AN43" s="32"/>
+      <c r="AO43" s="32"/>
+      <c r="AP43" s="32"/>
+      <c r="AQ43" s="32"/>
+    </row>
+    <row r="44" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB44" s="32"/>
+      <c r="AC44" s="32"/>
+      <c r="AD44" s="32"/>
+      <c r="AE44" s="32"/>
+      <c r="AF44" s="32"/>
+      <c r="AG44" s="32"/>
+      <c r="AH44" s="32"/>
+      <c r="AI44" s="32"/>
+      <c r="AJ44" s="32"/>
+      <c r="AK44" s="32"/>
+      <c r="AL44" s="32"/>
+      <c r="AM44" s="32"/>
+      <c r="AN44" s="32"/>
+      <c r="AO44" s="32"/>
+      <c r="AP44" s="32"/>
+      <c r="AQ44" s="32"/>
+    </row>
+    <row r="45" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB45" s="32"/>
+      <c r="AC45" s="32"/>
+      <c r="AD45" s="32"/>
+      <c r="AE45" s="32"/>
+      <c r="AF45" s="32"/>
+      <c r="AG45" s="32"/>
+      <c r="AH45" s="32"/>
+      <c r="AI45" s="32"/>
+      <c r="AJ45" s="32"/>
+      <c r="AK45" s="32"/>
+      <c r="AL45" s="32"/>
+      <c r="AM45" s="32"/>
+      <c r="AN45" s="32"/>
+      <c r="AO45" s="32"/>
+      <c r="AP45" s="32"/>
+      <c r="AQ45" s="32"/>
+    </row>
+    <row r="46" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB46" s="32"/>
+      <c r="AC46" s="32"/>
+      <c r="AD46" s="32"/>
+      <c r="AE46" s="32"/>
+      <c r="AF46" s="32"/>
+      <c r="AG46" s="32"/>
+      <c r="AH46" s="32"/>
+      <c r="AI46" s="32"/>
+      <c r="AJ46" s="32"/>
+      <c r="AK46" s="32"/>
+      <c r="AL46" s="32"/>
+      <c r="AM46" s="32"/>
+      <c r="AN46" s="32"/>
+      <c r="AO46" s="32"/>
+      <c r="AP46" s="32"/>
+      <c r="AQ46" s="32"/>
+    </row>
+    <row r="47" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB47" s="32"/>
+      <c r="AC47" s="32"/>
+      <c r="AD47" s="32"/>
+      <c r="AE47" s="32"/>
+      <c r="AF47" s="32"/>
+      <c r="AG47" s="32"/>
+      <c r="AH47" s="32"/>
+      <c r="AI47" s="32"/>
+      <c r="AJ47" s="32"/>
+      <c r="AK47" s="32"/>
+      <c r="AL47" s="32"/>
+      <c r="AM47" s="32"/>
+      <c r="AN47" s="32"/>
+      <c r="AO47" s="32"/>
+      <c r="AP47" s="32"/>
+      <c r="AQ47" s="32"/>
+    </row>
+    <row r="48" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB48" s="32"/>
+      <c r="AC48" s="32"/>
+      <c r="AD48" s="32"/>
+      <c r="AE48" s="32"/>
+      <c r="AF48" s="32"/>
+      <c r="AG48" s="32"/>
+      <c r="AH48" s="32"/>
+      <c r="AI48" s="32"/>
+      <c r="AJ48" s="32"/>
+      <c r="AK48" s="32"/>
+      <c r="AL48" s="32"/>
+      <c r="AM48" s="32"/>
+      <c r="AN48" s="32"/>
+      <c r="AO48" s="32"/>
+      <c r="AP48" s="32"/>
+      <c r="AQ48" s="32"/>
+    </row>
+    <row r="49" spans="28:43" x14ac:dyDescent="0.3">
+      <c r="AB49" s="32"/>
+      <c r="AC49" s="32"/>
+      <c r="AD49" s="32"/>
+      <c r="AE49" s="32"/>
+      <c r="AF49" s="32"/>
+      <c r="AG49" s="32"/>
+      <c r="AH49" s="32"/>
+      <c r="AI49" s="32"/>
+      <c r="AJ49" s="32"/>
+      <c r="AK49" s="32"/>
+      <c r="AL49" s="32"/>
+      <c r="AM49" s="32"/>
+      <c r="AN49" s="32"/>
+      <c r="AO49" s="32"/>
+      <c r="AP49" s="32"/>
+      <c r="AQ49" s="32"/>
+    </row>
+    <row r="50" spans="28:43" x14ac:dyDescent="0.3">
+      <c r="AB50" s="32"/>
+      <c r="AC50" s="32"/>
+      <c r="AD50" s="32"/>
+      <c r="AE50" s="32"/>
+      <c r="AF50" s="32"/>
+      <c r="AG50" s="32"/>
+      <c r="AH50" s="32"/>
+      <c r="AI50" s="32"/>
+      <c r="AJ50" s="32"/>
+      <c r="AK50" s="32"/>
+      <c r="AL50" s="32"/>
+      <c r="AM50" s="32"/>
+      <c r="AN50" s="32"/>
+      <c r="AO50" s="32"/>
+      <c r="AP50" s="32"/>
+      <c r="AQ50" s="32"/>
+    </row>
+    <row r="51" spans="28:43" x14ac:dyDescent="0.3">
+      <c r="AB51" s="32"/>
+      <c r="AC51" s="32"/>
+      <c r="AD51" s="32"/>
+      <c r="AE51" s="32"/>
+      <c r="AF51" s="32"/>
+      <c r="AG51" s="32"/>
+      <c r="AH51" s="32"/>
+      <c r="AI51" s="32"/>
+      <c r="AJ51" s="32"/>
+      <c r="AK51" s="32"/>
+      <c r="AL51" s="32"/>
+      <c r="AM51" s="32"/>
+      <c r="AN51" s="32"/>
+      <c r="AO51" s="32"/>
+      <c r="AP51" s="32"/>
+      <c r="AQ51" s="32"/>
+    </row>
+    <row r="52" spans="28:43" x14ac:dyDescent="0.3">
+      <c r="AB52" s="32"/>
+      <c r="AC52" s="32"/>
+      <c r="AD52" s="32"/>
+      <c r="AE52" s="32"/>
+      <c r="AF52" s="32"/>
+      <c r="AG52" s="32"/>
+      <c r="AH52" s="32"/>
+      <c r="AI52" s="32"/>
+      <c r="AJ52" s="32"/>
+      <c r="AK52" s="32"/>
+      <c r="AL52" s="32"/>
+      <c r="AM52" s="32"/>
+      <c r="AN52" s="32"/>
+      <c r="AO52" s="32"/>
+      <c r="AP52" s="32"/>
+      <c r="AQ52" s="32"/>
+    </row>
+    <row r="53" spans="28:43" x14ac:dyDescent="0.3">
+      <c r="AB53" s="32"/>
+      <c r="AC53" s="32"/>
+      <c r="AD53" s="32"/>
+      <c r="AE53" s="32"/>
+      <c r="AF53" s="32"/>
+      <c r="AG53" s="32"/>
+      <c r="AH53" s="32"/>
+      <c r="AI53" s="32"/>
+      <c r="AJ53" s="32"/>
+      <c r="AK53" s="32"/>
+      <c r="AL53" s="32"/>
+      <c r="AM53" s="32"/>
+      <c r="AN53" s="32"/>
+      <c r="AO53" s="32"/>
+      <c r="AP53" s="32"/>
+      <c r="AQ53" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="43">
@@ -3537,45 +3547,45 @@
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AY53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.28515625" customWidth="1"/>
+    <col min="2" max="2" width="35.33203125" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
-    <col min="5" max="16" width="4.28515625" customWidth="1"/>
-    <col min="19" max="19" width="8.85546875" customWidth="1"/>
+    <col min="5" max="16" width="4.33203125" customWidth="1"/>
+    <col min="19" max="19" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="42"/>
+        <v>45</v>
+      </c>
+      <c r="C3" s="42"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="43"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
       <c r="T3" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U3" s="22"/>
       <c r="V3" s="22"/>
       <c r="W3" s="22"/>
       <c r="X3" s="22"/>
     </row>
-    <row r="4" spans="1:24" ht="221.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="221.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="15" t="s">
         <v>16</v>
       </c>
@@ -3590,7 +3600,7 @@
         <v>Few_indicators_closest_DLS_coverage</v>
       </c>
       <c r="F4" s="9" t="str">
-        <v>Few indicators_SPI_preferred</v>
+        <v>Few_indicators_SPI_preferred</v>
       </c>
       <c r="G4" s="9" t="str">
         <v>No_non_DLS</v>
@@ -3602,7 +3612,7 @@
         <v>Few_indicators_closest_DLS_coverage_90</v>
       </c>
       <c r="J4" s="9" t="str">
-        <v>Few indicators_SPI_preferred_90</v>
+        <v>Few_indicators_SPI_preferred_90</v>
       </c>
       <c r="K4" s="23" t="str">
         <v>Few_indicators_closeDLS_subPrimSchool</v>
@@ -3625,18 +3635,18 @@
       <c r="Q4" s="23" t="str">
         <v>BHN</v>
       </c>
-      <c r="R4" s="23" t="str">
+      <c r="R4" s="29" t="str">
         <v>No_non_DLS_BHNFWB</v>
       </c>
-      <c r="T4" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="U4" s="30"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="30"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="T4" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="str" cm="1">
         <f t="array" ref="B5:B15">_xlfn.UNIQUE('Overview of indicators and DLS'!C4:C67)</f>
         <v>Food &amp; Nutrition</v>
@@ -3706,7 +3716,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="str">
         <v>Health Care</v>
       </c>
@@ -3775,7 +3785,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="str">
         <v>Water</v>
       </c>
@@ -3844,7 +3854,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="11" t="str">
         <v>Sanitation</v>
       </c>
@@ -3913,7 +3923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="11" t="str">
         <v>Food preparation</v>
       </c>
@@ -3923,7 +3933,7 @@
       </c>
       <c r="D9" s="8" cm="1">
         <f t="array" ref="D9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!D$2:D$64=1))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="8" cm="1">
         <f t="array" ref="E9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!E$2:E$64=1))</f>
@@ -3935,7 +3945,7 @@
       </c>
       <c r="G9" s="8" cm="1">
         <f t="array" ref="G9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!G$2:G$64=1))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" s="11" cm="1">
         <f t="array" ref="H9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!H$2:H$64=1))</f>
@@ -3955,7 +3965,7 @@
       </c>
       <c r="L9" s="8" cm="1">
         <f t="array" ref="L9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!L$2:L$64=1))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M9" s="8" cm="1">
         <f t="array" ref="M9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!M$2:M$64=1))</f>
@@ -3979,10 +3989,10 @@
       </c>
       <c r="R9" s="8" cm="1">
         <f t="array" ref="R9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!R$2:R$64=1))</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B10" s="11" t="str">
         <v>Thermal comfort</v>
       </c>
@@ -4051,7 +4061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B11" s="11" t="str">
         <v>Non material / Non-DLS</v>
       </c>
@@ -4120,7 +4130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="str">
         <v>Education</v>
       </c>
@@ -4189,7 +4199,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="str">
         <v>Social connectedness</v>
       </c>
@@ -4258,7 +4268,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="str">
         <v>Housing</v>
       </c>
@@ -4327,7 +4337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="str">
         <v>Physical Connectedness</v>
       </c>
@@ -4396,10 +4406,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="11"/>
       <c r="C16" s="20"/>
       <c r="D16" s="14"/>
@@ -4418,7 +4428,7 @@
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.3">
       <c r="B17" s="15" t="s">
         <v>33</v>
       </c>
@@ -4428,7 +4438,7 @@
       </c>
       <c r="D17" s="14">
         <f>SUM(D5:D15)</f>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E17" s="14">
         <f t="shared" ref="E17:Q17" si="0">SUM(E5:E15)</f>
@@ -4440,7 +4450,7 @@
       </c>
       <c r="G17" s="14">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H17" s="15">
         <f t="shared" si="0"/>
@@ -4460,7 +4470,7 @@
       </c>
       <c r="L17" s="14">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M17" s="14">
         <f t="shared" si="0"/>
@@ -4484,10 +4494,10 @@
       </c>
       <c r="R17" s="14">
         <f t="shared" ref="R17" si="1">SUM(R5:R15)</f>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:51" x14ac:dyDescent="0.3">
       <c r="B18" s="11" t="s">
         <v>34</v>
       </c>
@@ -4556,7 +4566,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.3">
       <c r="B19" s="11" t="s">
         <v>35</v>
       </c>
@@ -4566,7 +4576,7 @@
       </c>
       <c r="D19" s="8">
         <f>SUM(Experiments!D54:D64)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" s="8">
         <f>SUM(Experiments!E54:E64)</f>
@@ -4578,7 +4588,7 @@
       </c>
       <c r="G19" s="8">
         <f>SUM(Experiments!G54:G64)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H19" s="11">
         <f>SUM(Experiments!H54:H64)</f>
@@ -4598,7 +4608,7 @@
       </c>
       <c r="L19" s="8">
         <f>SUM(Experiments!L54:L64)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M19" s="8">
         <f>SUM(Experiments!M54:M64)</f>
@@ -4622,41 +4632,41 @@
       </c>
       <c r="R19" s="8">
         <f>SUM(Experiments!R54:R64)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="43"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="43"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="44"/>
       <c r="Q21" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AR21" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:51" ht="90.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:51" ht="90.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1</v>
       </c>
@@ -4664,1069 +4674,1069 @@
         <f t="array" ref="B22:B37">TRANSPOSE(_xlfn.ANCHORARRAY(C4))</f>
         <v>BHN_FWB</v>
       </c>
-      <c r="C22" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="38"/>
-      <c r="Q22" s="31" t="e" vm="9">
+      <c r="C22" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="39"/>
+      <c r="Q22" s="32" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31"/>
-      <c r="T22" s="31"/>
-      <c r="U22" s="31"/>
-      <c r="V22" s="31"/>
-      <c r="W22" s="31"/>
-      <c r="X22" s="31"/>
-      <c r="Y22" s="31"/>
-      <c r="Z22" s="31"/>
-      <c r="AA22" s="31"/>
-      <c r="AB22" s="31" t="e" vm="10">
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="32"/>
+      <c r="U22" s="32"/>
+      <c r="V22" s="32"/>
+      <c r="W22" s="32"/>
+      <c r="X22" s="32"/>
+      <c r="Y22" s="32"/>
+      <c r="Z22" s="32"/>
+      <c r="AA22" s="32"/>
+      <c r="AB22" s="32" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
-      <c r="AC22" s="31"/>
-      <c r="AD22" s="31"/>
-      <c r="AE22" s="31"/>
-      <c r="AF22" s="31"/>
-      <c r="AG22" s="31"/>
-      <c r="AH22" s="31"/>
-      <c r="AI22" s="31"/>
-      <c r="AJ22" s="31"/>
-      <c r="AK22" s="31"/>
-      <c r="AL22" s="31"/>
-      <c r="AM22" s="31"/>
-      <c r="AN22" s="31"/>
-      <c r="AO22" s="31"/>
-      <c r="AP22" s="31"/>
-      <c r="AQ22" s="31"/>
-      <c r="AR22" s="31" t="e" vm="3">
+      <c r="AC22" s="32"/>
+      <c r="AD22" s="32"/>
+      <c r="AE22" s="32"/>
+      <c r="AF22" s="32"/>
+      <c r="AG22" s="32"/>
+      <c r="AH22" s="32"/>
+      <c r="AI22" s="32"/>
+      <c r="AJ22" s="32"/>
+      <c r="AK22" s="32"/>
+      <c r="AL22" s="32"/>
+      <c r="AM22" s="32"/>
+      <c r="AN22" s="32"/>
+      <c r="AO22" s="32"/>
+      <c r="AP22" s="32"/>
+      <c r="AQ22" s="32"/>
+      <c r="AR22" s="32" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="AS22" s="31"/>
-      <c r="AT22" s="31"/>
-      <c r="AU22" s="31"/>
-      <c r="AV22" s="31"/>
-      <c r="AW22" s="31"/>
-      <c r="AX22" s="31"/>
-      <c r="AY22" s="31"/>
-    </row>
-    <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AS22" s="32"/>
+      <c r="AT22" s="32"/>
+      <c r="AU22" s="32"/>
+      <c r="AV22" s="32"/>
+      <c r="AW22" s="32"/>
+      <c r="AX22" s="32"/>
+      <c r="AY22" s="32"/>
+    </row>
+    <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23" s="26" t="str">
         <v>BHN_FWB_AllExt</v>
       </c>
-      <c r="C23" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="38"/>
-      <c r="Q23" s="31"/>
-      <c r="R23" s="31"/>
-      <c r="S23" s="31"/>
-      <c r="T23" s="31"/>
-      <c r="U23" s="31"/>
-      <c r="V23" s="31"/>
-      <c r="W23" s="31"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="31"/>
-      <c r="Z23" s="31"/>
-      <c r="AA23" s="31"/>
-      <c r="AB23" s="31"/>
-      <c r="AC23" s="31"/>
-      <c r="AD23" s="31"/>
-      <c r="AE23" s="31"/>
-      <c r="AF23" s="31"/>
-      <c r="AG23" s="31"/>
-      <c r="AH23" s="31"/>
-      <c r="AI23" s="31"/>
-      <c r="AJ23" s="31"/>
-      <c r="AK23" s="31"/>
-      <c r="AL23" s="31"/>
-      <c r="AM23" s="31"/>
-      <c r="AN23" s="31"/>
-      <c r="AO23" s="31"/>
-      <c r="AP23" s="31"/>
-      <c r="AQ23" s="31"/>
-      <c r="AR23" s="31"/>
-      <c r="AS23" s="31"/>
-      <c r="AT23" s="31"/>
-      <c r="AU23" s="31"/>
-      <c r="AV23" s="31"/>
-      <c r="AW23" s="31"/>
-      <c r="AX23" s="31"/>
-      <c r="AY23" s="31"/>
-    </row>
-    <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="39"/>
+      <c r="Q23" s="32"/>
+      <c r="R23" s="32"/>
+      <c r="S23" s="32"/>
+      <c r="T23" s="32"/>
+      <c r="U23" s="32"/>
+      <c r="V23" s="32"/>
+      <c r="W23" s="32"/>
+      <c r="X23" s="32"/>
+      <c r="Y23" s="32"/>
+      <c r="Z23" s="32"/>
+      <c r="AA23" s="32"/>
+      <c r="AB23" s="32"/>
+      <c r="AC23" s="32"/>
+      <c r="AD23" s="32"/>
+      <c r="AE23" s="32"/>
+      <c r="AF23" s="32"/>
+      <c r="AG23" s="32"/>
+      <c r="AH23" s="32"/>
+      <c r="AI23" s="32"/>
+      <c r="AJ23" s="32"/>
+      <c r="AK23" s="32"/>
+      <c r="AL23" s="32"/>
+      <c r="AM23" s="32"/>
+      <c r="AN23" s="32"/>
+      <c r="AO23" s="32"/>
+      <c r="AP23" s="32"/>
+      <c r="AQ23" s="32"/>
+      <c r="AR23" s="32"/>
+      <c r="AS23" s="32"/>
+      <c r="AT23" s="32"/>
+      <c r="AU23" s="32"/>
+      <c r="AV23" s="32"/>
+      <c r="AW23" s="32"/>
+      <c r="AX23" s="32"/>
+      <c r="AY23" s="32"/>
+    </row>
+    <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24" s="7" t="str">
         <v>Few_indicators_closest_DLS_coverage</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="Q24" s="32"/>
+      <c r="R24" s="32"/>
+      <c r="S24" s="32"/>
+      <c r="T24" s="32"/>
+      <c r="U24" s="32"/>
+      <c r="V24" s="32"/>
+      <c r="W24" s="32"/>
+      <c r="X24" s="32"/>
+      <c r="Y24" s="32"/>
+      <c r="Z24" s="32"/>
+      <c r="AA24" s="32"/>
+      <c r="AB24" s="32"/>
+      <c r="AC24" s="32"/>
+      <c r="AD24" s="32"/>
+      <c r="AE24" s="32"/>
+      <c r="AF24" s="32"/>
+      <c r="AG24" s="32"/>
+      <c r="AH24" s="32"/>
+      <c r="AI24" s="32"/>
+      <c r="AJ24" s="32"/>
+      <c r="AK24" s="32"/>
+      <c r="AL24" s="32"/>
+      <c r="AM24" s="32"/>
+      <c r="AN24" s="32"/>
+      <c r="AO24" s="32"/>
+      <c r="AP24" s="32"/>
+      <c r="AQ24" s="32"/>
+      <c r="AR24" s="32"/>
+      <c r="AS24" s="32"/>
+      <c r="AT24" s="32"/>
+      <c r="AU24" s="32"/>
+      <c r="AV24" s="32"/>
+      <c r="AW24" s="32"/>
+      <c r="AX24" s="32"/>
+      <c r="AY24" s="32"/>
+    </row>
+    <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25" s="7" t="str">
+        <v>Few_indicators_SPI_preferred</v>
+      </c>
+      <c r="C25" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="38"/>
-      <c r="Q24" s="31"/>
-      <c r="R24" s="31"/>
-      <c r="S24" s="31"/>
-      <c r="T24" s="31"/>
-      <c r="U24" s="31"/>
-      <c r="V24" s="31"/>
-      <c r="W24" s="31"/>
-      <c r="X24" s="31"/>
-      <c r="Y24" s="31"/>
-      <c r="Z24" s="31"/>
-      <c r="AA24" s="31"/>
-      <c r="AB24" s="31"/>
-      <c r="AC24" s="31"/>
-      <c r="AD24" s="31"/>
-      <c r="AE24" s="31"/>
-      <c r="AF24" s="31"/>
-      <c r="AG24" s="31"/>
-      <c r="AH24" s="31"/>
-      <c r="AI24" s="31"/>
-      <c r="AJ24" s="31"/>
-      <c r="AK24" s="31"/>
-      <c r="AL24" s="31"/>
-      <c r="AM24" s="31"/>
-      <c r="AN24" s="31"/>
-      <c r="AO24" s="31"/>
-      <c r="AP24" s="31"/>
-      <c r="AQ24" s="31"/>
-      <c r="AR24" s="31"/>
-      <c r="AS24" s="31"/>
-      <c r="AT24" s="31"/>
-      <c r="AU24" s="31"/>
-      <c r="AV24" s="31"/>
-      <c r="AW24" s="31"/>
-      <c r="AX24" s="31"/>
-      <c r="AY24" s="31"/>
-    </row>
-    <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>1</v>
-      </c>
-      <c r="B25" s="7" t="str">
-        <v>Few indicators_SPI_preferred</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="38"/>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="38"/>
-      <c r="AB25" s="31"/>
-      <c r="AC25" s="31"/>
-      <c r="AD25" s="31"/>
-      <c r="AE25" s="31"/>
-      <c r="AF25" s="31"/>
-      <c r="AG25" s="31"/>
-      <c r="AH25" s="31"/>
-      <c r="AI25" s="31"/>
-      <c r="AJ25" s="31"/>
-      <c r="AK25" s="31"/>
-      <c r="AL25" s="31"/>
-      <c r="AM25" s="31"/>
-      <c r="AN25" s="31"/>
-      <c r="AO25" s="31"/>
-      <c r="AP25" s="31"/>
-      <c r="AQ25" s="31"/>
-    </row>
-    <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="39"/>
+      <c r="AB25" s="32"/>
+      <c r="AC25" s="32"/>
+      <c r="AD25" s="32"/>
+      <c r="AE25" s="32"/>
+      <c r="AF25" s="32"/>
+      <c r="AG25" s="32"/>
+      <c r="AH25" s="32"/>
+      <c r="AI25" s="32"/>
+      <c r="AJ25" s="32"/>
+      <c r="AK25" s="32"/>
+      <c r="AL25" s="32"/>
+      <c r="AM25" s="32"/>
+      <c r="AN25" s="32"/>
+      <c r="AO25" s="32"/>
+      <c r="AP25" s="32"/>
+      <c r="AQ25" s="32"/>
+    </row>
+    <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26" s="7" t="str">
         <v>No_non_DLS</v>
       </c>
-      <c r="C26" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="38"/>
-      <c r="L26" s="38"/>
-      <c r="M26" s="38"/>
-      <c r="N26" s="38"/>
-      <c r="O26" s="38"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
-      <c r="S26" s="31"/>
-      <c r="T26" s="31"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="31"/>
-      <c r="W26" s="31"/>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="31"/>
-      <c r="Z26" s="31"/>
-      <c r="AA26" s="31"/>
-      <c r="AB26" s="31"/>
-      <c r="AC26" s="31"/>
-      <c r="AD26" s="31"/>
-      <c r="AE26" s="31"/>
-      <c r="AF26" s="31"/>
-      <c r="AG26" s="31"/>
-      <c r="AH26" s="31"/>
-      <c r="AI26" s="31"/>
-      <c r="AJ26" s="31"/>
-      <c r="AK26" s="31"/>
-      <c r="AL26" s="31"/>
-      <c r="AM26" s="31"/>
-      <c r="AN26" s="31"/>
-      <c r="AO26" s="31"/>
-      <c r="AP26" s="31"/>
-      <c r="AQ26" s="31"/>
-    </row>
-    <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="39"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="32"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="32"/>
+      <c r="X26" s="32"/>
+      <c r="Y26" s="32"/>
+      <c r="Z26" s="32"/>
+      <c r="AA26" s="32"/>
+      <c r="AB26" s="32"/>
+      <c r="AC26" s="32"/>
+      <c r="AD26" s="32"/>
+      <c r="AE26" s="32"/>
+      <c r="AF26" s="32"/>
+      <c r="AG26" s="32"/>
+      <c r="AH26" s="32"/>
+      <c r="AI26" s="32"/>
+      <c r="AJ26" s="32"/>
+      <c r="AK26" s="32"/>
+      <c r="AL26" s="32"/>
+      <c r="AM26" s="32"/>
+      <c r="AN26" s="32"/>
+      <c r="AO26" s="32"/>
+      <c r="AP26" s="32"/>
+      <c r="AQ26" s="32"/>
+    </row>
+    <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27" s="26" t="str">
         <v>Only_%_of_pop</v>
       </c>
-      <c r="C27" s="45" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="38"/>
-      <c r="J27" s="38"/>
-      <c r="K27" s="38"/>
-      <c r="L27" s="38"/>
-      <c r="M27" s="38"/>
-      <c r="N27" s="38"/>
-      <c r="O27" s="38"/>
-      <c r="Q27" s="31"/>
-      <c r="R27" s="31"/>
-      <c r="S27" s="31"/>
-      <c r="T27" s="31"/>
-      <c r="U27" s="31"/>
-      <c r="V27" s="31"/>
-      <c r="W27" s="31"/>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="31"/>
-      <c r="Z27" s="31"/>
-      <c r="AA27" s="31"/>
-      <c r="AB27" s="31"/>
-      <c r="AC27" s="31"/>
-      <c r="AD27" s="31"/>
-      <c r="AE27" s="31"/>
-      <c r="AF27" s="31"/>
-      <c r="AG27" s="31"/>
-      <c r="AH27" s="31"/>
-      <c r="AI27" s="31"/>
-      <c r="AJ27" s="31"/>
-      <c r="AK27" s="31"/>
-      <c r="AL27" s="31"/>
-      <c r="AM27" s="31"/>
-      <c r="AN27" s="31"/>
-      <c r="AO27" s="31"/>
-      <c r="AP27" s="31"/>
-      <c r="AQ27" s="31"/>
-    </row>
-    <row r="28" spans="1:51" ht="65.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="39"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="39"/>
+      <c r="Q27" s="32"/>
+      <c r="R27" s="32"/>
+      <c r="S27" s="32"/>
+      <c r="T27" s="32"/>
+      <c r="U27" s="32"/>
+      <c r="V27" s="32"/>
+      <c r="W27" s="32"/>
+      <c r="X27" s="32"/>
+      <c r="Y27" s="32"/>
+      <c r="Z27" s="32"/>
+      <c r="AA27" s="32"/>
+      <c r="AB27" s="32"/>
+      <c r="AC27" s="32"/>
+      <c r="AD27" s="32"/>
+      <c r="AE27" s="32"/>
+      <c r="AF27" s="32"/>
+      <c r="AG27" s="32"/>
+      <c r="AH27" s="32"/>
+      <c r="AI27" s="32"/>
+      <c r="AJ27" s="32"/>
+      <c r="AK27" s="32"/>
+      <c r="AL27" s="32"/>
+      <c r="AM27" s="32"/>
+      <c r="AN27" s="32"/>
+      <c r="AO27" s="32"/>
+      <c r="AP27" s="32"/>
+      <c r="AQ27" s="32"/>
+    </row>
+    <row r="28" spans="1:51" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" s="17" t="str">
         <v>Few_indicators_closest_DLS_coverage_90</v>
       </c>
-      <c r="C28" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="36"/>
-      <c r="K28" s="36"/>
-      <c r="L28" s="36"/>
-      <c r="M28" s="36"/>
-      <c r="N28" s="36"/>
-      <c r="O28" s="36"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="31"/>
-      <c r="V28" s="31"/>
-      <c r="W28" s="31"/>
-      <c r="X28" s="31"/>
-      <c r="Y28" s="31"/>
-      <c r="Z28" s="31"/>
-      <c r="AA28" s="31"/>
-      <c r="AB28" s="31"/>
-      <c r="AC28" s="31"/>
-      <c r="AD28" s="31"/>
-      <c r="AE28" s="31"/>
-      <c r="AF28" s="31"/>
-      <c r="AG28" s="31"/>
-      <c r="AH28" s="31"/>
-      <c r="AI28" s="31"/>
-      <c r="AJ28" s="31"/>
-      <c r="AK28" s="31"/>
-      <c r="AL28" s="31"/>
-      <c r="AM28" s="31"/>
-      <c r="AN28" s="31"/>
-      <c r="AO28" s="31"/>
-      <c r="AP28" s="31"/>
-      <c r="AQ28" s="31"/>
-    </row>
-    <row r="29" spans="1:51" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
+      <c r="O28" s="37"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="32"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="32"/>
+      <c r="X28" s="32"/>
+      <c r="Y28" s="32"/>
+      <c r="Z28" s="32"/>
+      <c r="AA28" s="32"/>
+      <c r="AB28" s="32"/>
+      <c r="AC28" s="32"/>
+      <c r="AD28" s="32"/>
+      <c r="AE28" s="32"/>
+      <c r="AF28" s="32"/>
+      <c r="AG28" s="32"/>
+      <c r="AH28" s="32"/>
+      <c r="AI28" s="32"/>
+      <c r="AJ28" s="32"/>
+      <c r="AK28" s="32"/>
+      <c r="AL28" s="32"/>
+      <c r="AM28" s="32"/>
+      <c r="AN28" s="32"/>
+      <c r="AO28" s="32"/>
+      <c r="AP28" s="32"/>
+      <c r="AQ28" s="32"/>
+    </row>
+    <row r="29" spans="1:51" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2</v>
       </c>
       <c r="B29" s="17" t="str">
-        <v>Few indicators_SPI_preferred_90</v>
-      </c>
-      <c r="C29" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="36"/>
-      <c r="K29" s="36"/>
-      <c r="L29" s="36"/>
-      <c r="M29" s="36"/>
-      <c r="N29" s="36"/>
-      <c r="O29" s="36"/>
-      <c r="Q29" s="31"/>
-      <c r="R29" s="31"/>
-      <c r="S29" s="31"/>
-      <c r="T29" s="31"/>
-      <c r="U29" s="31"/>
-      <c r="V29" s="31"/>
-      <c r="W29" s="31"/>
-      <c r="X29" s="31"/>
-      <c r="Y29" s="31"/>
-      <c r="Z29" s="31"/>
-      <c r="AA29" s="31"/>
-      <c r="AB29" s="31"/>
-      <c r="AC29" s="31"/>
-      <c r="AD29" s="31"/>
-      <c r="AE29" s="31"/>
-      <c r="AF29" s="31"/>
-      <c r="AG29" s="31"/>
-      <c r="AH29" s="31"/>
-      <c r="AI29" s="31"/>
-      <c r="AJ29" s="31"/>
-      <c r="AK29" s="31"/>
-      <c r="AL29" s="31"/>
-      <c r="AM29" s="31"/>
-      <c r="AN29" s="31"/>
-      <c r="AO29" s="31"/>
-      <c r="AP29" s="31"/>
-      <c r="AQ29" s="31"/>
-    </row>
-    <row r="30" spans="1:51" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>Few_indicators_SPI_preferred_90</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="37"/>
+      <c r="K29" s="37"/>
+      <c r="L29" s="37"/>
+      <c r="M29" s="37"/>
+      <c r="N29" s="37"/>
+      <c r="O29" s="37"/>
+      <c r="Q29" s="32"/>
+      <c r="R29" s="32"/>
+      <c r="S29" s="32"/>
+      <c r="T29" s="32"/>
+      <c r="U29" s="32"/>
+      <c r="V29" s="32"/>
+      <c r="W29" s="32"/>
+      <c r="X29" s="32"/>
+      <c r="Y29" s="32"/>
+      <c r="Z29" s="32"/>
+      <c r="AA29" s="32"/>
+      <c r="AB29" s="32"/>
+      <c r="AC29" s="32"/>
+      <c r="AD29" s="32"/>
+      <c r="AE29" s="32"/>
+      <c r="AF29" s="32"/>
+      <c r="AG29" s="32"/>
+      <c r="AH29" s="32"/>
+      <c r="AI29" s="32"/>
+      <c r="AJ29" s="32"/>
+      <c r="AK29" s="32"/>
+      <c r="AL29" s="32"/>
+      <c r="AM29" s="32"/>
+      <c r="AN29" s="32"/>
+      <c r="AO29" s="32"/>
+      <c r="AP29" s="32"/>
+      <c r="AQ29" s="32"/>
+    </row>
+    <row r="30" spans="1:51" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
       <c r="B30" s="17" t="str">
         <v>Few_indicators_closeDLS_subPrimSchool</v>
       </c>
-      <c r="C30" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
-      <c r="K30" s="36"/>
-      <c r="L30" s="36"/>
-      <c r="M30" s="36"/>
-      <c r="N30" s="36"/>
-      <c r="O30" s="36"/>
-      <c r="Q30" s="31"/>
-      <c r="R30" s="31"/>
-      <c r="S30" s="31"/>
-      <c r="T30" s="31"/>
-      <c r="U30" s="31"/>
-      <c r="V30" s="31"/>
-      <c r="W30" s="31"/>
-      <c r="X30" s="31"/>
-      <c r="Y30" s="31"/>
-      <c r="Z30" s="31"/>
-      <c r="AA30" s="31"/>
-      <c r="AB30" s="31"/>
-      <c r="AC30" s="31"/>
-      <c r="AD30" s="31"/>
-      <c r="AE30" s="31"/>
-      <c r="AF30" s="31"/>
-      <c r="AG30" s="31"/>
-      <c r="AH30" s="31"/>
-      <c r="AI30" s="31"/>
-      <c r="AJ30" s="31"/>
-      <c r="AK30" s="31"/>
-      <c r="AL30" s="31"/>
-      <c r="AM30" s="31"/>
-      <c r="AN30" s="31"/>
-      <c r="AO30" s="31"/>
-      <c r="AP30" s="31"/>
-      <c r="AQ30" s="31"/>
-    </row>
-    <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="33"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="37"/>
+      <c r="M30" s="37"/>
+      <c r="N30" s="37"/>
+      <c r="O30" s="37"/>
+      <c r="Q30" s="32"/>
+      <c r="R30" s="32"/>
+      <c r="S30" s="32"/>
+      <c r="T30" s="32"/>
+      <c r="U30" s="32"/>
+      <c r="V30" s="32"/>
+      <c r="W30" s="32"/>
+      <c r="X30" s="32"/>
+      <c r="Y30" s="32"/>
+      <c r="Z30" s="32"/>
+      <c r="AA30" s="32"/>
+      <c r="AB30" s="32"/>
+      <c r="AC30" s="32"/>
+      <c r="AD30" s="32"/>
+      <c r="AE30" s="32"/>
+      <c r="AF30" s="32"/>
+      <c r="AG30" s="32"/>
+      <c r="AH30" s="32"/>
+      <c r="AI30" s="32"/>
+      <c r="AJ30" s="32"/>
+      <c r="AK30" s="32"/>
+      <c r="AL30" s="32"/>
+      <c r="AM30" s="32"/>
+      <c r="AN30" s="32"/>
+      <c r="AO30" s="32"/>
+      <c r="AP30" s="32"/>
+      <c r="AQ30" s="32"/>
+    </row>
+    <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
       <c r="B31" s="27" t="str">
         <v>No_non_DLS_90</v>
       </c>
-      <c r="C31" s="48" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="J31" s="48"/>
-      <c r="K31" s="48"/>
-      <c r="L31" s="48"/>
-      <c r="M31" s="48"/>
-      <c r="N31" s="48"/>
-      <c r="O31" s="48"/>
-      <c r="Q31" s="31"/>
-      <c r="R31" s="31"/>
-      <c r="S31" s="31"/>
-      <c r="T31" s="31"/>
-      <c r="U31" s="31"/>
-      <c r="V31" s="31"/>
-      <c r="W31" s="31"/>
-      <c r="X31" s="31"/>
-      <c r="Y31" s="31"/>
-      <c r="Z31" s="31"/>
-      <c r="AA31" s="31"/>
-      <c r="AB31" s="31"/>
-      <c r="AC31" s="31"/>
-      <c r="AD31" s="31"/>
-      <c r="AE31" s="31"/>
-      <c r="AF31" s="31"/>
-      <c r="AG31" s="31"/>
-      <c r="AH31" s="31"/>
-      <c r="AI31" s="31"/>
-      <c r="AJ31" s="31"/>
-      <c r="AK31" s="31"/>
-      <c r="AL31" s="31"/>
-      <c r="AM31" s="31"/>
-      <c r="AN31" s="31"/>
-      <c r="AO31" s="31"/>
-      <c r="AP31" s="31"/>
-      <c r="AQ31" s="31"/>
-    </row>
-    <row r="32" spans="1:51" ht="103.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="49"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="J31" s="49"/>
+      <c r="K31" s="49"/>
+      <c r="L31" s="49"/>
+      <c r="M31" s="49"/>
+      <c r="N31" s="49"/>
+      <c r="O31" s="49"/>
+      <c r="Q31" s="32"/>
+      <c r="R31" s="32"/>
+      <c r="S31" s="32"/>
+      <c r="T31" s="32"/>
+      <c r="U31" s="32"/>
+      <c r="V31" s="32"/>
+      <c r="W31" s="32"/>
+      <c r="X31" s="32"/>
+      <c r="Y31" s="32"/>
+      <c r="Z31" s="32"/>
+      <c r="AA31" s="32"/>
+      <c r="AB31" s="32"/>
+      <c r="AC31" s="32"/>
+      <c r="AD31" s="32"/>
+      <c r="AE31" s="32"/>
+      <c r="AF31" s="32"/>
+      <c r="AG31" s="32"/>
+      <c r="AH31" s="32"/>
+      <c r="AI31" s="32"/>
+      <c r="AJ31" s="32"/>
+      <c r="AK31" s="32"/>
+      <c r="AL31" s="32"/>
+      <c r="AM31" s="32"/>
+      <c r="AN31" s="32"/>
+      <c r="AO31" s="32"/>
+      <c r="AP31" s="32"/>
+      <c r="AQ31" s="32"/>
+    </row>
+    <row r="32" spans="1:51" ht="103.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
       <c r="B32" s="27" t="str">
         <v>Few_Indicators_subWatSani</v>
       </c>
-      <c r="C32" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="36"/>
-      <c r="L32" s="36"/>
-      <c r="M32" s="36"/>
-      <c r="N32" s="36"/>
-      <c r="O32" s="36"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="31"/>
-      <c r="T32" s="31"/>
-      <c r="U32" s="31"/>
-      <c r="V32" s="31"/>
-      <c r="W32" s="31"/>
-      <c r="X32" s="31"/>
-      <c r="Y32" s="31"/>
-      <c r="Z32" s="31"/>
-      <c r="AA32" s="31"/>
-      <c r="AB32" s="31"/>
-      <c r="AC32" s="31"/>
-      <c r="AD32" s="31"/>
-      <c r="AE32" s="31"/>
-      <c r="AF32" s="31"/>
-      <c r="AG32" s="31"/>
-      <c r="AH32" s="31"/>
-      <c r="AI32" s="31"/>
-      <c r="AJ32" s="31"/>
-      <c r="AK32" s="31"/>
-      <c r="AL32" s="31"/>
-      <c r="AM32" s="31"/>
-      <c r="AN32" s="31"/>
-      <c r="AO32" s="31"/>
-      <c r="AP32" s="31"/>
-      <c r="AQ32" s="31"/>
-    </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="C32" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="49"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="49"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="49"/>
+      <c r="I32" s="37"/>
+      <c r="J32" s="37"/>
+      <c r="K32" s="37"/>
+      <c r="L32" s="37"/>
+      <c r="M32" s="37"/>
+      <c r="N32" s="37"/>
+      <c r="O32" s="37"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
+      <c r="V32" s="32"/>
+      <c r="W32" s="32"/>
+      <c r="X32" s="32"/>
+      <c r="Y32" s="32"/>
+      <c r="Z32" s="32"/>
+      <c r="AA32" s="32"/>
+      <c r="AB32" s="32"/>
+      <c r="AC32" s="32"/>
+      <c r="AD32" s="32"/>
+      <c r="AE32" s="32"/>
+      <c r="AF32" s="32"/>
+      <c r="AG32" s="32"/>
+      <c r="AH32" s="32"/>
+      <c r="AI32" s="32"/>
+      <c r="AJ32" s="32"/>
+      <c r="AK32" s="32"/>
+      <c r="AL32" s="32"/>
+      <c r="AM32" s="32"/>
+      <c r="AN32" s="32"/>
+      <c r="AO32" s="32"/>
+      <c r="AP32" s="32"/>
+      <c r="AQ32" s="32"/>
+    </row>
+    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>4</v>
       </c>
       <c r="B33" s="28" t="str">
         <v>Only_OPP</v>
       </c>
-      <c r="C33" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" s="49"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="49"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="49"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
-      <c r="O33" s="33"/>
-      <c r="Q33" s="31"/>
-      <c r="R33" s="31"/>
-      <c r="S33" s="31"/>
-      <c r="T33" s="31"/>
-      <c r="U33" s="31"/>
-      <c r="V33" s="31"/>
-      <c r="W33" s="31"/>
-      <c r="X33" s="31"/>
-      <c r="Y33" s="31"/>
-      <c r="Z33" s="31"/>
-      <c r="AA33" s="31"/>
-      <c r="AB33" s="31"/>
-      <c r="AC33" s="31"/>
-      <c r="AD33" s="31"/>
-      <c r="AE33" s="31"/>
-      <c r="AF33" s="31"/>
-      <c r="AG33" s="31"/>
-      <c r="AH33" s="31"/>
-      <c r="AI33" s="31"/>
-      <c r="AJ33" s="31"/>
-      <c r="AK33" s="31"/>
-      <c r="AL33" s="31"/>
-      <c r="AM33" s="31"/>
-      <c r="AN33" s="31"/>
-      <c r="AO33" s="31"/>
-      <c r="AP33" s="31"/>
-      <c r="AQ33" s="31"/>
-    </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="C33" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="50"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="34"/>
+      <c r="K33" s="34"/>
+      <c r="L33" s="34"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
+      <c r="O33" s="34"/>
+      <c r="Q33" s="32"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="32"/>
+      <c r="T33" s="32"/>
+      <c r="U33" s="32"/>
+      <c r="V33" s="32"/>
+      <c r="W33" s="32"/>
+      <c r="X33" s="32"/>
+      <c r="Y33" s="32"/>
+      <c r="Z33" s="32"/>
+      <c r="AA33" s="32"/>
+      <c r="AB33" s="32"/>
+      <c r="AC33" s="32"/>
+      <c r="AD33" s="32"/>
+      <c r="AE33" s="32"/>
+      <c r="AF33" s="32"/>
+      <c r="AG33" s="32"/>
+      <c r="AH33" s="32"/>
+      <c r="AI33" s="32"/>
+      <c r="AJ33" s="32"/>
+      <c r="AK33" s="32"/>
+      <c r="AL33" s="32"/>
+      <c r="AM33" s="32"/>
+      <c r="AN33" s="32"/>
+      <c r="AO33" s="32"/>
+      <c r="AP33" s="32"/>
+      <c r="AQ33" s="32"/>
+    </row>
+    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
       <c r="B34" s="6" t="str">
         <v>Baseline</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="33"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="33"/>
-      <c r="N34" s="33"/>
-      <c r="O34" s="33"/>
-      <c r="Q34" s="31"/>
-      <c r="R34" s="31"/>
-      <c r="S34" s="31"/>
-      <c r="T34" s="31"/>
-      <c r="U34" s="31"/>
-      <c r="V34" s="31"/>
-      <c r="W34" s="31"/>
-      <c r="X34" s="31"/>
-      <c r="Y34" s="31"/>
-      <c r="Z34" s="31"/>
-      <c r="AA34" s="31"/>
-      <c r="AB34" s="31"/>
-      <c r="AC34" s="31"/>
-      <c r="AD34" s="31"/>
-      <c r="AE34" s="31"/>
-      <c r="AF34" s="31"/>
-      <c r="AG34" s="31"/>
-      <c r="AH34" s="31"/>
-      <c r="AI34" s="31"/>
-      <c r="AJ34" s="31"/>
-      <c r="AK34" s="31"/>
-      <c r="AL34" s="31"/>
-      <c r="AM34" s="31"/>
-      <c r="AN34" s="31"/>
-      <c r="AO34" s="31"/>
-      <c r="AP34" s="31"/>
-      <c r="AQ34" s="31"/>
-    </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="34"/>
+      <c r="N34" s="34"/>
+      <c r="O34" s="34"/>
+      <c r="Q34" s="32"/>
+      <c r="R34" s="32"/>
+      <c r="S34" s="32"/>
+      <c r="T34" s="32"/>
+      <c r="U34" s="32"/>
+      <c r="V34" s="32"/>
+      <c r="W34" s="32"/>
+      <c r="X34" s="32"/>
+      <c r="Y34" s="32"/>
+      <c r="Z34" s="32"/>
+      <c r="AA34" s="32"/>
+      <c r="AB34" s="32"/>
+      <c r="AC34" s="32"/>
+      <c r="AD34" s="32"/>
+      <c r="AE34" s="32"/>
+      <c r="AF34" s="32"/>
+      <c r="AG34" s="32"/>
+      <c r="AH34" s="32"/>
+      <c r="AI34" s="32"/>
+      <c r="AJ34" s="32"/>
+      <c r="AK34" s="32"/>
+      <c r="AL34" s="32"/>
+      <c r="AM34" s="32"/>
+      <c r="AN34" s="32"/>
+      <c r="AO34" s="32"/>
+      <c r="AP34" s="32"/>
+      <c r="AQ34" s="32"/>
+    </row>
+    <row r="35" spans="1:43" x14ac:dyDescent="0.3">
       <c r="B35" s="28" t="str">
         <v>No_nonDLS_limExt</v>
       </c>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="46" t="s">
-        <v>73</v>
-      </c>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
-      <c r="L35" s="46"/>
-      <c r="M35" s="46"/>
-      <c r="N35" s="46"/>
-      <c r="O35" s="46"/>
-      <c r="Q35" s="31"/>
-      <c r="R35" s="31"/>
-      <c r="S35" s="31"/>
-      <c r="T35" s="31"/>
-      <c r="U35" s="31"/>
-      <c r="V35" s="31"/>
-      <c r="W35" s="31"/>
-      <c r="X35" s="31"/>
-      <c r="Y35" s="31"/>
-      <c r="Z35" s="31"/>
-      <c r="AA35" s="31"/>
-      <c r="AB35" s="31"/>
-      <c r="AC35" s="31"/>
-      <c r="AD35" s="31"/>
-      <c r="AE35" s="31"/>
-      <c r="AF35" s="31"/>
-      <c r="AG35" s="31"/>
-      <c r="AH35" s="31"/>
-      <c r="AI35" s="31"/>
-      <c r="AJ35" s="31"/>
-      <c r="AK35" s="31"/>
-      <c r="AL35" s="31"/>
-      <c r="AM35" s="31"/>
-      <c r="AN35" s="31"/>
-      <c r="AO35" s="31"/>
-      <c r="AP35" s="31"/>
-      <c r="AQ35" s="31"/>
-    </row>
-    <row r="36" spans="1:43" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="J35" s="47"/>
+      <c r="K35" s="47"/>
+      <c r="L35" s="47"/>
+      <c r="M35" s="47"/>
+      <c r="N35" s="47"/>
+      <c r="O35" s="47"/>
+      <c r="Q35" s="32"/>
+      <c r="R35" s="32"/>
+      <c r="S35" s="32"/>
+      <c r="T35" s="32"/>
+      <c r="U35" s="32"/>
+      <c r="V35" s="32"/>
+      <c r="W35" s="32"/>
+      <c r="X35" s="32"/>
+      <c r="Y35" s="32"/>
+      <c r="Z35" s="32"/>
+      <c r="AA35" s="32"/>
+      <c r="AB35" s="32"/>
+      <c r="AC35" s="32"/>
+      <c r="AD35" s="32"/>
+      <c r="AE35" s="32"/>
+      <c r="AF35" s="32"/>
+      <c r="AG35" s="32"/>
+      <c r="AH35" s="32"/>
+      <c r="AI35" s="32"/>
+      <c r="AJ35" s="32"/>
+      <c r="AK35" s="32"/>
+      <c r="AL35" s="32"/>
+      <c r="AM35" s="32"/>
+      <c r="AN35" s="32"/>
+      <c r="AO35" s="32"/>
+      <c r="AP35" s="32"/>
+      <c r="AQ35" s="32"/>
+    </row>
+    <row r="36" spans="1:43" ht="76.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="str">
         <v>BHN</v>
       </c>
-      <c r="C36" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="D36" s="37"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="37"/>
-      <c r="H36" s="37"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="33"/>
-      <c r="M36" s="33"/>
-      <c r="N36" s="33"/>
-      <c r="O36" s="33"/>
-      <c r="Q36" s="31"/>
-      <c r="R36" s="31"/>
-      <c r="S36" s="31"/>
-      <c r="T36" s="31"/>
-      <c r="U36" s="31"/>
-      <c r="V36" s="31"/>
-      <c r="W36" s="31"/>
-      <c r="X36" s="31"/>
-      <c r="Y36" s="31"/>
-      <c r="Z36" s="31"/>
-      <c r="AA36" s="31"/>
-      <c r="AB36" s="31"/>
-      <c r="AC36" s="31"/>
-      <c r="AD36" s="31"/>
-      <c r="AE36" s="31"/>
-      <c r="AF36" s="31"/>
-      <c r="AG36" s="31"/>
-      <c r="AH36" s="31"/>
-      <c r="AI36" s="31"/>
-      <c r="AJ36" s="31"/>
-      <c r="AK36" s="31"/>
-      <c r="AL36" s="31"/>
-      <c r="AM36" s="31"/>
-      <c r="AN36" s="31"/>
-      <c r="AO36" s="31"/>
-      <c r="AP36" s="31"/>
-      <c r="AQ36" s="31"/>
-    </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="C36" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="34"/>
+      <c r="J36" s="34"/>
+      <c r="K36" s="34"/>
+      <c r="L36" s="34"/>
+      <c r="M36" s="34"/>
+      <c r="N36" s="34"/>
+      <c r="O36" s="34"/>
+      <c r="Q36" s="32"/>
+      <c r="R36" s="32"/>
+      <c r="S36" s="32"/>
+      <c r="T36" s="32"/>
+      <c r="U36" s="32"/>
+      <c r="V36" s="32"/>
+      <c r="W36" s="32"/>
+      <c r="X36" s="32"/>
+      <c r="Y36" s="32"/>
+      <c r="Z36" s="32"/>
+      <c r="AA36" s="32"/>
+      <c r="AB36" s="32"/>
+      <c r="AC36" s="32"/>
+      <c r="AD36" s="32"/>
+      <c r="AE36" s="32"/>
+      <c r="AF36" s="32"/>
+      <c r="AG36" s="32"/>
+      <c r="AH36" s="32"/>
+      <c r="AI36" s="32"/>
+      <c r="AJ36" s="32"/>
+      <c r="AK36" s="32"/>
+      <c r="AL36" s="32"/>
+      <c r="AM36" s="32"/>
+      <c r="AN36" s="32"/>
+      <c r="AO36" s="32"/>
+      <c r="AP36" s="32"/>
+      <c r="AQ36" s="32"/>
+    </row>
+    <row r="37" spans="1:43" x14ac:dyDescent="0.3">
       <c r="B37" t="str">
         <v>No_non_DLS_BHNFWB</v>
       </c>
-      <c r="AB37" s="31"/>
-      <c r="AC37" s="31"/>
-      <c r="AD37" s="31"/>
-      <c r="AE37" s="31"/>
-      <c r="AF37" s="31"/>
-      <c r="AG37" s="31"/>
-      <c r="AH37" s="31"/>
-      <c r="AI37" s="31"/>
-      <c r="AJ37" s="31"/>
-      <c r="AK37" s="31"/>
-      <c r="AL37" s="31"/>
-      <c r="AM37" s="31"/>
-      <c r="AN37" s="31"/>
-      <c r="AO37" s="31"/>
-      <c r="AP37" s="31"/>
-      <c r="AQ37" s="31"/>
-    </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB38" s="31"/>
-      <c r="AC38" s="31"/>
-      <c r="AD38" s="31"/>
-      <c r="AE38" s="31"/>
-      <c r="AF38" s="31"/>
-      <c r="AG38" s="31"/>
-      <c r="AH38" s="31"/>
-      <c r="AI38" s="31"/>
-      <c r="AJ38" s="31"/>
-      <c r="AK38" s="31"/>
-      <c r="AL38" s="31"/>
-      <c r="AM38" s="31"/>
-      <c r="AN38" s="31"/>
-      <c r="AO38" s="31"/>
-      <c r="AP38" s="31"/>
-      <c r="AQ38" s="31"/>
-    </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB39" s="31"/>
-      <c r="AC39" s="31"/>
-      <c r="AD39" s="31"/>
-      <c r="AE39" s="31"/>
-      <c r="AF39" s="31"/>
-      <c r="AG39" s="31"/>
-      <c r="AH39" s="31"/>
-      <c r="AI39" s="31"/>
-      <c r="AJ39" s="31"/>
-      <c r="AK39" s="31"/>
-      <c r="AL39" s="31"/>
-      <c r="AM39" s="31"/>
-      <c r="AN39" s="31"/>
-      <c r="AO39" s="31"/>
-      <c r="AP39" s="31"/>
-      <c r="AQ39" s="31"/>
-    </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB40" s="31"/>
-      <c r="AC40" s="31"/>
-      <c r="AD40" s="31"/>
-      <c r="AE40" s="31"/>
-      <c r="AF40" s="31"/>
-      <c r="AG40" s="31"/>
-      <c r="AH40" s="31"/>
-      <c r="AI40" s="31"/>
-      <c r="AJ40" s="31"/>
-      <c r="AK40" s="31"/>
-      <c r="AL40" s="31"/>
-      <c r="AM40" s="31"/>
-      <c r="AN40" s="31"/>
-      <c r="AO40" s="31"/>
-      <c r="AP40" s="31"/>
-      <c r="AQ40" s="31"/>
-    </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB41" s="31"/>
-      <c r="AC41" s="31"/>
-      <c r="AD41" s="31"/>
-      <c r="AE41" s="31"/>
-      <c r="AF41" s="31"/>
-      <c r="AG41" s="31"/>
-      <c r="AH41" s="31"/>
-      <c r="AI41" s="31"/>
-      <c r="AJ41" s="31"/>
-      <c r="AK41" s="31"/>
-      <c r="AL41" s="31"/>
-      <c r="AM41" s="31"/>
-      <c r="AN41" s="31"/>
-      <c r="AO41" s="31"/>
-      <c r="AP41" s="31"/>
-      <c r="AQ41" s="31"/>
-    </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB42" s="31" t="e" vm="8">
+      <c r="AB37" s="32"/>
+      <c r="AC37" s="32"/>
+      <c r="AD37" s="32"/>
+      <c r="AE37" s="32"/>
+      <c r="AF37" s="32"/>
+      <c r="AG37" s="32"/>
+      <c r="AH37" s="32"/>
+      <c r="AI37" s="32"/>
+      <c r="AJ37" s="32"/>
+      <c r="AK37" s="32"/>
+      <c r="AL37" s="32"/>
+      <c r="AM37" s="32"/>
+      <c r="AN37" s="32"/>
+      <c r="AO37" s="32"/>
+      <c r="AP37" s="32"/>
+      <c r="AQ37" s="32"/>
+    </row>
+    <row r="38" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB38" s="32"/>
+      <c r="AC38" s="32"/>
+      <c r="AD38" s="32"/>
+      <c r="AE38" s="32"/>
+      <c r="AF38" s="32"/>
+      <c r="AG38" s="32"/>
+      <c r="AH38" s="32"/>
+      <c r="AI38" s="32"/>
+      <c r="AJ38" s="32"/>
+      <c r="AK38" s="32"/>
+      <c r="AL38" s="32"/>
+      <c r="AM38" s="32"/>
+      <c r="AN38" s="32"/>
+      <c r="AO38" s="32"/>
+      <c r="AP38" s="32"/>
+      <c r="AQ38" s="32"/>
+    </row>
+    <row r="39" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB39" s="32"/>
+      <c r="AC39" s="32"/>
+      <c r="AD39" s="32"/>
+      <c r="AE39" s="32"/>
+      <c r="AF39" s="32"/>
+      <c r="AG39" s="32"/>
+      <c r="AH39" s="32"/>
+      <c r="AI39" s="32"/>
+      <c r="AJ39" s="32"/>
+      <c r="AK39" s="32"/>
+      <c r="AL39" s="32"/>
+      <c r="AM39" s="32"/>
+      <c r="AN39" s="32"/>
+      <c r="AO39" s="32"/>
+      <c r="AP39" s="32"/>
+      <c r="AQ39" s="32"/>
+    </row>
+    <row r="40" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB40" s="32"/>
+      <c r="AC40" s="32"/>
+      <c r="AD40" s="32"/>
+      <c r="AE40" s="32"/>
+      <c r="AF40" s="32"/>
+      <c r="AG40" s="32"/>
+      <c r="AH40" s="32"/>
+      <c r="AI40" s="32"/>
+      <c r="AJ40" s="32"/>
+      <c r="AK40" s="32"/>
+      <c r="AL40" s="32"/>
+      <c r="AM40" s="32"/>
+      <c r="AN40" s="32"/>
+      <c r="AO40" s="32"/>
+      <c r="AP40" s="32"/>
+      <c r="AQ40" s="32"/>
+    </row>
+    <row r="41" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB41" s="32"/>
+      <c r="AC41" s="32"/>
+      <c r="AD41" s="32"/>
+      <c r="AE41" s="32"/>
+      <c r="AF41" s="32"/>
+      <c r="AG41" s="32"/>
+      <c r="AH41" s="32"/>
+      <c r="AI41" s="32"/>
+      <c r="AJ41" s="32"/>
+      <c r="AK41" s="32"/>
+      <c r="AL41" s="32"/>
+      <c r="AM41" s="32"/>
+      <c r="AN41" s="32"/>
+      <c r="AO41" s="32"/>
+      <c r="AP41" s="32"/>
+      <c r="AQ41" s="32"/>
+    </row>
+    <row r="42" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB42" s="32" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-      <c r="AC42" s="31"/>
-      <c r="AD42" s="31"/>
-      <c r="AE42" s="31"/>
-      <c r="AF42" s="31"/>
-      <c r="AG42" s="31"/>
-      <c r="AH42" s="31"/>
-      <c r="AI42" s="31"/>
-      <c r="AJ42" s="31"/>
-      <c r="AK42" s="31"/>
-      <c r="AL42" s="31"/>
-      <c r="AM42" s="31"/>
-      <c r="AN42" s="31"/>
-      <c r="AO42" s="31"/>
-      <c r="AP42" s="31"/>
-      <c r="AQ42" s="31"/>
-    </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB43" s="31"/>
-      <c r="AC43" s="31"/>
-      <c r="AD43" s="31"/>
-      <c r="AE43" s="31"/>
-      <c r="AF43" s="31"/>
-      <c r="AG43" s="31"/>
-      <c r="AH43" s="31"/>
-      <c r="AI43" s="31"/>
-      <c r="AJ43" s="31"/>
-      <c r="AK43" s="31"/>
-      <c r="AL43" s="31"/>
-      <c r="AM43" s="31"/>
-      <c r="AN43" s="31"/>
-      <c r="AO43" s="31"/>
-      <c r="AP43" s="31"/>
-      <c r="AQ43" s="31"/>
-    </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB44" s="31"/>
-      <c r="AC44" s="31"/>
-      <c r="AD44" s="31"/>
-      <c r="AE44" s="31"/>
-      <c r="AF44" s="31"/>
-      <c r="AG44" s="31"/>
-      <c r="AH44" s="31"/>
-      <c r="AI44" s="31"/>
-      <c r="AJ44" s="31"/>
-      <c r="AK44" s="31"/>
-      <c r="AL44" s="31"/>
-      <c r="AM44" s="31"/>
-      <c r="AN44" s="31"/>
-      <c r="AO44" s="31"/>
-      <c r="AP44" s="31"/>
-      <c r="AQ44" s="31"/>
-    </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB45" s="31"/>
-      <c r="AC45" s="31"/>
-      <c r="AD45" s="31"/>
-      <c r="AE45" s="31"/>
-      <c r="AF45" s="31"/>
-      <c r="AG45" s="31"/>
-      <c r="AH45" s="31"/>
-      <c r="AI45" s="31"/>
-      <c r="AJ45" s="31"/>
-      <c r="AK45" s="31"/>
-      <c r="AL45" s="31"/>
-      <c r="AM45" s="31"/>
-      <c r="AN45" s="31"/>
-      <c r="AO45" s="31"/>
-      <c r="AP45" s="31"/>
-      <c r="AQ45" s="31"/>
-    </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB46" s="31"/>
-      <c r="AC46" s="31"/>
-      <c r="AD46" s="31"/>
-      <c r="AE46" s="31"/>
-      <c r="AF46" s="31"/>
-      <c r="AG46" s="31"/>
-      <c r="AH46" s="31"/>
-      <c r="AI46" s="31"/>
-      <c r="AJ46" s="31"/>
-      <c r="AK46" s="31"/>
-      <c r="AL46" s="31"/>
-      <c r="AM46" s="31"/>
-      <c r="AN46" s="31"/>
-      <c r="AO46" s="31"/>
-      <c r="AP46" s="31"/>
-      <c r="AQ46" s="31"/>
-    </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB47" s="31"/>
-      <c r="AC47" s="31"/>
-      <c r="AD47" s="31"/>
-      <c r="AE47" s="31"/>
-      <c r="AF47" s="31"/>
-      <c r="AG47" s="31"/>
-      <c r="AH47" s="31"/>
-      <c r="AI47" s="31"/>
-      <c r="AJ47" s="31"/>
-      <c r="AK47" s="31"/>
-      <c r="AL47" s="31"/>
-      <c r="AM47" s="31"/>
-      <c r="AN47" s="31"/>
-      <c r="AO47" s="31"/>
-      <c r="AP47" s="31"/>
-      <c r="AQ47" s="31"/>
-    </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="AB48" s="31"/>
-      <c r="AC48" s="31"/>
-      <c r="AD48" s="31"/>
-      <c r="AE48" s="31"/>
-      <c r="AF48" s="31"/>
-      <c r="AG48" s="31"/>
-      <c r="AH48" s="31"/>
-      <c r="AI48" s="31"/>
-      <c r="AJ48" s="31"/>
-      <c r="AK48" s="31"/>
-      <c r="AL48" s="31"/>
-      <c r="AM48" s="31"/>
-      <c r="AN48" s="31"/>
-      <c r="AO48" s="31"/>
-      <c r="AP48" s="31"/>
-      <c r="AQ48" s="31"/>
-    </row>
-    <row r="49" spans="28:43" x14ac:dyDescent="0.25">
-      <c r="AB49" s="31"/>
-      <c r="AC49" s="31"/>
-      <c r="AD49" s="31"/>
-      <c r="AE49" s="31"/>
-      <c r="AF49" s="31"/>
-      <c r="AG49" s="31"/>
-      <c r="AH49" s="31"/>
-      <c r="AI49" s="31"/>
-      <c r="AJ49" s="31"/>
-      <c r="AK49" s="31"/>
-      <c r="AL49" s="31"/>
-      <c r="AM49" s="31"/>
-      <c r="AN49" s="31"/>
-      <c r="AO49" s="31"/>
-      <c r="AP49" s="31"/>
-      <c r="AQ49" s="31"/>
-    </row>
-    <row r="50" spans="28:43" x14ac:dyDescent="0.25">
-      <c r="AB50" s="31"/>
-      <c r="AC50" s="31"/>
-      <c r="AD50" s="31"/>
-      <c r="AE50" s="31"/>
-      <c r="AF50" s="31"/>
-      <c r="AG50" s="31"/>
-      <c r="AH50" s="31"/>
-      <c r="AI50" s="31"/>
-      <c r="AJ50" s="31"/>
-      <c r="AK50" s="31"/>
-      <c r="AL50" s="31"/>
-      <c r="AM50" s="31"/>
-      <c r="AN50" s="31"/>
-      <c r="AO50" s="31"/>
-      <c r="AP50" s="31"/>
-      <c r="AQ50" s="31"/>
-    </row>
-    <row r="51" spans="28:43" x14ac:dyDescent="0.25">
-      <c r="AB51" s="31"/>
-      <c r="AC51" s="31"/>
-      <c r="AD51" s="31"/>
-      <c r="AE51" s="31"/>
-      <c r="AF51" s="31"/>
-      <c r="AG51" s="31"/>
-      <c r="AH51" s="31"/>
-      <c r="AI51" s="31"/>
-      <c r="AJ51" s="31"/>
-      <c r="AK51" s="31"/>
-      <c r="AL51" s="31"/>
-      <c r="AM51" s="31"/>
-      <c r="AN51" s="31"/>
-      <c r="AO51" s="31"/>
-      <c r="AP51" s="31"/>
-      <c r="AQ51" s="31"/>
-    </row>
-    <row r="52" spans="28:43" x14ac:dyDescent="0.25">
-      <c r="AB52" s="31"/>
-      <c r="AC52" s="31"/>
-      <c r="AD52" s="31"/>
-      <c r="AE52" s="31"/>
-      <c r="AF52" s="31"/>
-      <c r="AG52" s="31"/>
-      <c r="AH52" s="31"/>
-      <c r="AI52" s="31"/>
-      <c r="AJ52" s="31"/>
-      <c r="AK52" s="31"/>
-      <c r="AL52" s="31"/>
-      <c r="AM52" s="31"/>
-      <c r="AN52" s="31"/>
-      <c r="AO52" s="31"/>
-      <c r="AP52" s="31"/>
-      <c r="AQ52" s="31"/>
-    </row>
-    <row r="53" spans="28:43" x14ac:dyDescent="0.25">
-      <c r="AB53" s="31"/>
-      <c r="AC53" s="31"/>
-      <c r="AD53" s="31"/>
-      <c r="AE53" s="31"/>
-      <c r="AF53" s="31"/>
-      <c r="AG53" s="31"/>
-      <c r="AH53" s="31"/>
-      <c r="AI53" s="31"/>
-      <c r="AJ53" s="31"/>
-      <c r="AK53" s="31"/>
-      <c r="AL53" s="31"/>
-      <c r="AM53" s="31"/>
-      <c r="AN53" s="31"/>
-      <c r="AO53" s="31"/>
-      <c r="AP53" s="31"/>
-      <c r="AQ53" s="31"/>
+      <c r="AC42" s="32"/>
+      <c r="AD42" s="32"/>
+      <c r="AE42" s="32"/>
+      <c r="AF42" s="32"/>
+      <c r="AG42" s="32"/>
+      <c r="AH42" s="32"/>
+      <c r="AI42" s="32"/>
+      <c r="AJ42" s="32"/>
+      <c r="AK42" s="32"/>
+      <c r="AL42" s="32"/>
+      <c r="AM42" s="32"/>
+      <c r="AN42" s="32"/>
+      <c r="AO42" s="32"/>
+      <c r="AP42" s="32"/>
+      <c r="AQ42" s="32"/>
+    </row>
+    <row r="43" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB43" s="32"/>
+      <c r="AC43" s="32"/>
+      <c r="AD43" s="32"/>
+      <c r="AE43" s="32"/>
+      <c r="AF43" s="32"/>
+      <c r="AG43" s="32"/>
+      <c r="AH43" s="32"/>
+      <c r="AI43" s="32"/>
+      <c r="AJ43" s="32"/>
+      <c r="AK43" s="32"/>
+      <c r="AL43" s="32"/>
+      <c r="AM43" s="32"/>
+      <c r="AN43" s="32"/>
+      <c r="AO43" s="32"/>
+      <c r="AP43" s="32"/>
+      <c r="AQ43" s="32"/>
+    </row>
+    <row r="44" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB44" s="32"/>
+      <c r="AC44" s="32"/>
+      <c r="AD44" s="32"/>
+      <c r="AE44" s="32"/>
+      <c r="AF44" s="32"/>
+      <c r="AG44" s="32"/>
+      <c r="AH44" s="32"/>
+      <c r="AI44" s="32"/>
+      <c r="AJ44" s="32"/>
+      <c r="AK44" s="32"/>
+      <c r="AL44" s="32"/>
+      <c r="AM44" s="32"/>
+      <c r="AN44" s="32"/>
+      <c r="AO44" s="32"/>
+      <c r="AP44" s="32"/>
+      <c r="AQ44" s="32"/>
+    </row>
+    <row r="45" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB45" s="32"/>
+      <c r="AC45" s="32"/>
+      <c r="AD45" s="32"/>
+      <c r="AE45" s="32"/>
+      <c r="AF45" s="32"/>
+      <c r="AG45" s="32"/>
+      <c r="AH45" s="32"/>
+      <c r="AI45" s="32"/>
+      <c r="AJ45" s="32"/>
+      <c r="AK45" s="32"/>
+      <c r="AL45" s="32"/>
+      <c r="AM45" s="32"/>
+      <c r="AN45" s="32"/>
+      <c r="AO45" s="32"/>
+      <c r="AP45" s="32"/>
+      <c r="AQ45" s="32"/>
+    </row>
+    <row r="46" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB46" s="32"/>
+      <c r="AC46" s="32"/>
+      <c r="AD46" s="32"/>
+      <c r="AE46" s="32"/>
+      <c r="AF46" s="32"/>
+      <c r="AG46" s="32"/>
+      <c r="AH46" s="32"/>
+      <c r="AI46" s="32"/>
+      <c r="AJ46" s="32"/>
+      <c r="AK46" s="32"/>
+      <c r="AL46" s="32"/>
+      <c r="AM46" s="32"/>
+      <c r="AN46" s="32"/>
+      <c r="AO46" s="32"/>
+      <c r="AP46" s="32"/>
+      <c r="AQ46" s="32"/>
+    </row>
+    <row r="47" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB47" s="32"/>
+      <c r="AC47" s="32"/>
+      <c r="AD47" s="32"/>
+      <c r="AE47" s="32"/>
+      <c r="AF47" s="32"/>
+      <c r="AG47" s="32"/>
+      <c r="AH47" s="32"/>
+      <c r="AI47" s="32"/>
+      <c r="AJ47" s="32"/>
+      <c r="AK47" s="32"/>
+      <c r="AL47" s="32"/>
+      <c r="AM47" s="32"/>
+      <c r="AN47" s="32"/>
+      <c r="AO47" s="32"/>
+      <c r="AP47" s="32"/>
+      <c r="AQ47" s="32"/>
+    </row>
+    <row r="48" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AB48" s="32"/>
+      <c r="AC48" s="32"/>
+      <c r="AD48" s="32"/>
+      <c r="AE48" s="32"/>
+      <c r="AF48" s="32"/>
+      <c r="AG48" s="32"/>
+      <c r="AH48" s="32"/>
+      <c r="AI48" s="32"/>
+      <c r="AJ48" s="32"/>
+      <c r="AK48" s="32"/>
+      <c r="AL48" s="32"/>
+      <c r="AM48" s="32"/>
+      <c r="AN48" s="32"/>
+      <c r="AO48" s="32"/>
+      <c r="AP48" s="32"/>
+      <c r="AQ48" s="32"/>
+    </row>
+    <row r="49" spans="28:43" x14ac:dyDescent="0.3">
+      <c r="AB49" s="32"/>
+      <c r="AC49" s="32"/>
+      <c r="AD49" s="32"/>
+      <c r="AE49" s="32"/>
+      <c r="AF49" s="32"/>
+      <c r="AG49" s="32"/>
+      <c r="AH49" s="32"/>
+      <c r="AI49" s="32"/>
+      <c r="AJ49" s="32"/>
+      <c r="AK49" s="32"/>
+      <c r="AL49" s="32"/>
+      <c r="AM49" s="32"/>
+      <c r="AN49" s="32"/>
+      <c r="AO49" s="32"/>
+      <c r="AP49" s="32"/>
+      <c r="AQ49" s="32"/>
+    </row>
+    <row r="50" spans="28:43" x14ac:dyDescent="0.3">
+      <c r="AB50" s="32"/>
+      <c r="AC50" s="32"/>
+      <c r="AD50" s="32"/>
+      <c r="AE50" s="32"/>
+      <c r="AF50" s="32"/>
+      <c r="AG50" s="32"/>
+      <c r="AH50" s="32"/>
+      <c r="AI50" s="32"/>
+      <c r="AJ50" s="32"/>
+      <c r="AK50" s="32"/>
+      <c r="AL50" s="32"/>
+      <c r="AM50" s="32"/>
+      <c r="AN50" s="32"/>
+      <c r="AO50" s="32"/>
+      <c r="AP50" s="32"/>
+      <c r="AQ50" s="32"/>
+    </row>
+    <row r="51" spans="28:43" x14ac:dyDescent="0.3">
+      <c r="AB51" s="32"/>
+      <c r="AC51" s="32"/>
+      <c r="AD51" s="32"/>
+      <c r="AE51" s="32"/>
+      <c r="AF51" s="32"/>
+      <c r="AG51" s="32"/>
+      <c r="AH51" s="32"/>
+      <c r="AI51" s="32"/>
+      <c r="AJ51" s="32"/>
+      <c r="AK51" s="32"/>
+      <c r="AL51" s="32"/>
+      <c r="AM51" s="32"/>
+      <c r="AN51" s="32"/>
+      <c r="AO51" s="32"/>
+      <c r="AP51" s="32"/>
+      <c r="AQ51" s="32"/>
+    </row>
+    <row r="52" spans="28:43" x14ac:dyDescent="0.3">
+      <c r="AB52" s="32"/>
+      <c r="AC52" s="32"/>
+      <c r="AD52" s="32"/>
+      <c r="AE52" s="32"/>
+      <c r="AF52" s="32"/>
+      <c r="AG52" s="32"/>
+      <c r="AH52" s="32"/>
+      <c r="AI52" s="32"/>
+      <c r="AJ52" s="32"/>
+      <c r="AK52" s="32"/>
+      <c r="AL52" s="32"/>
+      <c r="AM52" s="32"/>
+      <c r="AN52" s="32"/>
+      <c r="AO52" s="32"/>
+      <c r="AP52" s="32"/>
+      <c r="AQ52" s="32"/>
+    </row>
+    <row r="53" spans="28:43" x14ac:dyDescent="0.3">
+      <c r="AB53" s="32"/>
+      <c r="AC53" s="32"/>
+      <c r="AD53" s="32"/>
+      <c r="AE53" s="32"/>
+      <c r="AF53" s="32"/>
+      <c r="AG53" s="32"/>
+      <c r="AH53" s="32"/>
+      <c r="AI53" s="32"/>
+      <c r="AJ53" s="32"/>
+      <c r="AK53" s="32"/>
+      <c r="AL53" s="32"/>
+      <c r="AM53" s="32"/>
+      <c r="AN53" s="32"/>
+      <c r="AO53" s="32"/>
+      <c r="AP53" s="32"/>
+      <c r="AQ53" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="42">
@@ -5787,24 +5797,24 @@
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:R65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S65"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="62.5703125" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="1" max="1" width="62.5546875" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" customWidth="1"/>
+    <col min="11" max="11" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>17</v>
@@ -5819,7 +5829,7 @@
         <v>39</v>
       </c>
       <c r="F1" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="G1" t="s">
         <v>37</v>
@@ -5828,37 +5838,40 @@
         <v>38</v>
       </c>
       <c r="I1" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="J1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K1" s="21" t="s">
-        <v>63</v>
-      </c>
       <c r="L1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M1" t="s">
         <v>64</v>
       </c>
-      <c r="M1" t="s">
-        <v>66</v>
-      </c>
       <c r="N1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O1" t="s">
         <v>69</v>
       </c>
-      <c r="O1" t="s">
-        <v>71</v>
-      </c>
       <c r="P1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Q1" t="s">
         <v>14</v>
       </c>
       <c r="R1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="S1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="str" cm="1">
         <f t="array" ref="A2:A53">TRANSPOSE('[1]1990-2020 Time-series data'!$Y$2:$BX$2)</f>
         <v xml:space="preserve">Child stunting (% of pop.) </v>
@@ -5914,8 +5927,11 @@
       <c r="R2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="str">
         <v>Deaths from infectious diseases (deaths/100,000)</v>
       </c>
@@ -5970,8 +5986,11 @@
       <c r="R3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="str">
         <v xml:space="preserve">Maternal mortality  (deaths/100,000 live births) </v>
       </c>
@@ -6026,8 +6045,11 @@
       <c r="R4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="str">
         <v xml:space="preserve">Nutritional deficiencies (% of pop.) </v>
       </c>
@@ -6082,8 +6104,11 @@
       <c r="R5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="str">
         <v xml:space="preserve">Diet low in fruits and vegetables (0=low risk; 100=high risk) </v>
       </c>
@@ -6138,8 +6163,11 @@
       <c r="R6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="str">
         <v xml:space="preserve">Child mortality (deaths/1,000 live births) </v>
       </c>
@@ -6194,8 +6222,11 @@
       <c r="R7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="str">
         <v xml:space="preserve">No access to a handwashing facility (0=low risk; 100=high risk) </v>
       </c>
@@ -6250,8 +6281,11 @@
       <c r="R8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="str">
         <v>Deaths from unsafe water, sanitation and hygiene (deaths/100,000)</v>
       </c>
@@ -6306,8 +6340,11 @@
       <c r="R9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="str">
         <v xml:space="preserve">Improved sanitation (proportion of pop.) </v>
       </c>
@@ -6362,8 +6399,11 @@
       <c r="R10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="str">
         <v xml:space="preserve">Improved water source (proportion of pop.) </v>
       </c>
@@ -6418,8 +6458,11 @@
       <c r="R11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="str">
         <v>Deaths from household air pollution (deaths/100,000)</v>
       </c>
@@ -6474,8 +6517,11 @@
       <c r="R12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="str">
         <v xml:space="preserve">Prevalence of cooking with coal/biomass (proportion of pop.) </v>
       </c>
@@ -6530,8 +6576,11 @@
       <c r="R13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="str">
         <v xml:space="preserve">Access to electricity (% of pop.) </v>
       </c>
@@ -6586,8 +6635,11 @@
       <c r="R14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="str">
         <v>Deaths from road injuries (deaths/100,000)</v>
       </c>
@@ -6642,8 +6694,11 @@
       <c r="R15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="str">
         <v xml:space="preserve">Political violence (0=no violence; 4=violence often) </v>
       </c>
@@ -6698,8 +6753,11 @@
       <c r="R16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="str">
         <v>Political killings and torture (0=low freedom; 1=high freedom)</v>
       </c>
@@ -6754,8 +6812,11 @@
       <c r="R17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="str">
         <v xml:space="preserve">Intimate partner violence against women (% of women aged 15+) </v>
       </c>
@@ -6810,8 +6871,11 @@
       <c r="R18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="str">
         <v>Interpersonal violence  (deaths/100,000)</v>
       </c>
@@ -6866,8 +6930,11 @@
       <c r="R19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="str">
         <v xml:space="preserve">Population with no education (proportion of pop.) </v>
       </c>
@@ -6922,8 +6989,11 @@
       <c r="R20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="str">
         <v xml:space="preserve">Gender parity in basic education (distance from parity) </v>
       </c>
@@ -6978,8 +7048,11 @@
       <c r="R21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="str">
         <v xml:space="preserve">Equal access to quality education (0=unequal; 4=equal) </v>
       </c>
@@ -7034,8 +7107,11 @@
       <c r="R22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="str">
         <v>Mean years of schooling (years)</v>
       </c>
@@ -7090,8 +7166,11 @@
       <c r="R23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="str">
         <v>Alternative sources of information (0=low; 1=high)</v>
       </c>
@@ -7146,8 +7225,11 @@
       <c r="R24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="str">
         <v xml:space="preserve">Internet users (% of pop.) </v>
       </c>
@@ -7202,8 +7284,11 @@
       <c r="R25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="str">
         <v xml:space="preserve">Mobile and landline telephone subscriptions (subscriptions/100 people) </v>
       </c>
@@ -7258,8 +7343,11 @@
       <c r="R26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="str">
         <v>Life expectancy at 60 (years)</v>
       </c>
@@ -7314,8 +7402,11 @@
       <c r="R27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="str">
         <v>Premature deaths from non-communicable diseases (deaths/100,000)</v>
       </c>
@@ -7370,8 +7461,11 @@
       <c r="R28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="str">
         <v xml:space="preserve">Equal access to quality healthcare (0=unequal; 4=equal) </v>
       </c>
@@ -7426,8 +7520,11 @@
       <c r="R29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="str">
         <v xml:space="preserve">Universal health coverage (% of pop.) </v>
       </c>
@@ -7482,8 +7579,11 @@
       <c r="R30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="str">
         <v>Deaths from outdoor air pollution (deaths/100,000)</v>
       </c>
@@ -7538,8 +7638,11 @@
       <c r="R31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="str">
         <v>Particulate matter (2.5) pollution (mean annual exposure, µg/m3)</v>
       </c>
@@ -7594,8 +7697,11 @@
       <c r="R32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="str">
         <v>Deaths from lead exposure (deaths/100,000)</v>
       </c>
@@ -7650,8 +7756,11 @@
       <c r="R33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="str">
         <v>Species protection (0=low; 100=high)</v>
       </c>
@@ -7706,8 +7815,11 @@
       <c r="R34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="str">
         <v xml:space="preserve">Freedom of religion (0=no freedom; 4=full freedom) </v>
       </c>
@@ -7762,8 +7874,11 @@
       <c r="R35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="str">
         <v xml:space="preserve">Property rights for women (0=no rights; 5=full rights) </v>
       </c>
@@ -7818,8 +7933,11 @@
       <c r="R36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="str">
         <v xml:space="preserve">Freedom of assembly (0=no freedom; 4=full freedom) </v>
       </c>
@@ -7874,8 +7992,11 @@
       <c r="R37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="str">
         <v>Access to justice (0=nonexistent; 1=observed)</v>
       </c>
@@ -7930,8 +8051,11 @@
       <c r="R38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="str">
         <v>Freedom of discussion (0=low; 1=high)</v>
       </c>
@@ -7986,8 +8110,11 @@
       <c r="R39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="str">
         <v>Political rights (1=full rights; 7=no rights)</v>
       </c>
@@ -8042,8 +8169,11 @@
       <c r="R40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="str">
         <v>Public sector corruption (0=low corruption; 1=high corruption)</v>
       </c>
@@ -8098,8 +8228,11 @@
       <c r="R41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="str">
         <v>Freedom of domestic movement (0=low; 1=high)</v>
       </c>
@@ -8154,8 +8287,11 @@
       <c r="R42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="str">
         <v>Satisfied demand for contraception (% satisfied demand)</v>
       </c>
@@ -8210,8 +8346,11 @@
       <c r="R43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="str">
         <v>Early marriage (% of married women aged 15-19)</v>
       </c>
@@ -8266,8 +8405,11 @@
       <c r="R44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="str">
         <v xml:space="preserve">Vulnerable employment (% of total employment) </v>
       </c>
@@ -8322,8 +8464,11 @@
       <c r="R45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="str">
         <v>Equal protection of social groups (0=low; 1=high)</v>
       </c>
@@ -8378,8 +8523,11 @@
       <c r="R46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="str">
         <v>Equal access to power (0=low; 1=high)</v>
       </c>
@@ -8434,8 +8582,11 @@
       <c r="R47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="str">
         <v xml:space="preserve">Power distributed by sexual orientation (0=extremely unequal; 3=equal) </v>
       </c>
@@ -8490,8 +8641,11 @@
       <c r="R48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="str">
         <v xml:space="preserve">Access to public services distributed by social group (0=extremely unequal; 4=equal) </v>
       </c>
@@ -8546,8 +8700,11 @@
       <c r="R49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="str">
         <v xml:space="preserve">Population with advanced education (proportion of pop.) </v>
       </c>
@@ -8602,8 +8759,11 @@
       <c r="R50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="str">
         <v xml:space="preserve">Gender parity in advanced education (distance from parity) </v>
       </c>
@@ -8658,8 +8818,11 @@
       <c r="R51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="str">
         <v>Respect for academic freedom (0=low; 1=high)</v>
       </c>
@@ -8714,8 +8877,11 @@
       <c r="R52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="str">
         <v>Years of tertiary schooling (years)</v>
       </c>
@@ -8770,8 +8936,11 @@
       <c r="R53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>2</v>
       </c>
@@ -8826,8 +8995,11 @@
       <c r="R54">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>3</v>
       </c>
@@ -8882,8 +9054,11 @@
       <c r="R55">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -8938,8 +9113,11 @@
       <c r="R56">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -8994,8 +9172,11 @@
       <c r="R57">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -9050,8 +9231,11 @@
       <c r="R58">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -9106,8 +9290,11 @@
       <c r="R59">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -9162,8 +9349,11 @@
       <c r="R60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -9218,8 +9408,11 @@
       <c r="R61">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -9229,8 +9422,8 @@
       <c r="C62">
         <v>0</v>
       </c>
-      <c r="D62">
-        <v>1</v>
+      <c r="D62" s="30">
+        <v>0</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -9238,8 +9431,8 @@
       <c r="F62">
         <v>0</v>
       </c>
-      <c r="G62">
-        <v>1</v>
+      <c r="G62" s="30">
+        <v>0</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -9253,8 +9446,8 @@
       <c r="K62" s="21">
         <v>0</v>
       </c>
-      <c r="L62">
-        <v>1</v>
+      <c r="L62" s="30">
+        <v>0</v>
       </c>
       <c r="M62">
         <v>0</v>
@@ -9271,11 +9464,14 @@
       <c r="Q62">
         <v>0</v>
       </c>
-      <c r="R62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R62" s="30">
+        <v>0</v>
+      </c>
+      <c r="S62" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -9330,8 +9526,11 @@
       <c r="R63">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>12</v>
       </c>
@@ -9386,8 +9585,11 @@
       <c r="R64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="S64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>27</v>
       </c>
@@ -9403,13 +9605,13 @@
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A3:D67"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="61.7109375" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="61.6640625" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -9420,7 +9622,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -9432,7 +9634,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="str">
         <v>Deaths from infectious diseases (deaths/100,000)</v>
       </c>
@@ -9440,7 +9642,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="str">
         <v xml:space="preserve">Maternal mortality  (deaths/100,000 live births) </v>
       </c>
@@ -9448,7 +9650,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="str">
         <v xml:space="preserve">Nutritional deficiencies (% of pop.) </v>
       </c>
@@ -9456,7 +9658,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="str">
         <v xml:space="preserve">Diet low in fruits and vegetables (0=low risk; 100=high risk) </v>
       </c>
@@ -9464,7 +9666,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="str">
         <v xml:space="preserve">Child mortality (deaths/1,000 live births) </v>
       </c>
@@ -9472,7 +9674,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="str">
         <v xml:space="preserve">No access to a handwashing facility (0=low risk; 100=high risk) </v>
       </c>
@@ -9480,7 +9682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="str">
         <v>Deaths from unsafe water, sanitation and hygiene (deaths/100,000)</v>
       </c>
@@ -9488,7 +9690,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="str">
         <v xml:space="preserve">Improved sanitation (proportion of pop.) </v>
       </c>
@@ -9496,7 +9698,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="str">
         <v xml:space="preserve">Improved water source (proportion of pop.) </v>
       </c>
@@ -9504,7 +9706,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -9515,7 +9717,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="str">
         <v xml:space="preserve">Prevalence of cooking with coal/biomass (proportion of pop.) </v>
       </c>
@@ -9523,7 +9725,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="str">
         <v xml:space="preserve">Access to electricity (% of pop.) </v>
       </c>
@@ -9531,7 +9733,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="str">
         <v>Deaths from road injuries (deaths/100,000)</v>
       </c>
@@ -9539,7 +9741,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="str">
         <v xml:space="preserve">Political violence (0=no violence; 4=violence often) </v>
       </c>
@@ -9547,7 +9749,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="str">
         <v>Political killings and torture (0=low freedom; 1=high freedom)</v>
       </c>
@@ -9555,7 +9757,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="str">
         <v xml:space="preserve">Intimate partner violence against women (% of women aged 15+) </v>
       </c>
@@ -9563,7 +9765,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="str">
         <v>Interpersonal violence  (deaths/100,000)</v>
       </c>
@@ -9571,7 +9773,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="str">
         <v xml:space="preserve">Population with no education (proportion of pop.) </v>
       </c>
@@ -9579,7 +9781,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="str">
         <v xml:space="preserve">Gender parity in basic education (distance from parity) </v>
       </c>
@@ -9587,7 +9789,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="str">
         <v xml:space="preserve">Equal access to quality education (0=unequal; 4=equal) </v>
       </c>
@@ -9595,7 +9797,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="str">
         <v>Mean years of schooling (years)</v>
       </c>
@@ -9603,7 +9805,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="str">
         <v>Alternative sources of information (0=low; 1=high)</v>
       </c>
@@ -9611,7 +9813,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="str">
         <v xml:space="preserve">Internet users (% of pop.) </v>
       </c>
@@ -9619,7 +9821,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="str">
         <v xml:space="preserve">Mobile and landline telephone subscriptions (subscriptions/100 people) </v>
       </c>
@@ -9627,7 +9829,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="str">
         <v>Life expectancy at 60 (years)</v>
       </c>
@@ -9635,7 +9837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="str">
         <v>Premature deaths from non-communicable diseases (deaths/100,000)</v>
       </c>
@@ -9643,7 +9845,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="str">
         <v xml:space="preserve">Equal access to quality healthcare (0=unequal; 4=equal) </v>
       </c>
@@ -9651,7 +9853,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="str">
         <v xml:space="preserve">Universal health coverage (% of pop.) </v>
       </c>
@@ -9659,7 +9861,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B33" s="2" t="str">
         <v>Deaths from outdoor air pollution (deaths/100,000)</v>
       </c>
@@ -9667,7 +9869,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B34" s="2" t="str">
         <v>Particulate matter (2.5) pollution (mean annual exposure, µg/m3)</v>
       </c>
@@ -9675,7 +9877,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B35" s="2" t="str">
         <v>Deaths from lead exposure (deaths/100,000)</v>
       </c>
@@ -9683,7 +9885,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="str">
         <v>Species protection (0=low; 100=high)</v>
       </c>
@@ -9691,7 +9893,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -9702,7 +9904,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="str">
         <v xml:space="preserve">Property rights for women (0=no rights; 5=full rights) </v>
       </c>
@@ -9710,7 +9912,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="str">
         <v xml:space="preserve">Freedom of assembly (0=no freedom; 4=full freedom) </v>
       </c>
@@ -9718,7 +9920,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="str">
         <v>Access to justice (0=nonexistent; 1=observed)</v>
       </c>
@@ -9726,7 +9928,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="str">
         <v>Freedom of discussion (0=low; 1=high)</v>
       </c>
@@ -9734,7 +9936,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="str">
         <v>Political rights (1=full rights; 7=no rights)</v>
       </c>
@@ -9742,7 +9944,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="str">
         <v>Public sector corruption (0=low corruption; 1=high corruption)</v>
       </c>
@@ -9750,7 +9952,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="str">
         <v>Freedom of domestic movement (0=low; 1=high)</v>
       </c>
@@ -9758,7 +9960,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="str">
         <v>Satisfied demand for contraception (% satisfied demand)</v>
       </c>
@@ -9766,7 +9968,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="str">
         <v>Early marriage (% of married women aged 15-19)</v>
       </c>
@@ -9774,7 +9976,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="str">
         <v xml:space="preserve">Vulnerable employment (% of total employment) </v>
       </c>
@@ -9782,7 +9984,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="str">
         <v>Equal protection of social groups (0=low; 1=high)</v>
       </c>
@@ -9790,7 +9992,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="str">
         <v>Equal access to power (0=low; 1=high)</v>
       </c>
@@ -9798,7 +10000,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="str">
         <v xml:space="preserve">Power distributed by sexual orientation (0=extremely unequal; 3=equal) </v>
       </c>
@@ -9806,7 +10008,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="str">
         <v xml:space="preserve">Access to public services distributed by social group (0=extremely unequal; 4=equal) </v>
       </c>
@@ -9814,7 +10016,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="str">
         <v xml:space="preserve">Population with advanced education (proportion of pop.) </v>
       </c>
@@ -9822,7 +10024,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="str">
         <v xml:space="preserve">Gender parity in advanced education (distance from parity) </v>
       </c>
@@ -9830,7 +10032,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="str">
         <v>Respect for academic freedom (0=low; 1=high)</v>
       </c>
@@ -9838,7 +10040,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="str">
         <v>Years of tertiary schooling (years)</v>
       </c>
@@ -9846,7 +10048,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>1</v>
       </c>
@@ -9857,7 +10059,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>3</v>
       </c>
@@ -9865,7 +10067,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>4</v>
       </c>
@@ -9873,7 +10075,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>5</v>
       </c>
@@ -9881,7 +10083,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>7</v>
       </c>
@@ -9889,7 +10091,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>6</v>
       </c>
@@ -9897,7 +10099,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>8</v>
       </c>
@@ -9905,7 +10107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>9</v>
       </c>
@@ -9913,7 +10115,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>10</v>
       </c>
@@ -9921,7 +10123,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>11</v>
       </c>
@@ -9929,7 +10131,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>12</v>
       </c>
@@ -9937,7 +10139,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C67" t="s">
         <v>27</v>
       </c>

--- a/IndicatorsForClusters.xlsx
+++ b/IndicatorsForClusters.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1c3256d208fb6548/Personlig/Aske Banke Consultancy/YALE/Metodeartikel_WorldDevelopmentJournal/WorldDevelopmentArticleGit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="476" documentId="8_{9856C943-DD01-465B-AD17-0E409E296684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D884123-63F0-48D2-9055-F60C3EFE3D6D}"/>
+  <xr:revisionPtr revIDLastSave="543" documentId="8_{9856C943-DD01-465B-AD17-0E409E296684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8878DECD-3FB3-4C5B-B7AB-34D399F750D7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{726B2859-724A-4801-8E74-5A4E1AFAB973}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{726B2859-724A-4801-8E74-5A4E1AFAB973}"/>
   </bookViews>
   <sheets>
     <sheet name="Unscaled Experiments" sheetId="2" r:id="rId1"/>
     <sheet name="Scaled Experiments" sheetId="5" r:id="rId2"/>
     <sheet name="Experiments" sheetId="3" r:id="rId3"/>
     <sheet name="Overview of indicators and DLS" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -169,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="88">
   <si>
     <t>SPI</t>
   </si>
@@ -414,6 +415,30 @@
   <si>
     <t>Few_indicators_SPI_preferred</t>
   </si>
+  <si>
+    <t>SPI_Extended</t>
+  </si>
+  <si>
+    <t>DLS_dim_only</t>
+  </si>
+  <si>
+    <t>DLS_dim_only_limExt</t>
+  </si>
+  <si>
+    <t>DLS_dim_only_BHNFWB</t>
+  </si>
+  <si>
+    <t>DLSFew_coverage</t>
+  </si>
+  <si>
+    <t>DLSFew_coverage_90</t>
+  </si>
+  <si>
+    <t>DLSFew_bestAlignment</t>
+  </si>
+  <si>
+    <t>DLSFew_bestAlignment_90</t>
+  </si>
 </sst>
 </file>
 
@@ -587,7 +612,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -633,38 +658,14 @@
       <alignment textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -675,11 +676,41 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -687,17 +718,40 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1334,35 +1388,35 @@
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AY53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.33203125" customWidth="1"/>
+    <col min="2" max="2" width="35.28515625" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
-    <col min="5" max="16" width="4.33203125" customWidth="1"/>
-    <col min="19" max="19" width="8.88671875" customWidth="1"/>
+    <col min="5" max="16" width="4.28515625" customWidth="1"/>
+    <col min="19" max="19" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="42" t="s">
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="J3" s="43"/>
+      <c r="J3" s="35"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
@@ -1376,7 +1430,7 @@
       <c r="W3" s="22"/>
       <c r="X3" s="22"/>
     </row>
-    <row r="4" spans="1:24" ht="221.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" ht="221.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="15" t="s">
         <v>16</v>
       </c>
@@ -1426,15 +1480,15 @@
       <c r="Q4" s="9" t="str">
         <v>BHN</v>
       </c>
-      <c r="T4" s="31" t="s">
+      <c r="T4" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="U4" s="31"/>
-      <c r="V4" s="31"/>
-      <c r="W4" s="31"/>
-      <c r="X4" s="31"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="U4" s="43"/>
+      <c r="V4" s="43"/>
+      <c r="W4" s="43"/>
+      <c r="X4" s="43"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="str" cm="1">
         <f t="array" ref="B5:B15">_xlfn.UNIQUE('Overview of indicators and DLS'!C4:C67)</f>
         <v>Food &amp; Nutrition</v>
@@ -1503,7 +1557,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="str">
         <v>Health Care</v>
       </c>
@@ -1568,7 +1622,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="str">
         <v>Water</v>
       </c>
@@ -1633,7 +1687,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="str">
         <v>Sanitation</v>
       </c>
@@ -1698,7 +1752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="str">
         <v>Food preparation</v>
       </c>
@@ -1763,7 +1817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="str">
         <v>Thermal comfort</v>
       </c>
@@ -1828,7 +1882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="str">
         <v>Non material / Non-DLS</v>
       </c>
@@ -1893,7 +1947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="str">
         <v>Education</v>
       </c>
@@ -1958,7 +2012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="str">
         <v>Social connectedness</v>
       </c>
@@ -2023,7 +2077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="str">
         <v>Housing</v>
       </c>
@@ -2088,7 +2142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B15" s="13" t="str">
         <v>Physical Connectedness</v>
       </c>
@@ -2156,7 +2210,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B16" s="11"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
@@ -2174,7 +2228,7 @@
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>33</v>
       </c>
@@ -2239,7 +2293,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
         <v>34</v>
       </c>
@@ -2304,7 +2358,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B19" s="11" t="s">
         <v>35</v>
       </c>
@@ -2369,30 +2423,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>55</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="44" t="s">
+      <c r="C21" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44" t="s">
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="J21" s="44"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="44"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
       <c r="Q21" s="1" t="s">
         <v>58</v>
       </c>
@@ -2400,7 +2454,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:51" ht="90.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:51" ht="90.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1</v>
       </c>
@@ -2408,1097 +2462,1102 @@
         <f t="array" ref="B22:B36">TRANSPOSE(_xlfn.ANCHORARRAY(C4))</f>
         <v>BHN_FWB</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="39"/>
-      <c r="O22" s="39"/>
-      <c r="Q22" s="32" t="e" vm="1">
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="33"/>
+      <c r="Q22" s="41" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="R22" s="32"/>
-      <c r="S22" s="32"/>
-      <c r="T22" s="32"/>
-      <c r="U22" s="32"/>
-      <c r="V22" s="32"/>
-      <c r="W22" s="32"/>
-      <c r="X22" s="32"/>
-      <c r="Y22" s="32"/>
-      <c r="Z22" s="32"/>
-      <c r="AA22" s="32"/>
-      <c r="AB22" s="32" t="e" vm="2">
+      <c r="R22" s="41"/>
+      <c r="S22" s="41"/>
+      <c r="T22" s="41"/>
+      <c r="U22" s="41"/>
+      <c r="V22" s="41"/>
+      <c r="W22" s="41"/>
+      <c r="X22" s="41"/>
+      <c r="Y22" s="41"/>
+      <c r="Z22" s="41"/>
+      <c r="AA22" s="41"/>
+      <c r="AB22" s="41" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="AC22" s="32"/>
-      <c r="AD22" s="32"/>
-      <c r="AE22" s="32"/>
-      <c r="AF22" s="32"/>
-      <c r="AG22" s="32"/>
-      <c r="AH22" s="32"/>
-      <c r="AI22" s="32"/>
-      <c r="AJ22" s="32"/>
-      <c r="AK22" s="32"/>
-      <c r="AL22" s="32"/>
-      <c r="AM22" s="32"/>
-      <c r="AN22" s="32"/>
-      <c r="AO22" s="32"/>
-      <c r="AP22" s="32"/>
-      <c r="AQ22" s="32"/>
-      <c r="AR22" s="32" t="e" vm="3">
+      <c r="AC22" s="41"/>
+      <c r="AD22" s="41"/>
+      <c r="AE22" s="41"/>
+      <c r="AF22" s="41"/>
+      <c r="AG22" s="41"/>
+      <c r="AH22" s="41"/>
+      <c r="AI22" s="41"/>
+      <c r="AJ22" s="41"/>
+      <c r="AK22" s="41"/>
+      <c r="AL22" s="41"/>
+      <c r="AM22" s="41"/>
+      <c r="AN22" s="41"/>
+      <c r="AO22" s="41"/>
+      <c r="AP22" s="41"/>
+      <c r="AQ22" s="41"/>
+      <c r="AR22" s="41" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="AS22" s="32"/>
-      <c r="AT22" s="32"/>
-      <c r="AU22" s="32"/>
-      <c r="AV22" s="32"/>
-      <c r="AW22" s="32"/>
-      <c r="AX22" s="32"/>
-      <c r="AY22" s="32"/>
-    </row>
-    <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AS22" s="41"/>
+      <c r="AT22" s="41"/>
+      <c r="AU22" s="41"/>
+      <c r="AV22" s="41"/>
+      <c r="AW22" s="41"/>
+      <c r="AX22" s="41"/>
+      <c r="AY22" s="41"/>
+    </row>
+    <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23" s="7" t="str">
         <v>BHN_FWB_AllExt</v>
       </c>
-      <c r="C23" s="40" t="s">
+      <c r="C23" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="39"/>
-      <c r="Q23" s="32"/>
-      <c r="R23" s="32"/>
-      <c r="S23" s="32"/>
-      <c r="T23" s="32"/>
-      <c r="U23" s="32"/>
-      <c r="V23" s="32"/>
-      <c r="W23" s="32"/>
-      <c r="X23" s="32"/>
-      <c r="Y23" s="32"/>
-      <c r="Z23" s="32"/>
-      <c r="AA23" s="32"/>
-      <c r="AB23" s="32"/>
-      <c r="AC23" s="32"/>
-      <c r="AD23" s="32"/>
-      <c r="AE23" s="32"/>
-      <c r="AF23" s="32"/>
-      <c r="AG23" s="32"/>
-      <c r="AH23" s="32"/>
-      <c r="AI23" s="32"/>
-      <c r="AJ23" s="32"/>
-      <c r="AK23" s="32"/>
-      <c r="AL23" s="32"/>
-      <c r="AM23" s="32"/>
-      <c r="AN23" s="32"/>
-      <c r="AO23" s="32"/>
-      <c r="AP23" s="32"/>
-      <c r="AQ23" s="32"/>
-      <c r="AR23" s="32"/>
-      <c r="AS23" s="32"/>
-      <c r="AT23" s="32"/>
-      <c r="AU23" s="32"/>
-      <c r="AV23" s="32"/>
-      <c r="AW23" s="32"/>
-      <c r="AX23" s="32"/>
-      <c r="AY23" s="32"/>
-    </row>
-    <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+      <c r="N23" s="33"/>
+      <c r="O23" s="33"/>
+      <c r="Q23" s="41"/>
+      <c r="R23" s="41"/>
+      <c r="S23" s="41"/>
+      <c r="T23" s="41"/>
+      <c r="U23" s="41"/>
+      <c r="V23" s="41"/>
+      <c r="W23" s="41"/>
+      <c r="X23" s="41"/>
+      <c r="Y23" s="41"/>
+      <c r="Z23" s="41"/>
+      <c r="AA23" s="41"/>
+      <c r="AB23" s="41"/>
+      <c r="AC23" s="41"/>
+      <c r="AD23" s="41"/>
+      <c r="AE23" s="41"/>
+      <c r="AF23" s="41"/>
+      <c r="AG23" s="41"/>
+      <c r="AH23" s="41"/>
+      <c r="AI23" s="41"/>
+      <c r="AJ23" s="41"/>
+      <c r="AK23" s="41"/>
+      <c r="AL23" s="41"/>
+      <c r="AM23" s="41"/>
+      <c r="AN23" s="41"/>
+      <c r="AO23" s="41"/>
+      <c r="AP23" s="41"/>
+      <c r="AQ23" s="41"/>
+      <c r="AR23" s="41"/>
+      <c r="AS23" s="41"/>
+      <c r="AT23" s="41"/>
+      <c r="AU23" s="41"/>
+      <c r="AV23" s="41"/>
+      <c r="AW23" s="41"/>
+      <c r="AX23" s="41"/>
+      <c r="AY23" s="41"/>
+    </row>
+    <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24" s="7" t="str">
         <v>Few_indicators_closest_DLS_coverage</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="Q24" s="32"/>
-      <c r="R24" s="32"/>
-      <c r="S24" s="32"/>
-      <c r="T24" s="32"/>
-      <c r="U24" s="32"/>
-      <c r="V24" s="32"/>
-      <c r="W24" s="32"/>
-      <c r="X24" s="32"/>
-      <c r="Y24" s="32"/>
-      <c r="Z24" s="32"/>
-      <c r="AA24" s="32"/>
-      <c r="AB24" s="32"/>
-      <c r="AC24" s="32"/>
-      <c r="AD24" s="32"/>
-      <c r="AE24" s="32"/>
-      <c r="AF24" s="32"/>
-      <c r="AG24" s="32"/>
-      <c r="AH24" s="32"/>
-      <c r="AI24" s="32"/>
-      <c r="AJ24" s="32"/>
-      <c r="AK24" s="32"/>
-      <c r="AL24" s="32"/>
-      <c r="AM24" s="32"/>
-      <c r="AN24" s="32"/>
-      <c r="AO24" s="32"/>
-      <c r="AP24" s="32"/>
-      <c r="AQ24" s="32"/>
-      <c r="AR24" s="32"/>
-      <c r="AS24" s="32"/>
-      <c r="AT24" s="32"/>
-      <c r="AU24" s="32"/>
-      <c r="AV24" s="32"/>
-      <c r="AW24" s="32"/>
-      <c r="AX24" s="32"/>
-      <c r="AY24" s="32"/>
-    </row>
-    <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="Q24" s="41"/>
+      <c r="R24" s="41"/>
+      <c r="S24" s="41"/>
+      <c r="T24" s="41"/>
+      <c r="U24" s="41"/>
+      <c r="V24" s="41"/>
+      <c r="W24" s="41"/>
+      <c r="X24" s="41"/>
+      <c r="Y24" s="41"/>
+      <c r="Z24" s="41"/>
+      <c r="AA24" s="41"/>
+      <c r="AB24" s="41"/>
+      <c r="AC24" s="41"/>
+      <c r="AD24" s="41"/>
+      <c r="AE24" s="41"/>
+      <c r="AF24" s="41"/>
+      <c r="AG24" s="41"/>
+      <c r="AH24" s="41"/>
+      <c r="AI24" s="41"/>
+      <c r="AJ24" s="41"/>
+      <c r="AK24" s="41"/>
+      <c r="AL24" s="41"/>
+      <c r="AM24" s="41"/>
+      <c r="AN24" s="41"/>
+      <c r="AO24" s="41"/>
+      <c r="AP24" s="41"/>
+      <c r="AQ24" s="41"/>
+      <c r="AR24" s="41"/>
+      <c r="AS24" s="41"/>
+      <c r="AT24" s="41"/>
+      <c r="AU24" s="41"/>
+      <c r="AV24" s="41"/>
+      <c r="AW24" s="41"/>
+      <c r="AX24" s="41"/>
+      <c r="AY24" s="41"/>
+    </row>
+    <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25" s="7" t="str">
         <v>Few_indicators_SPI_preferred</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="39"/>
-      <c r="Q25" s="32"/>
-      <c r="R25" s="32"/>
-      <c r="S25" s="32"/>
-      <c r="T25" s="32"/>
-      <c r="U25" s="32"/>
-      <c r="V25" s="32"/>
-      <c r="W25" s="32"/>
-      <c r="X25" s="32"/>
-      <c r="Y25" s="32"/>
-      <c r="Z25" s="32"/>
-      <c r="AA25" s="32"/>
-      <c r="AB25" s="32"/>
-      <c r="AC25" s="32"/>
-      <c r="AD25" s="32"/>
-      <c r="AE25" s="32"/>
-      <c r="AF25" s="32"/>
-      <c r="AG25" s="32"/>
-      <c r="AH25" s="32"/>
-      <c r="AI25" s="32"/>
-      <c r="AJ25" s="32"/>
-      <c r="AK25" s="32"/>
-      <c r="AL25" s="32"/>
-      <c r="AM25" s="32"/>
-      <c r="AN25" s="32"/>
-      <c r="AO25" s="32"/>
-      <c r="AP25" s="32"/>
-      <c r="AQ25" s="32"/>
-    </row>
-    <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="Q25" s="41"/>
+      <c r="R25" s="41"/>
+      <c r="S25" s="41"/>
+      <c r="T25" s="41"/>
+      <c r="U25" s="41"/>
+      <c r="V25" s="41"/>
+      <c r="W25" s="41"/>
+      <c r="X25" s="41"/>
+      <c r="Y25" s="41"/>
+      <c r="Z25" s="41"/>
+      <c r="AA25" s="41"/>
+      <c r="AB25" s="41"/>
+      <c r="AC25" s="41"/>
+      <c r="AD25" s="41"/>
+      <c r="AE25" s="41"/>
+      <c r="AF25" s="41"/>
+      <c r="AG25" s="41"/>
+      <c r="AH25" s="41"/>
+      <c r="AI25" s="41"/>
+      <c r="AJ25" s="41"/>
+      <c r="AK25" s="41"/>
+      <c r="AL25" s="41"/>
+      <c r="AM25" s="41"/>
+      <c r="AN25" s="41"/>
+      <c r="AO25" s="41"/>
+      <c r="AP25" s="41"/>
+      <c r="AQ25" s="41"/>
+    </row>
+    <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26" s="7" t="str">
         <v>No_non_DLS</v>
       </c>
-      <c r="C26" s="41" t="s">
+      <c r="C26" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="39"/>
-      <c r="K26" s="39"/>
-      <c r="L26" s="39"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="39"/>
-      <c r="O26" s="39"/>
-      <c r="Q26" s="32" t="e" vm="4">
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33"/>
+      <c r="Q26" s="41" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="R26" s="32"/>
-      <c r="S26" s="32"/>
-      <c r="T26" s="32"/>
-      <c r="U26" s="32"/>
-      <c r="V26" s="32"/>
-      <c r="W26" s="32"/>
-      <c r="X26" s="32"/>
-      <c r="Y26" s="32"/>
-      <c r="Z26" s="32"/>
-      <c r="AA26" s="32"/>
-      <c r="AB26" s="32"/>
-      <c r="AC26" s="32"/>
-      <c r="AD26" s="32"/>
-      <c r="AE26" s="32"/>
-      <c r="AF26" s="32"/>
-      <c r="AG26" s="32"/>
-      <c r="AH26" s="32"/>
-      <c r="AI26" s="32"/>
-      <c r="AJ26" s="32"/>
-      <c r="AK26" s="32"/>
-      <c r="AL26" s="32"/>
-      <c r="AM26" s="32"/>
-      <c r="AN26" s="32"/>
-      <c r="AO26" s="32"/>
-      <c r="AP26" s="32"/>
-      <c r="AQ26" s="32"/>
-    </row>
-    <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R26" s="41"/>
+      <c r="S26" s="41"/>
+      <c r="T26" s="41"/>
+      <c r="U26" s="41"/>
+      <c r="V26" s="41"/>
+      <c r="W26" s="41"/>
+      <c r="X26" s="41"/>
+      <c r="Y26" s="41"/>
+      <c r="Z26" s="41"/>
+      <c r="AA26" s="41"/>
+      <c r="AB26" s="41"/>
+      <c r="AC26" s="41"/>
+      <c r="AD26" s="41"/>
+      <c r="AE26" s="41"/>
+      <c r="AF26" s="41"/>
+      <c r="AG26" s="41"/>
+      <c r="AH26" s="41"/>
+      <c r="AI26" s="41"/>
+      <c r="AJ26" s="41"/>
+      <c r="AK26" s="41"/>
+      <c r="AL26" s="41"/>
+      <c r="AM26" s="41"/>
+      <c r="AN26" s="41"/>
+      <c r="AO26" s="41"/>
+      <c r="AP26" s="41"/>
+      <c r="AQ26" s="41"/>
+    </row>
+    <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27" s="7" t="str">
         <v>Only_%_of_pop</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="39"/>
-      <c r="L27" s="39"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="39"/>
-      <c r="Q27" s="32"/>
-      <c r="R27" s="32"/>
-      <c r="S27" s="32"/>
-      <c r="T27" s="32"/>
-      <c r="U27" s="32"/>
-      <c r="V27" s="32"/>
-      <c r="W27" s="32"/>
-      <c r="X27" s="32"/>
-      <c r="Y27" s="32"/>
-      <c r="Z27" s="32"/>
-      <c r="AA27" s="32"/>
-      <c r="AB27" s="32"/>
-      <c r="AC27" s="32"/>
-      <c r="AD27" s="32"/>
-      <c r="AE27" s="32"/>
-      <c r="AF27" s="32"/>
-      <c r="AG27" s="32"/>
-      <c r="AH27" s="32"/>
-      <c r="AI27" s="32"/>
-      <c r="AJ27" s="32"/>
-      <c r="AK27" s="32"/>
-      <c r="AL27" s="32"/>
-      <c r="AM27" s="32"/>
-      <c r="AN27" s="32"/>
-      <c r="AO27" s="32"/>
-      <c r="AP27" s="32"/>
-      <c r="AQ27" s="32"/>
-    </row>
-    <row r="28" spans="1:51" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="41"/>
+      <c r="S27" s="41"/>
+      <c r="T27" s="41"/>
+      <c r="U27" s="41"/>
+      <c r="V27" s="41"/>
+      <c r="W27" s="41"/>
+      <c r="X27" s="41"/>
+      <c r="Y27" s="41"/>
+      <c r="Z27" s="41"/>
+      <c r="AA27" s="41"/>
+      <c r="AB27" s="41"/>
+      <c r="AC27" s="41"/>
+      <c r="AD27" s="41"/>
+      <c r="AE27" s="41"/>
+      <c r="AF27" s="41"/>
+      <c r="AG27" s="41"/>
+      <c r="AH27" s="41"/>
+      <c r="AI27" s="41"/>
+      <c r="AJ27" s="41"/>
+      <c r="AK27" s="41"/>
+      <c r="AL27" s="41"/>
+      <c r="AM27" s="41"/>
+      <c r="AN27" s="41"/>
+      <c r="AO27" s="41"/>
+      <c r="AP27" s="41"/>
+      <c r="AQ27" s="41"/>
+    </row>
+    <row r="28" spans="1:51" ht="65.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" s="17" t="str">
         <v>Few_indicators_closest_DLS_coverage_90</v>
       </c>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="37"/>
-      <c r="L28" s="37"/>
-      <c r="M28" s="37"/>
-      <c r="N28" s="37"/>
-      <c r="O28" s="37"/>
-      <c r="Q28" s="32"/>
-      <c r="R28" s="32"/>
-      <c r="S28" s="32"/>
-      <c r="T28" s="32"/>
-      <c r="U28" s="32"/>
-      <c r="V28" s="32"/>
-      <c r="W28" s="32"/>
-      <c r="X28" s="32"/>
-      <c r="Y28" s="32"/>
-      <c r="Z28" s="32"/>
-      <c r="AA28" s="32"/>
-      <c r="AB28" s="32" t="e" vm="5">
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="40"/>
+      <c r="M28" s="40"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="40"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="41"/>
+      <c r="S28" s="41"/>
+      <c r="T28" s="41"/>
+      <c r="U28" s="41"/>
+      <c r="V28" s="41"/>
+      <c r="W28" s="41"/>
+      <c r="X28" s="41"/>
+      <c r="Y28" s="41"/>
+      <c r="Z28" s="41"/>
+      <c r="AA28" s="41"/>
+      <c r="AB28" s="41" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="AC28" s="32"/>
-      <c r="AD28" s="32"/>
-      <c r="AE28" s="32"/>
-      <c r="AF28" s="32"/>
-      <c r="AG28" s="32"/>
-      <c r="AH28" s="32"/>
-      <c r="AI28" s="32"/>
-      <c r="AJ28" s="32"/>
-      <c r="AK28" s="32"/>
-      <c r="AL28" s="32"/>
-      <c r="AM28" s="32"/>
-      <c r="AN28" s="32"/>
-      <c r="AO28" s="32"/>
-      <c r="AP28" s="32"/>
-      <c r="AQ28" s="32"/>
-    </row>
-    <row r="29" spans="1:51" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AC28" s="41"/>
+      <c r="AD28" s="41"/>
+      <c r="AE28" s="41"/>
+      <c r="AF28" s="41"/>
+      <c r="AG28" s="41"/>
+      <c r="AH28" s="41"/>
+      <c r="AI28" s="41"/>
+      <c r="AJ28" s="41"/>
+      <c r="AK28" s="41"/>
+      <c r="AL28" s="41"/>
+      <c r="AM28" s="41"/>
+      <c r="AN28" s="41"/>
+      <c r="AO28" s="41"/>
+      <c r="AP28" s="41"/>
+      <c r="AQ28" s="41"/>
+    </row>
+    <row r="29" spans="1:51" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2</v>
       </c>
       <c r="B29" s="17" t="str">
         <v>Few_indicators_SPI_preferred_90</v>
       </c>
-      <c r="C29" s="35" t="s">
+      <c r="C29" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="37"/>
-      <c r="L29" s="37"/>
-      <c r="M29" s="37"/>
-      <c r="N29" s="37"/>
-      <c r="O29" s="37"/>
-      <c r="Q29" s="32"/>
-      <c r="R29" s="32"/>
-      <c r="S29" s="32"/>
-      <c r="T29" s="32"/>
-      <c r="U29" s="32"/>
-      <c r="V29" s="32"/>
-      <c r="W29" s="32"/>
-      <c r="X29" s="32"/>
-      <c r="Y29" s="32"/>
-      <c r="Z29" s="32"/>
-      <c r="AA29" s="32"/>
-      <c r="AB29" s="32"/>
-      <c r="AC29" s="32"/>
-      <c r="AD29" s="32"/>
-      <c r="AE29" s="32"/>
-      <c r="AF29" s="32"/>
-      <c r="AG29" s="32"/>
-      <c r="AH29" s="32"/>
-      <c r="AI29" s="32"/>
-      <c r="AJ29" s="32"/>
-      <c r="AK29" s="32"/>
-      <c r="AL29" s="32"/>
-      <c r="AM29" s="32"/>
-      <c r="AN29" s="32"/>
-      <c r="AO29" s="32"/>
-      <c r="AP29" s="32"/>
-      <c r="AQ29" s="32"/>
-    </row>
-    <row r="30" spans="1:51" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="40"/>
+      <c r="M29" s="40"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="40"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="41"/>
+      <c r="S29" s="41"/>
+      <c r="T29" s="41"/>
+      <c r="U29" s="41"/>
+      <c r="V29" s="41"/>
+      <c r="W29" s="41"/>
+      <c r="X29" s="41"/>
+      <c r="Y29" s="41"/>
+      <c r="Z29" s="41"/>
+      <c r="AA29" s="41"/>
+      <c r="AB29" s="41"/>
+      <c r="AC29" s="41"/>
+      <c r="AD29" s="41"/>
+      <c r="AE29" s="41"/>
+      <c r="AF29" s="41"/>
+      <c r="AG29" s="41"/>
+      <c r="AH29" s="41"/>
+      <c r="AI29" s="41"/>
+      <c r="AJ29" s="41"/>
+      <c r="AK29" s="41"/>
+      <c r="AL29" s="41"/>
+      <c r="AM29" s="41"/>
+      <c r="AN29" s="41"/>
+      <c r="AO29" s="41"/>
+      <c r="AP29" s="41"/>
+      <c r="AQ29" s="41"/>
+    </row>
+    <row r="30" spans="1:51" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>3</v>
       </c>
       <c r="B30" s="17" t="str">
         <v>Few_indicators_closeDLS_subPrimSchool</v>
       </c>
-      <c r="C30" s="33" t="s">
+      <c r="C30" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="37"/>
-      <c r="J30" s="37"/>
-      <c r="K30" s="37"/>
-      <c r="L30" s="37"/>
-      <c r="M30" s="37"/>
-      <c r="N30" s="37"/>
-      <c r="O30" s="37"/>
-      <c r="Q30" s="32" t="e" vm="6">
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="40"/>
+      <c r="K30" s="40"/>
+      <c r="L30" s="40"/>
+      <c r="M30" s="40"/>
+      <c r="N30" s="40"/>
+      <c r="O30" s="40"/>
+      <c r="Q30" s="41" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
-      <c r="R30" s="32"/>
-      <c r="S30" s="32"/>
-      <c r="T30" s="32"/>
-      <c r="U30" s="32"/>
-      <c r="V30" s="32"/>
-      <c r="W30" s="32"/>
-      <c r="X30" s="32"/>
-      <c r="Y30" s="32"/>
-      <c r="Z30" s="32"/>
-      <c r="AA30" s="32"/>
-      <c r="AB30" s="32"/>
-      <c r="AC30" s="32"/>
-      <c r="AD30" s="32"/>
-      <c r="AE30" s="32"/>
-      <c r="AF30" s="32"/>
-      <c r="AG30" s="32"/>
-      <c r="AH30" s="32"/>
-      <c r="AI30" s="32"/>
-      <c r="AJ30" s="32"/>
-      <c r="AK30" s="32"/>
-      <c r="AL30" s="32"/>
-      <c r="AM30" s="32"/>
-      <c r="AN30" s="32"/>
-      <c r="AO30" s="32"/>
-      <c r="AP30" s="32"/>
-      <c r="AQ30" s="32"/>
-    </row>
-    <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R30" s="41"/>
+      <c r="S30" s="41"/>
+      <c r="T30" s="41"/>
+      <c r="U30" s="41"/>
+      <c r="V30" s="41"/>
+      <c r="W30" s="41"/>
+      <c r="X30" s="41"/>
+      <c r="Y30" s="41"/>
+      <c r="Z30" s="41"/>
+      <c r="AA30" s="41"/>
+      <c r="AB30" s="41"/>
+      <c r="AC30" s="41"/>
+      <c r="AD30" s="41"/>
+      <c r="AE30" s="41"/>
+      <c r="AF30" s="41"/>
+      <c r="AG30" s="41"/>
+      <c r="AH30" s="41"/>
+      <c r="AI30" s="41"/>
+      <c r="AJ30" s="41"/>
+      <c r="AK30" s="41"/>
+      <c r="AL30" s="41"/>
+      <c r="AM30" s="41"/>
+      <c r="AN30" s="41"/>
+      <c r="AO30" s="41"/>
+      <c r="AP30" s="41"/>
+      <c r="AQ30" s="41"/>
+    </row>
+    <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>3</v>
       </c>
       <c r="B31" s="17" t="str">
         <v>No_non_DLS_90</v>
       </c>
-      <c r="C31" s="35" t="s">
+      <c r="C31" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="37"/>
-      <c r="J31" s="37"/>
-      <c r="K31" s="37"/>
-      <c r="L31" s="37"/>
-      <c r="M31" s="37"/>
-      <c r="N31" s="37"/>
-      <c r="O31" s="37"/>
-      <c r="Q31" s="32"/>
-      <c r="R31" s="32"/>
-      <c r="S31" s="32"/>
-      <c r="T31" s="32"/>
-      <c r="U31" s="32"/>
-      <c r="V31" s="32"/>
-      <c r="W31" s="32"/>
-      <c r="X31" s="32"/>
-      <c r="Y31" s="32"/>
-      <c r="Z31" s="32"/>
-      <c r="AA31" s="32"/>
-      <c r="AB31" s="32"/>
-      <c r="AC31" s="32"/>
-      <c r="AD31" s="32"/>
-      <c r="AE31" s="32"/>
-      <c r="AF31" s="32"/>
-      <c r="AG31" s="32"/>
-      <c r="AH31" s="32"/>
-      <c r="AI31" s="32"/>
-      <c r="AJ31" s="32"/>
-      <c r="AK31" s="32"/>
-      <c r="AL31" s="32"/>
-      <c r="AM31" s="32"/>
-      <c r="AN31" s="32"/>
-      <c r="AO31" s="32"/>
-      <c r="AP31" s="32"/>
-      <c r="AQ31" s="32"/>
-    </row>
-    <row r="32" spans="1:51" ht="103.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="40"/>
+      <c r="K31" s="40"/>
+      <c r="L31" s="40"/>
+      <c r="M31" s="40"/>
+      <c r="N31" s="40"/>
+      <c r="O31" s="40"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="41"/>
+      <c r="S31" s="41"/>
+      <c r="T31" s="41"/>
+      <c r="U31" s="41"/>
+      <c r="V31" s="41"/>
+      <c r="W31" s="41"/>
+      <c r="X31" s="41"/>
+      <c r="Y31" s="41"/>
+      <c r="Z31" s="41"/>
+      <c r="AA31" s="41"/>
+      <c r="AB31" s="41"/>
+      <c r="AC31" s="41"/>
+      <c r="AD31" s="41"/>
+      <c r="AE31" s="41"/>
+      <c r="AF31" s="41"/>
+      <c r="AG31" s="41"/>
+      <c r="AH31" s="41"/>
+      <c r="AI31" s="41"/>
+      <c r="AJ31" s="41"/>
+      <c r="AK31" s="41"/>
+      <c r="AL31" s="41"/>
+      <c r="AM31" s="41"/>
+      <c r="AN31" s="41"/>
+      <c r="AO31" s="41"/>
+      <c r="AP31" s="41"/>
+      <c r="AQ31" s="41"/>
+    </row>
+    <row r="32" spans="1:51" ht="103.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>3</v>
       </c>
       <c r="B32" s="17" t="str">
         <v>Few_Indicators_subWatSani</v>
       </c>
-      <c r="C32" s="35" t="s">
+      <c r="C32" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="37"/>
-      <c r="K32" s="37"/>
-      <c r="L32" s="37"/>
-      <c r="M32" s="37"/>
-      <c r="N32" s="37"/>
-      <c r="O32" s="37"/>
-      <c r="Q32" s="32"/>
-      <c r="R32" s="32"/>
-      <c r="S32" s="32"/>
-      <c r="T32" s="32"/>
-      <c r="U32" s="32"/>
-      <c r="V32" s="32"/>
-      <c r="W32" s="32"/>
-      <c r="X32" s="32"/>
-      <c r="Y32" s="32"/>
-      <c r="Z32" s="32"/>
-      <c r="AA32" s="32"/>
-      <c r="AB32" s="32" t="e" vm="7">
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="40"/>
+      <c r="J32" s="40"/>
+      <c r="K32" s="40"/>
+      <c r="L32" s="40"/>
+      <c r="M32" s="40"/>
+      <c r="N32" s="40"/>
+      <c r="O32" s="40"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="41"/>
+      <c r="S32" s="41"/>
+      <c r="T32" s="41"/>
+      <c r="U32" s="41"/>
+      <c r="V32" s="41"/>
+      <c r="W32" s="41"/>
+      <c r="X32" s="41"/>
+      <c r="Y32" s="41"/>
+      <c r="Z32" s="41"/>
+      <c r="AA32" s="41"/>
+      <c r="AB32" s="41" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
-      <c r="AC32" s="32"/>
-      <c r="AD32" s="32"/>
-      <c r="AE32" s="32"/>
-      <c r="AF32" s="32"/>
-      <c r="AG32" s="32"/>
-      <c r="AH32" s="32"/>
-      <c r="AI32" s="32"/>
-      <c r="AJ32" s="32"/>
-      <c r="AK32" s="32"/>
-      <c r="AL32" s="32"/>
-      <c r="AM32" s="32"/>
-      <c r="AN32" s="32"/>
-      <c r="AO32" s="32"/>
-      <c r="AP32" s="32"/>
-      <c r="AQ32" s="32"/>
-    </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AC32" s="41"/>
+      <c r="AD32" s="41"/>
+      <c r="AE32" s="41"/>
+      <c r="AF32" s="41"/>
+      <c r="AG32" s="41"/>
+      <c r="AH32" s="41"/>
+      <c r="AI32" s="41"/>
+      <c r="AJ32" s="41"/>
+      <c r="AK32" s="41"/>
+      <c r="AL32" s="41"/>
+      <c r="AM32" s="41"/>
+      <c r="AN32" s="41"/>
+      <c r="AO32" s="41"/>
+      <c r="AP32" s="41"/>
+      <c r="AQ32" s="41"/>
+    </row>
+    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>4</v>
       </c>
       <c r="B33" s="6" t="str">
         <v>Only_OPP</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="34"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="34"/>
-      <c r="Q33" s="32"/>
-      <c r="R33" s="32"/>
-      <c r="S33" s="32"/>
-      <c r="T33" s="32"/>
-      <c r="U33" s="32"/>
-      <c r="V33" s="32"/>
-      <c r="W33" s="32"/>
-      <c r="X33" s="32"/>
-      <c r="Y33" s="32"/>
-      <c r="Z33" s="32"/>
-      <c r="AA33" s="32"/>
-      <c r="AB33" s="32"/>
-      <c r="AC33" s="32"/>
-      <c r="AD33" s="32"/>
-      <c r="AE33" s="32"/>
-      <c r="AF33" s="32"/>
-      <c r="AG33" s="32"/>
-      <c r="AH33" s="32"/>
-      <c r="AI33" s="32"/>
-      <c r="AJ33" s="32"/>
-      <c r="AK33" s="32"/>
-      <c r="AL33" s="32"/>
-      <c r="AM33" s="32"/>
-      <c r="AN33" s="32"/>
-      <c r="AO33" s="32"/>
-      <c r="AP33" s="32"/>
-      <c r="AQ33" s="32"/>
-    </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="42"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="42"/>
+      <c r="N33" s="42"/>
+      <c r="O33" s="42"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="41"/>
+      <c r="S33" s="41"/>
+      <c r="T33" s="41"/>
+      <c r="U33" s="41"/>
+      <c r="V33" s="41"/>
+      <c r="W33" s="41"/>
+      <c r="X33" s="41"/>
+      <c r="Y33" s="41"/>
+      <c r="Z33" s="41"/>
+      <c r="AA33" s="41"/>
+      <c r="AB33" s="41"/>
+      <c r="AC33" s="41"/>
+      <c r="AD33" s="41"/>
+      <c r="AE33" s="41"/>
+      <c r="AF33" s="41"/>
+      <c r="AG33" s="41"/>
+      <c r="AH33" s="41"/>
+      <c r="AI33" s="41"/>
+      <c r="AJ33" s="41"/>
+      <c r="AK33" s="41"/>
+      <c r="AL33" s="41"/>
+      <c r="AM33" s="41"/>
+      <c r="AN33" s="41"/>
+      <c r="AO33" s="41"/>
+      <c r="AP33" s="41"/>
+      <c r="AQ33" s="41"/>
+    </row>
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="str">
         <v>Baseline</v>
       </c>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-      <c r="O34" s="34"/>
-      <c r="Q34" s="32"/>
-      <c r="R34" s="32"/>
-      <c r="S34" s="32"/>
-      <c r="T34" s="32"/>
-      <c r="U34" s="32"/>
-      <c r="V34" s="32"/>
-      <c r="W34" s="32"/>
-      <c r="X34" s="32"/>
-      <c r="Y34" s="32"/>
-      <c r="Z34" s="32"/>
-      <c r="AA34" s="32"/>
-      <c r="AB34" s="32"/>
-      <c r="AC34" s="32"/>
-      <c r="AD34" s="32"/>
-      <c r="AE34" s="32"/>
-      <c r="AF34" s="32"/>
-      <c r="AG34" s="32"/>
-      <c r="AH34" s="32"/>
-      <c r="AI34" s="32"/>
-      <c r="AJ34" s="32"/>
-      <c r="AK34" s="32"/>
-      <c r="AL34" s="32"/>
-      <c r="AM34" s="32"/>
-      <c r="AN34" s="32"/>
-      <c r="AO34" s="32"/>
-      <c r="AP34" s="32"/>
-      <c r="AQ34" s="32"/>
-    </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="42"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="42"/>
+      <c r="N34" s="42"/>
+      <c r="O34" s="42"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="41"/>
+      <c r="S34" s="41"/>
+      <c r="T34" s="41"/>
+      <c r="U34" s="41"/>
+      <c r="V34" s="41"/>
+      <c r="W34" s="41"/>
+      <c r="X34" s="41"/>
+      <c r="Y34" s="41"/>
+      <c r="Z34" s="41"/>
+      <c r="AA34" s="41"/>
+      <c r="AB34" s="41"/>
+      <c r="AC34" s="41"/>
+      <c r="AD34" s="41"/>
+      <c r="AE34" s="41"/>
+      <c r="AF34" s="41"/>
+      <c r="AG34" s="41"/>
+      <c r="AH34" s="41"/>
+      <c r="AI34" s="41"/>
+      <c r="AJ34" s="41"/>
+      <c r="AK34" s="41"/>
+      <c r="AL34" s="41"/>
+      <c r="AM34" s="41"/>
+      <c r="AN34" s="41"/>
+      <c r="AO34" s="41"/>
+      <c r="AP34" s="41"/>
+      <c r="AQ34" s="41"/>
+    </row>
+    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B35" s="6" t="str">
         <v>No_nonDLS_limExt</v>
       </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34" t="s">
+      <c r="C35" s="42"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
-      <c r="O35" s="34"/>
-      <c r="Q35" s="32"/>
-      <c r="R35" s="32"/>
-      <c r="S35" s="32"/>
-      <c r="T35" s="32"/>
-      <c r="U35" s="32"/>
-      <c r="V35" s="32"/>
-      <c r="W35" s="32"/>
-      <c r="X35" s="32"/>
-      <c r="Y35" s="32"/>
-      <c r="Z35" s="32"/>
-      <c r="AA35" s="32"/>
-      <c r="AB35" s="32"/>
-      <c r="AC35" s="32"/>
-      <c r="AD35" s="32"/>
-      <c r="AE35" s="32"/>
-      <c r="AF35" s="32"/>
-      <c r="AG35" s="32"/>
-      <c r="AH35" s="32"/>
-      <c r="AI35" s="32"/>
-      <c r="AJ35" s="32"/>
-      <c r="AK35" s="32"/>
-      <c r="AL35" s="32"/>
-      <c r="AM35" s="32"/>
-      <c r="AN35" s="32"/>
-      <c r="AO35" s="32"/>
-      <c r="AP35" s="32"/>
-      <c r="AQ35" s="32"/>
-    </row>
-    <row r="36" spans="1:43" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J35" s="42"/>
+      <c r="K35" s="42"/>
+      <c r="L35" s="42"/>
+      <c r="M35" s="42"/>
+      <c r="N35" s="42"/>
+      <c r="O35" s="42"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="41"/>
+      <c r="S35" s="41"/>
+      <c r="T35" s="41"/>
+      <c r="U35" s="41"/>
+      <c r="V35" s="41"/>
+      <c r="W35" s="41"/>
+      <c r="X35" s="41"/>
+      <c r="Y35" s="41"/>
+      <c r="Z35" s="41"/>
+      <c r="AA35" s="41"/>
+      <c r="AB35" s="41"/>
+      <c r="AC35" s="41"/>
+      <c r="AD35" s="41"/>
+      <c r="AE35" s="41"/>
+      <c r="AF35" s="41"/>
+      <c r="AG35" s="41"/>
+      <c r="AH35" s="41"/>
+      <c r="AI35" s="41"/>
+      <c r="AJ35" s="41"/>
+      <c r="AK35" s="41"/>
+      <c r="AL35" s="41"/>
+      <c r="AM35" s="41"/>
+      <c r="AN35" s="41"/>
+      <c r="AO35" s="41"/>
+      <c r="AP35" s="41"/>
+      <c r="AQ35" s="41"/>
+    </row>
+    <row r="36" spans="1:43" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="6" t="str">
         <v>BHN</v>
       </c>
-      <c r="C36" s="38" t="s">
+      <c r="C36" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="34"/>
-      <c r="O36" s="34"/>
-      <c r="Q36" s="32"/>
-      <c r="R36" s="32"/>
-      <c r="S36" s="32"/>
-      <c r="T36" s="32"/>
-      <c r="U36" s="32"/>
-      <c r="V36" s="32"/>
-      <c r="W36" s="32"/>
-      <c r="X36" s="32"/>
-      <c r="Y36" s="32"/>
-      <c r="Z36" s="32"/>
-      <c r="AA36" s="32"/>
-      <c r="AB36" s="32"/>
-      <c r="AC36" s="32"/>
-      <c r="AD36" s="32"/>
-      <c r="AE36" s="32"/>
-      <c r="AF36" s="32"/>
-      <c r="AG36" s="32"/>
-      <c r="AH36" s="32"/>
-      <c r="AI36" s="32"/>
-      <c r="AJ36" s="32"/>
-      <c r="AK36" s="32"/>
-      <c r="AL36" s="32"/>
-      <c r="AM36" s="32"/>
-      <c r="AN36" s="32"/>
-      <c r="AO36" s="32"/>
-      <c r="AP36" s="32"/>
-      <c r="AQ36" s="32"/>
-    </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB37" s="32"/>
-      <c r="AC37" s="32"/>
-      <c r="AD37" s="32"/>
-      <c r="AE37" s="32"/>
-      <c r="AF37" s="32"/>
-      <c r="AG37" s="32"/>
-      <c r="AH37" s="32"/>
-      <c r="AI37" s="32"/>
-      <c r="AJ37" s="32"/>
-      <c r="AK37" s="32"/>
-      <c r="AL37" s="32"/>
-      <c r="AM37" s="32"/>
-      <c r="AN37" s="32"/>
-      <c r="AO37" s="32"/>
-      <c r="AP37" s="32"/>
-      <c r="AQ37" s="32"/>
-    </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB38" s="32"/>
-      <c r="AC38" s="32"/>
-      <c r="AD38" s="32"/>
-      <c r="AE38" s="32"/>
-      <c r="AF38" s="32"/>
-      <c r="AG38" s="32"/>
-      <c r="AH38" s="32"/>
-      <c r="AI38" s="32"/>
-      <c r="AJ38" s="32"/>
-      <c r="AK38" s="32"/>
-      <c r="AL38" s="32"/>
-      <c r="AM38" s="32"/>
-      <c r="AN38" s="32"/>
-      <c r="AO38" s="32"/>
-      <c r="AP38" s="32"/>
-      <c r="AQ38" s="32"/>
-    </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB39" s="32"/>
-      <c r="AC39" s="32"/>
-      <c r="AD39" s="32"/>
-      <c r="AE39" s="32"/>
-      <c r="AF39" s="32"/>
-      <c r="AG39" s="32"/>
-      <c r="AH39" s="32"/>
-      <c r="AI39" s="32"/>
-      <c r="AJ39" s="32"/>
-      <c r="AK39" s="32"/>
-      <c r="AL39" s="32"/>
-      <c r="AM39" s="32"/>
-      <c r="AN39" s="32"/>
-      <c r="AO39" s="32"/>
-      <c r="AP39" s="32"/>
-      <c r="AQ39" s="32"/>
-    </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB40" s="32"/>
-      <c r="AC40" s="32"/>
-      <c r="AD40" s="32"/>
-      <c r="AE40" s="32"/>
-      <c r="AF40" s="32"/>
-      <c r="AG40" s="32"/>
-      <c r="AH40" s="32"/>
-      <c r="AI40" s="32"/>
-      <c r="AJ40" s="32"/>
-      <c r="AK40" s="32"/>
-      <c r="AL40" s="32"/>
-      <c r="AM40" s="32"/>
-      <c r="AN40" s="32"/>
-      <c r="AO40" s="32"/>
-      <c r="AP40" s="32"/>
-      <c r="AQ40" s="32"/>
-    </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB41" s="32"/>
-      <c r="AC41" s="32"/>
-      <c r="AD41" s="32"/>
-      <c r="AE41" s="32"/>
-      <c r="AF41" s="32"/>
-      <c r="AG41" s="32"/>
-      <c r="AH41" s="32"/>
-      <c r="AI41" s="32"/>
-      <c r="AJ41" s="32"/>
-      <c r="AK41" s="32"/>
-      <c r="AL41" s="32"/>
-      <c r="AM41" s="32"/>
-      <c r="AN41" s="32"/>
-      <c r="AO41" s="32"/>
-      <c r="AP41" s="32"/>
-      <c r="AQ41" s="32"/>
-    </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB42" s="32" t="e" vm="8">
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="41"/>
+      <c r="S36" s="41"/>
+      <c r="T36" s="41"/>
+      <c r="U36" s="41"/>
+      <c r="V36" s="41"/>
+      <c r="W36" s="41"/>
+      <c r="X36" s="41"/>
+      <c r="Y36" s="41"/>
+      <c r="Z36" s="41"/>
+      <c r="AA36" s="41"/>
+      <c r="AB36" s="41"/>
+      <c r="AC36" s="41"/>
+      <c r="AD36" s="41"/>
+      <c r="AE36" s="41"/>
+      <c r="AF36" s="41"/>
+      <c r="AG36" s="41"/>
+      <c r="AH36" s="41"/>
+      <c r="AI36" s="41"/>
+      <c r="AJ36" s="41"/>
+      <c r="AK36" s="41"/>
+      <c r="AL36" s="41"/>
+      <c r="AM36" s="41"/>
+      <c r="AN36" s="41"/>
+      <c r="AO36" s="41"/>
+      <c r="AP36" s="41"/>
+      <c r="AQ36" s="41"/>
+    </row>
+    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB37" s="41"/>
+      <c r="AC37" s="41"/>
+      <c r="AD37" s="41"/>
+      <c r="AE37" s="41"/>
+      <c r="AF37" s="41"/>
+      <c r="AG37" s="41"/>
+      <c r="AH37" s="41"/>
+      <c r="AI37" s="41"/>
+      <c r="AJ37" s="41"/>
+      <c r="AK37" s="41"/>
+      <c r="AL37" s="41"/>
+      <c r="AM37" s="41"/>
+      <c r="AN37" s="41"/>
+      <c r="AO37" s="41"/>
+      <c r="AP37" s="41"/>
+      <c r="AQ37" s="41"/>
+    </row>
+    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB38" s="41"/>
+      <c r="AC38" s="41"/>
+      <c r="AD38" s="41"/>
+      <c r="AE38" s="41"/>
+      <c r="AF38" s="41"/>
+      <c r="AG38" s="41"/>
+      <c r="AH38" s="41"/>
+      <c r="AI38" s="41"/>
+      <c r="AJ38" s="41"/>
+      <c r="AK38" s="41"/>
+      <c r="AL38" s="41"/>
+      <c r="AM38" s="41"/>
+      <c r="AN38" s="41"/>
+      <c r="AO38" s="41"/>
+      <c r="AP38" s="41"/>
+      <c r="AQ38" s="41"/>
+    </row>
+    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB39" s="41"/>
+      <c r="AC39" s="41"/>
+      <c r="AD39" s="41"/>
+      <c r="AE39" s="41"/>
+      <c r="AF39" s="41"/>
+      <c r="AG39" s="41"/>
+      <c r="AH39" s="41"/>
+      <c r="AI39" s="41"/>
+      <c r="AJ39" s="41"/>
+      <c r="AK39" s="41"/>
+      <c r="AL39" s="41"/>
+      <c r="AM39" s="41"/>
+      <c r="AN39" s="41"/>
+      <c r="AO39" s="41"/>
+      <c r="AP39" s="41"/>
+      <c r="AQ39" s="41"/>
+    </row>
+    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB40" s="41"/>
+      <c r="AC40" s="41"/>
+      <c r="AD40" s="41"/>
+      <c r="AE40" s="41"/>
+      <c r="AF40" s="41"/>
+      <c r="AG40" s="41"/>
+      <c r="AH40" s="41"/>
+      <c r="AI40" s="41"/>
+      <c r="AJ40" s="41"/>
+      <c r="AK40" s="41"/>
+      <c r="AL40" s="41"/>
+      <c r="AM40" s="41"/>
+      <c r="AN40" s="41"/>
+      <c r="AO40" s="41"/>
+      <c r="AP40" s="41"/>
+      <c r="AQ40" s="41"/>
+    </row>
+    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB41" s="41"/>
+      <c r="AC41" s="41"/>
+      <c r="AD41" s="41"/>
+      <c r="AE41" s="41"/>
+      <c r="AF41" s="41"/>
+      <c r="AG41" s="41"/>
+      <c r="AH41" s="41"/>
+      <c r="AI41" s="41"/>
+      <c r="AJ41" s="41"/>
+      <c r="AK41" s="41"/>
+      <c r="AL41" s="41"/>
+      <c r="AM41" s="41"/>
+      <c r="AN41" s="41"/>
+      <c r="AO41" s="41"/>
+      <c r="AP41" s="41"/>
+      <c r="AQ41" s="41"/>
+    </row>
+    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB42" s="41" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-      <c r="AC42" s="32"/>
-      <c r="AD42" s="32"/>
-      <c r="AE42" s="32"/>
-      <c r="AF42" s="32"/>
-      <c r="AG42" s="32"/>
-      <c r="AH42" s="32"/>
-      <c r="AI42" s="32"/>
-      <c r="AJ42" s="32"/>
-      <c r="AK42" s="32"/>
-      <c r="AL42" s="32"/>
-      <c r="AM42" s="32"/>
-      <c r="AN42" s="32"/>
-      <c r="AO42" s="32"/>
-      <c r="AP42" s="32"/>
-      <c r="AQ42" s="32"/>
-    </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB43" s="32"/>
-      <c r="AC43" s="32"/>
-      <c r="AD43" s="32"/>
-      <c r="AE43" s="32"/>
-      <c r="AF43" s="32"/>
-      <c r="AG43" s="32"/>
-      <c r="AH43" s="32"/>
-      <c r="AI43" s="32"/>
-      <c r="AJ43" s="32"/>
-      <c r="AK43" s="32"/>
-      <c r="AL43" s="32"/>
-      <c r="AM43" s="32"/>
-      <c r="AN43" s="32"/>
-      <c r="AO43" s="32"/>
-      <c r="AP43" s="32"/>
-      <c r="AQ43" s="32"/>
-    </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB44" s="32"/>
-      <c r="AC44" s="32"/>
-      <c r="AD44" s="32"/>
-      <c r="AE44" s="32"/>
-      <c r="AF44" s="32"/>
-      <c r="AG44" s="32"/>
-      <c r="AH44" s="32"/>
-      <c r="AI44" s="32"/>
-      <c r="AJ44" s="32"/>
-      <c r="AK44" s="32"/>
-      <c r="AL44" s="32"/>
-      <c r="AM44" s="32"/>
-      <c r="AN44" s="32"/>
-      <c r="AO44" s="32"/>
-      <c r="AP44" s="32"/>
-      <c r="AQ44" s="32"/>
-    </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB45" s="32"/>
-      <c r="AC45" s="32"/>
-      <c r="AD45" s="32"/>
-      <c r="AE45" s="32"/>
-      <c r="AF45" s="32"/>
-      <c r="AG45" s="32"/>
-      <c r="AH45" s="32"/>
-      <c r="AI45" s="32"/>
-      <c r="AJ45" s="32"/>
-      <c r="AK45" s="32"/>
-      <c r="AL45" s="32"/>
-      <c r="AM45" s="32"/>
-      <c r="AN45" s="32"/>
-      <c r="AO45" s="32"/>
-      <c r="AP45" s="32"/>
-      <c r="AQ45" s="32"/>
-    </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB46" s="32"/>
-      <c r="AC46" s="32"/>
-      <c r="AD46" s="32"/>
-      <c r="AE46" s="32"/>
-      <c r="AF46" s="32"/>
-      <c r="AG46" s="32"/>
-      <c r="AH46" s="32"/>
-      <c r="AI46" s="32"/>
-      <c r="AJ46" s="32"/>
-      <c r="AK46" s="32"/>
-      <c r="AL46" s="32"/>
-      <c r="AM46" s="32"/>
-      <c r="AN46" s="32"/>
-      <c r="AO46" s="32"/>
-      <c r="AP46" s="32"/>
-      <c r="AQ46" s="32"/>
-    </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB47" s="32"/>
-      <c r="AC47" s="32"/>
-      <c r="AD47" s="32"/>
-      <c r="AE47" s="32"/>
-      <c r="AF47" s="32"/>
-      <c r="AG47" s="32"/>
-      <c r="AH47" s="32"/>
-      <c r="AI47" s="32"/>
-      <c r="AJ47" s="32"/>
-      <c r="AK47" s="32"/>
-      <c r="AL47" s="32"/>
-      <c r="AM47" s="32"/>
-      <c r="AN47" s="32"/>
-      <c r="AO47" s="32"/>
-      <c r="AP47" s="32"/>
-      <c r="AQ47" s="32"/>
-    </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB48" s="32"/>
-      <c r="AC48" s="32"/>
-      <c r="AD48" s="32"/>
-      <c r="AE48" s="32"/>
-      <c r="AF48" s="32"/>
-      <c r="AG48" s="32"/>
-      <c r="AH48" s="32"/>
-      <c r="AI48" s="32"/>
-      <c r="AJ48" s="32"/>
-      <c r="AK48" s="32"/>
-      <c r="AL48" s="32"/>
-      <c r="AM48" s="32"/>
-      <c r="AN48" s="32"/>
-      <c r="AO48" s="32"/>
-      <c r="AP48" s="32"/>
-      <c r="AQ48" s="32"/>
-    </row>
-    <row r="49" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB49" s="32"/>
-      <c r="AC49" s="32"/>
-      <c r="AD49" s="32"/>
-      <c r="AE49" s="32"/>
-      <c r="AF49" s="32"/>
-      <c r="AG49" s="32"/>
-      <c r="AH49" s="32"/>
-      <c r="AI49" s="32"/>
-      <c r="AJ49" s="32"/>
-      <c r="AK49" s="32"/>
-      <c r="AL49" s="32"/>
-      <c r="AM49" s="32"/>
-      <c r="AN49" s="32"/>
-      <c r="AO49" s="32"/>
-      <c r="AP49" s="32"/>
-      <c r="AQ49" s="32"/>
-    </row>
-    <row r="50" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB50" s="32"/>
-      <c r="AC50" s="32"/>
-      <c r="AD50" s="32"/>
-      <c r="AE50" s="32"/>
-      <c r="AF50" s="32"/>
-      <c r="AG50" s="32"/>
-      <c r="AH50" s="32"/>
-      <c r="AI50" s="32"/>
-      <c r="AJ50" s="32"/>
-      <c r="AK50" s="32"/>
-      <c r="AL50" s="32"/>
-      <c r="AM50" s="32"/>
-      <c r="AN50" s="32"/>
-      <c r="AO50" s="32"/>
-      <c r="AP50" s="32"/>
-      <c r="AQ50" s="32"/>
-    </row>
-    <row r="51" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB51" s="32"/>
-      <c r="AC51" s="32"/>
-      <c r="AD51" s="32"/>
-      <c r="AE51" s="32"/>
-      <c r="AF51" s="32"/>
-      <c r="AG51" s="32"/>
-      <c r="AH51" s="32"/>
-      <c r="AI51" s="32"/>
-      <c r="AJ51" s="32"/>
-      <c r="AK51" s="32"/>
-      <c r="AL51" s="32"/>
-      <c r="AM51" s="32"/>
-      <c r="AN51" s="32"/>
-      <c r="AO51" s="32"/>
-      <c r="AP51" s="32"/>
-      <c r="AQ51" s="32"/>
-    </row>
-    <row r="52" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB52" s="32"/>
-      <c r="AC52" s="32"/>
-      <c r="AD52" s="32"/>
-      <c r="AE52" s="32"/>
-      <c r="AF52" s="32"/>
-      <c r="AG52" s="32"/>
-      <c r="AH52" s="32"/>
-      <c r="AI52" s="32"/>
-      <c r="AJ52" s="32"/>
-      <c r="AK52" s="32"/>
-      <c r="AL52" s="32"/>
-      <c r="AM52" s="32"/>
-      <c r="AN52" s="32"/>
-      <c r="AO52" s="32"/>
-      <c r="AP52" s="32"/>
-      <c r="AQ52" s="32"/>
-    </row>
-    <row r="53" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB53" s="32"/>
-      <c r="AC53" s="32"/>
-      <c r="AD53" s="32"/>
-      <c r="AE53" s="32"/>
-      <c r="AF53" s="32"/>
-      <c r="AG53" s="32"/>
-      <c r="AH53" s="32"/>
-      <c r="AI53" s="32"/>
-      <c r="AJ53" s="32"/>
-      <c r="AK53" s="32"/>
-      <c r="AL53" s="32"/>
-      <c r="AM53" s="32"/>
-      <c r="AN53" s="32"/>
-      <c r="AO53" s="32"/>
-      <c r="AP53" s="32"/>
-      <c r="AQ53" s="32"/>
+      <c r="AC42" s="41"/>
+      <c r="AD42" s="41"/>
+      <c r="AE42" s="41"/>
+      <c r="AF42" s="41"/>
+      <c r="AG42" s="41"/>
+      <c r="AH42" s="41"/>
+      <c r="AI42" s="41"/>
+      <c r="AJ42" s="41"/>
+      <c r="AK42" s="41"/>
+      <c r="AL42" s="41"/>
+      <c r="AM42" s="41"/>
+      <c r="AN42" s="41"/>
+      <c r="AO42" s="41"/>
+      <c r="AP42" s="41"/>
+      <c r="AQ42" s="41"/>
+    </row>
+    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB43" s="41"/>
+      <c r="AC43" s="41"/>
+      <c r="AD43" s="41"/>
+      <c r="AE43" s="41"/>
+      <c r="AF43" s="41"/>
+      <c r="AG43" s="41"/>
+      <c r="AH43" s="41"/>
+      <c r="AI43" s="41"/>
+      <c r="AJ43" s="41"/>
+      <c r="AK43" s="41"/>
+      <c r="AL43" s="41"/>
+      <c r="AM43" s="41"/>
+      <c r="AN43" s="41"/>
+      <c r="AO43" s="41"/>
+      <c r="AP43" s="41"/>
+      <c r="AQ43" s="41"/>
+    </row>
+    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB44" s="41"/>
+      <c r="AC44" s="41"/>
+      <c r="AD44" s="41"/>
+      <c r="AE44" s="41"/>
+      <c r="AF44" s="41"/>
+      <c r="AG44" s="41"/>
+      <c r="AH44" s="41"/>
+      <c r="AI44" s="41"/>
+      <c r="AJ44" s="41"/>
+      <c r="AK44" s="41"/>
+      <c r="AL44" s="41"/>
+      <c r="AM44" s="41"/>
+      <c r="AN44" s="41"/>
+      <c r="AO44" s="41"/>
+      <c r="AP44" s="41"/>
+      <c r="AQ44" s="41"/>
+    </row>
+    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB45" s="41"/>
+      <c r="AC45" s="41"/>
+      <c r="AD45" s="41"/>
+      <c r="AE45" s="41"/>
+      <c r="AF45" s="41"/>
+      <c r="AG45" s="41"/>
+      <c r="AH45" s="41"/>
+      <c r="AI45" s="41"/>
+      <c r="AJ45" s="41"/>
+      <c r="AK45" s="41"/>
+      <c r="AL45" s="41"/>
+      <c r="AM45" s="41"/>
+      <c r="AN45" s="41"/>
+      <c r="AO45" s="41"/>
+      <c r="AP45" s="41"/>
+      <c r="AQ45" s="41"/>
+    </row>
+    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB46" s="41"/>
+      <c r="AC46" s="41"/>
+      <c r="AD46" s="41"/>
+      <c r="AE46" s="41"/>
+      <c r="AF46" s="41"/>
+      <c r="AG46" s="41"/>
+      <c r="AH46" s="41"/>
+      <c r="AI46" s="41"/>
+      <c r="AJ46" s="41"/>
+      <c r="AK46" s="41"/>
+      <c r="AL46" s="41"/>
+      <c r="AM46" s="41"/>
+      <c r="AN46" s="41"/>
+      <c r="AO46" s="41"/>
+      <c r="AP46" s="41"/>
+      <c r="AQ46" s="41"/>
+    </row>
+    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB47" s="41"/>
+      <c r="AC47" s="41"/>
+      <c r="AD47" s="41"/>
+      <c r="AE47" s="41"/>
+      <c r="AF47" s="41"/>
+      <c r="AG47" s="41"/>
+      <c r="AH47" s="41"/>
+      <c r="AI47" s="41"/>
+      <c r="AJ47" s="41"/>
+      <c r="AK47" s="41"/>
+      <c r="AL47" s="41"/>
+      <c r="AM47" s="41"/>
+      <c r="AN47" s="41"/>
+      <c r="AO47" s="41"/>
+      <c r="AP47" s="41"/>
+      <c r="AQ47" s="41"/>
+    </row>
+    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB48" s="41"/>
+      <c r="AC48" s="41"/>
+      <c r="AD48" s="41"/>
+      <c r="AE48" s="41"/>
+      <c r="AF48" s="41"/>
+      <c r="AG48" s="41"/>
+      <c r="AH48" s="41"/>
+      <c r="AI48" s="41"/>
+      <c r="AJ48" s="41"/>
+      <c r="AK48" s="41"/>
+      <c r="AL48" s="41"/>
+      <c r="AM48" s="41"/>
+      <c r="AN48" s="41"/>
+      <c r="AO48" s="41"/>
+      <c r="AP48" s="41"/>
+      <c r="AQ48" s="41"/>
+    </row>
+    <row r="49" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB49" s="41"/>
+      <c r="AC49" s="41"/>
+      <c r="AD49" s="41"/>
+      <c r="AE49" s="41"/>
+      <c r="AF49" s="41"/>
+      <c r="AG49" s="41"/>
+      <c r="AH49" s="41"/>
+      <c r="AI49" s="41"/>
+      <c r="AJ49" s="41"/>
+      <c r="AK49" s="41"/>
+      <c r="AL49" s="41"/>
+      <c r="AM49" s="41"/>
+      <c r="AN49" s="41"/>
+      <c r="AO49" s="41"/>
+      <c r="AP49" s="41"/>
+      <c r="AQ49" s="41"/>
+    </row>
+    <row r="50" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB50" s="41"/>
+      <c r="AC50" s="41"/>
+      <c r="AD50" s="41"/>
+      <c r="AE50" s="41"/>
+      <c r="AF50" s="41"/>
+      <c r="AG50" s="41"/>
+      <c r="AH50" s="41"/>
+      <c r="AI50" s="41"/>
+      <c r="AJ50" s="41"/>
+      <c r="AK50" s="41"/>
+      <c r="AL50" s="41"/>
+      <c r="AM50" s="41"/>
+      <c r="AN50" s="41"/>
+      <c r="AO50" s="41"/>
+      <c r="AP50" s="41"/>
+      <c r="AQ50" s="41"/>
+    </row>
+    <row r="51" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB51" s="41"/>
+      <c r="AC51" s="41"/>
+      <c r="AD51" s="41"/>
+      <c r="AE51" s="41"/>
+      <c r="AF51" s="41"/>
+      <c r="AG51" s="41"/>
+      <c r="AH51" s="41"/>
+      <c r="AI51" s="41"/>
+      <c r="AJ51" s="41"/>
+      <c r="AK51" s="41"/>
+      <c r="AL51" s="41"/>
+      <c r="AM51" s="41"/>
+      <c r="AN51" s="41"/>
+      <c r="AO51" s="41"/>
+      <c r="AP51" s="41"/>
+      <c r="AQ51" s="41"/>
+    </row>
+    <row r="52" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB52" s="41"/>
+      <c r="AC52" s="41"/>
+      <c r="AD52" s="41"/>
+      <c r="AE52" s="41"/>
+      <c r="AF52" s="41"/>
+      <c r="AG52" s="41"/>
+      <c r="AH52" s="41"/>
+      <c r="AI52" s="41"/>
+      <c r="AJ52" s="41"/>
+      <c r="AK52" s="41"/>
+      <c r="AL52" s="41"/>
+      <c r="AM52" s="41"/>
+      <c r="AN52" s="41"/>
+      <c r="AO52" s="41"/>
+      <c r="AP52" s="41"/>
+      <c r="AQ52" s="41"/>
+    </row>
+    <row r="53" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB53" s="41"/>
+      <c r="AC53" s="41"/>
+      <c r="AD53" s="41"/>
+      <c r="AE53" s="41"/>
+      <c r="AF53" s="41"/>
+      <c r="AG53" s="41"/>
+      <c r="AH53" s="41"/>
+      <c r="AI53" s="41"/>
+      <c r="AJ53" s="41"/>
+      <c r="AK53" s="41"/>
+      <c r="AL53" s="41"/>
+      <c r="AM53" s="41"/>
+      <c r="AN53" s="41"/>
+      <c r="AO53" s="41"/>
+      <c r="AP53" s="41"/>
+      <c r="AQ53" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="I24:O24"/>
-    <mergeCell ref="I25:O25"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I21:O21"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C23:H23"/>
-    <mergeCell ref="I22:O22"/>
-    <mergeCell ref="I23:O23"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="T4:X4"/>
+    <mergeCell ref="AB42:AQ53"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="AB28:AQ31"/>
+    <mergeCell ref="Q26:AA29"/>
+    <mergeCell ref="I35:O35"/>
+    <mergeCell ref="C29:H29"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="I30:O30"/>
+    <mergeCell ref="I31:O31"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="I36:O36"/>
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="I28:O28"/>
     <mergeCell ref="I29:O29"/>
@@ -3515,25 +3574,20 @@
     <mergeCell ref="C24:H24"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
-    <mergeCell ref="T4:X4"/>
-    <mergeCell ref="AB42:AQ53"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="AB28:AQ31"/>
-    <mergeCell ref="Q26:AA29"/>
-    <mergeCell ref="I35:O35"/>
-    <mergeCell ref="C29:H29"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="I30:O30"/>
-    <mergeCell ref="I31:O31"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="I24:O24"/>
+    <mergeCell ref="I25:O25"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I21:O21"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="I22:O22"/>
+    <mergeCell ref="I23:O23"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="C21:H21"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:Q15">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3547,31 +3601,31 @@
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AY53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.33203125" customWidth="1"/>
+    <col min="2" max="2" width="35.28515625" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
-    <col min="5" max="16" width="4.33203125" customWidth="1"/>
-    <col min="19" max="19" width="8.88671875" customWidth="1"/>
+    <col min="5" max="16" width="4.28515625" customWidth="1"/>
+    <col min="19" max="19" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="43"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="35"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
@@ -3585,12 +3639,12 @@
       <c r="W3" s="22"/>
       <c r="X3" s="22"/>
     </row>
-    <row r="4" spans="1:24" ht="221.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" ht="221.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="15" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="25" t="str" cm="1">
-        <f t="array" ref="C4:R4">Experiments!C1:R1</f>
+        <f t="array" ref="C4:S4">Experiments!C1:S1</f>
         <v>BHN_FWB</v>
       </c>
       <c r="D4" s="23" t="str">
@@ -3638,15 +3692,18 @@
       <c r="R4" s="29" t="str">
         <v>No_non_DLS_BHNFWB</v>
       </c>
-      <c r="T4" s="31" t="s">
+      <c r="S4" s="29" t="str">
+        <v>All_indicators</v>
+      </c>
+      <c r="T4" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="U4" s="31"/>
-      <c r="V4" s="31"/>
-      <c r="W4" s="31"/>
-      <c r="X4" s="31"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="U4" s="43"/>
+      <c r="V4" s="43"/>
+      <c r="W4" s="43"/>
+      <c r="X4" s="43"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="str" cm="1">
         <f t="array" ref="B5:B15">_xlfn.UNIQUE('Overview of indicators and DLS'!C4:C67)</f>
         <v>Food &amp; Nutrition</v>
@@ -3715,8 +3772,12 @@
         <f t="array" ref="R5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!R$2:R$64=1))</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S5" s="8" cm="1">
+        <f t="array" ref="S5">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B5)*(Experiments!S$2:S$64=1))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="str">
         <v>Health Care</v>
       </c>
@@ -3784,8 +3845,12 @@
         <f t="array" ref="R6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!R$2:R$64=1))</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S6" s="8" cm="1">
+        <f t="array" ref="S6">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B6)*(Experiments!S$2:S$64=1))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="str">
         <v>Water</v>
       </c>
@@ -3853,8 +3918,12 @@
         <f t="array" ref="R7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!R$2:R$64=1))</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S7" s="8" cm="1">
+        <f t="array" ref="S7">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B7)*(Experiments!S$2:S$64=1))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="str">
         <v>Sanitation</v>
       </c>
@@ -3922,8 +3991,12 @@
         <f t="array" ref="R8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!R$2:R$64=1))</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S8" s="8" cm="1">
+        <f t="array" ref="S8">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B8)*(Experiments!S$2:S$64=1))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="str">
         <v>Food preparation</v>
       </c>
@@ -3991,8 +4064,12 @@
         <f t="array" ref="R9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!R$2:R$64=1))</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="S9" s="8" cm="1">
+        <f t="array" ref="S9">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B9)*(Experiments!S$2:S$64=1))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="str">
         <v>Thermal comfort</v>
       </c>
@@ -4060,8 +4137,12 @@
         <f t="array" ref="R10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!R$2:R$64=1))</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="S10" s="8" cm="1">
+        <f t="array" ref="S10">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B10)*(Experiments!S$2:S$64=1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="str">
         <v>Non material / Non-DLS</v>
       </c>
@@ -4129,8 +4210,12 @@
         <f t="array" ref="R11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!R$2:R$64=1))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="S11" s="8" cm="1">
+        <f t="array" ref="S11">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B11)*(Experiments!S$2:S$64=1))</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="str">
         <v>Education</v>
       </c>
@@ -4198,8 +4283,12 @@
         <f t="array" ref="R12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!R$2:R$64=1))</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="S12" s="8" cm="1">
+        <f t="array" ref="S12">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B12)*(Experiments!S$2:S$64=1))</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="str">
         <v>Social connectedness</v>
       </c>
@@ -4267,8 +4356,12 @@
         <f t="array" ref="R13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!R$2:R$64=1))</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="S13" s="8" cm="1">
+        <f t="array" ref="S13">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B13)*(Experiments!S$2:S$64=1))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="str">
         <v>Housing</v>
       </c>
@@ -4336,8 +4429,12 @@
         <f t="array" ref="R14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!R$2:R$64=1))</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="S14" s="8" cm="1">
+        <f t="array" ref="S14">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B14)*(Experiments!S$2:S$64=1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B15" s="13" t="str">
         <v>Physical Connectedness</v>
       </c>
@@ -4405,11 +4502,15 @@
         <f t="array" ref="R15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!R$2:R$64=1))</f>
         <v>0</v>
       </c>
-      <c r="S15" t="s">
+      <c r="S15" s="12" cm="1">
+        <f t="array" ref="S15">SUMPRODUCT(('Overview of indicators and DLS'!$C$4:$C$66=$B15)*(Experiments!S$2:S$64=1))</f>
+        <v>0</v>
+      </c>
+      <c r="U15" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B16" s="11"/>
       <c r="C16" s="20"/>
       <c r="D16" s="14"/>
@@ -4427,8 +4528,9 @@
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
-    </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="S16" s="8"/>
+    </row>
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>33</v>
       </c>
@@ -4493,11 +4595,15 @@
         <v>10</v>
       </c>
       <c r="R17" s="14">
-        <f t="shared" ref="R17" si="1">SUM(R5:R15)</f>
+        <f t="shared" ref="R17:S17" si="1">SUM(R5:R15)</f>
         <v>33</v>
       </c>
-    </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="S17" s="14">
+        <f t="shared" si="1"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
         <v>34</v>
       </c>
@@ -4565,8 +4671,12 @@
         <f>SUM(Experiments!R2:R53)</f>
         <v>24</v>
       </c>
-    </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="S18" s="8">
+        <f>SUM(Experiments!S2:S53)</f>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B19" s="11" t="s">
         <v>35</v>
       </c>
@@ -4634,31 +4744,35 @@
         <f>SUM(Experiments!R54:R64)</f>
         <v>9</v>
       </c>
-    </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="S19" s="8">
+        <f>SUM(Experiments!S54:S64)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>55</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="44" t="s">
+      <c r="C21" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44" t="s">
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="J21" s="44"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="44"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
       <c r="Q21" s="1" t="s">
         <v>58</v>
       </c>
@@ -4666,1080 +4780,1109 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:51" ht="90.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:51" ht="90.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22" s="7" t="str" cm="1">
-        <f t="array" ref="B22:B37">TRANSPOSE(_xlfn.ANCHORARRAY(C4))</f>
+        <f t="array" ref="B22:B38">TRANSPOSE(_xlfn.ANCHORARRAY(C4))</f>
         <v>BHN_FWB</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="39"/>
-      <c r="O22" s="39"/>
-      <c r="Q22" s="32" t="e" vm="9">
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="33"/>
+      <c r="Q22" s="41" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
-      <c r="R22" s="32"/>
-      <c r="S22" s="32"/>
-      <c r="T22" s="32"/>
-      <c r="U22" s="32"/>
-      <c r="V22" s="32"/>
-      <c r="W22" s="32"/>
-      <c r="X22" s="32"/>
-      <c r="Y22" s="32"/>
-      <c r="Z22" s="32"/>
-      <c r="AA22" s="32"/>
-      <c r="AB22" s="32" t="e" vm="10">
+      <c r="R22" s="41"/>
+      <c r="S22" s="41"/>
+      <c r="T22" s="41"/>
+      <c r="U22" s="41"/>
+      <c r="V22" s="41"/>
+      <c r="W22" s="41"/>
+      <c r="X22" s="41"/>
+      <c r="Y22" s="41"/>
+      <c r="Z22" s="41"/>
+      <c r="AA22" s="41"/>
+      <c r="AB22" s="41" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
-      <c r="AC22" s="32"/>
-      <c r="AD22" s="32"/>
-      <c r="AE22" s="32"/>
-      <c r="AF22" s="32"/>
-      <c r="AG22" s="32"/>
-      <c r="AH22" s="32"/>
-      <c r="AI22" s="32"/>
-      <c r="AJ22" s="32"/>
-      <c r="AK22" s="32"/>
-      <c r="AL22" s="32"/>
-      <c r="AM22" s="32"/>
-      <c r="AN22" s="32"/>
-      <c r="AO22" s="32"/>
-      <c r="AP22" s="32"/>
-      <c r="AQ22" s="32"/>
-      <c r="AR22" s="32" t="e" vm="3">
+      <c r="AC22" s="41"/>
+      <c r="AD22" s="41"/>
+      <c r="AE22" s="41"/>
+      <c r="AF22" s="41"/>
+      <c r="AG22" s="41"/>
+      <c r="AH22" s="41"/>
+      <c r="AI22" s="41"/>
+      <c r="AJ22" s="41"/>
+      <c r="AK22" s="41"/>
+      <c r="AL22" s="41"/>
+      <c r="AM22" s="41"/>
+      <c r="AN22" s="41"/>
+      <c r="AO22" s="41"/>
+      <c r="AP22" s="41"/>
+      <c r="AQ22" s="41"/>
+      <c r="AR22" s="41" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="AS22" s="32"/>
-      <c r="AT22" s="32"/>
-      <c r="AU22" s="32"/>
-      <c r="AV22" s="32"/>
-      <c r="AW22" s="32"/>
-      <c r="AX22" s="32"/>
-      <c r="AY22" s="32"/>
-    </row>
-    <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AS22" s="41"/>
+      <c r="AT22" s="41"/>
+      <c r="AU22" s="41"/>
+      <c r="AV22" s="41"/>
+      <c r="AW22" s="41"/>
+      <c r="AX22" s="41"/>
+      <c r="AY22" s="41"/>
+    </row>
+    <row r="23" spans="1:51" ht="87.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23" s="26" t="str">
         <v>BHN_FWB_AllExt</v>
       </c>
-      <c r="C23" s="48" t="s">
+      <c r="C23" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="39"/>
-      <c r="Q23" s="32"/>
-      <c r="R23" s="32"/>
-      <c r="S23" s="32"/>
-      <c r="T23" s="32"/>
-      <c r="U23" s="32"/>
-      <c r="V23" s="32"/>
-      <c r="W23" s="32"/>
-      <c r="X23" s="32"/>
-      <c r="Y23" s="32"/>
-      <c r="Z23" s="32"/>
-      <c r="AA23" s="32"/>
-      <c r="AB23" s="32"/>
-      <c r="AC23" s="32"/>
-      <c r="AD23" s="32"/>
-      <c r="AE23" s="32"/>
-      <c r="AF23" s="32"/>
-      <c r="AG23" s="32"/>
-      <c r="AH23" s="32"/>
-      <c r="AI23" s="32"/>
-      <c r="AJ23" s="32"/>
-      <c r="AK23" s="32"/>
-      <c r="AL23" s="32"/>
-      <c r="AM23" s="32"/>
-      <c r="AN23" s="32"/>
-      <c r="AO23" s="32"/>
-      <c r="AP23" s="32"/>
-      <c r="AQ23" s="32"/>
-      <c r="AR23" s="32"/>
-      <c r="AS23" s="32"/>
-      <c r="AT23" s="32"/>
-      <c r="AU23" s="32"/>
-      <c r="AV23" s="32"/>
-      <c r="AW23" s="32"/>
-      <c r="AX23" s="32"/>
-      <c r="AY23" s="32"/>
-    </row>
-    <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+      <c r="N23" s="33"/>
+      <c r="O23" s="33"/>
+      <c r="Q23" s="41"/>
+      <c r="R23" s="41"/>
+      <c r="S23" s="41"/>
+      <c r="T23" s="41"/>
+      <c r="U23" s="41"/>
+      <c r="V23" s="41"/>
+      <c r="W23" s="41"/>
+      <c r="X23" s="41"/>
+      <c r="Y23" s="41"/>
+      <c r="Z23" s="41"/>
+      <c r="AA23" s="41"/>
+      <c r="AB23" s="41"/>
+      <c r="AC23" s="41"/>
+      <c r="AD23" s="41"/>
+      <c r="AE23" s="41"/>
+      <c r="AF23" s="41"/>
+      <c r="AG23" s="41"/>
+      <c r="AH23" s="41"/>
+      <c r="AI23" s="41"/>
+      <c r="AJ23" s="41"/>
+      <c r="AK23" s="41"/>
+      <c r="AL23" s="41"/>
+      <c r="AM23" s="41"/>
+      <c r="AN23" s="41"/>
+      <c r="AO23" s="41"/>
+      <c r="AP23" s="41"/>
+      <c r="AQ23" s="41"/>
+      <c r="AR23" s="41"/>
+      <c r="AS23" s="41"/>
+      <c r="AT23" s="41"/>
+      <c r="AU23" s="41"/>
+      <c r="AV23" s="41"/>
+      <c r="AW23" s="41"/>
+      <c r="AX23" s="41"/>
+      <c r="AY23" s="41"/>
+    </row>
+    <row r="24" spans="1:51" ht="108.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24" s="7" t="str">
         <v>Few_indicators_closest_DLS_coverage</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="Q24" s="32"/>
-      <c r="R24" s="32"/>
-      <c r="S24" s="32"/>
-      <c r="T24" s="32"/>
-      <c r="U24" s="32"/>
-      <c r="V24" s="32"/>
-      <c r="W24" s="32"/>
-      <c r="X24" s="32"/>
-      <c r="Y24" s="32"/>
-      <c r="Z24" s="32"/>
-      <c r="AA24" s="32"/>
-      <c r="AB24" s="32"/>
-      <c r="AC24" s="32"/>
-      <c r="AD24" s="32"/>
-      <c r="AE24" s="32"/>
-      <c r="AF24" s="32"/>
-      <c r="AG24" s="32"/>
-      <c r="AH24" s="32"/>
-      <c r="AI24" s="32"/>
-      <c r="AJ24" s="32"/>
-      <c r="AK24" s="32"/>
-      <c r="AL24" s="32"/>
-      <c r="AM24" s="32"/>
-      <c r="AN24" s="32"/>
-      <c r="AO24" s="32"/>
-      <c r="AP24" s="32"/>
-      <c r="AQ24" s="32"/>
-      <c r="AR24" s="32"/>
-      <c r="AS24" s="32"/>
-      <c r="AT24" s="32"/>
-      <c r="AU24" s="32"/>
-      <c r="AV24" s="32"/>
-      <c r="AW24" s="32"/>
-      <c r="AX24" s="32"/>
-      <c r="AY24" s="32"/>
-    </row>
-    <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="Q24" s="41"/>
+      <c r="R24" s="41"/>
+      <c r="S24" s="41"/>
+      <c r="T24" s="41"/>
+      <c r="U24" s="41"/>
+      <c r="V24" s="41"/>
+      <c r="W24" s="41"/>
+      <c r="X24" s="41"/>
+      <c r="Y24" s="41"/>
+      <c r="Z24" s="41"/>
+      <c r="AA24" s="41"/>
+      <c r="AB24" s="41"/>
+      <c r="AC24" s="41"/>
+      <c r="AD24" s="41"/>
+      <c r="AE24" s="41"/>
+      <c r="AF24" s="41"/>
+      <c r="AG24" s="41"/>
+      <c r="AH24" s="41"/>
+      <c r="AI24" s="41"/>
+      <c r="AJ24" s="41"/>
+      <c r="AK24" s="41"/>
+      <c r="AL24" s="41"/>
+      <c r="AM24" s="41"/>
+      <c r="AN24" s="41"/>
+      <c r="AO24" s="41"/>
+      <c r="AP24" s="41"/>
+      <c r="AQ24" s="41"/>
+      <c r="AR24" s="41"/>
+      <c r="AS24" s="41"/>
+      <c r="AT24" s="41"/>
+      <c r="AU24" s="41"/>
+      <c r="AV24" s="41"/>
+      <c r="AW24" s="41"/>
+      <c r="AX24" s="41"/>
+      <c r="AY24" s="41"/>
+    </row>
+    <row r="25" spans="1:51" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25" s="7" t="str">
         <v>Few_indicators_SPI_preferred</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="39"/>
-      <c r="AB25" s="32"/>
-      <c r="AC25" s="32"/>
-      <c r="AD25" s="32"/>
-      <c r="AE25" s="32"/>
-      <c r="AF25" s="32"/>
-      <c r="AG25" s="32"/>
-      <c r="AH25" s="32"/>
-      <c r="AI25" s="32"/>
-      <c r="AJ25" s="32"/>
-      <c r="AK25" s="32"/>
-      <c r="AL25" s="32"/>
-      <c r="AM25" s="32"/>
-      <c r="AN25" s="32"/>
-      <c r="AO25" s="32"/>
-      <c r="AP25" s="32"/>
-      <c r="AQ25" s="32"/>
-    </row>
-    <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="AB25" s="41"/>
+      <c r="AC25" s="41"/>
+      <c r="AD25" s="41"/>
+      <c r="AE25" s="41"/>
+      <c r="AF25" s="41"/>
+      <c r="AG25" s="41"/>
+      <c r="AH25" s="41"/>
+      <c r="AI25" s="41"/>
+      <c r="AJ25" s="41"/>
+      <c r="AK25" s="41"/>
+      <c r="AL25" s="41"/>
+      <c r="AM25" s="41"/>
+      <c r="AN25" s="41"/>
+      <c r="AO25" s="41"/>
+      <c r="AP25" s="41"/>
+      <c r="AQ25" s="41"/>
+    </row>
+    <row r="26" spans="1:51" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26" s="7" t="str">
         <v>No_non_DLS</v>
       </c>
-      <c r="C26" s="41" t="s">
+      <c r="C26" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="39"/>
-      <c r="K26" s="39"/>
-      <c r="L26" s="39"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="39"/>
-      <c r="O26" s="39"/>
-      <c r="Q26" s="32"/>
-      <c r="R26" s="32"/>
-      <c r="S26" s="32"/>
-      <c r="T26" s="32"/>
-      <c r="U26" s="32"/>
-      <c r="V26" s="32"/>
-      <c r="W26" s="32"/>
-      <c r="X26" s="32"/>
-      <c r="Y26" s="32"/>
-      <c r="Z26" s="32"/>
-      <c r="AA26" s="32"/>
-      <c r="AB26" s="32"/>
-      <c r="AC26" s="32"/>
-      <c r="AD26" s="32"/>
-      <c r="AE26" s="32"/>
-      <c r="AF26" s="32"/>
-      <c r="AG26" s="32"/>
-      <c r="AH26" s="32"/>
-      <c r="AI26" s="32"/>
-      <c r="AJ26" s="32"/>
-      <c r="AK26" s="32"/>
-      <c r="AL26" s="32"/>
-      <c r="AM26" s="32"/>
-      <c r="AN26" s="32"/>
-      <c r="AO26" s="32"/>
-      <c r="AP26" s="32"/>
-      <c r="AQ26" s="32"/>
-    </row>
-    <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33"/>
+      <c r="Q26" s="41"/>
+      <c r="R26" s="41"/>
+      <c r="S26" s="41"/>
+      <c r="T26" s="41"/>
+      <c r="U26" s="41"/>
+      <c r="V26" s="41"/>
+      <c r="W26" s="41"/>
+      <c r="X26" s="41"/>
+      <c r="Y26" s="41"/>
+      <c r="Z26" s="41"/>
+      <c r="AA26" s="41"/>
+      <c r="AB26" s="41"/>
+      <c r="AC26" s="41"/>
+      <c r="AD26" s="41"/>
+      <c r="AE26" s="41"/>
+      <c r="AF26" s="41"/>
+      <c r="AG26" s="41"/>
+      <c r="AH26" s="41"/>
+      <c r="AI26" s="41"/>
+      <c r="AJ26" s="41"/>
+      <c r="AK26" s="41"/>
+      <c r="AL26" s="41"/>
+      <c r="AM26" s="41"/>
+      <c r="AN26" s="41"/>
+      <c r="AO26" s="41"/>
+      <c r="AP26" s="41"/>
+      <c r="AQ26" s="41"/>
+    </row>
+    <row r="27" spans="1:51" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27" s="26" t="str">
         <v>Only_%_of_pop</v>
       </c>
-      <c r="C27" s="46" t="s">
+      <c r="C27" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="39"/>
-      <c r="L27" s="39"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="39"/>
-      <c r="Q27" s="32"/>
-      <c r="R27" s="32"/>
-      <c r="S27" s="32"/>
-      <c r="T27" s="32"/>
-      <c r="U27" s="32"/>
-      <c r="V27" s="32"/>
-      <c r="W27" s="32"/>
-      <c r="X27" s="32"/>
-      <c r="Y27" s="32"/>
-      <c r="Z27" s="32"/>
-      <c r="AA27" s="32"/>
-      <c r="AB27" s="32"/>
-      <c r="AC27" s="32"/>
-      <c r="AD27" s="32"/>
-      <c r="AE27" s="32"/>
-      <c r="AF27" s="32"/>
-      <c r="AG27" s="32"/>
-      <c r="AH27" s="32"/>
-      <c r="AI27" s="32"/>
-      <c r="AJ27" s="32"/>
-      <c r="AK27" s="32"/>
-      <c r="AL27" s="32"/>
-      <c r="AM27" s="32"/>
-      <c r="AN27" s="32"/>
-      <c r="AO27" s="32"/>
-      <c r="AP27" s="32"/>
-      <c r="AQ27" s="32"/>
-    </row>
-    <row r="28" spans="1:51" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="41"/>
+      <c r="S27" s="41"/>
+      <c r="T27" s="41"/>
+      <c r="U27" s="41"/>
+      <c r="V27" s="41"/>
+      <c r="W27" s="41"/>
+      <c r="X27" s="41"/>
+      <c r="Y27" s="41"/>
+      <c r="Z27" s="41"/>
+      <c r="AA27" s="41"/>
+      <c r="AB27" s="41"/>
+      <c r="AC27" s="41"/>
+      <c r="AD27" s="41"/>
+      <c r="AE27" s="41"/>
+      <c r="AF27" s="41"/>
+      <c r="AG27" s="41"/>
+      <c r="AH27" s="41"/>
+      <c r="AI27" s="41"/>
+      <c r="AJ27" s="41"/>
+      <c r="AK27" s="41"/>
+      <c r="AL27" s="41"/>
+      <c r="AM27" s="41"/>
+      <c r="AN27" s="41"/>
+      <c r="AO27" s="41"/>
+      <c r="AP27" s="41"/>
+      <c r="AQ27" s="41"/>
+    </row>
+    <row r="28" spans="1:51" ht="65.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" s="17" t="str">
         <v>Few_indicators_closest_DLS_coverage_90</v>
       </c>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="37"/>
-      <c r="L28" s="37"/>
-      <c r="M28" s="37"/>
-      <c r="N28" s="37"/>
-      <c r="O28" s="37"/>
-      <c r="Q28" s="32"/>
-      <c r="R28" s="32"/>
-      <c r="S28" s="32"/>
-      <c r="T28" s="32"/>
-      <c r="U28" s="32"/>
-      <c r="V28" s="32"/>
-      <c r="W28" s="32"/>
-      <c r="X28" s="32"/>
-      <c r="Y28" s="32"/>
-      <c r="Z28" s="32"/>
-      <c r="AA28" s="32"/>
-      <c r="AB28" s="32"/>
-      <c r="AC28" s="32"/>
-      <c r="AD28" s="32"/>
-      <c r="AE28" s="32"/>
-      <c r="AF28" s="32"/>
-      <c r="AG28" s="32"/>
-      <c r="AH28" s="32"/>
-      <c r="AI28" s="32"/>
-      <c r="AJ28" s="32"/>
-      <c r="AK28" s="32"/>
-      <c r="AL28" s="32"/>
-      <c r="AM28" s="32"/>
-      <c r="AN28" s="32"/>
-      <c r="AO28" s="32"/>
-      <c r="AP28" s="32"/>
-      <c r="AQ28" s="32"/>
-    </row>
-    <row r="29" spans="1:51" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="40"/>
+      <c r="M28" s="40"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="40"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="41"/>
+      <c r="S28" s="41"/>
+      <c r="T28" s="41"/>
+      <c r="U28" s="41"/>
+      <c r="V28" s="41"/>
+      <c r="W28" s="41"/>
+      <c r="X28" s="41"/>
+      <c r="Y28" s="41"/>
+      <c r="Z28" s="41"/>
+      <c r="AA28" s="41"/>
+      <c r="AB28" s="41"/>
+      <c r="AC28" s="41"/>
+      <c r="AD28" s="41"/>
+      <c r="AE28" s="41"/>
+      <c r="AF28" s="41"/>
+      <c r="AG28" s="41"/>
+      <c r="AH28" s="41"/>
+      <c r="AI28" s="41"/>
+      <c r="AJ28" s="41"/>
+      <c r="AK28" s="41"/>
+      <c r="AL28" s="41"/>
+      <c r="AM28" s="41"/>
+      <c r="AN28" s="41"/>
+      <c r="AO28" s="41"/>
+      <c r="AP28" s="41"/>
+      <c r="AQ28" s="41"/>
+    </row>
+    <row r="29" spans="1:51" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2</v>
       </c>
       <c r="B29" s="17" t="str">
         <v>Few_indicators_SPI_preferred_90</v>
       </c>
-      <c r="C29" s="35" t="s">
+      <c r="C29" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="37"/>
-      <c r="L29" s="37"/>
-      <c r="M29" s="37"/>
-      <c r="N29" s="37"/>
-      <c r="O29" s="37"/>
-      <c r="Q29" s="32"/>
-      <c r="R29" s="32"/>
-      <c r="S29" s="32"/>
-      <c r="T29" s="32"/>
-      <c r="U29" s="32"/>
-      <c r="V29" s="32"/>
-      <c r="W29" s="32"/>
-      <c r="X29" s="32"/>
-      <c r="Y29" s="32"/>
-      <c r="Z29" s="32"/>
-      <c r="AA29" s="32"/>
-      <c r="AB29" s="32"/>
-      <c r="AC29" s="32"/>
-      <c r="AD29" s="32"/>
-      <c r="AE29" s="32"/>
-      <c r="AF29" s="32"/>
-      <c r="AG29" s="32"/>
-      <c r="AH29" s="32"/>
-      <c r="AI29" s="32"/>
-      <c r="AJ29" s="32"/>
-      <c r="AK29" s="32"/>
-      <c r="AL29" s="32"/>
-      <c r="AM29" s="32"/>
-      <c r="AN29" s="32"/>
-      <c r="AO29" s="32"/>
-      <c r="AP29" s="32"/>
-      <c r="AQ29" s="32"/>
-    </row>
-    <row r="30" spans="1:51" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="40"/>
+      <c r="M29" s="40"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="40"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="41"/>
+      <c r="S29" s="41"/>
+      <c r="T29" s="41"/>
+      <c r="U29" s="41"/>
+      <c r="V29" s="41"/>
+      <c r="W29" s="41"/>
+      <c r="X29" s="41"/>
+      <c r="Y29" s="41"/>
+      <c r="Z29" s="41"/>
+      <c r="AA29" s="41"/>
+      <c r="AB29" s="41"/>
+      <c r="AC29" s="41"/>
+      <c r="AD29" s="41"/>
+      <c r="AE29" s="41"/>
+      <c r="AF29" s="41"/>
+      <c r="AG29" s="41"/>
+      <c r="AH29" s="41"/>
+      <c r="AI29" s="41"/>
+      <c r="AJ29" s="41"/>
+      <c r="AK29" s="41"/>
+      <c r="AL29" s="41"/>
+      <c r="AM29" s="41"/>
+      <c r="AN29" s="41"/>
+      <c r="AO29" s="41"/>
+      <c r="AP29" s="41"/>
+      <c r="AQ29" s="41"/>
+    </row>
+    <row r="30" spans="1:51" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>3</v>
       </c>
       <c r="B30" s="17" t="str">
         <v>Few_indicators_closeDLS_subPrimSchool</v>
       </c>
-      <c r="C30" s="33" t="s">
+      <c r="C30" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="37"/>
-      <c r="J30" s="37"/>
-      <c r="K30" s="37"/>
-      <c r="L30" s="37"/>
-      <c r="M30" s="37"/>
-      <c r="N30" s="37"/>
-      <c r="O30" s="37"/>
-      <c r="Q30" s="32"/>
-      <c r="R30" s="32"/>
-      <c r="S30" s="32"/>
-      <c r="T30" s="32"/>
-      <c r="U30" s="32"/>
-      <c r="V30" s="32"/>
-      <c r="W30" s="32"/>
-      <c r="X30" s="32"/>
-      <c r="Y30" s="32"/>
-      <c r="Z30" s="32"/>
-      <c r="AA30" s="32"/>
-      <c r="AB30" s="32"/>
-      <c r="AC30" s="32"/>
-      <c r="AD30" s="32"/>
-      <c r="AE30" s="32"/>
-      <c r="AF30" s="32"/>
-      <c r="AG30" s="32"/>
-      <c r="AH30" s="32"/>
-      <c r="AI30" s="32"/>
-      <c r="AJ30" s="32"/>
-      <c r="AK30" s="32"/>
-      <c r="AL30" s="32"/>
-      <c r="AM30" s="32"/>
-      <c r="AN30" s="32"/>
-      <c r="AO30" s="32"/>
-      <c r="AP30" s="32"/>
-      <c r="AQ30" s="32"/>
-    </row>
-    <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="40"/>
+      <c r="K30" s="40"/>
+      <c r="L30" s="40"/>
+      <c r="M30" s="40"/>
+      <c r="N30" s="40"/>
+      <c r="O30" s="40"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="41"/>
+      <c r="S30" s="41"/>
+      <c r="T30" s="41"/>
+      <c r="U30" s="41"/>
+      <c r="V30" s="41"/>
+      <c r="W30" s="41"/>
+      <c r="X30" s="41"/>
+      <c r="Y30" s="41"/>
+      <c r="Z30" s="41"/>
+      <c r="AA30" s="41"/>
+      <c r="AB30" s="41"/>
+      <c r="AC30" s="41"/>
+      <c r="AD30" s="41"/>
+      <c r="AE30" s="41"/>
+      <c r="AF30" s="41"/>
+      <c r="AG30" s="41"/>
+      <c r="AH30" s="41"/>
+      <c r="AI30" s="41"/>
+      <c r="AJ30" s="41"/>
+      <c r="AK30" s="41"/>
+      <c r="AL30" s="41"/>
+      <c r="AM30" s="41"/>
+      <c r="AN30" s="41"/>
+      <c r="AO30" s="41"/>
+      <c r="AP30" s="41"/>
+      <c r="AQ30" s="41"/>
+    </row>
+    <row r="31" spans="1:51" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>3</v>
       </c>
       <c r="B31" s="27" t="str">
         <v>No_non_DLS_90</v>
       </c>
-      <c r="C31" s="49" t="s">
+      <c r="C31" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="49" t="s">
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="J31" s="49"/>
-      <c r="K31" s="49"/>
-      <c r="L31" s="49"/>
-      <c r="M31" s="49"/>
-      <c r="N31" s="49"/>
-      <c r="O31" s="49"/>
-      <c r="Q31" s="32"/>
-      <c r="R31" s="32"/>
-      <c r="S31" s="32"/>
-      <c r="T31" s="32"/>
-      <c r="U31" s="32"/>
-      <c r="V31" s="32"/>
-      <c r="W31" s="32"/>
-      <c r="X31" s="32"/>
-      <c r="Y31" s="32"/>
-      <c r="Z31" s="32"/>
-      <c r="AA31" s="32"/>
-      <c r="AB31" s="32"/>
-      <c r="AC31" s="32"/>
-      <c r="AD31" s="32"/>
-      <c r="AE31" s="32"/>
-      <c r="AF31" s="32"/>
-      <c r="AG31" s="32"/>
-      <c r="AH31" s="32"/>
-      <c r="AI31" s="32"/>
-      <c r="AJ31" s="32"/>
-      <c r="AK31" s="32"/>
-      <c r="AL31" s="32"/>
-      <c r="AM31" s="32"/>
-      <c r="AN31" s="32"/>
-      <c r="AO31" s="32"/>
-      <c r="AP31" s="32"/>
-      <c r="AQ31" s="32"/>
-    </row>
-    <row r="32" spans="1:51" ht="103.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J31" s="47"/>
+      <c r="K31" s="47"/>
+      <c r="L31" s="47"/>
+      <c r="M31" s="47"/>
+      <c r="N31" s="47"/>
+      <c r="O31" s="47"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="41"/>
+      <c r="S31" s="41"/>
+      <c r="T31" s="41"/>
+      <c r="U31" s="41"/>
+      <c r="V31" s="41"/>
+      <c r="W31" s="41"/>
+      <c r="X31" s="41"/>
+      <c r="Y31" s="41"/>
+      <c r="Z31" s="41"/>
+      <c r="AA31" s="41"/>
+      <c r="AB31" s="41"/>
+      <c r="AC31" s="41"/>
+      <c r="AD31" s="41"/>
+      <c r="AE31" s="41"/>
+      <c r="AF31" s="41"/>
+      <c r="AG31" s="41"/>
+      <c r="AH31" s="41"/>
+      <c r="AI31" s="41"/>
+      <c r="AJ31" s="41"/>
+      <c r="AK31" s="41"/>
+      <c r="AL31" s="41"/>
+      <c r="AM31" s="41"/>
+      <c r="AN31" s="41"/>
+      <c r="AO31" s="41"/>
+      <c r="AP31" s="41"/>
+      <c r="AQ31" s="41"/>
+    </row>
+    <row r="32" spans="1:51" ht="103.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>3</v>
       </c>
       <c r="B32" s="27" t="str">
         <v>Few_Indicators_subWatSani</v>
       </c>
-      <c r="C32" s="49" t="s">
+      <c r="C32" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="37"/>
-      <c r="K32" s="37"/>
-      <c r="L32" s="37"/>
-      <c r="M32" s="37"/>
-      <c r="N32" s="37"/>
-      <c r="O32" s="37"/>
-      <c r="Q32" s="32"/>
-      <c r="R32" s="32"/>
-      <c r="S32" s="32"/>
-      <c r="T32" s="32"/>
-      <c r="U32" s="32"/>
-      <c r="V32" s="32"/>
-      <c r="W32" s="32"/>
-      <c r="X32" s="32"/>
-      <c r="Y32" s="32"/>
-      <c r="Z32" s="32"/>
-      <c r="AA32" s="32"/>
-      <c r="AB32" s="32"/>
-      <c r="AC32" s="32"/>
-      <c r="AD32" s="32"/>
-      <c r="AE32" s="32"/>
-      <c r="AF32" s="32"/>
-      <c r="AG32" s="32"/>
-      <c r="AH32" s="32"/>
-      <c r="AI32" s="32"/>
-      <c r="AJ32" s="32"/>
-      <c r="AK32" s="32"/>
-      <c r="AL32" s="32"/>
-      <c r="AM32" s="32"/>
-      <c r="AN32" s="32"/>
-      <c r="AO32" s="32"/>
-      <c r="AP32" s="32"/>
-      <c r="AQ32" s="32"/>
-    </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="40"/>
+      <c r="J32" s="40"/>
+      <c r="K32" s="40"/>
+      <c r="L32" s="40"/>
+      <c r="M32" s="40"/>
+      <c r="N32" s="40"/>
+      <c r="O32" s="40"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="41"/>
+      <c r="S32" s="41"/>
+      <c r="T32" s="41"/>
+      <c r="U32" s="41"/>
+      <c r="V32" s="41"/>
+      <c r="W32" s="41"/>
+      <c r="X32" s="41"/>
+      <c r="Y32" s="41"/>
+      <c r="Z32" s="41"/>
+      <c r="AA32" s="41"/>
+      <c r="AB32" s="41"/>
+      <c r="AC32" s="41"/>
+      <c r="AD32" s="41"/>
+      <c r="AE32" s="41"/>
+      <c r="AF32" s="41"/>
+      <c r="AG32" s="41"/>
+      <c r="AH32" s="41"/>
+      <c r="AI32" s="41"/>
+      <c r="AJ32" s="41"/>
+      <c r="AK32" s="41"/>
+      <c r="AL32" s="41"/>
+      <c r="AM32" s="41"/>
+      <c r="AN32" s="41"/>
+      <c r="AO32" s="41"/>
+      <c r="AP32" s="41"/>
+      <c r="AQ32" s="41"/>
+    </row>
+    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>4</v>
       </c>
       <c r="B33" s="28" t="str">
         <v>Only_OPP</v>
       </c>
-      <c r="C33" s="50" t="s">
+      <c r="C33" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="50"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="34"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="34"/>
-      <c r="Q33" s="32"/>
-      <c r="R33" s="32"/>
-      <c r="S33" s="32"/>
-      <c r="T33" s="32"/>
-      <c r="U33" s="32"/>
-      <c r="V33" s="32"/>
-      <c r="W33" s="32"/>
-      <c r="X33" s="32"/>
-      <c r="Y33" s="32"/>
-      <c r="Z33" s="32"/>
-      <c r="AA33" s="32"/>
-      <c r="AB33" s="32"/>
-      <c r="AC33" s="32"/>
-      <c r="AD33" s="32"/>
-      <c r="AE33" s="32"/>
-      <c r="AF33" s="32"/>
-      <c r="AG33" s="32"/>
-      <c r="AH33" s="32"/>
-      <c r="AI33" s="32"/>
-      <c r="AJ33" s="32"/>
-      <c r="AK33" s="32"/>
-      <c r="AL33" s="32"/>
-      <c r="AM33" s="32"/>
-      <c r="AN33" s="32"/>
-      <c r="AO33" s="32"/>
-      <c r="AP33" s="32"/>
-      <c r="AQ33" s="32"/>
-    </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="42"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="42"/>
+      <c r="N33" s="42"/>
+      <c r="O33" s="42"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="41"/>
+      <c r="S33" s="41"/>
+      <c r="T33" s="41"/>
+      <c r="U33" s="41"/>
+      <c r="V33" s="41"/>
+      <c r="W33" s="41"/>
+      <c r="X33" s="41"/>
+      <c r="Y33" s="41"/>
+      <c r="Z33" s="41"/>
+      <c r="AA33" s="41"/>
+      <c r="AB33" s="41"/>
+      <c r="AC33" s="41"/>
+      <c r="AD33" s="41"/>
+      <c r="AE33" s="41"/>
+      <c r="AF33" s="41"/>
+      <c r="AG33" s="41"/>
+      <c r="AH33" s="41"/>
+      <c r="AI33" s="41"/>
+      <c r="AJ33" s="41"/>
+      <c r="AK33" s="41"/>
+      <c r="AL33" s="41"/>
+      <c r="AM33" s="41"/>
+      <c r="AN33" s="41"/>
+      <c r="AO33" s="41"/>
+      <c r="AP33" s="41"/>
+      <c r="AQ33" s="41"/>
+    </row>
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="str">
         <v>Baseline</v>
       </c>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-      <c r="O34" s="34"/>
-      <c r="Q34" s="32"/>
-      <c r="R34" s="32"/>
-      <c r="S34" s="32"/>
-      <c r="T34" s="32"/>
-      <c r="U34" s="32"/>
-      <c r="V34" s="32"/>
-      <c r="W34" s="32"/>
-      <c r="X34" s="32"/>
-      <c r="Y34" s="32"/>
-      <c r="Z34" s="32"/>
-      <c r="AA34" s="32"/>
-      <c r="AB34" s="32"/>
-      <c r="AC34" s="32"/>
-      <c r="AD34" s="32"/>
-      <c r="AE34" s="32"/>
-      <c r="AF34" s="32"/>
-      <c r="AG34" s="32"/>
-      <c r="AH34" s="32"/>
-      <c r="AI34" s="32"/>
-      <c r="AJ34" s="32"/>
-      <c r="AK34" s="32"/>
-      <c r="AL34" s="32"/>
-      <c r="AM34" s="32"/>
-      <c r="AN34" s="32"/>
-      <c r="AO34" s="32"/>
-      <c r="AP34" s="32"/>
-      <c r="AQ34" s="32"/>
-    </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="42"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="42"/>
+      <c r="N34" s="42"/>
+      <c r="O34" s="42"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="41"/>
+      <c r="S34" s="41"/>
+      <c r="T34" s="41"/>
+      <c r="U34" s="41"/>
+      <c r="V34" s="41"/>
+      <c r="W34" s="41"/>
+      <c r="X34" s="41"/>
+      <c r="Y34" s="41"/>
+      <c r="Z34" s="41"/>
+      <c r="AA34" s="41"/>
+      <c r="AB34" s="41"/>
+      <c r="AC34" s="41"/>
+      <c r="AD34" s="41"/>
+      <c r="AE34" s="41"/>
+      <c r="AF34" s="41"/>
+      <c r="AG34" s="41"/>
+      <c r="AH34" s="41"/>
+      <c r="AI34" s="41"/>
+      <c r="AJ34" s="41"/>
+      <c r="AK34" s="41"/>
+      <c r="AL34" s="41"/>
+      <c r="AM34" s="41"/>
+      <c r="AN34" s="41"/>
+      <c r="AO34" s="41"/>
+      <c r="AP34" s="41"/>
+      <c r="AQ34" s="41"/>
+    </row>
+    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B35" s="28" t="str">
         <v>No_nonDLS_limExt</v>
       </c>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47" t="s">
+      <c r="C35" s="49"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="49"/>
+      <c r="H35" s="49"/>
+      <c r="I35" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="J35" s="47"/>
-      <c r="K35" s="47"/>
-      <c r="L35" s="47"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="47"/>
-      <c r="O35" s="47"/>
-      <c r="Q35" s="32"/>
-      <c r="R35" s="32"/>
-      <c r="S35" s="32"/>
-      <c r="T35" s="32"/>
-      <c r="U35" s="32"/>
-      <c r="V35" s="32"/>
-      <c r="W35" s="32"/>
-      <c r="X35" s="32"/>
-      <c r="Y35" s="32"/>
-      <c r="Z35" s="32"/>
-      <c r="AA35" s="32"/>
-      <c r="AB35" s="32"/>
-      <c r="AC35" s="32"/>
-      <c r="AD35" s="32"/>
-      <c r="AE35" s="32"/>
-      <c r="AF35" s="32"/>
-      <c r="AG35" s="32"/>
-      <c r="AH35" s="32"/>
-      <c r="AI35" s="32"/>
-      <c r="AJ35" s="32"/>
-      <c r="AK35" s="32"/>
-      <c r="AL35" s="32"/>
-      <c r="AM35" s="32"/>
-      <c r="AN35" s="32"/>
-      <c r="AO35" s="32"/>
-      <c r="AP35" s="32"/>
-      <c r="AQ35" s="32"/>
-    </row>
-    <row r="36" spans="1:43" ht="76.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J35" s="49"/>
+      <c r="K35" s="49"/>
+      <c r="L35" s="49"/>
+      <c r="M35" s="49"/>
+      <c r="N35" s="49"/>
+      <c r="O35" s="49"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="41"/>
+      <c r="S35" s="41"/>
+      <c r="T35" s="41"/>
+      <c r="U35" s="41"/>
+      <c r="V35" s="41"/>
+      <c r="W35" s="41"/>
+      <c r="X35" s="41"/>
+      <c r="Y35" s="41"/>
+      <c r="Z35" s="41"/>
+      <c r="AA35" s="41"/>
+      <c r="AB35" s="41"/>
+      <c r="AC35" s="41"/>
+      <c r="AD35" s="41"/>
+      <c r="AE35" s="41"/>
+      <c r="AF35" s="41"/>
+      <c r="AG35" s="41"/>
+      <c r="AH35" s="41"/>
+      <c r="AI35" s="41"/>
+      <c r="AJ35" s="41"/>
+      <c r="AK35" s="41"/>
+      <c r="AL35" s="41"/>
+      <c r="AM35" s="41"/>
+      <c r="AN35" s="41"/>
+      <c r="AO35" s="41"/>
+      <c r="AP35" s="41"/>
+      <c r="AQ35" s="41"/>
+    </row>
+    <row r="36" spans="1:43" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="6" t="str">
         <v>BHN</v>
       </c>
-      <c r="C36" s="38" t="s">
+      <c r="C36" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="34"/>
-      <c r="O36" s="34"/>
-      <c r="Q36" s="32"/>
-      <c r="R36" s="32"/>
-      <c r="S36" s="32"/>
-      <c r="T36" s="32"/>
-      <c r="U36" s="32"/>
-      <c r="V36" s="32"/>
-      <c r="W36" s="32"/>
-      <c r="X36" s="32"/>
-      <c r="Y36" s="32"/>
-      <c r="Z36" s="32"/>
-      <c r="AA36" s="32"/>
-      <c r="AB36" s="32"/>
-      <c r="AC36" s="32"/>
-      <c r="AD36" s="32"/>
-      <c r="AE36" s="32"/>
-      <c r="AF36" s="32"/>
-      <c r="AG36" s="32"/>
-      <c r="AH36" s="32"/>
-      <c r="AI36" s="32"/>
-      <c r="AJ36" s="32"/>
-      <c r="AK36" s="32"/>
-      <c r="AL36" s="32"/>
-      <c r="AM36" s="32"/>
-      <c r="AN36" s="32"/>
-      <c r="AO36" s="32"/>
-      <c r="AP36" s="32"/>
-      <c r="AQ36" s="32"/>
-    </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="41"/>
+      <c r="S36" s="41"/>
+      <c r="T36" s="41"/>
+      <c r="U36" s="41"/>
+      <c r="V36" s="41"/>
+      <c r="W36" s="41"/>
+      <c r="X36" s="41"/>
+      <c r="Y36" s="41"/>
+      <c r="Z36" s="41"/>
+      <c r="AA36" s="41"/>
+      <c r="AB36" s="41"/>
+      <c r="AC36" s="41"/>
+      <c r="AD36" s="41"/>
+      <c r="AE36" s="41"/>
+      <c r="AF36" s="41"/>
+      <c r="AG36" s="41"/>
+      <c r="AH36" s="41"/>
+      <c r="AI36" s="41"/>
+      <c r="AJ36" s="41"/>
+      <c r="AK36" s="41"/>
+      <c r="AL36" s="41"/>
+      <c r="AM36" s="41"/>
+      <c r="AN36" s="41"/>
+      <c r="AO36" s="41"/>
+      <c r="AP36" s="41"/>
+      <c r="AQ36" s="41"/>
+    </row>
+    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B37" t="str">
         <v>No_non_DLS_BHNFWB</v>
       </c>
-      <c r="AB37" s="32"/>
-      <c r="AC37" s="32"/>
-      <c r="AD37" s="32"/>
-      <c r="AE37" s="32"/>
-      <c r="AF37" s="32"/>
-      <c r="AG37" s="32"/>
-      <c r="AH37" s="32"/>
-      <c r="AI37" s="32"/>
-      <c r="AJ37" s="32"/>
-      <c r="AK37" s="32"/>
-      <c r="AL37" s="32"/>
-      <c r="AM37" s="32"/>
-      <c r="AN37" s="32"/>
-      <c r="AO37" s="32"/>
-      <c r="AP37" s="32"/>
-      <c r="AQ37" s="32"/>
-    </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB38" s="32"/>
-      <c r="AC38" s="32"/>
-      <c r="AD38" s="32"/>
-      <c r="AE38" s="32"/>
-      <c r="AF38" s="32"/>
-      <c r="AG38" s="32"/>
-      <c r="AH38" s="32"/>
-      <c r="AI38" s="32"/>
-      <c r="AJ38" s="32"/>
-      <c r="AK38" s="32"/>
-      <c r="AL38" s="32"/>
-      <c r="AM38" s="32"/>
-      <c r="AN38" s="32"/>
-      <c r="AO38" s="32"/>
-      <c r="AP38" s="32"/>
-      <c r="AQ38" s="32"/>
-    </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB39" s="32"/>
-      <c r="AC39" s="32"/>
-      <c r="AD39" s="32"/>
-      <c r="AE39" s="32"/>
-      <c r="AF39" s="32"/>
-      <c r="AG39" s="32"/>
-      <c r="AH39" s="32"/>
-      <c r="AI39" s="32"/>
-      <c r="AJ39" s="32"/>
-      <c r="AK39" s="32"/>
-      <c r="AL39" s="32"/>
-      <c r="AM39" s="32"/>
-      <c r="AN39" s="32"/>
-      <c r="AO39" s="32"/>
-      <c r="AP39" s="32"/>
-      <c r="AQ39" s="32"/>
-    </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB40" s="32"/>
-      <c r="AC40" s="32"/>
-      <c r="AD40" s="32"/>
-      <c r="AE40" s="32"/>
-      <c r="AF40" s="32"/>
-      <c r="AG40" s="32"/>
-      <c r="AH40" s="32"/>
-      <c r="AI40" s="32"/>
-      <c r="AJ40" s="32"/>
-      <c r="AK40" s="32"/>
-      <c r="AL40" s="32"/>
-      <c r="AM40" s="32"/>
-      <c r="AN40" s="32"/>
-      <c r="AO40" s="32"/>
-      <c r="AP40" s="32"/>
-      <c r="AQ40" s="32"/>
-    </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB41" s="32"/>
-      <c r="AC41" s="32"/>
-      <c r="AD41" s="32"/>
-      <c r="AE41" s="32"/>
-      <c r="AF41" s="32"/>
-      <c r="AG41" s="32"/>
-      <c r="AH41" s="32"/>
-      <c r="AI41" s="32"/>
-      <c r="AJ41" s="32"/>
-      <c r="AK41" s="32"/>
-      <c r="AL41" s="32"/>
-      <c r="AM41" s="32"/>
-      <c r="AN41" s="32"/>
-      <c r="AO41" s="32"/>
-      <c r="AP41" s="32"/>
-      <c r="AQ41" s="32"/>
-    </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB42" s="32" t="e" vm="8">
+      <c r="AB37" s="41"/>
+      <c r="AC37" s="41"/>
+      <c r="AD37" s="41"/>
+      <c r="AE37" s="41"/>
+      <c r="AF37" s="41"/>
+      <c r="AG37" s="41"/>
+      <c r="AH37" s="41"/>
+      <c r="AI37" s="41"/>
+      <c r="AJ37" s="41"/>
+      <c r="AK37" s="41"/>
+      <c r="AL37" s="41"/>
+      <c r="AM37" s="41"/>
+      <c r="AN37" s="41"/>
+      <c r="AO37" s="41"/>
+      <c r="AP37" s="41"/>
+      <c r="AQ37" s="41"/>
+    </row>
+    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="B38" t="str">
+        <v>All_indicators</v>
+      </c>
+      <c r="AB38" s="41"/>
+      <c r="AC38" s="41"/>
+      <c r="AD38" s="41"/>
+      <c r="AE38" s="41"/>
+      <c r="AF38" s="41"/>
+      <c r="AG38" s="41"/>
+      <c r="AH38" s="41"/>
+      <c r="AI38" s="41"/>
+      <c r="AJ38" s="41"/>
+      <c r="AK38" s="41"/>
+      <c r="AL38" s="41"/>
+      <c r="AM38" s="41"/>
+      <c r="AN38" s="41"/>
+      <c r="AO38" s="41"/>
+      <c r="AP38" s="41"/>
+      <c r="AQ38" s="41"/>
+    </row>
+    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB39" s="41"/>
+      <c r="AC39" s="41"/>
+      <c r="AD39" s="41"/>
+      <c r="AE39" s="41"/>
+      <c r="AF39" s="41"/>
+      <c r="AG39" s="41"/>
+      <c r="AH39" s="41"/>
+      <c r="AI39" s="41"/>
+      <c r="AJ39" s="41"/>
+      <c r="AK39" s="41"/>
+      <c r="AL39" s="41"/>
+      <c r="AM39" s="41"/>
+      <c r="AN39" s="41"/>
+      <c r="AO39" s="41"/>
+      <c r="AP39" s="41"/>
+      <c r="AQ39" s="41"/>
+    </row>
+    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB40" s="41"/>
+      <c r="AC40" s="41"/>
+      <c r="AD40" s="41"/>
+      <c r="AE40" s="41"/>
+      <c r="AF40" s="41"/>
+      <c r="AG40" s="41"/>
+      <c r="AH40" s="41"/>
+      <c r="AI40" s="41"/>
+      <c r="AJ40" s="41"/>
+      <c r="AK40" s="41"/>
+      <c r="AL40" s="41"/>
+      <c r="AM40" s="41"/>
+      <c r="AN40" s="41"/>
+      <c r="AO40" s="41"/>
+      <c r="AP40" s="41"/>
+      <c r="AQ40" s="41"/>
+    </row>
+    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB41" s="41"/>
+      <c r="AC41" s="41"/>
+      <c r="AD41" s="41"/>
+      <c r="AE41" s="41"/>
+      <c r="AF41" s="41"/>
+      <c r="AG41" s="41"/>
+      <c r="AH41" s="41"/>
+      <c r="AI41" s="41"/>
+      <c r="AJ41" s="41"/>
+      <c r="AK41" s="41"/>
+      <c r="AL41" s="41"/>
+      <c r="AM41" s="41"/>
+      <c r="AN41" s="41"/>
+      <c r="AO41" s="41"/>
+      <c r="AP41" s="41"/>
+      <c r="AQ41" s="41"/>
+    </row>
+    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB42" s="41" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-      <c r="AC42" s="32"/>
-      <c r="AD42" s="32"/>
-      <c r="AE42" s="32"/>
-      <c r="AF42" s="32"/>
-      <c r="AG42" s="32"/>
-      <c r="AH42" s="32"/>
-      <c r="AI42" s="32"/>
-      <c r="AJ42" s="32"/>
-      <c r="AK42" s="32"/>
-      <c r="AL42" s="32"/>
-      <c r="AM42" s="32"/>
-      <c r="AN42" s="32"/>
-      <c r="AO42" s="32"/>
-      <c r="AP42" s="32"/>
-      <c r="AQ42" s="32"/>
-    </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB43" s="32"/>
-      <c r="AC43" s="32"/>
-      <c r="AD43" s="32"/>
-      <c r="AE43" s="32"/>
-      <c r="AF43" s="32"/>
-      <c r="AG43" s="32"/>
-      <c r="AH43" s="32"/>
-      <c r="AI43" s="32"/>
-      <c r="AJ43" s="32"/>
-      <c r="AK43" s="32"/>
-      <c r="AL43" s="32"/>
-      <c r="AM43" s="32"/>
-      <c r="AN43" s="32"/>
-      <c r="AO43" s="32"/>
-      <c r="AP43" s="32"/>
-      <c r="AQ43" s="32"/>
-    </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB44" s="32"/>
-      <c r="AC44" s="32"/>
-      <c r="AD44" s="32"/>
-      <c r="AE44" s="32"/>
-      <c r="AF44" s="32"/>
-      <c r="AG44" s="32"/>
-      <c r="AH44" s="32"/>
-      <c r="AI44" s="32"/>
-      <c r="AJ44" s="32"/>
-      <c r="AK44" s="32"/>
-      <c r="AL44" s="32"/>
-      <c r="AM44" s="32"/>
-      <c r="AN44" s="32"/>
-      <c r="AO44" s="32"/>
-      <c r="AP44" s="32"/>
-      <c r="AQ44" s="32"/>
-    </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB45" s="32"/>
-      <c r="AC45" s="32"/>
-      <c r="AD45" s="32"/>
-      <c r="AE45" s="32"/>
-      <c r="AF45" s="32"/>
-      <c r="AG45" s="32"/>
-      <c r="AH45" s="32"/>
-      <c r="AI45" s="32"/>
-      <c r="AJ45" s="32"/>
-      <c r="AK45" s="32"/>
-      <c r="AL45" s="32"/>
-      <c r="AM45" s="32"/>
-      <c r="AN45" s="32"/>
-      <c r="AO45" s="32"/>
-      <c r="AP45" s="32"/>
-      <c r="AQ45" s="32"/>
-    </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB46" s="32"/>
-      <c r="AC46" s="32"/>
-      <c r="AD46" s="32"/>
-      <c r="AE46" s="32"/>
-      <c r="AF46" s="32"/>
-      <c r="AG46" s="32"/>
-      <c r="AH46" s="32"/>
-      <c r="AI46" s="32"/>
-      <c r="AJ46" s="32"/>
-      <c r="AK46" s="32"/>
-      <c r="AL46" s="32"/>
-      <c r="AM46" s="32"/>
-      <c r="AN46" s="32"/>
-      <c r="AO46" s="32"/>
-      <c r="AP46" s="32"/>
-      <c r="AQ46" s="32"/>
-    </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB47" s="32"/>
-      <c r="AC47" s="32"/>
-      <c r="AD47" s="32"/>
-      <c r="AE47" s="32"/>
-      <c r="AF47" s="32"/>
-      <c r="AG47" s="32"/>
-      <c r="AH47" s="32"/>
-      <c r="AI47" s="32"/>
-      <c r="AJ47" s="32"/>
-      <c r="AK47" s="32"/>
-      <c r="AL47" s="32"/>
-      <c r="AM47" s="32"/>
-      <c r="AN47" s="32"/>
-      <c r="AO47" s="32"/>
-      <c r="AP47" s="32"/>
-      <c r="AQ47" s="32"/>
-    </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="AB48" s="32"/>
-      <c r="AC48" s="32"/>
-      <c r="AD48" s="32"/>
-      <c r="AE48" s="32"/>
-      <c r="AF48" s="32"/>
-      <c r="AG48" s="32"/>
-      <c r="AH48" s="32"/>
-      <c r="AI48" s="32"/>
-      <c r="AJ48" s="32"/>
-      <c r="AK48" s="32"/>
-      <c r="AL48" s="32"/>
-      <c r="AM48" s="32"/>
-      <c r="AN48" s="32"/>
-      <c r="AO48" s="32"/>
-      <c r="AP48" s="32"/>
-      <c r="AQ48" s="32"/>
-    </row>
-    <row r="49" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB49" s="32"/>
-      <c r="AC49" s="32"/>
-      <c r="AD49" s="32"/>
-      <c r="AE49" s="32"/>
-      <c r="AF49" s="32"/>
-      <c r="AG49" s="32"/>
-      <c r="AH49" s="32"/>
-      <c r="AI49" s="32"/>
-      <c r="AJ49" s="32"/>
-      <c r="AK49" s="32"/>
-      <c r="AL49" s="32"/>
-      <c r="AM49" s="32"/>
-      <c r="AN49" s="32"/>
-      <c r="AO49" s="32"/>
-      <c r="AP49" s="32"/>
-      <c r="AQ49" s="32"/>
-    </row>
-    <row r="50" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB50" s="32"/>
-      <c r="AC50" s="32"/>
-      <c r="AD50" s="32"/>
-      <c r="AE50" s="32"/>
-      <c r="AF50" s="32"/>
-      <c r="AG50" s="32"/>
-      <c r="AH50" s="32"/>
-      <c r="AI50" s="32"/>
-      <c r="AJ50" s="32"/>
-      <c r="AK50" s="32"/>
-      <c r="AL50" s="32"/>
-      <c r="AM50" s="32"/>
-      <c r="AN50" s="32"/>
-      <c r="AO50" s="32"/>
-      <c r="AP50" s="32"/>
-      <c r="AQ50" s="32"/>
-    </row>
-    <row r="51" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB51" s="32"/>
-      <c r="AC51" s="32"/>
-      <c r="AD51" s="32"/>
-      <c r="AE51" s="32"/>
-      <c r="AF51" s="32"/>
-      <c r="AG51" s="32"/>
-      <c r="AH51" s="32"/>
-      <c r="AI51" s="32"/>
-      <c r="AJ51" s="32"/>
-      <c r="AK51" s="32"/>
-      <c r="AL51" s="32"/>
-      <c r="AM51" s="32"/>
-      <c r="AN51" s="32"/>
-      <c r="AO51" s="32"/>
-      <c r="AP51" s="32"/>
-      <c r="AQ51" s="32"/>
-    </row>
-    <row r="52" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB52" s="32"/>
-      <c r="AC52" s="32"/>
-      <c r="AD52" s="32"/>
-      <c r="AE52" s="32"/>
-      <c r="AF52" s="32"/>
-      <c r="AG52" s="32"/>
-      <c r="AH52" s="32"/>
-      <c r="AI52" s="32"/>
-      <c r="AJ52" s="32"/>
-      <c r="AK52" s="32"/>
-      <c r="AL52" s="32"/>
-      <c r="AM52" s="32"/>
-      <c r="AN52" s="32"/>
-      <c r="AO52" s="32"/>
-      <c r="AP52" s="32"/>
-      <c r="AQ52" s="32"/>
-    </row>
-    <row r="53" spans="28:43" x14ac:dyDescent="0.3">
-      <c r="AB53" s="32"/>
-      <c r="AC53" s="32"/>
-      <c r="AD53" s="32"/>
-      <c r="AE53" s="32"/>
-      <c r="AF53" s="32"/>
-      <c r="AG53" s="32"/>
-      <c r="AH53" s="32"/>
-      <c r="AI53" s="32"/>
-      <c r="AJ53" s="32"/>
-      <c r="AK53" s="32"/>
-      <c r="AL53" s="32"/>
-      <c r="AM53" s="32"/>
-      <c r="AN53" s="32"/>
-      <c r="AO53" s="32"/>
-      <c r="AP53" s="32"/>
-      <c r="AQ53" s="32"/>
+      <c r="AC42" s="41"/>
+      <c r="AD42" s="41"/>
+      <c r="AE42" s="41"/>
+      <c r="AF42" s="41"/>
+      <c r="AG42" s="41"/>
+      <c r="AH42" s="41"/>
+      <c r="AI42" s="41"/>
+      <c r="AJ42" s="41"/>
+      <c r="AK42" s="41"/>
+      <c r="AL42" s="41"/>
+      <c r="AM42" s="41"/>
+      <c r="AN42" s="41"/>
+      <c r="AO42" s="41"/>
+      <c r="AP42" s="41"/>
+      <c r="AQ42" s="41"/>
+    </row>
+    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB43" s="41"/>
+      <c r="AC43" s="41"/>
+      <c r="AD43" s="41"/>
+      <c r="AE43" s="41"/>
+      <c r="AF43" s="41"/>
+      <c r="AG43" s="41"/>
+      <c r="AH43" s="41"/>
+      <c r="AI43" s="41"/>
+      <c r="AJ43" s="41"/>
+      <c r="AK43" s="41"/>
+      <c r="AL43" s="41"/>
+      <c r="AM43" s="41"/>
+      <c r="AN43" s="41"/>
+      <c r="AO43" s="41"/>
+      <c r="AP43" s="41"/>
+      <c r="AQ43" s="41"/>
+    </row>
+    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB44" s="41"/>
+      <c r="AC44" s="41"/>
+      <c r="AD44" s="41"/>
+      <c r="AE44" s="41"/>
+      <c r="AF44" s="41"/>
+      <c r="AG44" s="41"/>
+      <c r="AH44" s="41"/>
+      <c r="AI44" s="41"/>
+      <c r="AJ44" s="41"/>
+      <c r="AK44" s="41"/>
+      <c r="AL44" s="41"/>
+      <c r="AM44" s="41"/>
+      <c r="AN44" s="41"/>
+      <c r="AO44" s="41"/>
+      <c r="AP44" s="41"/>
+      <c r="AQ44" s="41"/>
+    </row>
+    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB45" s="41"/>
+      <c r="AC45" s="41"/>
+      <c r="AD45" s="41"/>
+      <c r="AE45" s="41"/>
+      <c r="AF45" s="41"/>
+      <c r="AG45" s="41"/>
+      <c r="AH45" s="41"/>
+      <c r="AI45" s="41"/>
+      <c r="AJ45" s="41"/>
+      <c r="AK45" s="41"/>
+      <c r="AL45" s="41"/>
+      <c r="AM45" s="41"/>
+      <c r="AN45" s="41"/>
+      <c r="AO45" s="41"/>
+      <c r="AP45" s="41"/>
+      <c r="AQ45" s="41"/>
+    </row>
+    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB46" s="41"/>
+      <c r="AC46" s="41"/>
+      <c r="AD46" s="41"/>
+      <c r="AE46" s="41"/>
+      <c r="AF46" s="41"/>
+      <c r="AG46" s="41"/>
+      <c r="AH46" s="41"/>
+      <c r="AI46" s="41"/>
+      <c r="AJ46" s="41"/>
+      <c r="AK46" s="41"/>
+      <c r="AL46" s="41"/>
+      <c r="AM46" s="41"/>
+      <c r="AN46" s="41"/>
+      <c r="AO46" s="41"/>
+      <c r="AP46" s="41"/>
+      <c r="AQ46" s="41"/>
+    </row>
+    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB47" s="41"/>
+      <c r="AC47" s="41"/>
+      <c r="AD47" s="41"/>
+      <c r="AE47" s="41"/>
+      <c r="AF47" s="41"/>
+      <c r="AG47" s="41"/>
+      <c r="AH47" s="41"/>
+      <c r="AI47" s="41"/>
+      <c r="AJ47" s="41"/>
+      <c r="AK47" s="41"/>
+      <c r="AL47" s="41"/>
+      <c r="AM47" s="41"/>
+      <c r="AN47" s="41"/>
+      <c r="AO47" s="41"/>
+      <c r="AP47" s="41"/>
+      <c r="AQ47" s="41"/>
+    </row>
+    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AB48" s="41"/>
+      <c r="AC48" s="41"/>
+      <c r="AD48" s="41"/>
+      <c r="AE48" s="41"/>
+      <c r="AF48" s="41"/>
+      <c r="AG48" s="41"/>
+      <c r="AH48" s="41"/>
+      <c r="AI48" s="41"/>
+      <c r="AJ48" s="41"/>
+      <c r="AK48" s="41"/>
+      <c r="AL48" s="41"/>
+      <c r="AM48" s="41"/>
+      <c r="AN48" s="41"/>
+      <c r="AO48" s="41"/>
+      <c r="AP48" s="41"/>
+      <c r="AQ48" s="41"/>
+    </row>
+    <row r="49" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB49" s="41"/>
+      <c r="AC49" s="41"/>
+      <c r="AD49" s="41"/>
+      <c r="AE49" s="41"/>
+      <c r="AF49" s="41"/>
+      <c r="AG49" s="41"/>
+      <c r="AH49" s="41"/>
+      <c r="AI49" s="41"/>
+      <c r="AJ49" s="41"/>
+      <c r="AK49" s="41"/>
+      <c r="AL49" s="41"/>
+      <c r="AM49" s="41"/>
+      <c r="AN49" s="41"/>
+      <c r="AO49" s="41"/>
+      <c r="AP49" s="41"/>
+      <c r="AQ49" s="41"/>
+    </row>
+    <row r="50" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB50" s="41"/>
+      <c r="AC50" s="41"/>
+      <c r="AD50" s="41"/>
+      <c r="AE50" s="41"/>
+      <c r="AF50" s="41"/>
+      <c r="AG50" s="41"/>
+      <c r="AH50" s="41"/>
+      <c r="AI50" s="41"/>
+      <c r="AJ50" s="41"/>
+      <c r="AK50" s="41"/>
+      <c r="AL50" s="41"/>
+      <c r="AM50" s="41"/>
+      <c r="AN50" s="41"/>
+      <c r="AO50" s="41"/>
+      <c r="AP50" s="41"/>
+      <c r="AQ50" s="41"/>
+    </row>
+    <row r="51" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB51" s="41"/>
+      <c r="AC51" s="41"/>
+      <c r="AD51" s="41"/>
+      <c r="AE51" s="41"/>
+      <c r="AF51" s="41"/>
+      <c r="AG51" s="41"/>
+      <c r="AH51" s="41"/>
+      <c r="AI51" s="41"/>
+      <c r="AJ51" s="41"/>
+      <c r="AK51" s="41"/>
+      <c r="AL51" s="41"/>
+      <c r="AM51" s="41"/>
+      <c r="AN51" s="41"/>
+      <c r="AO51" s="41"/>
+      <c r="AP51" s="41"/>
+      <c r="AQ51" s="41"/>
+    </row>
+    <row r="52" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB52" s="41"/>
+      <c r="AC52" s="41"/>
+      <c r="AD52" s="41"/>
+      <c r="AE52" s="41"/>
+      <c r="AF52" s="41"/>
+      <c r="AG52" s="41"/>
+      <c r="AH52" s="41"/>
+      <c r="AI52" s="41"/>
+      <c r="AJ52" s="41"/>
+      <c r="AK52" s="41"/>
+      <c r="AL52" s="41"/>
+      <c r="AM52" s="41"/>
+      <c r="AN52" s="41"/>
+      <c r="AO52" s="41"/>
+      <c r="AP52" s="41"/>
+      <c r="AQ52" s="41"/>
+    </row>
+    <row r="53" spans="28:43" x14ac:dyDescent="0.25">
+      <c r="AB53" s="41"/>
+      <c r="AC53" s="41"/>
+      <c r="AD53" s="41"/>
+      <c r="AE53" s="41"/>
+      <c r="AF53" s="41"/>
+      <c r="AG53" s="41"/>
+      <c r="AH53" s="41"/>
+      <c r="AI53" s="41"/>
+      <c r="AJ53" s="41"/>
+      <c r="AK53" s="41"/>
+      <c r="AL53" s="41"/>
+      <c r="AM53" s="41"/>
+      <c r="AN53" s="41"/>
+      <c r="AO53" s="41"/>
+      <c r="AP53" s="41"/>
+      <c r="AQ53" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="I27:O27"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="I28:O28"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="I21:O21"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="I22:O22"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="I35:O35"/>
+    <mergeCell ref="AR22:AY24"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="I23:O23"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="I24:O24"/>
+    <mergeCell ref="Q22:AA24"/>
+    <mergeCell ref="AB22:AQ31"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="I25:O25"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="I26:O26"/>
+    <mergeCell ref="Q26:AA29"/>
     <mergeCell ref="AB42:AQ53"/>
     <mergeCell ref="T4:X4"/>
     <mergeCell ref="AB32:AQ41"/>
@@ -5756,39 +5899,14 @@
     <mergeCell ref="I32:O32"/>
     <mergeCell ref="C33:H33"/>
     <mergeCell ref="I33:O33"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="I34:O34"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="I35:O35"/>
-    <mergeCell ref="AR22:AY24"/>
-    <mergeCell ref="C23:H23"/>
-    <mergeCell ref="I23:O23"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="I24:O24"/>
-    <mergeCell ref="Q22:AA24"/>
-    <mergeCell ref="AB22:AQ31"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="I25:O25"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="I26:O26"/>
-    <mergeCell ref="Q26:AA29"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="I27:O27"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="I28:O28"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="I21:O21"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="I22:O22"/>
   </mergeCells>
-  <conditionalFormatting sqref="C5:R15">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="C5:S15">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5798,21 +5916,21 @@
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:S65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="62.5546875" customWidth="1"/>
-    <col min="2" max="2" width="25.33203125" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" customWidth="1"/>
+    <col min="1" max="1" width="62.5703125" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" customWidth="1"/>
-    <col min="11" max="11" width="13.5546875" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -5871,7 +5989,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="str" cm="1">
         <f t="array" ref="A2:A53">TRANSPOSE('[1]1990-2020 Time-series data'!$Y$2:$BX$2)</f>
         <v xml:space="preserve">Child stunting (% of pop.) </v>
@@ -5931,7 +6049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="str">
         <v>Deaths from infectious diseases (deaths/100,000)</v>
       </c>
@@ -5990,7 +6108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="str">
         <v xml:space="preserve">Maternal mortality  (deaths/100,000 live births) </v>
       </c>
@@ -6049,7 +6167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="str">
         <v xml:space="preserve">Nutritional deficiencies (% of pop.) </v>
       </c>
@@ -6108,7 +6226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="str">
         <v xml:space="preserve">Diet low in fruits and vegetables (0=low risk; 100=high risk) </v>
       </c>
@@ -6167,7 +6285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="str">
         <v xml:space="preserve">Child mortality (deaths/1,000 live births) </v>
       </c>
@@ -6226,7 +6344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="str">
         <v xml:space="preserve">No access to a handwashing facility (0=low risk; 100=high risk) </v>
       </c>
@@ -6285,7 +6403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="str">
         <v>Deaths from unsafe water, sanitation and hygiene (deaths/100,000)</v>
       </c>
@@ -6344,7 +6462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="str">
         <v xml:space="preserve">Improved sanitation (proportion of pop.) </v>
       </c>
@@ -6403,7 +6521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="str">
         <v xml:space="preserve">Improved water source (proportion of pop.) </v>
       </c>
@@ -6462,7 +6580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="str">
         <v>Deaths from household air pollution (deaths/100,000)</v>
       </c>
@@ -6521,7 +6639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="str">
         <v xml:space="preserve">Prevalence of cooking with coal/biomass (proportion of pop.) </v>
       </c>
@@ -6580,7 +6698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="str">
         <v xml:space="preserve">Access to electricity (% of pop.) </v>
       </c>
@@ -6639,7 +6757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="str">
         <v>Deaths from road injuries (deaths/100,000)</v>
       </c>
@@ -6698,7 +6816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="str">
         <v xml:space="preserve">Political violence (0=no violence; 4=violence often) </v>
       </c>
@@ -6757,7 +6875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="str">
         <v>Political killings and torture (0=low freedom; 1=high freedom)</v>
       </c>
@@ -6816,7 +6934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="str">
         <v xml:space="preserve">Intimate partner violence against women (% of women aged 15+) </v>
       </c>
@@ -6875,7 +6993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="str">
         <v>Interpersonal violence  (deaths/100,000)</v>
       </c>
@@ -6934,7 +7052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="str">
         <v xml:space="preserve">Population with no education (proportion of pop.) </v>
       </c>
@@ -6993,7 +7111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="str">
         <v xml:space="preserve">Gender parity in basic education (distance from parity) </v>
       </c>
@@ -7052,7 +7170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="str">
         <v xml:space="preserve">Equal access to quality education (0=unequal; 4=equal) </v>
       </c>
@@ -7111,7 +7229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="str">
         <v>Mean years of schooling (years)</v>
       </c>
@@ -7170,7 +7288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="str">
         <v>Alternative sources of information (0=low; 1=high)</v>
       </c>
@@ -7229,7 +7347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="str">
         <v xml:space="preserve">Internet users (% of pop.) </v>
       </c>
@@ -7288,7 +7406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="str">
         <v xml:space="preserve">Mobile and landline telephone subscriptions (subscriptions/100 people) </v>
       </c>
@@ -7347,7 +7465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="str">
         <v>Life expectancy at 60 (years)</v>
       </c>
@@ -7406,7 +7524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="str">
         <v>Premature deaths from non-communicable diseases (deaths/100,000)</v>
       </c>
@@ -7465,7 +7583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="str">
         <v xml:space="preserve">Equal access to quality healthcare (0=unequal; 4=equal) </v>
       </c>
@@ -7524,7 +7642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="str">
         <v xml:space="preserve">Universal health coverage (% of pop.) </v>
       </c>
@@ -7583,7 +7701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="str">
         <v>Deaths from outdoor air pollution (deaths/100,000)</v>
       </c>
@@ -7642,7 +7760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="str">
         <v>Particulate matter (2.5) pollution (mean annual exposure, µg/m3)</v>
       </c>
@@ -7701,7 +7819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="str">
         <v>Deaths from lead exposure (deaths/100,000)</v>
       </c>
@@ -7760,7 +7878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="str">
         <v>Species protection (0=low; 100=high)</v>
       </c>
@@ -7819,7 +7937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="str">
         <v xml:space="preserve">Freedom of religion (0=no freedom; 4=full freedom) </v>
       </c>
@@ -7878,7 +7996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="str">
         <v xml:space="preserve">Property rights for women (0=no rights; 5=full rights) </v>
       </c>
@@ -7937,7 +8055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="str">
         <v xml:space="preserve">Freedom of assembly (0=no freedom; 4=full freedom) </v>
       </c>
@@ -7996,7 +8114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="str">
         <v>Access to justice (0=nonexistent; 1=observed)</v>
       </c>
@@ -8055,7 +8173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="str">
         <v>Freedom of discussion (0=low; 1=high)</v>
       </c>
@@ -8114,7 +8232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="str">
         <v>Political rights (1=full rights; 7=no rights)</v>
       </c>
@@ -8173,7 +8291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="str">
         <v>Public sector corruption (0=low corruption; 1=high corruption)</v>
       </c>
@@ -8232,7 +8350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="str">
         <v>Freedom of domestic movement (0=low; 1=high)</v>
       </c>
@@ -8291,7 +8409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="str">
         <v>Satisfied demand for contraception (% satisfied demand)</v>
       </c>
@@ -8350,7 +8468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="str">
         <v>Early marriage (% of married women aged 15-19)</v>
       </c>
@@ -8409,7 +8527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="str">
         <v xml:space="preserve">Vulnerable employment (% of total employment) </v>
       </c>
@@ -8468,7 +8586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="str">
         <v>Equal protection of social groups (0=low; 1=high)</v>
       </c>
@@ -8527,7 +8645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="str">
         <v>Equal access to power (0=low; 1=high)</v>
       </c>
@@ -8586,7 +8704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="str">
         <v xml:space="preserve">Power distributed by sexual orientation (0=extremely unequal; 3=equal) </v>
       </c>
@@ -8645,7 +8763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="str">
         <v xml:space="preserve">Access to public services distributed by social group (0=extremely unequal; 4=equal) </v>
       </c>
@@ -8704,7 +8822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="str">
         <v xml:space="preserve">Population with advanced education (proportion of pop.) </v>
       </c>
@@ -8763,7 +8881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="str">
         <v xml:space="preserve">Gender parity in advanced education (distance from parity) </v>
       </c>
@@ -8822,7 +8940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="str">
         <v>Respect for academic freedom (0=low; 1=high)</v>
       </c>
@@ -8881,7 +8999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="str">
         <v>Years of tertiary schooling (years)</v>
       </c>
@@ -8940,7 +9058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>2</v>
       </c>
@@ -8999,7 +9117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>3</v>
       </c>
@@ -9058,7 +9176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -9117,7 +9235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -9176,7 +9294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -9235,7 +9353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -9294,7 +9412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -9353,7 +9471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -9412,7 +9530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -9471,7 +9589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -9530,7 +9648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>12</v>
       </c>
@@ -9589,7 +9707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>27</v>
       </c>
@@ -9605,13 +9723,13 @@
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A3:D67"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="61.6640625" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" customWidth="1"/>
+    <col min="2" max="2" width="61.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -9622,7 +9740,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -9634,7 +9752,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="str">
         <v>Deaths from infectious diseases (deaths/100,000)</v>
       </c>
@@ -9642,7 +9760,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="str">
         <v xml:space="preserve">Maternal mortality  (deaths/100,000 live births) </v>
       </c>
@@ -9650,7 +9768,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="str">
         <v xml:space="preserve">Nutritional deficiencies (% of pop.) </v>
       </c>
@@ -9658,7 +9776,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="str">
         <v xml:space="preserve">Diet low in fruits and vegetables (0=low risk; 100=high risk) </v>
       </c>
@@ -9666,7 +9784,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="str">
         <v xml:space="preserve">Child mortality (deaths/1,000 live births) </v>
       </c>
@@ -9674,7 +9792,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="str">
         <v xml:space="preserve">No access to a handwashing facility (0=low risk; 100=high risk) </v>
       </c>
@@ -9682,7 +9800,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="str">
         <v>Deaths from unsafe water, sanitation and hygiene (deaths/100,000)</v>
       </c>
@@ -9690,7 +9808,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="str">
         <v xml:space="preserve">Improved sanitation (proportion of pop.) </v>
       </c>
@@ -9698,7 +9816,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="str">
         <v xml:space="preserve">Improved water source (proportion of pop.) </v>
       </c>
@@ -9706,7 +9824,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -9717,7 +9835,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="str">
         <v xml:space="preserve">Prevalence of cooking with coal/biomass (proportion of pop.) </v>
       </c>
@@ -9725,7 +9843,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="str">
         <v xml:space="preserve">Access to electricity (% of pop.) </v>
       </c>
@@ -9733,7 +9851,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="str">
         <v>Deaths from road injuries (deaths/100,000)</v>
       </c>
@@ -9741,7 +9859,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="str">
         <v xml:space="preserve">Political violence (0=no violence; 4=violence often) </v>
       </c>
@@ -9749,7 +9867,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="str">
         <v>Political killings and torture (0=low freedom; 1=high freedom)</v>
       </c>
@@ -9757,7 +9875,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="str">
         <v xml:space="preserve">Intimate partner violence against women (% of women aged 15+) </v>
       </c>
@@ -9765,7 +9883,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="str">
         <v>Interpersonal violence  (deaths/100,000)</v>
       </c>
@@ -9773,7 +9891,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="str">
         <v xml:space="preserve">Population with no education (proportion of pop.) </v>
       </c>
@@ -9781,7 +9899,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="str">
         <v xml:space="preserve">Gender parity in basic education (distance from parity) </v>
       </c>
@@ -9789,7 +9907,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="str">
         <v xml:space="preserve">Equal access to quality education (0=unequal; 4=equal) </v>
       </c>
@@ -9797,7 +9915,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="str">
         <v>Mean years of schooling (years)</v>
       </c>
@@ -9805,7 +9923,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="str">
         <v>Alternative sources of information (0=low; 1=high)</v>
       </c>
@@ -9813,7 +9931,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="str">
         <v xml:space="preserve">Internet users (% of pop.) </v>
       </c>
@@ -9821,7 +9939,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="str">
         <v xml:space="preserve">Mobile and landline telephone subscriptions (subscriptions/100 people) </v>
       </c>
@@ -9829,7 +9947,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="str">
         <v>Life expectancy at 60 (years)</v>
       </c>
@@ -9837,7 +9955,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="str">
         <v>Premature deaths from non-communicable diseases (deaths/100,000)</v>
       </c>
@@ -9845,7 +9963,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="str">
         <v xml:space="preserve">Equal access to quality healthcare (0=unequal; 4=equal) </v>
       </c>
@@ -9853,7 +9971,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="str">
         <v xml:space="preserve">Universal health coverage (% of pop.) </v>
       </c>
@@ -9861,7 +9979,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="str">
         <v>Deaths from outdoor air pollution (deaths/100,000)</v>
       </c>
@@ -9869,7 +9987,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="str">
         <v>Particulate matter (2.5) pollution (mean annual exposure, µg/m3)</v>
       </c>
@@ -9877,7 +9995,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="str">
         <v>Deaths from lead exposure (deaths/100,000)</v>
       </c>
@@ -9885,7 +10003,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="str">
         <v>Species protection (0=low; 100=high)</v>
       </c>
@@ -9893,7 +10011,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -9904,7 +10022,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B38" s="4" t="str">
         <v xml:space="preserve">Property rights for women (0=no rights; 5=full rights) </v>
       </c>
@@ -9912,7 +10030,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B39" s="4" t="str">
         <v xml:space="preserve">Freedom of assembly (0=no freedom; 4=full freedom) </v>
       </c>
@@ -9920,7 +10038,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="str">
         <v>Access to justice (0=nonexistent; 1=observed)</v>
       </c>
@@ -9928,7 +10046,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B41" s="4" t="str">
         <v>Freedom of discussion (0=low; 1=high)</v>
       </c>
@@ -9936,7 +10054,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B42" s="4" t="str">
         <v>Political rights (1=full rights; 7=no rights)</v>
       </c>
@@ -9944,7 +10062,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B43" s="4" t="str">
         <v>Public sector corruption (0=low corruption; 1=high corruption)</v>
       </c>
@@ -9952,7 +10070,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B44" s="4" t="str">
         <v>Freedom of domestic movement (0=low; 1=high)</v>
       </c>
@@ -9960,7 +10078,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="str">
         <v>Satisfied demand for contraception (% satisfied demand)</v>
       </c>
@@ -9968,7 +10086,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B46" s="4" t="str">
         <v>Early marriage (% of married women aged 15-19)</v>
       </c>
@@ -9976,7 +10094,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B47" s="4" t="str">
         <v xml:space="preserve">Vulnerable employment (% of total employment) </v>
       </c>
@@ -9984,7 +10102,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B48" s="4" t="str">
         <v>Equal protection of social groups (0=low; 1=high)</v>
       </c>
@@ -9992,7 +10110,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B49" s="4" t="str">
         <v>Equal access to power (0=low; 1=high)</v>
       </c>
@@ -10000,7 +10118,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B50" s="4" t="str">
         <v xml:space="preserve">Power distributed by sexual orientation (0=extremely unequal; 3=equal) </v>
       </c>
@@ -10008,7 +10126,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="str">
         <v xml:space="preserve">Access to public services distributed by social group (0=extremely unequal; 4=equal) </v>
       </c>
@@ -10016,7 +10134,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B52" s="4" t="str">
         <v xml:space="preserve">Population with advanced education (proportion of pop.) </v>
       </c>
@@ -10024,7 +10142,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="str">
         <v xml:space="preserve">Gender parity in advanced education (distance from parity) </v>
       </c>
@@ -10032,7 +10150,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B54" s="4" t="str">
         <v>Respect for academic freedom (0=low; 1=high)</v>
       </c>
@@ -10040,7 +10158,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B55" s="4" t="str">
         <v>Years of tertiary schooling (years)</v>
       </c>
@@ -10048,7 +10166,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>1</v>
       </c>
@@ -10059,7 +10177,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>3</v>
       </c>
@@ -10067,7 +10185,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>4</v>
       </c>
@@ -10075,7 +10193,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>5</v>
       </c>
@@ -10083,7 +10201,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>7</v>
       </c>
@@ -10091,7 +10209,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>6</v>
       </c>
@@ -10099,7 +10217,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>8</v>
       </c>
@@ -10107,7 +10225,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>9</v>
       </c>
@@ -10115,7 +10233,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>10</v>
       </c>
@@ -10123,7 +10241,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>11</v>
       </c>
@@ -10131,7 +10249,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>12</v>
       </c>
@@ -10139,7 +10257,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
         <v>27</v>
       </c>
@@ -10150,4 +10268,595 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D964353-93EB-4651-8113-59130569BFF4}">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.5703125" customWidth="1"/>
+    <col min="2" max="11" width="5.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="127.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="54" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="54" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="K1" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="P1" s="52"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="56" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="31">
+        <v>3</v>
+      </c>
+      <c r="C2" s="31">
+        <v>3</v>
+      </c>
+      <c r="D2" s="31">
+        <v>5</v>
+      </c>
+      <c r="E2" s="31">
+        <v>5</v>
+      </c>
+      <c r="F2" s="31">
+        <v>3</v>
+      </c>
+      <c r="G2" s="31">
+        <v>5</v>
+      </c>
+      <c r="H2" s="31">
+        <v>1</v>
+      </c>
+      <c r="I2" s="31">
+        <v>1</v>
+      </c>
+      <c r="J2" s="31">
+        <v>1</v>
+      </c>
+      <c r="K2" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="31">
+        <v>7</v>
+      </c>
+      <c r="C3" s="31">
+        <v>7</v>
+      </c>
+      <c r="D3" s="31">
+        <v>10</v>
+      </c>
+      <c r="E3" s="31">
+        <v>10</v>
+      </c>
+      <c r="F3" s="31">
+        <v>7</v>
+      </c>
+      <c r="G3" s="31">
+        <v>10</v>
+      </c>
+      <c r="H3" s="31">
+        <v>1</v>
+      </c>
+      <c r="I3" s="31">
+        <v>1</v>
+      </c>
+      <c r="J3" s="31">
+        <v>1</v>
+      </c>
+      <c r="K3" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="31">
+        <v>3</v>
+      </c>
+      <c r="C4" s="31">
+        <v>3</v>
+      </c>
+      <c r="D4" s="31">
+        <v>4</v>
+      </c>
+      <c r="E4" s="31">
+        <v>4</v>
+      </c>
+      <c r="F4" s="31">
+        <v>3</v>
+      </c>
+      <c r="G4" s="31">
+        <v>4</v>
+      </c>
+      <c r="H4" s="31">
+        <v>2</v>
+      </c>
+      <c r="I4" s="31">
+        <v>2</v>
+      </c>
+      <c r="J4" s="31">
+        <v>2</v>
+      </c>
+      <c r="K4" s="31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="31">
+        <v>1</v>
+      </c>
+      <c r="C5" s="31">
+        <v>1</v>
+      </c>
+      <c r="D5" s="31">
+        <v>2</v>
+      </c>
+      <c r="E5" s="31">
+        <v>2</v>
+      </c>
+      <c r="F5" s="31">
+        <v>1</v>
+      </c>
+      <c r="G5" s="31">
+        <v>2</v>
+      </c>
+      <c r="H5" s="31">
+        <v>1</v>
+      </c>
+      <c r="I5" s="31">
+        <v>1</v>
+      </c>
+      <c r="J5" s="31">
+        <v>1</v>
+      </c>
+      <c r="K5" s="31">
+        <v>1</v>
+      </c>
+      <c r="P5" t="str" cm="1">
+        <f t="array" ref="P5:P14">TRANSPOSE(B1:K1)</f>
+        <v>Baseline</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="56" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="31">
+        <v>2</v>
+      </c>
+      <c r="C6" s="31">
+        <v>2</v>
+      </c>
+      <c r="D6" s="31">
+        <v>2</v>
+      </c>
+      <c r="E6" s="31">
+        <v>2</v>
+      </c>
+      <c r="F6" s="31">
+        <v>2</v>
+      </c>
+      <c r="G6" s="31">
+        <v>2</v>
+      </c>
+      <c r="H6" s="31">
+        <v>1</v>
+      </c>
+      <c r="I6" s="31">
+        <v>1</v>
+      </c>
+      <c r="J6" s="31">
+        <v>1</v>
+      </c>
+      <c r="K6" s="31">
+        <v>1</v>
+      </c>
+      <c r="P6" t="str">
+        <v>BHN_FWB</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="56" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="31">
+        <v>1</v>
+      </c>
+      <c r="C7" s="31">
+        <v>1</v>
+      </c>
+      <c r="D7" s="31">
+        <v>1</v>
+      </c>
+      <c r="E7" s="31">
+        <v>1</v>
+      </c>
+      <c r="F7" s="31">
+        <v>1</v>
+      </c>
+      <c r="G7" s="31">
+        <v>1</v>
+      </c>
+      <c r="H7" s="31">
+        <v>1</v>
+      </c>
+      <c r="I7" s="31">
+        <v>1</v>
+      </c>
+      <c r="J7" s="31">
+        <v>1</v>
+      </c>
+      <c r="K7" s="31">
+        <v>1</v>
+      </c>
+      <c r="P7" t="str">
+        <v>SPI_Extended</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="31">
+        <v>8</v>
+      </c>
+      <c r="C8" s="31">
+        <v>4</v>
+      </c>
+      <c r="D8" s="31">
+        <v>9</v>
+      </c>
+      <c r="E8" s="31">
+        <v>9</v>
+      </c>
+      <c r="F8" s="31">
+        <v>8</v>
+      </c>
+      <c r="G8" s="31">
+        <v>5</v>
+      </c>
+      <c r="H8" s="31">
+        <v>1</v>
+      </c>
+      <c r="I8" s="31">
+        <v>1</v>
+      </c>
+      <c r="J8" s="31">
+        <v>1</v>
+      </c>
+      <c r="K8" s="31">
+        <v>1</v>
+      </c>
+      <c r="P8" t="str">
+        <v>DLS_dim_only</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="56" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="31">
+        <v>3</v>
+      </c>
+      <c r="C9" s="31">
+        <v>3</v>
+      </c>
+      <c r="D9" s="31">
+        <v>3</v>
+      </c>
+      <c r="E9" s="31">
+        <v>3</v>
+      </c>
+      <c r="F9" s="31">
+        <v>3</v>
+      </c>
+      <c r="G9" s="31">
+        <v>3</v>
+      </c>
+      <c r="H9" s="31">
+        <v>2</v>
+      </c>
+      <c r="I9" s="31">
+        <v>2</v>
+      </c>
+      <c r="J9" s="31">
+        <v>2</v>
+      </c>
+      <c r="K9" s="31">
+        <v>2</v>
+      </c>
+      <c r="P9" t="str">
+        <v>DLS_dim_only_limExt</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="31">
+        <v>0</v>
+      </c>
+      <c r="C10" s="31">
+        <v>0</v>
+      </c>
+      <c r="D10" s="31">
+        <v>1</v>
+      </c>
+      <c r="E10" s="31">
+        <v>1</v>
+      </c>
+      <c r="F10" s="31">
+        <v>1</v>
+      </c>
+      <c r="G10" s="31">
+        <v>1</v>
+      </c>
+      <c r="H10" s="31">
+        <v>1</v>
+      </c>
+      <c r="I10" s="31">
+        <v>1</v>
+      </c>
+      <c r="J10" s="31">
+        <v>1</v>
+      </c>
+      <c r="K10" s="31">
+        <v>1</v>
+      </c>
+      <c r="P10" t="str">
+        <v>DLS_dim_only_BHNFWB</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="56" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="59">
+        <v>0</v>
+      </c>
+      <c r="C11" s="59">
+        <v>0</v>
+      </c>
+      <c r="D11" s="59">
+        <v>0</v>
+      </c>
+      <c r="E11" s="59">
+        <v>0</v>
+      </c>
+      <c r="F11" s="59">
+        <v>0</v>
+      </c>
+      <c r="G11" s="59">
+        <v>0</v>
+      </c>
+      <c r="H11" s="59">
+        <v>0</v>
+      </c>
+      <c r="I11" s="59">
+        <v>0</v>
+      </c>
+      <c r="J11" s="59">
+        <v>0</v>
+      </c>
+      <c r="K11" s="59">
+        <v>0</v>
+      </c>
+      <c r="P11" t="str">
+        <v>DLSFew_coverage</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="57" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="53">
+        <v>24</v>
+      </c>
+      <c r="C12" s="53">
+        <v>9</v>
+      </c>
+      <c r="D12" s="53">
+        <v>25</v>
+      </c>
+      <c r="E12" s="53">
+        <v>0</v>
+      </c>
+      <c r="F12" s="53">
+        <v>0</v>
+      </c>
+      <c r="G12" s="53">
+        <v>0</v>
+      </c>
+      <c r="H12" s="53">
+        <v>0</v>
+      </c>
+      <c r="I12" s="53">
+        <v>0</v>
+      </c>
+      <c r="J12" s="53">
+        <v>0</v>
+      </c>
+      <c r="K12" s="53">
+        <v>0</v>
+      </c>
+      <c r="P12" t="str">
+        <v>DLSFew_coverage_90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="60">
+        <v>52</v>
+      </c>
+      <c r="C13" s="60">
+        <v>33</v>
+      </c>
+      <c r="D13" s="60">
+        <v>62</v>
+      </c>
+      <c r="E13" s="60">
+        <v>37</v>
+      </c>
+      <c r="F13" s="60">
+        <v>29</v>
+      </c>
+      <c r="G13" s="60">
+        <v>33</v>
+      </c>
+      <c r="H13" s="60">
+        <v>11</v>
+      </c>
+      <c r="I13" s="60">
+        <v>11</v>
+      </c>
+      <c r="J13" s="60">
+        <v>11</v>
+      </c>
+      <c r="K13" s="60">
+        <v>11</v>
+      </c>
+      <c r="P13" t="str">
+        <v>DLSFew_bestAlignment</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="31">
+        <v>52</v>
+      </c>
+      <c r="C14" s="31">
+        <v>33</v>
+      </c>
+      <c r="D14" s="31">
+        <v>52</v>
+      </c>
+      <c r="E14" s="31">
+        <v>28</v>
+      </c>
+      <c r="F14" s="31">
+        <v>28</v>
+      </c>
+      <c r="G14" s="31">
+        <v>24</v>
+      </c>
+      <c r="H14" s="31">
+        <v>10</v>
+      </c>
+      <c r="I14" s="31">
+        <v>10</v>
+      </c>
+      <c r="J14" s="31">
+        <v>7</v>
+      </c>
+      <c r="K14" s="31">
+        <v>7</v>
+      </c>
+      <c r="P14" t="str">
+        <v>DLSFew_bestAlignment_90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="31">
+        <v>0</v>
+      </c>
+      <c r="C15" s="31">
+        <v>0</v>
+      </c>
+      <c r="D15" s="31">
+        <v>10</v>
+      </c>
+      <c r="E15" s="31">
+        <v>9</v>
+      </c>
+      <c r="F15" s="31">
+        <v>1</v>
+      </c>
+      <c r="G15" s="31">
+        <v>9</v>
+      </c>
+      <c r="H15" s="31">
+        <v>1</v>
+      </c>
+      <c r="I15" s="31">
+        <v>1</v>
+      </c>
+      <c r="J15" s="31">
+        <v>4</v>
+      </c>
+      <c r="K15" s="31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B2:K12">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>B2&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/IndicatorsForClusters.xlsx
+++ b/IndicatorsForClusters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1c3256d208fb6548/Personlig/Aske Banke Consultancy/YALE/Metodeartikel_WorldDevelopmentJournal/WorldDevelopmentArticleGit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="543" documentId="8_{9856C943-DD01-465B-AD17-0E409E296684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8878DECD-3FB3-4C5B-B7AB-34D399F750D7}"/>
+  <xr:revisionPtr revIDLastSave="741" documentId="8_{9856C943-DD01-465B-AD17-0E409E296684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC687424-937E-4C92-895A-E846DA2EB505}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{726B2859-724A-4801-8E74-5A4E1AFAB973}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{726B2859-724A-4801-8E74-5A4E1AFAB973}"/>
   </bookViews>
   <sheets>
     <sheet name="Unscaled Experiments" sheetId="2" r:id="rId1"/>
@@ -18,9 +18,11 @@
     <sheet name="Experiments" sheetId="3" r:id="rId3"/>
     <sheet name="Overview of indicators and DLS" sheetId="1" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="6" r:id="rId5"/>
+    <sheet name="New table in report" sheetId="7" r:id="rId6"/>
+    <sheet name="Old table in report" sheetId="8" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -170,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="198">
   <si>
     <t>SPI</t>
   </si>
@@ -438,13 +440,852 @@
   </si>
   <si>
     <t>DLSFew_bestAlignment_90</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>DLS Indicator</t>
+  </si>
+  <si>
+    <t>DHS Variables with Minimum Thresholds Used to Define DLS</t>
+  </si>
+  <si>
+    <t>Food/Nutrition</t>
+  </si>
+  <si>
+    <t>Food prep/storage</t>
+  </si>
+  <si>
+    <r>
+      <t>Main source of drinking water (hv201):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Household has access to “Safely managed” drinking water as per WASH guidelines</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Type of toilet (hv205):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Household has access to “Safely managed” toilet facility as per WASH guidelines</t>
+    </r>
+  </si>
+  <si>
+    <t>Provision of health care</t>
+  </si>
+  <si>
+    <r>
+      <t>Problems faced in getting healthcare (v467a–v467j):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Binary indicator. If any of v467a–v467j indicates no access, response = 1</t>
+    </r>
+  </si>
+  <si>
+    <t>Social Connectedness</t>
+  </si>
+  <si>
+    <t>Indicators used in this study</t>
+  </si>
+  <si>
+    <t>Access to electricity </t>
+  </si>
+  <si>
+    <t>Child stunting </t>
+  </si>
+  <si>
+    <t>Nutritional deficiencies </t>
+  </si>
+  <si>
+    <t>Diet low in fruits and vegetables </t>
+  </si>
+  <si>
+    <t>Daily Calorie supply </t>
+  </si>
+  <si>
+    <t>Protein supply </t>
+  </si>
+  <si>
+    <t>Deaths from household air pollution </t>
+  </si>
+  <si>
+    <t>Prevalence of cooking with coal/biomass </t>
+  </si>
+  <si>
+    <t>Clean Fuels </t>
+  </si>
+  <si>
+    <t>No access to a handwashing facility </t>
+  </si>
+  <si>
+    <t>Deaths from unsafe water, sanitation and hygiene </t>
+  </si>
+  <si>
+    <t>Improved water source </t>
+  </si>
+  <si>
+    <t>Safely Managed Drinking Water </t>
+  </si>
+  <si>
+    <t>Improved sanitation </t>
+  </si>
+  <si>
+    <t>Safely Managed Sanitation </t>
+  </si>
+  <si>
+    <t>Deaths from infectious diseases </t>
+  </si>
+  <si>
+    <t>Maternal mortality </t>
+  </si>
+  <si>
+    <t>Child mortality  </t>
+  </si>
+  <si>
+    <t>Life expectancy at 60 years </t>
+  </si>
+  <si>
+    <t>Healthy life expectancy </t>
+  </si>
+  <si>
+    <t>Premature deaths from non-communicable diseases </t>
+  </si>
+  <si>
+    <t>Equal access to quality healthcare </t>
+  </si>
+  <si>
+    <t>Universal health coverage </t>
+  </si>
+  <si>
+    <t>Physicians per 1000 </t>
+  </si>
+  <si>
+    <t>Hospital beds per 1000 </t>
+  </si>
+  <si>
+    <t>Primary School Enrollment </t>
+  </si>
+  <si>
+    <t>Gender parity in basic/advanced education (distance from parity)  </t>
+  </si>
+  <si>
+    <t>Equal access to quality education (0=unequal; 4=equal)  </t>
+  </si>
+  <si>
+    <t>Mean years of schooling (years) </t>
+  </si>
+  <si>
+    <t>Population with advanced education (proportion of pop.)  </t>
+  </si>
+  <si>
+    <t>Years of tertiary schooling (years) </t>
+  </si>
+  <si>
+    <t>Respect for academic freedom (0=low; 1=high) </t>
+  </si>
+  <si>
+    <t>Population with no/advanced education (proportion of pop.)  </t>
+  </si>
+  <si>
+    <t>Alternative sources of information (0=low; 1=high) </t>
+  </si>
+  <si>
+    <t>Internet users (% of pop.)  </t>
+  </si>
+  <si>
+    <t>Mobile and landline telephone subscriptions (subscriptions/100 people)  </t>
+  </si>
+  <si>
+    <t>Child stunting</t>
+  </si>
+  <si>
+    <r>
+      <t>Household possesses bicycle (hv210):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If has bicycle, response = 1
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Household possesses motorcycle (hv211):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If has motorcycle, response = 1
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Household possesses car (hv212):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If has car, response = 1</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(All Binary Indicators)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Household possesses radio (hv207):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If has radio, response = 1
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Household possesses television (hv208):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If has TV, response = 1
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Household possesses computer (hv243):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If has computer, response = 1
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Household possesses telephone (hv221):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If has telephone, response = 1
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Household possesses cell phone (hv243A):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If has cellphone, response = 1</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(All Binary Indicators)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Is the household member still in school? (hv110):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Binary indicator. If in school and belongs to compulsory schooling age, response = 1
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Age of household members (hv105):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Compulsory schooling age between 6 and 10</t>
+    </r>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>UN HABITAT</t>
+  </si>
+  <si>
+    <r>
+      <t>BMI (v445):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If BMI is below 1850, then undernourished.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Height (v438):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> For BMI calculation
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Weight (v437):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> For BMI calculation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Wall material (hv214):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Finished wall materials (tin, cement, stone, bricks, wood planks)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Roof material (hv215):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Finished roof materials (tin, wood, ceramic tiles, cement, roofing shingles)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Access to electricity (hv206):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Binary indicator. If household has access, response = 1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Floor Material (hv213):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Finished floor material (parquet or polished wood, tiles, cement, carpet)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Household size (hv009)/Number of rooms (hv216):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Number of people per room is less than 3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Household has a refrigerator (hv209):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Binary indicator. If household has refrigerator, response = 1
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Household uses modern cooking fuel (hv239):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Household has access to at least one of the following types of fuels: gas, LPG, electricity, solar</t>
+    </r>
+  </si>
+  <si>
+    <t>The indicator used is an aggregate indicator measuring lack of one or more of the following: access to improved water, improved sanitation, sufficient living area, housing durability and security of tenure.  Rural population is not considered.</t>
+  </si>
+  <si>
+    <t>FAO</t>
+  </si>
+  <si>
+    <t>World Bank</t>
+  </si>
+  <si>
+    <t>UNESCO</t>
+  </si>
+  <si>
+    <t>https://data.worldbank.org/indicator/SE.PRM.NENR</t>
+  </si>
+  <si>
+    <t>https://databank.worldbank.org/source/world-development-indicators/Series/SH.MED.BEDS.ZS</t>
+  </si>
+  <si>
+    <t>https://databank.worldbank.org/source/health-nutrition-and-population-statistics/Series/SH.MED.PHYS.ZS</t>
+  </si>
+  <si>
+    <t>https://data.unhabitat.org/pages/housing-slums-and-informal-settlements</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>https://data.worldbank.org/indicator/SH.STA.SMSS.ZS</t>
+  </si>
+  <si>
+    <t>WHO / UNICEF JMP</t>
+  </si>
+  <si>
+    <t>https://data.worldbank.org/indicator/SH.H2O.SMDW.ZS</t>
+  </si>
+  <si>
+    <t>https://data.worldbank.org/indicator/EG.CFT.ACCS.ZS</t>
+  </si>
+  <si>
+    <t>IEA</t>
+  </si>
+  <si>
+    <t>https://www.who.int/data/gho/data/indicators/indicator-details/GHO/gho-ghe-hale-healthy-life-expectancy-at-birth</t>
+  </si>
+  <si>
+    <t>WHO</t>
+  </si>
+  <si>
+    <t>DLS answered</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Share of urban population living in slums</t>
+  </si>
+  <si>
+    <r>
+      <t>DLS dimension</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF0078D4"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>DHS variables </t>
+  </si>
+  <si>
+    <t>Indicator used in this study </t>
+  </si>
+  <si>
+    <t>Source </t>
+  </si>
+  <si>
+    <r>
+      <t>Comment</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>Housing </t>
+  </si>
+  <si>
+    <t>Floor type </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Share slums </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Share of urban population living in slums </t>
+    </r>
+  </si>
+  <si>
+    <t>Household size </t>
+  </si>
+  <si>
+    <t>Number of rooms </t>
+  </si>
+  <si>
+    <t>Thermal comfort </t>
+  </si>
+  <si>
+    <t>Wall type </t>
+  </si>
+  <si>
+    <t>Roof type </t>
+  </si>
+  <si>
+    <t>Electricity access </t>
+  </si>
+  <si>
+    <t>Food &amp; nutrition </t>
+  </si>
+  <si>
+    <t>Age of household members </t>
+  </si>
+  <si>
+    <t>Weight/heigh of household members </t>
+  </si>
+  <si>
+    <t>Food preparation </t>
+  </si>
+  <si>
+    <t>Use of modern cooking fuels </t>
+  </si>
+  <si>
+    <t>Possession of fridge </t>
+  </si>
+  <si>
+    <t>Water </t>
+  </si>
+  <si>
+    <t>Main water source (based on WASH criteria) </t>
+  </si>
+  <si>
+    <t>Sanitation </t>
+  </si>
+  <si>
+    <t>Type of toilet (based on WASH criteria) </t>
+  </si>
+  <si>
+    <t>Health Care </t>
+  </si>
+  <si>
+    <t>Reason for not using health care related to accessibility issues  </t>
+  </si>
+  <si>
+    <t>Education  </t>
+  </si>
+  <si>
+    <t>Highest level of schooling </t>
+  </si>
+  <si>
+    <t>Social Connectedness </t>
+  </si>
+  <si>
+    <r>
+      <t>House</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color rgb="FF0078D4"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>h</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ol</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color rgb="FF0078D4"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>s information assets (e.g. radio, tv, computer) </t>
+    </r>
+  </si>
+  <si>
+    <t>Communication assets (e.g. phone or mobile) </t>
+  </si>
+  <si>
+    <t>Physical Connectedness </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -479,6 +1320,81 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FF0078D4"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0078D4"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FF0078D4"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FF0078D4"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -531,7 +1447,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -608,11 +1524,295 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF999999"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF999999"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF999999"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF999999"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF999999"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF666666"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF666666"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF666666"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF666666"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF666666"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -661,66 +1861,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
@@ -734,14 +1874,228 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
@@ -1405,18 +2759,18 @@
       <c r="B3" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="34" t="s">
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="J3" s="35"/>
+      <c r="J3" s="52"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
@@ -1480,13 +2834,13 @@
       <c r="Q4" s="9" t="str">
         <v>BHN</v>
       </c>
-      <c r="T4" s="43" t="s">
+      <c r="T4" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="U4" s="43"/>
-      <c r="V4" s="43"/>
-      <c r="W4" s="43"/>
-      <c r="X4" s="43"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="40"/>
+      <c r="W4" s="40"/>
+      <c r="X4" s="40"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="str" cm="1">
@@ -2430,23 +3784,23 @@
       <c r="B21" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36" t="s">
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="53"/>
       <c r="Q21" s="1" t="s">
         <v>58</v>
       </c>
@@ -2462,21 +3816,21 @@
         <f t="array" ref="B22:B36">TRANSPOSE(_xlfn.ANCHORARRAY(C4))</f>
         <v>BHN_FWB</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C22" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
-      <c r="O22" s="33"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="48"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="48"/>
+      <c r="O22" s="48"/>
       <c r="Q22" s="41" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -2526,21 +3880,21 @@
       <c r="B23" s="7" t="str">
         <v>BHN_FWB_AllExt</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="33"/>
-      <c r="N23" s="33"/>
-      <c r="O23" s="33"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="48"/>
+      <c r="M23" s="48"/>
+      <c r="N23" s="48"/>
+      <c r="O23" s="48"/>
       <c r="Q23" s="41"/>
       <c r="R23" s="41"/>
       <c r="S23" s="41"/>
@@ -2584,21 +3938,21 @@
       <c r="B24" s="7" t="str">
         <v>Few_indicators_closest_DLS_coverage</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="49"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="48"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="48"/>
+      <c r="O24" s="48"/>
       <c r="Q24" s="41"/>
       <c r="R24" s="41"/>
       <c r="S24" s="41"/>
@@ -2642,21 +3996,21 @@
       <c r="B25" s="7" t="str">
         <v>Few_indicators_SPI_preferred</v>
       </c>
-      <c r="C25" s="37" t="s">
+      <c r="C25" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="33"/>
-      <c r="N25" s="33"/>
-      <c r="O25" s="33"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="48"/>
+      <c r="L25" s="48"/>
+      <c r="M25" s="48"/>
+      <c r="N25" s="48"/>
+      <c r="O25" s="48"/>
       <c r="Q25" s="41"/>
       <c r="R25" s="41"/>
       <c r="S25" s="41"/>
@@ -2692,21 +4046,21 @@
       <c r="B26" s="7" t="str">
         <v>No_non_DLS</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33"/>
-      <c r="O26" s="33"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="48"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="48"/>
+      <c r="O26" s="48"/>
       <c r="Q26" s="41" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
@@ -2744,21 +4098,21 @@
       <c r="B27" s="7" t="str">
         <v>Only_%_of_pop</v>
       </c>
-      <c r="C27" s="32" t="s">
+      <c r="C27" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="33"/>
-      <c r="O27" s="33"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="48"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="48"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="48"/>
+      <c r="O27" s="48"/>
       <c r="Q27" s="41"/>
       <c r="R27" s="41"/>
       <c r="S27" s="41"/>
@@ -2794,21 +4148,21 @@
       <c r="B28" s="17" t="str">
         <v>Few_indicators_closest_DLS_coverage_90</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="40"/>
-      <c r="M28" s="40"/>
-      <c r="N28" s="40"/>
-      <c r="O28" s="40"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="46"/>
       <c r="Q28" s="41"/>
       <c r="R28" s="41"/>
       <c r="S28" s="41"/>
@@ -2846,21 +4200,21 @@
       <c r="B29" s="17" t="str">
         <v>Few_indicators_SPI_preferred_90</v>
       </c>
-      <c r="C29" s="39" t="s">
+      <c r="C29" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="40"/>
-      <c r="M29" s="40"/>
-      <c r="N29" s="40"/>
-      <c r="O29" s="40"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="46"/>
+      <c r="J29" s="46"/>
+      <c r="K29" s="46"/>
+      <c r="L29" s="46"/>
+      <c r="M29" s="46"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="46"/>
       <c r="Q29" s="41"/>
       <c r="R29" s="41"/>
       <c r="S29" s="41"/>
@@ -2896,21 +4250,21 @@
       <c r="B30" s="17" t="str">
         <v>Few_indicators_closeDLS_subPrimSchool</v>
       </c>
-      <c r="C30" s="44" t="s">
+      <c r="C30" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="40"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="40"/>
-      <c r="M30" s="40"/>
-      <c r="N30" s="40"/>
-      <c r="O30" s="40"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
+      <c r="L30" s="46"/>
+      <c r="M30" s="46"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="46"/>
       <c r="Q30" s="41" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
@@ -2948,21 +4302,21 @@
       <c r="B31" s="17" t="str">
         <v>No_non_DLS_90</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="40"/>
-      <c r="K31" s="40"/>
-      <c r="L31" s="40"/>
-      <c r="M31" s="40"/>
-      <c r="N31" s="40"/>
-      <c r="O31" s="40"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
       <c r="Q31" s="41"/>
       <c r="R31" s="41"/>
       <c r="S31" s="41"/>
@@ -2998,21 +4352,21 @@
       <c r="B32" s="17" t="str">
         <v>Few_Indicators_subWatSani</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="39"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="40"/>
-      <c r="K32" s="40"/>
-      <c r="L32" s="40"/>
-      <c r="M32" s="40"/>
-      <c r="N32" s="40"/>
-      <c r="O32" s="40"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="46"/>
+      <c r="J32" s="46"/>
+      <c r="K32" s="46"/>
+      <c r="L32" s="46"/>
+      <c r="M32" s="46"/>
+      <c r="N32" s="46"/>
+      <c r="O32" s="46"/>
       <c r="Q32" s="41"/>
       <c r="R32" s="41"/>
       <c r="S32" s="41"/>
@@ -3058,13 +4412,13 @@
       <c r="F33" s="45"/>
       <c r="G33" s="45"/>
       <c r="H33" s="45"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="42"/>
-      <c r="K33" s="42"/>
-      <c r="L33" s="42"/>
-      <c r="M33" s="42"/>
-      <c r="N33" s="42"/>
-      <c r="O33" s="42"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="43"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
       <c r="Q33" s="41"/>
       <c r="R33" s="41"/>
       <c r="S33" s="41"/>
@@ -3097,19 +4451,19 @@
       <c r="B34" s="6" t="str">
         <v>Baseline</v>
       </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="42"/>
-      <c r="J34" s="42"/>
-      <c r="K34" s="42"/>
-      <c r="L34" s="42"/>
-      <c r="M34" s="42"/>
-      <c r="N34" s="42"/>
-      <c r="O34" s="42"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
+      <c r="L34" s="43"/>
+      <c r="M34" s="43"/>
+      <c r="N34" s="43"/>
+      <c r="O34" s="43"/>
       <c r="Q34" s="41"/>
       <c r="R34" s="41"/>
       <c r="S34" s="41"/>
@@ -3142,21 +4496,21 @@
       <c r="B35" s="6" t="str">
         <v>No_nonDLS_limExt</v>
       </c>
-      <c r="C35" s="42"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="42"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="42" t="s">
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="J35" s="42"/>
-      <c r="K35" s="42"/>
-      <c r="L35" s="42"/>
-      <c r="M35" s="42"/>
-      <c r="N35" s="42"/>
-      <c r="O35" s="42"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+      <c r="L35" s="43"/>
+      <c r="M35" s="43"/>
+      <c r="N35" s="43"/>
+      <c r="O35" s="43"/>
       <c r="Q35" s="41"/>
       <c r="R35" s="41"/>
       <c r="S35" s="41"/>
@@ -3189,21 +4543,21 @@
       <c r="B36" s="6" t="str">
         <v>BHN</v>
       </c>
-      <c r="C36" s="46" t="s">
+      <c r="C36" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+      <c r="L36" s="43"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
+      <c r="O36" s="43"/>
       <c r="Q36" s="41"/>
       <c r="R36" s="41"/>
       <c r="S36" s="41"/>
@@ -3542,6 +4896,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="I24:O24"/>
+    <mergeCell ref="I25:O25"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I21:O21"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="I22:O22"/>
+    <mergeCell ref="I23:O23"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="I28:O28"/>
+    <mergeCell ref="I29:O29"/>
+    <mergeCell ref="AR22:AY24"/>
+    <mergeCell ref="Q30:AA36"/>
+    <mergeCell ref="AB32:AQ41"/>
+    <mergeCell ref="I26:O26"/>
+    <mergeCell ref="I27:O27"/>
+    <mergeCell ref="I32:O32"/>
+    <mergeCell ref="I33:O33"/>
+    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="AB22:AQ27"/>
+    <mergeCell ref="Q22:AA25"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C26:H26"/>
     <mergeCell ref="T4:X4"/>
     <mergeCell ref="AB42:AQ53"/>
     <mergeCell ref="C30:H30"/>
@@ -3558,33 +4939,6 @@
     <mergeCell ref="I31:O31"/>
     <mergeCell ref="C36:H36"/>
     <mergeCell ref="I36:O36"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="I28:O28"/>
-    <mergeCell ref="I29:O29"/>
-    <mergeCell ref="AR22:AY24"/>
-    <mergeCell ref="Q30:AA36"/>
-    <mergeCell ref="AB32:AQ41"/>
-    <mergeCell ref="I26:O26"/>
-    <mergeCell ref="I27:O27"/>
-    <mergeCell ref="I32:O32"/>
-    <mergeCell ref="I33:O33"/>
-    <mergeCell ref="I34:O34"/>
-    <mergeCell ref="AB22:AQ27"/>
-    <mergeCell ref="Q22:AA25"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="I24:O24"/>
-    <mergeCell ref="I25:O25"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I21:O21"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C23:H23"/>
-    <mergeCell ref="I22:O22"/>
-    <mergeCell ref="I23:O23"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="C21:H21"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:Q15">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
@@ -3618,14 +4972,14 @@
       <c r="B3" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="35"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="52"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
@@ -3695,13 +5049,13 @@
       <c r="S4" s="29" t="str">
         <v>All_indicators</v>
       </c>
-      <c r="T4" s="43" t="s">
+      <c r="T4" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="U4" s="43"/>
-      <c r="V4" s="43"/>
-      <c r="W4" s="43"/>
-      <c r="X4" s="43"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="40"/>
+      <c r="W4" s="40"/>
+      <c r="X4" s="40"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="str" cm="1">
@@ -4756,23 +6110,23 @@
       <c r="B21" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36" t="s">
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="53"/>
       <c r="Q21" s="1" t="s">
         <v>58</v>
       </c>
@@ -4788,21 +6142,21 @@
         <f t="array" ref="B22:B38">TRANSPOSE(_xlfn.ANCHORARRAY(C4))</f>
         <v>BHN_FWB</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C22" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
-      <c r="O22" s="33"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="48"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="48"/>
+      <c r="O22" s="48"/>
       <c r="Q22" s="41" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
@@ -4852,21 +6206,21 @@
       <c r="B23" s="26" t="str">
         <v>BHN_FWB_AllExt</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="C23" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="33"/>
-      <c r="N23" s="33"/>
-      <c r="O23" s="33"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="48"/>
+      <c r="M23" s="48"/>
+      <c r="N23" s="48"/>
+      <c r="O23" s="48"/>
       <c r="Q23" s="41"/>
       <c r="R23" s="41"/>
       <c r="S23" s="41"/>
@@ -4910,21 +6264,21 @@
       <c r="B24" s="7" t="str">
         <v>Few_indicators_closest_DLS_coverage</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="49"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="48"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="48"/>
+      <c r="O24" s="48"/>
       <c r="Q24" s="41"/>
       <c r="R24" s="41"/>
       <c r="S24" s="41"/>
@@ -4968,21 +6322,21 @@
       <c r="B25" s="7" t="str">
         <v>Few_indicators_SPI_preferred</v>
       </c>
-      <c r="C25" s="37" t="s">
+      <c r="C25" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="33"/>
-      <c r="N25" s="33"/>
-      <c r="O25" s="33"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="48"/>
+      <c r="L25" s="48"/>
+      <c r="M25" s="48"/>
+      <c r="N25" s="48"/>
+      <c r="O25" s="48"/>
       <c r="AB25" s="41"/>
       <c r="AC25" s="41"/>
       <c r="AD25" s="41"/>
@@ -5007,21 +6361,21 @@
       <c r="B26" s="7" t="str">
         <v>No_non_DLS</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33"/>
-      <c r="O26" s="33"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="48"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="48"/>
+      <c r="O26" s="48"/>
       <c r="Q26" s="41"/>
       <c r="R26" s="41"/>
       <c r="S26" s="41"/>
@@ -5057,21 +6411,21 @@
       <c r="B27" s="26" t="str">
         <v>Only_%_of_pop</v>
       </c>
-      <c r="C27" s="51" t="s">
+      <c r="C27" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="33"/>
-      <c r="O27" s="33"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="55"/>
+      <c r="H27" s="55"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="48"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="48"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="48"/>
+      <c r="O27" s="48"/>
       <c r="Q27" s="41"/>
       <c r="R27" s="41"/>
       <c r="S27" s="41"/>
@@ -5107,21 +6461,21 @@
       <c r="B28" s="17" t="str">
         <v>Few_indicators_closest_DLS_coverage_90</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="40"/>
-      <c r="M28" s="40"/>
-      <c r="N28" s="40"/>
-      <c r="O28" s="40"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="46"/>
       <c r="Q28" s="41"/>
       <c r="R28" s="41"/>
       <c r="S28" s="41"/>
@@ -5157,21 +6511,21 @@
       <c r="B29" s="17" t="str">
         <v>Few_indicators_SPI_preferred_90</v>
       </c>
-      <c r="C29" s="39" t="s">
+      <c r="C29" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="40"/>
-      <c r="M29" s="40"/>
-      <c r="N29" s="40"/>
-      <c r="O29" s="40"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="46"/>
+      <c r="J29" s="46"/>
+      <c r="K29" s="46"/>
+      <c r="L29" s="46"/>
+      <c r="M29" s="46"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="46"/>
       <c r="Q29" s="41"/>
       <c r="R29" s="41"/>
       <c r="S29" s="41"/>
@@ -5207,21 +6561,21 @@
       <c r="B30" s="17" t="str">
         <v>Few_indicators_closeDLS_subPrimSchool</v>
       </c>
-      <c r="C30" s="44" t="s">
+      <c r="C30" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="40"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="40"/>
-      <c r="M30" s="40"/>
-      <c r="N30" s="40"/>
-      <c r="O30" s="40"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
+      <c r="L30" s="46"/>
+      <c r="M30" s="46"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="46"/>
       <c r="Q30" s="41"/>
       <c r="R30" s="41"/>
       <c r="S30" s="41"/>
@@ -5257,23 +6611,23 @@
       <c r="B31" s="27" t="str">
         <v>No_non_DLS_90</v>
       </c>
-      <c r="C31" s="47" t="s">
+      <c r="C31" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="47" t="s">
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="J31" s="47"/>
-      <c r="K31" s="47"/>
-      <c r="L31" s="47"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="47"/>
-      <c r="O31" s="47"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="58"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="58"/>
+      <c r="O31" s="58"/>
       <c r="Q31" s="41"/>
       <c r="R31" s="41"/>
       <c r="S31" s="41"/>
@@ -5309,21 +6663,21 @@
       <c r="B32" s="27" t="str">
         <v>Few_Indicators_subWatSani</v>
       </c>
-      <c r="C32" s="47" t="s">
+      <c r="C32" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="47"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="40"/>
-      <c r="K32" s="40"/>
-      <c r="L32" s="40"/>
-      <c r="M32" s="40"/>
-      <c r="N32" s="40"/>
-      <c r="O32" s="40"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="58"/>
+      <c r="H32" s="58"/>
+      <c r="I32" s="46"/>
+      <c r="J32" s="46"/>
+      <c r="K32" s="46"/>
+      <c r="L32" s="46"/>
+      <c r="M32" s="46"/>
+      <c r="N32" s="46"/>
+      <c r="O32" s="46"/>
       <c r="Q32" s="41"/>
       <c r="R32" s="41"/>
       <c r="S32" s="41"/>
@@ -5359,21 +6713,21 @@
       <c r="B33" s="28" t="str">
         <v>Only_OPP</v>
       </c>
-      <c r="C33" s="48" t="s">
+      <c r="C33" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="42"/>
-      <c r="K33" s="42"/>
-      <c r="L33" s="42"/>
-      <c r="M33" s="42"/>
-      <c r="N33" s="42"/>
-      <c r="O33" s="42"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="59"/>
+      <c r="H33" s="59"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="43"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
       <c r="Q33" s="41"/>
       <c r="R33" s="41"/>
       <c r="S33" s="41"/>
@@ -5406,19 +6760,19 @@
       <c r="B34" s="6" t="str">
         <v>Baseline</v>
       </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="42"/>
-      <c r="J34" s="42"/>
-      <c r="K34" s="42"/>
-      <c r="L34" s="42"/>
-      <c r="M34" s="42"/>
-      <c r="N34" s="42"/>
-      <c r="O34" s="42"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
+      <c r="L34" s="43"/>
+      <c r="M34" s="43"/>
+      <c r="N34" s="43"/>
+      <c r="O34" s="43"/>
       <c r="Q34" s="41"/>
       <c r="R34" s="41"/>
       <c r="S34" s="41"/>
@@ -5451,21 +6805,21 @@
       <c r="B35" s="28" t="str">
         <v>No_nonDLS_limExt</v>
       </c>
-      <c r="C35" s="49"/>
-      <c r="D35" s="49"/>
-      <c r="E35" s="49"/>
-      <c r="F35" s="49"/>
-      <c r="G35" s="49"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="49" t="s">
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56" t="s">
         <v>71</v>
       </c>
-      <c r="J35" s="49"/>
-      <c r="K35" s="49"/>
-      <c r="L35" s="49"/>
-      <c r="M35" s="49"/>
-      <c r="N35" s="49"/>
-      <c r="O35" s="49"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="56"/>
+      <c r="N35" s="56"/>
+      <c r="O35" s="56"/>
       <c r="Q35" s="41"/>
       <c r="R35" s="41"/>
       <c r="S35" s="41"/>
@@ -5498,21 +6852,21 @@
       <c r="B36" s="6" t="str">
         <v>BHN</v>
       </c>
-      <c r="C36" s="46" t="s">
+      <c r="C36" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+      <c r="L36" s="43"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
+      <c r="O36" s="43"/>
       <c r="Q36" s="41"/>
       <c r="R36" s="41"/>
       <c r="S36" s="41"/>
@@ -5857,16 +7211,22 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="I27:O27"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="I28:O28"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="I21:O21"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="I22:O22"/>
+    <mergeCell ref="AB42:AQ53"/>
+    <mergeCell ref="T4:X4"/>
+    <mergeCell ref="AB32:AQ41"/>
+    <mergeCell ref="Q30:AA36"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="C29:H29"/>
+    <mergeCell ref="I29:O29"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="I30:O30"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="I31:O31"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="I32:O32"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="I33:O33"/>
     <mergeCell ref="C34:H34"/>
     <mergeCell ref="I34:O34"/>
     <mergeCell ref="C35:H35"/>
@@ -5883,22 +7243,16 @@
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="I26:O26"/>
     <mergeCell ref="Q26:AA29"/>
-    <mergeCell ref="AB42:AQ53"/>
-    <mergeCell ref="T4:X4"/>
-    <mergeCell ref="AB32:AQ41"/>
-    <mergeCell ref="Q30:AA36"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="I36:O36"/>
-    <mergeCell ref="C29:H29"/>
-    <mergeCell ref="I29:O29"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="I30:O30"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="I31:O31"/>
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="I32:O32"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="I33:O33"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="I27:O27"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="I28:O28"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="I21:O21"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="I22:O22"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:S15">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
@@ -9722,14 +11076,16 @@
   <sheetPr>
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A3:D67"/>
+  <dimension ref="A3:F67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="61.7109375" customWidth="1"/>
     <col min="3" max="3" width="22.140625" customWidth="1"/>
+    <col min="6" max="6" width="24.5703125" customWidth="1"/>
+    <col min="7" max="7" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -9740,7 +11096,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -9751,72 +11107,81 @@
       <c r="C4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F4" s="60"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="str">
         <v>Deaths from infectious diseases (deaths/100,000)</v>
       </c>
       <c r="C5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F5" s="60"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="str">
         <v xml:space="preserve">Maternal mortality  (deaths/100,000 live births) </v>
       </c>
       <c r="C6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F6" s="60"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="str">
         <v xml:space="preserve">Nutritional deficiencies (% of pop.) </v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F7" s="60"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="str">
         <v xml:space="preserve">Diet low in fruits and vegetables (0=low risk; 100=high risk) </v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F8" s="60"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="str">
         <v xml:space="preserve">Child mortality (deaths/1,000 live births) </v>
       </c>
       <c r="C9" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F9" s="60"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="str">
         <v xml:space="preserve">No access to a handwashing facility (0=low risk; 100=high risk) </v>
       </c>
       <c r="C10" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F10" s="60"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="str">
         <v>Deaths from unsafe water, sanitation and hygiene (deaths/100,000)</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F11" s="60"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="str">
         <v xml:space="preserve">Improved sanitation (proportion of pop.) </v>
       </c>
       <c r="C12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F12" s="60"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="str">
         <v xml:space="preserve">Improved water source (proportion of pop.) </v>
       </c>
@@ -9824,7 +11189,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -9835,7 +11200,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="str">
         <v xml:space="preserve">Prevalence of cooking with coal/biomass (proportion of pop.) </v>
       </c>
@@ -9843,7 +11208,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="str">
         <v xml:space="preserve">Access to electricity (% of pop.) </v>
       </c>
@@ -10280,45 +11645,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="127.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="G1" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="54" t="s">
+      <c r="H1" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="I1" s="54" t="s">
+      <c r="I1" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="J1" s="54" t="s">
+      <c r="J1" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="K1" s="54" t="s">
+      <c r="K1" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="P1" s="52"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="P1" s="32"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="36" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="31">
@@ -10353,7 +11718,7 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="36" t="s">
         <v>25</v>
       </c>
       <c r="B3" s="31">
@@ -10388,7 +11753,7 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="36" t="s">
         <v>22</v>
       </c>
       <c r="B4" s="31">
@@ -10423,7 +11788,7 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="36" t="s">
         <v>24</v>
       </c>
       <c r="B5" s="31">
@@ -10462,7 +11827,7 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="36" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="31">
@@ -10500,7 +11865,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="56" t="s">
+      <c r="A7" s="36" t="s">
         <v>20</v>
       </c>
       <c r="B7" s="31">
@@ -10538,7 +11903,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="36" t="s">
         <v>23</v>
       </c>
       <c r="B8" s="31">
@@ -10576,7 +11941,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="56" t="s">
+      <c r="A9" s="36" t="s">
         <v>26</v>
       </c>
       <c r="B9" s="31">
@@ -10614,7 +11979,7 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="56" t="s">
+      <c r="A10" s="36" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="31">
@@ -10652,37 +12017,37 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="56" t="s">
+      <c r="A11" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="59">
-        <v>0</v>
-      </c>
-      <c r="C11" s="59">
-        <v>0</v>
-      </c>
-      <c r="D11" s="59">
-        <v>0</v>
-      </c>
-      <c r="E11" s="59">
-        <v>0</v>
-      </c>
-      <c r="F11" s="59">
-        <v>0</v>
-      </c>
-      <c r="G11" s="59">
-        <v>0</v>
-      </c>
-      <c r="H11" s="59">
-        <v>0</v>
-      </c>
-      <c r="I11" s="59">
-        <v>0</v>
-      </c>
-      <c r="J11" s="59">
-        <v>0</v>
-      </c>
-      <c r="K11" s="59">
+      <c r="B11" s="31">
+        <v>0</v>
+      </c>
+      <c r="C11" s="31">
+        <v>0</v>
+      </c>
+      <c r="D11" s="31">
+        <v>0</v>
+      </c>
+      <c r="E11" s="31">
+        <v>0</v>
+      </c>
+      <c r="F11" s="31">
+        <v>0</v>
+      </c>
+      <c r="G11" s="31">
+        <v>0</v>
+      </c>
+      <c r="H11" s="31">
+        <v>0</v>
+      </c>
+      <c r="I11" s="31">
+        <v>0</v>
+      </c>
+      <c r="J11" s="31">
+        <v>0</v>
+      </c>
+      <c r="K11" s="31">
         <v>0</v>
       </c>
       <c r="P11" t="str">
@@ -10690,37 +12055,37 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="57" t="s">
+      <c r="A12" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="53">
+      <c r="B12" s="33">
         <v>24</v>
       </c>
-      <c r="C12" s="53">
+      <c r="C12" s="33">
         <v>9</v>
       </c>
-      <c r="D12" s="53">
+      <c r="D12" s="33">
         <v>25</v>
       </c>
-      <c r="E12" s="53">
-        <v>0</v>
-      </c>
-      <c r="F12" s="53">
-        <v>0</v>
-      </c>
-      <c r="G12" s="53">
-        <v>0</v>
-      </c>
-      <c r="H12" s="53">
-        <v>0</v>
-      </c>
-      <c r="I12" s="53">
-        <v>0</v>
-      </c>
-      <c r="J12" s="53">
-        <v>0</v>
-      </c>
-      <c r="K12" s="53">
+      <c r="E12" s="33">
+        <v>0</v>
+      </c>
+      <c r="F12" s="33">
+        <v>0</v>
+      </c>
+      <c r="G12" s="33">
+        <v>0</v>
+      </c>
+      <c r="H12" s="33">
+        <v>0</v>
+      </c>
+      <c r="I12" s="33">
+        <v>0</v>
+      </c>
+      <c r="J12" s="33">
+        <v>0</v>
+      </c>
+      <c r="K12" s="33">
         <v>0</v>
       </c>
       <c r="P12" t="str">
@@ -10728,37 +12093,37 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="58" t="s">
+      <c r="A13" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="60">
+      <c r="B13" s="39">
         <v>52</v>
       </c>
-      <c r="C13" s="60">
+      <c r="C13" s="39">
         <v>33</v>
       </c>
-      <c r="D13" s="60">
+      <c r="D13" s="39">
         <v>62</v>
       </c>
-      <c r="E13" s="60">
+      <c r="E13" s="39">
         <v>37</v>
       </c>
-      <c r="F13" s="60">
+      <c r="F13" s="39">
         <v>29</v>
       </c>
-      <c r="G13" s="60">
+      <c r="G13" s="39">
         <v>33</v>
       </c>
-      <c r="H13" s="60">
+      <c r="H13" s="39">
         <v>11</v>
       </c>
-      <c r="I13" s="60">
+      <c r="I13" s="39">
         <v>11</v>
       </c>
-      <c r="J13" s="60">
+      <c r="J13" s="39">
         <v>11</v>
       </c>
-      <c r="K13" s="60">
+      <c r="K13" s="39">
         <v>11</v>
       </c>
       <c r="P13" t="str">
@@ -10766,7 +12131,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="36" t="s">
         <v>34</v>
       </c>
       <c r="B14" s="31">
@@ -10804,7 +12169,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="56" t="s">
+      <c r="A15" s="36" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="31">
@@ -10859,4 +12224,1262 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C45A346D-1A16-4F68-93D6-C1A89543708A}">
+  <dimension ref="A1:H72"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" style="31" customWidth="1"/>
+    <col min="3" max="3" width="71" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" style="31" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>98</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" s="66" t="s">
+        <v>161</v>
+      </c>
+      <c r="G1" s="61" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="69">
+        <v>1</v>
+      </c>
+      <c r="B2" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="70" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="71" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2" s="71" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2" s="78" t="s">
+        <v>162</v>
+      </c>
+      <c r="G2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H2" s="67" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="69">
+        <v>2</v>
+      </c>
+      <c r="B3" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="70" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" s="71" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="78" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="72">
+        <v>3</v>
+      </c>
+      <c r="B4" s="73" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="74" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="79" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="72"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="71" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="79"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="72"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="71" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="79"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="72"/>
+      <c r="B7" s="73"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="71" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="71" t="s">
+        <v>146</v>
+      </c>
+      <c r="F7" s="79"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="72"/>
+      <c r="B8" s="73"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="71" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" s="71" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" s="79"/>
+    </row>
+    <row r="9" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="72">
+        <v>4</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="74" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" s="71" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F9" s="79" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="72"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F10" s="79"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="72"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="71" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" s="71" t="s">
+        <v>158</v>
+      </c>
+      <c r="F11" s="79"/>
+      <c r="G11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="72">
+        <v>5</v>
+      </c>
+      <c r="B12" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="74" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="71" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F12" s="79" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="72"/>
+      <c r="B13" s="73"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="71" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F13" s="79"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="72"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="E14" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F14" s="79"/>
+    </row>
+    <row r="15" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="72"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="71" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="71" t="s">
+        <v>155</v>
+      </c>
+      <c r="F15" s="79"/>
+      <c r="G15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="72">
+        <v>6</v>
+      </c>
+      <c r="B16" s="73" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="74" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="71" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F16" s="79" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="72"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="74"/>
+      <c r="D17" s="71" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="71" t="s">
+        <v>155</v>
+      </c>
+      <c r="F17" s="79"/>
+      <c r="G17" s="77" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="72">
+        <v>7</v>
+      </c>
+      <c r="B18" s="73" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="71" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F18" s="79" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="72"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="71" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F19" s="79"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="72"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="71" t="s">
+        <v>116</v>
+      </c>
+      <c r="E20" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F20" s="79"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="72"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="71" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F21" s="79"/>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="72"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="71" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" s="71" t="s">
+        <v>160</v>
+      </c>
+      <c r="F22" s="79"/>
+      <c r="G22" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="72"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="71" t="s">
+        <v>119</v>
+      </c>
+      <c r="E23" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F23" s="79"/>
+    </row>
+    <row r="24" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="72"/>
+      <c r="B24" s="73"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="71" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F24" s="79"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="72"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="71" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F25" s="79"/>
+    </row>
+    <row r="26" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="72"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="74"/>
+      <c r="D26" s="71" t="s">
+        <v>122</v>
+      </c>
+      <c r="E26" s="71" t="s">
+        <v>147</v>
+      </c>
+      <c r="F26" s="79"/>
+      <c r="G26" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="72"/>
+      <c r="B27" s="73"/>
+      <c r="C27" s="74"/>
+      <c r="D27" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="E27" s="71" t="s">
+        <v>147</v>
+      </c>
+      <c r="F27" s="79"/>
+      <c r="G27" s="76" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="72">
+        <v>8</v>
+      </c>
+      <c r="B28" s="73" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="74" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" s="71" t="s">
+        <v>124</v>
+      </c>
+      <c r="E28" s="71" t="s">
+        <v>148</v>
+      </c>
+      <c r="F28" s="79" t="s">
+        <v>163</v>
+      </c>
+      <c r="G28" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="72"/>
+      <c r="B29" s="73"/>
+      <c r="C29" s="74"/>
+      <c r="D29" s="71" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F29" s="79"/>
+    </row>
+    <row r="30" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="72"/>
+      <c r="B30" s="73"/>
+      <c r="C30" s="74"/>
+      <c r="D30" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="E30" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F30" s="79"/>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="72"/>
+      <c r="B31" s="73"/>
+      <c r="C31" s="74"/>
+      <c r="D31" s="71" t="s">
+        <v>127</v>
+      </c>
+      <c r="E31" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F31" s="79"/>
+    </row>
+    <row r="32" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="72"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="74"/>
+      <c r="D32" s="71" t="s">
+        <v>128</v>
+      </c>
+      <c r="E32" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F32" s="79"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="72"/>
+      <c r="B33" s="73"/>
+      <c r="C33" s="74"/>
+      <c r="D33" s="71" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F33" s="79"/>
+    </row>
+    <row r="34" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="72"/>
+      <c r="B34" s="73"/>
+      <c r="C34" s="74"/>
+      <c r="D34" s="71" t="s">
+        <v>130</v>
+      </c>
+      <c r="E34" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F34" s="79"/>
+    </row>
+    <row r="35" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="72"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="74"/>
+      <c r="D35" s="71" t="s">
+        <v>131</v>
+      </c>
+      <c r="E35" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F35" s="79"/>
+    </row>
+    <row r="36" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="72">
+        <v>9</v>
+      </c>
+      <c r="B36" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36" s="74" t="s">
+        <v>137</v>
+      </c>
+      <c r="D36" s="71" t="s">
+        <v>132</v>
+      </c>
+      <c r="E36" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F36" s="79" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="72"/>
+      <c r="B37" s="73"/>
+      <c r="C37" s="74"/>
+      <c r="D37" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="E37" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F37" s="79"/>
+    </row>
+    <row r="38" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A38" s="72"/>
+      <c r="B38" s="73"/>
+      <c r="C38" s="74"/>
+      <c r="D38" s="71" t="s">
+        <v>134</v>
+      </c>
+      <c r="E38" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="F38" s="79"/>
+    </row>
+    <row r="39" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A39" s="69">
+        <v>10</v>
+      </c>
+      <c r="B39" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39" s="75"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="80" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E40" s="62"/>
+      <c r="F40" s="78"/>
+    </row>
+    <row r="41" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D41" s="63"/>
+      <c r="E41" s="62"/>
+      <c r="F41" s="78"/>
+    </row>
+    <row r="42" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D42" s="63"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="78"/>
+    </row>
+    <row r="43" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D43" s="63"/>
+      <c r="E43" s="62"/>
+      <c r="F43" s="78"/>
+    </row>
+    <row r="44" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D44" s="63"/>
+      <c r="E44" s="62"/>
+      <c r="F44" s="78"/>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E45" s="62"/>
+      <c r="F45" s="78"/>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E46" s="62"/>
+      <c r="F46" s="78"/>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E47" s="62"/>
+      <c r="F47" s="78"/>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E48" s="62"/>
+      <c r="F48" s="78"/>
+    </row>
+    <row r="49" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E49" s="62"/>
+      <c r="F49" s="78"/>
+    </row>
+    <row r="50" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E50" s="62"/>
+      <c r="F50" s="78"/>
+    </row>
+    <row r="51" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E51" s="62"/>
+      <c r="F51" s="78"/>
+    </row>
+    <row r="52" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E52" s="62"/>
+      <c r="F52" s="78"/>
+    </row>
+    <row r="53" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E53" s="62"/>
+      <c r="F53" s="78"/>
+    </row>
+    <row r="54" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E54" s="62"/>
+      <c r="F54" s="78"/>
+    </row>
+    <row r="55" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E55" s="62"/>
+      <c r="F55" s="78"/>
+    </row>
+    <row r="56" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E56" s="62"/>
+      <c r="F56" s="78"/>
+    </row>
+    <row r="57" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E57" s="62"/>
+      <c r="F57" s="78"/>
+    </row>
+    <row r="58" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E58" s="62"/>
+      <c r="F58" s="78"/>
+    </row>
+    <row r="59" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E59" s="62"/>
+      <c r="F59" s="78"/>
+    </row>
+    <row r="60" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E60" s="62"/>
+      <c r="F60" s="78"/>
+    </row>
+    <row r="61" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E61" s="62"/>
+      <c r="F61" s="78"/>
+    </row>
+    <row r="62" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E62" s="62"/>
+      <c r="F62" s="78"/>
+    </row>
+    <row r="63" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E63" s="62"/>
+      <c r="F63" s="78"/>
+    </row>
+    <row r="64" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E64" s="62"/>
+      <c r="F64" s="78"/>
+    </row>
+    <row r="65" spans="4:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E65" s="62"/>
+      <c r="F65" s="78"/>
+    </row>
+    <row r="66" spans="4:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E66" s="62"/>
+      <c r="F66" s="78"/>
+    </row>
+    <row r="67" spans="4:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E67" s="62"/>
+      <c r="F67" s="78"/>
+    </row>
+    <row r="68" spans="4:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E68" s="62"/>
+      <c r="F68" s="78"/>
+    </row>
+    <row r="69" spans="4:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E69" s="62"/>
+      <c r="F69" s="78"/>
+    </row>
+    <row r="70" spans="4:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E70" s="62"/>
+      <c r="F70" s="78"/>
+    </row>
+    <row r="71" spans="4:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E71" s="62"/>
+      <c r="F71" s="78"/>
+    </row>
+    <row r="72" spans="4:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D72" s="64"/>
+      <c r="E72" s="65"/>
+      <c r="F72" s="78"/>
+    </row>
+  </sheetData>
+  <mergeCells count="28">
+    <mergeCell ref="F4:F8"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="F36:F38"/>
+    <mergeCell ref="F28:F35"/>
+    <mergeCell ref="F18:F27"/>
+    <mergeCell ref="C28:C35"/>
+    <mergeCell ref="B28:B35"/>
+    <mergeCell ref="A28:A35"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="C18:C27"/>
+    <mergeCell ref="B18:B27"/>
+    <mergeCell ref="A18:A27"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="G27" r:id="rId1" xr:uid="{8F82EA5A-B040-442D-8D33-D437ACD7D892}"/>
+    <hyperlink ref="G17" r:id="rId2" xr:uid="{EDA6AEEC-14A3-4778-9A3E-A0590D612609}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{004663A5-903D-4F33-9CF8-4B48BA1B1476}">
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="85" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" s="86" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="86" t="s">
+        <v>168</v>
+      </c>
+      <c r="D1" s="86" t="s">
+        <v>169</v>
+      </c>
+      <c r="E1" s="87" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="22.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="96" t="s">
+        <v>171</v>
+      </c>
+      <c r="B2" s="81" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="99" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2" s="81"/>
+      <c r="E2" s="88"/>
+    </row>
+    <row r="3" spans="1:5" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="97"/>
+      <c r="B3" s="81" t="s">
+        <v>174</v>
+      </c>
+      <c r="C3" s="100"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="88"/>
+    </row>
+    <row r="4" spans="1:5" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="98"/>
+      <c r="B4" s="81" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" s="101"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="88"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="95" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="81" t="s">
+        <v>177</v>
+      </c>
+      <c r="C5" s="102" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" s="82"/>
+      <c r="E5" s="89"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="97"/>
+      <c r="B6" s="81" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="103"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="88"/>
+    </row>
+    <row r="7" spans="1:5" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="98"/>
+      <c r="B7" s="81" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="104"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="88"/>
+    </row>
+    <row r="8" spans="1:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="95" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="81" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" s="102" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="82"/>
+      <c r="E8" s="89"/>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="97"/>
+      <c r="B9" s="105" t="s">
+        <v>182</v>
+      </c>
+      <c r="C9" s="104"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="89"/>
+    </row>
+    <row r="10" spans="1:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="97"/>
+      <c r="B10" s="106"/>
+      <c r="C10" s="82" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="82"/>
+      <c r="E10" s="89"/>
+    </row>
+    <row r="11" spans="1:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="97"/>
+      <c r="B11" s="106"/>
+      <c r="C11" s="82" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="82"/>
+      <c r="E11" s="89"/>
+    </row>
+    <row r="12" spans="1:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="97"/>
+      <c r="B12" s="106"/>
+      <c r="C12" s="82" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="82"/>
+      <c r="E12" s="89"/>
+    </row>
+    <row r="13" spans="1:5" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="98"/>
+      <c r="B13" s="107"/>
+      <c r="C13" s="82" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="82"/>
+      <c r="E13" s="89"/>
+    </row>
+    <row r="14" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="95" t="s">
+        <v>183</v>
+      </c>
+      <c r="B14" s="105" t="s">
+        <v>184</v>
+      </c>
+      <c r="C14" s="82" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" s="82"/>
+      <c r="E14" s="89"/>
+    </row>
+    <row r="15" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="97"/>
+      <c r="B15" s="106"/>
+      <c r="C15" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="82"/>
+      <c r="E15" s="89"/>
+    </row>
+    <row r="16" spans="1:5" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="97"/>
+      <c r="B16" s="107"/>
+      <c r="C16" s="82" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="82"/>
+      <c r="E16" s="89"/>
+    </row>
+    <row r="17" spans="1:5" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="98"/>
+      <c r="B17" s="81" t="s">
+        <v>185</v>
+      </c>
+      <c r="C17" s="82"/>
+      <c r="D17" s="82"/>
+      <c r="E17" s="89"/>
+    </row>
+    <row r="18" spans="1:5" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="95" t="s">
+        <v>186</v>
+      </c>
+      <c r="B18" s="105" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18" s="82" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="82"/>
+      <c r="E18" s="89"/>
+    </row>
+    <row r="19" spans="1:5" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="97"/>
+      <c r="B19" s="106"/>
+      <c r="C19" s="82" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="82"/>
+      <c r="E19" s="89"/>
+    </row>
+    <row r="20" spans="1:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="97"/>
+      <c r="B20" s="106"/>
+      <c r="C20" s="82" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="82"/>
+      <c r="E20" s="89"/>
+    </row>
+    <row r="21" spans="1:5" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="98"/>
+      <c r="B21" s="107"/>
+      <c r="C21" s="82" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" s="82"/>
+      <c r="E21" s="89"/>
+    </row>
+    <row r="22" spans="1:5" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="108" t="s">
+        <v>188</v>
+      </c>
+      <c r="B22" s="110" t="s">
+        <v>189</v>
+      </c>
+      <c r="C22" s="83" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" s="83"/>
+      <c r="E22" s="90"/>
+    </row>
+    <row r="23" spans="1:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="109"/>
+      <c r="B23" s="111"/>
+      <c r="C23" s="83" t="s">
+        <v>113</v>
+      </c>
+      <c r="D23" s="83"/>
+      <c r="E23" s="90"/>
+    </row>
+    <row r="24" spans="1:5" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="108" t="s">
+        <v>190</v>
+      </c>
+      <c r="B24" s="110"/>
+      <c r="C24" s="83" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" s="83"/>
+      <c r="E24" s="90"/>
+    </row>
+    <row r="25" spans="1:5" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="112"/>
+      <c r="B25" s="113"/>
+      <c r="C25" s="83" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" s="83"/>
+      <c r="E25" s="90"/>
+    </row>
+    <row r="26" spans="1:5" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="112"/>
+      <c r="B26" s="113"/>
+      <c r="C26" s="83" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="83"/>
+      <c r="E26" s="90"/>
+    </row>
+    <row r="27" spans="1:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="112"/>
+      <c r="B27" s="113"/>
+      <c r="C27" s="83" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" s="83"/>
+      <c r="E27" s="90"/>
+    </row>
+    <row r="28" spans="1:5" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="112"/>
+      <c r="B28" s="113"/>
+      <c r="C28" s="83" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="83"/>
+      <c r="E28" s="90"/>
+    </row>
+    <row r="29" spans="1:5" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="112"/>
+      <c r="B29" s="111"/>
+      <c r="C29" s="83" t="s">
+        <v>119</v>
+      </c>
+      <c r="D29" s="83"/>
+      <c r="E29" s="90"/>
+    </row>
+    <row r="30" spans="1:5" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="112"/>
+      <c r="B30" s="110" t="s">
+        <v>191</v>
+      </c>
+      <c r="C30" s="83" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="83"/>
+      <c r="E30" s="90"/>
+    </row>
+    <row r="31" spans="1:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="112"/>
+      <c r="B31" s="113"/>
+      <c r="C31" s="83" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" s="83"/>
+      <c r="E31" s="90"/>
+    </row>
+    <row r="32" spans="1:5" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="112"/>
+      <c r="B32" s="113"/>
+      <c r="C32" s="83" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" s="83"/>
+      <c r="E32" s="90"/>
+    </row>
+    <row r="33" spans="1:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="109"/>
+      <c r="B33" s="111"/>
+      <c r="C33" s="83" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="83"/>
+      <c r="E33" s="90"/>
+    </row>
+    <row r="34" spans="1:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="108" t="s">
+        <v>192</v>
+      </c>
+      <c r="B34" s="110" t="s">
+        <v>181</v>
+      </c>
+      <c r="C34" s="83" t="s">
+        <v>124</v>
+      </c>
+      <c r="D34" s="83"/>
+      <c r="E34" s="90"/>
+    </row>
+    <row r="35" spans="1:5" ht="96.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="112"/>
+      <c r="B35" s="113"/>
+      <c r="C35" s="83" t="s">
+        <v>125</v>
+      </c>
+      <c r="D35" s="83"/>
+      <c r="E35" s="90"/>
+    </row>
+    <row r="36" spans="1:5" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="112"/>
+      <c r="B36" s="111"/>
+      <c r="C36" s="83" t="s">
+        <v>126</v>
+      </c>
+      <c r="D36" s="83"/>
+      <c r="E36" s="90"/>
+    </row>
+    <row r="37" spans="1:5" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="112"/>
+      <c r="B37" s="110" t="s">
+        <v>193</v>
+      </c>
+      <c r="C37" s="83" t="s">
+        <v>127</v>
+      </c>
+      <c r="D37" s="83"/>
+      <c r="E37" s="90"/>
+    </row>
+    <row r="38" spans="1:5" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="112"/>
+      <c r="B38" s="113"/>
+      <c r="C38" s="83" t="s">
+        <v>128</v>
+      </c>
+      <c r="D38" s="83"/>
+      <c r="E38" s="90"/>
+    </row>
+    <row r="39" spans="1:5" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="112"/>
+      <c r="B39" s="111"/>
+      <c r="C39" s="83" t="s">
+        <v>129</v>
+      </c>
+      <c r="D39" s="83"/>
+      <c r="E39" s="90"/>
+    </row>
+    <row r="40" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="109"/>
+      <c r="B40" s="84"/>
+      <c r="C40" s="83" t="s">
+        <v>130</v>
+      </c>
+      <c r="D40" s="83"/>
+      <c r="E40" s="90"/>
+    </row>
+    <row r="41" spans="1:5" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="91"/>
+      <c r="B41" s="84"/>
+      <c r="C41" s="83" t="s">
+        <v>131</v>
+      </c>
+      <c r="D41" s="83"/>
+      <c r="E41" s="90"/>
+    </row>
+    <row r="42" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="108" t="s">
+        <v>194</v>
+      </c>
+      <c r="B42" s="110" t="s">
+        <v>195</v>
+      </c>
+      <c r="C42" s="83" t="s">
+        <v>132</v>
+      </c>
+      <c r="D42" s="83"/>
+      <c r="E42" s="90"/>
+    </row>
+    <row r="43" spans="1:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="112"/>
+      <c r="B43" s="111"/>
+      <c r="C43" s="83" t="s">
+        <v>133</v>
+      </c>
+      <c r="D43" s="83"/>
+      <c r="E43" s="90"/>
+    </row>
+    <row r="44" spans="1:5" ht="96.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="109"/>
+      <c r="B44" s="84" t="s">
+        <v>196</v>
+      </c>
+      <c r="C44" s="83" t="s">
+        <v>134</v>
+      </c>
+      <c r="D44" s="83"/>
+      <c r="E44" s="90"/>
+    </row>
+    <row r="45" spans="1:5" ht="36" x14ac:dyDescent="0.25">
+      <c r="A45" s="92" t="s">
+        <v>197</v>
+      </c>
+      <c r="B45" s="93"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="94"/>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="B24:B29"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A34:A40"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="B9:B13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>